--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB1479D-E5AD-4A4D-BD8E-95B102C1D0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85FAE70-6119-47F0-9041-8862647B3ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45908,7 +45908,7 @@
         <v>503</v>
       </c>
       <c r="K863" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L863" s="60">
         <v>30000</v>
@@ -45958,7 +45958,7 @@
         <v>504</v>
       </c>
       <c r="K864" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L864" s="60">
         <v>30000</v>
@@ -46008,7 +46008,7 @@
         <v>505</v>
       </c>
       <c r="K865" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L865" s="60">
         <v>30000</v>
@@ -46058,7 +46058,7 @@
         <v>506</v>
       </c>
       <c r="K866" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L866" s="60">
         <v>30000</v>
@@ -46108,7 +46108,7 @@
         <v>507</v>
       </c>
       <c r="K867" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L867" s="60">
         <v>30000</v>
@@ -46158,7 +46158,7 @@
         <v>508</v>
       </c>
       <c r="K868" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L868" s="60">
         <v>30000</v>
@@ -46208,7 +46208,7 @@
         <v>506</v>
       </c>
       <c r="K869" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L869" s="60">
         <v>30000</v>
@@ -46258,7 +46258,7 @@
         <v>508</v>
       </c>
       <c r="K870" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L870" s="60">
         <v>30000</v>
@@ -46308,7 +46308,7 @@
         <v>507</v>
       </c>
       <c r="K871" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L871" s="60">
         <v>30000</v>
@@ -46358,7 +46358,7 @@
         <v>509</v>
       </c>
       <c r="K872" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L872" s="60">
         <v>30000</v>
@@ -46408,7 +46408,7 @@
         <v>446</v>
       </c>
       <c r="K873" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L873" s="60">
         <v>30000</v>
@@ -46458,7 +46458,7 @@
         <v>445</v>
       </c>
       <c r="K874" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L874" s="60">
         <v>30000</v>
@@ -46508,7 +46508,7 @@
         <v>444</v>
       </c>
       <c r="K875" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L875" s="60">
         <v>30000</v>
@@ -46558,7 +46558,7 @@
         <v>510</v>
       </c>
       <c r="K876" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L876" s="60">
         <v>30000</v>
@@ -46608,7 +46608,7 @@
         <v>445</v>
       </c>
       <c r="K877" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L877" s="60">
         <v>30000</v>
@@ -46658,7 +46658,7 @@
         <v>444</v>
       </c>
       <c r="K878" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L878" s="60">
         <v>30000</v>
@@ -46708,7 +46708,7 @@
         <v>511</v>
       </c>
       <c r="K879" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L879" s="60">
         <v>30000</v>
@@ -46758,7 +46758,7 @@
         <v>510</v>
       </c>
       <c r="K880" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L880" s="60">
         <v>30000</v>
@@ -46808,7 +46808,7 @@
         <v>510</v>
       </c>
       <c r="K881" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L881" s="60">
         <v>30000</v>
@@ -46858,7 +46858,7 @@
         <v>512</v>
       </c>
       <c r="K882" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L882" s="60">
         <v>30000</v>
@@ -46908,7 +46908,7 @@
         <v>513</v>
       </c>
       <c r="K883" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L883" s="60">
         <v>30000</v>
@@ -46958,7 +46958,7 @@
         <v>510</v>
       </c>
       <c r="K884" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L884" s="60">
         <v>30000</v>
@@ -47008,7 +47008,7 @@
         <v>514</v>
       </c>
       <c r="K885" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L885" s="60">
         <v>30000</v>
@@ -47058,7 +47058,7 @@
         <v>510</v>
       </c>
       <c r="K886" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L886" s="60">
         <v>30000</v>
@@ -47108,7 +47108,7 @@
         <v>515</v>
       </c>
       <c r="K887" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L887" s="60">
         <v>30000</v>
@@ -47158,7 +47158,7 @@
         <v>516</v>
       </c>
       <c r="K888" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L888" s="60">
         <v>30000</v>
@@ -47208,7 +47208,7 @@
         <v>517</v>
       </c>
       <c r="K889" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L889" s="60">
         <v>30000</v>
@@ -47258,7 +47258,7 @@
         <v>513</v>
       </c>
       <c r="K890" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L890" s="60">
         <v>30000</v>
@@ -47308,7 +47308,7 @@
         <v>451</v>
       </c>
       <c r="K891" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L891" s="60">
         <v>30000</v>
@@ -47358,7 +47358,7 @@
         <v>452</v>
       </c>
       <c r="K892" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L892" s="60">
         <v>30000</v>
@@ -47395,7 +47395,7 @@
       <c r="F893" s="62">
         <v>1</v>
       </c>
-      <c r="G893" s="62">
+      <c r="G893" s="60">
         <v>31</v>
       </c>
       <c r="H893" s="62">
@@ -47408,7 +47408,7 @@
         <v>452</v>
       </c>
       <c r="K893" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L893" s="62">
         <v>30000</v>
@@ -47445,7 +47445,7 @@
       <c r="F894" s="62">
         <v>1</v>
       </c>
-      <c r="G894" s="62">
+      <c r="G894" s="60">
         <v>32</v>
       </c>
       <c r="H894" s="62">
@@ -47458,7 +47458,7 @@
         <v>449</v>
       </c>
       <c r="K894" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L894" s="62">
         <v>30000</v>
@@ -47495,7 +47495,7 @@
       <c r="F895" s="62">
         <v>1</v>
       </c>
-      <c r="G895" s="62">
+      <c r="G895" s="60">
         <v>33</v>
       </c>
       <c r="H895" s="62">
@@ -47508,7 +47508,7 @@
         <v>450</v>
       </c>
       <c r="K895" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L895" s="62">
         <v>30000</v>
@@ -47545,7 +47545,7 @@
       <c r="F896" s="62">
         <v>1</v>
       </c>
-      <c r="G896" s="62">
+      <c r="G896" s="60">
         <v>34</v>
       </c>
       <c r="H896" s="62">
@@ -47558,7 +47558,7 @@
         <v>447</v>
       </c>
       <c r="K896" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L896" s="62">
         <v>30000</v>
@@ -47595,7 +47595,7 @@
       <c r="F897" s="62">
         <v>1</v>
       </c>
-      <c r="G897" s="62">
+      <c r="G897" s="60">
         <v>35</v>
       </c>
       <c r="H897" s="62">
@@ -47608,7 +47608,7 @@
         <v>453</v>
       </c>
       <c r="K897" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L897" s="62">
         <v>30000</v>
@@ -47645,7 +47645,7 @@
       <c r="F898" s="62">
         <v>1</v>
       </c>
-      <c r="G898" s="62">
+      <c r="G898" s="60">
         <v>36</v>
       </c>
       <c r="H898" s="62">
@@ -47658,7 +47658,7 @@
         <v>448</v>
       </c>
       <c r="K898" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L898" s="62">
         <v>30000</v>
@@ -47695,7 +47695,7 @@
       <c r="F899" s="62">
         <v>1</v>
       </c>
-      <c r="G899" s="62">
+      <c r="G899" s="60">
         <v>37</v>
       </c>
       <c r="H899" s="62">
@@ -47708,7 +47708,7 @@
         <v>454</v>
       </c>
       <c r="K899" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L899" s="62">
         <v>30000</v>
@@ -47745,7 +47745,7 @@
       <c r="F900" s="62">
         <v>1</v>
       </c>
-      <c r="G900" s="62">
+      <c r="G900" s="60">
         <v>38</v>
       </c>
       <c r="H900" s="62">
@@ -47758,7 +47758,7 @@
         <v>518</v>
       </c>
       <c r="K900" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L900" s="62">
         <v>30000</v>
@@ -47795,7 +47795,7 @@
       <c r="F901" s="62">
         <v>1</v>
       </c>
-      <c r="G901" s="62">
+      <c r="G901" s="60">
         <v>39</v>
       </c>
       <c r="H901" s="62">
@@ -47808,7 +47808,7 @@
         <v>454</v>
       </c>
       <c r="K901" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L901" s="62">
         <v>30000</v>
@@ -47845,7 +47845,7 @@
       <c r="F902" s="62">
         <v>1</v>
       </c>
-      <c r="G902" s="62">
+      <c r="G902" s="60">
         <v>40</v>
       </c>
       <c r="H902" s="62">
@@ -47858,7 +47858,7 @@
         <v>455</v>
       </c>
       <c r="K902" s="60">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L902" s="62">
         <v>30000</v>
@@ -48795,7 +48795,7 @@
       <c r="F921" s="64">
         <v>1</v>
       </c>
-      <c r="G921" s="64">
+      <c r="G921" s="62">
         <v>19</v>
       </c>
       <c r="H921" s="64">
@@ -49145,7 +49145,7 @@
       <c r="F928" s="66">
         <v>1</v>
       </c>
-      <c r="G928" s="66">
+      <c r="G928" s="62">
         <v>26</v>
       </c>
       <c r="H928" s="66">
@@ -49346,7 +49346,7 @@
         <v>1</v>
       </c>
       <c r="G932" s="62">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H932" s="62">
         <v>2000</v>
@@ -49396,7 +49396,7 @@
         <v>1</v>
       </c>
       <c r="G933" s="62">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H933" s="62">
         <v>3000</v>
@@ -49446,7 +49446,7 @@
         <v>1</v>
       </c>
       <c r="G934" s="62">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H934" s="62">
         <v>2000</v>
@@ -49496,7 +49496,7 @@
         <v>1</v>
       </c>
       <c r="G935" s="62">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H935" s="62">
         <v>3000</v>
@@ -49546,7 +49546,7 @@
         <v>1</v>
       </c>
       <c r="G936" s="62">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H936" s="62">
         <v>3000</v>
@@ -49595,8 +49595,8 @@
       <c r="F937" s="66">
         <v>1</v>
       </c>
-      <c r="G937" s="66">
-        <v>37</v>
+      <c r="G937" s="62">
+        <v>35</v>
       </c>
       <c r="H937" s="66">
         <v>2500</v>
@@ -49646,7 +49646,7 @@
         <v>1</v>
       </c>
       <c r="G938" s="62">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H938" s="62">
         <v>7500</v>
@@ -49696,7 +49696,7 @@
         <v>1</v>
       </c>
       <c r="G939" s="62">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H939" s="62">
         <v>2000</v>
@@ -49746,7 +49746,7 @@
         <v>1</v>
       </c>
       <c r="G940" s="62">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H940" s="62">
         <v>3000</v>
@@ -49796,7 +49796,7 @@
         <v>1</v>
       </c>
       <c r="G941" s="62">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H941" s="62">
         <v>3000</v>
@@ -49846,7 +49846,7 @@
         <v>1</v>
       </c>
       <c r="G942" s="62">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H942" s="62">
         <v>3500</v>
@@ -49896,7 +49896,7 @@
         <v>1</v>
       </c>
       <c r="G943" s="62">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H943" s="62">
         <v>2000</v>
@@ -49946,7 +49946,7 @@
         <v>1</v>
       </c>
       <c r="G944" s="62">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H944" s="62">
         <v>3000</v>
@@ -49996,7 +49996,7 @@
         <v>1</v>
       </c>
       <c r="G945" s="62">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H945" s="62">
         <v>3000</v>
@@ -50046,7 +50046,7 @@
         <v>1</v>
       </c>
       <c r="G946" s="62">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H946" s="62">
         <v>3500</v>
@@ -50095,8 +50095,8 @@
       <c r="F947" s="66">
         <v>1</v>
       </c>
-      <c r="G947" s="66">
-        <v>47</v>
+      <c r="G947" s="62">
+        <v>45</v>
       </c>
       <c r="H947" s="66">
         <v>2000</v>
@@ -50146,7 +50146,7 @@
         <v>1</v>
       </c>
       <c r="G948" s="62">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H948" s="62">
         <v>3000</v>
@@ -50196,7 +50196,7 @@
         <v>1</v>
       </c>
       <c r="G949" s="62">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H949" s="62">
         <v>3000</v>
@@ -50246,7 +50246,7 @@
         <v>1</v>
       </c>
       <c r="G950" s="62">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H950" s="62">
         <v>3500</v>
@@ -50296,7 +50296,7 @@
         <v>1</v>
       </c>
       <c r="G951" s="62">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H951" s="62">
         <v>2000</v>
@@ -50346,7 +50346,7 @@
         <v>1</v>
       </c>
       <c r="G952" s="62">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H952" s="62">
         <v>1</v>
@@ -50495,7 +50495,7 @@
       <c r="F955" s="68">
         <v>1</v>
       </c>
-      <c r="G955" s="68">
+      <c r="G955" s="62">
         <v>3</v>
       </c>
       <c r="H955" s="68">
@@ -50546,7 +50546,7 @@
         <v>1</v>
       </c>
       <c r="G956" s="62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H956" s="62">
         <v>3000</v>
@@ -50596,7 +50596,7 @@
         <v>1</v>
       </c>
       <c r="G957" s="62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H957" s="62">
         <v>4500</v>
@@ -50646,7 +50646,7 @@
         <v>1</v>
       </c>
       <c r="G958" s="62">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H958" s="62">
         <v>2500</v>
@@ -50695,8 +50695,8 @@
       <c r="F959" s="66">
         <v>1</v>
       </c>
-      <c r="G959" s="66">
-        <v>8</v>
+      <c r="G959" s="62">
+        <v>7</v>
       </c>
       <c r="H959" s="66">
         <v>4500</v>
@@ -50746,7 +50746,7 @@
         <v>1</v>
       </c>
       <c r="G960" s="62">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H960" s="62">
         <v>8000</v>
@@ -50796,7 +50796,7 @@
         <v>1</v>
       </c>
       <c r="G961" s="62">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H961" s="62">
         <v>2500</v>
@@ -50846,7 +50846,7 @@
         <v>1</v>
       </c>
       <c r="G962" s="62">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H962" s="62">
         <v>3500</v>
@@ -50896,7 +50896,7 @@
         <v>1</v>
       </c>
       <c r="G963" s="62">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H963" s="62">
         <v>2500</v>
@@ -50945,8 +50945,8 @@
       <c r="F964" s="66">
         <v>1</v>
       </c>
-      <c r="G964" s="66">
-        <v>13</v>
+      <c r="G964" s="62">
+        <v>12</v>
       </c>
       <c r="H964" s="66">
         <v>2500</v>
@@ -50996,7 +50996,7 @@
         <v>1</v>
       </c>
       <c r="G965" s="62">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H965" s="62">
         <v>3500</v>
@@ -51046,7 +51046,7 @@
         <v>1</v>
       </c>
       <c r="G966" s="62">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H966" s="62">
         <v>2500</v>
@@ -51146,7 +51146,7 @@
         <v>1</v>
       </c>
       <c r="G968" s="62">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H968" s="62">
         <v>2500</v>
@@ -51295,7 +51295,7 @@
       <c r="F971" s="64">
         <v>1</v>
       </c>
-      <c r="G971" s="64">
+      <c r="G971" s="62">
         <v>19</v>
       </c>
       <c r="H971" s="64">
@@ -51496,7 +51496,7 @@
         <v>1</v>
       </c>
       <c r="G975" s="62">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H975" s="62">
         <v>3500</v>
@@ -51546,7 +51546,7 @@
         <v>1</v>
       </c>
       <c r="G976" s="62">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H976" s="62">
         <v>2000</v>
@@ -51596,7 +51596,7 @@
         <v>1</v>
       </c>
       <c r="G977" s="62">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H977" s="62">
         <v>3000</v>
@@ -51646,7 +51646,7 @@
         <v>1</v>
       </c>
       <c r="G978" s="62">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H978" s="62">
         <v>2000</v>
@@ -51696,7 +51696,7 @@
         <v>1</v>
       </c>
       <c r="G979" s="62">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H979" s="62">
         <v>3000</v>
@@ -51745,8 +51745,8 @@
       <c r="F980" s="66">
         <v>1</v>
       </c>
-      <c r="G980" s="66">
-        <v>26</v>
+      <c r="G980" s="62">
+        <v>28</v>
       </c>
       <c r="H980" s="66">
         <v>3000</v>
@@ -51796,7 +51796,7 @@
         <v>1</v>
       </c>
       <c r="G981" s="62">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H981" s="62">
         <v>2500</v>
@@ -51846,7 +51846,7 @@
         <v>1</v>
       </c>
       <c r="G982" s="62">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H982" s="62">
         <v>7500</v>
@@ -51896,7 +51896,7 @@
         <v>1</v>
       </c>
       <c r="G983" s="62">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H983" s="62">
         <v>2000</v>
@@ -51946,7 +51946,7 @@
         <v>1</v>
       </c>
       <c r="G984" s="62">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H984" s="62">
         <v>3000</v>
@@ -51996,7 +51996,7 @@
         <v>1</v>
       </c>
       <c r="G985" s="62">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H985" s="62">
         <v>3000</v>
@@ -52046,7 +52046,7 @@
         <v>1</v>
       </c>
       <c r="G986" s="62">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H986" s="62">
         <v>3500</v>
@@ -52096,7 +52096,7 @@
         <v>1</v>
       </c>
       <c r="G987" s="62">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H987" s="62">
         <v>2000</v>
@@ -52146,7 +52146,7 @@
         <v>1</v>
       </c>
       <c r="G988" s="62">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H988" s="62">
         <v>3000</v>
@@ -52196,7 +52196,7 @@
         <v>1</v>
       </c>
       <c r="G989" s="62">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H989" s="62">
         <v>3000</v>
@@ -52245,8 +52245,8 @@
       <c r="F990" s="66">
         <v>1</v>
       </c>
-      <c r="G990" s="66">
-        <v>37</v>
+      <c r="G990" s="62">
+        <v>38</v>
       </c>
       <c r="H990" s="66">
         <v>3500</v>
@@ -52296,7 +52296,7 @@
         <v>1</v>
       </c>
       <c r="G991" s="62">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H991" s="62">
         <v>2000</v>
@@ -52346,7 +52346,7 @@
         <v>1</v>
       </c>
       <c r="G992" s="62">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H992" s="62">
         <v>3000</v>
@@ -52396,7 +52396,7 @@
         <v>1</v>
       </c>
       <c r="G993" s="62">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H993" s="62">
         <v>3000</v>
@@ -52446,7 +52446,7 @@
         <v>1</v>
       </c>
       <c r="G994" s="62">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H994" s="62">
         <v>3500</v>
@@ -52496,7 +52496,7 @@
         <v>1</v>
       </c>
       <c r="G995" s="62">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H995" s="62">
         <v>2000</v>
@@ -52546,7 +52546,7 @@
         <v>1</v>
       </c>
       <c r="G996" s="62">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H996" s="62">
         <v>7500</v>
@@ -52596,7 +52596,7 @@
         <v>1</v>
       </c>
       <c r="G997" s="62">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H997" s="62">
         <v>2000</v>
@@ -52646,7 +52646,7 @@
         <v>1</v>
       </c>
       <c r="G998" s="62">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H998" s="62">
         <v>3000</v>
@@ -52696,7 +52696,7 @@
         <v>1</v>
       </c>
       <c r="G999" s="62">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H999" s="62">
         <v>3000</v>
@@ -52746,7 +52746,7 @@
         <v>1</v>
       </c>
       <c r="G1000" s="62">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H1000" s="62">
         <v>3500</v>
@@ -52796,7 +52796,7 @@
         <v>1</v>
       </c>
       <c r="G1001" s="62">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H1001" s="62">
         <v>3000</v>
@@ -52845,8 +52845,8 @@
       <c r="F1002" s="66">
         <v>1</v>
       </c>
-      <c r="G1002" s="66">
-        <v>47</v>
+      <c r="G1002" s="62">
+        <v>50</v>
       </c>
       <c r="H1002" s="66">
         <v>3000</v>
@@ -52896,7 +52896,7 @@
         <v>1</v>
       </c>
       <c r="G1003" s="62">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H1003" s="62">
         <v>3500</v>
@@ -52946,7 +52946,7 @@
         <v>1</v>
       </c>
       <c r="G1004" s="62">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H1004" s="62">
         <v>3000</v>
@@ -52996,7 +52996,7 @@
         <v>1</v>
       </c>
       <c r="G1005" s="62">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H1005" s="62">
         <v>3000</v>
@@ -53046,7 +53046,7 @@
         <v>1</v>
       </c>
       <c r="G1006" s="62">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H1006" s="62">
         <v>3500</v>
@@ -53096,7 +53096,7 @@
         <v>1</v>
       </c>
       <c r="G1007" s="62">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H1007" s="62">
         <v>3000</v>
@@ -53146,7 +53146,7 @@
         <v>1</v>
       </c>
       <c r="G1008" s="62">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H1008" s="62">
         <v>3000</v>
@@ -53196,7 +53196,7 @@
         <v>1</v>
       </c>
       <c r="G1009" s="62">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H1009" s="62">
         <v>3500</v>
@@ -53246,7 +53246,7 @@
         <v>1</v>
       </c>
       <c r="G1010" s="62">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H1010" s="62">
         <v>3000</v>
@@ -53296,7 +53296,7 @@
         <v>1</v>
       </c>
       <c r="G1011" s="62">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H1011" s="62">
         <v>3500</v>
@@ -53346,7 +53346,7 @@
         <v>1</v>
       </c>
       <c r="G1012" s="62">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H1012" s="62">
         <v>1</v>
@@ -53378,17 +53378,17 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A1012">
+    <cfRule type="duplicateValues" dxfId="3" priority="29"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A5:A53">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:A96 A98:A102">
-    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A169:A331 A333:A892">
-    <cfRule type="duplicateValues" dxfId="1" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A1012">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85FAE70-6119-47F0-9041-8862647B3ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16062F5-BFF6-44F6-8511-4555382458A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="610">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1352,102 +1352,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>60,50</t>
-  </si>
-  <si>
-    <t>80,40</t>
-  </si>
-  <si>
-    <t>80,60,90,90</t>
-  </si>
-  <si>
-    <t>80,50</t>
-  </si>
-  <si>
-    <t>50,5,15,85</t>
-  </si>
-  <si>
-    <t>5,50,10,90</t>
-  </si>
-  <si>
-    <t>30,20,20,30</t>
-  </si>
-  <si>
-    <t>55,45,90,20</t>
-  </si>
-  <si>
-    <t>45,55,80,10</t>
-  </si>
-  <si>
-    <t>40,40,55,45,45,55</t>
-  </si>
-  <si>
-    <t>85,15,75,25</t>
-  </si>
-  <si>
-    <t>55,45,45,55,80,20</t>
-  </si>
-  <si>
-    <t>60,40,40,60</t>
-  </si>
-  <si>
-    <t>10,40,15,45,90,90</t>
-  </si>
-  <si>
-    <t>20,35,90,80,80,90</t>
-  </si>
-  <si>
-    <t>10,40,15,45</t>
-  </si>
-  <si>
-    <t>10,50,15,55,85,85</t>
-  </si>
-  <si>
-    <t>20,45,85,75,75,85</t>
-  </si>
-  <si>
-    <t>10,60,15,65</t>
-  </si>
-  <si>
-    <t>20,60,25,65,80,80</t>
-  </si>
-  <si>
-    <t>15,60,75,75</t>
-  </si>
-  <si>
-    <t>20,50,50,20,10,20</t>
-  </si>
-  <si>
-    <t>40,40,15,25,25,15</t>
-  </si>
-  <si>
-    <t>15,55,55,15</t>
-  </si>
-  <si>
-    <t>45,45,20,25,25,20</t>
-  </si>
-  <si>
-    <t>20,60,60,20,40,40</t>
-  </si>
-  <si>
-    <t>45,45,25,30,30,25</t>
-  </si>
-  <si>
-    <t>50,50,20,60,60,20</t>
-  </si>
-  <si>
-    <t>45,45,10,40,40,10</t>
-  </si>
-  <si>
-    <t>55,55,20,60,60,20</t>
-  </si>
-  <si>
-    <t>50,50,15,45,45,15</t>
-  </si>
-  <si>
-    <t>45,45,10,50,50,10</t>
-  </si>
-  <si>
     <t>71104</t>
   </si>
   <si>
@@ -1971,6 +1875,99 @@
   </si>
   <si>
     <t>60,40,60,50,60,60,65,45,65,55</t>
+  </si>
+  <si>
+    <t>88,28</t>
+  </si>
+  <si>
+    <t>88,35,95,62</t>
+  </si>
+  <si>
+    <t>85,40</t>
+  </si>
+  <si>
+    <t>88,15</t>
+  </si>
+  <si>
+    <t>88,15,66,62</t>
+  </si>
+  <si>
+    <t>88,28,60,57</t>
+  </si>
+  <si>
+    <t>36,65,36,60</t>
+  </si>
+  <si>
+    <t>40,60,36,5</t>
+  </si>
+  <si>
+    <t>40,60,40,10</t>
+  </si>
+  <si>
+    <t>45,60,40,65,40,55</t>
+  </si>
+  <si>
+    <t>45,10,45,15</t>
+  </si>
+  <si>
+    <t>40,50,40,45,50,10</t>
+  </si>
+  <si>
+    <t>45,50,45,45</t>
+  </si>
+  <si>
+    <t>40,65,47,65,70,60</t>
+  </si>
+  <si>
+    <t>44,56,75,50,75,55</t>
+  </si>
+  <si>
+    <t>40,65,47,65</t>
+  </si>
+  <si>
+    <t>40,65,47,65,70,50</t>
+  </si>
+  <si>
+    <t>44,56,70,45,70,40</t>
+  </si>
+  <si>
+    <t>40,65,47,65,75,35</t>
+  </si>
+  <si>
+    <t>44,65,75,30</t>
+  </si>
+  <si>
+    <t>40,75,47,75,20,90</t>
+  </si>
+  <si>
+    <t>44,70,15,85,15,80</t>
+  </si>
+  <si>
+    <t>40,80,47,80</t>
+  </si>
+  <si>
+    <t>44,70,10,90,10,80</t>
+  </si>
+  <si>
+    <t>40,80,47,80,44,85</t>
+  </si>
+  <si>
+    <t>44,80,15,70,15,75</t>
+  </si>
+  <si>
+    <t>44,70,40,80,47,80</t>
+  </si>
+  <si>
+    <t>44,80,10,70,10,75</t>
+  </si>
+  <si>
+    <t>44,70,15,70,15,75</t>
+  </si>
+  <si>
+    <t>44,80,30,95,35,95</t>
+  </si>
+  <si>
+    <t>44,85,25,95,40,95</t>
   </si>
 </sst>
 </file>
@@ -44305,7 +44302,7 @@
         <v>1</v>
       </c>
       <c r="J831" s="61" t="s">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="K831" s="60">
         <v>16</v>
@@ -44320,7 +44317,7 @@
         <v>0</v>
       </c>
       <c r="O831" s="1" t="s">
-        <v>404</v>
+        <v>579</v>
       </c>
       <c r="P831" s="1">
         <v>0</v>
@@ -44355,7 +44352,7 @@
         <v>1</v>
       </c>
       <c r="J832" s="61" t="s">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="K832" s="60">
         <v>16</v>
@@ -44370,7 +44367,7 @@
         <v>0</v>
       </c>
       <c r="O832" s="1" t="s">
-        <v>406</v>
+        <v>580</v>
       </c>
       <c r="P832" s="1">
         <v>0</v>
@@ -44405,7 +44402,7 @@
         <v>1</v>
       </c>
       <c r="J833" s="61" t="s">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="K833" s="60">
         <v>16</v>
@@ -44420,7 +44417,7 @@
         <v>0</v>
       </c>
       <c r="O833" s="1" t="s">
-        <v>405</v>
+        <v>581</v>
       </c>
       <c r="P833" s="1">
         <v>0</v>
@@ -44455,7 +44452,7 @@
         <v>2</v>
       </c>
       <c r="J834" s="61" t="s">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="K834" s="60">
         <v>16</v>
@@ -44470,7 +44467,7 @@
         <v>0</v>
       </c>
       <c r="O834" s="1" t="s">
-        <v>407</v>
+        <v>582</v>
       </c>
       <c r="P834" s="1">
         <v>0</v>
@@ -44505,7 +44502,7 @@
         <v>2</v>
       </c>
       <c r="J835" s="61" t="s">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="K835" s="60">
         <v>16</v>
@@ -44520,7 +44517,7 @@
         <v>0</v>
       </c>
       <c r="O835" s="1" t="s">
-        <v>408</v>
+        <v>583</v>
       </c>
       <c r="P835" s="1">
         <v>0</v>
@@ -44555,7 +44552,7 @@
         <v>2</v>
       </c>
       <c r="J836" s="61" t="s">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="K836" s="60">
         <v>16</v>
@@ -44570,7 +44567,7 @@
         <v>0</v>
       </c>
       <c r="O836" s="1" t="s">
-        <v>409</v>
+        <v>584</v>
       </c>
       <c r="P836" s="1">
         <v>0</v>
@@ -44605,7 +44602,7 @@
         <v>2</v>
       </c>
       <c r="J837" s="61" t="s">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="K837" s="60">
         <v>16</v>
@@ -44620,7 +44617,7 @@
         <v>0</v>
       </c>
       <c r="O837" s="1" t="s">
-        <v>410</v>
+        <v>585</v>
       </c>
       <c r="P837" s="1">
         <v>0</v>
@@ -44655,7 +44652,7 @@
         <v>3</v>
       </c>
       <c r="J838" s="61" t="s">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="K838" s="60">
         <v>16</v>
@@ -44670,7 +44667,7 @@
         <v>0</v>
       </c>
       <c r="O838" s="1" t="s">
-        <v>411</v>
+        <v>586</v>
       </c>
       <c r="P838" s="1">
         <v>0</v>
@@ -44705,7 +44702,7 @@
         <v>3</v>
       </c>
       <c r="J839" s="61" t="s">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="K839" s="60">
         <v>16</v>
@@ -44720,7 +44717,7 @@
         <v>0</v>
       </c>
       <c r="O839" s="1" t="s">
-        <v>412</v>
+        <v>587</v>
       </c>
       <c r="P839" s="1">
         <v>0</v>
@@ -44755,7 +44752,7 @@
         <v>3</v>
       </c>
       <c r="J840" s="61" t="s">
-        <v>443</v>
+        <v>411</v>
       </c>
       <c r="K840" s="60">
         <v>16</v>
@@ -44770,7 +44767,7 @@
         <v>0</v>
       </c>
       <c r="O840" s="1" t="s">
-        <v>413</v>
+        <v>588</v>
       </c>
       <c r="P840" s="1">
         <v>0</v>
@@ -44805,7 +44802,7 @@
         <v>3</v>
       </c>
       <c r="J841" s="61" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="K841" s="60">
         <v>16</v>
@@ -44820,7 +44817,7 @@
         <v>0</v>
       </c>
       <c r="O841" s="1" t="s">
-        <v>414</v>
+        <v>589</v>
       </c>
       <c r="P841" s="1">
         <v>0</v>
@@ -44855,7 +44852,7 @@
         <v>3</v>
       </c>
       <c r="J842" s="61" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="K842" s="60">
         <v>16</v>
@@ -44870,7 +44867,7 @@
         <v>0</v>
       </c>
       <c r="O842" s="1" t="s">
-        <v>415</v>
+        <v>590</v>
       </c>
       <c r="P842" s="1">
         <v>0</v>
@@ -44905,7 +44902,7 @@
         <v>3</v>
       </c>
       <c r="J843" s="61" t="s">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="K843" s="60">
         <v>16</v>
@@ -44920,7 +44917,7 @@
         <v>0</v>
       </c>
       <c r="O843" s="1" t="s">
-        <v>416</v>
+        <v>591</v>
       </c>
       <c r="P843" s="1">
         <v>0</v>
@@ -44955,7 +44952,7 @@
         <v>4</v>
       </c>
       <c r="J844" s="61" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="K844" s="60">
         <v>16</v>
@@ -44970,7 +44967,7 @@
         <v>0</v>
       </c>
       <c r="O844" s="1" t="s">
-        <v>417</v>
+        <v>592</v>
       </c>
       <c r="P844" s="1">
         <v>0</v>
@@ -45005,7 +45002,7 @@
         <v>4</v>
       </c>
       <c r="J845" s="61" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
       <c r="K845" s="60">
         <v>16</v>
@@ -45020,7 +45017,7 @@
         <v>0</v>
       </c>
       <c r="O845" s="1" t="s">
-        <v>418</v>
+        <v>593</v>
       </c>
       <c r="P845" s="1">
         <v>0</v>
@@ -45055,7 +45052,7 @@
         <v>4</v>
       </c>
       <c r="J846" s="61" t="s">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="K846" s="60">
         <v>16</v>
@@ -45070,7 +45067,7 @@
         <v>0</v>
       </c>
       <c r="O846" s="1" t="s">
-        <v>419</v>
+        <v>594</v>
       </c>
       <c r="P846" s="1">
         <v>0</v>
@@ -45105,7 +45102,7 @@
         <v>4</v>
       </c>
       <c r="J847" s="61" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="K847" s="60">
         <v>16</v>
@@ -45120,7 +45117,7 @@
         <v>0</v>
       </c>
       <c r="O847" s="1" t="s">
-        <v>420</v>
+        <v>595</v>
       </c>
       <c r="P847" s="1">
         <v>0</v>
@@ -45155,7 +45152,7 @@
         <v>4</v>
       </c>
       <c r="J848" s="61" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
       <c r="K848" s="60">
         <v>16</v>
@@ -45170,7 +45167,7 @@
         <v>0</v>
       </c>
       <c r="O848" s="1" t="s">
-        <v>421</v>
+        <v>596</v>
       </c>
       <c r="P848" s="1">
         <v>0</v>
@@ -45205,7 +45202,7 @@
         <v>4</v>
       </c>
       <c r="J849" s="61" t="s">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="K849" s="60">
         <v>16</v>
@@ -45220,7 +45217,7 @@
         <v>0</v>
       </c>
       <c r="O849" s="1" t="s">
-        <v>422</v>
+        <v>594</v>
       </c>
       <c r="P849" s="1">
         <v>0</v>
@@ -45255,7 +45252,7 @@
         <v>4</v>
       </c>
       <c r="J850" s="61" t="s">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="K850" s="60">
         <v>16</v>
@@ -45270,7 +45267,7 @@
         <v>0</v>
       </c>
       <c r="O850" s="1" t="s">
-        <v>423</v>
+        <v>597</v>
       </c>
       <c r="P850" s="1">
         <v>0</v>
@@ -45305,7 +45302,7 @@
         <v>4</v>
       </c>
       <c r="J851" s="61" t="s">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="K851" s="60">
         <v>16</v>
@@ -45320,7 +45317,7 @@
         <v>0</v>
       </c>
       <c r="O851" s="1" t="s">
-        <v>424</v>
+        <v>598</v>
       </c>
       <c r="P851" s="1">
         <v>0</v>
@@ -45355,7 +45352,7 @@
         <v>5</v>
       </c>
       <c r="J852" s="61" t="s">
-        <v>497</v>
+        <v>465</v>
       </c>
       <c r="K852" s="60">
         <v>16</v>
@@ -45370,7 +45367,7 @@
         <v>0</v>
       </c>
       <c r="O852" s="1" t="s">
-        <v>425</v>
+        <v>599</v>
       </c>
       <c r="P852" s="1">
         <v>0</v>
@@ -45405,7 +45402,7 @@
         <v>5</v>
       </c>
       <c r="J853" s="61" t="s">
-        <v>498</v>
+        <v>466</v>
       </c>
       <c r="K853" s="60">
         <v>16</v>
@@ -45420,7 +45417,7 @@
         <v>0</v>
       </c>
       <c r="O853" s="1" t="s">
-        <v>426</v>
+        <v>600</v>
       </c>
       <c r="P853" s="1">
         <v>0</v>
@@ -45455,7 +45452,7 @@
         <v>5</v>
       </c>
       <c r="J854" s="61" t="s">
-        <v>499</v>
+        <v>467</v>
       </c>
       <c r="K854" s="60">
         <v>16</v>
@@ -45470,7 +45467,7 @@
         <v>0</v>
       </c>
       <c r="O854" s="1" t="s">
-        <v>427</v>
+        <v>601</v>
       </c>
       <c r="P854" s="1">
         <v>0</v>
@@ -45505,7 +45502,7 @@
         <v>5</v>
       </c>
       <c r="J855" s="61" t="s">
-        <v>498</v>
+        <v>466</v>
       </c>
       <c r="K855" s="60">
         <v>16</v>
@@ -45520,7 +45517,7 @@
         <v>0</v>
       </c>
       <c r="O855" s="1" t="s">
-        <v>428</v>
+        <v>602</v>
       </c>
       <c r="P855" s="1">
         <v>0</v>
@@ -45555,7 +45552,7 @@
         <v>5</v>
       </c>
       <c r="J856" s="61" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="K856" s="60">
         <v>16</v>
@@ -45570,7 +45567,7 @@
         <v>0</v>
       </c>
       <c r="O856" s="1" t="s">
-        <v>429</v>
+        <v>603</v>
       </c>
       <c r="P856" s="1">
         <v>0</v>
@@ -45605,7 +45602,7 @@
         <v>5</v>
       </c>
       <c r="J857" s="61" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="K857" s="60">
         <v>16</v>
@@ -45620,7 +45617,7 @@
         <v>0</v>
       </c>
       <c r="O857" s="1" t="s">
-        <v>430</v>
+        <v>604</v>
       </c>
       <c r="P857" s="1">
         <v>0</v>
@@ -45655,7 +45652,7 @@
         <v>5</v>
       </c>
       <c r="J858" s="61" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="K858" s="60">
         <v>16</v>
@@ -45670,7 +45667,7 @@
         <v>0</v>
       </c>
       <c r="O858" s="1" t="s">
-        <v>431</v>
+        <v>605</v>
       </c>
       <c r="P858" s="1">
         <v>0</v>
@@ -45705,7 +45702,7 @@
         <v>5</v>
       </c>
       <c r="J859" s="61" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="K859" s="60">
         <v>16</v>
@@ -45720,7 +45717,7 @@
         <v>0</v>
       </c>
       <c r="O859" s="1" t="s">
-        <v>432</v>
+        <v>606</v>
       </c>
       <c r="P859" s="1">
         <v>0</v>
@@ -45755,7 +45752,7 @@
         <v>5</v>
       </c>
       <c r="J860" s="61" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="K860" s="60">
         <v>16</v>
@@ -45770,7 +45767,7 @@
         <v>0</v>
       </c>
       <c r="O860" s="1" t="s">
-        <v>433</v>
+        <v>607</v>
       </c>
       <c r="P860" s="1">
         <v>0</v>
@@ -45805,7 +45802,7 @@
         <v>5</v>
       </c>
       <c r="J861" s="61" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="K861" s="60">
         <v>16</v>
@@ -45820,7 +45817,7 @@
         <v>0</v>
       </c>
       <c r="O861" s="1" t="s">
-        <v>434</v>
+        <v>608</v>
       </c>
       <c r="P861" s="1">
         <v>0</v>
@@ -45855,7 +45852,7 @@
         <v>5</v>
       </c>
       <c r="J862" s="61" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="K862" s="60">
         <v>16</v>
@@ -45870,7 +45867,7 @@
         <v>0</v>
       </c>
       <c r="O862" s="1" t="s">
-        <v>435</v>
+        <v>609</v>
       </c>
       <c r="P862" s="1">
         <v>0</v>
@@ -45905,7 +45902,7 @@
         <v>1</v>
       </c>
       <c r="J863" s="61" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
       <c r="K863" s="60">
         <v>30</v>
@@ -45920,7 +45917,7 @@
         <v>1</v>
       </c>
       <c r="O863" s="1" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="P863" s="1">
         <v>0</v>
@@ -45955,7 +45952,7 @@
         <v>1</v>
       </c>
       <c r="J864" s="61" t="s">
-        <v>504</v>
+        <v>472</v>
       </c>
       <c r="K864" s="60">
         <v>30</v>
@@ -45970,7 +45967,7 @@
         <v>1</v>
       </c>
       <c r="O864" s="1" t="s">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="P864" s="1">
         <v>0</v>
@@ -46005,7 +46002,7 @@
         <v>1</v>
       </c>
       <c r="J865" s="61" t="s">
-        <v>505</v>
+        <v>473</v>
       </c>
       <c r="K865" s="60">
         <v>30</v>
@@ -46020,7 +46017,7 @@
         <v>1</v>
       </c>
       <c r="O865" s="1" t="s">
-        <v>481</v>
+        <v>449</v>
       </c>
       <c r="P865" s="1">
         <v>0</v>
@@ -46055,7 +46052,7 @@
         <v>1</v>
       </c>
       <c r="J866" s="61" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="K866" s="60">
         <v>30</v>
@@ -46070,7 +46067,7 @@
         <v>1</v>
       </c>
       <c r="O866" s="1" t="s">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="P866" s="1">
         <v>0</v>
@@ -46105,7 +46102,7 @@
         <v>2</v>
       </c>
       <c r="J867" s="61" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
       <c r="K867" s="60">
         <v>30</v>
@@ -46120,7 +46117,7 @@
         <v>1</v>
       </c>
       <c r="O867" s="1" t="s">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="P867" s="1">
         <v>0</v>
@@ -46155,7 +46152,7 @@
         <v>2</v>
       </c>
       <c r="J868" s="61" t="s">
-        <v>508</v>
+        <v>476</v>
       </c>
       <c r="K868" s="60">
         <v>30</v>
@@ -46170,7 +46167,7 @@
         <v>1</v>
       </c>
       <c r="O868" s="1" t="s">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="P868" s="1">
         <v>0</v>
@@ -46205,7 +46202,7 @@
         <v>2</v>
       </c>
       <c r="J869" s="61" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="K869" s="60">
         <v>30</v>
@@ -46220,7 +46217,7 @@
         <v>1</v>
       </c>
       <c r="O869" s="1" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="P869" s="1">
         <v>0</v>
@@ -46255,7 +46252,7 @@
         <v>2</v>
       </c>
       <c r="J870" s="61" t="s">
-        <v>508</v>
+        <v>476</v>
       </c>
       <c r="K870" s="60">
         <v>30</v>
@@ -46270,7 +46267,7 @@
         <v>1</v>
       </c>
       <c r="O870" s="1" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="P870" s="1">
         <v>0</v>
@@ -46305,7 +46302,7 @@
         <v>2</v>
       </c>
       <c r="J871" s="61" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
       <c r="K871" s="60">
         <v>30</v>
@@ -46320,7 +46317,7 @@
         <v>1</v>
       </c>
       <c r="O871" s="1" t="s">
-        <v>487</v>
+        <v>455</v>
       </c>
       <c r="P871" s="1">
         <v>0</v>
@@ -46355,7 +46352,7 @@
         <v>2</v>
       </c>
       <c r="J872" s="61" t="s">
-        <v>509</v>
+        <v>477</v>
       </c>
       <c r="K872" s="60">
         <v>30</v>
@@ -46370,7 +46367,7 @@
         <v>1</v>
       </c>
       <c r="O872" s="1" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="P872" s="1">
         <v>0</v>
@@ -46405,7 +46402,7 @@
         <v>3</v>
       </c>
       <c r="J873" s="61" t="s">
-        <v>446</v>
+        <v>414</v>
       </c>
       <c r="K873" s="60">
         <v>30</v>
@@ -46420,7 +46417,7 @@
         <v>1</v>
       </c>
       <c r="O873" s="1" t="s">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="P873" s="1">
         <v>0</v>
@@ -46455,7 +46452,7 @@
         <v>3</v>
       </c>
       <c r="J874" s="61" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="K874" s="60">
         <v>30</v>
@@ -46470,7 +46467,7 @@
         <v>1</v>
       </c>
       <c r="O874" s="1" t="s">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="P874" s="1">
         <v>0</v>
@@ -46505,7 +46502,7 @@
         <v>3</v>
       </c>
       <c r="J875" s="61" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="K875" s="60">
         <v>30</v>
@@ -46520,7 +46517,7 @@
         <v>1</v>
       </c>
       <c r="O875" s="1" t="s">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="P875" s="1">
         <v>0</v>
@@ -46555,7 +46552,7 @@
         <v>3</v>
       </c>
       <c r="J876" s="61" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="K876" s="60">
         <v>30</v>
@@ -46570,7 +46567,7 @@
         <v>1</v>
       </c>
       <c r="O876" s="1" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="P876" s="1">
         <v>0</v>
@@ -46605,7 +46602,7 @@
         <v>3</v>
       </c>
       <c r="J877" s="61" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="K877" s="60">
         <v>30</v>
@@ -46620,7 +46617,7 @@
         <v>1</v>
       </c>
       <c r="O877" s="1" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="P877" s="1">
         <v>0</v>
@@ -46655,7 +46652,7 @@
         <v>3</v>
       </c>
       <c r="J878" s="61" t="s">
-        <v>444</v>
+        <v>412</v>
       </c>
       <c r="K878" s="60">
         <v>30</v>
@@ -46670,7 +46667,7 @@
         <v>1</v>
       </c>
       <c r="O878" s="1" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="P878" s="1">
         <v>0</v>
@@ -46705,7 +46702,7 @@
         <v>3</v>
       </c>
       <c r="J879" s="61" t="s">
-        <v>511</v>
+        <v>479</v>
       </c>
       <c r="K879" s="60">
         <v>30</v>
@@ -46720,7 +46717,7 @@
         <v>1</v>
       </c>
       <c r="O879" s="1" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
       <c r="P879" s="1">
         <v>0</v>
@@ -46755,7 +46752,7 @@
         <v>3</v>
       </c>
       <c r="J880" s="61" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="K880" s="60">
         <v>30</v>
@@ -46770,7 +46767,7 @@
         <v>1</v>
       </c>
       <c r="O880" s="1" t="s">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="P880" s="1">
         <v>0</v>
@@ -46805,7 +46802,7 @@
         <v>4</v>
       </c>
       <c r="J881" s="61" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="K881" s="60">
         <v>30</v>
@@ -46820,7 +46817,7 @@
         <v>1</v>
       </c>
       <c r="O881" s="1" t="s">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="P881" s="1">
         <v>0</v>
@@ -46855,7 +46852,7 @@
         <v>4</v>
       </c>
       <c r="J882" s="61" t="s">
-        <v>512</v>
+        <v>480</v>
       </c>
       <c r="K882" s="60">
         <v>30</v>
@@ -46870,7 +46867,7 @@
         <v>1</v>
       </c>
       <c r="O882" s="1" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="P882" s="1">
         <v>0</v>
@@ -46905,7 +46902,7 @@
         <v>4</v>
       </c>
       <c r="J883" s="61" t="s">
-        <v>513</v>
+        <v>481</v>
       </c>
       <c r="K883" s="60">
         <v>30</v>
@@ -46920,7 +46917,7 @@
         <v>1</v>
       </c>
       <c r="O883" s="1" t="s">
-        <v>459</v>
+        <v>427</v>
       </c>
       <c r="P883" s="1">
         <v>0</v>
@@ -46955,7 +46952,7 @@
         <v>4</v>
       </c>
       <c r="J884" s="61" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="K884" s="60">
         <v>30</v>
@@ -46970,7 +46967,7 @@
         <v>1</v>
       </c>
       <c r="O884" s="1" t="s">
-        <v>460</v>
+        <v>428</v>
       </c>
       <c r="P884" s="1">
         <v>0</v>
@@ -47005,7 +47002,7 @@
         <v>4</v>
       </c>
       <c r="J885" s="61" t="s">
-        <v>514</v>
+        <v>482</v>
       </c>
       <c r="K885" s="60">
         <v>30</v>
@@ -47020,7 +47017,7 @@
         <v>1</v>
       </c>
       <c r="O885" s="1" t="s">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="P885" s="1">
         <v>0</v>
@@ -47055,7 +47052,7 @@
         <v>4</v>
       </c>
       <c r="J886" s="61" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="K886" s="60">
         <v>30</v>
@@ -47070,7 +47067,7 @@
         <v>1</v>
       </c>
       <c r="O886" s="1" t="s">
-        <v>462</v>
+        <v>430</v>
       </c>
       <c r="P886" s="1">
         <v>0</v>
@@ -47105,7 +47102,7 @@
         <v>4</v>
       </c>
       <c r="J887" s="61" t="s">
-        <v>515</v>
+        <v>483</v>
       </c>
       <c r="K887" s="60">
         <v>30</v>
@@ -47120,7 +47117,7 @@
         <v>1</v>
       </c>
       <c r="O887" s="1" t="s">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="P887" s="1">
         <v>0</v>
@@ -47155,7 +47152,7 @@
         <v>4</v>
       </c>
       <c r="J888" s="61" t="s">
-        <v>516</v>
+        <v>484</v>
       </c>
       <c r="K888" s="60">
         <v>30</v>
@@ -47170,7 +47167,7 @@
         <v>1</v>
       </c>
       <c r="O888" s="1" t="s">
-        <v>464</v>
+        <v>432</v>
       </c>
       <c r="P888" s="1">
         <v>0</v>
@@ -47205,7 +47202,7 @@
         <v>4</v>
       </c>
       <c r="J889" s="61" t="s">
-        <v>517</v>
+        <v>485</v>
       </c>
       <c r="K889" s="60">
         <v>30</v>
@@ -47220,7 +47217,7 @@
         <v>1</v>
       </c>
       <c r="O889" s="1" t="s">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="P889" s="1">
         <v>0</v>
@@ -47255,7 +47252,7 @@
         <v>4</v>
       </c>
       <c r="J890" s="61" t="s">
-        <v>513</v>
+        <v>481</v>
       </c>
       <c r="K890" s="60">
         <v>30</v>
@@ -47270,7 +47267,7 @@
         <v>1</v>
       </c>
       <c r="O890" s="1" t="s">
-        <v>466</v>
+        <v>434</v>
       </c>
       <c r="P890" s="1">
         <v>0</v>
@@ -47305,7 +47302,7 @@
         <v>5</v>
       </c>
       <c r="J891" s="61" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="K891" s="60">
         <v>30</v>
@@ -47320,7 +47317,7 @@
         <v>1</v>
       </c>
       <c r="O891" s="1" t="s">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="P891" s="1">
         <v>0</v>
@@ -47355,7 +47352,7 @@
         <v>5</v>
       </c>
       <c r="J892" s="61" t="s">
-        <v>452</v>
+        <v>420</v>
       </c>
       <c r="K892" s="60">
         <v>30</v>
@@ -47370,7 +47367,7 @@
         <v>1</v>
       </c>
       <c r="O892" s="1" t="s">
-        <v>468</v>
+        <v>436</v>
       </c>
       <c r="P892" s="1">
         <v>0</v>
@@ -47405,7 +47402,7 @@
         <v>5</v>
       </c>
       <c r="J893" s="63" t="s">
-        <v>452</v>
+        <v>420</v>
       </c>
       <c r="K893" s="60">
         <v>30</v>
@@ -47420,7 +47417,7 @@
         <v>1</v>
       </c>
       <c r="O893" s="1" t="s">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="P893" s="1">
         <v>0</v>
@@ -47455,7 +47452,7 @@
         <v>5</v>
       </c>
       <c r="J894" s="63" t="s">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="K894" s="60">
         <v>30</v>
@@ -47470,7 +47467,7 @@
         <v>1</v>
       </c>
       <c r="O894" s="1" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="P894" s="1">
         <v>0</v>
@@ -47505,7 +47502,7 @@
         <v>5</v>
       </c>
       <c r="J895" s="63" t="s">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="K895" s="60">
         <v>30</v>
@@ -47520,7 +47517,7 @@
         <v>1</v>
       </c>
       <c r="O895" s="1" t="s">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="P895" s="1">
         <v>0</v>
@@ -47555,7 +47552,7 @@
         <v>5</v>
       </c>
       <c r="J896" s="63" t="s">
-        <v>447</v>
+        <v>415</v>
       </c>
       <c r="K896" s="60">
         <v>30</v>
@@ -47570,7 +47567,7 @@
         <v>1</v>
       </c>
       <c r="O896" s="1" t="s">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="P896" s="1">
         <v>0</v>
@@ -47605,7 +47602,7 @@
         <v>5</v>
       </c>
       <c r="J897" s="63" t="s">
-        <v>453</v>
+        <v>421</v>
       </c>
       <c r="K897" s="60">
         <v>30</v>
@@ -47620,7 +47617,7 @@
         <v>1</v>
       </c>
       <c r="O897" s="1" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="P897" s="1">
         <v>0</v>
@@ -47655,7 +47652,7 @@
         <v>5</v>
       </c>
       <c r="J898" s="63" t="s">
-        <v>448</v>
+        <v>416</v>
       </c>
       <c r="K898" s="60">
         <v>30</v>
@@ -47670,7 +47667,7 @@
         <v>1</v>
       </c>
       <c r="O898" s="1" t="s">
-        <v>474</v>
+        <v>442</v>
       </c>
       <c r="P898" s="1">
         <v>0</v>
@@ -47705,7 +47702,7 @@
         <v>5</v>
       </c>
       <c r="J899" s="63" t="s">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="K899" s="60">
         <v>30</v>
@@ -47720,7 +47717,7 @@
         <v>1</v>
       </c>
       <c r="O899" s="1" t="s">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="P899" s="1">
         <v>0</v>
@@ -47755,7 +47752,7 @@
         <v>5</v>
       </c>
       <c r="J900" s="63" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
       <c r="K900" s="60">
         <v>30</v>
@@ -47770,7 +47767,7 @@
         <v>1</v>
       </c>
       <c r="O900" s="1" t="s">
-        <v>476</v>
+        <v>444</v>
       </c>
       <c r="P900" s="1">
         <v>0</v>
@@ -47805,7 +47802,7 @@
         <v>5</v>
       </c>
       <c r="J901" s="63" t="s">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="K901" s="60">
         <v>30</v>
@@ -47820,7 +47817,7 @@
         <v>1</v>
       </c>
       <c r="O901" s="1" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="P901" s="1">
         <v>0</v>
@@ -47855,7 +47852,7 @@
         <v>5</v>
       </c>
       <c r="J902" s="63" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="K902" s="60">
         <v>30</v>
@@ -47870,7 +47867,7 @@
         <v>1</v>
       </c>
       <c r="O902" s="1" t="s">
-        <v>478</v>
+        <v>446</v>
       </c>
       <c r="P902" s="1">
         <v>0</v>
@@ -47905,7 +47902,7 @@
         <v>1</v>
       </c>
       <c r="J903" s="63" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
       <c r="K903" s="62">
         <v>400</v>
@@ -47920,7 +47917,7 @@
         <v>2</v>
       </c>
       <c r="O903" s="1" t="s">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="P903" s="1">
         <v>0</v>
@@ -47955,7 +47952,7 @@
         <v>1</v>
       </c>
       <c r="J904" s="63" t="s">
-        <v>520</v>
+        <v>488</v>
       </c>
       <c r="K904" s="62">
         <v>400</v>
@@ -47970,7 +47967,7 @@
         <v>2</v>
       </c>
       <c r="O904" s="1" t="s">
-        <v>484</v>
+        <v>452</v>
       </c>
       <c r="P904" s="1">
         <v>0</v>
@@ -48005,7 +48002,7 @@
         <v>1</v>
       </c>
       <c r="J905" s="63" t="s">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="K905" s="62">
         <v>400</v>
@@ -48020,7 +48017,7 @@
         <v>2</v>
       </c>
       <c r="O905" s="1" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="P905" s="1">
         <v>0</v>
@@ -48055,7 +48052,7 @@
         <v>1</v>
       </c>
       <c r="J906" s="63" t="s">
-        <v>520</v>
+        <v>488</v>
       </c>
       <c r="K906" s="62">
         <v>400</v>
@@ -48070,7 +48067,7 @@
         <v>2</v>
       </c>
       <c r="O906" s="1" t="s">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="P906" s="1">
         <v>0</v>
@@ -48105,7 +48102,7 @@
         <v>1</v>
       </c>
       <c r="J907" s="63" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
       <c r="K907" s="62">
         <v>400</v>
@@ -48120,7 +48117,7 @@
         <v>2</v>
       </c>
       <c r="O907" s="1" t="s">
-        <v>487</v>
+        <v>455</v>
       </c>
       <c r="P907" s="1">
         <v>0</v>
@@ -48155,7 +48152,7 @@
         <v>1</v>
       </c>
       <c r="J908" s="63" t="s">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="K908" s="62">
         <v>400</v>
@@ -48170,7 +48167,7 @@
         <v>2</v>
       </c>
       <c r="O908" s="1" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="P908" s="1">
         <v>0</v>
@@ -48205,7 +48202,7 @@
         <v>2</v>
       </c>
       <c r="J909" s="63" t="s">
-        <v>522</v>
+        <v>490</v>
       </c>
       <c r="K909" s="62">
         <v>400</v>
@@ -48220,7 +48217,7 @@
         <v>2</v>
       </c>
       <c r="O909" s="1" t="s">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="P909" s="1">
         <v>0</v>
@@ -48255,7 +48252,7 @@
         <v>2</v>
       </c>
       <c r="J910" s="63" t="s">
-        <v>520</v>
+        <v>488</v>
       </c>
       <c r="K910" s="62">
         <v>400</v>
@@ -48270,7 +48267,7 @@
         <v>2</v>
       </c>
       <c r="O910" s="1" t="s">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="P910" s="1">
         <v>0</v>
@@ -48305,7 +48302,7 @@
         <v>2</v>
       </c>
       <c r="J911" s="63" t="s">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="K911" s="62">
         <v>400</v>
@@ -48320,7 +48317,7 @@
         <v>2</v>
       </c>
       <c r="O911" s="1" t="s">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="P911" s="1">
         <v>0</v>
@@ -48355,7 +48352,7 @@
         <v>2</v>
       </c>
       <c r="J912" s="63" t="s">
-        <v>523</v>
+        <v>491</v>
       </c>
       <c r="K912" s="62">
         <v>400</v>
@@ -48370,7 +48367,7 @@
         <v>2</v>
       </c>
       <c r="O912" s="1" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="P912" s="1">
         <v>0</v>
@@ -48405,7 +48402,7 @@
         <v>2</v>
       </c>
       <c r="J913" s="63" t="s">
-        <v>520</v>
+        <v>488</v>
       </c>
       <c r="K913" s="62">
         <v>400</v>
@@ -48420,7 +48417,7 @@
         <v>2</v>
       </c>
       <c r="O913" s="1" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="P913" s="1">
         <v>0</v>
@@ -48455,7 +48452,7 @@
         <v>2</v>
       </c>
       <c r="J914" s="63" t="s">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="K914" s="62">
         <v>400</v>
@@ -48470,7 +48467,7 @@
         <v>2</v>
       </c>
       <c r="O914" s="1" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="P914" s="1">
         <v>0</v>
@@ -48505,7 +48502,7 @@
         <v>2</v>
       </c>
       <c r="J915" s="63" t="s">
-        <v>524</v>
+        <v>492</v>
       </c>
       <c r="K915" s="62">
         <v>400</v>
@@ -48520,7 +48517,7 @@
         <v>2</v>
       </c>
       <c r="O915" s="1" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
       <c r="P915" s="1">
         <v>0</v>
@@ -48555,7 +48552,7 @@
         <v>2</v>
       </c>
       <c r="J916" s="63" t="s">
-        <v>523</v>
+        <v>491</v>
       </c>
       <c r="K916" s="62">
         <v>400</v>
@@ -48570,7 +48567,7 @@
         <v>2</v>
       </c>
       <c r="O916" s="1" t="s">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="P916" s="1">
         <v>0</v>
@@ -48605,7 +48602,7 @@
         <v>3</v>
       </c>
       <c r="J917" s="63" t="s">
-        <v>525</v>
+        <v>493</v>
       </c>
       <c r="K917" s="62">
         <v>400</v>
@@ -48620,7 +48617,7 @@
         <v>2</v>
       </c>
       <c r="O917" s="1" t="s">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="P917" s="1">
         <v>0</v>
@@ -48655,7 +48652,7 @@
         <v>3</v>
       </c>
       <c r="J918" s="63" t="s">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="K918" s="62">
         <v>400</v>
@@ -48670,7 +48667,7 @@
         <v>2</v>
       </c>
       <c r="O918" s="1" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="P918" s="1">
         <v>0</v>
@@ -48705,7 +48702,7 @@
         <v>3</v>
       </c>
       <c r="J919" s="63" t="s">
-        <v>527</v>
+        <v>495</v>
       </c>
       <c r="K919" s="62">
         <v>400</v>
@@ -48720,7 +48717,7 @@
         <v>2</v>
       </c>
       <c r="O919" s="1" t="s">
-        <v>459</v>
+        <v>427</v>
       </c>
       <c r="P919" s="1">
         <v>0</v>
@@ -48755,7 +48752,7 @@
         <v>3</v>
       </c>
       <c r="J920" s="63" t="s">
-        <v>525</v>
+        <v>493</v>
       </c>
       <c r="K920" s="62">
         <v>400</v>
@@ -48770,7 +48767,7 @@
         <v>2</v>
       </c>
       <c r="O920" s="1" t="s">
-        <v>460</v>
+        <v>428</v>
       </c>
       <c r="P920" s="1">
         <v>0</v>
@@ -48805,7 +48802,7 @@
         <v>3</v>
       </c>
       <c r="J921" s="65" t="s">
-        <v>528</v>
+        <v>496</v>
       </c>
       <c r="K921" s="62">
         <v>400</v>
@@ -48820,7 +48817,7 @@
         <v>2</v>
       </c>
       <c r="O921" s="1" t="s">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="P921" s="1">
         <v>0</v>
@@ -48855,7 +48852,7 @@
         <v>3</v>
       </c>
       <c r="J922" s="63" t="s">
-        <v>525</v>
+        <v>493</v>
       </c>
       <c r="K922" s="62">
         <v>400</v>
@@ -48870,7 +48867,7 @@
         <v>2</v>
       </c>
       <c r="O922" s="1" t="s">
-        <v>462</v>
+        <v>430</v>
       </c>
       <c r="P922" s="1">
         <v>0</v>
@@ -48905,7 +48902,7 @@
         <v>3</v>
       </c>
       <c r="J923" s="63" t="s">
-        <v>529</v>
+        <v>497</v>
       </c>
       <c r="K923" s="62">
         <v>400</v>
@@ -48920,7 +48917,7 @@
         <v>2</v>
       </c>
       <c r="O923" s="1" t="s">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="P923" s="1">
         <v>0</v>
@@ -48955,7 +48952,7 @@
         <v>3</v>
       </c>
       <c r="J924" s="63" t="s">
-        <v>530</v>
+        <v>498</v>
       </c>
       <c r="K924" s="62">
         <v>400</v>
@@ -48970,7 +48967,7 @@
         <v>2</v>
       </c>
       <c r="O924" s="1" t="s">
-        <v>464</v>
+        <v>432</v>
       </c>
       <c r="P924" s="1">
         <v>0</v>
@@ -49005,7 +49002,7 @@
         <v>3</v>
       </c>
       <c r="J925" s="63" t="s">
-        <v>531</v>
+        <v>499</v>
       </c>
       <c r="K925" s="62">
         <v>400</v>
@@ -49020,7 +49017,7 @@
         <v>2</v>
       </c>
       <c r="O925" s="1" t="s">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="P925" s="1">
         <v>0</v>
@@ -49055,7 +49052,7 @@
         <v>3</v>
       </c>
       <c r="J926" s="63" t="s">
-        <v>527</v>
+        <v>495</v>
       </c>
       <c r="K926" s="62">
         <v>400</v>
@@ -49070,7 +49067,7 @@
         <v>2</v>
       </c>
       <c r="O926" s="1" t="s">
-        <v>466</v>
+        <v>434</v>
       </c>
       <c r="P926" s="1">
         <v>0</v>
@@ -49105,7 +49102,7 @@
         <v>4</v>
       </c>
       <c r="J927" s="63" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
       <c r="K927" s="62">
         <v>400</v>
@@ -49120,7 +49117,7 @@
         <v>2</v>
       </c>
       <c r="O927" s="1" t="s">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="P927" s="1">
         <v>0</v>
@@ -49155,7 +49152,7 @@
         <v>4</v>
       </c>
       <c r="J928" s="67" t="s">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="K928" s="62">
         <v>400</v>
@@ -49170,7 +49167,7 @@
         <v>2</v>
       </c>
       <c r="O928" s="1" t="s">
-        <v>468</v>
+        <v>436</v>
       </c>
       <c r="P928" s="1">
         <v>0</v>
@@ -49205,7 +49202,7 @@
         <v>4</v>
       </c>
       <c r="J929" s="63" t="s">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="K929" s="62">
         <v>400</v>
@@ -49220,7 +49217,7 @@
         <v>2</v>
       </c>
       <c r="O929" s="1" t="s">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="P929" s="1">
         <v>0</v>
@@ -49255,7 +49252,7 @@
         <v>4</v>
       </c>
       <c r="J930" s="63" t="s">
-        <v>533</v>
+        <v>501</v>
       </c>
       <c r="K930" s="62">
         <v>400</v>
@@ -49270,7 +49267,7 @@
         <v>2</v>
       </c>
       <c r="O930" s="1" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="P930" s="1">
         <v>0</v>
@@ -49305,7 +49302,7 @@
         <v>4</v>
       </c>
       <c r="J931" s="63" t="s">
-        <v>534</v>
+        <v>502</v>
       </c>
       <c r="K931" s="62">
         <v>400</v>
@@ -49320,7 +49317,7 @@
         <v>2</v>
       </c>
       <c r="O931" s="1" t="s">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="P931" s="1">
         <v>0</v>
@@ -49355,7 +49352,7 @@
         <v>4</v>
       </c>
       <c r="J932" s="63" t="s">
-        <v>525</v>
+        <v>493</v>
       </c>
       <c r="K932" s="62">
         <v>400</v>
@@ -49370,7 +49367,7 @@
         <v>2</v>
       </c>
       <c r="O932" s="1" t="s">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="P932" s="1">
         <v>0</v>
@@ -49405,7 +49402,7 @@
         <v>4</v>
       </c>
       <c r="J933" s="63" t="s">
-        <v>535</v>
+        <v>503</v>
       </c>
       <c r="K933" s="62">
         <v>400</v>
@@ -49420,7 +49417,7 @@
         <v>2</v>
       </c>
       <c r="O933" s="1" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="P933" s="1">
         <v>0</v>
@@ -49455,7 +49452,7 @@
         <v>4</v>
       </c>
       <c r="J934" s="63" t="s">
-        <v>527</v>
+        <v>495</v>
       </c>
       <c r="K934" s="62">
         <v>400</v>
@@ -49470,7 +49467,7 @@
         <v>2</v>
       </c>
       <c r="O934" s="1" t="s">
-        <v>474</v>
+        <v>442</v>
       </c>
       <c r="P934" s="1">
         <v>0</v>
@@ -49505,7 +49502,7 @@
         <v>4</v>
       </c>
       <c r="J935" s="63" t="s">
-        <v>536</v>
+        <v>504</v>
       </c>
       <c r="K935" s="62">
         <v>400</v>
@@ -49520,7 +49517,7 @@
         <v>2</v>
       </c>
       <c r="O935" s="1" t="s">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="P935" s="1">
         <v>0</v>
@@ -49555,7 +49552,7 @@
         <v>4</v>
       </c>
       <c r="J936" s="63" t="s">
-        <v>537</v>
+        <v>505</v>
       </c>
       <c r="K936" s="62">
         <v>400</v>
@@ -49570,7 +49567,7 @@
         <v>2</v>
       </c>
       <c r="O936" s="1" t="s">
-        <v>476</v>
+        <v>444</v>
       </c>
       <c r="P936" s="1">
         <v>0</v>
@@ -49605,7 +49602,7 @@
         <v>4</v>
       </c>
       <c r="J937" s="67" t="s">
-        <v>536</v>
+        <v>504</v>
       </c>
       <c r="K937" s="62">
         <v>400</v>
@@ -49620,7 +49617,7 @@
         <v>2</v>
       </c>
       <c r="O937" s="1" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="P937" s="1">
         <v>0</v>
@@ -49655,7 +49652,7 @@
         <v>4</v>
       </c>
       <c r="J938" s="63" t="s">
-        <v>538</v>
+        <v>506</v>
       </c>
       <c r="K938" s="62">
         <v>400</v>
@@ -49670,7 +49667,7 @@
         <v>2</v>
       </c>
       <c r="O938" s="1" t="s">
-        <v>478</v>
+        <v>446</v>
       </c>
       <c r="P938" s="1">
         <v>0</v>
@@ -49705,7 +49702,7 @@
         <v>5</v>
       </c>
       <c r="J939" s="63" t="s">
-        <v>539</v>
+        <v>507</v>
       </c>
       <c r="K939" s="62">
         <v>400</v>
@@ -49720,7 +49717,7 @@
         <v>2</v>
       </c>
       <c r="O939" s="1" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="P939" s="1">
         <v>0</v>
@@ -49755,7 +49752,7 @@
         <v>5</v>
       </c>
       <c r="J940" s="63" t="s">
-        <v>540</v>
+        <v>508</v>
       </c>
       <c r="K940" s="62">
         <v>400</v>
@@ -49770,7 +49767,7 @@
         <v>2</v>
       </c>
       <c r="O940" s="1" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="P940" s="1">
         <v>0</v>
@@ -49805,7 +49802,7 @@
         <v>5</v>
       </c>
       <c r="J941" s="63" t="s">
-        <v>540</v>
+        <v>508</v>
       </c>
       <c r="K941" s="62">
         <v>400</v>
@@ -49820,7 +49817,7 @@
         <v>2</v>
       </c>
       <c r="O941" s="1" t="s">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="P941" s="1">
         <v>0</v>
@@ -49855,7 +49852,7 @@
         <v>5</v>
       </c>
       <c r="J942" s="63" t="s">
-        <v>541</v>
+        <v>509</v>
       </c>
       <c r="K942" s="62">
         <v>400</v>
@@ -49870,7 +49867,7 @@
         <v>2</v>
       </c>
       <c r="O942" s="1" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="P942" s="1">
         <v>0</v>
@@ -49905,7 +49902,7 @@
         <v>5</v>
       </c>
       <c r="J943" s="63" t="s">
-        <v>539</v>
+        <v>507</v>
       </c>
       <c r="K943" s="62">
         <v>400</v>
@@ -49920,7 +49917,7 @@
         <v>2</v>
       </c>
       <c r="O943" s="1" t="s">
-        <v>585</v>
+        <v>553</v>
       </c>
       <c r="P943" s="1">
         <v>0</v>
@@ -49955,7 +49952,7 @@
         <v>5</v>
       </c>
       <c r="J944" s="63" t="s">
-        <v>542</v>
+        <v>510</v>
       </c>
       <c r="K944" s="62">
         <v>400</v>
@@ -49970,7 +49967,7 @@
         <v>2</v>
       </c>
       <c r="O944" s="1" t="s">
-        <v>586</v>
+        <v>554</v>
       </c>
       <c r="P944" s="1">
         <v>0</v>
@@ -50005,7 +50002,7 @@
         <v>5</v>
       </c>
       <c r="J945" s="63" t="s">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="K945" s="62">
         <v>400</v>
@@ -50020,7 +50017,7 @@
         <v>2</v>
       </c>
       <c r="O945" s="1" t="s">
-        <v>587</v>
+        <v>555</v>
       </c>
       <c r="P945" s="1">
         <v>0</v>
@@ -50055,7 +50052,7 @@
         <v>5</v>
       </c>
       <c r="J946" s="63" t="s">
-        <v>544</v>
+        <v>512</v>
       </c>
       <c r="K946" s="62">
         <v>400</v>
@@ -50070,7 +50067,7 @@
         <v>2</v>
       </c>
       <c r="O946" s="1" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="P946" s="1">
         <v>0</v>
@@ -50105,7 +50102,7 @@
         <v>5</v>
       </c>
       <c r="J947" s="67" t="s">
-        <v>539</v>
+        <v>507</v>
       </c>
       <c r="K947" s="62">
         <v>400</v>
@@ -50120,7 +50117,7 @@
         <v>2</v>
       </c>
       <c r="O947" s="1" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
       <c r="P947" s="1">
         <v>0</v>
@@ -50155,7 +50152,7 @@
         <v>5</v>
       </c>
       <c r="J948" s="63" t="s">
-        <v>545</v>
+        <v>513</v>
       </c>
       <c r="K948" s="62">
         <v>400</v>
@@ -50170,7 +50167,7 @@
         <v>2</v>
       </c>
       <c r="O948" s="1" t="s">
-        <v>590</v>
+        <v>558</v>
       </c>
       <c r="P948" s="1">
         <v>0</v>
@@ -50205,7 +50202,7 @@
         <v>5</v>
       </c>
       <c r="J949" s="63" t="s">
-        <v>545</v>
+        <v>513</v>
       </c>
       <c r="K949" s="62">
         <v>400</v>
@@ -50220,7 +50217,7 @@
         <v>2</v>
       </c>
       <c r="O949" s="1" t="s">
-        <v>591</v>
+        <v>559</v>
       </c>
       <c r="P949" s="1">
         <v>0</v>
@@ -50255,7 +50252,7 @@
         <v>5</v>
       </c>
       <c r="J950" s="63" t="s">
-        <v>546</v>
+        <v>514</v>
       </c>
       <c r="K950" s="62">
         <v>400</v>
@@ -50270,7 +50267,7 @@
         <v>2</v>
       </c>
       <c r="O950" s="1" t="s">
-        <v>592</v>
+        <v>560</v>
       </c>
       <c r="P950" s="1">
         <v>0</v>
@@ -50305,7 +50302,7 @@
         <v>5</v>
       </c>
       <c r="J951" s="63" t="s">
-        <v>539</v>
+        <v>507</v>
       </c>
       <c r="K951" s="62">
         <v>400</v>
@@ -50320,7 +50317,7 @@
         <v>2</v>
       </c>
       <c r="O951" s="1" t="s">
-        <v>593</v>
+        <v>561</v>
       </c>
       <c r="P951" s="1">
         <v>0</v>
@@ -50355,7 +50352,7 @@
         <v>5</v>
       </c>
       <c r="J952" s="63" t="s">
-        <v>547</v>
+        <v>515</v>
       </c>
       <c r="K952" s="62">
         <v>400</v>
@@ -50370,7 +50367,7 @@
         <v>2</v>
       </c>
       <c r="O952" s="1" t="s">
-        <v>594</v>
+        <v>562</v>
       </c>
       <c r="P952" s="1">
         <v>0</v>
@@ -50405,7 +50402,7 @@
         <v>1</v>
       </c>
       <c r="J953" s="63" t="s">
-        <v>548</v>
+        <v>516</v>
       </c>
       <c r="K953" s="62">
         <v>6000</v>
@@ -50420,7 +50417,7 @@
         <v>3</v>
       </c>
       <c r="O953" s="1" t="s">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="P953" s="1">
         <v>0</v>
@@ -50455,7 +50452,7 @@
         <v>1</v>
       </c>
       <c r="J954" s="63" t="s">
-        <v>549</v>
+        <v>517</v>
       </c>
       <c r="K954" s="62">
         <v>6000</v>
@@ -50470,7 +50467,7 @@
         <v>3</v>
       </c>
       <c r="O954" s="1" t="s">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="P954" s="1">
         <v>0</v>
@@ -50505,7 +50502,7 @@
         <v>1</v>
       </c>
       <c r="J955" s="69" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="K955" s="62">
         <v>6000</v>
@@ -50520,7 +50517,7 @@
         <v>3</v>
       </c>
       <c r="O955" s="1" t="s">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="P955" s="1">
         <v>0</v>
@@ -50555,7 +50552,7 @@
         <v>1</v>
       </c>
       <c r="J956" s="63" t="s">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="K956" s="62">
         <v>6000</v>
@@ -50570,7 +50567,7 @@
         <v>3</v>
       </c>
       <c r="O956" s="1" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="P956" s="1">
         <v>0</v>
@@ -50605,7 +50602,7 @@
         <v>1</v>
       </c>
       <c r="J957" s="63" t="s">
-        <v>549</v>
+        <v>517</v>
       </c>
       <c r="K957" s="62">
         <v>6000</v>
@@ -50620,7 +50617,7 @@
         <v>3</v>
       </c>
       <c r="O957" s="1" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="P957" s="1">
         <v>0</v>
@@ -50655,7 +50652,7 @@
         <v>1</v>
       </c>
       <c r="J958" s="63" t="s">
-        <v>550</v>
+        <v>518</v>
       </c>
       <c r="K958" s="62">
         <v>6000</v>
@@ -50670,7 +50667,7 @@
         <v>3</v>
       </c>
       <c r="O958" s="1" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="P958" s="1">
         <v>0</v>
@@ -50705,7 +50702,7 @@
         <v>1</v>
       </c>
       <c r="J959" s="67" t="s">
-        <v>552</v>
+        <v>520</v>
       </c>
       <c r="K959" s="62">
         <v>6000</v>
@@ -50720,7 +50717,7 @@
         <v>3</v>
       </c>
       <c r="O959" s="1" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
       <c r="P959" s="1">
         <v>0</v>
@@ -50755,7 +50752,7 @@
         <v>1</v>
       </c>
       <c r="J960" s="63" t="s">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="K960" s="62">
         <v>6000</v>
@@ -50770,7 +50767,7 @@
         <v>3</v>
       </c>
       <c r="O960" s="1" t="s">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="P960" s="1">
         <v>0</v>
@@ -50805,7 +50802,7 @@
         <v>2</v>
       </c>
       <c r="J961" s="63" t="s">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="K961" s="62">
         <v>6000</v>
@@ -50820,7 +50817,7 @@
         <v>3</v>
       </c>
       <c r="O961" s="1" t="s">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="P961" s="1">
         <v>0</v>
@@ -50855,7 +50852,7 @@
         <v>2</v>
       </c>
       <c r="J962" s="63" t="s">
-        <v>553</v>
+        <v>521</v>
       </c>
       <c r="K962" s="62">
         <v>6000</v>
@@ -50870,7 +50867,7 @@
         <v>3</v>
       </c>
       <c r="O962" s="1" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="P962" s="1">
         <v>0</v>
@@ -50905,7 +50902,7 @@
         <v>2</v>
       </c>
       <c r="J963" s="63" t="s">
-        <v>554</v>
+        <v>522</v>
       </c>
       <c r="K963" s="62">
         <v>6000</v>
@@ -50920,7 +50917,7 @@
         <v>3</v>
       </c>
       <c r="O963" s="1" t="s">
-        <v>459</v>
+        <v>427</v>
       </c>
       <c r="P963" s="1">
         <v>0</v>
@@ -50955,7 +50952,7 @@
         <v>2</v>
       </c>
       <c r="J964" s="67" t="s">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="K964" s="62">
         <v>6000</v>
@@ -50970,7 +50967,7 @@
         <v>3</v>
       </c>
       <c r="O964" s="1" t="s">
-        <v>460</v>
+        <v>428</v>
       </c>
       <c r="P964" s="1">
         <v>0</v>
@@ -51005,7 +51002,7 @@
         <v>2</v>
       </c>
       <c r="J965" s="63" t="s">
-        <v>555</v>
+        <v>523</v>
       </c>
       <c r="K965" s="62">
         <v>6000</v>
@@ -51020,7 +51017,7 @@
         <v>3</v>
       </c>
       <c r="O965" s="1" t="s">
-        <v>461</v>
+        <v>429</v>
       </c>
       <c r="P965" s="1">
         <v>0</v>
@@ -51055,7 +51052,7 @@
         <v>2</v>
       </c>
       <c r="J966" s="63" t="s">
-        <v>551</v>
+        <v>519</v>
       </c>
       <c r="K966" s="62">
         <v>6000</v>
@@ -51070,7 +51067,7 @@
         <v>3</v>
       </c>
       <c r="O966" s="1" t="s">
-        <v>462</v>
+        <v>430</v>
       </c>
       <c r="P966" s="1">
         <v>0</v>
@@ -51105,7 +51102,7 @@
         <v>2</v>
       </c>
       <c r="J967" s="63" t="s">
-        <v>556</v>
+        <v>524</v>
       </c>
       <c r="K967" s="62">
         <v>6000</v>
@@ -51120,7 +51117,7 @@
         <v>3</v>
       </c>
       <c r="O967" s="1" t="s">
-        <v>463</v>
+        <v>431</v>
       </c>
       <c r="P967" s="1">
         <v>0</v>
@@ -51155,7 +51152,7 @@
         <v>2</v>
       </c>
       <c r="J968" s="63" t="s">
-        <v>557</v>
+        <v>525</v>
       </c>
       <c r="K968" s="62">
         <v>6000</v>
@@ -51170,7 +51167,7 @@
         <v>3</v>
       </c>
       <c r="O968" s="1" t="s">
-        <v>464</v>
+        <v>432</v>
       </c>
       <c r="P968" s="1">
         <v>0</v>
@@ -51205,7 +51202,7 @@
         <v>2</v>
       </c>
       <c r="J969" s="63" t="s">
-        <v>558</v>
+        <v>526</v>
       </c>
       <c r="K969" s="62">
         <v>6000</v>
@@ -51220,7 +51217,7 @@
         <v>3</v>
       </c>
       <c r="O969" s="1" t="s">
-        <v>465</v>
+        <v>433</v>
       </c>
       <c r="P969" s="1">
         <v>0</v>
@@ -51255,7 +51252,7 @@
         <v>2</v>
       </c>
       <c r="J970" s="63" t="s">
-        <v>554</v>
+        <v>522</v>
       </c>
       <c r="K970" s="62">
         <v>6000</v>
@@ -51270,7 +51267,7 @@
         <v>3</v>
       </c>
       <c r="O970" s="1" t="s">
-        <v>466</v>
+        <v>434</v>
       </c>
       <c r="P970" s="1">
         <v>0</v>
@@ -51305,7 +51302,7 @@
         <v>3</v>
       </c>
       <c r="J971" s="65" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="K971" s="62">
         <v>6000</v>
@@ -51320,7 +51317,7 @@
         <v>3</v>
       </c>
       <c r="O971" s="1" t="s">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="P971" s="1">
         <v>0</v>
@@ -51355,7 +51352,7 @@
         <v>3</v>
       </c>
       <c r="J972" s="63" t="s">
-        <v>560</v>
+        <v>528</v>
       </c>
       <c r="K972" s="62">
         <v>6000</v>
@@ -51370,7 +51367,7 @@
         <v>3</v>
       </c>
       <c r="O972" s="1" t="s">
-        <v>468</v>
+        <v>436</v>
       </c>
       <c r="P972" s="1">
         <v>0</v>
@@ -51405,7 +51402,7 @@
         <v>3</v>
       </c>
       <c r="J973" s="63" t="s">
-        <v>560</v>
+        <v>528</v>
       </c>
       <c r="K973" s="62">
         <v>6000</v>
@@ -51420,7 +51417,7 @@
         <v>3</v>
       </c>
       <c r="O973" s="1" t="s">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="P973" s="1">
         <v>0</v>
@@ -51455,7 +51452,7 @@
         <v>3</v>
       </c>
       <c r="J974" s="63" t="s">
-        <v>561</v>
+        <v>529</v>
       </c>
       <c r="K974" s="62">
         <v>6000</v>
@@ -51470,7 +51467,7 @@
         <v>3</v>
       </c>
       <c r="O974" s="1" t="s">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="P974" s="1">
         <v>0</v>
@@ -51505,7 +51502,7 @@
         <v>3</v>
       </c>
       <c r="J975" s="63" t="s">
-        <v>562</v>
+        <v>530</v>
       </c>
       <c r="K975" s="62">
         <v>6000</v>
@@ -51520,7 +51517,7 @@
         <v>3</v>
       </c>
       <c r="O975" s="1" t="s">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="P975" s="1">
         <v>0</v>
@@ -51555,7 +51552,7 @@
         <v>3</v>
       </c>
       <c r="J976" s="63" t="s">
-        <v>563</v>
+        <v>531</v>
       </c>
       <c r="K976" s="62">
         <v>6000</v>
@@ -51570,7 +51567,7 @@
         <v>3</v>
       </c>
       <c r="O976" s="1" t="s">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="P976" s="1">
         <v>0</v>
@@ -51605,7 +51602,7 @@
         <v>3</v>
       </c>
       <c r="J977" s="63" t="s">
-        <v>564</v>
+        <v>532</v>
       </c>
       <c r="K977" s="62">
         <v>6000</v>
@@ -51620,7 +51617,7 @@
         <v>3</v>
       </c>
       <c r="O977" s="1" t="s">
-        <v>473</v>
+        <v>441</v>
       </c>
       <c r="P977" s="1">
         <v>0</v>
@@ -51655,7 +51652,7 @@
         <v>3</v>
       </c>
       <c r="J978" s="63" t="s">
-        <v>565</v>
+        <v>533</v>
       </c>
       <c r="K978" s="62">
         <v>6000</v>
@@ -51670,7 +51667,7 @@
         <v>3</v>
       </c>
       <c r="O978" s="1" t="s">
-        <v>474</v>
+        <v>442</v>
       </c>
       <c r="P978" s="1">
         <v>0</v>
@@ -51705,7 +51702,7 @@
         <v>3</v>
       </c>
       <c r="J979" s="63" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
       <c r="K979" s="62">
         <v>6000</v>
@@ -51720,7 +51717,7 @@
         <v>3</v>
       </c>
       <c r="O979" s="1" t="s">
-        <v>475</v>
+        <v>443</v>
       </c>
       <c r="P979" s="1">
         <v>0</v>
@@ -51755,7 +51752,7 @@
         <v>3</v>
       </c>
       <c r="J980" s="67" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
       <c r="K980" s="62">
         <v>6000</v>
@@ -51770,7 +51767,7 @@
         <v>3</v>
       </c>
       <c r="O980" s="1" t="s">
-        <v>476</v>
+        <v>444</v>
       </c>
       <c r="P980" s="1">
         <v>0</v>
@@ -51805,7 +51802,7 @@
         <v>3</v>
       </c>
       <c r="J981" s="63" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
       <c r="K981" s="62">
         <v>6000</v>
@@ -51820,7 +51817,7 @@
         <v>3</v>
       </c>
       <c r="O981" s="1" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="P981" s="1">
         <v>0</v>
@@ -51855,7 +51852,7 @@
         <v>3</v>
       </c>
       <c r="J982" s="63" t="s">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="K982" s="62">
         <v>6000</v>
@@ -51870,7 +51867,7 @@
         <v>3</v>
       </c>
       <c r="O982" s="1" t="s">
-        <v>478</v>
+        <v>446</v>
       </c>
       <c r="P982" s="1">
         <v>0</v>
@@ -51905,7 +51902,7 @@
         <v>4</v>
       </c>
       <c r="J983" s="63" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="K983" s="62">
         <v>6000</v>
@@ -51920,7 +51917,7 @@
         <v>3</v>
       </c>
       <c r="O983" s="1" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="P983" s="1">
         <v>0</v>
@@ -51955,7 +51952,7 @@
         <v>4</v>
       </c>
       <c r="J984" s="63" t="s">
-        <v>569</v>
+        <v>537</v>
       </c>
       <c r="K984" s="62">
         <v>6000</v>
@@ -51970,7 +51967,7 @@
         <v>3</v>
       </c>
       <c r="O984" s="1" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="P984" s="1">
         <v>0</v>
@@ -52005,7 +52002,7 @@
         <v>4</v>
       </c>
       <c r="J985" s="63" t="s">
-        <v>569</v>
+        <v>537</v>
       </c>
       <c r="K985" s="62">
         <v>6000</v>
@@ -52020,7 +52017,7 @@
         <v>3</v>
       </c>
       <c r="O985" s="1" t="s">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="P985" s="1">
         <v>0</v>
@@ -52055,7 +52052,7 @@
         <v>4</v>
       </c>
       <c r="J986" s="63" t="s">
-        <v>570</v>
+        <v>538</v>
       </c>
       <c r="K986" s="62">
         <v>6000</v>
@@ -52070,7 +52067,7 @@
         <v>3</v>
       </c>
       <c r="O986" s="1" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="P986" s="1">
         <v>0</v>
@@ -52105,7 +52102,7 @@
         <v>4</v>
       </c>
       <c r="J987" s="63" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="K987" s="62">
         <v>6000</v>
@@ -52120,7 +52117,7 @@
         <v>3</v>
       </c>
       <c r="O987" s="1" t="s">
-        <v>585</v>
+        <v>553</v>
       </c>
       <c r="P987" s="1">
         <v>0</v>
@@ -52155,7 +52152,7 @@
         <v>4</v>
       </c>
       <c r="J988" s="63" t="s">
-        <v>568</v>
+        <v>536</v>
       </c>
       <c r="K988" s="62">
         <v>6000</v>
@@ -52170,7 +52167,7 @@
         <v>3</v>
       </c>
       <c r="O988" s="1" t="s">
-        <v>586</v>
+        <v>554</v>
       </c>
       <c r="P988" s="1">
         <v>0</v>
@@ -52205,7 +52202,7 @@
         <v>4</v>
       </c>
       <c r="J989" s="63" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
       <c r="K989" s="62">
         <v>6000</v>
@@ -52220,7 +52217,7 @@
         <v>3</v>
       </c>
       <c r="O989" s="1" t="s">
-        <v>587</v>
+        <v>555</v>
       </c>
       <c r="P989" s="1">
         <v>0</v>
@@ -52255,7 +52252,7 @@
         <v>4</v>
       </c>
       <c r="J990" s="67" t="s">
-        <v>562</v>
+        <v>530</v>
       </c>
       <c r="K990" s="62">
         <v>6000</v>
@@ -52270,7 +52267,7 @@
         <v>3</v>
       </c>
       <c r="O990" s="1" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="P990" s="1">
         <v>0</v>
@@ -52305,7 +52302,7 @@
         <v>4</v>
       </c>
       <c r="J991" s="63" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="K991" s="62">
         <v>6000</v>
@@ -52320,7 +52317,7 @@
         <v>3</v>
       </c>
       <c r="O991" s="1" t="s">
-        <v>589</v>
+        <v>557</v>
       </c>
       <c r="P991" s="1">
         <v>0</v>
@@ -52355,7 +52352,7 @@
         <v>4</v>
       </c>
       <c r="J992" s="63" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
       <c r="K992" s="62">
         <v>6000</v>
@@ -52370,7 +52367,7 @@
         <v>3</v>
       </c>
       <c r="O992" s="1" t="s">
-        <v>590</v>
+        <v>558</v>
       </c>
       <c r="P992" s="1">
         <v>0</v>
@@ -52405,7 +52402,7 @@
         <v>4</v>
       </c>
       <c r="J993" s="63" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
       <c r="K993" s="62">
         <v>6000</v>
@@ -52420,7 +52417,7 @@
         <v>3</v>
       </c>
       <c r="O993" s="1" t="s">
-        <v>591</v>
+        <v>559</v>
       </c>
       <c r="P993" s="1">
         <v>0</v>
@@ -52455,7 +52452,7 @@
         <v>4</v>
       </c>
       <c r="J994" s="63" t="s">
-        <v>572</v>
+        <v>540</v>
       </c>
       <c r="K994" s="62">
         <v>6000</v>
@@ -52470,7 +52467,7 @@
         <v>3</v>
       </c>
       <c r="O994" s="1" t="s">
-        <v>592</v>
+        <v>560</v>
       </c>
       <c r="P994" s="1">
         <v>0</v>
@@ -52505,7 +52502,7 @@
         <v>4</v>
       </c>
       <c r="J995" s="63" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="K995" s="62">
         <v>6000</v>
@@ -52520,7 +52517,7 @@
         <v>3</v>
       </c>
       <c r="O995" s="1" t="s">
-        <v>593</v>
+        <v>561</v>
       </c>
       <c r="P995" s="1">
         <v>0</v>
@@ -52570,7 +52567,7 @@
         <v>3</v>
       </c>
       <c r="O996" s="1" t="s">
-        <v>594</v>
+        <v>562</v>
       </c>
       <c r="P996" s="1">
         <v>0</v>
@@ -52605,7 +52602,7 @@
         <v>5</v>
       </c>
       <c r="J997" s="63" t="s">
-        <v>573</v>
+        <v>541</v>
       </c>
       <c r="K997" s="62">
         <v>6000</v>
@@ -52620,7 +52617,7 @@
         <v>3</v>
       </c>
       <c r="O997" s="1" t="s">
-        <v>595</v>
+        <v>563</v>
       </c>
       <c r="P997" s="1">
         <v>0</v>
@@ -52655,7 +52652,7 @@
         <v>5</v>
       </c>
       <c r="J998" s="63" t="s">
-        <v>574</v>
+        <v>542</v>
       </c>
       <c r="K998" s="62">
         <v>6000</v>
@@ -52670,7 +52667,7 @@
         <v>3</v>
       </c>
       <c r="O998" s="1" t="s">
-        <v>596</v>
+        <v>564</v>
       </c>
       <c r="P998" s="1">
         <v>0</v>
@@ -52705,7 +52702,7 @@
         <v>5</v>
       </c>
       <c r="J999" s="63" t="s">
-        <v>574</v>
+        <v>542</v>
       </c>
       <c r="K999" s="62">
         <v>6000</v>
@@ -52720,7 +52717,7 @@
         <v>3</v>
       </c>
       <c r="O999" s="1" t="s">
-        <v>597</v>
+        <v>565</v>
       </c>
       <c r="P999" s="1">
         <v>0</v>
@@ -52755,7 +52752,7 @@
         <v>5</v>
       </c>
       <c r="J1000" s="63" t="s">
-        <v>575</v>
+        <v>543</v>
       </c>
       <c r="K1000" s="62">
         <v>6000</v>
@@ -52770,7 +52767,7 @@
         <v>3</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>598</v>
+        <v>566</v>
       </c>
       <c r="P1000" s="1">
         <v>0</v>
@@ -52805,7 +52802,7 @@
         <v>5</v>
       </c>
       <c r="J1001" s="63" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="K1001" s="62">
         <v>6000</v>
@@ -52820,7 +52817,7 @@
         <v>3</v>
       </c>
       <c r="O1001" s="1" t="s">
-        <v>599</v>
+        <v>567</v>
       </c>
       <c r="P1001" s="1">
         <v>0</v>
@@ -52855,7 +52852,7 @@
         <v>5</v>
       </c>
       <c r="J1002" s="67" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="K1002" s="62">
         <v>6000</v>
@@ -52870,7 +52867,7 @@
         <v>3</v>
       </c>
       <c r="O1002" s="1" t="s">
-        <v>600</v>
+        <v>568</v>
       </c>
       <c r="P1002" s="1">
         <v>0</v>
@@ -52905,7 +52902,7 @@
         <v>5</v>
       </c>
       <c r="J1003" s="63" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="K1003" s="62">
         <v>6000</v>
@@ -52920,7 +52917,7 @@
         <v>3</v>
       </c>
       <c r="O1003" s="1" t="s">
-        <v>601</v>
+        <v>569</v>
       </c>
       <c r="P1003" s="1">
         <v>0</v>
@@ -52955,7 +52952,7 @@
         <v>5</v>
       </c>
       <c r="J1004" s="63" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="K1004" s="62">
         <v>6000</v>
@@ -52970,7 +52967,7 @@
         <v>3</v>
       </c>
       <c r="O1004" s="1" t="s">
-        <v>602</v>
+        <v>570</v>
       </c>
       <c r="P1004" s="1">
         <v>0</v>
@@ -53005,7 +53002,7 @@
         <v>5</v>
       </c>
       <c r="J1005" s="63" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="K1005" s="62">
         <v>6000</v>
@@ -53020,7 +53017,7 @@
         <v>3</v>
       </c>
       <c r="O1005" s="1" t="s">
-        <v>603</v>
+        <v>571</v>
       </c>
       <c r="P1005" s="1">
         <v>0</v>
@@ -53055,7 +53052,7 @@
         <v>5</v>
       </c>
       <c r="J1006" s="63" t="s">
-        <v>578</v>
+        <v>546</v>
       </c>
       <c r="K1006" s="62">
         <v>6000</v>
@@ -53070,7 +53067,7 @@
         <v>3</v>
       </c>
       <c r="O1006" s="1" t="s">
-        <v>604</v>
+        <v>572</v>
       </c>
       <c r="P1006" s="1">
         <v>0</v>
@@ -53105,7 +53102,7 @@
         <v>5</v>
       </c>
       <c r="J1007" s="63" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="K1007" s="62">
         <v>6000</v>
@@ -53120,7 +53117,7 @@
         <v>3</v>
       </c>
       <c r="O1007" s="1" t="s">
-        <v>605</v>
+        <v>573</v>
       </c>
       <c r="P1007" s="1">
         <v>0</v>
@@ -53155,7 +53152,7 @@
         <v>5</v>
       </c>
       <c r="J1008" s="63" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="K1008" s="62">
         <v>6000</v>
@@ -53170,7 +53167,7 @@
         <v>3</v>
       </c>
       <c r="O1008" s="1" t="s">
-        <v>606</v>
+        <v>574</v>
       </c>
       <c r="P1008" s="1">
         <v>0</v>
@@ -53205,7 +53202,7 @@
         <v>5</v>
       </c>
       <c r="J1009" s="63" t="s">
-        <v>578</v>
+        <v>546</v>
       </c>
       <c r="K1009" s="62">
         <v>6000</v>
@@ -53220,7 +53217,7 @@
         <v>3</v>
       </c>
       <c r="O1009" s="1" t="s">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="P1009" s="1">
         <v>0</v>
@@ -53255,7 +53252,7 @@
         <v>5</v>
       </c>
       <c r="J1010" s="63" t="s">
-        <v>576</v>
+        <v>544</v>
       </c>
       <c r="K1010" s="62">
         <v>6000</v>
@@ -53270,7 +53267,7 @@
         <v>3</v>
       </c>
       <c r="O1010" s="1" t="s">
-        <v>608</v>
+        <v>576</v>
       </c>
       <c r="P1010" s="1">
         <v>0</v>
@@ -53305,7 +53302,7 @@
         <v>5</v>
       </c>
       <c r="J1011" s="63" t="s">
-        <v>579</v>
+        <v>547</v>
       </c>
       <c r="K1011" s="62">
         <v>6000</v>
@@ -53320,7 +53317,7 @@
         <v>3</v>
       </c>
       <c r="O1011" s="1" t="s">
-        <v>609</v>
+        <v>577</v>
       </c>
       <c r="P1011" s="1">
         <v>0</v>
@@ -53355,7 +53352,7 @@
         <v>5</v>
       </c>
       <c r="J1012" s="63" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
       <c r="K1012" s="62">
         <v>6000</v>
@@ -53370,7 +53367,7 @@
         <v>3</v>
       </c>
       <c r="O1012" s="1" t="s">
-        <v>610</v>
+        <v>578</v>
       </c>
       <c r="P1012" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16062F5-BFF6-44F6-8511-4555382458A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD1ABA6-C951-4148-AD1B-AEFB8DA5F650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="611">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1877,97 +1877,100 @@
     <t>60,40,60,50,60,60,65,45,65,55</t>
   </si>
   <si>
-    <t>88,28</t>
-  </si>
-  <si>
-    <t>88,35,95,62</t>
-  </si>
-  <si>
-    <t>85,40</t>
-  </si>
-  <si>
-    <t>88,15</t>
-  </si>
-  <si>
-    <t>88,15,66,62</t>
-  </si>
-  <si>
-    <t>88,28,60,57</t>
-  </si>
-  <si>
-    <t>36,65,36,60</t>
-  </si>
-  <si>
-    <t>40,60,36,5</t>
-  </si>
-  <si>
-    <t>40,60,40,10</t>
-  </si>
-  <si>
-    <t>45,60,40,65,40,55</t>
-  </si>
-  <si>
-    <t>45,10,45,15</t>
-  </si>
-  <si>
-    <t>40,50,40,45,50,10</t>
-  </si>
-  <si>
-    <t>45,50,45,45</t>
-  </si>
-  <si>
-    <t>40,65,47,65,70,60</t>
-  </si>
-  <si>
-    <t>44,56,75,50,75,55</t>
-  </si>
-  <si>
-    <t>40,65,47,65</t>
-  </si>
-  <si>
-    <t>40,65,47,65,70,50</t>
-  </si>
-  <si>
-    <t>44,56,70,45,70,40</t>
-  </si>
-  <si>
-    <t>40,65,47,65,75,35</t>
-  </si>
-  <si>
-    <t>44,65,75,30</t>
-  </si>
-  <si>
-    <t>40,75,47,75,20,90</t>
-  </si>
-  <si>
-    <t>44,70,15,85,15,80</t>
-  </si>
-  <si>
-    <t>40,80,47,80</t>
-  </si>
-  <si>
-    <t>44,70,10,90,10,80</t>
-  </si>
-  <si>
-    <t>40,80,47,80,44,85</t>
-  </si>
-  <si>
-    <t>44,80,15,70,15,75</t>
-  </si>
-  <si>
-    <t>44,70,40,80,47,80</t>
-  </si>
-  <si>
-    <t>44,80,10,70,10,75</t>
-  </si>
-  <si>
-    <t>44,70,15,70,15,75</t>
-  </si>
-  <si>
-    <t>44,80,30,95,35,95</t>
-  </si>
-  <si>
-    <t>44,85,25,95,40,95</t>
+    <t>90,25</t>
+  </si>
+  <si>
+    <t>90,30,95,47</t>
+  </si>
+  <si>
+    <t>85,35</t>
+  </si>
+  <si>
+    <t>90,12</t>
+  </si>
+  <si>
+    <t>90,12,60,48</t>
+  </si>
+  <si>
+    <t>90,15,55,45</t>
+  </si>
+  <si>
+    <t>87,15,93,15</t>
+  </si>
+  <si>
+    <t>40,50,41,10</t>
+  </si>
+  <si>
+    <t>40,45,46,10</t>
+  </si>
+  <si>
+    <t>45,45,40,50,40,40</t>
+  </si>
+  <si>
+    <t>41,15,46,15</t>
+  </si>
+  <si>
+    <t>40,45,40,40,43,15</t>
+  </si>
+  <si>
+    <t>40,45,40,40</t>
+  </si>
+  <si>
+    <t>40,50,47,50,75,40</t>
+  </si>
+  <si>
+    <t>44,45,80,46,80,34</t>
+  </si>
+  <si>
+    <t>40,48,47,48</t>
+  </si>
+  <si>
+    <t>40,52,47,52,80,40</t>
+  </si>
+  <si>
+    <t>44,45,75,46,75,34</t>
+  </si>
+  <si>
+    <t>40,55,47,55</t>
+  </si>
+  <si>
+    <t>40,55,47,55,85,46</t>
+  </si>
+  <si>
+    <t>44,50,85,34</t>
+  </si>
+  <si>
+    <t>40,70,47,70,10,90</t>
+  </si>
+  <si>
+    <t>44,65,5,95,5,85</t>
+  </si>
+  <si>
+    <t>40,75,47,75</t>
+  </si>
+  <si>
+    <t>44,65,10,95,10,85</t>
+  </si>
+  <si>
+    <t>40,80,44,80,47,80</t>
+  </si>
+  <si>
+    <t>44,75,15,95,15,85</t>
+  </si>
+  <si>
+    <t>44,65,47,80,44,80</t>
+  </si>
+  <si>
+    <t>44,75,5,90,15,90</t>
+  </si>
+  <si>
+    <t>44,65,47,85,44,85</t>
+  </si>
+  <si>
+    <t>44,80,5,80,15,80</t>
+  </si>
+  <si>
+    <t>44,85,10,80,10,75</t>
   </si>
 </sst>
 </file>
@@ -45217,7 +45220,7 @@
         <v>0</v>
       </c>
       <c r="O849" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="P849" s="1">
         <v>0</v>
@@ -45267,7 +45270,7 @@
         <v>0</v>
       </c>
       <c r="O850" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P850" s="1">
         <v>0</v>
@@ -45317,7 +45320,7 @@
         <v>0</v>
       </c>
       <c r="O851" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P851" s="1">
         <v>0</v>
@@ -45367,7 +45370,7 @@
         <v>0</v>
       </c>
       <c r="O852" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P852" s="1">
         <v>0</v>
@@ -45417,7 +45420,7 @@
         <v>0</v>
       </c>
       <c r="O853" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="P853" s="1">
         <v>0</v>
@@ -45467,7 +45470,7 @@
         <v>0</v>
       </c>
       <c r="O854" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P854" s="1">
         <v>0</v>
@@ -45517,7 +45520,7 @@
         <v>0</v>
       </c>
       <c r="O855" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P855" s="1">
         <v>0</v>
@@ -45567,7 +45570,7 @@
         <v>0</v>
       </c>
       <c r="O856" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P856" s="1">
         <v>0</v>
@@ -45617,7 +45620,7 @@
         <v>0</v>
       </c>
       <c r="O857" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P857" s="1">
         <v>0</v>
@@ -45667,7 +45670,7 @@
         <v>0</v>
       </c>
       <c r="O858" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P858" s="1">
         <v>0</v>
@@ -45717,7 +45720,7 @@
         <v>0</v>
       </c>
       <c r="O859" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P859" s="1">
         <v>0</v>
@@ -45767,7 +45770,7 @@
         <v>0</v>
       </c>
       <c r="O860" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P860" s="1">
         <v>0</v>
@@ -45817,7 +45820,7 @@
         <v>0</v>
       </c>
       <c r="O861" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P861" s="1">
         <v>0</v>
@@ -45867,7 +45870,7 @@
         <v>0</v>
       </c>
       <c r="O862" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P862" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0E5FEE-AF0E-4CA9-B21C-36B7E6153624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A215EC5-A953-424A-8A87-C29322BC6869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="522">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1484,17 +1484,6 @@
     <t>44,85,10,80,10,75</t>
   </si>
   <si>
-    <t>80,50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>72104</t>
-  </si>
-  <si>
-    <t>72104</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>90,40</t>
   </si>
   <si>
@@ -1515,6 +1504,210 @@
   <si>
     <t>50,20</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>75,20,75,10</t>
+  </si>
+  <si>
+    <t>75,15,68,18</t>
+  </si>
+  <si>
+    <t>72,15,63,24,63,12</t>
+  </si>
+  <si>
+    <t>70,15,70,20,70,10</t>
+  </si>
+  <si>
+    <t>60,60,65,60,70,95</t>
+  </si>
+  <si>
+    <t>63,55,75,90,80,90</t>
+  </si>
+  <si>
+    <t>60,60,65,60,70,60</t>
+  </si>
+  <si>
+    <t>63,55,75,95,80,95</t>
+  </si>
+  <si>
+    <t>60,60,65,60,65,95</t>
+  </si>
+  <si>
+    <t>60,65,65,65,70,65,65,90</t>
+  </si>
+  <si>
+    <t>55,90,60,85,55,80,85,15</t>
+  </si>
+  <si>
+    <t>60,85,55,90,55,80,80,15</t>
+  </si>
+  <si>
+    <t>50,90,55,85,50,80</t>
+  </si>
+  <si>
+    <t>50,90,50,80,85,10,80,10</t>
+  </si>
+  <si>
+    <t>55,85,75,10,75,15</t>
+  </si>
+  <si>
+    <t>45,90,50,85,45,80</t>
+  </si>
+  <si>
+    <t>55,85,69,10,69,15</t>
+  </si>
+  <si>
+    <t>45,90,45,80,63,10,63,15</t>
+  </si>
+  <si>
+    <t>80,80,72,80,40,90,35,80</t>
+  </si>
+  <si>
+    <t>75,70,83,80,67,80,35,90</t>
+  </si>
+  <si>
+    <t>65,90,65,80,65,70,65,60</t>
+  </si>
+  <si>
+    <t>65,80,65,70,40,80,40,70</t>
+  </si>
+  <si>
+    <t>70,80,70,70,65,90,65,60</t>
+  </si>
+  <si>
+    <t>60,80,60,70,40,80,45,70</t>
+  </si>
+  <si>
+    <t>65,75,60,90,60,60,55,75</t>
+  </si>
+  <si>
+    <t>30,90,30,80,30,70,30,60</t>
+  </si>
+  <si>
+    <t>65,75,55,90,55,60,25,80,25,60</t>
+  </si>
+  <si>
+    <t>50,90,50,80,50,70,50,60</t>
+  </si>
+  <si>
+    <t>26,20,32,20,29,25,15,85,10,75</t>
+  </si>
+  <si>
+    <t>45,70,50,60,50,80,75,80</t>
+  </si>
+  <si>
+    <t>45,65,50,55,50,75,75,60</t>
+  </si>
+  <si>
+    <t>50,50,50,70,75,70,80,80,80,60</t>
+  </si>
+  <si>
+    <t>29,30,26,20,32,20,26,15,32,15</t>
+  </si>
+  <si>
+    <t>26,20,32,20,20,85,15,75</t>
+  </si>
+  <si>
+    <t>45,80,45,60,70,55,70,70,70,85</t>
+  </si>
+  <si>
+    <t>50,50,50,70,55,60,55,80</t>
+  </si>
+  <si>
+    <t>27,35,31,35,30,90,35,90</t>
+  </si>
+  <si>
+    <t>29,35,26,20,32,20,25,90</t>
+  </si>
+  <si>
+    <t>45,80,45,60,80,70,80,50</t>
+  </si>
+  <si>
+    <t>45,75,45,55,50,50,50,70,55,60</t>
+  </si>
+  <si>
+    <t>72104,72104</t>
+  </si>
+  <si>
+    <t>72104,72101</t>
+  </si>
+  <si>
+    <t>72104,72101,72101</t>
+  </si>
+  <si>
+    <t>72104,72104,72104</t>
+  </si>
+  <si>
+    <t>72104,72104,72101</t>
+  </si>
+  <si>
+    <t>72107,72101,72101</t>
+  </si>
+  <si>
+    <t>72104,72104,72104,72101</t>
+  </si>
+  <si>
+    <t>72105,72105,72105,72102</t>
+  </si>
+  <si>
+    <t>72108,72102,72102</t>
+  </si>
+  <si>
+    <t>72105,72105,72105</t>
+  </si>
+  <si>
+    <t>72105,72105,72102,72102</t>
+  </si>
+  <si>
+    <t>72111,72102,72102</t>
+  </si>
+  <si>
+    <t>72108,72105,72105,72102</t>
+  </si>
+  <si>
+    <t>72105,72105,72105,72105</t>
+  </si>
+  <si>
+    <t>72108,72108,72105,72105</t>
+  </si>
+  <si>
+    <t>72111,72105,72105,72105</t>
+  </si>
+  <si>
+    <t>72102,72102,72102,72102</t>
+  </si>
+  <si>
+    <t>72108,72105,72105,72102,72102</t>
+  </si>
+  <si>
+    <t>72106,72106,72106,72103,72103</t>
+  </si>
+  <si>
+    <t>72109,72106,72106,72103</t>
+  </si>
+  <si>
+    <t>72106,72106,72103,72103,72103</t>
+  </si>
+  <si>
+    <t>72112,72106,72106,72106,72106</t>
+  </si>
+  <si>
+    <t>72106,72106,72103,72103</t>
+  </si>
+  <si>
+    <t>72109,72109,72103,72103,72103</t>
+  </si>
+  <si>
+    <t>72106,72106,72106,72106</t>
+  </si>
+  <si>
+    <t>72109,72109,72103,72103</t>
+  </si>
+  <si>
+    <t>72112,72106,72106,72103</t>
+  </si>
+  <si>
+    <t>72109,72109,72106,72106,72106</t>
   </si>
 </sst>
 </file>
@@ -43855,7 +44048,7 @@
         <v>0</v>
       </c>
       <c r="O831" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="P831" s="1">
         <v>0</v>
@@ -43905,7 +44098,7 @@
         <v>0</v>
       </c>
       <c r="O832" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="P832" s="1">
         <v>0</v>
@@ -45440,7 +45633,7 @@
         <v>1</v>
       </c>
       <c r="J863" s="61" t="s">
-        <v>450</v>
+        <v>494</v>
       </c>
       <c r="K863" s="60">
         <v>30</v>
@@ -45455,7 +45648,7 @@
         <v>1</v>
       </c>
       <c r="O863" s="1" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P863" s="1">
         <v>0</v>
@@ -45490,7 +45683,7 @@
         <v>1</v>
       </c>
       <c r="J864" s="61" t="s">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="K864" s="60">
         <v>30</v>
@@ -45505,7 +45698,7 @@
         <v>1</v>
       </c>
       <c r="O864" s="1" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="P864" s="1">
         <v>0</v>
@@ -45540,7 +45733,7 @@
         <v>1</v>
       </c>
       <c r="J865" s="61" t="s">
-        <v>449</v>
+        <v>496</v>
       </c>
       <c r="K865" s="60">
         <v>30</v>
@@ -45555,7 +45748,7 @@
         <v>1</v>
       </c>
       <c r="O865" s="1" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="P865" s="1">
         <v>0</v>
@@ -45590,7 +45783,7 @@
         <v>1</v>
       </c>
       <c r="J866" s="61" t="s">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="K866" s="60">
         <v>30</v>
@@ -45605,7 +45798,7 @@
         <v>1</v>
       </c>
       <c r="O866" s="1" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="P866" s="1">
         <v>0</v>
@@ -45640,7 +45833,7 @@
         <v>2</v>
       </c>
       <c r="J867" s="61" t="s">
-        <v>449</v>
+        <v>498</v>
       </c>
       <c r="K867" s="60">
         <v>30</v>
@@ -45655,7 +45848,7 @@
         <v>1</v>
       </c>
       <c r="O867" s="1" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="P867" s="1">
         <v>0</v>
@@ -45690,7 +45883,7 @@
         <v>2</v>
       </c>
       <c r="J868" s="61" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="K868" s="60">
         <v>30</v>
@@ -45705,7 +45898,7 @@
         <v>1</v>
       </c>
       <c r="O868" s="1" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="P868" s="1">
         <v>0</v>
@@ -45740,7 +45933,7 @@
         <v>2</v>
       </c>
       <c r="J869" s="61" t="s">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="K869" s="60">
         <v>30</v>
@@ -45755,7 +45948,7 @@
         <v>1</v>
       </c>
       <c r="O869" s="1" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="P869" s="1">
         <v>0</v>
@@ -45790,7 +45983,7 @@
         <v>2</v>
       </c>
       <c r="J870" s="61" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="K870" s="60">
         <v>30</v>
@@ -45805,7 +45998,7 @@
         <v>1</v>
       </c>
       <c r="O870" s="1" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="P870" s="1">
         <v>0</v>
@@ -45840,7 +46033,7 @@
         <v>2</v>
       </c>
       <c r="J871" s="61" t="s">
-        <v>449</v>
+        <v>498</v>
       </c>
       <c r="K871" s="60">
         <v>30</v>
@@ -45855,7 +46048,7 @@
         <v>1</v>
       </c>
       <c r="O871" s="1" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="P871" s="1">
         <v>0</v>
@@ -45890,7 +46083,7 @@
         <v>2</v>
       </c>
       <c r="J872" s="61" t="s">
-        <v>449</v>
+        <v>500</v>
       </c>
       <c r="K872" s="60">
         <v>30</v>
@@ -45905,7 +46098,7 @@
         <v>1</v>
       </c>
       <c r="O872" s="1" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="P872" s="1">
         <v>0</v>
@@ -45940,7 +46133,7 @@
         <v>3</v>
       </c>
       <c r="J873" s="61" t="s">
-        <v>449</v>
+        <v>501</v>
       </c>
       <c r="K873" s="60">
         <v>30</v>
@@ -45955,7 +46148,7 @@
         <v>1</v>
       </c>
       <c r="O873" s="1" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="P873" s="1">
         <v>0</v>
@@ -45990,7 +46183,7 @@
         <v>3</v>
       </c>
       <c r="J874" s="61" t="s">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="K874" s="60">
         <v>30</v>
@@ -46005,7 +46198,7 @@
         <v>1</v>
       </c>
       <c r="O874" s="1" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="P874" s="1">
         <v>0</v>
@@ -46040,7 +46233,7 @@
         <v>3</v>
       </c>
       <c r="J875" s="61" t="s">
-        <v>449</v>
+        <v>503</v>
       </c>
       <c r="K875" s="60">
         <v>30</v>
@@ -46055,7 +46248,7 @@
         <v>1</v>
       </c>
       <c r="O875" s="1" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="P875" s="1">
         <v>0</v>
@@ -46090,7 +46283,7 @@
         <v>3</v>
       </c>
       <c r="J876" s="61" t="s">
-        <v>449</v>
+        <v>504</v>
       </c>
       <c r="K876" s="60">
         <v>30</v>
@@ -46105,7 +46298,7 @@
         <v>1</v>
       </c>
       <c r="O876" s="1" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="P876" s="1">
         <v>0</v>
@@ -46140,7 +46333,7 @@
         <v>3</v>
       </c>
       <c r="J877" s="61" t="s">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="K877" s="60">
         <v>30</v>
@@ -46155,7 +46348,7 @@
         <v>1</v>
       </c>
       <c r="O877" s="1" t="s">
-        <v>448</v>
+        <v>468</v>
       </c>
       <c r="P877" s="1">
         <v>0</v>
@@ -46190,7 +46383,7 @@
         <v>3</v>
       </c>
       <c r="J878" s="61" t="s">
-        <v>449</v>
+        <v>503</v>
       </c>
       <c r="K878" s="60">
         <v>30</v>
@@ -46205,7 +46398,7 @@
         <v>1</v>
       </c>
       <c r="O878" s="1" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="P878" s="1">
         <v>0</v>
@@ -46240,7 +46433,7 @@
         <v>3</v>
       </c>
       <c r="J879" s="61" t="s">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="K879" s="60">
         <v>30</v>
@@ -46255,7 +46448,7 @@
         <v>1</v>
       </c>
       <c r="O879" s="1" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="P879" s="1">
         <v>0</v>
@@ -46290,7 +46483,7 @@
         <v>3</v>
       </c>
       <c r="J880" s="61" t="s">
-        <v>449</v>
+        <v>504</v>
       </c>
       <c r="K880" s="60">
         <v>30</v>
@@ -46305,7 +46498,7 @@
         <v>1</v>
       </c>
       <c r="O880" s="1" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="P880" s="1">
         <v>0</v>
@@ -46340,7 +46533,7 @@
         <v>4</v>
       </c>
       <c r="J881" s="61" t="s">
-        <v>449</v>
+        <v>504</v>
       </c>
       <c r="K881" s="60">
         <v>30</v>
@@ -46355,7 +46548,7 @@
         <v>1</v>
       </c>
       <c r="O881" s="1" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="P881" s="1">
         <v>0</v>
@@ -46390,7 +46583,7 @@
         <v>4</v>
       </c>
       <c r="J882" s="61" t="s">
-        <v>449</v>
+        <v>506</v>
       </c>
       <c r="K882" s="60">
         <v>30</v>
@@ -46405,7 +46598,7 @@
         <v>1</v>
       </c>
       <c r="O882" s="1" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="P882" s="1">
         <v>0</v>
@@ -46440,7 +46633,7 @@
         <v>4</v>
       </c>
       <c r="J883" s="61" t="s">
-        <v>449</v>
+        <v>507</v>
       </c>
       <c r="K883" s="60">
         <v>30</v>
@@ -46455,7 +46648,7 @@
         <v>1</v>
       </c>
       <c r="O883" s="1" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="P883" s="1">
         <v>0</v>
@@ -46490,7 +46683,7 @@
         <v>4</v>
       </c>
       <c r="J884" s="61" t="s">
-        <v>449</v>
+        <v>504</v>
       </c>
       <c r="K884" s="60">
         <v>30</v>
@@ -46505,7 +46698,7 @@
         <v>1</v>
       </c>
       <c r="O884" s="1" t="s">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="P884" s="1">
         <v>0</v>
@@ -46540,7 +46733,7 @@
         <v>4</v>
       </c>
       <c r="J885" s="61" t="s">
-        <v>449</v>
+        <v>508</v>
       </c>
       <c r="K885" s="60">
         <v>30</v>
@@ -46555,7 +46748,7 @@
         <v>1</v>
       </c>
       <c r="O885" s="1" t="s">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="P885" s="1">
         <v>0</v>
@@ -46590,7 +46783,7 @@
         <v>4</v>
       </c>
       <c r="J886" s="61" t="s">
-        <v>449</v>
+        <v>504</v>
       </c>
       <c r="K886" s="60">
         <v>30</v>
@@ -46605,7 +46798,7 @@
         <v>1</v>
       </c>
       <c r="O886" s="1" t="s">
-        <v>448</v>
+        <v>477</v>
       </c>
       <c r="P886" s="1">
         <v>0</v>
@@ -46640,7 +46833,7 @@
         <v>4</v>
       </c>
       <c r="J887" s="61" t="s">
-        <v>449</v>
+        <v>509</v>
       </c>
       <c r="K887" s="60">
         <v>30</v>
@@ -46655,7 +46848,7 @@
         <v>1</v>
       </c>
       <c r="O887" s="1" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="P887" s="1">
         <v>0</v>
@@ -46690,7 +46883,7 @@
         <v>4</v>
       </c>
       <c r="J888" s="61" t="s">
-        <v>449</v>
+        <v>510</v>
       </c>
       <c r="K888" s="60">
         <v>30</v>
@@ -46705,7 +46898,7 @@
         <v>1</v>
       </c>
       <c r="O888" s="1" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="P888" s="1">
         <v>0</v>
@@ -46740,7 +46933,7 @@
         <v>4</v>
       </c>
       <c r="J889" s="61" t="s">
-        <v>449</v>
+        <v>511</v>
       </c>
       <c r="K889" s="60">
         <v>30</v>
@@ -46755,7 +46948,7 @@
         <v>1</v>
       </c>
       <c r="O889" s="1" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="P889" s="1">
         <v>0</v>
@@ -46790,7 +46983,7 @@
         <v>4</v>
       </c>
       <c r="J890" s="61" t="s">
-        <v>449</v>
+        <v>507</v>
       </c>
       <c r="K890" s="60">
         <v>30</v>
@@ -46805,7 +46998,7 @@
         <v>1</v>
       </c>
       <c r="O890" s="1" t="s">
-        <v>448</v>
+        <v>481</v>
       </c>
       <c r="P890" s="1">
         <v>0</v>
@@ -46840,7 +47033,7 @@
         <v>5</v>
       </c>
       <c r="J891" s="61" t="s">
-        <v>449</v>
+        <v>512</v>
       </c>
       <c r="K891" s="60">
         <v>30</v>
@@ -46855,7 +47048,7 @@
         <v>1</v>
       </c>
       <c r="O891" s="1" t="s">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="P891" s="1">
         <v>0</v>
@@ -46890,7 +47083,7 @@
         <v>5</v>
       </c>
       <c r="J892" s="61" t="s">
-        <v>449</v>
+        <v>513</v>
       </c>
       <c r="K892" s="60">
         <v>30</v>
@@ -46905,7 +47098,7 @@
         <v>1</v>
       </c>
       <c r="O892" s="1" t="s">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="P892" s="1">
         <v>0</v>
@@ -46940,7 +47133,7 @@
         <v>5</v>
       </c>
       <c r="J893" s="63" t="s">
-        <v>449</v>
+        <v>513</v>
       </c>
       <c r="K893" s="60">
         <v>30</v>
@@ -46955,7 +47148,7 @@
         <v>1</v>
       </c>
       <c r="O893" s="1" t="s">
-        <v>448</v>
+        <v>484</v>
       </c>
       <c r="P893" s="1">
         <v>0</v>
@@ -46990,7 +47183,7 @@
         <v>5</v>
       </c>
       <c r="J894" s="63" t="s">
-        <v>449</v>
+        <v>514</v>
       </c>
       <c r="K894" s="60">
         <v>30</v>
@@ -47005,7 +47198,7 @@
         <v>1</v>
       </c>
       <c r="O894" s="1" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="P894" s="1">
         <v>0</v>
@@ -47040,7 +47233,7 @@
         <v>5</v>
       </c>
       <c r="J895" s="63" t="s">
-        <v>449</v>
+        <v>515</v>
       </c>
       <c r="K895" s="60">
         <v>30</v>
@@ -47055,7 +47248,7 @@
         <v>1</v>
       </c>
       <c r="O895" s="1" t="s">
-        <v>448</v>
+        <v>486</v>
       </c>
       <c r="P895" s="1">
         <v>0</v>
@@ -47090,7 +47283,7 @@
         <v>5</v>
       </c>
       <c r="J896" s="63" t="s">
-        <v>449</v>
+        <v>516</v>
       </c>
       <c r="K896" s="60">
         <v>30</v>
@@ -47105,7 +47298,7 @@
         <v>1</v>
       </c>
       <c r="O896" s="1" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
       <c r="P896" s="1">
         <v>0</v>
@@ -47140,7 +47333,7 @@
         <v>5</v>
       </c>
       <c r="J897" s="63" t="s">
-        <v>449</v>
+        <v>517</v>
       </c>
       <c r="K897" s="60">
         <v>30</v>
@@ -47155,7 +47348,7 @@
         <v>1</v>
       </c>
       <c r="O897" s="1" t="s">
-        <v>448</v>
+        <v>488</v>
       </c>
       <c r="P897" s="1">
         <v>0</v>
@@ -47190,7 +47383,7 @@
         <v>5</v>
       </c>
       <c r="J898" s="63" t="s">
-        <v>449</v>
+        <v>518</v>
       </c>
       <c r="K898" s="60">
         <v>30</v>
@@ -47205,7 +47398,7 @@
         <v>1</v>
       </c>
       <c r="O898" s="1" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="P898" s="1">
         <v>0</v>
@@ -47240,7 +47433,7 @@
         <v>5</v>
       </c>
       <c r="J899" s="63" t="s">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="K899" s="60">
         <v>30</v>
@@ -47255,7 +47448,7 @@
         <v>1</v>
       </c>
       <c r="O899" s="1" t="s">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="P899" s="1">
         <v>0</v>
@@ -47290,7 +47483,7 @@
         <v>5</v>
       </c>
       <c r="J900" s="63" t="s">
-        <v>449</v>
+        <v>520</v>
       </c>
       <c r="K900" s="60">
         <v>30</v>
@@ -47305,7 +47498,7 @@
         <v>1</v>
       </c>
       <c r="O900" s="1" t="s">
-        <v>448</v>
+        <v>491</v>
       </c>
       <c r="P900" s="1">
         <v>0</v>
@@ -47340,7 +47533,7 @@
         <v>5</v>
       </c>
       <c r="J901" s="63" t="s">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="K901" s="60">
         <v>30</v>
@@ -47355,7 +47548,7 @@
         <v>1</v>
       </c>
       <c r="O901" s="1" t="s">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="P901" s="1">
         <v>0</v>
@@ -47390,7 +47583,7 @@
         <v>5</v>
       </c>
       <c r="J902" s="63" t="s">
-        <v>449</v>
+        <v>521</v>
       </c>
       <c r="K902" s="60">
         <v>30</v>
@@ -47405,7 +47598,7 @@
         <v>1</v>
       </c>
       <c r="O902" s="1" t="s">
-        <v>448</v>
+        <v>493</v>
       </c>
       <c r="P902" s="1">
         <v>0</v>
@@ -47440,7 +47633,7 @@
         <v>1</v>
       </c>
       <c r="J903" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K903" s="62">
         <v>400</v>
@@ -47455,7 +47648,7 @@
         <v>2</v>
       </c>
       <c r="O903" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="P903" s="1">
         <v>0</v>
@@ -47490,7 +47683,7 @@
         <v>1</v>
       </c>
       <c r="J904" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K904" s="62">
         <v>400</v>
@@ -47540,7 +47733,7 @@
         <v>1</v>
       </c>
       <c r="J905" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K905" s="62">
         <v>400</v>
@@ -47590,7 +47783,7 @@
         <v>1</v>
       </c>
       <c r="J906" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K906" s="62">
         <v>400</v>
@@ -47640,7 +47833,7 @@
         <v>1</v>
       </c>
       <c r="J907" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K907" s="62">
         <v>400</v>
@@ -47690,7 +47883,7 @@
         <v>1</v>
       </c>
       <c r="J908" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K908" s="62">
         <v>400</v>
@@ -47740,7 +47933,7 @@
         <v>2</v>
       </c>
       <c r="J909" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K909" s="62">
         <v>400</v>
@@ -47790,7 +47983,7 @@
         <v>2</v>
       </c>
       <c r="J910" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K910" s="62">
         <v>400</v>
@@ -47840,7 +48033,7 @@
         <v>2</v>
       </c>
       <c r="J911" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K911" s="62">
         <v>400</v>
@@ -47890,7 +48083,7 @@
         <v>2</v>
       </c>
       <c r="J912" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K912" s="62">
         <v>400</v>
@@ -47940,7 +48133,7 @@
         <v>2</v>
       </c>
       <c r="J913" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K913" s="62">
         <v>400</v>
@@ -47990,7 +48183,7 @@
         <v>2</v>
       </c>
       <c r="J914" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K914" s="62">
         <v>400</v>
@@ -48040,7 +48233,7 @@
         <v>2</v>
       </c>
       <c r="J915" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K915" s="62">
         <v>400</v>
@@ -48090,7 +48283,7 @@
         <v>2</v>
       </c>
       <c r="J916" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K916" s="62">
         <v>400</v>
@@ -48140,7 +48333,7 @@
         <v>3</v>
       </c>
       <c r="J917" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K917" s="62">
         <v>400</v>
@@ -48190,7 +48383,7 @@
         <v>3</v>
       </c>
       <c r="J918" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K918" s="62">
         <v>400</v>
@@ -48240,7 +48433,7 @@
         <v>3</v>
       </c>
       <c r="J919" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K919" s="62">
         <v>400</v>
@@ -48290,7 +48483,7 @@
         <v>3</v>
       </c>
       <c r="J920" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K920" s="62">
         <v>400</v>
@@ -48340,7 +48533,7 @@
         <v>3</v>
       </c>
       <c r="J921" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K921" s="62">
         <v>400</v>
@@ -48390,7 +48583,7 @@
         <v>3</v>
       </c>
       <c r="J922" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K922" s="62">
         <v>400</v>
@@ -48440,7 +48633,7 @@
         <v>3</v>
       </c>
       <c r="J923" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K923" s="62">
         <v>400</v>
@@ -48490,7 +48683,7 @@
         <v>3</v>
       </c>
       <c r="J924" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K924" s="62">
         <v>400</v>
@@ -48540,7 +48733,7 @@
         <v>3</v>
       </c>
       <c r="J925" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K925" s="62">
         <v>400</v>
@@ -48590,7 +48783,7 @@
         <v>3</v>
       </c>
       <c r="J926" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K926" s="62">
         <v>400</v>
@@ -48640,7 +48833,7 @@
         <v>4</v>
       </c>
       <c r="J927" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K927" s="62">
         <v>400</v>
@@ -48690,7 +48883,7 @@
         <v>4</v>
       </c>
       <c r="J928" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K928" s="62">
         <v>400</v>
@@ -48740,7 +48933,7 @@
         <v>4</v>
       </c>
       <c r="J929" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K929" s="62">
         <v>400</v>
@@ -48790,7 +48983,7 @@
         <v>4</v>
       </c>
       <c r="J930" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K930" s="62">
         <v>400</v>
@@ -48840,7 +49033,7 @@
         <v>4</v>
       </c>
       <c r="J931" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K931" s="62">
         <v>400</v>
@@ -48890,7 +49083,7 @@
         <v>4</v>
       </c>
       <c r="J932" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K932" s="62">
         <v>400</v>
@@ -48940,7 +49133,7 @@
         <v>4</v>
       </c>
       <c r="J933" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K933" s="62">
         <v>400</v>
@@ -48990,7 +49183,7 @@
         <v>4</v>
       </c>
       <c r="J934" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K934" s="62">
         <v>400</v>
@@ -49040,7 +49233,7 @@
         <v>4</v>
       </c>
       <c r="J935" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K935" s="62">
         <v>400</v>
@@ -49090,7 +49283,7 @@
         <v>4</v>
       </c>
       <c r="J936" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K936" s="62">
         <v>400</v>
@@ -49140,7 +49333,7 @@
         <v>4</v>
       </c>
       <c r="J937" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K937" s="62">
         <v>400</v>
@@ -49190,7 +49383,7 @@
         <v>4</v>
       </c>
       <c r="J938" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K938" s="62">
         <v>400</v>
@@ -49240,7 +49433,7 @@
         <v>5</v>
       </c>
       <c r="J939" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K939" s="62">
         <v>400</v>
@@ -49290,7 +49483,7 @@
         <v>5</v>
       </c>
       <c r="J940" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K940" s="62">
         <v>400</v>
@@ -49340,7 +49533,7 @@
         <v>5</v>
       </c>
       <c r="J941" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K941" s="62">
         <v>400</v>
@@ -49390,7 +49583,7 @@
         <v>5</v>
       </c>
       <c r="J942" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K942" s="62">
         <v>400</v>
@@ -49440,7 +49633,7 @@
         <v>5</v>
       </c>
       <c r="J943" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K943" s="62">
         <v>400</v>
@@ -49490,7 +49683,7 @@
         <v>5</v>
       </c>
       <c r="J944" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K944" s="62">
         <v>400</v>
@@ -49540,7 +49733,7 @@
         <v>5</v>
       </c>
       <c r="J945" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K945" s="62">
         <v>400</v>
@@ -49590,7 +49783,7 @@
         <v>5</v>
       </c>
       <c r="J946" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K946" s="62">
         <v>400</v>
@@ -49640,7 +49833,7 @@
         <v>5</v>
       </c>
       <c r="J947" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K947" s="62">
         <v>400</v>
@@ -49690,7 +49883,7 @@
         <v>5</v>
       </c>
       <c r="J948" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K948" s="62">
         <v>400</v>
@@ -49740,7 +49933,7 @@
         <v>5</v>
       </c>
       <c r="J949" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K949" s="62">
         <v>400</v>
@@ -49790,7 +49983,7 @@
         <v>5</v>
       </c>
       <c r="J950" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K950" s="62">
         <v>400</v>
@@ -49840,7 +50033,7 @@
         <v>5</v>
       </c>
       <c r="J951" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K951" s="62">
         <v>400</v>
@@ -49890,7 +50083,7 @@
         <v>5</v>
       </c>
       <c r="J952" s="63" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K952" s="62">
         <v>400</v>
@@ -49940,7 +50133,7 @@
         <v>1</v>
       </c>
       <c r="J953" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K953" s="62">
         <v>6000</v>
@@ -49955,7 +50148,7 @@
         <v>3</v>
       </c>
       <c r="O953" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P953" s="1">
         <v>0</v>
@@ -49990,7 +50183,7 @@
         <v>1</v>
       </c>
       <c r="J954" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K954" s="62">
         <v>6000</v>
@@ -50005,7 +50198,7 @@
         <v>3</v>
       </c>
       <c r="O954" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P954" s="1">
         <v>0</v>
@@ -50040,7 +50233,7 @@
         <v>1</v>
       </c>
       <c r="J955" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K955" s="62">
         <v>6000</v>
@@ -50055,7 +50248,7 @@
         <v>3</v>
       </c>
       <c r="O955" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P955" s="1">
         <v>0</v>
@@ -50090,7 +50283,7 @@
         <v>1</v>
       </c>
       <c r="J956" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K956" s="62">
         <v>6000</v>
@@ -50105,7 +50298,7 @@
         <v>3</v>
       </c>
       <c r="O956" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P956" s="1">
         <v>0</v>
@@ -50140,7 +50333,7 @@
         <v>1</v>
       </c>
       <c r="J957" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K957" s="62">
         <v>6000</v>
@@ -50155,7 +50348,7 @@
         <v>3</v>
       </c>
       <c r="O957" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P957" s="1">
         <v>0</v>
@@ -50190,7 +50383,7 @@
         <v>1</v>
       </c>
       <c r="J958" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K958" s="62">
         <v>6000</v>
@@ -50205,7 +50398,7 @@
         <v>3</v>
       </c>
       <c r="O958" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P958" s="1">
         <v>0</v>
@@ -50240,7 +50433,7 @@
         <v>1</v>
       </c>
       <c r="J959" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K959" s="62">
         <v>6000</v>
@@ -50255,7 +50448,7 @@
         <v>3</v>
       </c>
       <c r="O959" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P959" s="1">
         <v>0</v>
@@ -50290,7 +50483,7 @@
         <v>1</v>
       </c>
       <c r="J960" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K960" s="62">
         <v>6000</v>
@@ -50305,7 +50498,7 @@
         <v>3</v>
       </c>
       <c r="O960" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P960" s="1">
         <v>0</v>
@@ -50340,7 +50533,7 @@
         <v>2</v>
       </c>
       <c r="J961" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K961" s="62">
         <v>6000</v>
@@ -50355,7 +50548,7 @@
         <v>3</v>
       </c>
       <c r="O961" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P961" s="1">
         <v>0</v>
@@ -50390,7 +50583,7 @@
         <v>2</v>
       </c>
       <c r="J962" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K962" s="62">
         <v>6000</v>
@@ -50405,7 +50598,7 @@
         <v>3</v>
       </c>
       <c r="O962" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P962" s="1">
         <v>0</v>
@@ -50440,7 +50633,7 @@
         <v>2</v>
       </c>
       <c r="J963" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K963" s="62">
         <v>6000</v>
@@ -50455,7 +50648,7 @@
         <v>3</v>
       </c>
       <c r="O963" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P963" s="1">
         <v>0</v>
@@ -50490,7 +50683,7 @@
         <v>2</v>
       </c>
       <c r="J964" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K964" s="62">
         <v>6000</v>
@@ -50505,7 +50698,7 @@
         <v>3</v>
       </c>
       <c r="O964" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P964" s="1">
         <v>0</v>
@@ -50540,7 +50733,7 @@
         <v>2</v>
       </c>
       <c r="J965" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K965" s="62">
         <v>6000</v>
@@ -50555,7 +50748,7 @@
         <v>3</v>
       </c>
       <c r="O965" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P965" s="1">
         <v>0</v>
@@ -50590,7 +50783,7 @@
         <v>2</v>
       </c>
       <c r="J966" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K966" s="62">
         <v>6000</v>
@@ -50605,7 +50798,7 @@
         <v>3</v>
       </c>
       <c r="O966" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P966" s="1">
         <v>0</v>
@@ -50640,7 +50833,7 @@
         <v>2</v>
       </c>
       <c r="J967" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K967" s="62">
         <v>6000</v>
@@ -50655,7 +50848,7 @@
         <v>3</v>
       </c>
       <c r="O967" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P967" s="1">
         <v>0</v>
@@ -50690,7 +50883,7 @@
         <v>2</v>
       </c>
       <c r="J968" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K968" s="62">
         <v>6000</v>
@@ -50705,7 +50898,7 @@
         <v>3</v>
       </c>
       <c r="O968" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P968" s="1">
         <v>0</v>
@@ -50740,7 +50933,7 @@
         <v>2</v>
       </c>
       <c r="J969" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K969" s="62">
         <v>6000</v>
@@ -50755,7 +50948,7 @@
         <v>3</v>
       </c>
       <c r="O969" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P969" s="1">
         <v>0</v>
@@ -50790,7 +50983,7 @@
         <v>2</v>
       </c>
       <c r="J970" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K970" s="62">
         <v>6000</v>
@@ -50805,7 +50998,7 @@
         <v>3</v>
       </c>
       <c r="O970" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P970" s="1">
         <v>0</v>
@@ -50840,7 +51033,7 @@
         <v>3</v>
       </c>
       <c r="J971" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K971" s="62">
         <v>6000</v>
@@ -50855,7 +51048,7 @@
         <v>3</v>
       </c>
       <c r="O971" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P971" s="1">
         <v>0</v>
@@ -50890,7 +51083,7 @@
         <v>3</v>
       </c>
       <c r="J972" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K972" s="62">
         <v>6000</v>
@@ -50905,7 +51098,7 @@
         <v>3</v>
       </c>
       <c r="O972" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P972" s="1">
         <v>0</v>
@@ -50940,7 +51133,7 @@
         <v>3</v>
       </c>
       <c r="J973" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K973" s="62">
         <v>6000</v>
@@ -50955,7 +51148,7 @@
         <v>3</v>
       </c>
       <c r="O973" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P973" s="1">
         <v>0</v>
@@ -50990,7 +51183,7 @@
         <v>3</v>
       </c>
       <c r="J974" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K974" s="62">
         <v>6000</v>
@@ -51005,7 +51198,7 @@
         <v>3</v>
       </c>
       <c r="O974" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P974" s="1">
         <v>0</v>
@@ -51040,7 +51233,7 @@
         <v>3</v>
       </c>
       <c r="J975" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K975" s="62">
         <v>6000</v>
@@ -51055,7 +51248,7 @@
         <v>3</v>
       </c>
       <c r="O975" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P975" s="1">
         <v>0</v>
@@ -51090,7 +51283,7 @@
         <v>3</v>
       </c>
       <c r="J976" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K976" s="62">
         <v>6000</v>
@@ -51105,7 +51298,7 @@
         <v>3</v>
       </c>
       <c r="O976" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P976" s="1">
         <v>0</v>
@@ -51140,7 +51333,7 @@
         <v>3</v>
       </c>
       <c r="J977" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K977" s="62">
         <v>6000</v>
@@ -51155,7 +51348,7 @@
         <v>3</v>
       </c>
       <c r="O977" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P977" s="1">
         <v>0</v>
@@ -51190,7 +51383,7 @@
         <v>3</v>
       </c>
       <c r="J978" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K978" s="62">
         <v>6000</v>
@@ -51205,7 +51398,7 @@
         <v>3</v>
       </c>
       <c r="O978" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P978" s="1">
         <v>0</v>
@@ -51240,7 +51433,7 @@
         <v>3</v>
       </c>
       <c r="J979" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K979" s="62">
         <v>6000</v>
@@ -51255,7 +51448,7 @@
         <v>3</v>
       </c>
       <c r="O979" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P979" s="1">
         <v>0</v>
@@ -51290,7 +51483,7 @@
         <v>3</v>
       </c>
       <c r="J980" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K980" s="62">
         <v>6000</v>
@@ -51305,7 +51498,7 @@
         <v>3</v>
       </c>
       <c r="O980" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P980" s="1">
         <v>0</v>
@@ -51340,7 +51533,7 @@
         <v>3</v>
       </c>
       <c r="J981" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K981" s="62">
         <v>6000</v>
@@ -51355,7 +51548,7 @@
         <v>3</v>
       </c>
       <c r="O981" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P981" s="1">
         <v>0</v>
@@ -51390,7 +51583,7 @@
         <v>3</v>
       </c>
       <c r="J982" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K982" s="62">
         <v>6000</v>
@@ -51405,7 +51598,7 @@
         <v>3</v>
       </c>
       <c r="O982" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P982" s="1">
         <v>0</v>
@@ -51440,7 +51633,7 @@
         <v>4</v>
       </c>
       <c r="J983" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K983" s="62">
         <v>6000</v>
@@ -51455,7 +51648,7 @@
         <v>3</v>
       </c>
       <c r="O983" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P983" s="1">
         <v>0</v>
@@ -51490,7 +51683,7 @@
         <v>4</v>
       </c>
       <c r="J984" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K984" s="62">
         <v>6000</v>
@@ -51505,7 +51698,7 @@
         <v>3</v>
       </c>
       <c r="O984" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P984" s="1">
         <v>0</v>
@@ -51540,7 +51733,7 @@
         <v>4</v>
       </c>
       <c r="J985" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K985" s="62">
         <v>6000</v>
@@ -51555,7 +51748,7 @@
         <v>3</v>
       </c>
       <c r="O985" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P985" s="1">
         <v>0</v>
@@ -51590,7 +51783,7 @@
         <v>4</v>
       </c>
       <c r="J986" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K986" s="62">
         <v>6000</v>
@@ -51605,7 +51798,7 @@
         <v>3</v>
       </c>
       <c r="O986" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P986" s="1">
         <v>0</v>
@@ -51640,7 +51833,7 @@
         <v>4</v>
       </c>
       <c r="J987" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K987" s="62">
         <v>6000</v>
@@ -51655,7 +51848,7 @@
         <v>3</v>
       </c>
       <c r="O987" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P987" s="1">
         <v>0</v>
@@ -51690,7 +51883,7 @@
         <v>4</v>
       </c>
       <c r="J988" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K988" s="62">
         <v>6000</v>
@@ -51705,7 +51898,7 @@
         <v>3</v>
       </c>
       <c r="O988" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P988" s="1">
         <v>0</v>
@@ -51740,7 +51933,7 @@
         <v>4</v>
       </c>
       <c r="J989" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K989" s="62">
         <v>6000</v>
@@ -51755,7 +51948,7 @@
         <v>3</v>
       </c>
       <c r="O989" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P989" s="1">
         <v>0</v>
@@ -51790,7 +51983,7 @@
         <v>4</v>
       </c>
       <c r="J990" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K990" s="62">
         <v>6000</v>
@@ -51805,7 +51998,7 @@
         <v>3</v>
       </c>
       <c r="O990" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P990" s="1">
         <v>0</v>
@@ -51840,7 +52033,7 @@
         <v>4</v>
       </c>
       <c r="J991" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K991" s="62">
         <v>6000</v>
@@ -51855,7 +52048,7 @@
         <v>3</v>
       </c>
       <c r="O991" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P991" s="1">
         <v>0</v>
@@ -51890,7 +52083,7 @@
         <v>4</v>
       </c>
       <c r="J992" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K992" s="62">
         <v>6000</v>
@@ -51905,7 +52098,7 @@
         <v>3</v>
       </c>
       <c r="O992" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P992" s="1">
         <v>0</v>
@@ -51940,7 +52133,7 @@
         <v>4</v>
       </c>
       <c r="J993" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K993" s="62">
         <v>6000</v>
@@ -51955,7 +52148,7 @@
         <v>3</v>
       </c>
       <c r="O993" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P993" s="1">
         <v>0</v>
@@ -51990,7 +52183,7 @@
         <v>4</v>
       </c>
       <c r="J994" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K994" s="62">
         <v>6000</v>
@@ -52005,7 +52198,7 @@
         <v>3</v>
       </c>
       <c r="O994" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P994" s="1">
         <v>0</v>
@@ -52040,7 +52233,7 @@
         <v>4</v>
       </c>
       <c r="J995" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K995" s="62">
         <v>6000</v>
@@ -52055,7 +52248,7 @@
         <v>3</v>
       </c>
       <c r="O995" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P995" s="1">
         <v>0</v>
@@ -52090,7 +52283,7 @@
         <v>4</v>
       </c>
       <c r="J996" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K996" s="62">
         <v>6000</v>
@@ -52105,7 +52298,7 @@
         <v>3</v>
       </c>
       <c r="O996" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P996" s="1">
         <v>0</v>
@@ -52140,7 +52333,7 @@
         <v>5</v>
       </c>
       <c r="J997" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K997" s="62">
         <v>6000</v>
@@ -52155,7 +52348,7 @@
         <v>3</v>
       </c>
       <c r="O997" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P997" s="1">
         <v>0</v>
@@ -52190,7 +52383,7 @@
         <v>5</v>
       </c>
       <c r="J998" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K998" s="62">
         <v>6000</v>
@@ -52205,7 +52398,7 @@
         <v>3</v>
       </c>
       <c r="O998" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P998" s="1">
         <v>0</v>
@@ -52240,7 +52433,7 @@
         <v>5</v>
       </c>
       <c r="J999" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K999" s="62">
         <v>6000</v>
@@ -52255,7 +52448,7 @@
         <v>3</v>
       </c>
       <c r="O999" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P999" s="1">
         <v>0</v>
@@ -52290,7 +52483,7 @@
         <v>5</v>
       </c>
       <c r="J1000" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1000" s="62">
         <v>6000</v>
@@ -52305,7 +52498,7 @@
         <v>3</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1000" s="1">
         <v>0</v>
@@ -52340,7 +52533,7 @@
         <v>5</v>
       </c>
       <c r="J1001" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1001" s="62">
         <v>6000</v>
@@ -52355,7 +52548,7 @@
         <v>3</v>
       </c>
       <c r="O1001" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1001" s="1">
         <v>0</v>
@@ -52390,7 +52583,7 @@
         <v>5</v>
       </c>
       <c r="J1002" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1002" s="62">
         <v>6000</v>
@@ -52405,7 +52598,7 @@
         <v>3</v>
       </c>
       <c r="O1002" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1002" s="1">
         <v>0</v>
@@ -52440,7 +52633,7 @@
         <v>5</v>
       </c>
       <c r="J1003" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1003" s="62">
         <v>6000</v>
@@ -52455,7 +52648,7 @@
         <v>3</v>
       </c>
       <c r="O1003" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1003" s="1">
         <v>0</v>
@@ -52490,7 +52683,7 @@
         <v>5</v>
       </c>
       <c r="J1004" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1004" s="62">
         <v>6000</v>
@@ -52505,7 +52698,7 @@
         <v>3</v>
       </c>
       <c r="O1004" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1004" s="1">
         <v>0</v>
@@ -52540,7 +52733,7 @@
         <v>5</v>
       </c>
       <c r="J1005" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1005" s="62">
         <v>6000</v>
@@ -52555,7 +52748,7 @@
         <v>3</v>
       </c>
       <c r="O1005" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1005" s="1">
         <v>0</v>
@@ -52590,7 +52783,7 @@
         <v>5</v>
       </c>
       <c r="J1006" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1006" s="62">
         <v>6000</v>
@@ -52605,7 +52798,7 @@
         <v>3</v>
       </c>
       <c r="O1006" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1006" s="1">
         <v>0</v>
@@ -52640,7 +52833,7 @@
         <v>5</v>
       </c>
       <c r="J1007" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1007" s="62">
         <v>6000</v>
@@ -52655,7 +52848,7 @@
         <v>3</v>
       </c>
       <c r="O1007" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1007" s="1">
         <v>0</v>
@@ -52690,7 +52883,7 @@
         <v>5</v>
       </c>
       <c r="J1008" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1008" s="62">
         <v>6000</v>
@@ -52705,7 +52898,7 @@
         <v>3</v>
       </c>
       <c r="O1008" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1008" s="1">
         <v>0</v>
@@ -52740,7 +52933,7 @@
         <v>5</v>
       </c>
       <c r="J1009" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1009" s="62">
         <v>6000</v>
@@ -52755,7 +52948,7 @@
         <v>3</v>
       </c>
       <c r="O1009" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1009" s="1">
         <v>0</v>
@@ -52790,7 +52983,7 @@
         <v>5</v>
       </c>
       <c r="J1010" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1010" s="62">
         <v>6000</v>
@@ -52805,7 +52998,7 @@
         <v>3</v>
       </c>
       <c r="O1010" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1010" s="1">
         <v>0</v>
@@ -52840,7 +53033,7 @@
         <v>5</v>
       </c>
       <c r="J1011" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1011" s="62">
         <v>6000</v>
@@ -52855,7 +53048,7 @@
         <v>3</v>
       </c>
       <c r="O1011" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1011" s="1">
         <v>0</v>
@@ -52890,7 +53083,7 @@
         <v>5</v>
       </c>
       <c r="J1012" s="63" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K1012" s="62">
         <v>6000</v>
@@ -52905,7 +53098,7 @@
         <v>3</v>
       </c>
       <c r="O1012" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="P1012" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A215EC5-A953-424A-8A87-C29322BC6869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46D504F-9BD5-4799-B447-2016FA7AD767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="599">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1490,14 +1490,6 @@
     <t>90,35,95,47</t>
   </si>
   <si>
-    <t>50,60</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>73104</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>74104</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1539,9 +1531,6 @@
     <t>55,90,60,85,55,80,85,15</t>
   </si>
   <si>
-    <t>60,85,55,90,55,80,80,15</t>
-  </si>
-  <si>
     <t>50,90,55,85,50,80</t>
   </si>
   <si>
@@ -1708,6 +1697,246 @@
   </si>
   <si>
     <t>72109,72109,72106,72106,72106</t>
+  </si>
+  <si>
+    <t>60,85,80,15,90,10</t>
+  </si>
+  <si>
+    <t>73104,73104,73101</t>
+  </si>
+  <si>
+    <t>73107,73101,73101</t>
+  </si>
+  <si>
+    <t>73104,73104,73104</t>
+  </si>
+  <si>
+    <t>73104,73104,73104,73101</t>
+  </si>
+  <si>
+    <t>73104,73104,73101,73101</t>
+  </si>
+  <si>
+    <t>73110,73101,73101</t>
+  </si>
+  <si>
+    <t>73105,73105,73102,73102</t>
+  </si>
+  <si>
+    <t>73108,73105,73105,73102</t>
+  </si>
+  <si>
+    <t>73105,73105,73105,73105</t>
+  </si>
+  <si>
+    <t>73108,73108,73105,73105</t>
+  </si>
+  <si>
+    <t>73111,73105,73105,73105</t>
+  </si>
+  <si>
+    <t>73102,73102,73102,73102</t>
+  </si>
+  <si>
+    <t>73108,73105,73105,73102,73102</t>
+  </si>
+  <si>
+    <t>73105,73105,73105,73102,73102</t>
+  </si>
+  <si>
+    <t>73105,73105,73102,73102,73102</t>
+  </si>
+  <si>
+    <t>73111,73105,73105,73105,73105</t>
+  </si>
+  <si>
+    <t>73108,73108,73102,73102,73102</t>
+  </si>
+  <si>
+    <t>73108,73108,73102,73102</t>
+  </si>
+  <si>
+    <t>73111,73105,73105,73102</t>
+  </si>
+  <si>
+    <t>73108,73108,73105,73105,73105</t>
+  </si>
+  <si>
+    <t>73106,73106,73106,73103,73103</t>
+  </si>
+  <si>
+    <t>73109,73106,73106,73103,73103</t>
+  </si>
+  <si>
+    <t>73112,73106,73106,73106</t>
+  </si>
+  <si>
+    <t>73109,73109,73106,73106,73106</t>
+  </si>
+  <si>
+    <t>73109,73109,73103,73103</t>
+  </si>
+  <si>
+    <t>73112,73106,73106,73106,73106</t>
+  </si>
+  <si>
+    <t>73109,73109,73109,73103,73103</t>
+  </si>
+  <si>
+    <t>73112,73109,73109,73103,73103</t>
+  </si>
+  <si>
+    <t>73109,73109,73109,73109</t>
+  </si>
+  <si>
+    <t>6,60,12,60,9,80</t>
+  </si>
+  <si>
+    <t>9,55,6,60,12,60</t>
+  </si>
+  <si>
+    <t>4,65,9,65,14,65</t>
+  </si>
+  <si>
+    <t>9,55,6,85,12,85</t>
+  </si>
+  <si>
+    <t>4,60,14,60,18,80</t>
+  </si>
+  <si>
+    <t>4,65,9,65,14,65,20,75</t>
+  </si>
+  <si>
+    <t>40,90,40,75,40,60,70,75</t>
+  </si>
+  <si>
+    <t>35,75,70,90,70,60</t>
+  </si>
+  <si>
+    <t>40,90,40,75,40,60</t>
+  </si>
+  <si>
+    <t>45,80,45,60,75,90,75,60</t>
+  </si>
+  <si>
+    <t>40,75,75,80,75,70</t>
+  </si>
+  <si>
+    <t>50,75,50,60,50,90</t>
+  </si>
+  <si>
+    <t>40,75,65,60,65,90</t>
+  </si>
+  <si>
+    <t>50,70,50,80,65,80,65,70</t>
+  </si>
+  <si>
+    <t>85,83,85,67,95,80,90,90</t>
+  </si>
+  <si>
+    <t>75,75,80,83,80,67,95,70</t>
+  </si>
+  <si>
+    <t>80,90,80,60,85,80,85,70</t>
+  </si>
+  <si>
+    <t>80,80,80,70,95,60,95,50</t>
+  </si>
+  <si>
+    <t>75,82,75,68,80,90,80,60</t>
+  </si>
+  <si>
+    <t>80,80,80,70,85,45,90,45</t>
+  </si>
+  <si>
+    <t>75,75,80,75,80,90,80,60</t>
+  </si>
+  <si>
+    <t>90,40,95,40,90,35,95,35</t>
+  </si>
+  <si>
+    <t>75,75,80,90,80,60,90,30,95,30</t>
+  </si>
+  <si>
+    <t>85,60,85,70,85,90,85,80</t>
+  </si>
+  <si>
+    <t>50,65,50,75,50,85,20,70,20,80</t>
+  </si>
+  <si>
+    <t>55,75,50,65,50,85,25,70</t>
+  </si>
+  <si>
+    <t>55,75,50,65,50,85,25,80</t>
+  </si>
+  <si>
+    <t>45,70,45,80,20,90,20,60,20,75</t>
+  </si>
+  <si>
+    <t>50,70,45,60,45,80,45,70,45,90</t>
+  </si>
+  <si>
+    <t>40,80,40,70,15,70,15,80</t>
+  </si>
+  <si>
+    <t>50,70,50,80,15,90,15,60,15,75</t>
+  </si>
+  <si>
+    <t>40,60,40,80,40,70,40,90</t>
+  </si>
+  <si>
+    <t>50,70,50,80,10,70,10,80</t>
+  </si>
+  <si>
+    <t>50,75,40,65,40,85,10,75</t>
+  </si>
+  <si>
+    <t>50,70,50,80,10,90,10,60</t>
+  </si>
+  <si>
+    <t>45,70,45,80,35,75,35,65,35,85</t>
+  </si>
+  <si>
+    <t>80,75,80,90,80,60,95,80,95,70</t>
+  </si>
+  <si>
+    <t>80,75,80,90,80,60,90,85,90,65</t>
+  </si>
+  <si>
+    <t>75,75,85,75,80,60,85,90,85,60</t>
+  </si>
+  <si>
+    <t>30,75,25,75,25,90,25,60</t>
+  </si>
+  <si>
+    <t>20,75,20,90,20,60,5,80,5,70</t>
+  </si>
+  <si>
+    <t>30,80,30,70,25,75,25,85,25,65</t>
+  </si>
+  <si>
+    <t>30,80,30,70,10,85,10,65</t>
+  </si>
+  <si>
+    <t>30,75,25,80,25,70,20,85,20,65</t>
+  </si>
+  <si>
+    <t>25,75,20,85,20,65,15,90,15,60</t>
+  </si>
+  <si>
+    <t>75,75,75,85,75,65,85,80,85,70</t>
+  </si>
+  <si>
+    <t>75,75,75,90,75,60,80,90,80,60</t>
+  </si>
+  <si>
+    <t>25,75,20,90,20,60,15,80,15,70</t>
+  </si>
+  <si>
+    <t>20,75,20,85,20,65,20,90,20,60</t>
+  </si>
+  <si>
+    <t>75,60,75,70,75,80,75,90</t>
   </si>
 </sst>
 </file>
@@ -45633,7 +45862,7 @@
         <v>1</v>
       </c>
       <c r="J863" s="61" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="K863" s="60">
         <v>30</v>
@@ -45648,7 +45877,7 @@
         <v>1</v>
       </c>
       <c r="O863" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P863" s="1">
         <v>0</v>
@@ -45683,7 +45912,7 @@
         <v>1</v>
       </c>
       <c r="J864" s="61" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="K864" s="60">
         <v>30</v>
@@ -45698,7 +45927,7 @@
         <v>1</v>
       </c>
       <c r="O864" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="P864" s="1">
         <v>0</v>
@@ -45733,7 +45962,7 @@
         <v>1</v>
       </c>
       <c r="J865" s="61" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="K865" s="60">
         <v>30</v>
@@ -45748,7 +45977,7 @@
         <v>1</v>
       </c>
       <c r="O865" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P865" s="1">
         <v>0</v>
@@ -45783,7 +46012,7 @@
         <v>1</v>
       </c>
       <c r="J866" s="61" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="K866" s="60">
         <v>30</v>
@@ -45798,7 +46027,7 @@
         <v>1</v>
       </c>
       <c r="O866" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P866" s="1">
         <v>0</v>
@@ -45833,7 +46062,7 @@
         <v>2</v>
       </c>
       <c r="J867" s="61" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="K867" s="60">
         <v>30</v>
@@ -45848,7 +46077,7 @@
         <v>1</v>
       </c>
       <c r="O867" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P867" s="1">
         <v>0</v>
@@ -45883,7 +46112,7 @@
         <v>2</v>
       </c>
       <c r="J868" s="61" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="K868" s="60">
         <v>30</v>
@@ -45898,7 +46127,7 @@
         <v>1</v>
       </c>
       <c r="O868" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="P868" s="1">
         <v>0</v>
@@ -45933,7 +46162,7 @@
         <v>2</v>
       </c>
       <c r="J869" s="61" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="K869" s="60">
         <v>30</v>
@@ -45948,7 +46177,7 @@
         <v>1</v>
       </c>
       <c r="O869" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P869" s="1">
         <v>0</v>
@@ -45983,7 +46212,7 @@
         <v>2</v>
       </c>
       <c r="J870" s="61" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="K870" s="60">
         <v>30</v>
@@ -45998,7 +46227,7 @@
         <v>1</v>
       </c>
       <c r="O870" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P870" s="1">
         <v>0</v>
@@ -46033,7 +46262,7 @@
         <v>2</v>
       </c>
       <c r="J871" s="61" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="K871" s="60">
         <v>30</v>
@@ -46048,7 +46277,7 @@
         <v>1</v>
       </c>
       <c r="O871" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P871" s="1">
         <v>0</v>
@@ -46083,7 +46312,7 @@
         <v>2</v>
       </c>
       <c r="J872" s="61" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K872" s="60">
         <v>30</v>
@@ -46098,7 +46327,7 @@
         <v>1</v>
       </c>
       <c r="O872" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P872" s="1">
         <v>0</v>
@@ -46133,7 +46362,7 @@
         <v>3</v>
       </c>
       <c r="J873" s="61" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="K873" s="60">
         <v>30</v>
@@ -46148,7 +46377,7 @@
         <v>1</v>
       </c>
       <c r="O873" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P873" s="1">
         <v>0</v>
@@ -46183,7 +46412,7 @@
         <v>3</v>
       </c>
       <c r="J874" s="61" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="K874" s="60">
         <v>30</v>
@@ -46198,7 +46427,7 @@
         <v>1</v>
       </c>
       <c r="O874" s="1" t="s">
-        <v>465</v>
+        <v>519</v>
       </c>
       <c r="P874" s="1">
         <v>0</v>
@@ -46233,7 +46462,7 @@
         <v>3</v>
       </c>
       <c r="J875" s="61" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K875" s="60">
         <v>30</v>
@@ -46248,7 +46477,7 @@
         <v>1</v>
       </c>
       <c r="O875" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="P875" s="1">
         <v>0</v>
@@ -46283,7 +46512,7 @@
         <v>3</v>
       </c>
       <c r="J876" s="61" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K876" s="60">
         <v>30</v>
@@ -46298,7 +46527,7 @@
         <v>1</v>
       </c>
       <c r="O876" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="P876" s="1">
         <v>0</v>
@@ -46333,7 +46562,7 @@
         <v>3</v>
       </c>
       <c r="J877" s="61" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="K877" s="60">
         <v>30</v>
@@ -46348,7 +46577,7 @@
         <v>1</v>
       </c>
       <c r="O877" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="P877" s="1">
         <v>0</v>
@@ -46383,7 +46612,7 @@
         <v>3</v>
       </c>
       <c r="J878" s="61" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K878" s="60">
         <v>30</v>
@@ -46398,7 +46627,7 @@
         <v>1</v>
       </c>
       <c r="O878" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="P878" s="1">
         <v>0</v>
@@ -46433,7 +46662,7 @@
         <v>3</v>
       </c>
       <c r="J879" s="61" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="K879" s="60">
         <v>30</v>
@@ -46448,7 +46677,7 @@
         <v>1</v>
       </c>
       <c r="O879" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="P879" s="1">
         <v>0</v>
@@ -46483,7 +46712,7 @@
         <v>3</v>
       </c>
       <c r="J880" s="61" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K880" s="60">
         <v>30</v>
@@ -46498,7 +46727,7 @@
         <v>1</v>
       </c>
       <c r="O880" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="P880" s="1">
         <v>0</v>
@@ -46533,7 +46762,7 @@
         <v>4</v>
       </c>
       <c r="J881" s="61" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K881" s="60">
         <v>30</v>
@@ -46548,7 +46777,7 @@
         <v>1</v>
       </c>
       <c r="O881" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="P881" s="1">
         <v>0</v>
@@ -46583,7 +46812,7 @@
         <v>4</v>
       </c>
       <c r="J882" s="61" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="K882" s="60">
         <v>30</v>
@@ -46598,7 +46827,7 @@
         <v>1</v>
       </c>
       <c r="O882" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="P882" s="1">
         <v>0</v>
@@ -46633,7 +46862,7 @@
         <v>4</v>
       </c>
       <c r="J883" s="61" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="K883" s="60">
         <v>30</v>
@@ -46648,7 +46877,7 @@
         <v>1</v>
       </c>
       <c r="O883" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="P883" s="1">
         <v>0</v>
@@ -46683,7 +46912,7 @@
         <v>4</v>
       </c>
       <c r="J884" s="61" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K884" s="60">
         <v>30</v>
@@ -46698,7 +46927,7 @@
         <v>1</v>
       </c>
       <c r="O884" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="P884" s="1">
         <v>0</v>
@@ -46733,7 +46962,7 @@
         <v>4</v>
       </c>
       <c r="J885" s="61" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="K885" s="60">
         <v>30</v>
@@ -46748,7 +46977,7 @@
         <v>1</v>
       </c>
       <c r="O885" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="P885" s="1">
         <v>0</v>
@@ -46783,7 +47012,7 @@
         <v>4</v>
       </c>
       <c r="J886" s="61" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K886" s="60">
         <v>30</v>
@@ -46798,7 +47027,7 @@
         <v>1</v>
       </c>
       <c r="O886" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="P886" s="1">
         <v>0</v>
@@ -46833,7 +47062,7 @@
         <v>4</v>
       </c>
       <c r="J887" s="61" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="K887" s="60">
         <v>30</v>
@@ -46848,7 +47077,7 @@
         <v>1</v>
       </c>
       <c r="O887" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="P887" s="1">
         <v>0</v>
@@ -46883,7 +47112,7 @@
         <v>4</v>
       </c>
       <c r="J888" s="61" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="K888" s="60">
         <v>30</v>
@@ -46898,7 +47127,7 @@
         <v>1</v>
       </c>
       <c r="O888" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="P888" s="1">
         <v>0</v>
@@ -46933,7 +47162,7 @@
         <v>4</v>
       </c>
       <c r="J889" s="61" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="K889" s="60">
         <v>30</v>
@@ -46948,7 +47177,7 @@
         <v>1</v>
       </c>
       <c r="O889" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="P889" s="1">
         <v>0</v>
@@ -46983,7 +47212,7 @@
         <v>4</v>
       </c>
       <c r="J890" s="61" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="K890" s="60">
         <v>30</v>
@@ -46998,7 +47227,7 @@
         <v>1</v>
       </c>
       <c r="O890" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="P890" s="1">
         <v>0</v>
@@ -47033,7 +47262,7 @@
         <v>5</v>
       </c>
       <c r="J891" s="61" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="K891" s="60">
         <v>30</v>
@@ -47048,7 +47277,7 @@
         <v>1</v>
       </c>
       <c r="O891" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="P891" s="1">
         <v>0</v>
@@ -47083,7 +47312,7 @@
         <v>5</v>
       </c>
       <c r="J892" s="61" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="K892" s="60">
         <v>30</v>
@@ -47098,7 +47327,7 @@
         <v>1</v>
       </c>
       <c r="O892" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="P892" s="1">
         <v>0</v>
@@ -47133,7 +47362,7 @@
         <v>5</v>
       </c>
       <c r="J893" s="63" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="K893" s="60">
         <v>30</v>
@@ -47148,7 +47377,7 @@
         <v>1</v>
       </c>
       <c r="O893" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="P893" s="1">
         <v>0</v>
@@ -47183,7 +47412,7 @@
         <v>5</v>
       </c>
       <c r="J894" s="63" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K894" s="60">
         <v>30</v>
@@ -47198,7 +47427,7 @@
         <v>1</v>
       </c>
       <c r="O894" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="P894" s="1">
         <v>0</v>
@@ -47233,7 +47462,7 @@
         <v>5</v>
       </c>
       <c r="J895" s="63" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="K895" s="60">
         <v>30</v>
@@ -47248,7 +47477,7 @@
         <v>1</v>
       </c>
       <c r="O895" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="P895" s="1">
         <v>0</v>
@@ -47283,7 +47512,7 @@
         <v>5</v>
       </c>
       <c r="J896" s="63" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="K896" s="60">
         <v>30</v>
@@ -47298,7 +47527,7 @@
         <v>1</v>
       </c>
       <c r="O896" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="P896" s="1">
         <v>0</v>
@@ -47333,7 +47562,7 @@
         <v>5</v>
       </c>
       <c r="J897" s="63" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="K897" s="60">
         <v>30</v>
@@ -47348,7 +47577,7 @@
         <v>1</v>
       </c>
       <c r="O897" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="P897" s="1">
         <v>0</v>
@@ -47383,7 +47612,7 @@
         <v>5</v>
       </c>
       <c r="J898" s="63" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="K898" s="60">
         <v>30</v>
@@ -47398,7 +47627,7 @@
         <v>1</v>
       </c>
       <c r="O898" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="P898" s="1">
         <v>0</v>
@@ -47433,7 +47662,7 @@
         <v>5</v>
       </c>
       <c r="J899" s="63" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="K899" s="60">
         <v>30</v>
@@ -47448,7 +47677,7 @@
         <v>1</v>
       </c>
       <c r="O899" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="P899" s="1">
         <v>0</v>
@@ -47483,7 +47712,7 @@
         <v>5</v>
       </c>
       <c r="J900" s="63" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="K900" s="60">
         <v>30</v>
@@ -47498,7 +47727,7 @@
         <v>1</v>
       </c>
       <c r="O900" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="P900" s="1">
         <v>0</v>
@@ -47533,7 +47762,7 @@
         <v>5</v>
       </c>
       <c r="J901" s="63" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="K901" s="60">
         <v>30</v>
@@ -47548,7 +47777,7 @@
         <v>1</v>
       </c>
       <c r="O901" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="P901" s="1">
         <v>0</v>
@@ -47583,7 +47812,7 @@
         <v>5</v>
       </c>
       <c r="J902" s="63" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="K902" s="60">
         <v>30</v>
@@ -47598,7 +47827,7 @@
         <v>1</v>
       </c>
       <c r="O902" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="P902" s="1">
         <v>0</v>
@@ -47633,7 +47862,7 @@
         <v>1</v>
       </c>
       <c r="J903" s="63" t="s">
-        <v>451</v>
+        <v>520</v>
       </c>
       <c r="K903" s="62">
         <v>400</v>
@@ -47648,7 +47877,7 @@
         <v>2</v>
       </c>
       <c r="O903" s="1" t="s">
-        <v>450</v>
+        <v>549</v>
       </c>
       <c r="P903" s="1">
         <v>0</v>
@@ -47683,7 +47912,7 @@
         <v>1</v>
       </c>
       <c r="J904" s="63" t="s">
-        <v>451</v>
+        <v>521</v>
       </c>
       <c r="K904" s="62">
         <v>400</v>
@@ -47698,7 +47927,7 @@
         <v>2</v>
       </c>
       <c r="O904" s="1" t="s">
-        <v>164</v>
+        <v>550</v>
       </c>
       <c r="P904" s="1">
         <v>0</v>
@@ -47733,7 +47962,7 @@
         <v>1</v>
       </c>
       <c r="J905" s="63" t="s">
-        <v>451</v>
+        <v>522</v>
       </c>
       <c r="K905" s="62">
         <v>400</v>
@@ -47748,7 +47977,7 @@
         <v>2</v>
       </c>
       <c r="O905" s="1" t="s">
-        <v>164</v>
+        <v>551</v>
       </c>
       <c r="P905" s="1">
         <v>0</v>
@@ -47783,7 +48012,7 @@
         <v>1</v>
       </c>
       <c r="J906" s="63" t="s">
-        <v>451</v>
+        <v>521</v>
       </c>
       <c r="K906" s="62">
         <v>400</v>
@@ -47798,7 +48027,7 @@
         <v>2</v>
       </c>
       <c r="O906" s="1" t="s">
-        <v>164</v>
+        <v>552</v>
       </c>
       <c r="P906" s="1">
         <v>0</v>
@@ -47833,7 +48062,7 @@
         <v>1</v>
       </c>
       <c r="J907" s="63" t="s">
-        <v>451</v>
+        <v>520</v>
       </c>
       <c r="K907" s="62">
         <v>400</v>
@@ -47848,7 +48077,7 @@
         <v>2</v>
       </c>
       <c r="O907" s="1" t="s">
-        <v>164</v>
+        <v>553</v>
       </c>
       <c r="P907" s="1">
         <v>0</v>
@@ -47883,7 +48112,7 @@
         <v>1</v>
       </c>
       <c r="J908" s="63" t="s">
-        <v>451</v>
+        <v>523</v>
       </c>
       <c r="K908" s="62">
         <v>400</v>
@@ -47898,7 +48127,7 @@
         <v>2</v>
       </c>
       <c r="O908" s="1" t="s">
-        <v>164</v>
+        <v>554</v>
       </c>
       <c r="P908" s="1">
         <v>0</v>
@@ -47933,7 +48162,7 @@
         <v>2</v>
       </c>
       <c r="J909" s="63" t="s">
-        <v>451</v>
+        <v>523</v>
       </c>
       <c r="K909" s="62">
         <v>400</v>
@@ -47948,7 +48177,7 @@
         <v>2</v>
       </c>
       <c r="O909" s="1" t="s">
-        <v>164</v>
+        <v>555</v>
       </c>
       <c r="P909" s="1">
         <v>0</v>
@@ -47983,7 +48212,7 @@
         <v>2</v>
       </c>
       <c r="J910" s="63" t="s">
-        <v>451</v>
+        <v>521</v>
       </c>
       <c r="K910" s="62">
         <v>400</v>
@@ -47998,7 +48227,7 @@
         <v>2</v>
       </c>
       <c r="O910" s="1" t="s">
-        <v>164</v>
+        <v>556</v>
       </c>
       <c r="P910" s="1">
         <v>0</v>
@@ -48033,7 +48262,7 @@
         <v>2</v>
       </c>
       <c r="J911" s="63" t="s">
-        <v>451</v>
+        <v>522</v>
       </c>
       <c r="K911" s="62">
         <v>400</v>
@@ -48048,7 +48277,7 @@
         <v>2</v>
       </c>
       <c r="O911" s="1" t="s">
-        <v>164</v>
+        <v>557</v>
       </c>
       <c r="P911" s="1">
         <v>0</v>
@@ -48083,7 +48312,7 @@
         <v>2</v>
       </c>
       <c r="J912" s="63" t="s">
-        <v>451</v>
+        <v>524</v>
       </c>
       <c r="K912" s="62">
         <v>400</v>
@@ -48098,7 +48327,7 @@
         <v>2</v>
       </c>
       <c r="O912" s="1" t="s">
-        <v>164</v>
+        <v>558</v>
       </c>
       <c r="P912" s="1">
         <v>0</v>
@@ -48133,7 +48362,7 @@
         <v>2</v>
       </c>
       <c r="J913" s="63" t="s">
-        <v>451</v>
+        <v>521</v>
       </c>
       <c r="K913" s="62">
         <v>400</v>
@@ -48148,7 +48377,7 @@
         <v>2</v>
       </c>
       <c r="O913" s="1" t="s">
-        <v>164</v>
+        <v>559</v>
       </c>
       <c r="P913" s="1">
         <v>0</v>
@@ -48183,7 +48412,7 @@
         <v>2</v>
       </c>
       <c r="J914" s="63" t="s">
-        <v>451</v>
+        <v>522</v>
       </c>
       <c r="K914" s="62">
         <v>400</v>
@@ -48198,7 +48427,7 @@
         <v>2</v>
       </c>
       <c r="O914" s="1" t="s">
-        <v>164</v>
+        <v>560</v>
       </c>
       <c r="P914" s="1">
         <v>0</v>
@@ -48233,7 +48462,7 @@
         <v>2</v>
       </c>
       <c r="J915" s="63" t="s">
-        <v>451</v>
+        <v>525</v>
       </c>
       <c r="K915" s="62">
         <v>400</v>
@@ -48248,7 +48477,7 @@
         <v>2</v>
       </c>
       <c r="O915" s="1" t="s">
-        <v>164</v>
+        <v>561</v>
       </c>
       <c r="P915" s="1">
         <v>0</v>
@@ -48283,7 +48512,7 @@
         <v>2</v>
       </c>
       <c r="J916" s="63" t="s">
-        <v>451</v>
+        <v>524</v>
       </c>
       <c r="K916" s="62">
         <v>400</v>
@@ -48298,7 +48527,7 @@
         <v>2</v>
       </c>
       <c r="O916" s="1" t="s">
-        <v>164</v>
+        <v>562</v>
       </c>
       <c r="P916" s="1">
         <v>0</v>
@@ -48333,7 +48562,7 @@
         <v>3</v>
       </c>
       <c r="J917" s="63" t="s">
-        <v>451</v>
+        <v>526</v>
       </c>
       <c r="K917" s="62">
         <v>400</v>
@@ -48348,7 +48577,7 @@
         <v>2</v>
       </c>
       <c r="O917" s="1" t="s">
-        <v>164</v>
+        <v>563</v>
       </c>
       <c r="P917" s="1">
         <v>0</v>
@@ -48383,7 +48612,7 @@
         <v>3</v>
       </c>
       <c r="J918" s="63" t="s">
-        <v>451</v>
+        <v>527</v>
       </c>
       <c r="K918" s="62">
         <v>400</v>
@@ -48398,7 +48627,7 @@
         <v>2</v>
       </c>
       <c r="O918" s="1" t="s">
-        <v>164</v>
+        <v>564</v>
       </c>
       <c r="P918" s="1">
         <v>0</v>
@@ -48433,7 +48662,7 @@
         <v>3</v>
       </c>
       <c r="J919" s="63" t="s">
-        <v>451</v>
+        <v>528</v>
       </c>
       <c r="K919" s="62">
         <v>400</v>
@@ -48448,7 +48677,7 @@
         <v>2</v>
       </c>
       <c r="O919" s="1" t="s">
-        <v>164</v>
+        <v>565</v>
       </c>
       <c r="P919" s="1">
         <v>0</v>
@@ -48483,7 +48712,7 @@
         <v>3</v>
       </c>
       <c r="J920" s="63" t="s">
-        <v>451</v>
+        <v>526</v>
       </c>
       <c r="K920" s="62">
         <v>400</v>
@@ -48498,7 +48727,7 @@
         <v>2</v>
       </c>
       <c r="O920" s="1" t="s">
-        <v>164</v>
+        <v>566</v>
       </c>
       <c r="P920" s="1">
         <v>0</v>
@@ -48533,7 +48762,7 @@
         <v>3</v>
       </c>
       <c r="J921" s="63" t="s">
-        <v>451</v>
+        <v>529</v>
       </c>
       <c r="K921" s="62">
         <v>400</v>
@@ -48548,7 +48777,7 @@
         <v>2</v>
       </c>
       <c r="O921" s="1" t="s">
-        <v>164</v>
+        <v>567</v>
       </c>
       <c r="P921" s="1">
         <v>0</v>
@@ -48583,7 +48812,7 @@
         <v>3</v>
       </c>
       <c r="J922" s="63" t="s">
-        <v>451</v>
+        <v>526</v>
       </c>
       <c r="K922" s="62">
         <v>400</v>
@@ -48598,7 +48827,7 @@
         <v>2</v>
       </c>
       <c r="O922" s="1" t="s">
-        <v>164</v>
+        <v>568</v>
       </c>
       <c r="P922" s="1">
         <v>0</v>
@@ -48633,7 +48862,7 @@
         <v>3</v>
       </c>
       <c r="J923" s="63" t="s">
-        <v>451</v>
+        <v>530</v>
       </c>
       <c r="K923" s="62">
         <v>400</v>
@@ -48648,7 +48877,7 @@
         <v>2</v>
       </c>
       <c r="O923" s="1" t="s">
-        <v>164</v>
+        <v>569</v>
       </c>
       <c r="P923" s="1">
         <v>0</v>
@@ -48683,7 +48912,7 @@
         <v>3</v>
       </c>
       <c r="J924" s="63" t="s">
-        <v>451</v>
+        <v>531</v>
       </c>
       <c r="K924" s="62">
         <v>400</v>
@@ -48698,7 +48927,7 @@
         <v>2</v>
       </c>
       <c r="O924" s="1" t="s">
-        <v>164</v>
+        <v>570</v>
       </c>
       <c r="P924" s="1">
         <v>0</v>
@@ -48733,7 +48962,7 @@
         <v>3</v>
       </c>
       <c r="J925" s="63" t="s">
-        <v>451</v>
+        <v>532</v>
       </c>
       <c r="K925" s="62">
         <v>400</v>
@@ -48748,7 +48977,7 @@
         <v>2</v>
       </c>
       <c r="O925" s="1" t="s">
-        <v>164</v>
+        <v>571</v>
       </c>
       <c r="P925" s="1">
         <v>0</v>
@@ -48783,7 +49012,7 @@
         <v>3</v>
       </c>
       <c r="J926" s="63" t="s">
-        <v>451</v>
+        <v>528</v>
       </c>
       <c r="K926" s="62">
         <v>400</v>
@@ -48798,7 +49027,7 @@
         <v>2</v>
       </c>
       <c r="O926" s="1" t="s">
-        <v>164</v>
+        <v>572</v>
       </c>
       <c r="P926" s="1">
         <v>0</v>
@@ -48833,7 +49062,7 @@
         <v>4</v>
       </c>
       <c r="J927" s="63" t="s">
-        <v>451</v>
+        <v>533</v>
       </c>
       <c r="K927" s="62">
         <v>400</v>
@@ -48848,7 +49077,7 @@
         <v>2</v>
       </c>
       <c r="O927" s="1" t="s">
-        <v>164</v>
+        <v>573</v>
       </c>
       <c r="P927" s="1">
         <v>0</v>
@@ -48883,7 +49112,7 @@
         <v>4</v>
       </c>
       <c r="J928" s="63" t="s">
-        <v>451</v>
+        <v>527</v>
       </c>
       <c r="K928" s="62">
         <v>400</v>
@@ -48898,7 +49127,7 @@
         <v>2</v>
       </c>
       <c r="O928" s="1" t="s">
-        <v>164</v>
+        <v>574</v>
       </c>
       <c r="P928" s="1">
         <v>0</v>
@@ -48933,7 +49162,7 @@
         <v>4</v>
       </c>
       <c r="J929" s="63" t="s">
-        <v>451</v>
+        <v>527</v>
       </c>
       <c r="K929" s="62">
         <v>400</v>
@@ -48948,7 +49177,7 @@
         <v>2</v>
       </c>
       <c r="O929" s="1" t="s">
-        <v>164</v>
+        <v>575</v>
       </c>
       <c r="P929" s="1">
         <v>0</v>
@@ -48983,7 +49212,7 @@
         <v>4</v>
       </c>
       <c r="J930" s="63" t="s">
-        <v>451</v>
+        <v>534</v>
       </c>
       <c r="K930" s="62">
         <v>400</v>
@@ -48998,7 +49227,7 @@
         <v>2</v>
       </c>
       <c r="O930" s="1" t="s">
-        <v>164</v>
+        <v>576</v>
       </c>
       <c r="P930" s="1">
         <v>0</v>
@@ -49033,7 +49262,7 @@
         <v>4</v>
       </c>
       <c r="J931" s="63" t="s">
-        <v>451</v>
+        <v>535</v>
       </c>
       <c r="K931" s="62">
         <v>400</v>
@@ -49048,7 +49277,7 @@
         <v>2</v>
       </c>
       <c r="O931" s="1" t="s">
-        <v>164</v>
+        <v>577</v>
       </c>
       <c r="P931" s="1">
         <v>0</v>
@@ -49083,7 +49312,7 @@
         <v>4</v>
       </c>
       <c r="J932" s="63" t="s">
-        <v>451</v>
+        <v>526</v>
       </c>
       <c r="K932" s="62">
         <v>400</v>
@@ -49098,7 +49327,7 @@
         <v>2</v>
       </c>
       <c r="O932" s="1" t="s">
-        <v>164</v>
+        <v>578</v>
       </c>
       <c r="P932" s="1">
         <v>0</v>
@@ -49133,7 +49362,7 @@
         <v>4</v>
       </c>
       <c r="J933" s="63" t="s">
-        <v>451</v>
+        <v>536</v>
       </c>
       <c r="K933" s="62">
         <v>400</v>
@@ -49148,7 +49377,7 @@
         <v>2</v>
       </c>
       <c r="O933" s="1" t="s">
-        <v>164</v>
+        <v>579</v>
       </c>
       <c r="P933" s="1">
         <v>0</v>
@@ -49183,7 +49412,7 @@
         <v>4</v>
       </c>
       <c r="J934" s="63" t="s">
-        <v>451</v>
+        <v>528</v>
       </c>
       <c r="K934" s="62">
         <v>400</v>
@@ -49198,7 +49427,7 @@
         <v>2</v>
       </c>
       <c r="O934" s="1" t="s">
-        <v>164</v>
+        <v>580</v>
       </c>
       <c r="P934" s="1">
         <v>0</v>
@@ -49233,7 +49462,7 @@
         <v>4</v>
       </c>
       <c r="J935" s="63" t="s">
-        <v>451</v>
+        <v>537</v>
       </c>
       <c r="K935" s="62">
         <v>400</v>
@@ -49248,7 +49477,7 @@
         <v>2</v>
       </c>
       <c r="O935" s="1" t="s">
-        <v>164</v>
+        <v>581</v>
       </c>
       <c r="P935" s="1">
         <v>0</v>
@@ -49283,7 +49512,7 @@
         <v>4</v>
       </c>
       <c r="J936" s="63" t="s">
-        <v>451</v>
+        <v>538</v>
       </c>
       <c r="K936" s="62">
         <v>400</v>
@@ -49298,7 +49527,7 @@
         <v>2</v>
       </c>
       <c r="O936" s="1" t="s">
-        <v>164</v>
+        <v>582</v>
       </c>
       <c r="P936" s="1">
         <v>0</v>
@@ -49333,7 +49562,7 @@
         <v>4</v>
       </c>
       <c r="J937" s="63" t="s">
-        <v>451</v>
+        <v>537</v>
       </c>
       <c r="K937" s="62">
         <v>400</v>
@@ -49348,7 +49577,7 @@
         <v>2</v>
       </c>
       <c r="O937" s="1" t="s">
-        <v>164</v>
+        <v>583</v>
       </c>
       <c r="P937" s="1">
         <v>0</v>
@@ -49383,7 +49612,7 @@
         <v>4</v>
       </c>
       <c r="J938" s="63" t="s">
-        <v>451</v>
+        <v>539</v>
       </c>
       <c r="K938" s="62">
         <v>400</v>
@@ -49398,7 +49627,7 @@
         <v>2</v>
       </c>
       <c r="O938" s="1" t="s">
-        <v>164</v>
+        <v>584</v>
       </c>
       <c r="P938" s="1">
         <v>0</v>
@@ -49433,7 +49662,7 @@
         <v>5</v>
       </c>
       <c r="J939" s="63" t="s">
-        <v>451</v>
+        <v>540</v>
       </c>
       <c r="K939" s="62">
         <v>400</v>
@@ -49448,7 +49677,7 @@
         <v>2</v>
       </c>
       <c r="O939" s="1" t="s">
-        <v>164</v>
+        <v>585</v>
       </c>
       <c r="P939" s="1">
         <v>0</v>
@@ -49483,7 +49712,7 @@
         <v>5</v>
       </c>
       <c r="J940" s="63" t="s">
-        <v>451</v>
+        <v>541</v>
       </c>
       <c r="K940" s="62">
         <v>400</v>
@@ -49498,7 +49727,7 @@
         <v>2</v>
       </c>
       <c r="O940" s="1" t="s">
-        <v>164</v>
+        <v>586</v>
       </c>
       <c r="P940" s="1">
         <v>0</v>
@@ -49533,7 +49762,7 @@
         <v>5</v>
       </c>
       <c r="J941" s="63" t="s">
-        <v>451</v>
+        <v>541</v>
       </c>
       <c r="K941" s="62">
         <v>400</v>
@@ -49548,7 +49777,7 @@
         <v>2</v>
       </c>
       <c r="O941" s="1" t="s">
-        <v>164</v>
+        <v>587</v>
       </c>
       <c r="P941" s="1">
         <v>0</v>
@@ -49583,7 +49812,7 @@
         <v>5</v>
       </c>
       <c r="J942" s="63" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="K942" s="62">
         <v>400</v>
@@ -49598,7 +49827,7 @@
         <v>2</v>
       </c>
       <c r="O942" s="1" t="s">
-        <v>164</v>
+        <v>588</v>
       </c>
       <c r="P942" s="1">
         <v>0</v>
@@ -49633,7 +49862,7 @@
         <v>5</v>
       </c>
       <c r="J943" s="63" t="s">
-        <v>451</v>
+        <v>540</v>
       </c>
       <c r="K943" s="62">
         <v>400</v>
@@ -49648,7 +49877,7 @@
         <v>2</v>
       </c>
       <c r="O943" s="1" t="s">
-        <v>164</v>
+        <v>589</v>
       </c>
       <c r="P943" s="1">
         <v>0</v>
@@ -49683,7 +49912,7 @@
         <v>5</v>
       </c>
       <c r="J944" s="63" t="s">
-        <v>451</v>
+        <v>543</v>
       </c>
       <c r="K944" s="62">
         <v>400</v>
@@ -49698,7 +49927,7 @@
         <v>2</v>
       </c>
       <c r="O944" s="1" t="s">
-        <v>164</v>
+        <v>590</v>
       </c>
       <c r="P944" s="1">
         <v>0</v>
@@ -49733,7 +49962,7 @@
         <v>5</v>
       </c>
       <c r="J945" s="63" t="s">
-        <v>451</v>
+        <v>544</v>
       </c>
       <c r="K945" s="62">
         <v>400</v>
@@ -49748,7 +49977,7 @@
         <v>2</v>
       </c>
       <c r="O945" s="1" t="s">
-        <v>164</v>
+        <v>591</v>
       </c>
       <c r="P945" s="1">
         <v>0</v>
@@ -49783,7 +50012,7 @@
         <v>5</v>
       </c>
       <c r="J946" s="63" t="s">
-        <v>451</v>
+        <v>545</v>
       </c>
       <c r="K946" s="62">
         <v>400</v>
@@ -49798,7 +50027,7 @@
         <v>2</v>
       </c>
       <c r="O946" s="1" t="s">
-        <v>164</v>
+        <v>592</v>
       </c>
       <c r="P946" s="1">
         <v>0</v>
@@ -49833,7 +50062,7 @@
         <v>5</v>
       </c>
       <c r="J947" s="63" t="s">
-        <v>451</v>
+        <v>540</v>
       </c>
       <c r="K947" s="62">
         <v>400</v>
@@ -49848,7 +50077,7 @@
         <v>2</v>
       </c>
       <c r="O947" s="1" t="s">
-        <v>164</v>
+        <v>593</v>
       </c>
       <c r="P947" s="1">
         <v>0</v>
@@ -49883,7 +50112,7 @@
         <v>5</v>
       </c>
       <c r="J948" s="63" t="s">
-        <v>451</v>
+        <v>546</v>
       </c>
       <c r="K948" s="62">
         <v>400</v>
@@ -49898,7 +50127,7 @@
         <v>2</v>
       </c>
       <c r="O948" s="1" t="s">
-        <v>164</v>
+        <v>594</v>
       </c>
       <c r="P948" s="1">
         <v>0</v>
@@ -49933,7 +50162,7 @@
         <v>5</v>
       </c>
       <c r="J949" s="63" t="s">
-        <v>451</v>
+        <v>546</v>
       </c>
       <c r="K949" s="62">
         <v>400</v>
@@ -49948,7 +50177,7 @@
         <v>2</v>
       </c>
       <c r="O949" s="1" t="s">
-        <v>164</v>
+        <v>595</v>
       </c>
       <c r="P949" s="1">
         <v>0</v>
@@ -49983,7 +50212,7 @@
         <v>5</v>
       </c>
       <c r="J950" s="63" t="s">
-        <v>451</v>
+        <v>547</v>
       </c>
       <c r="K950" s="62">
         <v>400</v>
@@ -49998,7 +50227,7 @@
         <v>2</v>
       </c>
       <c r="O950" s="1" t="s">
-        <v>164</v>
+        <v>596</v>
       </c>
       <c r="P950" s="1">
         <v>0</v>
@@ -50033,7 +50262,7 @@
         <v>5</v>
       </c>
       <c r="J951" s="63" t="s">
-        <v>451</v>
+        <v>540</v>
       </c>
       <c r="K951" s="62">
         <v>400</v>
@@ -50048,7 +50277,7 @@
         <v>2</v>
       </c>
       <c r="O951" s="1" t="s">
-        <v>164</v>
+        <v>597</v>
       </c>
       <c r="P951" s="1">
         <v>0</v>
@@ -50083,7 +50312,7 @@
         <v>5</v>
       </c>
       <c r="J952" s="63" t="s">
-        <v>451</v>
+        <v>548</v>
       </c>
       <c r="K952" s="62">
         <v>400</v>
@@ -50098,7 +50327,7 @@
         <v>2</v>
       </c>
       <c r="O952" s="1" t="s">
-        <v>164</v>
+        <v>598</v>
       </c>
       <c r="P952" s="1">
         <v>0</v>
@@ -50133,7 +50362,7 @@
         <v>1</v>
       </c>
       <c r="J953" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K953" s="62">
         <v>6000</v>
@@ -50148,7 +50377,7 @@
         <v>3</v>
       </c>
       <c r="O953" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P953" s="1">
         <v>0</v>
@@ -50183,7 +50412,7 @@
         <v>1</v>
       </c>
       <c r="J954" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K954" s="62">
         <v>6000</v>
@@ -50198,7 +50427,7 @@
         <v>3</v>
       </c>
       <c r="O954" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P954" s="1">
         <v>0</v>
@@ -50233,7 +50462,7 @@
         <v>1</v>
       </c>
       <c r="J955" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K955" s="62">
         <v>6000</v>
@@ -50248,7 +50477,7 @@
         <v>3</v>
       </c>
       <c r="O955" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P955" s="1">
         <v>0</v>
@@ -50283,7 +50512,7 @@
         <v>1</v>
       </c>
       <c r="J956" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K956" s="62">
         <v>6000</v>
@@ -50298,7 +50527,7 @@
         <v>3</v>
       </c>
       <c r="O956" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P956" s="1">
         <v>0</v>
@@ -50333,7 +50562,7 @@
         <v>1</v>
       </c>
       <c r="J957" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K957" s="62">
         <v>6000</v>
@@ -50348,7 +50577,7 @@
         <v>3</v>
       </c>
       <c r="O957" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P957" s="1">
         <v>0</v>
@@ -50383,7 +50612,7 @@
         <v>1</v>
       </c>
       <c r="J958" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K958" s="62">
         <v>6000</v>
@@ -50398,7 +50627,7 @@
         <v>3</v>
       </c>
       <c r="O958" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P958" s="1">
         <v>0</v>
@@ -50433,7 +50662,7 @@
         <v>1</v>
       </c>
       <c r="J959" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K959" s="62">
         <v>6000</v>
@@ -50448,7 +50677,7 @@
         <v>3</v>
       </c>
       <c r="O959" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P959" s="1">
         <v>0</v>
@@ -50483,7 +50712,7 @@
         <v>1</v>
       </c>
       <c r="J960" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K960" s="62">
         <v>6000</v>
@@ -50498,7 +50727,7 @@
         <v>3</v>
       </c>
       <c r="O960" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P960" s="1">
         <v>0</v>
@@ -50533,7 +50762,7 @@
         <v>2</v>
       </c>
       <c r="J961" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K961" s="62">
         <v>6000</v>
@@ -50548,7 +50777,7 @@
         <v>3</v>
       </c>
       <c r="O961" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P961" s="1">
         <v>0</v>
@@ -50583,7 +50812,7 @@
         <v>2</v>
       </c>
       <c r="J962" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K962" s="62">
         <v>6000</v>
@@ -50598,7 +50827,7 @@
         <v>3</v>
       </c>
       <c r="O962" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P962" s="1">
         <v>0</v>
@@ -50633,7 +50862,7 @@
         <v>2</v>
       </c>
       <c r="J963" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K963" s="62">
         <v>6000</v>
@@ -50648,7 +50877,7 @@
         <v>3</v>
       </c>
       <c r="O963" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P963" s="1">
         <v>0</v>
@@ -50683,7 +50912,7 @@
         <v>2</v>
       </c>
       <c r="J964" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K964" s="62">
         <v>6000</v>
@@ -50698,7 +50927,7 @@
         <v>3</v>
       </c>
       <c r="O964" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P964" s="1">
         <v>0</v>
@@ -50733,7 +50962,7 @@
         <v>2</v>
       </c>
       <c r="J965" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K965" s="62">
         <v>6000</v>
@@ -50748,7 +50977,7 @@
         <v>3</v>
       </c>
       <c r="O965" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P965" s="1">
         <v>0</v>
@@ -50783,7 +51012,7 @@
         <v>2</v>
       </c>
       <c r="J966" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K966" s="62">
         <v>6000</v>
@@ -50798,7 +51027,7 @@
         <v>3</v>
       </c>
       <c r="O966" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P966" s="1">
         <v>0</v>
@@ -50833,7 +51062,7 @@
         <v>2</v>
       </c>
       <c r="J967" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K967" s="62">
         <v>6000</v>
@@ -50848,7 +51077,7 @@
         <v>3</v>
       </c>
       <c r="O967" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P967" s="1">
         <v>0</v>
@@ -50883,7 +51112,7 @@
         <v>2</v>
       </c>
       <c r="J968" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K968" s="62">
         <v>6000</v>
@@ -50898,7 +51127,7 @@
         <v>3</v>
       </c>
       <c r="O968" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P968" s="1">
         <v>0</v>
@@ -50933,7 +51162,7 @@
         <v>2</v>
       </c>
       <c r="J969" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K969" s="62">
         <v>6000</v>
@@ -50948,7 +51177,7 @@
         <v>3</v>
       </c>
       <c r="O969" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P969" s="1">
         <v>0</v>
@@ -50983,7 +51212,7 @@
         <v>2</v>
       </c>
       <c r="J970" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K970" s="62">
         <v>6000</v>
@@ -50998,7 +51227,7 @@
         <v>3</v>
       </c>
       <c r="O970" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P970" s="1">
         <v>0</v>
@@ -51033,7 +51262,7 @@
         <v>3</v>
       </c>
       <c r="J971" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K971" s="62">
         <v>6000</v>
@@ -51048,7 +51277,7 @@
         <v>3</v>
       </c>
       <c r="O971" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P971" s="1">
         <v>0</v>
@@ -51083,7 +51312,7 @@
         <v>3</v>
       </c>
       <c r="J972" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K972" s="62">
         <v>6000</v>
@@ -51098,7 +51327,7 @@
         <v>3</v>
       </c>
       <c r="O972" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P972" s="1">
         <v>0</v>
@@ -51133,7 +51362,7 @@
         <v>3</v>
       </c>
       <c r="J973" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K973" s="62">
         <v>6000</v>
@@ -51148,7 +51377,7 @@
         <v>3</v>
       </c>
       <c r="O973" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P973" s="1">
         <v>0</v>
@@ -51183,7 +51412,7 @@
         <v>3</v>
       </c>
       <c r="J974" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K974" s="62">
         <v>6000</v>
@@ -51198,7 +51427,7 @@
         <v>3</v>
       </c>
       <c r="O974" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P974" s="1">
         <v>0</v>
@@ -51233,7 +51462,7 @@
         <v>3</v>
       </c>
       <c r="J975" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K975" s="62">
         <v>6000</v>
@@ -51248,7 +51477,7 @@
         <v>3</v>
       </c>
       <c r="O975" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P975" s="1">
         <v>0</v>
@@ -51283,7 +51512,7 @@
         <v>3</v>
       </c>
       <c r="J976" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K976" s="62">
         <v>6000</v>
@@ -51298,7 +51527,7 @@
         <v>3</v>
       </c>
       <c r="O976" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P976" s="1">
         <v>0</v>
@@ -51333,7 +51562,7 @@
         <v>3</v>
       </c>
       <c r="J977" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K977" s="62">
         <v>6000</v>
@@ -51348,7 +51577,7 @@
         <v>3</v>
       </c>
       <c r="O977" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P977" s="1">
         <v>0</v>
@@ -51383,7 +51612,7 @@
         <v>3</v>
       </c>
       <c r="J978" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K978" s="62">
         <v>6000</v>
@@ -51398,7 +51627,7 @@
         <v>3</v>
       </c>
       <c r="O978" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P978" s="1">
         <v>0</v>
@@ -51433,7 +51662,7 @@
         <v>3</v>
       </c>
       <c r="J979" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K979" s="62">
         <v>6000</v>
@@ -51448,7 +51677,7 @@
         <v>3</v>
       </c>
       <c r="O979" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P979" s="1">
         <v>0</v>
@@ -51483,7 +51712,7 @@
         <v>3</v>
       </c>
       <c r="J980" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K980" s="62">
         <v>6000</v>
@@ -51498,7 +51727,7 @@
         <v>3</v>
       </c>
       <c r="O980" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P980" s="1">
         <v>0</v>
@@ -51533,7 +51762,7 @@
         <v>3</v>
       </c>
       <c r="J981" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K981" s="62">
         <v>6000</v>
@@ -51548,7 +51777,7 @@
         <v>3</v>
       </c>
       <c r="O981" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P981" s="1">
         <v>0</v>
@@ -51583,7 +51812,7 @@
         <v>3</v>
       </c>
       <c r="J982" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K982" s="62">
         <v>6000</v>
@@ -51598,7 +51827,7 @@
         <v>3</v>
       </c>
       <c r="O982" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P982" s="1">
         <v>0</v>
@@ -51633,7 +51862,7 @@
         <v>4</v>
       </c>
       <c r="J983" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K983" s="62">
         <v>6000</v>
@@ -51648,7 +51877,7 @@
         <v>3</v>
       </c>
       <c r="O983" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P983" s="1">
         <v>0</v>
@@ -51683,7 +51912,7 @@
         <v>4</v>
       </c>
       <c r="J984" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K984" s="62">
         <v>6000</v>
@@ -51698,7 +51927,7 @@
         <v>3</v>
       </c>
       <c r="O984" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P984" s="1">
         <v>0</v>
@@ -51733,7 +51962,7 @@
         <v>4</v>
       </c>
       <c r="J985" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K985" s="62">
         <v>6000</v>
@@ -51748,7 +51977,7 @@
         <v>3</v>
       </c>
       <c r="O985" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P985" s="1">
         <v>0</v>
@@ -51783,7 +52012,7 @@
         <v>4</v>
       </c>
       <c r="J986" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K986" s="62">
         <v>6000</v>
@@ -51798,7 +52027,7 @@
         <v>3</v>
       </c>
       <c r="O986" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P986" s="1">
         <v>0</v>
@@ -51833,7 +52062,7 @@
         <v>4</v>
       </c>
       <c r="J987" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K987" s="62">
         <v>6000</v>
@@ -51848,7 +52077,7 @@
         <v>3</v>
       </c>
       <c r="O987" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P987" s="1">
         <v>0</v>
@@ -51883,7 +52112,7 @@
         <v>4</v>
       </c>
       <c r="J988" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K988" s="62">
         <v>6000</v>
@@ -51898,7 +52127,7 @@
         <v>3</v>
       </c>
       <c r="O988" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P988" s="1">
         <v>0</v>
@@ -51933,7 +52162,7 @@
         <v>4</v>
       </c>
       <c r="J989" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K989" s="62">
         <v>6000</v>
@@ -51948,7 +52177,7 @@
         <v>3</v>
       </c>
       <c r="O989" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P989" s="1">
         <v>0</v>
@@ -51983,7 +52212,7 @@
         <v>4</v>
       </c>
       <c r="J990" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K990" s="62">
         <v>6000</v>
@@ -51998,7 +52227,7 @@
         <v>3</v>
       </c>
       <c r="O990" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P990" s="1">
         <v>0</v>
@@ -52033,7 +52262,7 @@
         <v>4</v>
       </c>
       <c r="J991" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K991" s="62">
         <v>6000</v>
@@ -52048,7 +52277,7 @@
         <v>3</v>
       </c>
       <c r="O991" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P991" s="1">
         <v>0</v>
@@ -52083,7 +52312,7 @@
         <v>4</v>
       </c>
       <c r="J992" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K992" s="62">
         <v>6000</v>
@@ -52098,7 +52327,7 @@
         <v>3</v>
       </c>
       <c r="O992" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P992" s="1">
         <v>0</v>
@@ -52133,7 +52362,7 @@
         <v>4</v>
       </c>
       <c r="J993" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K993" s="62">
         <v>6000</v>
@@ -52148,7 +52377,7 @@
         <v>3</v>
       </c>
       <c r="O993" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P993" s="1">
         <v>0</v>
@@ -52183,7 +52412,7 @@
         <v>4</v>
       </c>
       <c r="J994" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K994" s="62">
         <v>6000</v>
@@ -52198,7 +52427,7 @@
         <v>3</v>
       </c>
       <c r="O994" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P994" s="1">
         <v>0</v>
@@ -52233,7 +52462,7 @@
         <v>4</v>
       </c>
       <c r="J995" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K995" s="62">
         <v>6000</v>
@@ -52248,7 +52477,7 @@
         <v>3</v>
       </c>
       <c r="O995" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P995" s="1">
         <v>0</v>
@@ -52283,7 +52512,7 @@
         <v>4</v>
       </c>
       <c r="J996" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K996" s="62">
         <v>6000</v>
@@ -52298,7 +52527,7 @@
         <v>3</v>
       </c>
       <c r="O996" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P996" s="1">
         <v>0</v>
@@ -52333,7 +52562,7 @@
         <v>5</v>
       </c>
       <c r="J997" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K997" s="62">
         <v>6000</v>
@@ -52348,7 +52577,7 @@
         <v>3</v>
       </c>
       <c r="O997" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P997" s="1">
         <v>0</v>
@@ -52383,7 +52612,7 @@
         <v>5</v>
       </c>
       <c r="J998" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K998" s="62">
         <v>6000</v>
@@ -52398,7 +52627,7 @@
         <v>3</v>
       </c>
       <c r="O998" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P998" s="1">
         <v>0</v>
@@ -52433,7 +52662,7 @@
         <v>5</v>
       </c>
       <c r="J999" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K999" s="62">
         <v>6000</v>
@@ -52448,7 +52677,7 @@
         <v>3</v>
       </c>
       <c r="O999" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P999" s="1">
         <v>0</v>
@@ -52483,7 +52712,7 @@
         <v>5</v>
       </c>
       <c r="J1000" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1000" s="62">
         <v>6000</v>
@@ -52498,7 +52727,7 @@
         <v>3</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1000" s="1">
         <v>0</v>
@@ -52533,7 +52762,7 @@
         <v>5</v>
       </c>
       <c r="J1001" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1001" s="62">
         <v>6000</v>
@@ -52548,7 +52777,7 @@
         <v>3</v>
       </c>
       <c r="O1001" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1001" s="1">
         <v>0</v>
@@ -52583,7 +52812,7 @@
         <v>5</v>
       </c>
       <c r="J1002" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1002" s="62">
         <v>6000</v>
@@ -52598,7 +52827,7 @@
         <v>3</v>
       </c>
       <c r="O1002" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1002" s="1">
         <v>0</v>
@@ -52633,7 +52862,7 @@
         <v>5</v>
       </c>
       <c r="J1003" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1003" s="62">
         <v>6000</v>
@@ -52648,7 +52877,7 @@
         <v>3</v>
       </c>
       <c r="O1003" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1003" s="1">
         <v>0</v>
@@ -52683,7 +52912,7 @@
         <v>5</v>
       </c>
       <c r="J1004" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1004" s="62">
         <v>6000</v>
@@ -52698,7 +52927,7 @@
         <v>3</v>
       </c>
       <c r="O1004" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1004" s="1">
         <v>0</v>
@@ -52733,7 +52962,7 @@
         <v>5</v>
       </c>
       <c r="J1005" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1005" s="62">
         <v>6000</v>
@@ -52748,7 +52977,7 @@
         <v>3</v>
       </c>
       <c r="O1005" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1005" s="1">
         <v>0</v>
@@ -52783,7 +53012,7 @@
         <v>5</v>
       </c>
       <c r="J1006" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1006" s="62">
         <v>6000</v>
@@ -52798,7 +53027,7 @@
         <v>3</v>
       </c>
       <c r="O1006" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1006" s="1">
         <v>0</v>
@@ -52833,7 +53062,7 @@
         <v>5</v>
       </c>
       <c r="J1007" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1007" s="62">
         <v>6000</v>
@@ -52848,7 +53077,7 @@
         <v>3</v>
       </c>
       <c r="O1007" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1007" s="1">
         <v>0</v>
@@ -52883,7 +53112,7 @@
         <v>5</v>
       </c>
       <c r="J1008" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1008" s="62">
         <v>6000</v>
@@ -52898,7 +53127,7 @@
         <v>3</v>
       </c>
       <c r="O1008" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1008" s="1">
         <v>0</v>
@@ -52933,7 +53162,7 @@
         <v>5</v>
       </c>
       <c r="J1009" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1009" s="62">
         <v>6000</v>
@@ -52948,7 +53177,7 @@
         <v>3</v>
       </c>
       <c r="O1009" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1009" s="1">
         <v>0</v>
@@ -52983,7 +53212,7 @@
         <v>5</v>
       </c>
       <c r="J1010" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1010" s="62">
         <v>6000</v>
@@ -52998,7 +53227,7 @@
         <v>3</v>
       </c>
       <c r="O1010" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1010" s="1">
         <v>0</v>
@@ -53033,7 +53262,7 @@
         <v>5</v>
       </c>
       <c r="J1011" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1011" s="62">
         <v>6000</v>
@@ -53048,7 +53277,7 @@
         <v>3</v>
       </c>
       <c r="O1011" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1011" s="1">
         <v>0</v>
@@ -53083,7 +53312,7 @@
         <v>5</v>
       </c>
       <c r="J1012" s="63" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K1012" s="62">
         <v>6000</v>
@@ -53098,7 +53327,7 @@
         <v>3</v>
       </c>
       <c r="O1012" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P1012" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C46D504F-9BD5-4799-B447-2016FA7AD767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1E6836-C6FE-4445-8DA3-DFB6AFBDB10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="690">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1490,14 +1490,6 @@
     <t>90,35,95,47</t>
   </si>
   <si>
-    <t>74104</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>50,20</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>75,20,75,10</t>
   </si>
   <si>
@@ -1937,6 +1929,285 @@
   </si>
   <si>
     <t>75,60,75,70,75,80,75,90</t>
+  </si>
+  <si>
+    <t>74104,74104,74104,74101</t>
+  </si>
+  <si>
+    <t>74107,74101,74101</t>
+  </si>
+  <si>
+    <t>74104,74104,74104</t>
+  </si>
+  <si>
+    <t>74104,74104,74101,74101</t>
+  </si>
+  <si>
+    <t>74110,74101,74101</t>
+  </si>
+  <si>
+    <t>74107,74104,74104,74101</t>
+  </si>
+  <si>
+    <t>74104,74104,74104,74104</t>
+  </si>
+  <si>
+    <t>74107,74107,74104,74104</t>
+  </si>
+  <si>
+    <t>74110,74104,74104,74104</t>
+  </si>
+  <si>
+    <t>74101,74101,74101,74101</t>
+  </si>
+  <si>
+    <t>74107,74104,74104,74101,74101</t>
+  </si>
+  <si>
+    <t>74105,74105,74105,74102,74102</t>
+  </si>
+  <si>
+    <t>74108,74105,74105,74102</t>
+  </si>
+  <si>
+    <t>74105,74105,74102,74102,74102</t>
+  </si>
+  <si>
+    <t>74111,74105,74105,74105,74105</t>
+  </si>
+  <si>
+    <t>74105,74105,74102,74102</t>
+  </si>
+  <si>
+    <t>74108,74108,74102,74102,74102</t>
+  </si>
+  <si>
+    <t>74105,74105,74105,74105</t>
+  </si>
+  <si>
+    <t>74108,74108,74102,74102</t>
+  </si>
+  <si>
+    <t>74111,74105,74105,74102</t>
+  </si>
+  <si>
+    <t>74108,74108,74105,74105,74105</t>
+  </si>
+  <si>
+    <t>74108,74105,74105,74102,74102</t>
+  </si>
+  <si>
+    <t>74111,74105,74105,74105</t>
+  </si>
+  <si>
+    <t>74108,74108,74108,74102,74102</t>
+  </si>
+  <si>
+    <t>74111,74108,74108,74102,74102</t>
+  </si>
+  <si>
+    <t>74108,74108,74108,74108</t>
+  </si>
+  <si>
+    <t>74106,74106,74106,74106,74103,74103</t>
+  </si>
+  <si>
+    <t>74109,74109,74106,74106,74103,74103</t>
+  </si>
+  <si>
+    <t>74112,74109,74109,74106,74106</t>
+  </si>
+  <si>
+    <t>74109,74109,74109,74103,74103</t>
+  </si>
+  <si>
+    <t>74112,74109,74109,74109</t>
+  </si>
+  <si>
+    <t>74112,74112,74109,74109,74109,74109</t>
+  </si>
+  <si>
+    <t>74112,74112,74112,74103,74103</t>
+  </si>
+  <si>
+    <t>74109,74109,74109,74109,74109</t>
+  </si>
+  <si>
+    <t>50,25,50,30,50,20,40,35</t>
+  </si>
+  <si>
+    <t>55,25,40,30,40,25</t>
+  </si>
+  <si>
+    <t>50,25,50,30,50,20</t>
+  </si>
+  <si>
+    <t>45,30,45,20,35,35,35,25</t>
+  </si>
+  <si>
+    <t>45,25,45,35,50,35</t>
+  </si>
+  <si>
+    <t>40,25,40,30,40,20</t>
+  </si>
+  <si>
+    <t>45,25,40,30,40,20</t>
+  </si>
+  <si>
+    <t>40,30,40,20,30,25,30,30</t>
+  </si>
+  <si>
+    <t>70,35,70,30,90,35,90,30</t>
+  </si>
+  <si>
+    <t>70,30,75,35,75,25,90,25</t>
+  </si>
+  <si>
+    <t>75,35,75,28,75,21,75,14</t>
+  </si>
+  <si>
+    <t>75,30,75,20,90,20,90,15</t>
+  </si>
+  <si>
+    <t>70,25,70,15,75,30,75,10</t>
+  </si>
+  <si>
+    <t>75,25,75,15,85,10,85,15</t>
+  </si>
+  <si>
+    <t>70,20,75,30,75,10,75,20</t>
+  </si>
+  <si>
+    <t>80,25,80,10,80,15,80,20</t>
+  </si>
+  <si>
+    <t>70,20,75,30,75,10,75,10,70,5</t>
+  </si>
+  <si>
+    <t>75,10,75,17,75,24,75,31</t>
+  </si>
+  <si>
+    <t>69,45,75,45,72,50,69,90,75,90</t>
+  </si>
+  <si>
+    <t>72,50,69,55,75,55,69,85</t>
+  </si>
+  <si>
+    <t>72,50,69,55,75,55,75,85</t>
+  </si>
+  <si>
+    <t>69,35,75,35,69,25,75,25,72,20</t>
+  </si>
+  <si>
+    <t>72,40,69,35,75,35,69,30,75,30</t>
+  </si>
+  <si>
+    <t>69,35,75,35,69,20,75,20,72,15</t>
+  </si>
+  <si>
+    <t>69,60,75,60,69,80,75,80,72,75</t>
+  </si>
+  <si>
+    <t>60,32,68,32,76,32,84,32</t>
+  </si>
+  <si>
+    <t>66,30,77,30,66,10,77,10</t>
+  </si>
+  <si>
+    <t>72,30,66,25,77,25,72,5</t>
+  </si>
+  <si>
+    <t>66,25,77,25,58,10,85,10</t>
+  </si>
+  <si>
+    <t>66,25,77,25,60,20,72,20,84,20</t>
+  </si>
+  <si>
+    <t>40,35,40,30,40,25,25,35,25,27</t>
+  </si>
+  <si>
+    <t>40,30,35,35,35,20,20,35,20,27</t>
+  </si>
+  <si>
+    <t>40,30,35,35,35,20,15,35,15,27</t>
+  </si>
+  <si>
+    <t>65,30,70,30,70,35,70,25</t>
+  </si>
+  <si>
+    <t>70,30,70,35,70,25,40,10,45,10</t>
+  </si>
+  <si>
+    <t>65,30,65,25,70,30,70,35,70,25</t>
+  </si>
+  <si>
+    <t>65,30,65,25,50,10,55,10</t>
+  </si>
+  <si>
+    <t>40,30,35,35,35,30,35,25,35,20</t>
+  </si>
+  <si>
+    <t>80,35,80,30,80,25,60,10,65,10</t>
+  </si>
+  <si>
+    <t>75,35,75,30,75,25,70,10,75,10</t>
+  </si>
+  <si>
+    <t>75,35,75,30,75,25,80,10,85,10</t>
+  </si>
+  <si>
+    <t>35,30,30,35,30,25,90,10,95,15</t>
+  </si>
+  <si>
+    <t>30,30,30,25,30,35,95,20,95,25</t>
+  </si>
+  <si>
+    <t>35,25,35,32,80,25,80,32</t>
+  </si>
+  <si>
+    <t>60,35,65,35,70,35,75,35,69,50,75,50</t>
+  </si>
+  <si>
+    <t>50,20,50,25,45,20,45,15,45,5,40,10</t>
+  </si>
+  <si>
+    <t>85,20,85,25,90,20,90,15,95,5,90,10</t>
+  </si>
+  <si>
+    <t>72,35,67,40,75,40,67,35,75,35</t>
+  </si>
+  <si>
+    <t>50,20,50,25,45,20,50,10,55,10</t>
+  </si>
+  <si>
+    <t>85,20,85,25,90,20,85,10,80,10</t>
+  </si>
+  <si>
+    <t>72,35,67,40,75,40,72,40</t>
+  </si>
+  <si>
+    <t>50,20,50,25,45,20,60,10,65,10</t>
+  </si>
+  <si>
+    <t>85,20,85,25,90,20,75,10,70,10</t>
+  </si>
+  <si>
+    <t>60,35,80,35,67,40,76,40,55,30,85,30</t>
+  </si>
+  <si>
+    <t>50,20,50,25,45,20,30,15,35,15</t>
+  </si>
+  <si>
+    <t>85,20,85,25,90,20,95,15,90,15</t>
+  </si>
+  <si>
+    <t>50,20,50,25,45,20,40,15,45,15</t>
+  </si>
+  <si>
+    <t>60,35,80,35,72,40,85,15,80,15</t>
+  </si>
+  <si>
+    <t>85,20,85,25,90,20,80,25,75,20</t>
   </si>
 </sst>
 </file>
@@ -45862,7 +46133,7 @@
         <v>1</v>
       </c>
       <c r="J863" s="61" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K863" s="60">
         <v>30</v>
@@ -45877,7 +46148,7 @@
         <v>1</v>
       </c>
       <c r="O863" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P863" s="1">
         <v>0</v>
@@ -45912,7 +46183,7 @@
         <v>1</v>
       </c>
       <c r="J864" s="61" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K864" s="60">
         <v>30</v>
@@ -45927,7 +46198,7 @@
         <v>1</v>
       </c>
       <c r="O864" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P864" s="1">
         <v>0</v>
@@ -45962,7 +46233,7 @@
         <v>1</v>
       </c>
       <c r="J865" s="61" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K865" s="60">
         <v>30</v>
@@ -45977,7 +46248,7 @@
         <v>1</v>
       </c>
       <c r="O865" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P865" s="1">
         <v>0</v>
@@ -46012,7 +46283,7 @@
         <v>1</v>
       </c>
       <c r="J866" s="61" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K866" s="60">
         <v>30</v>
@@ -46027,7 +46298,7 @@
         <v>1</v>
       </c>
       <c r="O866" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="P866" s="1">
         <v>0</v>
@@ -46062,7 +46333,7 @@
         <v>2</v>
       </c>
       <c r="J867" s="61" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="K867" s="60">
         <v>30</v>
@@ -46077,7 +46348,7 @@
         <v>1</v>
       </c>
       <c r="O867" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P867" s="1">
         <v>0</v>
@@ -46112,7 +46383,7 @@
         <v>2</v>
       </c>
       <c r="J868" s="61" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K868" s="60">
         <v>30</v>
@@ -46127,7 +46398,7 @@
         <v>1</v>
       </c>
       <c r="O868" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P868" s="1">
         <v>0</v>
@@ -46162,7 +46433,7 @@
         <v>2</v>
       </c>
       <c r="J869" s="61" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K869" s="60">
         <v>30</v>
@@ -46177,7 +46448,7 @@
         <v>1</v>
       </c>
       <c r="O869" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P869" s="1">
         <v>0</v>
@@ -46212,7 +46483,7 @@
         <v>2</v>
       </c>
       <c r="J870" s="61" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K870" s="60">
         <v>30</v>
@@ -46227,7 +46498,7 @@
         <v>1</v>
       </c>
       <c r="O870" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="P870" s="1">
         <v>0</v>
@@ -46262,7 +46533,7 @@
         <v>2</v>
       </c>
       <c r="J871" s="61" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="K871" s="60">
         <v>30</v>
@@ -46277,7 +46548,7 @@
         <v>1</v>
       </c>
       <c r="O871" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P871" s="1">
         <v>0</v>
@@ -46312,7 +46583,7 @@
         <v>2</v>
       </c>
       <c r="J872" s="61" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="K872" s="60">
         <v>30</v>
@@ -46327,7 +46598,7 @@
         <v>1</v>
       </c>
       <c r="O872" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P872" s="1">
         <v>0</v>
@@ -46362,7 +46633,7 @@
         <v>3</v>
       </c>
       <c r="J873" s="61" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="K873" s="60">
         <v>30</v>
@@ -46377,7 +46648,7 @@
         <v>1</v>
       </c>
       <c r="O873" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P873" s="1">
         <v>0</v>
@@ -46412,7 +46683,7 @@
         <v>3</v>
       </c>
       <c r="J874" s="61" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="K874" s="60">
         <v>30</v>
@@ -46427,7 +46698,7 @@
         <v>1</v>
       </c>
       <c r="O874" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="P874" s="1">
         <v>0</v>
@@ -46462,7 +46733,7 @@
         <v>3</v>
       </c>
       <c r="J875" s="61" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K875" s="60">
         <v>30</v>
@@ -46477,7 +46748,7 @@
         <v>1</v>
       </c>
       <c r="O875" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P875" s="1">
         <v>0</v>
@@ -46512,7 +46783,7 @@
         <v>3</v>
       </c>
       <c r="J876" s="61" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K876" s="60">
         <v>30</v>
@@ -46527,7 +46798,7 @@
         <v>1</v>
       </c>
       <c r="O876" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P876" s="1">
         <v>0</v>
@@ -46562,7 +46833,7 @@
         <v>3</v>
       </c>
       <c r="J877" s="61" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="K877" s="60">
         <v>30</v>
@@ -46577,7 +46848,7 @@
         <v>1</v>
       </c>
       <c r="O877" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="P877" s="1">
         <v>0</v>
@@ -46612,7 +46883,7 @@
         <v>3</v>
       </c>
       <c r="J878" s="61" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K878" s="60">
         <v>30</v>
@@ -46627,7 +46898,7 @@
         <v>1</v>
       </c>
       <c r="O878" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P878" s="1">
         <v>0</v>
@@ -46662,7 +46933,7 @@
         <v>3</v>
       </c>
       <c r="J879" s="61" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="K879" s="60">
         <v>30</v>
@@ -46677,7 +46948,7 @@
         <v>1</v>
       </c>
       <c r="O879" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="P879" s="1">
         <v>0</v>
@@ -46712,7 +46983,7 @@
         <v>3</v>
       </c>
       <c r="J880" s="61" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K880" s="60">
         <v>30</v>
@@ -46727,7 +46998,7 @@
         <v>1</v>
       </c>
       <c r="O880" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P880" s="1">
         <v>0</v>
@@ -46762,7 +47033,7 @@
         <v>4</v>
       </c>
       <c r="J881" s="61" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K881" s="60">
         <v>30</v>
@@ -46777,7 +47048,7 @@
         <v>1</v>
       </c>
       <c r="O881" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P881" s="1">
         <v>0</v>
@@ -46812,7 +47083,7 @@
         <v>4</v>
       </c>
       <c r="J882" s="61" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K882" s="60">
         <v>30</v>
@@ -46827,7 +47098,7 @@
         <v>1</v>
       </c>
       <c r="O882" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="P882" s="1">
         <v>0</v>
@@ -46862,7 +47133,7 @@
         <v>4</v>
       </c>
       <c r="J883" s="61" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K883" s="60">
         <v>30</v>
@@ -46877,7 +47148,7 @@
         <v>1</v>
       </c>
       <c r="O883" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="P883" s="1">
         <v>0</v>
@@ -46912,7 +47183,7 @@
         <v>4</v>
       </c>
       <c r="J884" s="61" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K884" s="60">
         <v>30</v>
@@ -46927,7 +47198,7 @@
         <v>1</v>
       </c>
       <c r="O884" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P884" s="1">
         <v>0</v>
@@ -46962,7 +47233,7 @@
         <v>4</v>
       </c>
       <c r="J885" s="61" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K885" s="60">
         <v>30</v>
@@ -46977,7 +47248,7 @@
         <v>1</v>
       </c>
       <c r="O885" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="P885" s="1">
         <v>0</v>
@@ -47012,7 +47283,7 @@
         <v>4</v>
       </c>
       <c r="J886" s="61" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K886" s="60">
         <v>30</v>
@@ -47027,7 +47298,7 @@
         <v>1</v>
       </c>
       <c r="O886" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P886" s="1">
         <v>0</v>
@@ -47062,7 +47333,7 @@
         <v>4</v>
       </c>
       <c r="J887" s="61" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="K887" s="60">
         <v>30</v>
@@ -47077,7 +47348,7 @@
         <v>1</v>
       </c>
       <c r="O887" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="P887" s="1">
         <v>0</v>
@@ -47112,7 +47383,7 @@
         <v>4</v>
       </c>
       <c r="J888" s="61" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="K888" s="60">
         <v>30</v>
@@ -47127,7 +47398,7 @@
         <v>1</v>
       </c>
       <c r="O888" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="P888" s="1">
         <v>0</v>
@@ -47162,7 +47433,7 @@
         <v>4</v>
       </c>
       <c r="J889" s="61" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="K889" s="60">
         <v>30</v>
@@ -47177,7 +47448,7 @@
         <v>1</v>
       </c>
       <c r="O889" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="P889" s="1">
         <v>0</v>
@@ -47212,7 +47483,7 @@
         <v>4</v>
       </c>
       <c r="J890" s="61" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K890" s="60">
         <v>30</v>
@@ -47227,7 +47498,7 @@
         <v>1</v>
       </c>
       <c r="O890" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P890" s="1">
         <v>0</v>
@@ -47262,7 +47533,7 @@
         <v>5</v>
       </c>
       <c r="J891" s="61" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K891" s="60">
         <v>30</v>
@@ -47277,7 +47548,7 @@
         <v>1</v>
       </c>
       <c r="O891" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="P891" s="1">
         <v>0</v>
@@ -47312,7 +47583,7 @@
         <v>5</v>
       </c>
       <c r="J892" s="61" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K892" s="60">
         <v>30</v>
@@ -47327,7 +47598,7 @@
         <v>1</v>
       </c>
       <c r="O892" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="P892" s="1">
         <v>0</v>
@@ -47362,7 +47633,7 @@
         <v>5</v>
       </c>
       <c r="J893" s="63" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K893" s="60">
         <v>30</v>
@@ -47377,7 +47648,7 @@
         <v>1</v>
       </c>
       <c r="O893" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P893" s="1">
         <v>0</v>
@@ -47412,7 +47683,7 @@
         <v>5</v>
       </c>
       <c r="J894" s="63" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K894" s="60">
         <v>30</v>
@@ -47427,7 +47698,7 @@
         <v>1</v>
       </c>
       <c r="O894" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="P894" s="1">
         <v>0</v>
@@ -47462,7 +47733,7 @@
         <v>5</v>
       </c>
       <c r="J895" s="63" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="K895" s="60">
         <v>30</v>
@@ -47477,7 +47748,7 @@
         <v>1</v>
       </c>
       <c r="O895" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="P895" s="1">
         <v>0</v>
@@ -47512,7 +47783,7 @@
         <v>5</v>
       </c>
       <c r="J896" s="63" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="K896" s="60">
         <v>30</v>
@@ -47527,7 +47798,7 @@
         <v>1</v>
       </c>
       <c r="O896" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="P896" s="1">
         <v>0</v>
@@ -47562,7 +47833,7 @@
         <v>5</v>
       </c>
       <c r="J897" s="63" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K897" s="60">
         <v>30</v>
@@ -47577,7 +47848,7 @@
         <v>1</v>
       </c>
       <c r="O897" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P897" s="1">
         <v>0</v>
@@ -47612,7 +47883,7 @@
         <v>5</v>
       </c>
       <c r="J898" s="63" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K898" s="60">
         <v>30</v>
@@ -47627,7 +47898,7 @@
         <v>1</v>
       </c>
       <c r="O898" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P898" s="1">
         <v>0</v>
@@ -47662,7 +47933,7 @@
         <v>5</v>
       </c>
       <c r="J899" s="63" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K899" s="60">
         <v>30</v>
@@ -47677,7 +47948,7 @@
         <v>1</v>
       </c>
       <c r="O899" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="P899" s="1">
         <v>0</v>
@@ -47712,7 +47983,7 @@
         <v>5</v>
       </c>
       <c r="J900" s="63" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K900" s="60">
         <v>30</v>
@@ -47727,7 +47998,7 @@
         <v>1</v>
       </c>
       <c r="O900" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="P900" s="1">
         <v>0</v>
@@ -47762,7 +48033,7 @@
         <v>5</v>
       </c>
       <c r="J901" s="63" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K901" s="60">
         <v>30</v>
@@ -47777,7 +48048,7 @@
         <v>1</v>
       </c>
       <c r="O901" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="P901" s="1">
         <v>0</v>
@@ -47812,7 +48083,7 @@
         <v>5</v>
       </c>
       <c r="J902" s="63" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K902" s="60">
         <v>30</v>
@@ -47827,7 +48098,7 @@
         <v>1</v>
       </c>
       <c r="O902" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="P902" s="1">
         <v>0</v>
@@ -47862,7 +48133,7 @@
         <v>1</v>
       </c>
       <c r="J903" s="63" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="K903" s="62">
         <v>400</v>
@@ -47877,7 +48148,7 @@
         <v>2</v>
       </c>
       <c r="O903" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="P903" s="1">
         <v>0</v>
@@ -47912,7 +48183,7 @@
         <v>1</v>
       </c>
       <c r="J904" s="63" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K904" s="62">
         <v>400</v>
@@ -47927,7 +48198,7 @@
         <v>2</v>
       </c>
       <c r="O904" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="P904" s="1">
         <v>0</v>
@@ -47962,7 +48233,7 @@
         <v>1</v>
       </c>
       <c r="J905" s="63" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="K905" s="62">
         <v>400</v>
@@ -47977,7 +48248,7 @@
         <v>2</v>
       </c>
       <c r="O905" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="P905" s="1">
         <v>0</v>
@@ -48012,7 +48283,7 @@
         <v>1</v>
       </c>
       <c r="J906" s="63" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K906" s="62">
         <v>400</v>
@@ -48027,7 +48298,7 @@
         <v>2</v>
       </c>
       <c r="O906" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="P906" s="1">
         <v>0</v>
@@ -48062,7 +48333,7 @@
         <v>1</v>
       </c>
       <c r="J907" s="63" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="K907" s="62">
         <v>400</v>
@@ -48077,7 +48348,7 @@
         <v>2</v>
       </c>
       <c r="O907" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="P907" s="1">
         <v>0</v>
@@ -48112,7 +48383,7 @@
         <v>1</v>
       </c>
       <c r="J908" s="63" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K908" s="62">
         <v>400</v>
@@ -48127,7 +48398,7 @@
         <v>2</v>
       </c>
       <c r="O908" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="P908" s="1">
         <v>0</v>
@@ -48162,7 +48433,7 @@
         <v>2</v>
       </c>
       <c r="J909" s="63" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K909" s="62">
         <v>400</v>
@@ -48177,7 +48448,7 @@
         <v>2</v>
       </c>
       <c r="O909" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="P909" s="1">
         <v>0</v>
@@ -48212,7 +48483,7 @@
         <v>2</v>
       </c>
       <c r="J910" s="63" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K910" s="62">
         <v>400</v>
@@ -48227,7 +48498,7 @@
         <v>2</v>
       </c>
       <c r="O910" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="P910" s="1">
         <v>0</v>
@@ -48262,7 +48533,7 @@
         <v>2</v>
       </c>
       <c r="J911" s="63" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="K911" s="62">
         <v>400</v>
@@ -48277,7 +48548,7 @@
         <v>2</v>
       </c>
       <c r="O911" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="P911" s="1">
         <v>0</v>
@@ -48312,7 +48583,7 @@
         <v>2</v>
       </c>
       <c r="J912" s="63" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K912" s="62">
         <v>400</v>
@@ -48327,7 +48598,7 @@
         <v>2</v>
       </c>
       <c r="O912" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="P912" s="1">
         <v>0</v>
@@ -48362,7 +48633,7 @@
         <v>2</v>
       </c>
       <c r="J913" s="63" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K913" s="62">
         <v>400</v>
@@ -48377,7 +48648,7 @@
         <v>2</v>
       </c>
       <c r="O913" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="P913" s="1">
         <v>0</v>
@@ -48412,7 +48683,7 @@
         <v>2</v>
       </c>
       <c r="J914" s="63" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="K914" s="62">
         <v>400</v>
@@ -48427,7 +48698,7 @@
         <v>2</v>
       </c>
       <c r="O914" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="P914" s="1">
         <v>0</v>
@@ -48462,7 +48733,7 @@
         <v>2</v>
       </c>
       <c r="J915" s="63" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="K915" s="62">
         <v>400</v>
@@ -48477,7 +48748,7 @@
         <v>2</v>
       </c>
       <c r="O915" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="P915" s="1">
         <v>0</v>
@@ -48512,7 +48783,7 @@
         <v>2</v>
       </c>
       <c r="J916" s="63" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K916" s="62">
         <v>400</v>
@@ -48527,7 +48798,7 @@
         <v>2</v>
       </c>
       <c r="O916" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P916" s="1">
         <v>0</v>
@@ -48562,7 +48833,7 @@
         <v>3</v>
       </c>
       <c r="J917" s="63" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K917" s="62">
         <v>400</v>
@@ -48577,7 +48848,7 @@
         <v>2</v>
       </c>
       <c r="O917" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="P917" s="1">
         <v>0</v>
@@ -48612,7 +48883,7 @@
         <v>3</v>
       </c>
       <c r="J918" s="63" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K918" s="62">
         <v>400</v>
@@ -48627,7 +48898,7 @@
         <v>2</v>
       </c>
       <c r="O918" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="P918" s="1">
         <v>0</v>
@@ -48662,7 +48933,7 @@
         <v>3</v>
       </c>
       <c r="J919" s="63" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K919" s="62">
         <v>400</v>
@@ -48677,7 +48948,7 @@
         <v>2</v>
       </c>
       <c r="O919" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="P919" s="1">
         <v>0</v>
@@ -48712,7 +48983,7 @@
         <v>3</v>
       </c>
       <c r="J920" s="63" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K920" s="62">
         <v>400</v>
@@ -48727,7 +48998,7 @@
         <v>2</v>
       </c>
       <c r="O920" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="P920" s="1">
         <v>0</v>
@@ -48762,7 +49033,7 @@
         <v>3</v>
       </c>
       <c r="J921" s="63" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K921" s="62">
         <v>400</v>
@@ -48777,7 +49048,7 @@
         <v>2</v>
       </c>
       <c r="O921" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="P921" s="1">
         <v>0</v>
@@ -48812,7 +49083,7 @@
         <v>3</v>
       </c>
       <c r="J922" s="63" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K922" s="62">
         <v>400</v>
@@ -48827,7 +49098,7 @@
         <v>2</v>
       </c>
       <c r="O922" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="P922" s="1">
         <v>0</v>
@@ -48862,7 +49133,7 @@
         <v>3</v>
       </c>
       <c r="J923" s="63" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K923" s="62">
         <v>400</v>
@@ -48877,7 +49148,7 @@
         <v>2</v>
       </c>
       <c r="O923" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="P923" s="1">
         <v>0</v>
@@ -48912,7 +49183,7 @@
         <v>3</v>
       </c>
       <c r="J924" s="63" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="K924" s="62">
         <v>400</v>
@@ -48927,7 +49198,7 @@
         <v>2</v>
       </c>
       <c r="O924" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="P924" s="1">
         <v>0</v>
@@ -48962,7 +49233,7 @@
         <v>3</v>
       </c>
       <c r="J925" s="63" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K925" s="62">
         <v>400</v>
@@ -48977,7 +49248,7 @@
         <v>2</v>
       </c>
       <c r="O925" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="P925" s="1">
         <v>0</v>
@@ -49012,7 +49283,7 @@
         <v>3</v>
       </c>
       <c r="J926" s="63" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K926" s="62">
         <v>400</v>
@@ -49027,7 +49298,7 @@
         <v>2</v>
       </c>
       <c r="O926" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="P926" s="1">
         <v>0</v>
@@ -49062,7 +49333,7 @@
         <v>4</v>
       </c>
       <c r="J927" s="63" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="K927" s="62">
         <v>400</v>
@@ -49077,7 +49348,7 @@
         <v>2</v>
       </c>
       <c r="O927" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P927" s="1">
         <v>0</v>
@@ -49112,7 +49383,7 @@
         <v>4</v>
       </c>
       <c r="J928" s="63" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K928" s="62">
         <v>400</v>
@@ -49127,7 +49398,7 @@
         <v>2</v>
       </c>
       <c r="O928" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P928" s="1">
         <v>0</v>
@@ -49162,7 +49433,7 @@
         <v>4</v>
       </c>
       <c r="J929" s="63" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K929" s="62">
         <v>400</v>
@@ -49177,7 +49448,7 @@
         <v>2</v>
       </c>
       <c r="O929" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="P929" s="1">
         <v>0</v>
@@ -49212,7 +49483,7 @@
         <v>4</v>
       </c>
       <c r="J930" s="63" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K930" s="62">
         <v>400</v>
@@ -49227,7 +49498,7 @@
         <v>2</v>
       </c>
       <c r="O930" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="P930" s="1">
         <v>0</v>
@@ -49262,7 +49533,7 @@
         <v>4</v>
       </c>
       <c r="J931" s="63" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K931" s="62">
         <v>400</v>
@@ -49277,7 +49548,7 @@
         <v>2</v>
       </c>
       <c r="O931" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="P931" s="1">
         <v>0</v>
@@ -49312,7 +49583,7 @@
         <v>4</v>
       </c>
       <c r="J932" s="63" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K932" s="62">
         <v>400</v>
@@ -49327,7 +49598,7 @@
         <v>2</v>
       </c>
       <c r="O932" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="P932" s="1">
         <v>0</v>
@@ -49362,7 +49633,7 @@
         <v>4</v>
       </c>
       <c r="J933" s="63" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K933" s="62">
         <v>400</v>
@@ -49377,7 +49648,7 @@
         <v>2</v>
       </c>
       <c r="O933" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="P933" s="1">
         <v>0</v>
@@ -49412,7 +49683,7 @@
         <v>4</v>
       </c>
       <c r="J934" s="63" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K934" s="62">
         <v>400</v>
@@ -49427,7 +49698,7 @@
         <v>2</v>
       </c>
       <c r="O934" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="P934" s="1">
         <v>0</v>
@@ -49462,7 +49733,7 @@
         <v>4</v>
       </c>
       <c r="J935" s="63" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K935" s="62">
         <v>400</v>
@@ -49477,7 +49748,7 @@
         <v>2</v>
       </c>
       <c r="O935" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="P935" s="1">
         <v>0</v>
@@ -49512,7 +49783,7 @@
         <v>4</v>
       </c>
       <c r="J936" s="63" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="K936" s="62">
         <v>400</v>
@@ -49527,7 +49798,7 @@
         <v>2</v>
       </c>
       <c r="O936" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="P936" s="1">
         <v>0</v>
@@ -49562,7 +49833,7 @@
         <v>4</v>
       </c>
       <c r="J937" s="63" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="K937" s="62">
         <v>400</v>
@@ -49577,7 +49848,7 @@
         <v>2</v>
       </c>
       <c r="O937" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="P937" s="1">
         <v>0</v>
@@ -49612,7 +49883,7 @@
         <v>4</v>
       </c>
       <c r="J938" s="63" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K938" s="62">
         <v>400</v>
@@ -49627,7 +49898,7 @@
         <v>2</v>
       </c>
       <c r="O938" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="P938" s="1">
         <v>0</v>
@@ -49662,7 +49933,7 @@
         <v>5</v>
       </c>
       <c r="J939" s="63" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K939" s="62">
         <v>400</v>
@@ -49677,7 +49948,7 @@
         <v>2</v>
       </c>
       <c r="O939" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="P939" s="1">
         <v>0</v>
@@ -49712,7 +49983,7 @@
         <v>5</v>
       </c>
       <c r="J940" s="63" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K940" s="62">
         <v>400</v>
@@ -49727,7 +49998,7 @@
         <v>2</v>
       </c>
       <c r="O940" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P940" s="1">
         <v>0</v>
@@ -49762,7 +50033,7 @@
         <v>5</v>
       </c>
       <c r="J941" s="63" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K941" s="62">
         <v>400</v>
@@ -49777,7 +50048,7 @@
         <v>2</v>
       </c>
       <c r="O941" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="P941" s="1">
         <v>0</v>
@@ -49812,7 +50083,7 @@
         <v>5</v>
       </c>
       <c r="J942" s="63" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="K942" s="62">
         <v>400</v>
@@ -49827,7 +50098,7 @@
         <v>2</v>
       </c>
       <c r="O942" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="P942" s="1">
         <v>0</v>
@@ -49862,7 +50133,7 @@
         <v>5</v>
       </c>
       <c r="J943" s="63" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K943" s="62">
         <v>400</v>
@@ -49877,7 +50148,7 @@
         <v>2</v>
       </c>
       <c r="O943" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="P943" s="1">
         <v>0</v>
@@ -49912,7 +50183,7 @@
         <v>5</v>
       </c>
       <c r="J944" s="63" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K944" s="62">
         <v>400</v>
@@ -49927,7 +50198,7 @@
         <v>2</v>
       </c>
       <c r="O944" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="P944" s="1">
         <v>0</v>
@@ -49962,7 +50233,7 @@
         <v>5</v>
       </c>
       <c r="J945" s="63" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="K945" s="62">
         <v>400</v>
@@ -49977,7 +50248,7 @@
         <v>2</v>
       </c>
       <c r="O945" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="P945" s="1">
         <v>0</v>
@@ -50012,7 +50283,7 @@
         <v>5</v>
       </c>
       <c r="J946" s="63" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="K946" s="62">
         <v>400</v>
@@ -50027,7 +50298,7 @@
         <v>2</v>
       </c>
       <c r="O946" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="P946" s="1">
         <v>0</v>
@@ -50062,7 +50333,7 @@
         <v>5</v>
       </c>
       <c r="J947" s="63" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K947" s="62">
         <v>400</v>
@@ -50077,7 +50348,7 @@
         <v>2</v>
       </c>
       <c r="O947" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="P947" s="1">
         <v>0</v>
@@ -50112,7 +50383,7 @@
         <v>5</v>
       </c>
       <c r="J948" s="63" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K948" s="62">
         <v>400</v>
@@ -50127,7 +50398,7 @@
         <v>2</v>
       </c>
       <c r="O948" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="P948" s="1">
         <v>0</v>
@@ -50162,7 +50433,7 @@
         <v>5</v>
       </c>
       <c r="J949" s="63" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K949" s="62">
         <v>400</v>
@@ -50177,7 +50448,7 @@
         <v>2</v>
       </c>
       <c r="O949" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="P949" s="1">
         <v>0</v>
@@ -50212,7 +50483,7 @@
         <v>5</v>
       </c>
       <c r="J950" s="63" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="K950" s="62">
         <v>400</v>
@@ -50227,7 +50498,7 @@
         <v>2</v>
       </c>
       <c r="O950" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="P950" s="1">
         <v>0</v>
@@ -50262,7 +50533,7 @@
         <v>5</v>
       </c>
       <c r="J951" s="63" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K951" s="62">
         <v>400</v>
@@ -50277,7 +50548,7 @@
         <v>2</v>
       </c>
       <c r="O951" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="P951" s="1">
         <v>0</v>
@@ -50312,7 +50583,7 @@
         <v>5</v>
       </c>
       <c r="J952" s="63" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="K952" s="62">
         <v>400</v>
@@ -50327,7 +50598,7 @@
         <v>2</v>
       </c>
       <c r="O952" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="P952" s="1">
         <v>0</v>
@@ -50362,7 +50633,7 @@
         <v>1</v>
       </c>
       <c r="J953" s="63" t="s">
-        <v>450</v>
+        <v>597</v>
       </c>
       <c r="K953" s="62">
         <v>6000</v>
@@ -50377,7 +50648,7 @@
         <v>3</v>
       </c>
       <c r="O953" s="1" t="s">
-        <v>451</v>
+        <v>631</v>
       </c>
       <c r="P953" s="1">
         <v>0</v>
@@ -50412,7 +50683,7 @@
         <v>1</v>
       </c>
       <c r="J954" s="63" t="s">
-        <v>450</v>
+        <v>598</v>
       </c>
       <c r="K954" s="62">
         <v>6000</v>
@@ -50427,7 +50698,7 @@
         <v>3</v>
       </c>
       <c r="O954" s="1" t="s">
-        <v>451</v>
+        <v>632</v>
       </c>
       <c r="P954" s="1">
         <v>0</v>
@@ -50462,7 +50733,7 @@
         <v>1</v>
       </c>
       <c r="J955" s="63" t="s">
-        <v>450</v>
+        <v>599</v>
       </c>
       <c r="K955" s="62">
         <v>6000</v>
@@ -50477,7 +50748,7 @@
         <v>3</v>
       </c>
       <c r="O955" s="1" t="s">
-        <v>451</v>
+        <v>633</v>
       </c>
       <c r="P955" s="1">
         <v>0</v>
@@ -50512,7 +50783,7 @@
         <v>1</v>
       </c>
       <c r="J956" s="63" t="s">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="K956" s="62">
         <v>6000</v>
@@ -50527,7 +50798,7 @@
         <v>3</v>
       </c>
       <c r="O956" s="1" t="s">
-        <v>451</v>
+        <v>634</v>
       </c>
       <c r="P956" s="1">
         <v>0</v>
@@ -50562,7 +50833,7 @@
         <v>1</v>
       </c>
       <c r="J957" s="63" t="s">
-        <v>450</v>
+        <v>598</v>
       </c>
       <c r="K957" s="62">
         <v>6000</v>
@@ -50577,7 +50848,7 @@
         <v>3</v>
       </c>
       <c r="O957" s="1" t="s">
-        <v>451</v>
+        <v>635</v>
       </c>
       <c r="P957" s="1">
         <v>0</v>
@@ -50612,7 +50883,7 @@
         <v>1</v>
       </c>
       <c r="J958" s="63" t="s">
-        <v>450</v>
+        <v>599</v>
       </c>
       <c r="K958" s="62">
         <v>6000</v>
@@ -50627,7 +50898,7 @@
         <v>3</v>
       </c>
       <c r="O958" s="1" t="s">
-        <v>451</v>
+        <v>636</v>
       </c>
       <c r="P958" s="1">
         <v>0</v>
@@ -50662,7 +50933,7 @@
         <v>1</v>
       </c>
       <c r="J959" s="63" t="s">
-        <v>450</v>
+        <v>601</v>
       </c>
       <c r="K959" s="62">
         <v>6000</v>
@@ -50677,7 +50948,7 @@
         <v>3</v>
       </c>
       <c r="O959" s="1" t="s">
-        <v>451</v>
+        <v>637</v>
       </c>
       <c r="P959" s="1">
         <v>0</v>
@@ -50712,7 +50983,7 @@
         <v>1</v>
       </c>
       <c r="J960" s="63" t="s">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="K960" s="62">
         <v>6000</v>
@@ -50727,7 +50998,7 @@
         <v>3</v>
       </c>
       <c r="O960" s="1" t="s">
-        <v>451</v>
+        <v>638</v>
       </c>
       <c r="P960" s="1">
         <v>0</v>
@@ -50762,7 +51033,7 @@
         <v>2</v>
       </c>
       <c r="J961" s="63" t="s">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="K961" s="62">
         <v>6000</v>
@@ -50777,7 +51048,7 @@
         <v>3</v>
       </c>
       <c r="O961" s="1" t="s">
-        <v>451</v>
+        <v>639</v>
       </c>
       <c r="P961" s="1">
         <v>0</v>
@@ -50812,7 +51083,7 @@
         <v>2</v>
       </c>
       <c r="J962" s="63" t="s">
-        <v>450</v>
+        <v>602</v>
       </c>
       <c r="K962" s="62">
         <v>6000</v>
@@ -50827,7 +51098,7 @@
         <v>3</v>
       </c>
       <c r="O962" s="1" t="s">
-        <v>451</v>
+        <v>640</v>
       </c>
       <c r="P962" s="1">
         <v>0</v>
@@ -50862,7 +51133,7 @@
         <v>2</v>
       </c>
       <c r="J963" s="63" t="s">
-        <v>450</v>
+        <v>603</v>
       </c>
       <c r="K963" s="62">
         <v>6000</v>
@@ -50877,7 +51148,7 @@
         <v>3</v>
       </c>
       <c r="O963" s="1" t="s">
-        <v>451</v>
+        <v>641</v>
       </c>
       <c r="P963" s="1">
         <v>0</v>
@@ -50912,7 +51183,7 @@
         <v>2</v>
       </c>
       <c r="J964" s="63" t="s">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="K964" s="62">
         <v>6000</v>
@@ -50927,7 +51198,7 @@
         <v>3</v>
       </c>
       <c r="O964" s="1" t="s">
-        <v>451</v>
+        <v>642</v>
       </c>
       <c r="P964" s="1">
         <v>0</v>
@@ -50962,7 +51233,7 @@
         <v>2</v>
       </c>
       <c r="J965" s="63" t="s">
-        <v>450</v>
+        <v>604</v>
       </c>
       <c r="K965" s="62">
         <v>6000</v>
@@ -50977,7 +51248,7 @@
         <v>3</v>
       </c>
       <c r="O965" s="1" t="s">
-        <v>451</v>
+        <v>643</v>
       </c>
       <c r="P965" s="1">
         <v>0</v>
@@ -51012,7 +51283,7 @@
         <v>2</v>
       </c>
       <c r="J966" s="63" t="s">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="K966" s="62">
         <v>6000</v>
@@ -51027,7 +51298,7 @@
         <v>3</v>
       </c>
       <c r="O966" s="1" t="s">
-        <v>451</v>
+        <v>644</v>
       </c>
       <c r="P966" s="1">
         <v>0</v>
@@ -51062,7 +51333,7 @@
         <v>2</v>
       </c>
       <c r="J967" s="63" t="s">
-        <v>450</v>
+        <v>605</v>
       </c>
       <c r="K967" s="62">
         <v>6000</v>
@@ -51077,7 +51348,7 @@
         <v>3</v>
       </c>
       <c r="O967" s="1" t="s">
-        <v>451</v>
+        <v>645</v>
       </c>
       <c r="P967" s="1">
         <v>0</v>
@@ -51112,7 +51383,7 @@
         <v>2</v>
       </c>
       <c r="J968" s="63" t="s">
-        <v>450</v>
+        <v>606</v>
       </c>
       <c r="K968" s="62">
         <v>6000</v>
@@ -51127,7 +51398,7 @@
         <v>3</v>
       </c>
       <c r="O968" s="1" t="s">
-        <v>451</v>
+        <v>646</v>
       </c>
       <c r="P968" s="1">
         <v>0</v>
@@ -51162,7 +51433,7 @@
         <v>2</v>
       </c>
       <c r="J969" s="63" t="s">
-        <v>450</v>
+        <v>607</v>
       </c>
       <c r="K969" s="62">
         <v>6000</v>
@@ -51177,7 +51448,7 @@
         <v>3</v>
       </c>
       <c r="O969" s="1" t="s">
-        <v>451</v>
+        <v>647</v>
       </c>
       <c r="P969" s="1">
         <v>0</v>
@@ -51212,7 +51483,7 @@
         <v>2</v>
       </c>
       <c r="J970" s="63" t="s">
-        <v>450</v>
+        <v>603</v>
       </c>
       <c r="K970" s="62">
         <v>6000</v>
@@ -51227,7 +51498,7 @@
         <v>3</v>
       </c>
       <c r="O970" s="1" t="s">
-        <v>451</v>
+        <v>648</v>
       </c>
       <c r="P970" s="1">
         <v>0</v>
@@ -51262,7 +51533,7 @@
         <v>3</v>
       </c>
       <c r="J971" s="63" t="s">
-        <v>450</v>
+        <v>608</v>
       </c>
       <c r="K971" s="62">
         <v>6000</v>
@@ -51277,7 +51548,7 @@
         <v>3</v>
       </c>
       <c r="O971" s="1" t="s">
-        <v>451</v>
+        <v>649</v>
       </c>
       <c r="P971" s="1">
         <v>0</v>
@@ -51312,7 +51583,7 @@
         <v>3</v>
       </c>
       <c r="J972" s="63" t="s">
-        <v>450</v>
+        <v>609</v>
       </c>
       <c r="K972" s="62">
         <v>6000</v>
@@ -51327,7 +51598,7 @@
         <v>3</v>
       </c>
       <c r="O972" s="1" t="s">
-        <v>451</v>
+        <v>650</v>
       </c>
       <c r="P972" s="1">
         <v>0</v>
@@ -51362,7 +51633,7 @@
         <v>3</v>
       </c>
       <c r="J973" s="63" t="s">
-        <v>450</v>
+        <v>609</v>
       </c>
       <c r="K973" s="62">
         <v>6000</v>
@@ -51377,7 +51648,7 @@
         <v>3</v>
       </c>
       <c r="O973" s="1" t="s">
-        <v>451</v>
+        <v>651</v>
       </c>
       <c r="P973" s="1">
         <v>0</v>
@@ -51412,7 +51683,7 @@
         <v>3</v>
       </c>
       <c r="J974" s="63" t="s">
-        <v>450</v>
+        <v>610</v>
       </c>
       <c r="K974" s="62">
         <v>6000</v>
@@ -51427,7 +51698,7 @@
         <v>3</v>
       </c>
       <c r="O974" s="1" t="s">
-        <v>451</v>
+        <v>652</v>
       </c>
       <c r="P974" s="1">
         <v>0</v>
@@ -51462,7 +51733,7 @@
         <v>3</v>
       </c>
       <c r="J975" s="63" t="s">
-        <v>450</v>
+        <v>611</v>
       </c>
       <c r="K975" s="62">
         <v>6000</v>
@@ -51477,7 +51748,7 @@
         <v>3</v>
       </c>
       <c r="O975" s="1" t="s">
-        <v>451</v>
+        <v>653</v>
       </c>
       <c r="P975" s="1">
         <v>0</v>
@@ -51512,7 +51783,7 @@
         <v>3</v>
       </c>
       <c r="J976" s="63" t="s">
-        <v>450</v>
+        <v>612</v>
       </c>
       <c r="K976" s="62">
         <v>6000</v>
@@ -51527,7 +51798,7 @@
         <v>3</v>
       </c>
       <c r="O976" s="1" t="s">
-        <v>451</v>
+        <v>654</v>
       </c>
       <c r="P976" s="1">
         <v>0</v>
@@ -51562,7 +51833,7 @@
         <v>3</v>
       </c>
       <c r="J977" s="63" t="s">
-        <v>450</v>
+        <v>613</v>
       </c>
       <c r="K977" s="62">
         <v>6000</v>
@@ -51577,7 +51848,7 @@
         <v>3</v>
       </c>
       <c r="O977" s="1" t="s">
-        <v>451</v>
+        <v>655</v>
       </c>
       <c r="P977" s="1">
         <v>0</v>
@@ -51612,7 +51883,7 @@
         <v>3</v>
       </c>
       <c r="J978" s="63" t="s">
-        <v>450</v>
+        <v>614</v>
       </c>
       <c r="K978" s="62">
         <v>6000</v>
@@ -51627,7 +51898,7 @@
         <v>3</v>
       </c>
       <c r="O978" s="1" t="s">
-        <v>451</v>
+        <v>656</v>
       </c>
       <c r="P978" s="1">
         <v>0</v>
@@ -51662,7 +51933,7 @@
         <v>3</v>
       </c>
       <c r="J979" s="63" t="s">
-        <v>450</v>
+        <v>615</v>
       </c>
       <c r="K979" s="62">
         <v>6000</v>
@@ -51677,7 +51948,7 @@
         <v>3</v>
       </c>
       <c r="O979" s="1" t="s">
-        <v>451</v>
+        <v>657</v>
       </c>
       <c r="P979" s="1">
         <v>0</v>
@@ -51712,7 +51983,7 @@
         <v>3</v>
       </c>
       <c r="J980" s="63" t="s">
-        <v>450</v>
+        <v>616</v>
       </c>
       <c r="K980" s="62">
         <v>6000</v>
@@ -51727,7 +51998,7 @@
         <v>3</v>
       </c>
       <c r="O980" s="1" t="s">
-        <v>451</v>
+        <v>658</v>
       </c>
       <c r="P980" s="1">
         <v>0</v>
@@ -51762,7 +52033,7 @@
         <v>3</v>
       </c>
       <c r="J981" s="63" t="s">
-        <v>450</v>
+        <v>615</v>
       </c>
       <c r="K981" s="62">
         <v>6000</v>
@@ -51777,7 +52048,7 @@
         <v>3</v>
       </c>
       <c r="O981" s="1" t="s">
-        <v>451</v>
+        <v>659</v>
       </c>
       <c r="P981" s="1">
         <v>0</v>
@@ -51812,7 +52083,7 @@
         <v>3</v>
       </c>
       <c r="J982" s="63" t="s">
-        <v>450</v>
+        <v>617</v>
       </c>
       <c r="K982" s="62">
         <v>6000</v>
@@ -51827,7 +52098,7 @@
         <v>3</v>
       </c>
       <c r="O982" s="1" t="s">
-        <v>451</v>
+        <v>660</v>
       </c>
       <c r="P982" s="1">
         <v>0</v>
@@ -51862,7 +52133,7 @@
         <v>4</v>
       </c>
       <c r="J983" s="63" t="s">
-        <v>450</v>
+        <v>608</v>
       </c>
       <c r="K983" s="62">
         <v>6000</v>
@@ -51877,7 +52148,7 @@
         <v>3</v>
       </c>
       <c r="O983" s="1" t="s">
-        <v>451</v>
+        <v>661</v>
       </c>
       <c r="P983" s="1">
         <v>0</v>
@@ -51912,7 +52183,7 @@
         <v>4</v>
       </c>
       <c r="J984" s="63" t="s">
-        <v>450</v>
+        <v>618</v>
       </c>
       <c r="K984" s="62">
         <v>6000</v>
@@ -51927,7 +52198,7 @@
         <v>3</v>
       </c>
       <c r="O984" s="1" t="s">
-        <v>451</v>
+        <v>662</v>
       </c>
       <c r="P984" s="1">
         <v>0</v>
@@ -51962,7 +52233,7 @@
         <v>4</v>
       </c>
       <c r="J985" s="63" t="s">
-        <v>450</v>
+        <v>618</v>
       </c>
       <c r="K985" s="62">
         <v>6000</v>
@@ -51977,7 +52248,7 @@
         <v>3</v>
       </c>
       <c r="O985" s="1" t="s">
-        <v>451</v>
+        <v>663</v>
       </c>
       <c r="P985" s="1">
         <v>0</v>
@@ -52012,7 +52283,7 @@
         <v>4</v>
       </c>
       <c r="J986" s="63" t="s">
-        <v>450</v>
+        <v>619</v>
       </c>
       <c r="K986" s="62">
         <v>6000</v>
@@ -52027,7 +52298,7 @@
         <v>3</v>
       </c>
       <c r="O986" s="1" t="s">
-        <v>451</v>
+        <v>664</v>
       </c>
       <c r="P986" s="1">
         <v>0</v>
@@ -52062,7 +52333,7 @@
         <v>4</v>
       </c>
       <c r="J987" s="63" t="s">
-        <v>450</v>
+        <v>608</v>
       </c>
       <c r="K987" s="62">
         <v>6000</v>
@@ -52077,7 +52348,7 @@
         <v>3</v>
       </c>
       <c r="O987" s="1" t="s">
-        <v>451</v>
+        <v>665</v>
       </c>
       <c r="P987" s="1">
         <v>0</v>
@@ -52112,7 +52383,7 @@
         <v>4</v>
       </c>
       <c r="J988" s="63" t="s">
-        <v>450</v>
+        <v>617</v>
       </c>
       <c r="K988" s="62">
         <v>6000</v>
@@ -52127,7 +52398,7 @@
         <v>3</v>
       </c>
       <c r="O988" s="1" t="s">
-        <v>451</v>
+        <v>666</v>
       </c>
       <c r="P988" s="1">
         <v>0</v>
@@ -52162,7 +52433,7 @@
         <v>4</v>
       </c>
       <c r="J989" s="63" t="s">
-        <v>450</v>
+        <v>615</v>
       </c>
       <c r="K989" s="62">
         <v>6000</v>
@@ -52177,7 +52448,7 @@
         <v>3</v>
       </c>
       <c r="O989" s="1" t="s">
-        <v>451</v>
+        <v>667</v>
       </c>
       <c r="P989" s="1">
         <v>0</v>
@@ -52212,7 +52483,7 @@
         <v>4</v>
       </c>
       <c r="J990" s="63" t="s">
-        <v>450</v>
+        <v>611</v>
       </c>
       <c r="K990" s="62">
         <v>6000</v>
@@ -52227,7 +52498,7 @@
         <v>3</v>
       </c>
       <c r="O990" s="1" t="s">
-        <v>451</v>
+        <v>668</v>
       </c>
       <c r="P990" s="1">
         <v>0</v>
@@ -52262,7 +52533,7 @@
         <v>4</v>
       </c>
       <c r="J991" s="63" t="s">
-        <v>450</v>
+        <v>608</v>
       </c>
       <c r="K991" s="62">
         <v>6000</v>
@@ -52277,7 +52548,7 @@
         <v>3</v>
       </c>
       <c r="O991" s="1" t="s">
-        <v>451</v>
+        <v>669</v>
       </c>
       <c r="P991" s="1">
         <v>0</v>
@@ -52312,7 +52583,7 @@
         <v>4</v>
       </c>
       <c r="J992" s="63" t="s">
-        <v>450</v>
+        <v>620</v>
       </c>
       <c r="K992" s="62">
         <v>6000</v>
@@ -52327,7 +52598,7 @@
         <v>3</v>
       </c>
       <c r="O992" s="1" t="s">
-        <v>451</v>
+        <v>670</v>
       </c>
       <c r="P992" s="1">
         <v>0</v>
@@ -52362,7 +52633,7 @@
         <v>4</v>
       </c>
       <c r="J993" s="63" t="s">
-        <v>450</v>
+        <v>620</v>
       </c>
       <c r="K993" s="62">
         <v>6000</v>
@@ -52377,7 +52648,7 @@
         <v>3</v>
       </c>
       <c r="O993" s="1" t="s">
-        <v>451</v>
+        <v>671</v>
       </c>
       <c r="P993" s="1">
         <v>0</v>
@@ -52412,7 +52683,7 @@
         <v>4</v>
       </c>
       <c r="J994" s="63" t="s">
-        <v>450</v>
+        <v>621</v>
       </c>
       <c r="K994" s="62">
         <v>6000</v>
@@ -52427,7 +52698,7 @@
         <v>3</v>
       </c>
       <c r="O994" s="1" t="s">
-        <v>451</v>
+        <v>672</v>
       </c>
       <c r="P994" s="1">
         <v>0</v>
@@ -52462,7 +52733,7 @@
         <v>4</v>
       </c>
       <c r="J995" s="63" t="s">
-        <v>450</v>
+        <v>608</v>
       </c>
       <c r="K995" s="62">
         <v>6000</v>
@@ -52477,7 +52748,7 @@
         <v>3</v>
       </c>
       <c r="O995" s="1" t="s">
-        <v>451</v>
+        <v>673</v>
       </c>
       <c r="P995" s="1">
         <v>0</v>
@@ -52512,7 +52783,7 @@
         <v>4</v>
       </c>
       <c r="J996" s="63" t="s">
-        <v>450</v>
+        <v>622</v>
       </c>
       <c r="K996" s="62">
         <v>6000</v>
@@ -52527,7 +52798,7 @@
         <v>3</v>
       </c>
       <c r="O996" s="1" t="s">
-        <v>451</v>
+        <v>674</v>
       </c>
       <c r="P996" s="1">
         <v>0</v>
@@ -52562,7 +52833,7 @@
         <v>5</v>
       </c>
       <c r="J997" s="63" t="s">
-        <v>450</v>
+        <v>623</v>
       </c>
       <c r="K997" s="62">
         <v>6000</v>
@@ -52577,7 +52848,7 @@
         <v>3</v>
       </c>
       <c r="O997" s="1" t="s">
-        <v>451</v>
+        <v>675</v>
       </c>
       <c r="P997" s="1">
         <v>0</v>
@@ -52612,7 +52883,7 @@
         <v>5</v>
       </c>
       <c r="J998" s="63" t="s">
-        <v>450</v>
+        <v>624</v>
       </c>
       <c r="K998" s="62">
         <v>6000</v>
@@ -52627,7 +52898,7 @@
         <v>3</v>
       </c>
       <c r="O998" s="1" t="s">
-        <v>451</v>
+        <v>676</v>
       </c>
       <c r="P998" s="1">
         <v>0</v>
@@ -52662,7 +52933,7 @@
         <v>5</v>
       </c>
       <c r="J999" s="63" t="s">
-        <v>450</v>
+        <v>624</v>
       </c>
       <c r="K999" s="62">
         <v>6000</v>
@@ -52677,7 +52948,7 @@
         <v>3</v>
       </c>
       <c r="O999" s="1" t="s">
-        <v>451</v>
+        <v>677</v>
       </c>
       <c r="P999" s="1">
         <v>0</v>
@@ -52712,7 +52983,7 @@
         <v>5</v>
       </c>
       <c r="J1000" s="63" t="s">
-        <v>450</v>
+        <v>625</v>
       </c>
       <c r="K1000" s="62">
         <v>6000</v>
@@ -52727,7 +52998,7 @@
         <v>3</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>451</v>
+        <v>678</v>
       </c>
       <c r="P1000" s="1">
         <v>0</v>
@@ -52762,7 +53033,7 @@
         <v>5</v>
       </c>
       <c r="J1001" s="63" t="s">
-        <v>450</v>
+        <v>626</v>
       </c>
       <c r="K1001" s="62">
         <v>6000</v>
@@ -52777,7 +53048,7 @@
         <v>3</v>
       </c>
       <c r="O1001" s="1" t="s">
-        <v>451</v>
+        <v>679</v>
       </c>
       <c r="P1001" s="1">
         <v>0</v>
@@ -52812,7 +53083,7 @@
         <v>5</v>
       </c>
       <c r="J1002" s="63" t="s">
-        <v>450</v>
+        <v>626</v>
       </c>
       <c r="K1002" s="62">
         <v>6000</v>
@@ -52827,7 +53098,7 @@
         <v>3</v>
       </c>
       <c r="O1002" s="1" t="s">
-        <v>451</v>
+        <v>680</v>
       </c>
       <c r="P1002" s="1">
         <v>0</v>
@@ -52862,7 +53133,7 @@
         <v>5</v>
       </c>
       <c r="J1003" s="63" t="s">
-        <v>450</v>
+        <v>627</v>
       </c>
       <c r="K1003" s="62">
         <v>6000</v>
@@ -52877,7 +53148,7 @@
         <v>3</v>
       </c>
       <c r="O1003" s="1" t="s">
-        <v>451</v>
+        <v>681</v>
       </c>
       <c r="P1003" s="1">
         <v>0</v>
@@ -52912,7 +53183,7 @@
         <v>5</v>
       </c>
       <c r="J1004" s="63" t="s">
-        <v>450</v>
+        <v>626</v>
       </c>
       <c r="K1004" s="62">
         <v>6000</v>
@@ -52927,7 +53198,7 @@
         <v>3</v>
       </c>
       <c r="O1004" s="1" t="s">
-        <v>451</v>
+        <v>682</v>
       </c>
       <c r="P1004" s="1">
         <v>0</v>
@@ -52962,7 +53233,7 @@
         <v>5</v>
       </c>
       <c r="J1005" s="63" t="s">
-        <v>450</v>
+        <v>626</v>
       </c>
       <c r="K1005" s="62">
         <v>6000</v>
@@ -52977,7 +53248,7 @@
         <v>3</v>
       </c>
       <c r="O1005" s="1" t="s">
-        <v>451</v>
+        <v>683</v>
       </c>
       <c r="P1005" s="1">
         <v>0</v>
@@ -53012,7 +53283,7 @@
         <v>5</v>
       </c>
       <c r="J1006" s="63" t="s">
-        <v>450</v>
+        <v>628</v>
       </c>
       <c r="K1006" s="62">
         <v>6000</v>
@@ -53027,7 +53298,7 @@
         <v>3</v>
       </c>
       <c r="O1006" s="1" t="s">
-        <v>451</v>
+        <v>684</v>
       </c>
       <c r="P1006" s="1">
         <v>0</v>
@@ -53062,7 +53333,7 @@
         <v>5</v>
       </c>
       <c r="J1007" s="63" t="s">
-        <v>450</v>
+        <v>626</v>
       </c>
       <c r="K1007" s="62">
         <v>6000</v>
@@ -53077,7 +53348,7 @@
         <v>3</v>
       </c>
       <c r="O1007" s="1" t="s">
-        <v>451</v>
+        <v>685</v>
       </c>
       <c r="P1007" s="1">
         <v>0</v>
@@ -53112,7 +53383,7 @@
         <v>5</v>
       </c>
       <c r="J1008" s="63" t="s">
-        <v>450</v>
+        <v>626</v>
       </c>
       <c r="K1008" s="62">
         <v>6000</v>
@@ -53127,7 +53398,7 @@
         <v>3</v>
       </c>
       <c r="O1008" s="1" t="s">
-        <v>451</v>
+        <v>686</v>
       </c>
       <c r="P1008" s="1">
         <v>0</v>
@@ -53162,7 +53433,7 @@
         <v>5</v>
       </c>
       <c r="J1009" s="63" t="s">
-        <v>450</v>
+        <v>628</v>
       </c>
       <c r="K1009" s="62">
         <v>6000</v>
@@ -53177,7 +53448,7 @@
         <v>3</v>
       </c>
       <c r="O1009" s="1" t="s">
-        <v>451</v>
+        <v>684</v>
       </c>
       <c r="P1009" s="1">
         <v>0</v>
@@ -53212,7 +53483,7 @@
         <v>5</v>
       </c>
       <c r="J1010" s="63" t="s">
-        <v>450</v>
+        <v>626</v>
       </c>
       <c r="K1010" s="62">
         <v>6000</v>
@@ -53227,7 +53498,7 @@
         <v>3</v>
       </c>
       <c r="O1010" s="1" t="s">
-        <v>451</v>
+        <v>687</v>
       </c>
       <c r="P1010" s="1">
         <v>0</v>
@@ -53262,7 +53533,7 @@
         <v>5</v>
       </c>
       <c r="J1011" s="63" t="s">
-        <v>450</v>
+        <v>629</v>
       </c>
       <c r="K1011" s="62">
         <v>6000</v>
@@ -53277,7 +53548,7 @@
         <v>3</v>
       </c>
       <c r="O1011" s="1" t="s">
-        <v>451</v>
+        <v>688</v>
       </c>
       <c r="P1011" s="1">
         <v>0</v>
@@ -53312,7 +53583,7 @@
         <v>5</v>
       </c>
       <c r="J1012" s="63" t="s">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="K1012" s="62">
         <v>6000</v>
@@ -53327,7 +53598,7 @@
         <v>3</v>
       </c>
       <c r="O1012" s="1" t="s">
-        <v>451</v>
+        <v>689</v>
       </c>
       <c r="P1012" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1E6836-C6FE-4445-8DA3-DFB6AFBDB10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3571A641-2409-43FD-9D7B-0258C246ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2102,9 +2102,6 @@
     <t>72,40,69,35,75,35,69,30,75,30</t>
   </si>
   <si>
-    <t>69,35,75,35,69,20,75,20,72,15</t>
-  </si>
-  <si>
     <t>69,60,75,60,69,80,75,80,72,75</t>
   </si>
   <si>
@@ -2208,6 +2205,9 @@
   </si>
   <si>
     <t>85,20,85,25,90,20,80,25,75,20</t>
+  </si>
+  <si>
+    <t>69,35,75,35,69,20,75,20</t>
   </si>
 </sst>
 </file>
@@ -51798,7 +51798,7 @@
         <v>3</v>
       </c>
       <c r="O976" s="1" t="s">
-        <v>654</v>
+        <v>689</v>
       </c>
       <c r="P976" s="1">
         <v>0</v>
@@ -51848,7 +51848,7 @@
         <v>3</v>
       </c>
       <c r="O977" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="P977" s="1">
         <v>0</v>
@@ -51898,7 +51898,7 @@
         <v>3</v>
       </c>
       <c r="O978" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="P978" s="1">
         <v>0</v>
@@ -51948,7 +51948,7 @@
         <v>3</v>
       </c>
       <c r="O979" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="P979" s="1">
         <v>0</v>
@@ -51998,7 +51998,7 @@
         <v>3</v>
       </c>
       <c r="O980" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="P980" s="1">
         <v>0</v>
@@ -52048,7 +52048,7 @@
         <v>3</v>
       </c>
       <c r="O981" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="P981" s="1">
         <v>0</v>
@@ -52098,7 +52098,7 @@
         <v>3</v>
       </c>
       <c r="O982" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="P982" s="1">
         <v>0</v>
@@ -52148,7 +52148,7 @@
         <v>3</v>
       </c>
       <c r="O983" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="P983" s="1">
         <v>0</v>
@@ -52198,7 +52198,7 @@
         <v>3</v>
       </c>
       <c r="O984" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="P984" s="1">
         <v>0</v>
@@ -52248,7 +52248,7 @@
         <v>3</v>
       </c>
       <c r="O985" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="P985" s="1">
         <v>0</v>
@@ -52298,7 +52298,7 @@
         <v>3</v>
       </c>
       <c r="O986" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="P986" s="1">
         <v>0</v>
@@ -52348,7 +52348,7 @@
         <v>3</v>
       </c>
       <c r="O987" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P987" s="1">
         <v>0</v>
@@ -52398,7 +52398,7 @@
         <v>3</v>
       </c>
       <c r="O988" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="P988" s="1">
         <v>0</v>
@@ -52448,7 +52448,7 @@
         <v>3</v>
       </c>
       <c r="O989" s="1" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="P989" s="1">
         <v>0</v>
@@ -52498,7 +52498,7 @@
         <v>3</v>
       </c>
       <c r="O990" s="1" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="P990" s="1">
         <v>0</v>
@@ -52548,7 +52548,7 @@
         <v>3</v>
       </c>
       <c r="O991" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="P991" s="1">
         <v>0</v>
@@ -52598,7 +52598,7 @@
         <v>3</v>
       </c>
       <c r="O992" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P992" s="1">
         <v>0</v>
@@ -52648,7 +52648,7 @@
         <v>3</v>
       </c>
       <c r="O993" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P993" s="1">
         <v>0</v>
@@ -52698,7 +52698,7 @@
         <v>3</v>
       </c>
       <c r="O994" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="P994" s="1">
         <v>0</v>
@@ -52748,7 +52748,7 @@
         <v>3</v>
       </c>
       <c r="O995" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="P995" s="1">
         <v>0</v>
@@ -52798,7 +52798,7 @@
         <v>3</v>
       </c>
       <c r="O996" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="P996" s="1">
         <v>0</v>
@@ -52848,7 +52848,7 @@
         <v>3</v>
       </c>
       <c r="O997" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="P997" s="1">
         <v>0</v>
@@ -52898,7 +52898,7 @@
         <v>3</v>
       </c>
       <c r="O998" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="P998" s="1">
         <v>0</v>
@@ -52948,7 +52948,7 @@
         <v>3</v>
       </c>
       <c r="O999" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="P999" s="1">
         <v>0</v>
@@ -52998,7 +52998,7 @@
         <v>3</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="P1000" s="1">
         <v>0</v>
@@ -53048,7 +53048,7 @@
         <v>3</v>
       </c>
       <c r="O1001" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P1001" s="1">
         <v>0</v>
@@ -53098,7 +53098,7 @@
         <v>3</v>
       </c>
       <c r="O1002" s="1" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="P1002" s="1">
         <v>0</v>
@@ -53148,7 +53148,7 @@
         <v>3</v>
       </c>
       <c r="O1003" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="P1003" s="1">
         <v>0</v>
@@ -53198,7 +53198,7 @@
         <v>3</v>
       </c>
       <c r="O1004" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="P1004" s="1">
         <v>0</v>
@@ -53248,7 +53248,7 @@
         <v>3</v>
       </c>
       <c r="O1005" s="1" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="P1005" s="1">
         <v>0</v>
@@ -53298,7 +53298,7 @@
         <v>3</v>
       </c>
       <c r="O1006" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="P1006" s="1">
         <v>0</v>
@@ -53348,7 +53348,7 @@
         <v>3</v>
       </c>
       <c r="O1007" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="P1007" s="1">
         <v>0</v>
@@ -53398,7 +53398,7 @@
         <v>3</v>
       </c>
       <c r="O1008" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="P1008" s="1">
         <v>0</v>
@@ -53448,7 +53448,7 @@
         <v>3</v>
       </c>
       <c r="O1009" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="P1009" s="1">
         <v>0</v>
@@ -53498,7 +53498,7 @@
         <v>3</v>
       </c>
       <c r="O1010" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="P1010" s="1">
         <v>0</v>
@@ -53548,7 +53548,7 @@
         <v>3</v>
       </c>
       <c r="O1011" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="P1011" s="1">
         <v>0</v>
@@ -53598,7 +53598,7 @@
         <v>3</v>
       </c>
       <c r="O1012" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="P1012" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3571A641-2409-43FD-9D7B-0258C246ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15836107-CD04-4730-ADBE-8E1A8F42F40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="691">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1397,18 +1397,6 @@
     <t>85,35</t>
   </si>
   <si>
-    <t>90,12</t>
-  </si>
-  <si>
-    <t>90,12,60,48</t>
-  </si>
-  <si>
-    <t>90,15,55,45</t>
-  </si>
-  <si>
-    <t>87,15,93,15</t>
-  </si>
-  <si>
     <t>40,50,41,10</t>
   </si>
   <si>
@@ -1421,9 +1409,6 @@
     <t>41,15,46,15</t>
   </si>
   <si>
-    <t>40,45,40,40,43,15</t>
-  </si>
-  <si>
     <t>40,45,40,40</t>
   </si>
   <si>
@@ -1472,9 +1457,6 @@
     <t>44,65,47,80,44,80</t>
   </si>
   <si>
-    <t>44,75,5,90,15,90</t>
-  </si>
-  <si>
     <t>44,65,47,85,44,85</t>
   </si>
   <si>
@@ -1487,9 +1469,6 @@
     <t>90,40</t>
   </si>
   <si>
-    <t>90,35,95,47</t>
-  </si>
-  <si>
     <t>75,20,75,10</t>
   </si>
   <si>
@@ -2192,15 +2171,9 @@
     <t>60,35,80,35,67,40,76,40,55,30,85,30</t>
   </si>
   <si>
-    <t>50,20,50,25,45,20,30,15,35,15</t>
-  </si>
-  <si>
     <t>85,20,85,25,90,20,95,15,90,15</t>
   </si>
   <si>
-    <t>50,20,50,25,45,20,40,15,45,15</t>
-  </si>
-  <si>
     <t>60,35,80,35,72,40,85,15,80,15</t>
   </si>
   <si>
@@ -2208,6 +2181,36 @@
   </si>
   <si>
     <t>69,35,75,35,69,20,75,20</t>
+  </si>
+  <si>
+    <t>85,45,90,5</t>
+  </si>
+  <si>
+    <t>85,45,65,48</t>
+  </si>
+  <si>
+    <t>85,40,60,45</t>
+  </si>
+  <si>
+    <t>80,35,80,40</t>
+  </si>
+  <si>
+    <t>40,45,40,40,40,35</t>
+  </si>
+  <si>
+    <t>44,75,44,65,47,85</t>
+  </si>
+  <si>
+    <t>71107,71101</t>
+  </si>
+  <si>
+    <t>71105,71105,71105</t>
+  </si>
+  <si>
+    <t>50,20,50,25,45,20,45,15,40,15</t>
+  </si>
+  <si>
+    <t>50,20,50,25,45,20,50,15,45,15</t>
   </si>
 </sst>
 </file>
@@ -44548,7 +44551,7 @@
         <v>0</v>
       </c>
       <c r="O831" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="P831" s="1">
         <v>0</v>
@@ -44598,7 +44601,7 @@
         <v>0</v>
       </c>
       <c r="O832" s="1" t="s">
-        <v>449</v>
+        <v>681</v>
       </c>
       <c r="P832" s="1">
         <v>0</v>
@@ -44698,7 +44701,7 @@
         <v>0</v>
       </c>
       <c r="O834" s="1" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="P834" s="1">
         <v>0</v>
@@ -44748,7 +44751,7 @@
         <v>0</v>
       </c>
       <c r="O835" s="1" t="s">
-        <v>420</v>
+        <v>682</v>
       </c>
       <c r="P835" s="1">
         <v>0</v>
@@ -44783,7 +44786,7 @@
         <v>2</v>
       </c>
       <c r="J836" s="61" t="s">
-        <v>404</v>
+        <v>687</v>
       </c>
       <c r="K836" s="60">
         <v>16</v>
@@ -44798,7 +44801,7 @@
         <v>0</v>
       </c>
       <c r="O836" s="1" t="s">
-        <v>421</v>
+        <v>683</v>
       </c>
       <c r="P836" s="1">
         <v>0</v>
@@ -44848,7 +44851,7 @@
         <v>0</v>
       </c>
       <c r="O837" s="1" t="s">
-        <v>422</v>
+        <v>684</v>
       </c>
       <c r="P837" s="1">
         <v>0</v>
@@ -44898,7 +44901,7 @@
         <v>0</v>
       </c>
       <c r="O838" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="P838" s="1">
         <v>0</v>
@@ -44948,7 +44951,7 @@
         <v>0</v>
       </c>
       <c r="O839" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="P839" s="1">
         <v>0</v>
@@ -44998,7 +45001,7 @@
         <v>0</v>
       </c>
       <c r="O840" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="P840" s="1">
         <v>0</v>
@@ -45048,7 +45051,7 @@
         <v>0</v>
       </c>
       <c r="O841" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="P841" s="1">
         <v>0</v>
@@ -45083,7 +45086,7 @@
         <v>3</v>
       </c>
       <c r="J842" s="61" t="s">
-        <v>406</v>
+        <v>688</v>
       </c>
       <c r="K842" s="60">
         <v>16</v>
@@ -45098,7 +45101,7 @@
         <v>0</v>
       </c>
       <c r="O842" s="1" t="s">
-        <v>427</v>
+        <v>685</v>
       </c>
       <c r="P842" s="1">
         <v>0</v>
@@ -45148,7 +45151,7 @@
         <v>0</v>
       </c>
       <c r="O843" s="1" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="P843" s="1">
         <v>0</v>
@@ -45198,7 +45201,7 @@
         <v>0</v>
       </c>
       <c r="O844" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="P844" s="1">
         <v>0</v>
@@ -45248,7 +45251,7 @@
         <v>0</v>
       </c>
       <c r="O845" s="1" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="P845" s="1">
         <v>0</v>
@@ -45298,7 +45301,7 @@
         <v>0</v>
       </c>
       <c r="O846" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="P846" s="1">
         <v>0</v>
@@ -45348,7 +45351,7 @@
         <v>0</v>
       </c>
       <c r="O847" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P847" s="1">
         <v>0</v>
@@ -45398,7 +45401,7 @@
         <v>0</v>
       </c>
       <c r="O848" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P848" s="1">
         <v>0</v>
@@ -45448,7 +45451,7 @@
         <v>0</v>
       </c>
       <c r="O849" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="P849" s="1">
         <v>0</v>
@@ -45498,7 +45501,7 @@
         <v>0</v>
       </c>
       <c r="O850" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="P850" s="1">
         <v>0</v>
@@ -45548,7 +45551,7 @@
         <v>0</v>
       </c>
       <c r="O851" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="P851" s="1">
         <v>0</v>
@@ -45598,7 +45601,7 @@
         <v>0</v>
       </c>
       <c r="O852" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="P852" s="1">
         <v>0</v>
@@ -45648,7 +45651,7 @@
         <v>0</v>
       </c>
       <c r="O853" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="P853" s="1">
         <v>0</v>
@@ -45698,7 +45701,7 @@
         <v>0</v>
       </c>
       <c r="O854" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="P854" s="1">
         <v>0</v>
@@ -45748,7 +45751,7 @@
         <v>0</v>
       </c>
       <c r="O855" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="P855" s="1">
         <v>0</v>
@@ -45798,7 +45801,7 @@
         <v>0</v>
       </c>
       <c r="O856" s="1" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P856" s="1">
         <v>0</v>
@@ -45848,7 +45851,7 @@
         <v>0</v>
       </c>
       <c r="O857" s="1" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="P857" s="1">
         <v>0</v>
@@ -45898,7 +45901,7 @@
         <v>0</v>
       </c>
       <c r="O858" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="P858" s="1">
         <v>0</v>
@@ -45933,7 +45936,7 @@
         <v>5</v>
       </c>
       <c r="J859" s="61" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K859" s="60">
         <v>16</v>
@@ -45948,7 +45951,7 @@
         <v>0</v>
       </c>
       <c r="O859" s="1" t="s">
-        <v>444</v>
+        <v>686</v>
       </c>
       <c r="P859" s="1">
         <v>0</v>
@@ -45998,7 +46001,7 @@
         <v>0</v>
       </c>
       <c r="O860" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="P860" s="1">
         <v>0</v>
@@ -46048,7 +46051,7 @@
         <v>0</v>
       </c>
       <c r="O861" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="P861" s="1">
         <v>0</v>
@@ -46098,7 +46101,7 @@
         <v>0</v>
       </c>
       <c r="O862" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="P862" s="1">
         <v>0</v>
@@ -46133,7 +46136,7 @@
         <v>1</v>
       </c>
       <c r="J863" s="61" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="K863" s="60">
         <v>30</v>
@@ -46148,7 +46151,7 @@
         <v>1</v>
       </c>
       <c r="O863" s="1" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="P863" s="1">
         <v>0</v>
@@ -46183,7 +46186,7 @@
         <v>1</v>
       </c>
       <c r="J864" s="61" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="K864" s="60">
         <v>30</v>
@@ -46198,7 +46201,7 @@
         <v>1</v>
       </c>
       <c r="O864" s="1" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="P864" s="1">
         <v>0</v>
@@ -46233,7 +46236,7 @@
         <v>1</v>
       </c>
       <c r="J865" s="61" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="K865" s="60">
         <v>30</v>
@@ -46248,7 +46251,7 @@
         <v>1</v>
       </c>
       <c r="O865" s="1" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="P865" s="1">
         <v>0</v>
@@ -46283,7 +46286,7 @@
         <v>1</v>
       </c>
       <c r="J866" s="61" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="K866" s="60">
         <v>30</v>
@@ -46298,7 +46301,7 @@
         <v>1</v>
       </c>
       <c r="O866" s="1" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="P866" s="1">
         <v>0</v>
@@ -46333,7 +46336,7 @@
         <v>2</v>
       </c>
       <c r="J867" s="61" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="K867" s="60">
         <v>30</v>
@@ -46348,7 +46351,7 @@
         <v>1</v>
       </c>
       <c r="O867" s="1" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="P867" s="1">
         <v>0</v>
@@ -46383,7 +46386,7 @@
         <v>2</v>
       </c>
       <c r="J868" s="61" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="K868" s="60">
         <v>30</v>
@@ -46398,7 +46401,7 @@
         <v>1</v>
       </c>
       <c r="O868" s="1" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="P868" s="1">
         <v>0</v>
@@ -46433,7 +46436,7 @@
         <v>2</v>
       </c>
       <c r="J869" s="61" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="K869" s="60">
         <v>30</v>
@@ -46448,7 +46451,7 @@
         <v>1</v>
       </c>
       <c r="O869" s="1" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="P869" s="1">
         <v>0</v>
@@ -46483,7 +46486,7 @@
         <v>2</v>
       </c>
       <c r="J870" s="61" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="K870" s="60">
         <v>30</v>
@@ -46498,7 +46501,7 @@
         <v>1</v>
       </c>
       <c r="O870" s="1" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="P870" s="1">
         <v>0</v>
@@ -46533,7 +46536,7 @@
         <v>2</v>
       </c>
       <c r="J871" s="61" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="K871" s="60">
         <v>30</v>
@@ -46548,7 +46551,7 @@
         <v>1</v>
       </c>
       <c r="O871" s="1" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="P871" s="1">
         <v>0</v>
@@ -46583,7 +46586,7 @@
         <v>2</v>
       </c>
       <c r="J872" s="61" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="K872" s="60">
         <v>30</v>
@@ -46598,7 +46601,7 @@
         <v>1</v>
       </c>
       <c r="O872" s="1" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="P872" s="1">
         <v>0</v>
@@ -46633,7 +46636,7 @@
         <v>3</v>
       </c>
       <c r="J873" s="61" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
       <c r="K873" s="60">
         <v>30</v>
@@ -46648,7 +46651,7 @@
         <v>1</v>
       </c>
       <c r="O873" s="1" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="P873" s="1">
         <v>0</v>
@@ -46683,7 +46686,7 @@
         <v>3</v>
       </c>
       <c r="J874" s="61" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="K874" s="60">
         <v>30</v>
@@ -46698,7 +46701,7 @@
         <v>1</v>
       </c>
       <c r="O874" s="1" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="P874" s="1">
         <v>0</v>
@@ -46733,7 +46736,7 @@
         <v>3</v>
       </c>
       <c r="J875" s="61" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="K875" s="60">
         <v>30</v>
@@ -46748,7 +46751,7 @@
         <v>1</v>
       </c>
       <c r="O875" s="1" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
       <c r="P875" s="1">
         <v>0</v>
@@ -46783,7 +46786,7 @@
         <v>3</v>
       </c>
       <c r="J876" s="61" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="K876" s="60">
         <v>30</v>
@@ -46798,7 +46801,7 @@
         <v>1</v>
       </c>
       <c r="O876" s="1" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="P876" s="1">
         <v>0</v>
@@ -46833,7 +46836,7 @@
         <v>3</v>
       </c>
       <c r="J877" s="61" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="K877" s="60">
         <v>30</v>
@@ -46848,7 +46851,7 @@
         <v>1</v>
       </c>
       <c r="O877" s="1" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="P877" s="1">
         <v>0</v>
@@ -46883,7 +46886,7 @@
         <v>3</v>
       </c>
       <c r="J878" s="61" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="K878" s="60">
         <v>30</v>
@@ -46898,7 +46901,7 @@
         <v>1</v>
       </c>
       <c r="O878" s="1" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="P878" s="1">
         <v>0</v>
@@ -46933,7 +46936,7 @@
         <v>3</v>
       </c>
       <c r="J879" s="61" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="K879" s="60">
         <v>30</v>
@@ -46948,7 +46951,7 @@
         <v>1</v>
       </c>
       <c r="O879" s="1" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="P879" s="1">
         <v>0</v>
@@ -46983,7 +46986,7 @@
         <v>3</v>
       </c>
       <c r="J880" s="61" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="K880" s="60">
         <v>30</v>
@@ -46998,7 +47001,7 @@
         <v>1</v>
       </c>
       <c r="O880" s="1" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="P880" s="1">
         <v>0</v>
@@ -47033,7 +47036,7 @@
         <v>4</v>
       </c>
       <c r="J881" s="61" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="K881" s="60">
         <v>30</v>
@@ -47048,7 +47051,7 @@
         <v>1</v>
       </c>
       <c r="O881" s="1" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="P881" s="1">
         <v>0</v>
@@ -47083,7 +47086,7 @@
         <v>4</v>
       </c>
       <c r="J882" s="61" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="K882" s="60">
         <v>30</v>
@@ -47098,7 +47101,7 @@
         <v>1</v>
       </c>
       <c r="O882" s="1" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="P882" s="1">
         <v>0</v>
@@ -47133,7 +47136,7 @@
         <v>4</v>
       </c>
       <c r="J883" s="61" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="K883" s="60">
         <v>30</v>
@@ -47148,7 +47151,7 @@
         <v>1</v>
       </c>
       <c r="O883" s="1" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="P883" s="1">
         <v>0</v>
@@ -47183,7 +47186,7 @@
         <v>4</v>
       </c>
       <c r="J884" s="61" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="K884" s="60">
         <v>30</v>
@@ -47198,7 +47201,7 @@
         <v>1</v>
       </c>
       <c r="O884" s="1" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="P884" s="1">
         <v>0</v>
@@ -47233,7 +47236,7 @@
         <v>4</v>
       </c>
       <c r="J885" s="61" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="K885" s="60">
         <v>30</v>
@@ -47248,7 +47251,7 @@
         <v>1</v>
       </c>
       <c r="O885" s="1" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="P885" s="1">
         <v>0</v>
@@ -47283,7 +47286,7 @@
         <v>4</v>
       </c>
       <c r="J886" s="61" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="K886" s="60">
         <v>30</v>
@@ -47298,7 +47301,7 @@
         <v>1</v>
       </c>
       <c r="O886" s="1" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="P886" s="1">
         <v>0</v>
@@ -47333,7 +47336,7 @@
         <v>4</v>
       </c>
       <c r="J887" s="61" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="K887" s="60">
         <v>30</v>
@@ -47348,7 +47351,7 @@
         <v>1</v>
       </c>
       <c r="O887" s="1" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="P887" s="1">
         <v>0</v>
@@ -47383,7 +47386,7 @@
         <v>4</v>
       </c>
       <c r="J888" s="61" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="K888" s="60">
         <v>30</v>
@@ -47398,7 +47401,7 @@
         <v>1</v>
       </c>
       <c r="O888" s="1" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="P888" s="1">
         <v>0</v>
@@ -47433,7 +47436,7 @@
         <v>4</v>
       </c>
       <c r="J889" s="61" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="K889" s="60">
         <v>30</v>
@@ -47448,7 +47451,7 @@
         <v>1</v>
       </c>
       <c r="O889" s="1" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="P889" s="1">
         <v>0</v>
@@ -47483,7 +47486,7 @@
         <v>4</v>
       </c>
       <c r="J890" s="61" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="K890" s="60">
         <v>30</v>
@@ -47498,7 +47501,7 @@
         <v>1</v>
       </c>
       <c r="O890" s="1" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="P890" s="1">
         <v>0</v>
@@ -47533,7 +47536,7 @@
         <v>5</v>
       </c>
       <c r="J891" s="61" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="K891" s="60">
         <v>30</v>
@@ -47548,7 +47551,7 @@
         <v>1</v>
       </c>
       <c r="O891" s="1" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="P891" s="1">
         <v>0</v>
@@ -47583,7 +47586,7 @@
         <v>5</v>
       </c>
       <c r="J892" s="61" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="K892" s="60">
         <v>30</v>
@@ -47598,7 +47601,7 @@
         <v>1</v>
       </c>
       <c r="O892" s="1" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="P892" s="1">
         <v>0</v>
@@ -47633,7 +47636,7 @@
         <v>5</v>
       </c>
       <c r="J893" s="63" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="K893" s="60">
         <v>30</v>
@@ -47648,7 +47651,7 @@
         <v>1</v>
       </c>
       <c r="O893" s="1" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="P893" s="1">
         <v>0</v>
@@ -47683,7 +47686,7 @@
         <v>5</v>
       </c>
       <c r="J894" s="63" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="K894" s="60">
         <v>30</v>
@@ -47698,7 +47701,7 @@
         <v>1</v>
       </c>
       <c r="O894" s="1" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="P894" s="1">
         <v>0</v>
@@ -47733,7 +47736,7 @@
         <v>5</v>
       </c>
       <c r="J895" s="63" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="K895" s="60">
         <v>30</v>
@@ -47748,7 +47751,7 @@
         <v>1</v>
       </c>
       <c r="O895" s="1" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="P895" s="1">
         <v>0</v>
@@ -47783,7 +47786,7 @@
         <v>5</v>
       </c>
       <c r="J896" s="63" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="K896" s="60">
         <v>30</v>
@@ -47798,7 +47801,7 @@
         <v>1</v>
       </c>
       <c r="O896" s="1" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="P896" s="1">
         <v>0</v>
@@ -47833,7 +47836,7 @@
         <v>5</v>
       </c>
       <c r="J897" s="63" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="K897" s="60">
         <v>30</v>
@@ -47848,7 +47851,7 @@
         <v>1</v>
       </c>
       <c r="O897" s="1" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="P897" s="1">
         <v>0</v>
@@ -47883,7 +47886,7 @@
         <v>5</v>
       </c>
       <c r="J898" s="63" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="K898" s="60">
         <v>30</v>
@@ -47898,7 +47901,7 @@
         <v>1</v>
       </c>
       <c r="O898" s="1" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="P898" s="1">
         <v>0</v>
@@ -47933,7 +47936,7 @@
         <v>5</v>
       </c>
       <c r="J899" s="63" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K899" s="60">
         <v>30</v>
@@ -47948,7 +47951,7 @@
         <v>1</v>
       </c>
       <c r="O899" s="1" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="P899" s="1">
         <v>0</v>
@@ -47983,7 +47986,7 @@
         <v>5</v>
       </c>
       <c r="J900" s="63" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="K900" s="60">
         <v>30</v>
@@ -47998,7 +48001,7 @@
         <v>1</v>
       </c>
       <c r="O900" s="1" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="P900" s="1">
         <v>0</v>
@@ -48033,7 +48036,7 @@
         <v>5</v>
       </c>
       <c r="J901" s="63" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="K901" s="60">
         <v>30</v>
@@ -48048,7 +48051,7 @@
         <v>1</v>
       </c>
       <c r="O901" s="1" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="P901" s="1">
         <v>0</v>
@@ -48083,7 +48086,7 @@
         <v>5</v>
       </c>
       <c r="J902" s="63" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="K902" s="60">
         <v>30</v>
@@ -48098,7 +48101,7 @@
         <v>1</v>
       </c>
       <c r="O902" s="1" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="P902" s="1">
         <v>0</v>
@@ -48133,7 +48136,7 @@
         <v>1</v>
       </c>
       <c r="J903" s="63" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K903" s="62">
         <v>400</v>
@@ -48148,7 +48151,7 @@
         <v>2</v>
       </c>
       <c r="O903" s="1" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="P903" s="1">
         <v>0</v>
@@ -48183,7 +48186,7 @@
         <v>1</v>
       </c>
       <c r="J904" s="63" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="K904" s="62">
         <v>400</v>
@@ -48198,7 +48201,7 @@
         <v>2</v>
       </c>
       <c r="O904" s="1" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="P904" s="1">
         <v>0</v>
@@ -48233,7 +48236,7 @@
         <v>1</v>
       </c>
       <c r="J905" s="63" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="K905" s="62">
         <v>400</v>
@@ -48248,7 +48251,7 @@
         <v>2</v>
       </c>
       <c r="O905" s="1" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="P905" s="1">
         <v>0</v>
@@ -48283,7 +48286,7 @@
         <v>1</v>
       </c>
       <c r="J906" s="63" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="K906" s="62">
         <v>400</v>
@@ -48298,7 +48301,7 @@
         <v>2</v>
       </c>
       <c r="O906" s="1" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="P906" s="1">
         <v>0</v>
@@ -48333,7 +48336,7 @@
         <v>1</v>
       </c>
       <c r="J907" s="63" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="K907" s="62">
         <v>400</v>
@@ -48348,7 +48351,7 @@
         <v>2</v>
       </c>
       <c r="O907" s="1" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="P907" s="1">
         <v>0</v>
@@ -48383,7 +48386,7 @@
         <v>1</v>
       </c>
       <c r="J908" s="63" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="K908" s="62">
         <v>400</v>
@@ -48398,7 +48401,7 @@
         <v>2</v>
       </c>
       <c r="O908" s="1" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="P908" s="1">
         <v>0</v>
@@ -48433,7 +48436,7 @@
         <v>2</v>
       </c>
       <c r="J909" s="63" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="K909" s="62">
         <v>400</v>
@@ -48448,7 +48451,7 @@
         <v>2</v>
       </c>
       <c r="O909" s="1" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="P909" s="1">
         <v>0</v>
@@ -48483,7 +48486,7 @@
         <v>2</v>
       </c>
       <c r="J910" s="63" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="K910" s="62">
         <v>400</v>
@@ -48498,7 +48501,7 @@
         <v>2</v>
       </c>
       <c r="O910" s="1" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="P910" s="1">
         <v>0</v>
@@ -48533,7 +48536,7 @@
         <v>2</v>
       </c>
       <c r="J911" s="63" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="K911" s="62">
         <v>400</v>
@@ -48548,7 +48551,7 @@
         <v>2</v>
       </c>
       <c r="O911" s="1" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="P911" s="1">
         <v>0</v>
@@ -48583,7 +48586,7 @@
         <v>2</v>
       </c>
       <c r="J912" s="63" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="K912" s="62">
         <v>400</v>
@@ -48598,7 +48601,7 @@
         <v>2</v>
       </c>
       <c r="O912" s="1" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="P912" s="1">
         <v>0</v>
@@ -48633,7 +48636,7 @@
         <v>2</v>
       </c>
       <c r="J913" s="63" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="K913" s="62">
         <v>400</v>
@@ -48648,7 +48651,7 @@
         <v>2</v>
       </c>
       <c r="O913" s="1" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="P913" s="1">
         <v>0</v>
@@ -48683,7 +48686,7 @@
         <v>2</v>
       </c>
       <c r="J914" s="63" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="K914" s="62">
         <v>400</v>
@@ -48698,7 +48701,7 @@
         <v>2</v>
       </c>
       <c r="O914" s="1" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="P914" s="1">
         <v>0</v>
@@ -48733,7 +48736,7 @@
         <v>2</v>
       </c>
       <c r="J915" s="63" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="K915" s="62">
         <v>400</v>
@@ -48748,7 +48751,7 @@
         <v>2</v>
       </c>
       <c r="O915" s="1" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="P915" s="1">
         <v>0</v>
@@ -48783,7 +48786,7 @@
         <v>2</v>
       </c>
       <c r="J916" s="63" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="K916" s="62">
         <v>400</v>
@@ -48798,7 +48801,7 @@
         <v>2</v>
       </c>
       <c r="O916" s="1" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="P916" s="1">
         <v>0</v>
@@ -48833,7 +48836,7 @@
         <v>3</v>
       </c>
       <c r="J917" s="63" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="K917" s="62">
         <v>400</v>
@@ -48848,7 +48851,7 @@
         <v>2</v>
       </c>
       <c r="O917" s="1" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="P917" s="1">
         <v>0</v>
@@ -48883,7 +48886,7 @@
         <v>3</v>
       </c>
       <c r="J918" s="63" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="K918" s="62">
         <v>400</v>
@@ -48898,7 +48901,7 @@
         <v>2</v>
       </c>
       <c r="O918" s="1" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="P918" s="1">
         <v>0</v>
@@ -48933,7 +48936,7 @@
         <v>3</v>
       </c>
       <c r="J919" s="63" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="K919" s="62">
         <v>400</v>
@@ -48948,7 +48951,7 @@
         <v>2</v>
       </c>
       <c r="O919" s="1" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="P919" s="1">
         <v>0</v>
@@ -48983,7 +48986,7 @@
         <v>3</v>
       </c>
       <c r="J920" s="63" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="K920" s="62">
         <v>400</v>
@@ -48998,7 +49001,7 @@
         <v>2</v>
       </c>
       <c r="O920" s="1" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="P920" s="1">
         <v>0</v>
@@ -49033,7 +49036,7 @@
         <v>3</v>
       </c>
       <c r="J921" s="63" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="K921" s="62">
         <v>400</v>
@@ -49048,7 +49051,7 @@
         <v>2</v>
       </c>
       <c r="O921" s="1" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="P921" s="1">
         <v>0</v>
@@ -49083,7 +49086,7 @@
         <v>3</v>
       </c>
       <c r="J922" s="63" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="K922" s="62">
         <v>400</v>
@@ -49098,7 +49101,7 @@
         <v>2</v>
       </c>
       <c r="O922" s="1" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="P922" s="1">
         <v>0</v>
@@ -49133,7 +49136,7 @@
         <v>3</v>
       </c>
       <c r="J923" s="63" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="K923" s="62">
         <v>400</v>
@@ -49148,7 +49151,7 @@
         <v>2</v>
       </c>
       <c r="O923" s="1" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="P923" s="1">
         <v>0</v>
@@ -49183,7 +49186,7 @@
         <v>3</v>
       </c>
       <c r="J924" s="63" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="K924" s="62">
         <v>400</v>
@@ -49198,7 +49201,7 @@
         <v>2</v>
       </c>
       <c r="O924" s="1" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="P924" s="1">
         <v>0</v>
@@ -49233,7 +49236,7 @@
         <v>3</v>
       </c>
       <c r="J925" s="63" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="K925" s="62">
         <v>400</v>
@@ -49248,7 +49251,7 @@
         <v>2</v>
       </c>
       <c r="O925" s="1" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="P925" s="1">
         <v>0</v>
@@ -49283,7 +49286,7 @@
         <v>3</v>
       </c>
       <c r="J926" s="63" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="K926" s="62">
         <v>400</v>
@@ -49298,7 +49301,7 @@
         <v>2</v>
       </c>
       <c r="O926" s="1" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="P926" s="1">
         <v>0</v>
@@ -49333,7 +49336,7 @@
         <v>4</v>
       </c>
       <c r="J927" s="63" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="K927" s="62">
         <v>400</v>
@@ -49348,7 +49351,7 @@
         <v>2</v>
       </c>
       <c r="O927" s="1" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="P927" s="1">
         <v>0</v>
@@ -49383,7 +49386,7 @@
         <v>4</v>
       </c>
       <c r="J928" s="63" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="K928" s="62">
         <v>400</v>
@@ -49398,7 +49401,7 @@
         <v>2</v>
       </c>
       <c r="O928" s="1" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="P928" s="1">
         <v>0</v>
@@ -49433,7 +49436,7 @@
         <v>4</v>
       </c>
       <c r="J929" s="63" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="K929" s="62">
         <v>400</v>
@@ -49448,7 +49451,7 @@
         <v>2</v>
       </c>
       <c r="O929" s="1" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="P929" s="1">
         <v>0</v>
@@ -49483,7 +49486,7 @@
         <v>4</v>
       </c>
       <c r="J930" s="63" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="K930" s="62">
         <v>400</v>
@@ -49498,7 +49501,7 @@
         <v>2</v>
       </c>
       <c r="O930" s="1" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="P930" s="1">
         <v>0</v>
@@ -49533,7 +49536,7 @@
         <v>4</v>
       </c>
       <c r="J931" s="63" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="K931" s="62">
         <v>400</v>
@@ -49548,7 +49551,7 @@
         <v>2</v>
       </c>
       <c r="O931" s="1" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="P931" s="1">
         <v>0</v>
@@ -49583,7 +49586,7 @@
         <v>4</v>
       </c>
       <c r="J932" s="63" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="K932" s="62">
         <v>400</v>
@@ -49598,7 +49601,7 @@
         <v>2</v>
       </c>
       <c r="O932" s="1" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="P932" s="1">
         <v>0</v>
@@ -49633,7 +49636,7 @@
         <v>4</v>
       </c>
       <c r="J933" s="63" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="K933" s="62">
         <v>400</v>
@@ -49648,7 +49651,7 @@
         <v>2</v>
       </c>
       <c r="O933" s="1" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="P933" s="1">
         <v>0</v>
@@ -49683,7 +49686,7 @@
         <v>4</v>
       </c>
       <c r="J934" s="63" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="K934" s="62">
         <v>400</v>
@@ -49698,7 +49701,7 @@
         <v>2</v>
       </c>
       <c r="O934" s="1" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="P934" s="1">
         <v>0</v>
@@ -49733,7 +49736,7 @@
         <v>4</v>
       </c>
       <c r="J935" s="63" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="K935" s="62">
         <v>400</v>
@@ -49748,7 +49751,7 @@
         <v>2</v>
       </c>
       <c r="O935" s="1" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="P935" s="1">
         <v>0</v>
@@ -49783,7 +49786,7 @@
         <v>4</v>
       </c>
       <c r="J936" s="63" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="K936" s="62">
         <v>400</v>
@@ -49798,7 +49801,7 @@
         <v>2</v>
       </c>
       <c r="O936" s="1" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="P936" s="1">
         <v>0</v>
@@ -49833,7 +49836,7 @@
         <v>4</v>
       </c>
       <c r="J937" s="63" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="K937" s="62">
         <v>400</v>
@@ -49848,7 +49851,7 @@
         <v>2</v>
       </c>
       <c r="O937" s="1" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="P937" s="1">
         <v>0</v>
@@ -49883,7 +49886,7 @@
         <v>4</v>
       </c>
       <c r="J938" s="63" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="K938" s="62">
         <v>400</v>
@@ -49898,7 +49901,7 @@
         <v>2</v>
       </c>
       <c r="O938" s="1" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="P938" s="1">
         <v>0</v>
@@ -49933,7 +49936,7 @@
         <v>5</v>
       </c>
       <c r="J939" s="63" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="K939" s="62">
         <v>400</v>
@@ -49948,7 +49951,7 @@
         <v>2</v>
       </c>
       <c r="O939" s="1" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="P939" s="1">
         <v>0</v>
@@ -49983,7 +49986,7 @@
         <v>5</v>
       </c>
       <c r="J940" s="63" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="K940" s="62">
         <v>400</v>
@@ -49998,7 +50001,7 @@
         <v>2</v>
       </c>
       <c r="O940" s="1" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="P940" s="1">
         <v>0</v>
@@ -50033,7 +50036,7 @@
         <v>5</v>
       </c>
       <c r="J941" s="63" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="K941" s="62">
         <v>400</v>
@@ -50048,7 +50051,7 @@
         <v>2</v>
       </c>
       <c r="O941" s="1" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="P941" s="1">
         <v>0</v>
@@ -50083,7 +50086,7 @@
         <v>5</v>
       </c>
       <c r="J942" s="63" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="K942" s="62">
         <v>400</v>
@@ -50098,7 +50101,7 @@
         <v>2</v>
       </c>
       <c r="O942" s="1" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="P942" s="1">
         <v>0</v>
@@ -50133,7 +50136,7 @@
         <v>5</v>
       </c>
       <c r="J943" s="63" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="K943" s="62">
         <v>400</v>
@@ -50148,7 +50151,7 @@
         <v>2</v>
       </c>
       <c r="O943" s="1" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="P943" s="1">
         <v>0</v>
@@ -50183,7 +50186,7 @@
         <v>5</v>
       </c>
       <c r="J944" s="63" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="K944" s="62">
         <v>400</v>
@@ -50198,7 +50201,7 @@
         <v>2</v>
       </c>
       <c r="O944" s="1" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="P944" s="1">
         <v>0</v>
@@ -50233,7 +50236,7 @@
         <v>5</v>
       </c>
       <c r="J945" s="63" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="K945" s="62">
         <v>400</v>
@@ -50248,7 +50251,7 @@
         <v>2</v>
       </c>
       <c r="O945" s="1" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="P945" s="1">
         <v>0</v>
@@ -50283,7 +50286,7 @@
         <v>5</v>
       </c>
       <c r="J946" s="63" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="K946" s="62">
         <v>400</v>
@@ -50298,7 +50301,7 @@
         <v>2</v>
       </c>
       <c r="O946" s="1" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="P946" s="1">
         <v>0</v>
@@ -50333,7 +50336,7 @@
         <v>5</v>
       </c>
       <c r="J947" s="63" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="K947" s="62">
         <v>400</v>
@@ -50348,7 +50351,7 @@
         <v>2</v>
       </c>
       <c r="O947" s="1" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="P947" s="1">
         <v>0</v>
@@ -50383,7 +50386,7 @@
         <v>5</v>
       </c>
       <c r="J948" s="63" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="K948" s="62">
         <v>400</v>
@@ -50398,7 +50401,7 @@
         <v>2</v>
       </c>
       <c r="O948" s="1" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="P948" s="1">
         <v>0</v>
@@ -50433,7 +50436,7 @@
         <v>5</v>
       </c>
       <c r="J949" s="63" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="K949" s="62">
         <v>400</v>
@@ -50448,7 +50451,7 @@
         <v>2</v>
       </c>
       <c r="O949" s="1" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="P949" s="1">
         <v>0</v>
@@ -50483,7 +50486,7 @@
         <v>5</v>
       </c>
       <c r="J950" s="63" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="K950" s="62">
         <v>400</v>
@@ -50498,7 +50501,7 @@
         <v>2</v>
       </c>
       <c r="O950" s="1" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="P950" s="1">
         <v>0</v>
@@ -50533,7 +50536,7 @@
         <v>5</v>
       </c>
       <c r="J951" s="63" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="K951" s="62">
         <v>400</v>
@@ -50548,7 +50551,7 @@
         <v>2</v>
       </c>
       <c r="O951" s="1" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="P951" s="1">
         <v>0</v>
@@ -50583,7 +50586,7 @@
         <v>5</v>
       </c>
       <c r="J952" s="63" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="K952" s="62">
         <v>400</v>
@@ -50598,7 +50601,7 @@
         <v>2</v>
       </c>
       <c r="O952" s="1" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="P952" s="1">
         <v>0</v>
@@ -50633,7 +50636,7 @@
         <v>1</v>
       </c>
       <c r="J953" s="63" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="K953" s="62">
         <v>6000</v>
@@ -50648,7 +50651,7 @@
         <v>3</v>
       </c>
       <c r="O953" s="1" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="P953" s="1">
         <v>0</v>
@@ -50683,7 +50686,7 @@
         <v>1</v>
       </c>
       <c r="J954" s="63" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="K954" s="62">
         <v>6000</v>
@@ -50698,7 +50701,7 @@
         <v>3</v>
       </c>
       <c r="O954" s="1" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="P954" s="1">
         <v>0</v>
@@ -50733,7 +50736,7 @@
         <v>1</v>
       </c>
       <c r="J955" s="63" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="K955" s="62">
         <v>6000</v>
@@ -50748,7 +50751,7 @@
         <v>3</v>
       </c>
       <c r="O955" s="1" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="P955" s="1">
         <v>0</v>
@@ -50783,7 +50786,7 @@
         <v>1</v>
       </c>
       <c r="J956" s="63" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="K956" s="62">
         <v>6000</v>
@@ -50798,7 +50801,7 @@
         <v>3</v>
       </c>
       <c r="O956" s="1" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="P956" s="1">
         <v>0</v>
@@ -50833,7 +50836,7 @@
         <v>1</v>
       </c>
       <c r="J957" s="63" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="K957" s="62">
         <v>6000</v>
@@ -50848,7 +50851,7 @@
         <v>3</v>
       </c>
       <c r="O957" s="1" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="P957" s="1">
         <v>0</v>
@@ -50883,7 +50886,7 @@
         <v>1</v>
       </c>
       <c r="J958" s="63" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="K958" s="62">
         <v>6000</v>
@@ -50898,7 +50901,7 @@
         <v>3</v>
       </c>
       <c r="O958" s="1" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="P958" s="1">
         <v>0</v>
@@ -50933,7 +50936,7 @@
         <v>1</v>
       </c>
       <c r="J959" s="63" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="K959" s="62">
         <v>6000</v>
@@ -50948,7 +50951,7 @@
         <v>3</v>
       </c>
       <c r="O959" s="1" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="P959" s="1">
         <v>0</v>
@@ -50983,7 +50986,7 @@
         <v>1</v>
       </c>
       <c r="J960" s="63" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="K960" s="62">
         <v>6000</v>
@@ -50998,7 +51001,7 @@
         <v>3</v>
       </c>
       <c r="O960" s="1" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="P960" s="1">
         <v>0</v>
@@ -51033,7 +51036,7 @@
         <v>2</v>
       </c>
       <c r="J961" s="63" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="K961" s="62">
         <v>6000</v>
@@ -51048,7 +51051,7 @@
         <v>3</v>
       </c>
       <c r="O961" s="1" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="P961" s="1">
         <v>0</v>
@@ -51083,7 +51086,7 @@
         <v>2</v>
       </c>
       <c r="J962" s="63" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="K962" s="62">
         <v>6000</v>
@@ -51098,7 +51101,7 @@
         <v>3</v>
       </c>
       <c r="O962" s="1" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="P962" s="1">
         <v>0</v>
@@ -51133,7 +51136,7 @@
         <v>2</v>
       </c>
       <c r="J963" s="63" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="K963" s="62">
         <v>6000</v>
@@ -51148,7 +51151,7 @@
         <v>3</v>
       </c>
       <c r="O963" s="1" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="P963" s="1">
         <v>0</v>
@@ -51183,7 +51186,7 @@
         <v>2</v>
       </c>
       <c r="J964" s="63" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="K964" s="62">
         <v>6000</v>
@@ -51198,7 +51201,7 @@
         <v>3</v>
       </c>
       <c r="O964" s="1" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="P964" s="1">
         <v>0</v>
@@ -51233,7 +51236,7 @@
         <v>2</v>
       </c>
       <c r="J965" s="63" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="K965" s="62">
         <v>6000</v>
@@ -51248,7 +51251,7 @@
         <v>3</v>
       </c>
       <c r="O965" s="1" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="P965" s="1">
         <v>0</v>
@@ -51283,7 +51286,7 @@
         <v>2</v>
       </c>
       <c r="J966" s="63" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="K966" s="62">
         <v>6000</v>
@@ -51298,7 +51301,7 @@
         <v>3</v>
       </c>
       <c r="O966" s="1" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="P966" s="1">
         <v>0</v>
@@ -51333,7 +51336,7 @@
         <v>2</v>
       </c>
       <c r="J967" s="63" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="K967" s="62">
         <v>6000</v>
@@ -51348,7 +51351,7 @@
         <v>3</v>
       </c>
       <c r="O967" s="1" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="P967" s="1">
         <v>0</v>
@@ -51383,7 +51386,7 @@
         <v>2</v>
       </c>
       <c r="J968" s="63" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="K968" s="62">
         <v>6000</v>
@@ -51398,7 +51401,7 @@
         <v>3</v>
       </c>
       <c r="O968" s="1" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="P968" s="1">
         <v>0</v>
@@ -51433,7 +51436,7 @@
         <v>2</v>
       </c>
       <c r="J969" s="63" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="K969" s="62">
         <v>6000</v>
@@ -51448,7 +51451,7 @@
         <v>3</v>
       </c>
       <c r="O969" s="1" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="P969" s="1">
         <v>0</v>
@@ -51483,7 +51486,7 @@
         <v>2</v>
       </c>
       <c r="J970" s="63" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="K970" s="62">
         <v>6000</v>
@@ -51498,7 +51501,7 @@
         <v>3</v>
       </c>
       <c r="O970" s="1" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="P970" s="1">
         <v>0</v>
@@ -51533,7 +51536,7 @@
         <v>3</v>
       </c>
       <c r="J971" s="63" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="K971" s="62">
         <v>6000</v>
@@ -51548,7 +51551,7 @@
         <v>3</v>
       </c>
       <c r="O971" s="1" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="P971" s="1">
         <v>0</v>
@@ -51583,7 +51586,7 @@
         <v>3</v>
       </c>
       <c r="J972" s="63" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="K972" s="62">
         <v>6000</v>
@@ -51598,7 +51601,7 @@
         <v>3</v>
       </c>
       <c r="O972" s="1" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="P972" s="1">
         <v>0</v>
@@ -51633,7 +51636,7 @@
         <v>3</v>
       </c>
       <c r="J973" s="63" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="K973" s="62">
         <v>6000</v>
@@ -51648,7 +51651,7 @@
         <v>3</v>
       </c>
       <c r="O973" s="1" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="P973" s="1">
         <v>0</v>
@@ -51683,7 +51686,7 @@
         <v>3</v>
       </c>
       <c r="J974" s="63" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="K974" s="62">
         <v>6000</v>
@@ -51698,7 +51701,7 @@
         <v>3</v>
       </c>
       <c r="O974" s="1" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="P974" s="1">
         <v>0</v>
@@ -51733,7 +51736,7 @@
         <v>3</v>
       </c>
       <c r="J975" s="63" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="K975" s="62">
         <v>6000</v>
@@ -51748,7 +51751,7 @@
         <v>3</v>
       </c>
       <c r="O975" s="1" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="P975" s="1">
         <v>0</v>
@@ -51783,7 +51786,7 @@
         <v>3</v>
       </c>
       <c r="J976" s="63" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="K976" s="62">
         <v>6000</v>
@@ -51798,7 +51801,7 @@
         <v>3</v>
       </c>
       <c r="O976" s="1" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="P976" s="1">
         <v>0</v>
@@ -51833,7 +51836,7 @@
         <v>3</v>
       </c>
       <c r="J977" s="63" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="K977" s="62">
         <v>6000</v>
@@ -51848,7 +51851,7 @@
         <v>3</v>
       </c>
       <c r="O977" s="1" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="P977" s="1">
         <v>0</v>
@@ -51883,7 +51886,7 @@
         <v>3</v>
       </c>
       <c r="J978" s="63" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="K978" s="62">
         <v>6000</v>
@@ -51898,7 +51901,7 @@
         <v>3</v>
       </c>
       <c r="O978" s="1" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="P978" s="1">
         <v>0</v>
@@ -51933,7 +51936,7 @@
         <v>3</v>
       </c>
       <c r="J979" s="63" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="K979" s="62">
         <v>6000</v>
@@ -51948,7 +51951,7 @@
         <v>3</v>
       </c>
       <c r="O979" s="1" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="P979" s="1">
         <v>0</v>
@@ -51983,7 +51986,7 @@
         <v>3</v>
       </c>
       <c r="J980" s="63" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="K980" s="62">
         <v>6000</v>
@@ -51998,7 +52001,7 @@
         <v>3</v>
       </c>
       <c r="O980" s="1" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="P980" s="1">
         <v>0</v>
@@ -52033,7 +52036,7 @@
         <v>3</v>
       </c>
       <c r="J981" s="63" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="K981" s="62">
         <v>6000</v>
@@ -52048,7 +52051,7 @@
         <v>3</v>
       </c>
       <c r="O981" s="1" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="P981" s="1">
         <v>0</v>
@@ -52083,7 +52086,7 @@
         <v>3</v>
       </c>
       <c r="J982" s="63" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="K982" s="62">
         <v>6000</v>
@@ -52098,7 +52101,7 @@
         <v>3</v>
       </c>
       <c r="O982" s="1" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="P982" s="1">
         <v>0</v>
@@ -52133,7 +52136,7 @@
         <v>4</v>
       </c>
       <c r="J983" s="63" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="K983" s="62">
         <v>6000</v>
@@ -52148,7 +52151,7 @@
         <v>3</v>
       </c>
       <c r="O983" s="1" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="P983" s="1">
         <v>0</v>
@@ -52183,7 +52186,7 @@
         <v>4</v>
       </c>
       <c r="J984" s="63" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="K984" s="62">
         <v>6000</v>
@@ -52198,7 +52201,7 @@
         <v>3</v>
       </c>
       <c r="O984" s="1" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="P984" s="1">
         <v>0</v>
@@ -52233,7 +52236,7 @@
         <v>4</v>
       </c>
       <c r="J985" s="63" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="K985" s="62">
         <v>6000</v>
@@ -52248,7 +52251,7 @@
         <v>3</v>
       </c>
       <c r="O985" s="1" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="P985" s="1">
         <v>0</v>
@@ -52283,7 +52286,7 @@
         <v>4</v>
       </c>
       <c r="J986" s="63" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="K986" s="62">
         <v>6000</v>
@@ -52298,7 +52301,7 @@
         <v>3</v>
       </c>
       <c r="O986" s="1" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="P986" s="1">
         <v>0</v>
@@ -52333,7 +52336,7 @@
         <v>4</v>
       </c>
       <c r="J987" s="63" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="K987" s="62">
         <v>6000</v>
@@ -52348,7 +52351,7 @@
         <v>3</v>
       </c>
       <c r="O987" s="1" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="P987" s="1">
         <v>0</v>
@@ -52383,7 +52386,7 @@
         <v>4</v>
       </c>
       <c r="J988" s="63" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="K988" s="62">
         <v>6000</v>
@@ -52398,7 +52401,7 @@
         <v>3</v>
       </c>
       <c r="O988" s="1" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="P988" s="1">
         <v>0</v>
@@ -52433,7 +52436,7 @@
         <v>4</v>
       </c>
       <c r="J989" s="63" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="K989" s="62">
         <v>6000</v>
@@ -52448,7 +52451,7 @@
         <v>3</v>
       </c>
       <c r="O989" s="1" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="P989" s="1">
         <v>0</v>
@@ -52483,7 +52486,7 @@
         <v>4</v>
       </c>
       <c r="J990" s="63" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="K990" s="62">
         <v>6000</v>
@@ -52498,7 +52501,7 @@
         <v>3</v>
       </c>
       <c r="O990" s="1" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="P990" s="1">
         <v>0</v>
@@ -52533,7 +52536,7 @@
         <v>4</v>
       </c>
       <c r="J991" s="63" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="K991" s="62">
         <v>6000</v>
@@ -52548,7 +52551,7 @@
         <v>3</v>
       </c>
       <c r="O991" s="1" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="P991" s="1">
         <v>0</v>
@@ -52583,7 +52586,7 @@
         <v>4</v>
       </c>
       <c r="J992" s="63" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="K992" s="62">
         <v>6000</v>
@@ -52598,7 +52601,7 @@
         <v>3</v>
       </c>
       <c r="O992" s="1" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="P992" s="1">
         <v>0</v>
@@ -52633,7 +52636,7 @@
         <v>4</v>
       </c>
       <c r="J993" s="63" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="K993" s="62">
         <v>6000</v>
@@ -52648,7 +52651,7 @@
         <v>3</v>
       </c>
       <c r="O993" s="1" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="P993" s="1">
         <v>0</v>
@@ -52683,7 +52686,7 @@
         <v>4</v>
       </c>
       <c r="J994" s="63" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="K994" s="62">
         <v>6000</v>
@@ -52698,7 +52701,7 @@
         <v>3</v>
       </c>
       <c r="O994" s="1" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="P994" s="1">
         <v>0</v>
@@ -52733,7 +52736,7 @@
         <v>4</v>
       </c>
       <c r="J995" s="63" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="K995" s="62">
         <v>6000</v>
@@ -52748,7 +52751,7 @@
         <v>3</v>
       </c>
       <c r="O995" s="1" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="P995" s="1">
         <v>0</v>
@@ -52783,7 +52786,7 @@
         <v>4</v>
       </c>
       <c r="J996" s="63" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="K996" s="62">
         <v>6000</v>
@@ -52798,7 +52801,7 @@
         <v>3</v>
       </c>
       <c r="O996" s="1" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="P996" s="1">
         <v>0</v>
@@ -52833,7 +52836,7 @@
         <v>5</v>
       </c>
       <c r="J997" s="63" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="K997" s="62">
         <v>6000</v>
@@ -52848,7 +52851,7 @@
         <v>3</v>
       </c>
       <c r="O997" s="1" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="P997" s="1">
         <v>0</v>
@@ -52883,7 +52886,7 @@
         <v>5</v>
       </c>
       <c r="J998" s="63" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="K998" s="62">
         <v>6000</v>
@@ -52898,7 +52901,7 @@
         <v>3</v>
       </c>
       <c r="O998" s="1" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
       <c r="P998" s="1">
         <v>0</v>
@@ -52933,7 +52936,7 @@
         <v>5</v>
       </c>
       <c r="J999" s="63" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="K999" s="62">
         <v>6000</v>
@@ -52948,7 +52951,7 @@
         <v>3</v>
       </c>
       <c r="O999" s="1" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="P999" s="1">
         <v>0</v>
@@ -52983,7 +52986,7 @@
         <v>5</v>
       </c>
       <c r="J1000" s="63" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="K1000" s="62">
         <v>6000</v>
@@ -52998,7 +53001,7 @@
         <v>3</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="P1000" s="1">
         <v>0</v>
@@ -53033,7 +53036,7 @@
         <v>5</v>
       </c>
       <c r="J1001" s="63" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="K1001" s="62">
         <v>6000</v>
@@ -53048,7 +53051,7 @@
         <v>3</v>
       </c>
       <c r="O1001" s="1" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="P1001" s="1">
         <v>0</v>
@@ -53083,7 +53086,7 @@
         <v>5</v>
       </c>
       <c r="J1002" s="63" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="K1002" s="62">
         <v>6000</v>
@@ -53098,7 +53101,7 @@
         <v>3</v>
       </c>
       <c r="O1002" s="1" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="P1002" s="1">
         <v>0</v>
@@ -53133,7 +53136,7 @@
         <v>5</v>
       </c>
       <c r="J1003" s="63" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="K1003" s="62">
         <v>6000</v>
@@ -53148,7 +53151,7 @@
         <v>3</v>
       </c>
       <c r="O1003" s="1" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="P1003" s="1">
         <v>0</v>
@@ -53183,7 +53186,7 @@
         <v>5</v>
       </c>
       <c r="J1004" s="63" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="K1004" s="62">
         <v>6000</v>
@@ -53198,7 +53201,7 @@
         <v>3</v>
       </c>
       <c r="O1004" s="1" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="P1004" s="1">
         <v>0</v>
@@ -53233,7 +53236,7 @@
         <v>5</v>
       </c>
       <c r="J1005" s="63" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="K1005" s="62">
         <v>6000</v>
@@ -53248,7 +53251,7 @@
         <v>3</v>
       </c>
       <c r="O1005" s="1" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="P1005" s="1">
         <v>0</v>
@@ -53283,7 +53286,7 @@
         <v>5</v>
       </c>
       <c r="J1006" s="63" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="K1006" s="62">
         <v>6000</v>
@@ -53298,7 +53301,7 @@
         <v>3</v>
       </c>
       <c r="O1006" s="1" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="P1006" s="1">
         <v>0</v>
@@ -53333,7 +53336,7 @@
         <v>5</v>
       </c>
       <c r="J1007" s="63" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="K1007" s="62">
         <v>6000</v>
@@ -53348,7 +53351,7 @@
         <v>3</v>
       </c>
       <c r="O1007" s="1" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="P1007" s="1">
         <v>0</v>
@@ -53383,7 +53386,7 @@
         <v>5</v>
       </c>
       <c r="J1008" s="63" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="K1008" s="62">
         <v>6000</v>
@@ -53398,7 +53401,7 @@
         <v>3</v>
       </c>
       <c r="O1008" s="1" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="P1008" s="1">
         <v>0</v>
@@ -53433,7 +53436,7 @@
         <v>5</v>
       </c>
       <c r="J1009" s="63" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="K1009" s="62">
         <v>6000</v>
@@ -53448,7 +53451,7 @@
         <v>3</v>
       </c>
       <c r="O1009" s="1" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="P1009" s="1">
         <v>0</v>
@@ -53483,7 +53486,7 @@
         <v>5</v>
       </c>
       <c r="J1010" s="63" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="K1010" s="62">
         <v>6000</v>
@@ -53498,7 +53501,7 @@
         <v>3</v>
       </c>
       <c r="O1010" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="P1010" s="1">
         <v>0</v>
@@ -53533,7 +53536,7 @@
         <v>5</v>
       </c>
       <c r="J1011" s="63" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="K1011" s="62">
         <v>6000</v>
@@ -53548,7 +53551,7 @@
         <v>3</v>
       </c>
       <c r="O1011" s="1" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="P1011" s="1">
         <v>0</v>
@@ -53583,7 +53586,7 @@
         <v>5</v>
       </c>
       <c r="J1012" s="63" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="K1012" s="62">
         <v>6000</v>
@@ -53598,7 +53601,7 @@
         <v>3</v>
       </c>
       <c r="O1012" s="1" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="P1012" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA4299C9-D3FC-4AFC-A2A2-DFF0471C1F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A201FDF-6869-43C9-A9B0-21CA8366C80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="759">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2219,6 +2219,204 @@
   <si>
     <t>Brushing_monsters_position</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>71105</t>
+  </si>
+  <si>
+    <t>71105,71102,71102</t>
+  </si>
+  <si>
+    <t>71108,71102</t>
+  </si>
+  <si>
+    <t>71106,71103</t>
+  </si>
+  <si>
+    <t>71104,71104,71101</t>
+  </si>
+  <si>
+    <t>71107,71104,71104</t>
+  </si>
+  <si>
+    <t>71104,71101,71101</t>
+  </si>
+  <si>
+    <t>71102,71102,71105</t>
+  </si>
+  <si>
+    <t>71108,71105,71102</t>
+  </si>
+  <si>
+    <t>71105,71105,71102,71105</t>
+  </si>
+  <si>
+    <t>71105,71102,71105,71105</t>
+  </si>
+  <si>
+    <t>71105,71105,71105,71105</t>
+  </si>
+  <si>
+    <t>71108,71102,71102,71105</t>
+  </si>
+  <si>
+    <t>71108,71105,71102,71105,71102</t>
+  </si>
+  <si>
+    <t>71108,71102,71102,71105,71105</t>
+  </si>
+  <si>
+    <t>71105,71102,71105,71102,71105</t>
+  </si>
+  <si>
+    <t>71106,71106,71106,71103,71103</t>
+  </si>
+  <si>
+    <t>71109,71103,71103,71106,71106</t>
+  </si>
+  <si>
+    <t>71109,71103,71106,71106,71106</t>
+  </si>
+  <si>
+    <t>71106,71106,71103,71103,71106</t>
+  </si>
+  <si>
+    <t>71106,71106,71106,71106,71106,71106</t>
+  </si>
+  <si>
+    <t>71106,71103,71103,71106,71106</t>
+  </si>
+  <si>
+    <t>71109,71109,71103,71106,71106,71106</t>
+  </si>
+  <si>
+    <t>71106,71106,71103,71106,71106,71106</t>
+  </si>
+  <si>
+    <t>8,60</t>
+  </si>
+  <si>
+    <t>8,65,8,90</t>
+  </si>
+  <si>
+    <t>8,70</t>
+  </si>
+  <si>
+    <t>40,75</t>
+  </si>
+  <si>
+    <t>45,75,80,75</t>
+  </si>
+  <si>
+    <t>50,75,85,80</t>
+  </si>
+  <si>
+    <t>60,75</t>
+  </si>
+  <si>
+    <t>55,75,20,75</t>
+  </si>
+  <si>
+    <t>50,75</t>
+  </si>
+  <si>
+    <t>45,75,15,85,15,65</t>
+  </si>
+  <si>
+    <t>40,70,40,80</t>
+  </si>
+  <si>
+    <t>45,65,45,85</t>
+  </si>
+  <si>
+    <t>50,65,50,85,85,80</t>
+  </si>
+  <si>
+    <t>60,70,60,80</t>
+  </si>
+  <si>
+    <t>55,75,50,65,50,85</t>
+  </si>
+  <si>
+    <t>50,75,15,80,15,70</t>
+  </si>
+  <si>
+    <t>50,75,85,75</t>
+  </si>
+  <si>
+    <t>55,70,55,80,90,85</t>
+  </si>
+  <si>
+    <t>60,65,60,85,90,65</t>
+  </si>
+  <si>
+    <t>50,75,20,70,20,80</t>
+  </si>
+  <si>
+    <t>45,75,15,65,15,85</t>
+  </si>
+  <si>
+    <t>40,70,40,80,15,75</t>
+  </si>
+  <si>
+    <t>45,75,50,65,50,85</t>
+  </si>
+  <si>
+    <t>55,75,80,70,80,80</t>
+  </si>
+  <si>
+    <t>55,75,85,65,85,85</t>
+  </si>
+  <si>
+    <t>55,75,60,75,90,80</t>
+  </si>
+  <si>
+    <t>60,65,60,85,90,70,65,75</t>
+  </si>
+  <si>
+    <t>60,75,20,75,60,85,60,65</t>
+  </si>
+  <si>
+    <t>55,90,55,80,55,70,55,60</t>
+  </si>
+  <si>
+    <t>55,75,20,85,20,65,50,75</t>
+  </si>
+  <si>
+    <t>50,75,45,85,15,70,45,65,15,80</t>
+  </si>
+  <si>
+    <t>45,90,45,80,45,70,45,60</t>
+  </si>
+  <si>
+    <t>45,75,15,60,15,90,40,85,40,65</t>
+  </si>
+  <si>
+    <t>40,85,10,85,40,75,10,65,40,65</t>
+  </si>
+  <si>
+    <t>40,75,40,65,40,85,80,70,80,80</t>
+  </si>
+  <si>
+    <t>45,75,85,90,85,60,40,65,40,85</t>
+  </si>
+  <si>
+    <t>50,75,85,75,45,75,45,90,45,60</t>
+  </si>
+  <si>
+    <t>50,65,50,85,85,90,85,60,50,75</t>
+  </si>
+  <si>
+    <t>50,75,50,65,50,85,55,75,55,65,55,85</t>
+  </si>
+  <si>
+    <t>55,75,90,90,90,60,55,85,55,65</t>
+  </si>
+  <si>
+    <t>55,85,55,65,90,80,60,75,60,90,60,60</t>
+  </si>
+  <si>
+    <t>65,90,65,80,90,70,65,70,65,60,70,75</t>
   </si>
 </sst>
 </file>
@@ -3031,7 +3229,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q1012"/>
+  <dimension ref="A1:Q1061"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -47007,7 +47205,7 @@
         <v>710101</v>
       </c>
       <c r="B831" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C831" s="60">
         <v>5000101</v>
@@ -47060,7 +47258,7 @@
         <v>710102</v>
       </c>
       <c r="B832" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C832" s="60">
         <v>5000101</v>
@@ -47113,7 +47311,7 @@
         <v>710103</v>
       </c>
       <c r="B833" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C833" s="60">
         <v>5000101</v>
@@ -47166,7 +47364,7 @@
         <v>710201</v>
       </c>
       <c r="B834" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C834" s="60">
         <v>5000101</v>
@@ -47219,7 +47417,7 @@
         <v>710202</v>
       </c>
       <c r="B835" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C835" s="60">
         <v>5000101</v>
@@ -47272,7 +47470,7 @@
         <v>710203</v>
       </c>
       <c r="B836" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C836" s="60">
         <v>5000101</v>
@@ -47325,7 +47523,7 @@
         <v>710301</v>
       </c>
       <c r="B837" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C837" s="60">
         <v>5000101</v>
@@ -47378,7 +47576,7 @@
         <v>710302</v>
       </c>
       <c r="B838" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C838" s="60">
         <v>5000101</v>
@@ -47431,7 +47629,7 @@
         <v>710303</v>
       </c>
       <c r="B839" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C839" s="60">
         <v>5000101</v>
@@ -47484,7 +47682,7 @@
         <v>710304</v>
       </c>
       <c r="B840" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C840" s="60">
         <v>5000101</v>
@@ -47537,7 +47735,7 @@
         <v>710401</v>
       </c>
       <c r="B841" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C841" s="60">
         <v>5000101</v>
@@ -47590,7 +47788,7 @@
         <v>710402</v>
       </c>
       <c r="B842" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C842" s="60">
         <v>5000101</v>
@@ -47643,7 +47841,7 @@
         <v>710403</v>
       </c>
       <c r="B843" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C843" s="60">
         <v>5000101</v>
@@ -47696,7 +47894,7 @@
         <v>710404</v>
       </c>
       <c r="B844" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C844" s="60">
         <v>7000101</v>
@@ -47749,7 +47947,7 @@
         <v>710501</v>
       </c>
       <c r="B845" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C845" s="60">
         <v>7000101</v>
@@ -47802,7 +48000,7 @@
         <v>710502</v>
       </c>
       <c r="B846" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C846" s="60">
         <v>7000101</v>
@@ -47855,7 +48053,7 @@
         <v>710503</v>
       </c>
       <c r="B847" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C847" s="60">
         <v>7000101</v>
@@ -47908,7 +48106,7 @@
         <v>710504</v>
       </c>
       <c r="B848" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C848" s="60">
         <v>7000101</v>
@@ -47961,7 +48159,7 @@
         <v>710505</v>
       </c>
       <c r="B849" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C849" s="60">
         <v>7000101</v>
@@ -48014,7 +48212,7 @@
         <v>710601</v>
       </c>
       <c r="B850" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C850" s="60">
         <v>7000101</v>
@@ -48067,7 +48265,7 @@
         <v>710602</v>
       </c>
       <c r="B851" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C851" s="60">
         <v>7000101</v>
@@ -48120,7 +48318,7 @@
         <v>710603</v>
       </c>
       <c r="B852" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C852" s="60">
         <v>7000101</v>
@@ -48173,7 +48371,7 @@
         <v>710604</v>
       </c>
       <c r="B853" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C853" s="60">
         <v>7000101</v>
@@ -48226,7 +48424,7 @@
         <v>710605</v>
       </c>
       <c r="B854" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C854" s="60">
         <v>7000101</v>
@@ -48279,7 +48477,7 @@
         <v>710606</v>
       </c>
       <c r="B855" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C855" s="60">
         <v>7000101</v>
@@ -48332,7 +48530,7 @@
         <v>710701</v>
       </c>
       <c r="B856" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C856" s="60">
         <v>7000101</v>
@@ -48385,7 +48583,7 @@
         <v>710702</v>
       </c>
       <c r="B857" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C857" s="60">
         <v>7000101</v>
@@ -48438,7 +48636,7 @@
         <v>710703</v>
       </c>
       <c r="B858" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C858" s="60">
         <v>7000101</v>
@@ -48491,7 +48689,7 @@
         <v>710704</v>
       </c>
       <c r="B859" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C859" s="60">
         <v>7000101</v>
@@ -48544,7 +48742,7 @@
         <v>710705</v>
       </c>
       <c r="B860" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C860" s="60">
         <v>7000101</v>
@@ -48597,7 +48795,7 @@
         <v>710706</v>
       </c>
       <c r="B861" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C861" s="60">
         <v>7000101</v>
@@ -48650,7 +48848,7 @@
         <v>710801</v>
       </c>
       <c r="B862" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C862" s="60">
         <v>7000101</v>
@@ -48703,7 +48901,7 @@
         <v>720101</v>
       </c>
       <c r="B863" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C863" s="60">
         <v>5000101</v>
@@ -48756,7 +48954,7 @@
         <v>720102</v>
       </c>
       <c r="B864" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C864" s="60">
         <v>5000101</v>
@@ -48809,7 +49007,7 @@
         <v>720103</v>
       </c>
       <c r="B865" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C865" s="60">
         <v>5000101</v>
@@ -48862,7 +49060,7 @@
         <v>720201</v>
       </c>
       <c r="B866" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C866" s="60">
         <v>5000101</v>
@@ -48915,7 +49113,7 @@
         <v>720202</v>
       </c>
       <c r="B867" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C867" s="60">
         <v>5000101</v>
@@ -48968,7 +49166,7 @@
         <v>720203</v>
       </c>
       <c r="B868" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C868" s="60">
         <v>5000101</v>
@@ -49021,7 +49219,7 @@
         <v>720204</v>
       </c>
       <c r="B869" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C869" s="60">
         <v>5000101</v>
@@ -49074,7 +49272,7 @@
         <v>720301</v>
       </c>
       <c r="B870" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C870" s="60">
         <v>5000101</v>
@@ -49127,7 +49325,7 @@
         <v>720302</v>
       </c>
       <c r="B871" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C871" s="60">
         <v>5000101</v>
@@ -49180,7 +49378,7 @@
         <v>720303</v>
       </c>
       <c r="B872" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C872" s="60">
         <v>5000101</v>
@@ -49233,7 +49431,7 @@
         <v>720304</v>
       </c>
       <c r="B873" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C873" s="60">
         <v>5000101</v>
@@ -49286,7 +49484,7 @@
         <v>720305</v>
       </c>
       <c r="B874" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C874" s="60">
         <v>5000101</v>
@@ -49339,7 +49537,7 @@
         <v>720401</v>
       </c>
       <c r="B875" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C875" s="60">
         <v>5000101</v>
@@ -49392,7 +49590,7 @@
         <v>720402</v>
       </c>
       <c r="B876" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C876" s="60">
         <v>7000101</v>
@@ -49445,7 +49643,7 @@
         <v>720403</v>
       </c>
       <c r="B877" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C877" s="60">
         <v>7000101</v>
@@ -49498,7 +49696,7 @@
         <v>720404</v>
       </c>
       <c r="B878" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C878" s="60">
         <v>7000101</v>
@@ -49551,7 +49749,7 @@
         <v>720405</v>
       </c>
       <c r="B879" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C879" s="60">
         <v>7000101</v>
@@ -49604,7 +49802,7 @@
         <v>720406</v>
       </c>
       <c r="B880" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C880" s="60">
         <v>7000101</v>
@@ -49657,7 +49855,7 @@
         <v>720501</v>
       </c>
       <c r="B881" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C881" s="60">
         <v>7000101</v>
@@ -49710,7 +49908,7 @@
         <v>720502</v>
       </c>
       <c r="B882" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C882" s="60">
         <v>7000101</v>
@@ -49763,7 +49961,7 @@
         <v>720503</v>
       </c>
       <c r="B883" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C883" s="60">
         <v>7000101</v>
@@ -49816,7 +50014,7 @@
         <v>720504</v>
       </c>
       <c r="B884" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C884" s="60">
         <v>7000101</v>
@@ -49869,7 +50067,7 @@
         <v>720505</v>
       </c>
       <c r="B885" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C885" s="60">
         <v>7000101</v>
@@ -49922,7 +50120,7 @@
         <v>720506</v>
       </c>
       <c r="B886" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C886" s="60">
         <v>7000101</v>
@@ -49975,7 +50173,7 @@
         <v>720507</v>
       </c>
       <c r="B887" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C887" s="60">
         <v>7000101</v>
@@ -50028,7 +50226,7 @@
         <v>720601</v>
       </c>
       <c r="B888" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C888" s="60">
         <v>7000101</v>
@@ -50081,7 +50279,7 @@
         <v>720602</v>
       </c>
       <c r="B889" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C889" s="60">
         <v>7000101</v>
@@ -50134,7 +50332,7 @@
         <v>720603</v>
       </c>
       <c r="B890" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C890" s="60">
         <v>7000101</v>
@@ -50187,7 +50385,7 @@
         <v>720604</v>
       </c>
       <c r="B891" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C891" s="60">
         <v>7000101</v>
@@ -50240,7 +50438,7 @@
         <v>720605</v>
       </c>
       <c r="B892" s="60">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C892" s="60">
         <v>7000101</v>
@@ -50292,8 +50490,8 @@
       <c r="A893" s="62">
         <v>720606</v>
       </c>
-      <c r="B893" s="62">
-        <v>7</v>
+      <c r="B893" s="60">
+        <v>8</v>
       </c>
       <c r="C893" s="62">
         <v>7000101</v>
@@ -50345,8 +50543,8 @@
       <c r="A894" s="62">
         <v>720607</v>
       </c>
-      <c r="B894" s="62">
-        <v>7</v>
+      <c r="B894" s="60">
+        <v>8</v>
       </c>
       <c r="C894" s="62">
         <v>7000101</v>
@@ -50398,8 +50596,8 @@
       <c r="A895" s="62">
         <v>720608</v>
       </c>
-      <c r="B895" s="62">
-        <v>7</v>
+      <c r="B895" s="60">
+        <v>8</v>
       </c>
       <c r="C895" s="62">
         <v>7000101</v>
@@ -50451,8 +50649,8 @@
       <c r="A896" s="62">
         <v>720701</v>
       </c>
-      <c r="B896" s="62">
-        <v>7</v>
+      <c r="B896" s="60">
+        <v>8</v>
       </c>
       <c r="C896" s="62">
         <v>7000101</v>
@@ -50504,8 +50702,8 @@
       <c r="A897" s="62">
         <v>720702</v>
       </c>
-      <c r="B897" s="62">
-        <v>7</v>
+      <c r="B897" s="60">
+        <v>8</v>
       </c>
       <c r="C897" s="62">
         <v>7000101</v>
@@ -50557,8 +50755,8 @@
       <c r="A898" s="62">
         <v>720703</v>
       </c>
-      <c r="B898" s="62">
-        <v>7</v>
+      <c r="B898" s="60">
+        <v>8</v>
       </c>
       <c r="C898" s="62">
         <v>7000101</v>
@@ -50610,8 +50808,8 @@
       <c r="A899" s="62">
         <v>720704</v>
       </c>
-      <c r="B899" s="62">
-        <v>7</v>
+      <c r="B899" s="60">
+        <v>8</v>
       </c>
       <c r="C899" s="62">
         <v>7000101</v>
@@ -50663,8 +50861,8 @@
       <c r="A900" s="62">
         <v>720705</v>
       </c>
-      <c r="B900" s="62">
-        <v>7</v>
+      <c r="B900" s="60">
+        <v>8</v>
       </c>
       <c r="C900" s="62">
         <v>7000101</v>
@@ -50716,8 +50914,8 @@
       <c r="A901" s="62">
         <v>720706</v>
       </c>
-      <c r="B901" s="62">
-        <v>7</v>
+      <c r="B901" s="60">
+        <v>8</v>
       </c>
       <c r="C901" s="62">
         <v>7000101</v>
@@ -50769,8 +50967,8 @@
       <c r="A902" s="62">
         <v>720707</v>
       </c>
-      <c r="B902" s="62">
-        <v>7</v>
+      <c r="B902" s="60">
+        <v>8</v>
       </c>
       <c r="C902" s="62">
         <v>8000101</v>
@@ -50822,8 +51020,8 @@
       <c r="A903" s="62">
         <v>730101</v>
       </c>
-      <c r="B903" s="62">
-        <v>7</v>
+      <c r="B903" s="60">
+        <v>8</v>
       </c>
       <c r="C903" s="62">
         <v>5000101</v>
@@ -50875,8 +51073,8 @@
       <c r="A904" s="62">
         <v>730102</v>
       </c>
-      <c r="B904" s="62">
-        <v>7</v>
+      <c r="B904" s="60">
+        <v>8</v>
       </c>
       <c r="C904" s="62">
         <v>5000101</v>
@@ -50928,8 +51126,8 @@
       <c r="A905" s="62">
         <v>730103</v>
       </c>
-      <c r="B905" s="62">
-        <v>7</v>
+      <c r="B905" s="60">
+        <v>8</v>
       </c>
       <c r="C905" s="62">
         <v>5000101</v>
@@ -50981,8 +51179,8 @@
       <c r="A906" s="62">
         <v>730201</v>
       </c>
-      <c r="B906" s="62">
-        <v>7</v>
+      <c r="B906" s="60">
+        <v>8</v>
       </c>
       <c r="C906" s="62">
         <v>5000101</v>
@@ -51034,8 +51232,8 @@
       <c r="A907" s="62">
         <v>730202</v>
       </c>
-      <c r="B907" s="62">
-        <v>7</v>
+      <c r="B907" s="60">
+        <v>8</v>
       </c>
       <c r="C907" s="62">
         <v>5000101</v>
@@ -51087,8 +51285,8 @@
       <c r="A908" s="62">
         <v>730203</v>
       </c>
-      <c r="B908" s="62">
-        <v>7</v>
+      <c r="B908" s="60">
+        <v>8</v>
       </c>
       <c r="C908" s="62">
         <v>5000101</v>
@@ -51140,8 +51338,8 @@
       <c r="A909" s="62">
         <v>730204</v>
       </c>
-      <c r="B909" s="62">
-        <v>7</v>
+      <c r="B909" s="60">
+        <v>8</v>
       </c>
       <c r="C909" s="62">
         <v>5000101</v>
@@ -51193,8 +51391,8 @@
       <c r="A910" s="62">
         <v>730301</v>
       </c>
-      <c r="B910" s="62">
-        <v>7</v>
+      <c r="B910" s="60">
+        <v>8</v>
       </c>
       <c r="C910" s="62">
         <v>5000101</v>
@@ -51246,8 +51444,8 @@
       <c r="A911" s="62">
         <v>730302</v>
       </c>
-      <c r="B911" s="62">
-        <v>7</v>
+      <c r="B911" s="60">
+        <v>8</v>
       </c>
       <c r="C911" s="62">
         <v>5000101</v>
@@ -51299,8 +51497,8 @@
       <c r="A912" s="62">
         <v>730303</v>
       </c>
-      <c r="B912" s="62">
-        <v>7</v>
+      <c r="B912" s="60">
+        <v>8</v>
       </c>
       <c r="C912" s="62">
         <v>5000101</v>
@@ -51352,8 +51550,8 @@
       <c r="A913" s="62">
         <v>730304</v>
       </c>
-      <c r="B913" s="62">
-        <v>7</v>
+      <c r="B913" s="60">
+        <v>8</v>
       </c>
       <c r="C913" s="62">
         <v>5000101</v>
@@ -51405,8 +51603,8 @@
       <c r="A914" s="62">
         <v>730305</v>
       </c>
-      <c r="B914" s="62">
-        <v>7</v>
+      <c r="B914" s="60">
+        <v>8</v>
       </c>
       <c r="C914" s="62">
         <v>5000101</v>
@@ -51458,8 +51656,8 @@
       <c r="A915" s="62">
         <v>730401</v>
       </c>
-      <c r="B915" s="62">
-        <v>7</v>
+      <c r="B915" s="60">
+        <v>8</v>
       </c>
       <c r="C915" s="62">
         <v>5000101</v>
@@ -51511,8 +51709,8 @@
       <c r="A916" s="62">
         <v>730402</v>
       </c>
-      <c r="B916" s="62">
-        <v>7</v>
+      <c r="B916" s="60">
+        <v>8</v>
       </c>
       <c r="C916" s="62">
         <v>7000101</v>
@@ -51564,8 +51762,8 @@
       <c r="A917" s="62">
         <v>730403</v>
       </c>
-      <c r="B917" s="62">
-        <v>7</v>
+      <c r="B917" s="60">
+        <v>8</v>
       </c>
       <c r="C917" s="62">
         <v>7000101</v>
@@ -51617,8 +51815,8 @@
       <c r="A918" s="62">
         <v>730404</v>
       </c>
-      <c r="B918" s="62">
-        <v>7</v>
+      <c r="B918" s="60">
+        <v>8</v>
       </c>
       <c r="C918" s="62">
         <v>7000101</v>
@@ -51670,8 +51868,8 @@
       <c r="A919" s="62">
         <v>730405</v>
       </c>
-      <c r="B919" s="62">
-        <v>7</v>
+      <c r="B919" s="60">
+        <v>8</v>
       </c>
       <c r="C919" s="62">
         <v>7000101</v>
@@ -51723,8 +51921,8 @@
       <c r="A920" s="62">
         <v>730406</v>
       </c>
-      <c r="B920" s="62">
-        <v>7</v>
+      <c r="B920" s="60">
+        <v>8</v>
       </c>
       <c r="C920" s="62">
         <v>7000101</v>
@@ -51776,8 +51974,8 @@
       <c r="A921" s="64">
         <v>730407</v>
       </c>
-      <c r="B921" s="64">
-        <v>7</v>
+      <c r="B921" s="60">
+        <v>8</v>
       </c>
       <c r="C921" s="64">
         <v>7000101</v>
@@ -51829,8 +52027,8 @@
       <c r="A922" s="62">
         <v>730501</v>
       </c>
-      <c r="B922" s="62">
-        <v>7</v>
+      <c r="B922" s="60">
+        <v>8</v>
       </c>
       <c r="C922" s="62">
         <v>7000101</v>
@@ -51882,8 +52080,8 @@
       <c r="A923" s="62">
         <v>730502</v>
       </c>
-      <c r="B923" s="62">
-        <v>7</v>
+      <c r="B923" s="60">
+        <v>8</v>
       </c>
       <c r="C923" s="62">
         <v>7000101</v>
@@ -51935,8 +52133,8 @@
       <c r="A924" s="62">
         <v>730503</v>
       </c>
-      <c r="B924" s="62">
-        <v>7</v>
+      <c r="B924" s="60">
+        <v>8</v>
       </c>
       <c r="C924" s="62">
         <v>7000101</v>
@@ -51988,8 +52186,8 @@
       <c r="A925" s="62">
         <v>730504</v>
       </c>
-      <c r="B925" s="62">
-        <v>7</v>
+      <c r="B925" s="60">
+        <v>8</v>
       </c>
       <c r="C925" s="62">
         <v>7000101</v>
@@ -52041,8 +52239,8 @@
       <c r="A926" s="62">
         <v>730505</v>
       </c>
-      <c r="B926" s="62">
-        <v>7</v>
+      <c r="B926" s="60">
+        <v>8</v>
       </c>
       <c r="C926" s="62">
         <v>7000101</v>
@@ -52094,8 +52292,8 @@
       <c r="A927" s="62">
         <v>730506</v>
       </c>
-      <c r="B927" s="62">
-        <v>7</v>
+      <c r="B927" s="60">
+        <v>8</v>
       </c>
       <c r="C927" s="62">
         <v>7000101</v>
@@ -52147,8 +52345,8 @@
       <c r="A928" s="65">
         <v>730507</v>
       </c>
-      <c r="B928" s="65">
-        <v>7</v>
+      <c r="B928" s="60">
+        <v>8</v>
       </c>
       <c r="C928" s="65">
         <v>7000101</v>
@@ -52200,8 +52398,8 @@
       <c r="A929" s="62">
         <v>730601</v>
       </c>
-      <c r="B929" s="62">
-        <v>7</v>
+      <c r="B929" s="60">
+        <v>8</v>
       </c>
       <c r="C929" s="62">
         <v>7000101</v>
@@ -52253,8 +52451,8 @@
       <c r="A930" s="62">
         <v>730602</v>
       </c>
-      <c r="B930" s="62">
-        <v>7</v>
+      <c r="B930" s="60">
+        <v>8</v>
       </c>
       <c r="C930" s="62">
         <v>7000101</v>
@@ -52306,8 +52504,8 @@
       <c r="A931" s="62">
         <v>730603</v>
       </c>
-      <c r="B931" s="62">
-        <v>7</v>
+      <c r="B931" s="60">
+        <v>8</v>
       </c>
       <c r="C931" s="62">
         <v>7000101</v>
@@ -52359,8 +52557,8 @@
       <c r="A932" s="62">
         <v>730604</v>
       </c>
-      <c r="B932" s="62">
-        <v>7</v>
+      <c r="B932" s="60">
+        <v>8</v>
       </c>
       <c r="C932" s="62">
         <v>7000101</v>
@@ -52412,8 +52610,8 @@
       <c r="A933" s="62">
         <v>730605</v>
       </c>
-      <c r="B933" s="62">
-        <v>7</v>
+      <c r="B933" s="60">
+        <v>8</v>
       </c>
       <c r="C933" s="62">
         <v>7000101</v>
@@ -52465,8 +52663,8 @@
       <c r="A934" s="62">
         <v>730606</v>
       </c>
-      <c r="B934" s="62">
-        <v>7</v>
+      <c r="B934" s="60">
+        <v>8</v>
       </c>
       <c r="C934" s="62">
         <v>7000101</v>
@@ -52518,8 +52716,8 @@
       <c r="A935" s="62">
         <v>730607</v>
       </c>
-      <c r="B935" s="62">
-        <v>7</v>
+      <c r="B935" s="60">
+        <v>8</v>
       </c>
       <c r="C935" s="62">
         <v>7000101</v>
@@ -52571,8 +52769,8 @@
       <c r="A936" s="62">
         <v>730608</v>
       </c>
-      <c r="B936" s="62">
-        <v>7</v>
+      <c r="B936" s="60">
+        <v>8</v>
       </c>
       <c r="C936" s="62">
         <v>7000101</v>
@@ -52624,8 +52822,8 @@
       <c r="A937" s="65">
         <v>730609</v>
       </c>
-      <c r="B937" s="65">
-        <v>7</v>
+      <c r="B937" s="60">
+        <v>8</v>
       </c>
       <c r="C937" s="65">
         <v>7000101</v>
@@ -52677,8 +52875,8 @@
       <c r="A938" s="62">
         <v>730701</v>
       </c>
-      <c r="B938" s="62">
-        <v>7</v>
+      <c r="B938" s="60">
+        <v>8</v>
       </c>
       <c r="C938" s="62">
         <v>7000101</v>
@@ -52730,8 +52928,8 @@
       <c r="A939" s="62">
         <v>730702</v>
       </c>
-      <c r="B939" s="62">
-        <v>7</v>
+      <c r="B939" s="60">
+        <v>8</v>
       </c>
       <c r="C939" s="62">
         <v>7000101</v>
@@ -52783,8 +52981,8 @@
       <c r="A940" s="62">
         <v>730703</v>
       </c>
-      <c r="B940" s="62">
-        <v>7</v>
+      <c r="B940" s="60">
+        <v>8</v>
       </c>
       <c r="C940" s="62">
         <v>7000101</v>
@@ -52836,8 +53034,8 @@
       <c r="A941" s="62">
         <v>730704</v>
       </c>
-      <c r="B941" s="62">
-        <v>7</v>
+      <c r="B941" s="60">
+        <v>8</v>
       </c>
       <c r="C941" s="62">
         <v>7000101</v>
@@ -52889,8 +53087,8 @@
       <c r="A942" s="62">
         <v>730705</v>
       </c>
-      <c r="B942" s="62">
-        <v>7</v>
+      <c r="B942" s="60">
+        <v>8</v>
       </c>
       <c r="C942" s="62">
         <v>7000101</v>
@@ -52942,8 +53140,8 @@
       <c r="A943" s="62">
         <v>730706</v>
       </c>
-      <c r="B943" s="62">
-        <v>7</v>
+      <c r="B943" s="60">
+        <v>8</v>
       </c>
       <c r="C943" s="62">
         <v>8000101</v>
@@ -52995,8 +53193,8 @@
       <c r="A944" s="62">
         <v>730707</v>
       </c>
-      <c r="B944" s="62">
-        <v>7</v>
+      <c r="B944" s="60">
+        <v>8</v>
       </c>
       <c r="C944" s="62">
         <v>8000101</v>
@@ -53048,8 +53246,8 @@
       <c r="A945" s="62">
         <v>730708</v>
       </c>
-      <c r="B945" s="62">
-        <v>7</v>
+      <c r="B945" s="60">
+        <v>8</v>
       </c>
       <c r="C945" s="62">
         <v>8000101</v>
@@ -53101,8 +53299,8 @@
       <c r="A946" s="62">
         <v>730709</v>
       </c>
-      <c r="B946" s="62">
-        <v>7</v>
+      <c r="B946" s="60">
+        <v>8</v>
       </c>
       <c r="C946" s="62">
         <v>8000101</v>
@@ -53154,8 +53352,8 @@
       <c r="A947" s="65">
         <v>730710</v>
       </c>
-      <c r="B947" s="65">
-        <v>7</v>
+      <c r="B947" s="60">
+        <v>8</v>
       </c>
       <c r="C947" s="65">
         <v>5000101</v>
@@ -53207,8 +53405,8 @@
       <c r="A948" s="62">
         <v>730801</v>
       </c>
-      <c r="B948" s="62">
-        <v>7</v>
+      <c r="B948" s="60">
+        <v>8</v>
       </c>
       <c r="C948" s="62">
         <v>5000101</v>
@@ -53260,8 +53458,8 @@
       <c r="A949" s="62">
         <v>730802</v>
       </c>
-      <c r="B949" s="62">
-        <v>7</v>
+      <c r="B949" s="60">
+        <v>8</v>
       </c>
       <c r="C949" s="62">
         <v>5000101</v>
@@ -53313,8 +53511,8 @@
       <c r="A950" s="62">
         <v>730803</v>
       </c>
-      <c r="B950" s="62">
-        <v>7</v>
+      <c r="B950" s="60">
+        <v>8</v>
       </c>
       <c r="C950" s="62">
         <v>5000101</v>
@@ -53366,8 +53564,8 @@
       <c r="A951" s="62">
         <v>730804</v>
       </c>
-      <c r="B951" s="62">
-        <v>7</v>
+      <c r="B951" s="60">
+        <v>8</v>
       </c>
       <c r="C951" s="62">
         <v>5000101</v>
@@ -53419,8 +53617,8 @@
       <c r="A952" s="62">
         <v>730805</v>
       </c>
-      <c r="B952" s="62">
-        <v>7</v>
+      <c r="B952" s="60">
+        <v>8</v>
       </c>
       <c r="C952" s="62">
         <v>5000101</v>
@@ -53472,8 +53670,8 @@
       <c r="A953" s="62">
         <v>740101</v>
       </c>
-      <c r="B953" s="62">
-        <v>7</v>
+      <c r="B953" s="60">
+        <v>8</v>
       </c>
       <c r="C953" s="62">
         <v>5000101</v>
@@ -53525,8 +53723,8 @@
       <c r="A954" s="62">
         <v>740102</v>
       </c>
-      <c r="B954" s="62">
-        <v>7</v>
+      <c r="B954" s="60">
+        <v>8</v>
       </c>
       <c r="C954" s="62">
         <v>5000101</v>
@@ -53578,8 +53776,8 @@
       <c r="A955" s="66">
         <v>740103</v>
       </c>
-      <c r="B955" s="66">
-        <v>7</v>
+      <c r="B955" s="60">
+        <v>8</v>
       </c>
       <c r="C955" s="66">
         <v>5000101</v>
@@ -53631,8 +53829,8 @@
       <c r="A956" s="62">
         <v>740201</v>
       </c>
-      <c r="B956" s="62">
-        <v>7</v>
+      <c r="B956" s="60">
+        <v>8</v>
       </c>
       <c r="C956" s="62">
         <v>5000101</v>
@@ -53684,8 +53882,8 @@
       <c r="A957" s="62">
         <v>740202</v>
       </c>
-      <c r="B957" s="62">
-        <v>7</v>
+      <c r="B957" s="60">
+        <v>8</v>
       </c>
       <c r="C957" s="62">
         <v>5000101</v>
@@ -53737,8 +53935,8 @@
       <c r="A958" s="62">
         <v>740203</v>
       </c>
-      <c r="B958" s="62">
-        <v>7</v>
+      <c r="B958" s="60">
+        <v>8</v>
       </c>
       <c r="C958" s="62">
         <v>5000101</v>
@@ -53790,8 +53988,8 @@
       <c r="A959" s="65">
         <v>740204</v>
       </c>
-      <c r="B959" s="65">
-        <v>7</v>
+      <c r="B959" s="60">
+        <v>8</v>
       </c>
       <c r="C959" s="65">
         <v>5000101</v>
@@ -53843,8 +54041,8 @@
       <c r="A960" s="62">
         <v>740301</v>
       </c>
-      <c r="B960" s="62">
-        <v>7</v>
+      <c r="B960" s="60">
+        <v>8</v>
       </c>
       <c r="C960" s="62">
         <v>5000101</v>
@@ -53896,8 +54094,8 @@
       <c r="A961" s="62">
         <v>740302</v>
       </c>
-      <c r="B961" s="62">
-        <v>7</v>
+      <c r="B961" s="60">
+        <v>8</v>
       </c>
       <c r="C961" s="62">
         <v>5000101</v>
@@ -53949,8 +54147,8 @@
       <c r="A962" s="62">
         <v>740303</v>
       </c>
-      <c r="B962" s="62">
-        <v>7</v>
+      <c r="B962" s="60">
+        <v>8</v>
       </c>
       <c r="C962" s="62">
         <v>5000101</v>
@@ -54002,8 +54200,8 @@
       <c r="A963" s="62">
         <v>740304</v>
       </c>
-      <c r="B963" s="62">
-        <v>7</v>
+      <c r="B963" s="60">
+        <v>8</v>
       </c>
       <c r="C963" s="62">
         <v>5000101</v>
@@ -54055,8 +54253,8 @@
       <c r="A964" s="65">
         <v>740305</v>
       </c>
-      <c r="B964" s="65">
-        <v>7</v>
+      <c r="B964" s="60">
+        <v>8</v>
       </c>
       <c r="C964" s="65">
         <v>5000101</v>
@@ -54108,8 +54306,8 @@
       <c r="A965" s="62">
         <v>740401</v>
       </c>
-      <c r="B965" s="62">
-        <v>7</v>
+      <c r="B965" s="60">
+        <v>8</v>
       </c>
       <c r="C965" s="62">
         <v>7000101</v>
@@ -54161,8 +54359,8 @@
       <c r="A966" s="62">
         <v>740402</v>
       </c>
-      <c r="B966" s="62">
-        <v>7</v>
+      <c r="B966" s="60">
+        <v>8</v>
       </c>
       <c r="C966" s="62">
         <v>7000101</v>
@@ -54214,8 +54412,8 @@
       <c r="A967" s="62">
         <v>740403</v>
       </c>
-      <c r="B967" s="62">
-        <v>7</v>
+      <c r="B967" s="60">
+        <v>8</v>
       </c>
       <c r="C967" s="62">
         <v>7000101</v>
@@ -54267,8 +54465,8 @@
       <c r="A968" s="62">
         <v>740404</v>
       </c>
-      <c r="B968" s="62">
-        <v>7</v>
+      <c r="B968" s="60">
+        <v>8</v>
       </c>
       <c r="C968" s="62">
         <v>7000101</v>
@@ -54320,8 +54518,8 @@
       <c r="A969" s="62">
         <v>740405</v>
       </c>
-      <c r="B969" s="62">
-        <v>7</v>
+      <c r="B969" s="60">
+        <v>8</v>
       </c>
       <c r="C969" s="62">
         <v>7000101</v>
@@ -54373,8 +54571,8 @@
       <c r="A970" s="62">
         <v>740406</v>
       </c>
-      <c r="B970" s="62">
-        <v>7</v>
+      <c r="B970" s="60">
+        <v>8</v>
       </c>
       <c r="C970" s="62">
         <v>7000101</v>
@@ -54426,8 +54624,8 @@
       <c r="A971" s="64">
         <v>740407</v>
       </c>
-      <c r="B971" s="64">
-        <v>7</v>
+      <c r="B971" s="60">
+        <v>8</v>
       </c>
       <c r="C971" s="64">
         <v>7000101</v>
@@ -54479,8 +54677,8 @@
       <c r="A972" s="62">
         <v>740501</v>
       </c>
-      <c r="B972" s="62">
-        <v>7</v>
+      <c r="B972" s="60">
+        <v>8</v>
       </c>
       <c r="C972" s="62">
         <v>7000101</v>
@@ -54532,8 +54730,8 @@
       <c r="A973" s="62">
         <v>740502</v>
       </c>
-      <c r="B973" s="62">
-        <v>7</v>
+      <c r="B973" s="60">
+        <v>8</v>
       </c>
       <c r="C973" s="62">
         <v>7000101</v>
@@ -54585,8 +54783,8 @@
       <c r="A974" s="62">
         <v>740503</v>
       </c>
-      <c r="B974" s="62">
-        <v>7</v>
+      <c r="B974" s="60">
+        <v>8</v>
       </c>
       <c r="C974" s="62">
         <v>7000101</v>
@@ -54638,8 +54836,8 @@
       <c r="A975" s="62">
         <v>740504</v>
       </c>
-      <c r="B975" s="62">
-        <v>7</v>
+      <c r="B975" s="60">
+        <v>8</v>
       </c>
       <c r="C975" s="62">
         <v>7000101</v>
@@ -54691,8 +54889,8 @@
       <c r="A976" s="62">
         <v>740505</v>
       </c>
-      <c r="B976" s="62">
-        <v>7</v>
+      <c r="B976" s="60">
+        <v>8</v>
       </c>
       <c r="C976" s="62">
         <v>7000101</v>
@@ -54744,8 +54942,8 @@
       <c r="A977" s="62">
         <v>740506</v>
       </c>
-      <c r="B977" s="62">
-        <v>7</v>
+      <c r="B977" s="60">
+        <v>8</v>
       </c>
       <c r="C977" s="62">
         <v>7000101</v>
@@ -54797,8 +54995,8 @@
       <c r="A978" s="62">
         <v>740507</v>
       </c>
-      <c r="B978" s="62">
-        <v>7</v>
+      <c r="B978" s="60">
+        <v>8</v>
       </c>
       <c r="C978" s="62">
         <v>7000101</v>
@@ -54850,8 +55048,8 @@
       <c r="A979" s="62">
         <v>740508</v>
       </c>
-      <c r="B979" s="62">
-        <v>7</v>
+      <c r="B979" s="60">
+        <v>8</v>
       </c>
       <c r="C979" s="62">
         <v>7000101</v>
@@ -54903,8 +55101,8 @@
       <c r="A980" s="65">
         <v>740509</v>
       </c>
-      <c r="B980" s="65">
-        <v>7</v>
+      <c r="B980" s="60">
+        <v>8</v>
       </c>
       <c r="C980" s="65">
         <v>7000101</v>
@@ -54956,8 +55154,8 @@
       <c r="A981" s="62">
         <v>740601</v>
       </c>
-      <c r="B981" s="62">
-        <v>7</v>
+      <c r="B981" s="60">
+        <v>8</v>
       </c>
       <c r="C981" s="62">
         <v>7000101</v>
@@ -55009,8 +55207,8 @@
       <c r="A982" s="62">
         <v>740602</v>
       </c>
-      <c r="B982" s="62">
-        <v>7</v>
+      <c r="B982" s="60">
+        <v>8</v>
       </c>
       <c r="C982" s="62">
         <v>7000101</v>
@@ -55062,8 +55260,8 @@
       <c r="A983" s="62">
         <v>740603</v>
       </c>
-      <c r="B983" s="62">
-        <v>7</v>
+      <c r="B983" s="60">
+        <v>8</v>
       </c>
       <c r="C983" s="62">
         <v>7000101</v>
@@ -55115,8 +55313,8 @@
       <c r="A984" s="62">
         <v>740604</v>
       </c>
-      <c r="B984" s="62">
-        <v>7</v>
+      <c r="B984" s="60">
+        <v>8</v>
       </c>
       <c r="C984" s="62">
         <v>7000101</v>
@@ -55168,8 +55366,8 @@
       <c r="A985" s="62">
         <v>740605</v>
       </c>
-      <c r="B985" s="62">
-        <v>7</v>
+      <c r="B985" s="60">
+        <v>8</v>
       </c>
       <c r="C985" s="62">
         <v>7000101</v>
@@ -55221,8 +55419,8 @@
       <c r="A986" s="62">
         <v>740606</v>
       </c>
-      <c r="B986" s="62">
-        <v>7</v>
+      <c r="B986" s="60">
+        <v>8</v>
       </c>
       <c r="C986" s="62">
         <v>7000101</v>
@@ -55274,8 +55472,8 @@
       <c r="A987" s="62">
         <v>740607</v>
       </c>
-      <c r="B987" s="62">
-        <v>7</v>
+      <c r="B987" s="60">
+        <v>8</v>
       </c>
       <c r="C987" s="62">
         <v>7000101</v>
@@ -55327,8 +55525,8 @@
       <c r="A988" s="62">
         <v>740608</v>
       </c>
-      <c r="B988" s="62">
-        <v>7</v>
+      <c r="B988" s="60">
+        <v>8</v>
       </c>
       <c r="C988" s="62">
         <v>7000101</v>
@@ -55380,8 +55578,8 @@
       <c r="A989" s="62">
         <v>740609</v>
       </c>
-      <c r="B989" s="62">
-        <v>7</v>
+      <c r="B989" s="60">
+        <v>8</v>
       </c>
       <c r="C989" s="62">
         <v>7000101</v>
@@ -55433,8 +55631,8 @@
       <c r="A990" s="65">
         <v>740610</v>
       </c>
-      <c r="B990" s="65">
-        <v>7</v>
+      <c r="B990" s="60">
+        <v>8</v>
       </c>
       <c r="C990" s="65">
         <v>7000101</v>
@@ -55486,8 +55684,8 @@
       <c r="A991" s="62">
         <v>740701</v>
       </c>
-      <c r="B991" s="62">
-        <v>7</v>
+      <c r="B991" s="60">
+        <v>8</v>
       </c>
       <c r="C991" s="62">
         <v>7000101</v>
@@ -55539,8 +55737,8 @@
       <c r="A992" s="62">
         <v>740702</v>
       </c>
-      <c r="B992" s="62">
-        <v>7</v>
+      <c r="B992" s="60">
+        <v>8</v>
       </c>
       <c r="C992" s="62">
         <v>7000101</v>
@@ -55592,8 +55790,8 @@
       <c r="A993" s="62">
         <v>740703</v>
       </c>
-      <c r="B993" s="62">
-        <v>7</v>
+      <c r="B993" s="60">
+        <v>8</v>
       </c>
       <c r="C993" s="62">
         <v>7000101</v>
@@ -55645,8 +55843,8 @@
       <c r="A994" s="62">
         <v>740704</v>
       </c>
-      <c r="B994" s="62">
-        <v>7</v>
+      <c r="B994" s="60">
+        <v>8</v>
       </c>
       <c r="C994" s="62">
         <v>7000101</v>
@@ -55698,8 +55896,8 @@
       <c r="A995" s="62">
         <v>740705</v>
       </c>
-      <c r="B995" s="62">
-        <v>7</v>
+      <c r="B995" s="60">
+        <v>8</v>
       </c>
       <c r="C995" s="62">
         <v>7000101</v>
@@ -55751,8 +55949,8 @@
       <c r="A996" s="62">
         <v>740706</v>
       </c>
-      <c r="B996" s="62">
-        <v>7</v>
+      <c r="B996" s="60">
+        <v>8</v>
       </c>
       <c r="C996" s="62">
         <v>7000101</v>
@@ -55804,8 +56002,8 @@
       <c r="A997" s="62">
         <v>740707</v>
       </c>
-      <c r="B997" s="62">
-        <v>7</v>
+      <c r="B997" s="60">
+        <v>8</v>
       </c>
       <c r="C997" s="62">
         <v>7000101</v>
@@ -55857,8 +56055,8 @@
       <c r="A998" s="62">
         <v>740708</v>
       </c>
-      <c r="B998" s="62">
-        <v>7</v>
+      <c r="B998" s="60">
+        <v>8</v>
       </c>
       <c r="C998" s="62">
         <v>8000101</v>
@@ -55910,8 +56108,8 @@
       <c r="A999" s="62">
         <v>740709</v>
       </c>
-      <c r="B999" s="62">
-        <v>7</v>
+      <c r="B999" s="60">
+        <v>8</v>
       </c>
       <c r="C999" s="62">
         <v>8000101</v>
@@ -55963,8 +56161,8 @@
       <c r="A1000" s="62">
         <v>740710</v>
       </c>
-      <c r="B1000" s="62">
-        <v>7</v>
+      <c r="B1000" s="60">
+        <v>8</v>
       </c>
       <c r="C1000" s="62">
         <v>8000101</v>
@@ -56016,8 +56214,8 @@
       <c r="A1001" s="62">
         <v>740711</v>
       </c>
-      <c r="B1001" s="62">
-        <v>7</v>
+      <c r="B1001" s="60">
+        <v>8</v>
       </c>
       <c r="C1001" s="62">
         <v>8000101</v>
@@ -56069,8 +56267,8 @@
       <c r="A1002" s="65">
         <v>740712</v>
       </c>
-      <c r="B1002" s="65">
-        <v>7</v>
+      <c r="B1002" s="60">
+        <v>8</v>
       </c>
       <c r="C1002" s="65">
         <v>5000101</v>
@@ -56122,8 +56320,8 @@
       <c r="A1003" s="62">
         <v>740801</v>
       </c>
-      <c r="B1003" s="62">
-        <v>7</v>
+      <c r="B1003" s="60">
+        <v>8</v>
       </c>
       <c r="C1003" s="62">
         <v>5000101</v>
@@ -56175,8 +56373,8 @@
       <c r="A1004" s="62">
         <v>740802</v>
       </c>
-      <c r="B1004" s="62">
-        <v>7</v>
+      <c r="B1004" s="60">
+        <v>8</v>
       </c>
       <c r="C1004" s="62">
         <v>5000101</v>
@@ -56228,8 +56426,8 @@
       <c r="A1005" s="62">
         <v>740803</v>
       </c>
-      <c r="B1005" s="62">
-        <v>7</v>
+      <c r="B1005" s="60">
+        <v>8</v>
       </c>
       <c r="C1005" s="62">
         <v>5000101</v>
@@ -56281,8 +56479,8 @@
       <c r="A1006" s="62">
         <v>740804</v>
       </c>
-      <c r="B1006" s="62">
-        <v>7</v>
+      <c r="B1006" s="60">
+        <v>8</v>
       </c>
       <c r="C1006" s="62">
         <v>5000101</v>
@@ -56334,8 +56532,8 @@
       <c r="A1007" s="62">
         <v>740805</v>
       </c>
-      <c r="B1007" s="62">
-        <v>7</v>
+      <c r="B1007" s="60">
+        <v>8</v>
       </c>
       <c r="C1007" s="62">
         <v>5000101</v>
@@ -56387,8 +56585,8 @@
       <c r="A1008" s="62">
         <v>740806</v>
       </c>
-      <c r="B1008" s="62">
-        <v>7</v>
+      <c r="B1008" s="60">
+        <v>8</v>
       </c>
       <c r="C1008" s="62">
         <v>5000101</v>
@@ -56440,8 +56638,8 @@
       <c r="A1009" s="62">
         <v>740807</v>
       </c>
-      <c r="B1009" s="62">
-        <v>7</v>
+      <c r="B1009" s="60">
+        <v>8</v>
       </c>
       <c r="C1009" s="62">
         <v>5000101</v>
@@ -56493,8 +56691,8 @@
       <c r="A1010" s="62">
         <v>740808</v>
       </c>
-      <c r="B1010" s="62">
-        <v>7</v>
+      <c r="B1010" s="60">
+        <v>8</v>
       </c>
       <c r="C1010" s="62">
         <v>5000101</v>
@@ -56546,8 +56744,8 @@
       <c r="A1011" s="62">
         <v>740809</v>
       </c>
-      <c r="B1011" s="62">
-        <v>7</v>
+      <c r="B1011" s="60">
+        <v>8</v>
       </c>
       <c r="C1011" s="62">
         <v>5000101</v>
@@ -56599,8 +56797,8 @@
       <c r="A1012" s="62">
         <v>740810</v>
       </c>
-      <c r="B1012" s="62">
-        <v>7</v>
+      <c r="B1012" s="60">
+        <v>8</v>
       </c>
       <c r="C1012" s="62">
         <v>5000101</v>
@@ -56645,6 +56843,2603 @@
         <v>0</v>
       </c>
       <c r="Q1012" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1013" s="1">
+        <v>770101</v>
+      </c>
+      <c r="B1013" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1013" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1013" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1013" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1013" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1013" s="1">
+        <v>1</v>
+      </c>
+      <c r="H1013" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1013" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1013" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="K1013" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1013" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1013" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1013" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1013" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="P1013" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1013" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1014" s="1">
+        <v>770102</v>
+      </c>
+      <c r="B1014" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1014" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1014" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1014" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1014" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1014" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1014" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1014" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1014" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K1014" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1014" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1014" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1014" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1014" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="P1014" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1014" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1015" s="1">
+        <v>770103</v>
+      </c>
+      <c r="B1015" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1015" s="1">
+        <v>1</v>
+      </c>
+      <c r="D1015" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1015" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1015" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1015" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1015" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I1015" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1015" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="K1015" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1015" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1015" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1015" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1015" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="P1015" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1015" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1016" s="1">
+        <v>770201</v>
+      </c>
+      <c r="B1016" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1016" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1016" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1016" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1016" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1016" s="1">
+        <v>4</v>
+      </c>
+      <c r="H1016" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1016" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1016" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="K1016" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1016" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1016" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1016" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1016" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="P1016" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1016" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1017" s="1">
+        <v>770202</v>
+      </c>
+      <c r="B1017" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1017" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1017" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1017" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1017" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1017" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1017" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1017" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1017" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K1017" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1017" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1017" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1017" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1017" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="P1017" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1017" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1018" s="1">
+        <v>770203</v>
+      </c>
+      <c r="B1018" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1018" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1018" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1018" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1018" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1018" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1018" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I1018" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1018" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K1018" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1018" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1018" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1018" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1018" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="P1018" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1018" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1019" s="1">
+        <v>770301</v>
+      </c>
+      <c r="B1019" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1019" s="1">
+        <v>3</v>
+      </c>
+      <c r="D1019" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1019" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1019" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1019" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1019" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I1019" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1019" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="K1019" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1019" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1019" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1019" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1019" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="P1019" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1019" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1020" s="1">
+        <v>770302</v>
+      </c>
+      <c r="B1020" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1020" s="1">
+        <v>3</v>
+      </c>
+      <c r="D1020" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1020" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1020" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1020" s="1">
+        <v>8</v>
+      </c>
+      <c r="H1020" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1020" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1020" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="K1020" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1020" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1020" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1020" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1020" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="P1020" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1020" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1021" s="1">
+        <v>770303</v>
+      </c>
+      <c r="B1021" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1021" s="1">
+        <v>3</v>
+      </c>
+      <c r="D1021" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1021" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1021" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1021" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1021" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I1021" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1021" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="K1021" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1021" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1021" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1021" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1021" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="P1021" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1021" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1022" s="1">
+        <v>770304</v>
+      </c>
+      <c r="B1022" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1022" s="1">
+        <v>3</v>
+      </c>
+      <c r="D1022" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1022" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1022" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1022" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1022" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I1022" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1022" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="K1022" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1022" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1022" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1022" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1022" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="P1022" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1022" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1023" s="1">
+        <v>770401</v>
+      </c>
+      <c r="B1023" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1023" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1023" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1023" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1023" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1023" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1023" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I1023" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1023" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="K1023" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1023" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1023" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1023" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1023" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="P1023" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1023" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1024" s="1">
+        <v>770402</v>
+      </c>
+      <c r="B1024" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1024" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1024" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1024" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1024" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1024" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1024" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1024" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1024" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="K1024" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1024" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1024" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1024" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1024" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="P1024" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1024" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1025" s="1">
+        <v>770403</v>
+      </c>
+      <c r="B1025" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1025" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1025" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1025" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1025" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1025" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1025" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1025" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1025" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="K1025" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1025" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1025" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1025" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1025" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="P1025" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1025" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1026" s="1">
+        <v>770404</v>
+      </c>
+      <c r="B1026" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1026" s="1">
+        <v>4</v>
+      </c>
+      <c r="D1026" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1026" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1026" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1026" s="1">
+        <v>14</v>
+      </c>
+      <c r="H1026" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I1026" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1026" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K1026" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1026" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1026" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1026" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1026" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="P1026" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1026" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1027" s="1">
+        <v>770501</v>
+      </c>
+      <c r="B1027" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1027" s="1">
+        <v>5</v>
+      </c>
+      <c r="D1027" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1027" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1027" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1027" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1027" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1027" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1027" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="K1027" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1027" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1027" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1027" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1027" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="P1027" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1027" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1028" s="1">
+        <v>770502</v>
+      </c>
+      <c r="B1028" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1028" s="1">
+        <v>5</v>
+      </c>
+      <c r="D1028" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1028" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1028" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1028" s="1">
+        <v>16</v>
+      </c>
+      <c r="H1028" s="1">
+        <v>4500</v>
+      </c>
+      <c r="I1028" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1028" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="K1028" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1028" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1028" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1028" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1028" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="P1028" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1028" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1029" s="1">
+        <v>770503</v>
+      </c>
+      <c r="B1029" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1029" s="1">
+        <v>5</v>
+      </c>
+      <c r="D1029" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1029" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1029" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1029" s="1">
+        <v>17</v>
+      </c>
+      <c r="H1029" s="1">
+        <v>4500</v>
+      </c>
+      <c r="I1029" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1029" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="K1029" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1029" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1029" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1029" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1029" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="P1029" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1029" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1030" s="1">
+        <v>770504</v>
+      </c>
+      <c r="B1030" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1030" s="1">
+        <v>5</v>
+      </c>
+      <c r="D1030" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1030" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1030" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1030" s="1">
+        <v>18</v>
+      </c>
+      <c r="H1030" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I1030" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1030" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="K1030" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1030" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1030" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1030" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1030" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="P1030" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1030" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1031" s="1">
+        <v>770601</v>
+      </c>
+      <c r="B1031" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1031" s="1">
+        <v>6</v>
+      </c>
+      <c r="D1031" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1031" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1031" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1031" s="1">
+        <v>19</v>
+      </c>
+      <c r="H1031" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1031" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1031" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="K1031" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1031" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1031" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1031" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1031" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="P1031" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1031" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1032" s="1">
+        <v>770602</v>
+      </c>
+      <c r="B1032" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1032" s="1">
+        <v>6</v>
+      </c>
+      <c r="D1032" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1032" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1032" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1032" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1032" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1032" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1032" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K1032" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1032" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1032" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1032" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1032" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="P1032" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1032" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1033" s="1">
+        <v>770603</v>
+      </c>
+      <c r="B1033" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1033" s="1">
+        <v>6</v>
+      </c>
+      <c r="D1033" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1033" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1033" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1033" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1033" s="1">
+        <v>4500</v>
+      </c>
+      <c r="I1033" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1033" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="K1033" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1033" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1033" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1033" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1033" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="P1033" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1033" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1034" s="1">
+        <v>770604</v>
+      </c>
+      <c r="B1034" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1034" s="1">
+        <v>6</v>
+      </c>
+      <c r="D1034" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1034" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1034" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1034" s="1">
+        <v>22</v>
+      </c>
+      <c r="H1034" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1034" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1034" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="K1034" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1034" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1034" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1034" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1034" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="P1034" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1034" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1035" s="1">
+        <v>770605</v>
+      </c>
+      <c r="B1035" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1035" s="1">
+        <v>6</v>
+      </c>
+      <c r="D1035" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1035" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1035" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1035" s="1">
+        <v>23</v>
+      </c>
+      <c r="H1035" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1035" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1035" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="K1035" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1035" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1035" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1035" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1035" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="P1035" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1035" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1036" s="1">
+        <v>770701</v>
+      </c>
+      <c r="B1036" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1036" s="1">
+        <v>7</v>
+      </c>
+      <c r="D1036" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1036" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1036" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1036" s="1">
+        <v>24</v>
+      </c>
+      <c r="H1036" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1036" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1036" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="K1036" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1036" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1036" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1036" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1036" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="P1036" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1036" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1037" s="1">
+        <v>770702</v>
+      </c>
+      <c r="B1037" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1037" s="1">
+        <v>7</v>
+      </c>
+      <c r="D1037" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1037" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1037" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1037" s="1">
+        <v>25</v>
+      </c>
+      <c r="H1037" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1037" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1037" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="K1037" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1037" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1037" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1037" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1037" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="P1037" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1037" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1038" s="1">
+        <v>770703</v>
+      </c>
+      <c r="B1038" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1038" s="1">
+        <v>7</v>
+      </c>
+      <c r="D1038" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1038" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1038" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1038" s="1">
+        <v>26</v>
+      </c>
+      <c r="H1038" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1038" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1038" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="K1038" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1038" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1038" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1038" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1038" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="P1038" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1038" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1039" s="1">
+        <v>770704</v>
+      </c>
+      <c r="B1039" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1039" s="1">
+        <v>7</v>
+      </c>
+      <c r="D1039" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1039" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1039" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1039" s="1">
+        <v>27</v>
+      </c>
+      <c r="H1039" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1039" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1039" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="K1039" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1039" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1039" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1039" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1039" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="P1039" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1039" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1040" s="1">
+        <v>770705</v>
+      </c>
+      <c r="B1040" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1040" s="1">
+        <v>7</v>
+      </c>
+      <c r="D1040" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1040" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1040" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1040" s="1">
+        <v>28</v>
+      </c>
+      <c r="H1040" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1040" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1040" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="K1040" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1040" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1040" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1040" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1040" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="P1040" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1040" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1041" s="1">
+        <v>770801</v>
+      </c>
+      <c r="B1041" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1041" s="1">
+        <v>8</v>
+      </c>
+      <c r="D1041" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1041" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1041" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1041" s="1">
+        <v>29</v>
+      </c>
+      <c r="H1041" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1041" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1041" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="K1041" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1041" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1041" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1041" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1041" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="P1041" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1041" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1042" s="1">
+        <v>770802</v>
+      </c>
+      <c r="B1042" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1042" s="1">
+        <v>8</v>
+      </c>
+      <c r="D1042" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1042" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1042" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1042" s="1">
+        <v>30</v>
+      </c>
+      <c r="H1042" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1042" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1042" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="K1042" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1042" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1042" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1042" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1042" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="P1042" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1042" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1043" s="1">
+        <v>770803</v>
+      </c>
+      <c r="B1043" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1043" s="1">
+        <v>8</v>
+      </c>
+      <c r="D1043" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1043" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1043" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1043" s="1">
+        <v>31</v>
+      </c>
+      <c r="H1043" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1043" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1043" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="K1043" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1043" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1043" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1043" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1043" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="P1043" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1043" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1044" s="1">
+        <v>770804</v>
+      </c>
+      <c r="B1044" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1044" s="1">
+        <v>8</v>
+      </c>
+      <c r="D1044" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1044" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1044" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1044" s="1">
+        <v>32</v>
+      </c>
+      <c r="H1044" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1044" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1044" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="K1044" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1044" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1044" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1044" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1044" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="P1044" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1044" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1045" s="1">
+        <v>770805</v>
+      </c>
+      <c r="B1045" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1045" s="1">
+        <v>8</v>
+      </c>
+      <c r="D1045" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1045" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1045" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1045" s="1">
+        <v>33</v>
+      </c>
+      <c r="H1045" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1045" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1045" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="K1045" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1045" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1045" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1045" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1045" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="P1045" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1045" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1046" s="1">
+        <v>770806</v>
+      </c>
+      <c r="B1046" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1046" s="1">
+        <v>8</v>
+      </c>
+      <c r="D1046" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1046" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1046" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1046" s="1">
+        <v>34</v>
+      </c>
+      <c r="H1046" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1046" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1046" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="K1046" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1046" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1046" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1046" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1046" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="P1046" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1046" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1047" s="1">
+        <v>770901</v>
+      </c>
+      <c r="B1047" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1047" s="1">
+        <v>9</v>
+      </c>
+      <c r="D1047" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1047" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1047" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1047" s="1">
+        <v>35</v>
+      </c>
+      <c r="H1047" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1047" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1047" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="K1047" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1047" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1047" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1047" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1047" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="P1047" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1047" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1048" s="1">
+        <v>770902</v>
+      </c>
+      <c r="B1048" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1048" s="1">
+        <v>9</v>
+      </c>
+      <c r="D1048" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1048" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1048" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1048" s="1">
+        <v>36</v>
+      </c>
+      <c r="H1048" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1048" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1048" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="K1048" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1048" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1048" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1048" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1048" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="P1048" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1048" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1049" s="1">
+        <v>770903</v>
+      </c>
+      <c r="B1049" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1049" s="1">
+        <v>9</v>
+      </c>
+      <c r="D1049" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1049" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1049" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1049" s="1">
+        <v>37</v>
+      </c>
+      <c r="H1049" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1049" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1049" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="K1049" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1049" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1049" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1049" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1049" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="P1049" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1049" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1050" s="1">
+        <v>770904</v>
+      </c>
+      <c r="B1050" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1050" s="1">
+        <v>9</v>
+      </c>
+      <c r="D1050" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1050" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1050" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1050" s="1">
+        <v>38</v>
+      </c>
+      <c r="H1050" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1050" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1050" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="K1050" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1050" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1050" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1050" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1050" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="P1050" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1050" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1051" s="1">
+        <v>770905</v>
+      </c>
+      <c r="B1051" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1051" s="1">
+        <v>9</v>
+      </c>
+      <c r="D1051" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1051" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1051" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1051" s="1">
+        <v>39</v>
+      </c>
+      <c r="H1051" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1051" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1051" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="K1051" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1051" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1051" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1051" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1051" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="P1051" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1051" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1052" s="1">
+        <v>770906</v>
+      </c>
+      <c r="B1052" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1052" s="1">
+        <v>9</v>
+      </c>
+      <c r="D1052" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1052" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1052" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1052" s="1">
+        <v>40</v>
+      </c>
+      <c r="H1052" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1052" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1052" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="K1052" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1052" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1052" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1052" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1052" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="P1052" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1052" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1053" s="1">
+        <v>770907</v>
+      </c>
+      <c r="B1053" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1053" s="1">
+        <v>9</v>
+      </c>
+      <c r="D1053" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1053" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1053" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1053" s="1">
+        <v>41</v>
+      </c>
+      <c r="H1053" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1053" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1053" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="K1053" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1053" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1053" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1053" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1053" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="P1053" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1053" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1054" s="1">
+        <v>771001</v>
+      </c>
+      <c r="B1054" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1054" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1054" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1054" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1054" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1054" s="1">
+        <v>42</v>
+      </c>
+      <c r="H1054" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1054" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1054" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="K1054" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1054" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1054" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1054" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1054" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="P1054" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1054" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1055" s="1">
+        <v>771002</v>
+      </c>
+      <c r="B1055" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1055" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1055" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1055" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1055" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1055" s="1">
+        <v>43</v>
+      </c>
+      <c r="H1055" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1055" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1055" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="K1055" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1055" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1055" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1055" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1055" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="P1055" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1055" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1056" s="1">
+        <v>771003</v>
+      </c>
+      <c r="B1056" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1056" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1056" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1056" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1056" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1056" s="1">
+        <v>44</v>
+      </c>
+      <c r="H1056" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1056" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1056" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="K1056" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1056" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1056" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1056" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1056" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="P1056" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1056" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1057" s="1">
+        <v>771004</v>
+      </c>
+      <c r="B1057" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1057" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1057" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1057" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1057" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1057" s="1">
+        <v>45</v>
+      </c>
+      <c r="H1057" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1057" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1057" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="K1057" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1057" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1057" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1057" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1057" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="P1057" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1057" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1058" s="1">
+        <v>771005</v>
+      </c>
+      <c r="B1058" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1058" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1058" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1058" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1058" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1058" s="1">
+        <v>46</v>
+      </c>
+      <c r="H1058" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1058" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1058" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="K1058" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1058" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1058" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1058" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1058" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="P1058" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1058" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1059" s="1">
+        <v>771006</v>
+      </c>
+      <c r="B1059" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1059" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1059" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1059" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1059" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1059" s="1">
+        <v>47</v>
+      </c>
+      <c r="H1059" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1059" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1059" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="K1059" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1059" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1059" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1059" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1059" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="P1059" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1059" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1060" s="1">
+        <v>771007</v>
+      </c>
+      <c r="B1060" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1060" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1060" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1060" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1060" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1060" s="1">
+        <v>48</v>
+      </c>
+      <c r="H1060" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1060" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1060" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="K1060" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1060" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1060" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1060" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1060" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="P1060" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1060" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1061" s="1">
+        <v>771008</v>
+      </c>
+      <c r="B1061" s="1">
+        <v>7</v>
+      </c>
+      <c r="C1061" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1061" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1061" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1061" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1061" s="1">
+        <v>49</v>
+      </c>
+      <c r="H1061" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1061" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1061" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="K1061" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1061" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1061" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1061" s="1">
+        <v>2</v>
+      </c>
+      <c r="O1061" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="P1061" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1061" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A201FDF-6869-43C9-A9B0-21CA8366C80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340029A4-9CE5-4194-B0BE-5A2716775A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47214,7 +47214,7 @@
         <v>1</v>
       </c>
       <c r="E831" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F831" s="60">
         <v>1</v>
@@ -47267,7 +47267,7 @@
         <v>1</v>
       </c>
       <c r="E832" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F832" s="60">
         <v>1</v>
@@ -47320,7 +47320,7 @@
         <v>1</v>
       </c>
       <c r="E833" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F833" s="60">
         <v>1</v>
@@ -47373,7 +47373,7 @@
         <v>1</v>
       </c>
       <c r="E834" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F834" s="60">
         <v>1</v>
@@ -47426,7 +47426,7 @@
         <v>1</v>
       </c>
       <c r="E835" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F835" s="60">
         <v>1</v>
@@ -47479,7 +47479,7 @@
         <v>1</v>
       </c>
       <c r="E836" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F836" s="60">
         <v>1</v>
@@ -47532,7 +47532,7 @@
         <v>1</v>
       </c>
       <c r="E837" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F837" s="60">
         <v>1</v>
@@ -47585,7 +47585,7 @@
         <v>1</v>
       </c>
       <c r="E838" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F838" s="60">
         <v>1</v>
@@ -47638,7 +47638,7 @@
         <v>1</v>
       </c>
       <c r="E839" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F839" s="60">
         <v>1</v>
@@ -47691,7 +47691,7 @@
         <v>1</v>
       </c>
       <c r="E840" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F840" s="60">
         <v>1</v>
@@ -47744,7 +47744,7 @@
         <v>1</v>
       </c>
       <c r="E841" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F841" s="60">
         <v>1</v>
@@ -47797,7 +47797,7 @@
         <v>1</v>
       </c>
       <c r="E842" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F842" s="60">
         <v>1</v>
@@ -47850,7 +47850,7 @@
         <v>1</v>
       </c>
       <c r="E843" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F843" s="60">
         <v>1</v>
@@ -47903,7 +47903,7 @@
         <v>1</v>
       </c>
       <c r="E844" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F844" s="60">
         <v>1</v>
@@ -47956,7 +47956,7 @@
         <v>1</v>
       </c>
       <c r="E845" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F845" s="60">
         <v>1</v>
@@ -48009,7 +48009,7 @@
         <v>1</v>
       </c>
       <c r="E846" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F846" s="60">
         <v>1</v>
@@ -48062,7 +48062,7 @@
         <v>1</v>
       </c>
       <c r="E847" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F847" s="60">
         <v>1</v>
@@ -48115,7 +48115,7 @@
         <v>1</v>
       </c>
       <c r="E848" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F848" s="60">
         <v>1</v>
@@ -48168,7 +48168,7 @@
         <v>1</v>
       </c>
       <c r="E849" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F849" s="60">
         <v>1</v>
@@ -48221,7 +48221,7 @@
         <v>1</v>
       </c>
       <c r="E850" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F850" s="60">
         <v>1</v>
@@ -48274,7 +48274,7 @@
         <v>1</v>
       </c>
       <c r="E851" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F851" s="60">
         <v>1</v>
@@ -48327,7 +48327,7 @@
         <v>1</v>
       </c>
       <c r="E852" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F852" s="60">
         <v>1</v>
@@ -48380,7 +48380,7 @@
         <v>1</v>
       </c>
       <c r="E853" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F853" s="60">
         <v>1</v>
@@ -48433,7 +48433,7 @@
         <v>1</v>
       </c>
       <c r="E854" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F854" s="60">
         <v>1</v>
@@ -48486,7 +48486,7 @@
         <v>1</v>
       </c>
       <c r="E855" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F855" s="60">
         <v>1</v>
@@ -48539,7 +48539,7 @@
         <v>1</v>
       </c>
       <c r="E856" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F856" s="60">
         <v>1</v>
@@ -48592,7 +48592,7 @@
         <v>1</v>
       </c>
       <c r="E857" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F857" s="60">
         <v>1</v>
@@ -48645,7 +48645,7 @@
         <v>1</v>
       </c>
       <c r="E858" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F858" s="60">
         <v>1</v>
@@ -48698,7 +48698,7 @@
         <v>1</v>
       </c>
       <c r="E859" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F859" s="60">
         <v>1</v>
@@ -48751,7 +48751,7 @@
         <v>1</v>
       </c>
       <c r="E860" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F860" s="60">
         <v>1</v>
@@ -48804,7 +48804,7 @@
         <v>1</v>
       </c>
       <c r="E861" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F861" s="60">
         <v>1</v>
@@ -48857,7 +48857,7 @@
         <v>1</v>
       </c>
       <c r="E862" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F862" s="60">
         <v>1</v>
@@ -48910,7 +48910,7 @@
         <v>2</v>
       </c>
       <c r="E863" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F863" s="60">
         <v>1</v>
@@ -48963,7 +48963,7 @@
         <v>2</v>
       </c>
       <c r="E864" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F864" s="60">
         <v>1</v>
@@ -49016,7 +49016,7 @@
         <v>2</v>
       </c>
       <c r="E865" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F865" s="60">
         <v>1</v>
@@ -49069,7 +49069,7 @@
         <v>2</v>
       </c>
       <c r="E866" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F866" s="60">
         <v>1</v>
@@ -49122,7 +49122,7 @@
         <v>2</v>
       </c>
       <c r="E867" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F867" s="60">
         <v>1</v>
@@ -49175,7 +49175,7 @@
         <v>2</v>
       </c>
       <c r="E868" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F868" s="60">
         <v>1</v>
@@ -49228,7 +49228,7 @@
         <v>2</v>
       </c>
       <c r="E869" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F869" s="60">
         <v>1</v>
@@ -49281,7 +49281,7 @@
         <v>2</v>
       </c>
       <c r="E870" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F870" s="60">
         <v>1</v>
@@ -49334,7 +49334,7 @@
         <v>2</v>
       </c>
       <c r="E871" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F871" s="60">
         <v>1</v>
@@ -49387,7 +49387,7 @@
         <v>2</v>
       </c>
       <c r="E872" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F872" s="60">
         <v>1</v>
@@ -49440,7 +49440,7 @@
         <v>2</v>
       </c>
       <c r="E873" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F873" s="60">
         <v>1</v>
@@ -49493,7 +49493,7 @@
         <v>2</v>
       </c>
       <c r="E874" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F874" s="60">
         <v>1</v>
@@ -49546,7 +49546,7 @@
         <v>2</v>
       </c>
       <c r="E875" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F875" s="60">
         <v>1</v>
@@ -49599,7 +49599,7 @@
         <v>2</v>
       </c>
       <c r="E876" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F876" s="60">
         <v>1</v>
@@ -49652,7 +49652,7 @@
         <v>2</v>
       </c>
       <c r="E877" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F877" s="60">
         <v>1</v>
@@ -49705,7 +49705,7 @@
         <v>2</v>
       </c>
       <c r="E878" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F878" s="60">
         <v>1</v>
@@ -49758,7 +49758,7 @@
         <v>2</v>
       </c>
       <c r="E879" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F879" s="60">
         <v>1</v>
@@ -49811,7 +49811,7 @@
         <v>2</v>
       </c>
       <c r="E880" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F880" s="60">
         <v>1</v>
@@ -49864,7 +49864,7 @@
         <v>2</v>
       </c>
       <c r="E881" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F881" s="60">
         <v>1</v>
@@ -49917,7 +49917,7 @@
         <v>2</v>
       </c>
       <c r="E882" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F882" s="60">
         <v>1</v>
@@ -49970,7 +49970,7 @@
         <v>2</v>
       </c>
       <c r="E883" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F883" s="60">
         <v>1</v>
@@ -50023,7 +50023,7 @@
         <v>2</v>
       </c>
       <c r="E884" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F884" s="60">
         <v>1</v>
@@ -50076,7 +50076,7 @@
         <v>2</v>
       </c>
       <c r="E885" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F885" s="60">
         <v>1</v>
@@ -50129,7 +50129,7 @@
         <v>2</v>
       </c>
       <c r="E886" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F886" s="60">
         <v>1</v>
@@ -50182,7 +50182,7 @@
         <v>2</v>
       </c>
       <c r="E887" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F887" s="60">
         <v>1</v>
@@ -50235,7 +50235,7 @@
         <v>2</v>
       </c>
       <c r="E888" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F888" s="60">
         <v>1</v>
@@ -50288,7 +50288,7 @@
         <v>2</v>
       </c>
       <c r="E889" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F889" s="60">
         <v>1</v>
@@ -50341,7 +50341,7 @@
         <v>2</v>
       </c>
       <c r="E890" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F890" s="60">
         <v>1</v>
@@ -50394,7 +50394,7 @@
         <v>2</v>
       </c>
       <c r="E891" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F891" s="60">
         <v>1</v>
@@ -50447,7 +50447,7 @@
         <v>2</v>
       </c>
       <c r="E892" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F892" s="60">
         <v>1</v>
@@ -50500,7 +50500,7 @@
         <v>2</v>
       </c>
       <c r="E893" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F893" s="62">
         <v>1</v>
@@ -50553,7 +50553,7 @@
         <v>2</v>
       </c>
       <c r="E894" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F894" s="62">
         <v>1</v>
@@ -50606,7 +50606,7 @@
         <v>2</v>
       </c>
       <c r="E895" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F895" s="62">
         <v>1</v>
@@ -50659,7 +50659,7 @@
         <v>2</v>
       </c>
       <c r="E896" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F896" s="62">
         <v>1</v>
@@ -50712,7 +50712,7 @@
         <v>2</v>
       </c>
       <c r="E897" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F897" s="62">
         <v>1</v>
@@ -50765,7 +50765,7 @@
         <v>2</v>
       </c>
       <c r="E898" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F898" s="62">
         <v>1</v>
@@ -50818,7 +50818,7 @@
         <v>2</v>
       </c>
       <c r="E899" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F899" s="62">
         <v>1</v>
@@ -50871,7 +50871,7 @@
         <v>2</v>
       </c>
       <c r="E900" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F900" s="62">
         <v>1</v>
@@ -50924,7 +50924,7 @@
         <v>2</v>
       </c>
       <c r="E901" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F901" s="62">
         <v>1</v>
@@ -50977,7 +50977,7 @@
         <v>2</v>
       </c>
       <c r="E902" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F902" s="62">
         <v>1</v>
@@ -51030,7 +51030,7 @@
         <v>3</v>
       </c>
       <c r="E903" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F903" s="62">
         <v>1</v>
@@ -51083,7 +51083,7 @@
         <v>3</v>
       </c>
       <c r="E904" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F904" s="62">
         <v>1</v>
@@ -51136,7 +51136,7 @@
         <v>3</v>
       </c>
       <c r="E905" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F905" s="62">
         <v>1</v>
@@ -51189,7 +51189,7 @@
         <v>3</v>
       </c>
       <c r="E906" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F906" s="62">
         <v>1</v>
@@ -51242,7 +51242,7 @@
         <v>3</v>
       </c>
       <c r="E907" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F907" s="62">
         <v>1</v>
@@ -51295,7 +51295,7 @@
         <v>3</v>
       </c>
       <c r="E908" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F908" s="62">
         <v>1</v>
@@ -51348,7 +51348,7 @@
         <v>3</v>
       </c>
       <c r="E909" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F909" s="62">
         <v>1</v>
@@ -51401,7 +51401,7 @@
         <v>3</v>
       </c>
       <c r="E910" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F910" s="62">
         <v>1</v>
@@ -51454,7 +51454,7 @@
         <v>3</v>
       </c>
       <c r="E911" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F911" s="62">
         <v>1</v>
@@ -51507,7 +51507,7 @@
         <v>3</v>
       </c>
       <c r="E912" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F912" s="62">
         <v>1</v>
@@ -51560,7 +51560,7 @@
         <v>3</v>
       </c>
       <c r="E913" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F913" s="62">
         <v>1</v>
@@ -51613,7 +51613,7 @@
         <v>3</v>
       </c>
       <c r="E914" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F914" s="62">
         <v>1</v>
@@ -51666,7 +51666,7 @@
         <v>3</v>
       </c>
       <c r="E915" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F915" s="62">
         <v>1</v>
@@ -51719,7 +51719,7 @@
         <v>3</v>
       </c>
       <c r="E916" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F916" s="62">
         <v>1</v>
@@ -51772,7 +51772,7 @@
         <v>3</v>
       </c>
       <c r="E917" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F917" s="62">
         <v>1</v>
@@ -51825,7 +51825,7 @@
         <v>3</v>
       </c>
       <c r="E918" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F918" s="62">
         <v>1</v>
@@ -51878,7 +51878,7 @@
         <v>3</v>
       </c>
       <c r="E919" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F919" s="62">
         <v>1</v>
@@ -51931,7 +51931,7 @@
         <v>3</v>
       </c>
       <c r="E920" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F920" s="62">
         <v>1</v>
@@ -51984,7 +51984,7 @@
         <v>3</v>
       </c>
       <c r="E921" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F921" s="64">
         <v>1</v>
@@ -52037,7 +52037,7 @@
         <v>3</v>
       </c>
       <c r="E922" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F922" s="62">
         <v>1</v>
@@ -52090,7 +52090,7 @@
         <v>3</v>
       </c>
       <c r="E923" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F923" s="62">
         <v>1</v>
@@ -52143,7 +52143,7 @@
         <v>3</v>
       </c>
       <c r="E924" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F924" s="62">
         <v>1</v>
@@ -52196,7 +52196,7 @@
         <v>3</v>
       </c>
       <c r="E925" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F925" s="62">
         <v>1</v>
@@ -52249,7 +52249,7 @@
         <v>3</v>
       </c>
       <c r="E926" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F926" s="62">
         <v>1</v>
@@ -52302,7 +52302,7 @@
         <v>3</v>
       </c>
       <c r="E927" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F927" s="62">
         <v>1</v>
@@ -52355,7 +52355,7 @@
         <v>3</v>
       </c>
       <c r="E928" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F928" s="65">
         <v>1</v>
@@ -52408,7 +52408,7 @@
         <v>3</v>
       </c>
       <c r="E929" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F929" s="62">
         <v>1</v>
@@ -52461,7 +52461,7 @@
         <v>3</v>
       </c>
       <c r="E930" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F930" s="62">
         <v>1</v>
@@ -52514,7 +52514,7 @@
         <v>3</v>
       </c>
       <c r="E931" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F931" s="62">
         <v>1</v>
@@ -52567,7 +52567,7 @@
         <v>3</v>
       </c>
       <c r="E932" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F932" s="62">
         <v>1</v>
@@ -52620,7 +52620,7 @@
         <v>3</v>
       </c>
       <c r="E933" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F933" s="62">
         <v>1</v>
@@ -52673,7 +52673,7 @@
         <v>3</v>
       </c>
       <c r="E934" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F934" s="62">
         <v>1</v>
@@ -52726,7 +52726,7 @@
         <v>3</v>
       </c>
       <c r="E935" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F935" s="62">
         <v>1</v>
@@ -52779,7 +52779,7 @@
         <v>3</v>
       </c>
       <c r="E936" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F936" s="62">
         <v>1</v>
@@ -52832,7 +52832,7 @@
         <v>3</v>
       </c>
       <c r="E937" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F937" s="65">
         <v>1</v>
@@ -52885,7 +52885,7 @@
         <v>3</v>
       </c>
       <c r="E938" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F938" s="62">
         <v>1</v>
@@ -52938,7 +52938,7 @@
         <v>3</v>
       </c>
       <c r="E939" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F939" s="62">
         <v>1</v>
@@ -52991,7 +52991,7 @@
         <v>3</v>
       </c>
       <c r="E940" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F940" s="62">
         <v>1</v>
@@ -53044,7 +53044,7 @@
         <v>3</v>
       </c>
       <c r="E941" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F941" s="62">
         <v>1</v>
@@ -53097,7 +53097,7 @@
         <v>3</v>
       </c>
       <c r="E942" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F942" s="62">
         <v>1</v>
@@ -53150,7 +53150,7 @@
         <v>3</v>
       </c>
       <c r="E943" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F943" s="62">
         <v>1</v>
@@ -53203,7 +53203,7 @@
         <v>3</v>
       </c>
       <c r="E944" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F944" s="62">
         <v>1</v>
@@ -53256,7 +53256,7 @@
         <v>3</v>
       </c>
       <c r="E945" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F945" s="62">
         <v>1</v>
@@ -53309,7 +53309,7 @@
         <v>3</v>
       </c>
       <c r="E946" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F946" s="62">
         <v>1</v>
@@ -53362,7 +53362,7 @@
         <v>3</v>
       </c>
       <c r="E947" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F947" s="65">
         <v>1</v>
@@ -53415,7 +53415,7 @@
         <v>3</v>
       </c>
       <c r="E948" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F948" s="62">
         <v>1</v>
@@ -53468,7 +53468,7 @@
         <v>3</v>
       </c>
       <c r="E949" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F949" s="62">
         <v>1</v>
@@ -53521,7 +53521,7 @@
         <v>3</v>
       </c>
       <c r="E950" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F950" s="62">
         <v>1</v>
@@ -53574,7 +53574,7 @@
         <v>3</v>
       </c>
       <c r="E951" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F951" s="62">
         <v>1</v>
@@ -53627,7 +53627,7 @@
         <v>3</v>
       </c>
       <c r="E952" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F952" s="62">
         <v>1</v>
@@ -53680,7 +53680,7 @@
         <v>4</v>
       </c>
       <c r="E953" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F953" s="62">
         <v>1</v>
@@ -53733,7 +53733,7 @@
         <v>4</v>
       </c>
       <c r="E954" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F954" s="62">
         <v>1</v>
@@ -53786,7 +53786,7 @@
         <v>4</v>
       </c>
       <c r="E955" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F955" s="66">
         <v>1</v>
@@ -53839,7 +53839,7 @@
         <v>4</v>
       </c>
       <c r="E956" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F956" s="62">
         <v>1</v>
@@ -53892,7 +53892,7 @@
         <v>4</v>
       </c>
       <c r="E957" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F957" s="62">
         <v>1</v>
@@ -53945,7 +53945,7 @@
         <v>4</v>
       </c>
       <c r="E958" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F958" s="62">
         <v>1</v>
@@ -53998,7 +53998,7 @@
         <v>4</v>
       </c>
       <c r="E959" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F959" s="65">
         <v>1</v>
@@ -54051,7 +54051,7 @@
         <v>4</v>
       </c>
       <c r="E960" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F960" s="62">
         <v>1</v>
@@ -54104,7 +54104,7 @@
         <v>4</v>
       </c>
       <c r="E961" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F961" s="62">
         <v>1</v>
@@ -54157,7 +54157,7 @@
         <v>4</v>
       </c>
       <c r="E962" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F962" s="62">
         <v>1</v>
@@ -54210,7 +54210,7 @@
         <v>4</v>
       </c>
       <c r="E963" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F963" s="62">
         <v>1</v>
@@ -54263,7 +54263,7 @@
         <v>4</v>
       </c>
       <c r="E964" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F964" s="65">
         <v>1</v>
@@ -54316,7 +54316,7 @@
         <v>4</v>
       </c>
       <c r="E965" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F965" s="62">
         <v>1</v>
@@ -54369,7 +54369,7 @@
         <v>4</v>
       </c>
       <c r="E966" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F966" s="62">
         <v>1</v>
@@ -54422,7 +54422,7 @@
         <v>4</v>
       </c>
       <c r="E967" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F967" s="62">
         <v>1</v>
@@ -54475,7 +54475,7 @@
         <v>4</v>
       </c>
       <c r="E968" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F968" s="62">
         <v>1</v>
@@ -54528,7 +54528,7 @@
         <v>4</v>
       </c>
       <c r="E969" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F969" s="62">
         <v>1</v>
@@ -54581,7 +54581,7 @@
         <v>4</v>
       </c>
       <c r="E970" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F970" s="62">
         <v>1</v>
@@ -54634,7 +54634,7 @@
         <v>4</v>
       </c>
       <c r="E971" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F971" s="64">
         <v>1</v>
@@ -54687,7 +54687,7 @@
         <v>4</v>
       </c>
       <c r="E972" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F972" s="62">
         <v>1</v>
@@ -54740,7 +54740,7 @@
         <v>4</v>
       </c>
       <c r="E973" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F973" s="62">
         <v>1</v>
@@ -54793,7 +54793,7 @@
         <v>4</v>
       </c>
       <c r="E974" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F974" s="62">
         <v>1</v>
@@ -54846,7 +54846,7 @@
         <v>4</v>
       </c>
       <c r="E975" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F975" s="62">
         <v>1</v>
@@ -54899,7 +54899,7 @@
         <v>4</v>
       </c>
       <c r="E976" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F976" s="62">
         <v>1</v>
@@ -54952,7 +54952,7 @@
         <v>4</v>
       </c>
       <c r="E977" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F977" s="62">
         <v>1</v>
@@ -55005,7 +55005,7 @@
         <v>4</v>
       </c>
       <c r="E978" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F978" s="62">
         <v>1</v>
@@ -55058,7 +55058,7 @@
         <v>4</v>
       </c>
       <c r="E979" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F979" s="62">
         <v>1</v>
@@ -55111,7 +55111,7 @@
         <v>4</v>
       </c>
       <c r="E980" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F980" s="65">
         <v>1</v>
@@ -55164,7 +55164,7 @@
         <v>4</v>
       </c>
       <c r="E981" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F981" s="62">
         <v>1</v>
@@ -55217,7 +55217,7 @@
         <v>4</v>
       </c>
       <c r="E982" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F982" s="62">
         <v>1</v>
@@ -55270,7 +55270,7 @@
         <v>4</v>
       </c>
       <c r="E983" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F983" s="62">
         <v>1</v>
@@ -55323,7 +55323,7 @@
         <v>4</v>
       </c>
       <c r="E984" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F984" s="62">
         <v>1</v>
@@ -55376,7 +55376,7 @@
         <v>4</v>
       </c>
       <c r="E985" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F985" s="62">
         <v>1</v>
@@ -55429,7 +55429,7 @@
         <v>4</v>
       </c>
       <c r="E986" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F986" s="62">
         <v>1</v>
@@ -55482,7 +55482,7 @@
         <v>4</v>
       </c>
       <c r="E987" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F987" s="62">
         <v>1</v>
@@ -55535,7 +55535,7 @@
         <v>4</v>
       </c>
       <c r="E988" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F988" s="62">
         <v>1</v>
@@ -55588,7 +55588,7 @@
         <v>4</v>
       </c>
       <c r="E989" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F989" s="62">
         <v>1</v>
@@ -55641,7 +55641,7 @@
         <v>4</v>
       </c>
       <c r="E990" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F990" s="65">
         <v>1</v>
@@ -55694,7 +55694,7 @@
         <v>4</v>
       </c>
       <c r="E991" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F991" s="62">
         <v>1</v>
@@ -55747,7 +55747,7 @@
         <v>4</v>
       </c>
       <c r="E992" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F992" s="62">
         <v>1</v>
@@ -55800,7 +55800,7 @@
         <v>4</v>
       </c>
       <c r="E993" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F993" s="62">
         <v>1</v>
@@ -55853,7 +55853,7 @@
         <v>4</v>
       </c>
       <c r="E994" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F994" s="62">
         <v>1</v>
@@ -55906,7 +55906,7 @@
         <v>4</v>
       </c>
       <c r="E995" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F995" s="62">
         <v>1</v>
@@ -55959,7 +55959,7 @@
         <v>4</v>
       </c>
       <c r="E996" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F996" s="62">
         <v>1</v>
@@ -56012,7 +56012,7 @@
         <v>4</v>
       </c>
       <c r="E997" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F997" s="62">
         <v>1</v>
@@ -56065,7 +56065,7 @@
         <v>4</v>
       </c>
       <c r="E998" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F998" s="62">
         <v>1</v>
@@ -56118,7 +56118,7 @@
         <v>4</v>
       </c>
       <c r="E999" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F999" s="62">
         <v>1</v>
@@ -56171,7 +56171,7 @@
         <v>4</v>
       </c>
       <c r="E1000" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1000" s="62">
         <v>1</v>
@@ -56224,7 +56224,7 @@
         <v>4</v>
       </c>
       <c r="E1001" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1001" s="62">
         <v>1</v>
@@ -56277,7 +56277,7 @@
         <v>4</v>
       </c>
       <c r="E1002" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1002" s="65">
         <v>1</v>
@@ -56330,7 +56330,7 @@
         <v>4</v>
       </c>
       <c r="E1003" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1003" s="62">
         <v>1</v>
@@ -56383,7 +56383,7 @@
         <v>4</v>
       </c>
       <c r="E1004" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1004" s="62">
         <v>1</v>
@@ -56436,7 +56436,7 @@
         <v>4</v>
       </c>
       <c r="E1005" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1005" s="62">
         <v>1</v>
@@ -56489,7 +56489,7 @@
         <v>4</v>
       </c>
       <c r="E1006" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1006" s="62">
         <v>1</v>
@@ -56542,7 +56542,7 @@
         <v>4</v>
       </c>
       <c r="E1007" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1007" s="62">
         <v>1</v>
@@ -56595,7 +56595,7 @@
         <v>4</v>
       </c>
       <c r="E1008" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1008" s="62">
         <v>1</v>
@@ -56648,7 +56648,7 @@
         <v>4</v>
       </c>
       <c r="E1009" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1009" s="62">
         <v>1</v>
@@ -56701,7 +56701,7 @@
         <v>4</v>
       </c>
       <c r="E1010" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1010" s="62">
         <v>1</v>
@@ -56754,7 +56754,7 @@
         <v>4</v>
       </c>
       <c r="E1011" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1011" s="62">
         <v>1</v>
@@ -56807,7 +56807,7 @@
         <v>4</v>
       </c>
       <c r="E1012" s="60">
-        <v>70001</v>
+        <v>80001</v>
       </c>
       <c r="F1012" s="62">
         <v>1</v>
@@ -56887,7 +56887,7 @@
         <v>0</v>
       </c>
       <c r="N1013" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1013" s="1" t="s">
         <v>717</v>
@@ -56940,7 +56940,7 @@
         <v>0</v>
       </c>
       <c r="N1014" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1014" s="1" t="s">
         <v>718</v>
@@ -56993,7 +56993,7 @@
         <v>0</v>
       </c>
       <c r="N1015" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1015" s="1" t="s">
         <v>719</v>
@@ -57046,7 +57046,7 @@
         <v>0</v>
       </c>
       <c r="N1016" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1016" s="1" t="s">
         <v>720</v>
@@ -57099,7 +57099,7 @@
         <v>0</v>
       </c>
       <c r="N1017" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1017" s="1" t="s">
         <v>721</v>
@@ -57152,7 +57152,7 @@
         <v>0</v>
       </c>
       <c r="N1018" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1018" s="1" t="s">
         <v>722</v>
@@ -57205,7 +57205,7 @@
         <v>0</v>
       </c>
       <c r="N1019" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1019" s="1" t="s">
         <v>723</v>
@@ -57258,7 +57258,7 @@
         <v>0</v>
       </c>
       <c r="N1020" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1020" s="1" t="s">
         <v>724</v>
@@ -57311,7 +57311,7 @@
         <v>0</v>
       </c>
       <c r="N1021" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1021" s="1" t="s">
         <v>725</v>
@@ -57364,7 +57364,7 @@
         <v>0</v>
       </c>
       <c r="N1022" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1022" s="1" t="s">
         <v>726</v>
@@ -57417,7 +57417,7 @@
         <v>0</v>
       </c>
       <c r="N1023" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1023" s="1" t="s">
         <v>727</v>
@@ -57470,7 +57470,7 @@
         <v>0</v>
       </c>
       <c r="N1024" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1024" s="1" t="s">
         <v>728</v>
@@ -57523,7 +57523,7 @@
         <v>0</v>
       </c>
       <c r="N1025" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1025" s="1" t="s">
         <v>721</v>
@@ -57576,7 +57576,7 @@
         <v>0</v>
       </c>
       <c r="N1026" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1026" s="1" t="s">
         <v>729</v>
@@ -57629,7 +57629,7 @@
         <v>0</v>
       </c>
       <c r="N1027" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1027" s="1" t="s">
         <v>730</v>
@@ -57682,7 +57682,7 @@
         <v>0</v>
       </c>
       <c r="N1028" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1028" s="1" t="s">
         <v>724</v>
@@ -57735,7 +57735,7 @@
         <v>0</v>
       </c>
       <c r="N1029" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1029" s="1" t="s">
         <v>731</v>
@@ -57788,7 +57788,7 @@
         <v>0</v>
       </c>
       <c r="N1030" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1030" s="1" t="s">
         <v>732</v>
@@ -57841,7 +57841,7 @@
         <v>0</v>
       </c>
       <c r="N1031" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1031" s="1" t="s">
         <v>727</v>
@@ -57894,7 +57894,7 @@
         <v>0</v>
       </c>
       <c r="N1032" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1032" s="1" t="s">
         <v>721</v>
@@ -57947,7 +57947,7 @@
         <v>0</v>
       </c>
       <c r="N1033" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1033" s="1" t="s">
         <v>733</v>
@@ -58000,7 +58000,7 @@
         <v>0</v>
       </c>
       <c r="N1034" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1034" s="1" t="s">
         <v>734</v>
@@ -58053,7 +58053,7 @@
         <v>0</v>
       </c>
       <c r="N1035" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1035" s="1" t="s">
         <v>735</v>
@@ -58106,7 +58106,7 @@
         <v>0</v>
       </c>
       <c r="N1036" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1036" s="1" t="s">
         <v>730</v>
@@ -58159,7 +58159,7 @@
         <v>0</v>
       </c>
       <c r="N1037" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1037" s="1" t="s">
         <v>731</v>
@@ -58212,7 +58212,7 @@
         <v>0</v>
       </c>
       <c r="N1038" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1038" s="1" t="s">
         <v>736</v>
@@ -58265,7 +58265,7 @@
         <v>0</v>
       </c>
       <c r="N1039" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1039" s="1" t="s">
         <v>737</v>
@@ -58318,7 +58318,7 @@
         <v>0</v>
       </c>
       <c r="N1040" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1040" s="1" t="s">
         <v>738</v>
@@ -58371,7 +58371,7 @@
         <v>0</v>
       </c>
       <c r="N1041" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1041" s="1" t="s">
         <v>728</v>
@@ -58424,7 +58424,7 @@
         <v>0</v>
       </c>
       <c r="N1042" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1042" s="1" t="s">
         <v>739</v>
@@ -58477,7 +58477,7 @@
         <v>0</v>
       </c>
       <c r="N1043" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1043" s="1" t="s">
         <v>740</v>
@@ -58530,7 +58530,7 @@
         <v>0</v>
       </c>
       <c r="N1044" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1044" s="1" t="s">
         <v>741</v>
@@ -58583,7 +58583,7 @@
         <v>0</v>
       </c>
       <c r="N1045" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1045" s="1" t="s">
         <v>742</v>
@@ -58636,7 +58636,7 @@
         <v>0</v>
       </c>
       <c r="N1046" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1046" s="1" t="s">
         <v>743</v>
@@ -58689,7 +58689,7 @@
         <v>0</v>
       </c>
       <c r="N1047" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1047" s="1" t="s">
         <v>744</v>
@@ -58742,7 +58742,7 @@
         <v>0</v>
       </c>
       <c r="N1048" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1048" s="1" t="s">
         <v>745</v>
@@ -58795,7 +58795,7 @@
         <v>0</v>
       </c>
       <c r="N1049" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1049" s="1" t="s">
         <v>746</v>
@@ -58848,7 +58848,7 @@
         <v>0</v>
       </c>
       <c r="N1050" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1050" s="1" t="s">
         <v>747</v>
@@ -58901,7 +58901,7 @@
         <v>0</v>
       </c>
       <c r="N1051" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1051" s="1" t="s">
         <v>748</v>
@@ -58954,7 +58954,7 @@
         <v>0</v>
       </c>
       <c r="N1052" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1052" s="1" t="s">
         <v>749</v>
@@ -59007,7 +59007,7 @@
         <v>0</v>
       </c>
       <c r="N1053" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1053" s="1" t="s">
         <v>750</v>
@@ -59060,7 +59060,7 @@
         <v>0</v>
       </c>
       <c r="N1054" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1054" s="1" t="s">
         <v>751</v>
@@ -59113,7 +59113,7 @@
         <v>0</v>
       </c>
       <c r="N1055" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1055" s="1" t="s">
         <v>752</v>
@@ -59166,7 +59166,7 @@
         <v>0</v>
       </c>
       <c r="N1056" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1056" s="1" t="s">
         <v>753</v>
@@ -59219,7 +59219,7 @@
         <v>0</v>
       </c>
       <c r="N1057" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1057" s="1" t="s">
         <v>754</v>
@@ -59272,7 +59272,7 @@
         <v>0</v>
       </c>
       <c r="N1058" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1058" s="1" t="s">
         <v>755</v>
@@ -59325,7 +59325,7 @@
         <v>0</v>
       </c>
       <c r="N1059" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1059" s="1" t="s">
         <v>756</v>
@@ -59378,7 +59378,7 @@
         <v>0</v>
       </c>
       <c r="N1060" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1060" s="1" t="s">
         <v>757</v>
@@ -59431,7 +59431,7 @@
         <v>0</v>
       </c>
       <c r="N1061" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O1061" s="1" t="s">
         <v>758</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340029A4-9CE5-4194-B0BE-5A2716775A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451981B5-5AFA-458A-B453-017BCDCC0C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2166" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2178" uniqueCount="771">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2242,9 +2242,6 @@
     <t>71104,71101,71101</t>
   </si>
   <si>
-    <t>71102,71102,71105</t>
-  </si>
-  <si>
     <t>71108,71105,71102</t>
   </si>
   <si>
@@ -2281,9 +2278,6 @@
     <t>71106,71106,71103,71103,71106</t>
   </si>
   <si>
-    <t>71106,71106,71106,71106,71106,71106</t>
-  </si>
-  <si>
     <t>71106,71103,71103,71106,71106</t>
   </si>
   <si>
@@ -2299,124 +2293,166 @@
     <t>8,65,8,90</t>
   </si>
   <si>
-    <t>8,70</t>
-  </si>
-  <si>
     <t>40,75</t>
   </si>
   <si>
-    <t>45,75,80,75</t>
-  </si>
-  <si>
-    <t>50,75,85,80</t>
-  </si>
-  <si>
-    <t>60,75</t>
-  </si>
-  <si>
-    <t>55,75,20,75</t>
-  </si>
-  <si>
-    <t>50,75</t>
-  </si>
-  <si>
-    <t>45,75,15,85,15,65</t>
-  </si>
-  <si>
-    <t>40,70,40,80</t>
-  </si>
-  <si>
     <t>45,65,45,85</t>
   </si>
   <si>
-    <t>50,65,50,85,85,80</t>
-  </si>
-  <si>
-    <t>60,70,60,80</t>
-  </si>
-  <si>
-    <t>55,75,50,65,50,85</t>
-  </si>
-  <si>
-    <t>50,75,15,80,15,70</t>
-  </si>
-  <si>
-    <t>50,75,85,75</t>
-  </si>
-  <si>
-    <t>55,70,55,80,90,85</t>
-  </si>
-  <si>
-    <t>60,65,60,85,90,65</t>
-  </si>
-  <si>
-    <t>50,75,20,70,20,80</t>
-  </si>
-  <si>
-    <t>45,75,15,65,15,85</t>
-  </si>
-  <si>
-    <t>40,70,40,80,15,75</t>
-  </si>
-  <si>
-    <t>45,75,50,65,50,85</t>
-  </si>
-  <si>
     <t>55,75,80,70,80,80</t>
   </si>
   <si>
-    <t>55,75,85,65,85,85</t>
-  </si>
-  <si>
-    <t>55,75,60,75,90,80</t>
-  </si>
-  <si>
-    <t>60,65,60,85,90,70,65,75</t>
-  </si>
-  <si>
-    <t>60,75,20,75,60,85,60,65</t>
-  </si>
-  <si>
     <t>55,90,55,80,55,70,55,60</t>
   </si>
   <si>
-    <t>55,75,20,85,20,65,50,75</t>
-  </si>
-  <si>
-    <t>50,75,45,85,15,70,45,65,15,80</t>
-  </si>
-  <si>
     <t>45,90,45,80,45,70,45,60</t>
   </si>
   <si>
-    <t>45,75,15,60,15,90,40,85,40,65</t>
-  </si>
-  <si>
-    <t>40,85,10,85,40,75,10,65,40,65</t>
-  </si>
-  <si>
-    <t>40,75,40,65,40,85,80,70,80,80</t>
-  </si>
-  <si>
-    <t>45,75,85,90,85,60,40,65,40,85</t>
-  </si>
-  <si>
-    <t>50,75,85,75,45,75,45,90,45,60</t>
-  </si>
-  <si>
-    <t>50,65,50,85,85,90,85,60,50,75</t>
-  </si>
-  <si>
-    <t>50,75,50,65,50,85,55,75,55,65,55,85</t>
-  </si>
-  <si>
-    <t>55,75,90,90,90,60,55,85,55,65</t>
-  </si>
-  <si>
-    <t>55,85,55,65,90,80,60,75,60,90,60,60</t>
-  </si>
-  <si>
-    <t>65,90,65,80,90,70,65,70,65,60,70,75</t>
+    <t>8,45</t>
+  </si>
+  <si>
+    <t>50,75,65,75</t>
+  </si>
+  <si>
+    <t>55,75,75,75</t>
+  </si>
+  <si>
+    <t>80,75</t>
+  </si>
+  <si>
+    <t>80,75,95,85</t>
+  </si>
+  <si>
+    <t>80,60</t>
+  </si>
+  <si>
+    <t>85,60,95,75,95,65</t>
+  </si>
+  <si>
+    <t>50,70,50,80</t>
+  </si>
+  <si>
+    <t>45,75,30,75</t>
+  </si>
+  <si>
+    <t>40,65,40,85,25,80</t>
+  </si>
+  <si>
+    <t>55,70,55,80</t>
+  </si>
+  <si>
+    <t>60,75,60,65,60,85</t>
+  </si>
+  <si>
+    <t>60,75,80,80,80,70</t>
+  </si>
+  <si>
+    <t>50,75,25,75</t>
+  </si>
+  <si>
+    <t>45,75,20,75</t>
+  </si>
+  <si>
+    <t>40,70,40,80,20,85</t>
+  </si>
+  <si>
+    <t>40,65,40,85,20,65</t>
+  </si>
+  <si>
+    <t>55,75,60,65,60,85</t>
+  </si>
+  <si>
+    <t>60,75,85,65,85,85</t>
+  </si>
+  <si>
+    <t>60,65,60,85,60,75,85,75</t>
+  </si>
+  <si>
+    <t>50,65,50,85</t>
+  </si>
+  <si>
+    <t>45,75,45,65,45,85</t>
+  </si>
+  <si>
+    <t>40,75,80,70,80,80</t>
+  </si>
+  <si>
+    <t>40,75,85,65,85,85</t>
+  </si>
+  <si>
+    <t>40,75,60,75,90,80</t>
+  </si>
+  <si>
+    <t>40,65,40,85,90,70,40,75</t>
+  </si>
+  <si>
+    <t>65,60,70,70,70,80,65,90</t>
+  </si>
+  <si>
+    <t>60,75,30,75,60,85,60,65</t>
+  </si>
+  <si>
+    <t>55,75,30,85,30,65,50,75</t>
+  </si>
+  <si>
+    <t>50,75,45,85,25,70,45,65,25,80</t>
+  </si>
+  <si>
+    <t>40,90,40,80,40,70</t>
+  </si>
+  <si>
+    <t>45,75,20,60,20,90,40,85,40,65</t>
+  </si>
+  <si>
+    <t>40,85,40,75,40,65</t>
+  </si>
+  <si>
+    <t>35,85,20,85,35,75,20,65,35,65</t>
+  </si>
+  <si>
+    <t>50,75,50,65,50,85,70,70,70,80</t>
+  </si>
+  <si>
+    <t>50,75,75,90,75,60,50,65,50,85</t>
+  </si>
+  <si>
+    <t>55,70,55,80,60,60,60,90</t>
+  </si>
+  <si>
+    <t>55,75,80,75,60,75,60,90,60,60</t>
+  </si>
+  <si>
+    <t>60,65,60,85,80,90,80,60,60,75</t>
+  </si>
+  <si>
+    <t>60,75,65,85,85,90,85,60,65,65</t>
+  </si>
+  <si>
+    <t>65,60,65,70,65,80,65,90</t>
+  </si>
+  <si>
+    <t>65,75,85,90,85,60,65,85,65,65</t>
+  </si>
+  <si>
+    <t>65,85,65,65,90,80,70,75,70,90,70,60</t>
+  </si>
+  <si>
+    <t>75,85,75,65,75,75,75,95,75,55</t>
+  </si>
+  <si>
+    <t>75,90,75,60,90,75,80,75,80,65,80,85</t>
+  </si>
+  <si>
+    <t>71104,71104,71104,71101</t>
+  </si>
+  <si>
+    <t>71106,71106,71106,71106</t>
+  </si>
+  <si>
+    <t>71109,71106,71103,71103,71106</t>
+  </si>
+  <si>
+    <t>71106,71106,71106,71106,71106</t>
   </si>
 </sst>
 </file>
@@ -3229,7 +3265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q1061"/>
+  <dimension ref="A1:Q1067"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -56890,7 +56926,7 @@
         <v>0</v>
       </c>
       <c r="O1013" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="P1013" s="1">
         <v>0</v>
@@ -56943,7 +56979,7 @@
         <v>0</v>
       </c>
       <c r="O1014" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="P1014" s="1">
         <v>0</v>
@@ -56996,7 +57032,7 @@
         <v>0</v>
       </c>
       <c r="O1015" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="P1015" s="1">
         <v>0</v>
@@ -57049,7 +57085,7 @@
         <v>0</v>
       </c>
       <c r="O1016" s="1" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="P1016" s="1">
         <v>0</v>
@@ -57102,7 +57138,7 @@
         <v>0</v>
       </c>
       <c r="O1017" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="P1017" s="1">
         <v>0</v>
@@ -57155,7 +57191,7 @@
         <v>0</v>
       </c>
       <c r="O1018" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="P1018" s="1">
         <v>0</v>
@@ -57208,7 +57244,7 @@
         <v>0</v>
       </c>
       <c r="O1019" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="P1019" s="1">
         <v>0</v>
@@ -57261,7 +57297,7 @@
         <v>0</v>
       </c>
       <c r="O1020" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="P1020" s="1">
         <v>0</v>
@@ -57314,7 +57350,7 @@
         <v>0</v>
       </c>
       <c r="O1021" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="P1021" s="1">
         <v>0</v>
@@ -57367,7 +57403,7 @@
         <v>0</v>
       </c>
       <c r="O1022" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="P1022" s="1">
         <v>0</v>
@@ -57420,7 +57456,7 @@
         <v>0</v>
       </c>
       <c r="O1023" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="P1023" s="1">
         <v>0</v>
@@ -57473,7 +57509,7 @@
         <v>0</v>
       </c>
       <c r="O1024" s="1" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
       <c r="P1024" s="1">
         <v>0</v>
@@ -57526,7 +57562,7 @@
         <v>0</v>
       </c>
       <c r="O1025" s="1" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="P1025" s="1">
         <v>0</v>
@@ -57579,7 +57615,7 @@
         <v>0</v>
       </c>
       <c r="O1026" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="P1026" s="1">
         <v>0</v>
@@ -57632,7 +57668,7 @@
         <v>0</v>
       </c>
       <c r="O1027" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="P1027" s="1">
         <v>0</v>
@@ -57738,7 +57774,7 @@
         <v>0</v>
       </c>
       <c r="O1029" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="P1029" s="1">
         <v>0</v>
@@ -57791,7 +57827,7 @@
         <v>0</v>
       </c>
       <c r="O1030" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="P1030" s="1">
         <v>0</v>
@@ -57844,7 +57880,7 @@
         <v>0</v>
       </c>
       <c r="O1031" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="P1031" s="1">
         <v>0</v>
@@ -57897,7 +57933,7 @@
         <v>0</v>
       </c>
       <c r="O1032" s="1" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="P1032" s="1">
         <v>0</v>
@@ -57950,7 +57986,7 @@
         <v>0</v>
       </c>
       <c r="O1033" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="P1033" s="1">
         <v>0</v>
@@ -58003,7 +58039,7 @@
         <v>0</v>
       </c>
       <c r="O1034" s="1" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="P1034" s="1">
         <v>0</v>
@@ -58056,7 +58092,7 @@
         <v>0</v>
       </c>
       <c r="O1035" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="P1035" s="1">
         <v>0</v>
@@ -58109,7 +58145,7 @@
         <v>0</v>
       </c>
       <c r="O1036" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="P1036" s="1">
         <v>0</v>
@@ -58162,7 +58198,7 @@
         <v>0</v>
       </c>
       <c r="O1037" s="1" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="P1037" s="1">
         <v>0</v>
@@ -58215,7 +58251,7 @@
         <v>0</v>
       </c>
       <c r="O1038" s="1" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
       <c r="P1038" s="1">
         <v>0</v>
@@ -58268,7 +58304,7 @@
         <v>0</v>
       </c>
       <c r="O1039" s="1" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="P1039" s="1">
         <v>0</v>
@@ -58306,7 +58342,7 @@
         <v>7</v>
       </c>
       <c r="J1040" s="2" t="s">
-        <v>697</v>
+        <v>767</v>
       </c>
       <c r="K1040" s="1">
         <v>120</v>
@@ -58321,7 +58357,7 @@
         <v>0</v>
       </c>
       <c r="O1040" s="1" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="P1040" s="1">
         <v>0</v>
@@ -58374,7 +58410,7 @@
         <v>0</v>
       </c>
       <c r="O1041" s="1" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
       <c r="P1041" s="1">
         <v>0</v>
@@ -58427,7 +58463,7 @@
         <v>0</v>
       </c>
       <c r="O1042" s="1" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="P1042" s="1">
         <v>0</v>
@@ -58465,7 +58501,7 @@
         <v>8</v>
       </c>
       <c r="J1043" s="2" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="K1043" s="1">
         <v>120</v>
@@ -58480,7 +58516,7 @@
         <v>0</v>
       </c>
       <c r="O1043" s="1" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="P1043" s="1">
         <v>0</v>
@@ -58533,7 +58569,7 @@
         <v>0</v>
       </c>
       <c r="O1044" s="1" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="P1044" s="1">
         <v>0</v>
@@ -58571,7 +58607,7 @@
         <v>8</v>
       </c>
       <c r="J1045" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="K1045" s="1">
         <v>120</v>
@@ -58586,7 +58622,7 @@
         <v>0</v>
       </c>
       <c r="O1045" s="1" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="P1045" s="1">
         <v>0</v>
@@ -58618,13 +58654,13 @@
         <v>34</v>
       </c>
       <c r="H1046" s="1">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="I1046" s="1">
         <v>8</v>
       </c>
       <c r="J1046" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="K1046" s="1">
         <v>120</v>
@@ -58639,7 +58675,7 @@
         <v>0</v>
       </c>
       <c r="O1046" s="1" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="P1046" s="1">
         <v>0</v>
@@ -58671,10 +58707,10 @@
         <v>35</v>
       </c>
       <c r="H1047" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="I1047" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1047" s="2" t="s">
         <v>703</v>
@@ -58692,7 +58728,7 @@
         <v>0</v>
       </c>
       <c r="O1047" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="P1047" s="1">
         <v>0</v>
@@ -58730,7 +58766,7 @@
         <v>9</v>
       </c>
       <c r="J1048" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K1048" s="1">
         <v>120</v>
@@ -58745,7 +58781,7 @@
         <v>0</v>
       </c>
       <c r="O1048" s="1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="P1048" s="1">
         <v>0</v>
@@ -58783,7 +58819,7 @@
         <v>9</v>
       </c>
       <c r="J1049" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="K1049" s="1">
         <v>120</v>
@@ -58798,7 +58834,7 @@
         <v>0</v>
       </c>
       <c r="O1049" s="1" t="s">
-        <v>746</v>
+        <v>720</v>
       </c>
       <c r="P1049" s="1">
         <v>0</v>
@@ -58836,7 +58872,7 @@
         <v>9</v>
       </c>
       <c r="J1050" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K1050" s="1">
         <v>120</v>
@@ -58851,7 +58887,7 @@
         <v>0</v>
       </c>
       <c r="O1050" s="1" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="P1050" s="1">
         <v>0</v>
@@ -58889,7 +58925,7 @@
         <v>9</v>
       </c>
       <c r="J1051" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K1051" s="1">
         <v>120</v>
@@ -58904,7 +58940,7 @@
         <v>0</v>
       </c>
       <c r="O1051" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="P1051" s="1">
         <v>0</v>
@@ -58936,13 +58972,13 @@
         <v>40</v>
       </c>
       <c r="H1052" s="1">
-        <v>4000</v>
+        <v>1</v>
       </c>
       <c r="I1052" s="1">
         <v>9</v>
       </c>
       <c r="J1052" s="2" t="s">
-        <v>707</v>
+        <v>682</v>
       </c>
       <c r="K1052" s="1">
         <v>120</v>
@@ -58957,7 +58993,7 @@
         <v>0</v>
       </c>
       <c r="O1052" s="1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="P1052" s="1">
         <v>0</v>
@@ -58989,13 +59025,13 @@
         <v>41</v>
       </c>
       <c r="H1053" s="1">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="I1053" s="1">
         <v>9</v>
       </c>
       <c r="J1053" s="2" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="K1053" s="1">
         <v>120</v>
@@ -59010,7 +59046,7 @@
         <v>0</v>
       </c>
       <c r="O1053" s="1" t="s">
-        <v>750</v>
+        <v>721</v>
       </c>
       <c r="P1053" s="1">
         <v>0</v>
@@ -59042,13 +59078,13 @@
         <v>42</v>
       </c>
       <c r="H1054" s="1">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="I1054" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1054" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="K1054" s="1">
         <v>120</v>
@@ -59063,7 +59099,7 @@
         <v>0</v>
       </c>
       <c r="O1054" s="1" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="P1054" s="1">
         <v>0</v>
@@ -59095,13 +59131,13 @@
         <v>43</v>
       </c>
       <c r="H1055" s="1">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="I1055" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1055" s="2" t="s">
-        <v>710</v>
+        <v>682</v>
       </c>
       <c r="K1055" s="1">
         <v>120</v>
@@ -59116,7 +59152,7 @@
         <v>0</v>
       </c>
       <c r="O1055" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="P1055" s="1">
         <v>0</v>
@@ -59148,13 +59184,13 @@
         <v>44</v>
       </c>
       <c r="H1056" s="1">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="I1056" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1056" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="K1056" s="1">
         <v>120</v>
@@ -59169,7 +59205,7 @@
         <v>0</v>
       </c>
       <c r="O1056" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="P1056" s="1">
         <v>0</v>
@@ -59207,7 +59243,7 @@
         <v>10</v>
       </c>
       <c r="J1057" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="K1057" s="1">
         <v>120</v>
@@ -59222,7 +59258,7 @@
         <v>0</v>
       </c>
       <c r="O1057" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="P1057" s="1">
         <v>0</v>
@@ -59260,7 +59296,7 @@
         <v>10</v>
       </c>
       <c r="J1058" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="K1058" s="1">
         <v>120</v>
@@ -59275,7 +59311,7 @@
         <v>0</v>
       </c>
       <c r="O1058" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="P1058" s="1">
         <v>0</v>
@@ -59307,13 +59343,13 @@
         <v>47</v>
       </c>
       <c r="H1059" s="1">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="I1059" s="1">
         <v>10</v>
       </c>
       <c r="J1059" s="2" t="s">
-        <v>714</v>
+        <v>768</v>
       </c>
       <c r="K1059" s="1">
         <v>120</v>
@@ -59328,7 +59364,7 @@
         <v>0</v>
       </c>
       <c r="O1059" s="1" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="P1059" s="1">
         <v>0</v>
@@ -59366,7 +59402,7 @@
         <v>10</v>
       </c>
       <c r="J1060" s="2" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="K1060" s="1">
         <v>120</v>
@@ -59381,7 +59417,7 @@
         <v>0</v>
       </c>
       <c r="O1060" s="1" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="P1060" s="1">
         <v>0</v>
@@ -59413,13 +59449,13 @@
         <v>49</v>
       </c>
       <c r="H1061" s="1">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="I1061" s="1">
         <v>10</v>
       </c>
       <c r="J1061" s="2" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="K1061" s="1">
         <v>120</v>
@@ -59434,13 +59470,259 @@
         <v>0</v>
       </c>
       <c r="O1061" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="P1061" s="1">
         <v>0</v>
       </c>
       <c r="Q1061" s="1">
         <v>0</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1062" s="1">
+        <v>771009</v>
+      </c>
+      <c r="B1062" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1062" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1062" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1062" s="1">
+        <v>50</v>
+      </c>
+      <c r="H1062" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1062" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1062" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="K1062" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1062" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1062" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1062" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1062" s="1" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1063" s="1">
+        <v>771010</v>
+      </c>
+      <c r="B1063" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1063" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1063" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1063" s="1">
+        <v>51</v>
+      </c>
+      <c r="H1063" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1063" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1063" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="K1063" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1063" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1063" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1063" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1063" s="1" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1064" s="1">
+        <v>771011</v>
+      </c>
+      <c r="B1064" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1064" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1064" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1064" s="1">
+        <v>52</v>
+      </c>
+      <c r="H1064" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1064" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1064" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="K1064" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1064" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1064" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1064" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1064" s="1" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1065" s="1">
+        <v>771012</v>
+      </c>
+      <c r="B1065" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1065" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1065" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1065" s="1">
+        <v>53</v>
+      </c>
+      <c r="H1065" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1065" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1065" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="K1065" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1065" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1065" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1065" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1065" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1066" s="1">
+        <v>771013</v>
+      </c>
+      <c r="B1066" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1066" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1066" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1066" s="1">
+        <v>54</v>
+      </c>
+      <c r="H1066" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1066" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1066" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="K1066" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1066" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1066" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1066" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1066" s="1" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1067" s="1">
+        <v>771014</v>
+      </c>
+      <c r="B1067" s="1">
+        <v>7</v>
+      </c>
+      <c r="E1067" s="1">
+        <v>70001</v>
+      </c>
+      <c r="F1067" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1067" s="1">
+        <v>55</v>
+      </c>
+      <c r="H1067" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1067" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1067" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="K1067" s="1">
+        <v>120</v>
+      </c>
+      <c r="L1067" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1067" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1067" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1067" s="1" t="s">
+        <v>766</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F785AE8-66BC-4CEF-B2D5-F15BEA8DD8D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0486CB-499D-4737-981D-34A1F7D66761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2181" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="793">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2461,6 +2461,66 @@
   <si>
     <t>是否需要默认显示</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,70,50,50</t>
+  </si>
+  <si>
+    <t>50,50</t>
+  </si>
+  <si>
+    <t>5,40,75,20</t>
+  </si>
+  <si>
+    <t>95,30,25,10</t>
+  </si>
+  <si>
+    <t>30,80</t>
+  </si>
+  <si>
+    <t>3,65,12,35</t>
+  </si>
+  <si>
+    <t>22,57</t>
+  </si>
+  <si>
+    <t>3,50,5,40,20,40</t>
+  </si>
+  <si>
+    <t>50,20,55,2</t>
+  </si>
+  <si>
+    <t>75,16,75,6</t>
+  </si>
+  <si>
+    <t>70,11,85,11</t>
+  </si>
+  <si>
+    <t>72,20,78,2,90,11</t>
+  </si>
+  <si>
+    <t>91104</t>
+  </si>
+  <si>
+    <t>91104,91101</t>
+  </si>
+  <si>
+    <t>91105</t>
+  </si>
+  <si>
+    <t>91105,91102</t>
+  </si>
+  <si>
+    <t>91105,91102,91102</t>
+  </si>
+  <si>
+    <t>91105,91105</t>
+  </si>
+  <si>
+    <t>91108,91102</t>
+  </si>
+  <si>
+    <t>91105,91105,91102</t>
   </si>
 </sst>
 </file>
@@ -3273,7 +3333,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1067"/>
+  <dimension ref="A1:R1081"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -62676,7 +62736,7 @@
         <v>7</v>
       </c>
       <c r="E1062" s="1">
-        <v>70001</v>
+        <v>90001</v>
       </c>
       <c r="F1062" s="1">
         <v>1</v>
@@ -62726,7 +62786,7 @@
         <v>7</v>
       </c>
       <c r="E1063" s="1">
-        <v>70001</v>
+        <v>90001</v>
       </c>
       <c r="F1063" s="1">
         <v>1</v>
@@ -62776,7 +62836,7 @@
         <v>7</v>
       </c>
       <c r="E1064" s="1">
-        <v>70001</v>
+        <v>90001</v>
       </c>
       <c r="F1064" s="1">
         <v>1</v>
@@ -62826,7 +62886,7 @@
         <v>7</v>
       </c>
       <c r="E1065" s="1">
-        <v>70001</v>
+        <v>90001</v>
       </c>
       <c r="F1065" s="1">
         <v>1</v>
@@ -62876,7 +62936,7 @@
         <v>7</v>
       </c>
       <c r="E1066" s="1">
-        <v>70001</v>
+        <v>90001</v>
       </c>
       <c r="F1066" s="1">
         <v>1</v>
@@ -62926,7 +62986,7 @@
         <v>7</v>
       </c>
       <c r="E1067" s="1">
-        <v>70001</v>
+        <v>90001</v>
       </c>
       <c r="F1067" s="1">
         <v>1</v>
@@ -62965,6 +63025,706 @@
         <v>0</v>
       </c>
       <c r="R1067" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1068" s="1">
+        <v>910101</v>
+      </c>
+      <c r="B1068" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1068" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1068" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1068" s="1">
+        <v>1</v>
+      </c>
+      <c r="H1068" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1068" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1068" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="K1068" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1068" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1068" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1068" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1068" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="P1068" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1068" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1068" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1069" s="1">
+        <v>910102</v>
+      </c>
+      <c r="B1069" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1069" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1069" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1069" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1069" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1069" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1069" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="K1069" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1069" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1069" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1069" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1069" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="P1069" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1069" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1069" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1070" s="1">
+        <v>910103</v>
+      </c>
+      <c r="B1070" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1070" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1070" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1070" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1070" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I1070" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1070" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="K1070" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1070" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1070" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1070" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1070" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="P1070" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1070" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1070" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1071" s="1">
+        <v>910201</v>
+      </c>
+      <c r="B1071" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1071" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1071" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1071" s="1">
+        <v>4</v>
+      </c>
+      <c r="H1071" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1071" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1071" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="K1071" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1071" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1071" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1071" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1071" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="P1071" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1071" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1071" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1072" s="1">
+        <v>910202</v>
+      </c>
+      <c r="B1072" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1072" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1072" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1072" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1072" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1072" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1072" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="K1072" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1072" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1072" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1072" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1072" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="P1072" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1072" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1072" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1073" s="1">
+        <v>910203</v>
+      </c>
+      <c r="B1073" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1073" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1073" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1073" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1073" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I1073" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1073" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="K1073" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1073" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1073" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1073" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1073" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="P1073" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1073" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1073" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1074" s="1">
+        <v>910301</v>
+      </c>
+      <c r="B1074" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1074" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1074" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1074" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1074" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I1074" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1074" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="K1074" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1074" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1074" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1074" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1074" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="P1074" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1074" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1074" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1075" s="1">
+        <v>910302</v>
+      </c>
+      <c r="B1075" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1075" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1075" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1075" s="1">
+        <v>8</v>
+      </c>
+      <c r="H1075" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1075" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1075" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="K1075" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1075" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1075" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1075" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1075" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="P1075" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1075" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1075" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1076" s="1">
+        <v>910303</v>
+      </c>
+      <c r="B1076" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1076" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1076" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1076" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1076" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I1076" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1076" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="K1076" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1076" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1076" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1076" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1076" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="P1076" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1076" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1076" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1077" s="1">
+        <v>910304</v>
+      </c>
+      <c r="B1077" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1077" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1077" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1077" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1077" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I1077" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1077" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="K1077" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1077" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1077" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1077" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1077" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="P1077" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1077" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1077" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1078" s="1">
+        <v>910401</v>
+      </c>
+      <c r="B1078" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1078" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1078" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1078" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1078" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I1078" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1078" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="K1078" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1078" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1078" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1078" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1078" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="P1078" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1078" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1078" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1079" s="1">
+        <v>910402</v>
+      </c>
+      <c r="B1079" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1079" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1079" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1079" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1079" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1079" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1079" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="K1079" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1079" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1079" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1079" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1079" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="P1079" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1079" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1079" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1080" s="1">
+        <v>910403</v>
+      </c>
+      <c r="B1080" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1080" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1080" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1080" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1080" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1080" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1080" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="K1080" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1080" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1080" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1080" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1080" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="P1080" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1080" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1080" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1081" s="1">
+        <v>910404</v>
+      </c>
+      <c r="B1081" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1081" s="1">
+        <v>90001</v>
+      </c>
+      <c r="F1081" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1081" s="1">
+        <v>14</v>
+      </c>
+      <c r="H1081" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I1081" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1081" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="K1081" s="1">
+        <v>100</v>
+      </c>
+      <c r="L1081" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1081" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1081" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1081" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="P1081" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1081" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1081" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0486CB-499D-4737-981D-34A1F7D66761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102D32C5-9DA7-4258-AC13-07299E89584D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62736,7 +62736,7 @@
         <v>7</v>
       </c>
       <c r="E1062" s="1">
-        <v>90001</v>
+        <v>70001</v>
       </c>
       <c r="F1062" s="1">
         <v>1</v>
@@ -62786,7 +62786,7 @@
         <v>7</v>
       </c>
       <c r="E1063" s="1">
-        <v>90001</v>
+        <v>70001</v>
       </c>
       <c r="F1063" s="1">
         <v>1</v>
@@ -62836,7 +62836,7 @@
         <v>7</v>
       </c>
       <c r="E1064" s="1">
-        <v>90001</v>
+        <v>70001</v>
       </c>
       <c r="F1064" s="1">
         <v>1</v>
@@ -62886,7 +62886,7 @@
         <v>7</v>
       </c>
       <c r="E1065" s="1">
-        <v>90001</v>
+        <v>70001</v>
       </c>
       <c r="F1065" s="1">
         <v>1</v>
@@ -62936,7 +62936,7 @@
         <v>7</v>
       </c>
       <c r="E1066" s="1">
-        <v>90001</v>
+        <v>70001</v>
       </c>
       <c r="F1066" s="1">
         <v>1</v>
@@ -62986,7 +62986,7 @@
         <v>7</v>
       </c>
       <c r="E1067" s="1">
-        <v>90001</v>
+        <v>70001</v>
       </c>
       <c r="F1067" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102D32C5-9DA7-4258-AC13-07299E89584D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5C37DE-5CBB-48B4-B7D5-77D996F08E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62735,6 +62735,12 @@
       <c r="B1062" s="1">
         <v>7</v>
       </c>
+      <c r="C1062" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1062" s="1">
+        <v>3</v>
+      </c>
       <c r="E1062" s="1">
         <v>70001</v>
       </c>
@@ -62785,6 +62791,12 @@
       <c r="B1063" s="1">
         <v>7</v>
       </c>
+      <c r="C1063" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1063" s="1">
+        <v>3</v>
+      </c>
       <c r="E1063" s="1">
         <v>70001</v>
       </c>
@@ -62835,6 +62847,12 @@
       <c r="B1064" s="1">
         <v>7</v>
       </c>
+      <c r="C1064" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1064" s="1">
+        <v>3</v>
+      </c>
       <c r="E1064" s="1">
         <v>70001</v>
       </c>
@@ -62885,6 +62903,12 @@
       <c r="B1065" s="1">
         <v>7</v>
       </c>
+      <c r="C1065" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1065" s="1">
+        <v>3</v>
+      </c>
       <c r="E1065" s="1">
         <v>70001</v>
       </c>
@@ -62935,6 +62959,12 @@
       <c r="B1066" s="1">
         <v>7</v>
       </c>
+      <c r="C1066" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1066" s="1">
+        <v>3</v>
+      </c>
       <c r="E1066" s="1">
         <v>70001</v>
       </c>
@@ -62985,6 +63015,12 @@
       <c r="B1067" s="1">
         <v>7</v>
       </c>
+      <c r="C1067" s="1">
+        <v>10</v>
+      </c>
+      <c r="D1067" s="1">
+        <v>3</v>
+      </c>
       <c r="E1067" s="1">
         <v>70001</v>
       </c>
@@ -63225,7 +63261,7 @@
         <v>0</v>
       </c>
       <c r="R1071" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1072" spans="1:18" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5C37DE-5CBB-48B4-B7D5-77D996F08E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2678E7-527A-485D-84C8-5E358306411A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="791">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2499,28 +2499,22 @@
     <t>72,20,78,2,90,11</t>
   </si>
   <si>
-    <t>91104</t>
-  </si>
-  <si>
-    <t>91104,91101</t>
-  </si>
-  <si>
     <t>91105</t>
   </si>
   <si>
-    <t>91105,91102</t>
-  </si>
-  <si>
-    <t>91105,91102,91102</t>
-  </si>
-  <si>
     <t>91105,91105</t>
   </si>
   <si>
-    <t>91108,91102</t>
-  </si>
-  <si>
-    <t>91105,91105,91102</t>
+    <t>91106,91106</t>
+  </si>
+  <si>
+    <t>91105,91105,91105</t>
+  </si>
+  <si>
+    <t>91106,91105</t>
+  </si>
+  <si>
+    <t>91106,91106,91105</t>
   </si>
 </sst>
 </file>
@@ -63387,7 +63381,7 @@
         <v>3</v>
       </c>
       <c r="J1074" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="K1074" s="1">
         <v>100</v>
@@ -63437,7 +63431,7 @@
         <v>3</v>
       </c>
       <c r="J1075" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="K1075" s="1">
         <v>100</v>
@@ -63487,7 +63481,7 @@
         <v>3</v>
       </c>
       <c r="J1076" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="K1076" s="1">
         <v>100</v>
@@ -63537,7 +63531,7 @@
         <v>3</v>
       </c>
       <c r="J1077" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K1077" s="1">
         <v>100</v>
@@ -63587,7 +63581,7 @@
         <v>4</v>
       </c>
       <c r="J1078" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="K1078" s="1">
         <v>100</v>
@@ -63637,7 +63631,7 @@
         <v>4</v>
       </c>
       <c r="J1079" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="K1079" s="1">
         <v>100</v>
@@ -63687,7 +63681,7 @@
         <v>4</v>
       </c>
       <c r="J1080" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="K1080" s="1">
         <v>100</v>
@@ -63737,7 +63731,7 @@
         <v>4</v>
       </c>
       <c r="J1081" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="K1081" s="1">
         <v>100</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2678E7-527A-485D-84C8-5E358306411A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E247E0C-2705-4915-80F9-A449A379639D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_brush_foe_v8" sheetId="2" r:id="rId1"/>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="793">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2469,12 +2469,6 @@
     <t>50,50</t>
   </si>
   <si>
-    <t>5,40,75,20</t>
-  </si>
-  <si>
-    <t>95,30,25,10</t>
-  </si>
-  <si>
     <t>30,80</t>
   </si>
   <si>
@@ -2515,6 +2509,22 @@
   </si>
   <si>
     <t>91106,91106,91105</t>
+  </si>
+  <si>
+    <t>5,40</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>95,30,25,10,75,20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>91105</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>91105,91105,91105</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -63081,7 +63091,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -63131,7 +63141,7 @@
         <v>1</v>
       </c>
       <c r="J1069" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="K1069" s="1">
         <v>100</v>
@@ -63181,7 +63191,7 @@
         <v>1</v>
       </c>
       <c r="J1070" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="K1070" s="1">
         <v>100</v>
@@ -63231,7 +63241,7 @@
         <v>2</v>
       </c>
       <c r="J1071" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="K1071" s="1">
         <v>100</v>
@@ -63255,7 +63265,7 @@
         <v>0</v>
       </c>
       <c r="R1071" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1072" spans="1:18" x14ac:dyDescent="0.2">
@@ -63281,7 +63291,7 @@
         <v>2</v>
       </c>
       <c r="J1072" s="2" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="K1072" s="1">
         <v>100</v>
@@ -63296,7 +63306,7 @@
         <v>0</v>
       </c>
       <c r="O1072" s="1" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="P1072" s="1">
         <v>0</v>
@@ -63305,7 +63315,7 @@
         <v>0</v>
       </c>
       <c r="R1072" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1073" spans="1:18" x14ac:dyDescent="0.2">
@@ -63331,7 +63341,7 @@
         <v>2</v>
       </c>
       <c r="J1073" s="2" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="K1073" s="1">
         <v>100</v>
@@ -63346,7 +63356,7 @@
         <v>0</v>
       </c>
       <c r="O1073" s="1" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
       <c r="P1073" s="1">
         <v>0</v>
@@ -63381,7 +63391,7 @@
         <v>3</v>
       </c>
       <c r="J1074" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="K1074" s="1">
         <v>100</v>
@@ -63396,7 +63406,7 @@
         <v>1</v>
       </c>
       <c r="O1074" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="P1074" s="1">
         <v>0</v>
@@ -63431,7 +63441,7 @@
         <v>3</v>
       </c>
       <c r="J1075" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="K1075" s="1">
         <v>100</v>
@@ -63446,7 +63456,7 @@
         <v>1</v>
       </c>
       <c r="O1075" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="P1075" s="1">
         <v>0</v>
@@ -63481,7 +63491,7 @@
         <v>3</v>
       </c>
       <c r="J1076" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="K1076" s="1">
         <v>100</v>
@@ -63496,7 +63506,7 @@
         <v>1</v>
       </c>
       <c r="O1076" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="P1076" s="1">
         <v>0</v>
@@ -63531,7 +63541,7 @@
         <v>3</v>
       </c>
       <c r="J1077" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="K1077" s="1">
         <v>100</v>
@@ -63546,7 +63556,7 @@
         <v>1</v>
       </c>
       <c r="O1077" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="P1077" s="1">
         <v>0</v>
@@ -63581,7 +63591,7 @@
         <v>4</v>
       </c>
       <c r="J1078" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="K1078" s="1">
         <v>100</v>
@@ -63596,7 +63606,7 @@
         <v>1</v>
       </c>
       <c r="O1078" s="1" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="P1078" s="1">
         <v>0</v>
@@ -63631,7 +63641,7 @@
         <v>4</v>
       </c>
       <c r="J1079" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="K1079" s="1">
         <v>100</v>
@@ -63646,7 +63656,7 @@
         <v>1</v>
       </c>
       <c r="O1079" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="P1079" s="1">
         <v>0</v>
@@ -63681,7 +63691,7 @@
         <v>4</v>
       </c>
       <c r="J1080" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="K1080" s="1">
         <v>100</v>
@@ -63696,7 +63706,7 @@
         <v>1</v>
       </c>
       <c r="O1080" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="P1080" s="1">
         <v>0</v>
@@ -63731,7 +63741,7 @@
         <v>4</v>
       </c>
       <c r="J1081" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="K1081" s="1">
         <v>100</v>
@@ -63746,7 +63756,7 @@
         <v>1</v>
       </c>
       <c r="O1081" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="P1081" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E247E0C-2705-4915-80F9-A449A379639D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BBFFD5-5FEA-4ABC-AABF-A3C586FB4A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="794">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2463,12 +2463,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>50,70,50,50</t>
-  </si>
-  <si>
-    <t>50,50</t>
-  </si>
-  <si>
     <t>30,80</t>
   </si>
   <si>
@@ -2509,14 +2503,6 @@
   </si>
   <si>
     <t>91106,91106,91105</t>
-  </si>
-  <si>
-    <t>5,40</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>95,30,25,10,75,20</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>91105</t>
@@ -2525,6 +2511,21 @@
   <si>
     <t>91105,91105,91105</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50,55</t>
+  </si>
+  <si>
+    <t>50,50,50,40</t>
+  </si>
+  <si>
+    <t>50,30</t>
+  </si>
+  <si>
+    <t>5,20,75,15</t>
+  </si>
+  <si>
+    <t>95,15,25,10</t>
   </si>
 </sst>
 </file>
@@ -63091,7 +63092,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -63106,7 +63107,7 @@
         <v>0</v>
       </c>
       <c r="O1068" s="1" t="s">
-        <v>166</v>
+        <v>789</v>
       </c>
       <c r="P1068" s="1">
         <v>0</v>
@@ -63141,7 +63142,7 @@
         <v>1</v>
       </c>
       <c r="J1069" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="K1069" s="1">
         <v>100</v>
@@ -63156,7 +63157,7 @@
         <v>0</v>
       </c>
       <c r="O1069" s="1" t="s">
-        <v>773</v>
+        <v>790</v>
       </c>
       <c r="P1069" s="1">
         <v>0</v>
@@ -63191,7 +63192,7 @@
         <v>1</v>
       </c>
       <c r="J1070" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="K1070" s="1">
         <v>100</v>
@@ -63206,7 +63207,7 @@
         <v>0</v>
       </c>
       <c r="O1070" s="1" t="s">
-        <v>164</v>
+        <v>791</v>
       </c>
       <c r="P1070" s="1">
         <v>0</v>
@@ -63241,7 +63242,7 @@
         <v>2</v>
       </c>
       <c r="J1071" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="K1071" s="1">
         <v>100</v>
@@ -63256,7 +63257,7 @@
         <v>0</v>
       </c>
       <c r="O1071" s="1" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="P1071" s="1">
         <v>0</v>
@@ -63291,7 +63292,7 @@
         <v>2</v>
       </c>
       <c r="J1072" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="K1072" s="1">
         <v>100</v>
@@ -63306,7 +63307,7 @@
         <v>0</v>
       </c>
       <c r="O1072" s="1" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="P1072" s="1">
         <v>0</v>
@@ -63341,7 +63342,7 @@
         <v>2</v>
       </c>
       <c r="J1073" s="2" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="K1073" s="1">
         <v>100</v>
@@ -63356,7 +63357,7 @@
         <v>0</v>
       </c>
       <c r="O1073" s="1" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="P1073" s="1">
         <v>0</v>
@@ -63391,7 +63392,7 @@
         <v>3</v>
       </c>
       <c r="J1074" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="K1074" s="1">
         <v>100</v>
@@ -63406,7 +63407,7 @@
         <v>1</v>
       </c>
       <c r="O1074" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="P1074" s="1">
         <v>0</v>
@@ -63441,7 +63442,7 @@
         <v>3</v>
       </c>
       <c r="J1075" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="K1075" s="1">
         <v>100</v>
@@ -63456,7 +63457,7 @@
         <v>1</v>
       </c>
       <c r="O1075" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="P1075" s="1">
         <v>0</v>
@@ -63491,7 +63492,7 @@
         <v>3</v>
       </c>
       <c r="J1076" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="K1076" s="1">
         <v>100</v>
@@ -63506,7 +63507,7 @@
         <v>1</v>
       </c>
       <c r="O1076" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="P1076" s="1">
         <v>0</v>
@@ -63541,7 +63542,7 @@
         <v>3</v>
       </c>
       <c r="J1077" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="K1077" s="1">
         <v>100</v>
@@ -63556,7 +63557,7 @@
         <v>1</v>
       </c>
       <c r="O1077" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="P1077" s="1">
         <v>0</v>
@@ -63591,7 +63592,7 @@
         <v>4</v>
       </c>
       <c r="J1078" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="K1078" s="1">
         <v>100</v>
@@ -63606,7 +63607,7 @@
         <v>1</v>
       </c>
       <c r="O1078" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="P1078" s="1">
         <v>0</v>
@@ -63641,7 +63642,7 @@
         <v>4</v>
       </c>
       <c r="J1079" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="K1079" s="1">
         <v>100</v>
@@ -63656,7 +63657,7 @@
         <v>1</v>
       </c>
       <c r="O1079" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="P1079" s="1">
         <v>0</v>
@@ -63691,7 +63692,7 @@
         <v>4</v>
       </c>
       <c r="J1080" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="K1080" s="1">
         <v>100</v>
@@ -63706,7 +63707,7 @@
         <v>1</v>
       </c>
       <c r="O1080" s="1" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="P1080" s="1">
         <v>0</v>
@@ -63741,7 +63742,7 @@
         <v>4</v>
       </c>
       <c r="J1081" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="K1081" s="1">
         <v>100</v>
@@ -63756,7 +63757,7 @@
         <v>1</v>
       </c>
       <c r="O1081" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="P1081" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BBFFD5-5FEA-4ABC-AABF-A3C586FB4A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CA3646-6613-4DC1-A7CE-476EF181E24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_brush_foe_v8" sheetId="2" r:id="rId1"/>
@@ -2522,10 +2522,10 @@
     <t>50,30</t>
   </si>
   <si>
-    <t>5,20,75,15</t>
-  </si>
-  <si>
-    <t>95,15,25,10</t>
+    <t>5,20</t>
+  </si>
+  <si>
+    <t>95,15,25,10,75,15</t>
   </si>
 </sst>
 </file>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30CA3646-6613-4DC1-A7CE-476EF181E24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B03C2A-F01E-4E82-AA33-8E34B891C321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="795">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2493,26 +2493,6 @@
     <t>91105,91105</t>
   </si>
   <si>
-    <t>91106,91106</t>
-  </si>
-  <si>
-    <t>91105,91105,91105</t>
-  </si>
-  <si>
-    <t>91106,91105</t>
-  </si>
-  <si>
-    <t>91106,91106,91105</t>
-  </si>
-  <si>
-    <t>91105</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>91105,91105,91105</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>50,55</t>
   </si>
   <si>
@@ -2526,6 +2506,27 @@
   </si>
   <si>
     <t>95,15,25,10,75,15</t>
+  </si>
+  <si>
+    <t>91101</t>
+  </si>
+  <si>
+    <t>91102,91102</t>
+  </si>
+  <si>
+    <t>91103</t>
+  </si>
+  <si>
+    <t>91103,91104,91104</t>
+  </si>
+  <si>
+    <t>91101,91101,91101</t>
+  </si>
+  <si>
+    <t>91102,91101</t>
+  </si>
+  <si>
+    <t>91102,91102,91101</t>
   </si>
 </sst>
 </file>
@@ -63092,7 +63093,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -63107,7 +63108,7 @@
         <v>0</v>
       </c>
       <c r="O1068" s="1" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="P1068" s="1">
         <v>0</v>
@@ -63142,7 +63143,7 @@
         <v>1</v>
       </c>
       <c r="J1069" s="2" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="K1069" s="1">
         <v>100</v>
@@ -63157,7 +63158,7 @@
         <v>0</v>
       </c>
       <c r="O1069" s="1" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="P1069" s="1">
         <v>0</v>
@@ -63192,7 +63193,7 @@
         <v>1</v>
       </c>
       <c r="J1070" s="2" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="K1070" s="1">
         <v>100</v>
@@ -63207,7 +63208,7 @@
         <v>0</v>
       </c>
       <c r="O1070" s="1" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="P1070" s="1">
         <v>0</v>
@@ -63242,7 +63243,7 @@
         <v>2</v>
       </c>
       <c r="J1071" s="2" t="s">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="K1071" s="1">
         <v>100</v>
@@ -63257,7 +63258,7 @@
         <v>0</v>
       </c>
       <c r="O1071" s="1" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="P1071" s="1">
         <v>0</v>
@@ -63292,7 +63293,7 @@
         <v>2</v>
       </c>
       <c r="J1072" s="2" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="K1072" s="1">
         <v>100</v>
@@ -63307,7 +63308,7 @@
         <v>0</v>
       </c>
       <c r="O1072" s="1" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="P1072" s="1">
         <v>0</v>
@@ -63342,7 +63343,7 @@
         <v>2</v>
       </c>
       <c r="J1073" s="2" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="K1073" s="1">
         <v>100</v>
@@ -63357,7 +63358,7 @@
         <v>0</v>
       </c>
       <c r="O1073" s="1" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="P1073" s="1">
         <v>0</v>
@@ -63492,7 +63493,7 @@
         <v>3</v>
       </c>
       <c r="J1076" s="2" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="K1076" s="1">
         <v>100</v>
@@ -63542,7 +63543,7 @@
         <v>3</v>
       </c>
       <c r="J1077" s="2" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="K1077" s="1">
         <v>100</v>
@@ -63592,7 +63593,7 @@
         <v>4</v>
       </c>
       <c r="J1078" s="2" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="K1078" s="1">
         <v>100</v>
@@ -63642,7 +63643,7 @@
         <v>4</v>
       </c>
       <c r="J1079" s="2" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="K1079" s="1">
         <v>100</v>
@@ -63692,7 +63693,7 @@
         <v>4</v>
       </c>
       <c r="J1080" s="2" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="K1080" s="1">
         <v>100</v>
@@ -63742,7 +63743,7 @@
         <v>4</v>
       </c>
       <c r="J1081" s="2" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="K1081" s="1">
         <v>100</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B03C2A-F01E-4E82-AA33-8E34B891C321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A76BF84-1768-4CDE-BB04-BFA194F64E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="806">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2527,6 +2527,39 @@
   </si>
   <si>
     <t>91102,91102,91101</t>
+  </si>
+  <si>
+    <t>10,45</t>
+  </si>
+  <si>
+    <t>10,55,35,65</t>
+  </si>
+  <si>
+    <t>10,60</t>
+  </si>
+  <si>
+    <t>55,62</t>
+  </si>
+  <si>
+    <t>45,75,45,95</t>
+  </si>
+  <si>
+    <t>70,95,80,95</t>
+  </si>
+  <si>
+    <t>111101</t>
+  </si>
+  <si>
+    <t>111101,111104</t>
+  </si>
+  <si>
+    <t>111102</t>
+  </si>
+  <si>
+    <t>111102,111105</t>
+  </si>
+  <si>
+    <t>111105,111105</t>
   </si>
 </sst>
 </file>
@@ -3339,7 +3372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1081"/>
+  <dimension ref="A1:R1087"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -63770,6 +63803,306 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1082" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1082" s="1">
+        <v>1110101</v>
+      </c>
+      <c r="B1082" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1082" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1082" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1082" s="1">
+        <v>1</v>
+      </c>
+      <c r="H1082" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1082" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1082" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="K1082" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1082" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1082" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="P1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1082" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1083" s="1">
+        <v>1110102</v>
+      </c>
+      <c r="B1083" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1083" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1083" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1083" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1083" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1083" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1083" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="K1083" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1083" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1083" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1083" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1083" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="P1083" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1083" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1083" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1084" s="1">
+        <v>1110103</v>
+      </c>
+      <c r="B1084" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1084" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1084" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1084" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1084" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1084" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1084" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="K1084" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1084" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1084" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1084" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1084" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="P1084" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1084" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1084" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1085" s="1">
+        <v>1110201</v>
+      </c>
+      <c r="B1085" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1085" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1085" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1085" s="1">
+        <v>4</v>
+      </c>
+      <c r="H1085" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1085" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1085" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="K1085" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1085" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1085" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1085" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1085" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="P1085" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1085" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1085" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1086" s="1">
+        <v>1110202</v>
+      </c>
+      <c r="B1086" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1086" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1086" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1086" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1086" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1086" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1086" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="K1086" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1086" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1086" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1086" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1086" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="P1086" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1086" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1086" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1087" s="1">
+        <v>1110203</v>
+      </c>
+      <c r="B1087" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1087" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1087" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1087" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1087" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1087" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1087" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="K1087" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1087" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1087" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="P1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1087" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2:A1012">

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A76BF84-1768-4CDE-BB04-BFA194F64E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5140F13-EE70-4944-B01F-0E2987771F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="827">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2529,37 +2529,100 @@
     <t>91102,91102,91101</t>
   </si>
   <si>
-    <t>10,45</t>
-  </si>
-  <si>
-    <t>10,55,35,65</t>
-  </si>
-  <si>
-    <t>10,60</t>
-  </si>
-  <si>
-    <t>55,62</t>
-  </si>
-  <si>
-    <t>45,75,45,95</t>
-  </si>
-  <si>
-    <t>70,95,80,95</t>
-  </si>
-  <si>
     <t>111101</t>
   </si>
   <si>
     <t>111101,111104</t>
   </si>
   <si>
-    <t>111102</t>
-  </si>
-  <si>
-    <t>111102,111105</t>
-  </si>
-  <si>
     <t>111105,111105</t>
+  </si>
+  <si>
+    <t>12,15</t>
+  </si>
+  <si>
+    <t>25,27,12,35</t>
+  </si>
+  <si>
+    <t>3,25</t>
+  </si>
+  <si>
+    <t>12,45</t>
+  </si>
+  <si>
+    <t>25,57,18,65</t>
+  </si>
+  <si>
+    <t>2,50,33,50</t>
+  </si>
+  <si>
+    <t>40,67</t>
+  </si>
+  <si>
+    <t>40,58,57,62</t>
+  </si>
+  <si>
+    <t>40,67,52,72</t>
+  </si>
+  <si>
+    <t>42,70,42,62</t>
+  </si>
+  <si>
+    <t>15,70,15,60</t>
+  </si>
+  <si>
+    <t>44,35,44,25</t>
+  </si>
+  <si>
+    <t>12,35,18,35,27,24</t>
+  </si>
+  <si>
+    <t>15,35,12,30,18,24</t>
+  </si>
+  <si>
+    <t>12,30,12,30</t>
+  </si>
+  <si>
+    <t>12,47,12,67</t>
+  </si>
+  <si>
+    <t>18,55,15,60,52,63</t>
+  </si>
+  <si>
+    <t>45,90,50,88,55,86</t>
+  </si>
+  <si>
+    <t>58,91,65,94,93,92</t>
+  </si>
+  <si>
+    <t>65,88,65,94,93,84</t>
+  </si>
+  <si>
+    <t>65,91,70,88,70,94,93,76</t>
+  </si>
+  <si>
+    <t>111105</t>
+  </si>
+  <si>
+    <t>111105,111104</t>
+  </si>
+  <si>
+    <t>111101,111101</t>
+  </si>
+  <si>
+    <t>111102,111104</t>
+  </si>
+  <si>
+    <t>111101,111101,111104</t>
+  </si>
+  <si>
+    <t>111102,111101,111104</t>
+  </si>
+  <si>
+    <t>111105,111105,111105</t>
+  </si>
+  <si>
+    <t>111102,111105,111105,111104</t>
   </si>
 </sst>
 </file>
@@ -2855,7 +2918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3053,6 +3116,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3372,7 +3438,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1087"/>
+  <dimension ref="A1:R1102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -63810,6 +63876,9 @@
       <c r="B1082" s="1">
         <v>11</v>
       </c>
+      <c r="D1082" s="1">
+        <v>1</v>
+      </c>
       <c r="E1082" s="1">
         <v>110001</v>
       </c>
@@ -63819,17 +63888,17 @@
       <c r="G1082" s="1">
         <v>1</v>
       </c>
-      <c r="H1082" s="1">
+      <c r="H1082" s="67">
         <v>5000</v>
       </c>
       <c r="I1082" s="1">
         <v>1</v>
       </c>
       <c r="J1082" s="2" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="K1082" s="1">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="L1082" s="1">
         <v>30000</v>
@@ -63841,7 +63910,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -63860,6 +63929,9 @@
       <c r="B1083" s="1">
         <v>11</v>
       </c>
+      <c r="D1083" s="1">
+        <v>1</v>
+      </c>
       <c r="E1083" s="1">
         <v>110001</v>
       </c>
@@ -63869,17 +63941,17 @@
       <c r="G1083" s="1">
         <v>2</v>
       </c>
-      <c r="H1083" s="1">
+      <c r="H1083" s="67">
         <v>5000</v>
       </c>
       <c r="I1083" s="1">
         <v>1</v>
       </c>
       <c r="J1083" s="2" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="K1083" s="1">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="L1083" s="1">
         <v>30000</v>
@@ -63891,7 +63963,7 @@
         <v>0</v>
       </c>
       <c r="O1083" s="1" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="P1083" s="1">
         <v>0</v>
@@ -63910,6 +63982,9 @@
       <c r="B1084" s="1">
         <v>11</v>
       </c>
+      <c r="D1084" s="1">
+        <v>1</v>
+      </c>
       <c r="E1084" s="1">
         <v>110001</v>
       </c>
@@ -63919,17 +63994,17 @@
       <c r="G1084" s="1">
         <v>3</v>
       </c>
-      <c r="H1084" s="1">
-        <v>5000</v>
+      <c r="H1084" s="67">
+        <v>10000</v>
       </c>
       <c r="I1084" s="1">
         <v>1</v>
       </c>
       <c r="J1084" s="2" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="K1084" s="1">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="L1084" s="1">
         <v>30000</v>
@@ -63941,7 +64016,7 @@
         <v>0</v>
       </c>
       <c r="O1084" s="1" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="P1084" s="1">
         <v>0</v>
@@ -63950,7 +64025,7 @@
         <v>0</v>
       </c>
       <c r="R1084" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1085" spans="1:18" x14ac:dyDescent="0.2">
@@ -63960,6 +64035,9 @@
       <c r="B1085" s="1">
         <v>11</v>
       </c>
+      <c r="D1085" s="1">
+        <v>1</v>
+      </c>
       <c r="E1085" s="1">
         <v>110001</v>
       </c>
@@ -63969,17 +64047,17 @@
       <c r="G1085" s="1">
         <v>4</v>
       </c>
-      <c r="H1085" s="1">
-        <v>5000</v>
+      <c r="H1085" s="67">
+        <v>4000</v>
       </c>
       <c r="I1085" s="1">
         <v>2</v>
       </c>
       <c r="J1085" s="2" t="s">
-        <v>803</v>
+        <v>819</v>
       </c>
       <c r="K1085" s="1">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="L1085" s="1">
         <v>30000</v>
@@ -63991,7 +64069,7 @@
         <v>0</v>
       </c>
       <c r="O1085" s="1" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="P1085" s="1">
         <v>0</v>
@@ -64000,7 +64078,7 @@
         <v>0</v>
       </c>
       <c r="R1085" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1086" spans="1:18" x14ac:dyDescent="0.2">
@@ -64010,6 +64088,9 @@
       <c r="B1086" s="1">
         <v>11</v>
       </c>
+      <c r="D1086" s="1">
+        <v>1</v>
+      </c>
       <c r="E1086" s="1">
         <v>110001</v>
       </c>
@@ -64019,17 +64100,17 @@
       <c r="G1086" s="1">
         <v>5</v>
       </c>
-      <c r="H1086" s="1">
-        <v>5000</v>
+      <c r="H1086" s="67">
+        <v>4000</v>
       </c>
       <c r="I1086" s="1">
         <v>2</v>
       </c>
       <c r="J1086" s="2" t="s">
-        <v>804</v>
+        <v>820</v>
       </c>
       <c r="K1086" s="1">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="L1086" s="1">
         <v>30000</v>
@@ -64041,7 +64122,7 @@
         <v>0</v>
       </c>
       <c r="O1086" s="1" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="P1086" s="1">
         <v>0</v>
@@ -64060,6 +64141,9 @@
       <c r="B1087" s="1">
         <v>11</v>
       </c>
+      <c r="D1087" s="1">
+        <v>1</v>
+      </c>
       <c r="E1087" s="1">
         <v>110001</v>
       </c>
@@ -64069,37 +64153,832 @@
       <c r="G1087" s="1">
         <v>6</v>
       </c>
-      <c r="H1087" s="1">
-        <v>1</v>
+      <c r="H1087" s="67">
+        <v>9000</v>
       </c>
       <c r="I1087" s="1">
         <v>2</v>
       </c>
       <c r="J1087" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="K1087" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1087" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1087" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="P1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1087" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1088" s="1">
+        <v>1110301</v>
+      </c>
+      <c r="B1088" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1088" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1088" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1088" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1088" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1088" s="67">
+        <v>3500</v>
+      </c>
+      <c r="I1088" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1088" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="K1088" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1088" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1088" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1088" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1088" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="P1088" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1088" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1088" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1089" s="1">
+        <v>1110302</v>
+      </c>
+      <c r="B1089" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1089" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1089" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1089" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1089" s="1">
+        <v>8</v>
+      </c>
+      <c r="H1089" s="67">
+        <v>3500</v>
+      </c>
+      <c r="I1089" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1089" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="K1089" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1089" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1089" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1089" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1089" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="K1087" s="1">
-        <v>150</v>
-      </c>
-      <c r="L1087" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1087" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1087" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1087" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="P1087" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1087" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1087" s="1">
+      <c r="P1089" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1089" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1089" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1090" s="1">
+        <v>1110303</v>
+      </c>
+      <c r="B1090" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1090" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1090" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1090" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1090" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1090" s="67">
+        <v>4500</v>
+      </c>
+      <c r="I1090" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1090" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="K1090" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1090" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1090" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1090" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1090" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="P1090" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1090" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1090" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1091" s="1">
+        <v>1110304</v>
+      </c>
+      <c r="B1091" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1091" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1091" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1091" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1091" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1091" s="67">
+        <v>8000</v>
+      </c>
+      <c r="I1091" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1091" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="K1091" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1091" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1091" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1091" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1091" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="P1091" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1091" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1091" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1092" s="1">
+        <v>1110401</v>
+      </c>
+      <c r="B1092" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1092" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1092" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1092" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1092" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1092" s="67">
+        <v>3500</v>
+      </c>
+      <c r="I1092" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1092" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="K1092" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1092" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1092" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1092" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1092" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="P1092" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1092" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1092" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1093" s="1">
+        <v>1110402</v>
+      </c>
+      <c r="B1093" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1093" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1093" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1093" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1093" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1093" s="67">
+        <v>4500</v>
+      </c>
+      <c r="I1093" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1093" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="K1093" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1093" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1093" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1093" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1093" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="P1093" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1093" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1093" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1094" s="1">
+        <v>1110403</v>
+      </c>
+      <c r="B1094" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1094" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1094" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1094" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1094" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1094" s="67">
+        <v>3500</v>
+      </c>
+      <c r="I1094" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1094" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="K1094" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1094" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1094" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1094" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1094" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="P1094" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1094" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1094" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1095" s="1">
+        <v>1110404</v>
+      </c>
+      <c r="B1095" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1095" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1095" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1095" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1095" s="1">
+        <v>14</v>
+      </c>
+      <c r="H1095" s="67">
+        <v>4500</v>
+      </c>
+      <c r="I1095" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1095" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K1095" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1095" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1095" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1095" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1095" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="P1095" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1095" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1095" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1096" s="1">
+        <v>1110405</v>
+      </c>
+      <c r="B1096" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1096" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1096" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1096" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1096" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1096" s="67">
+        <v>7500</v>
+      </c>
+      <c r="I1096" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1096" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="K1096" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1096" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1096" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1096" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1096" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="P1096" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1096" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1096" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1097" s="1">
+        <v>1110501</v>
+      </c>
+      <c r="B1097" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1097" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1097" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1097" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1097" s="1">
+        <v>16</v>
+      </c>
+      <c r="H1097" s="67">
+        <v>3000</v>
+      </c>
+      <c r="I1097" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1097" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="K1097" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1097" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1097" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1097" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1097" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="P1097" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1097" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1097" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1098" s="1">
+        <v>1110502</v>
+      </c>
+      <c r="B1098" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1098" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1098" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1098" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1098" s="1">
+        <v>17</v>
+      </c>
+      <c r="H1098" s="67">
+        <v>4000</v>
+      </c>
+      <c r="I1098" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1098" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K1098" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1098" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1098" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1098" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1098" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="P1098" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1098" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1098" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1099" s="1">
+        <v>1110503</v>
+      </c>
+      <c r="B1099" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1099" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1099" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1099" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1099" s="1">
+        <v>18</v>
+      </c>
+      <c r="H1099" s="67">
+        <v>3000</v>
+      </c>
+      <c r="I1099" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1099" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="K1099" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1099" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1099" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1099" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1099" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="P1099" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1099" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1099" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1100" s="1">
+        <v>1110504</v>
+      </c>
+      <c r="B1100" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1100" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1100" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1100" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1100" s="1">
+        <v>19</v>
+      </c>
+      <c r="H1100" s="67">
+        <v>4000</v>
+      </c>
+      <c r="I1100" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1100" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K1100" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1100" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1100" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1100" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1100" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="P1100" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1100" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1101" s="1">
+        <v>1110505</v>
+      </c>
+      <c r="B1101" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1101" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1101" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1101" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1101" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1101" s="67">
+        <v>3000</v>
+      </c>
+      <c r="I1101" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1101" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="K1101" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1101" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1101" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1101" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1101" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="P1101" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1101" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1102" s="1">
+        <v>1110506</v>
+      </c>
+      <c r="B1102" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1102" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1102" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1102" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1102" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1102" s="67">
+        <v>1</v>
+      </c>
+      <c r="I1102" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1102" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="K1102" s="1">
+        <v>60</v>
+      </c>
+      <c r="L1102" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1102" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1102" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1102" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="P1102" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1102" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1102" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5140F13-EE70-4944-B01F-0E2987771F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C622EC81-FEDD-4B83-9BC9-721204D1A71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2538,12 +2538,6 @@
     <t>111105,111105</t>
   </si>
   <si>
-    <t>12,15</t>
-  </si>
-  <si>
-    <t>25,27,12,35</t>
-  </si>
-  <si>
     <t>3,25</t>
   </si>
   <si>
@@ -2623,6 +2617,12 @@
   </si>
   <si>
     <t>111102,111105,111105,111104</t>
+  </si>
+  <si>
+    <t>10,10</t>
+  </si>
+  <si>
+    <t>25,27,12,40</t>
   </si>
 </sst>
 </file>
@@ -63910,7 +63910,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>798</v>
+        <v>825</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -63963,7 +63963,7 @@
         <v>0</v>
       </c>
       <c r="O1083" s="1" t="s">
-        <v>799</v>
+        <v>826</v>
       </c>
       <c r="P1083" s="1">
         <v>0</v>
@@ -64016,7 +64016,7 @@
         <v>0</v>
       </c>
       <c r="O1084" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="P1084" s="1">
         <v>0</v>
@@ -64054,7 +64054,7 @@
         <v>2</v>
       </c>
       <c r="J1085" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="K1085" s="1">
         <v>60</v>
@@ -64069,7 +64069,7 @@
         <v>0</v>
       </c>
       <c r="O1085" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="P1085" s="1">
         <v>0</v>
@@ -64107,7 +64107,7 @@
         <v>2</v>
       </c>
       <c r="J1086" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="K1086" s="1">
         <v>60</v>
@@ -64122,7 +64122,7 @@
         <v>0</v>
       </c>
       <c r="O1086" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="P1086" s="1">
         <v>0</v>
@@ -64160,7 +64160,7 @@
         <v>2</v>
       </c>
       <c r="J1087" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="K1087" s="1">
         <v>60</v>
@@ -64175,7 +64175,7 @@
         <v>0</v>
       </c>
       <c r="O1087" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="P1087" s="1">
         <v>0</v>
@@ -64228,7 +64228,7 @@
         <v>0</v>
       </c>
       <c r="O1088" s="1" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="P1088" s="1">
         <v>0</v>
@@ -64281,7 +64281,7 @@
         <v>0</v>
       </c>
       <c r="O1089" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="P1089" s="1">
         <v>0</v>
@@ -64319,7 +64319,7 @@
         <v>3</v>
       </c>
       <c r="J1090" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="K1090" s="1">
         <v>60</v>
@@ -64334,7 +64334,7 @@
         <v>0</v>
       </c>
       <c r="O1090" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="P1090" s="1">
         <v>0</v>
@@ -64387,7 +64387,7 @@
         <v>0</v>
       </c>
       <c r="O1091" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="P1091" s="1">
         <v>0</v>
@@ -64440,7 +64440,7 @@
         <v>0</v>
       </c>
       <c r="O1092" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="P1092" s="1">
         <v>0</v>
@@ -64478,7 +64478,7 @@
         <v>4</v>
       </c>
       <c r="J1093" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="K1093" s="1">
         <v>60</v>
@@ -64493,7 +64493,7 @@
         <v>0</v>
       </c>
       <c r="O1093" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="P1093" s="1">
         <v>0</v>
@@ -64531,7 +64531,7 @@
         <v>4</v>
       </c>
       <c r="J1094" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="K1094" s="1">
         <v>60</v>
@@ -64546,7 +64546,7 @@
         <v>0</v>
       </c>
       <c r="O1094" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="P1094" s="1">
         <v>0</v>
@@ -64584,7 +64584,7 @@
         <v>4</v>
       </c>
       <c r="J1095" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K1095" s="1">
         <v>60</v>
@@ -64599,7 +64599,7 @@
         <v>0</v>
       </c>
       <c r="O1095" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="P1095" s="1">
         <v>0</v>
@@ -64652,7 +64652,7 @@
         <v>0</v>
       </c>
       <c r="O1096" s="1" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="P1096" s="1">
         <v>0</v>
@@ -64705,7 +64705,7 @@
         <v>0</v>
       </c>
       <c r="O1097" s="1" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="P1097" s="1">
         <v>0</v>
@@ -64743,7 +64743,7 @@
         <v>5</v>
       </c>
       <c r="J1098" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K1098" s="1">
         <v>60</v>
@@ -64758,7 +64758,7 @@
         <v>0</v>
       </c>
       <c r="O1098" s="1" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="P1098" s="1">
         <v>0</v>
@@ -64796,7 +64796,7 @@
         <v>5</v>
       </c>
       <c r="J1099" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="K1099" s="1">
         <v>60</v>
@@ -64811,7 +64811,7 @@
         <v>0</v>
       </c>
       <c r="O1099" s="1" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="P1099" s="1">
         <v>0</v>
@@ -64849,7 +64849,7 @@
         <v>5</v>
       </c>
       <c r="J1100" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K1100" s="1">
         <v>60</v>
@@ -64864,7 +64864,7 @@
         <v>0</v>
       </c>
       <c r="O1100" s="1" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="P1100" s="1">
         <v>0</v>
@@ -64902,7 +64902,7 @@
         <v>5</v>
       </c>
       <c r="J1101" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="K1101" s="1">
         <v>60</v>
@@ -64917,7 +64917,7 @@
         <v>0</v>
       </c>
       <c r="O1101" s="1" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="P1101" s="1">
         <v>0</v>
@@ -64955,7 +64955,7 @@
         <v>5</v>
       </c>
       <c r="J1102" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K1102" s="1">
         <v>60</v>
@@ -64970,7 +64970,7 @@
         <v>0</v>
       </c>
       <c r="O1102" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="P1102" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C622EC81-FEDD-4B83-9BC9-721204D1A71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B75E44-C46F-4C9F-A537-EF3467B61417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="828">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2623,6 +2623,9 @@
   </si>
   <si>
     <t>25,27,12,40</t>
+  </si>
+  <si>
+    <t>111104</t>
   </si>
 </sst>
 </file>
@@ -63889,13 +63892,13 @@
         <v>1</v>
       </c>
       <c r="H1082" s="67">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I1082" s="1">
         <v>1</v>
       </c>
       <c r="J1082" s="2" t="s">
-        <v>795</v>
+        <v>827</v>
       </c>
       <c r="K1082" s="1">
         <v>60</v>
@@ -63942,7 +63945,7 @@
         <v>2</v>
       </c>
       <c r="H1083" s="67">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I1083" s="1">
         <v>1</v>
@@ -63995,7 +63998,7 @@
         <v>3</v>
       </c>
       <c r="H1084" s="67">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="I1084" s="1">
         <v>1</v>
@@ -64048,7 +64051,7 @@
         <v>4</v>
       </c>
       <c r="H1085" s="67">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I1085" s="1">
         <v>2</v>
@@ -64154,7 +64157,7 @@
         <v>6</v>
       </c>
       <c r="H1087" s="67">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="I1087" s="1">
         <v>2</v>
@@ -64207,7 +64210,7 @@
         <v>7</v>
       </c>
       <c r="H1088" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1088" s="1">
         <v>3</v>
@@ -64260,7 +64263,7 @@
         <v>8</v>
       </c>
       <c r="H1089" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1089" s="1">
         <v>3</v>
@@ -64313,7 +64316,7 @@
         <v>9</v>
       </c>
       <c r="H1090" s="67">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I1090" s="1">
         <v>3</v>
@@ -64366,7 +64369,7 @@
         <v>10</v>
       </c>
       <c r="H1091" s="67">
-        <v>8000</v>
+        <v>3500</v>
       </c>
       <c r="I1091" s="1">
         <v>3</v>
@@ -64419,7 +64422,7 @@
         <v>11</v>
       </c>
       <c r="H1092" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1092" s="1">
         <v>4</v>
@@ -64472,7 +64475,7 @@
         <v>12</v>
       </c>
       <c r="H1093" s="67">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I1093" s="1">
         <v>4</v>
@@ -64525,7 +64528,7 @@
         <v>13</v>
       </c>
       <c r="H1094" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1094" s="1">
         <v>4</v>
@@ -64578,7 +64581,7 @@
         <v>14</v>
       </c>
       <c r="H1095" s="67">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I1095" s="1">
         <v>4</v>
@@ -64631,7 +64634,7 @@
         <v>15</v>
       </c>
       <c r="H1096" s="67">
-        <v>7500</v>
+        <v>2500</v>
       </c>
       <c r="I1096" s="1">
         <v>4</v>
@@ -64684,7 +64687,7 @@
         <v>16</v>
       </c>
       <c r="H1097" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1097" s="1">
         <v>5</v>
@@ -64737,7 +64740,7 @@
         <v>17</v>
       </c>
       <c r="H1098" s="67">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I1098" s="1">
         <v>5</v>
@@ -64790,7 +64793,7 @@
         <v>18</v>
       </c>
       <c r="H1099" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1099" s="1">
         <v>5</v>
@@ -64843,7 +64846,7 @@
         <v>19</v>
       </c>
       <c r="H1100" s="67">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I1100" s="1">
         <v>5</v>
@@ -64896,7 +64899,7 @@
         <v>20</v>
       </c>
       <c r="H1101" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1101" s="1">
         <v>5</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B75E44-C46F-4C9F-A537-EF3467B61417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF9716F-1E42-457A-B4E2-293D919563D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63892,7 +63892,7 @@
         <v>1</v>
       </c>
       <c r="H1082" s="67">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="I1082" s="1">
         <v>1</v>
@@ -63945,7 +63945,7 @@
         <v>2</v>
       </c>
       <c r="H1083" s="67">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="I1083" s="1">
         <v>1</v>
@@ -63998,7 +63998,7 @@
         <v>3</v>
       </c>
       <c r="H1084" s="67">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="I1084" s="1">
         <v>1</v>
@@ -64051,7 +64051,7 @@
         <v>4</v>
       </c>
       <c r="H1085" s="67">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="I1085" s="1">
         <v>2</v>
@@ -64104,7 +64104,7 @@
         <v>5</v>
       </c>
       <c r="H1086" s="67">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="I1086" s="1">
         <v>2</v>
@@ -64157,7 +64157,7 @@
         <v>6</v>
       </c>
       <c r="H1087" s="67">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="I1087" s="1">
         <v>2</v>
@@ -64210,7 +64210,7 @@
         <v>7</v>
       </c>
       <c r="H1088" s="67">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I1088" s="1">
         <v>3</v>
@@ -64263,7 +64263,7 @@
         <v>8</v>
       </c>
       <c r="H1089" s="67">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I1089" s="1">
         <v>3</v>
@@ -64316,7 +64316,7 @@
         <v>9</v>
       </c>
       <c r="H1090" s="67">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="I1090" s="1">
         <v>3</v>
@@ -64369,7 +64369,7 @@
         <v>10</v>
       </c>
       <c r="H1091" s="67">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="I1091" s="1">
         <v>3</v>
@@ -64422,7 +64422,7 @@
         <v>11</v>
       </c>
       <c r="H1092" s="67">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I1092" s="1">
         <v>4</v>
@@ -64475,7 +64475,7 @@
         <v>12</v>
       </c>
       <c r="H1093" s="67">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="I1093" s="1">
         <v>4</v>
@@ -64528,7 +64528,7 @@
         <v>13</v>
       </c>
       <c r="H1094" s="67">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I1094" s="1">
         <v>4</v>
@@ -64581,7 +64581,7 @@
         <v>14</v>
       </c>
       <c r="H1095" s="67">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="I1095" s="1">
         <v>4</v>
@@ -64634,7 +64634,7 @@
         <v>15</v>
       </c>
       <c r="H1096" s="67">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I1096" s="1">
         <v>4</v>
@@ -64687,7 +64687,7 @@
         <v>16</v>
       </c>
       <c r="H1097" s="67">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I1097" s="1">
         <v>5</v>
@@ -64740,7 +64740,7 @@
         <v>17</v>
       </c>
       <c r="H1098" s="67">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="I1098" s="1">
         <v>5</v>
@@ -64793,7 +64793,7 @@
         <v>18</v>
       </c>
       <c r="H1099" s="67">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I1099" s="1">
         <v>5</v>
@@ -64846,7 +64846,7 @@
         <v>19</v>
       </c>
       <c r="H1100" s="67">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="I1100" s="1">
         <v>5</v>
@@ -64899,7 +64899,7 @@
         <v>20</v>
       </c>
       <c r="H1101" s="67">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I1101" s="1">
         <v>5</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF9716F-1E42-457A-B4E2-293D919563D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE22E96-3B87-48CA-994A-165AA5CB06BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_brush_foe_v8" sheetId="2" r:id="rId1"/>
@@ -2619,13 +2619,14 @@
     <t>111102,111105,111105,111104</t>
   </si>
   <si>
-    <t>10,10</t>
-  </si>
-  <si>
     <t>25,27,12,40</t>
   </si>
   <si>
     <t>111104</t>
+  </si>
+  <si>
+    <t>10,13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -63898,7 +63899,7 @@
         <v>1</v>
       </c>
       <c r="J1082" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K1082" s="1">
         <v>60</v>
@@ -63913,7 +63914,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -63966,7 +63967,7 @@
         <v>0</v>
       </c>
       <c r="O1083" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="P1083" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE22E96-3B87-48CA-994A-165AA5CB06BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E80116-5012-4E70-A766-2AF05F830EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_brush_foe_v8" sheetId="2" r:id="rId1"/>
@@ -63893,7 +63893,7 @@
         <v>1</v>
       </c>
       <c r="H1082" s="67">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I1082" s="1">
         <v>1</v>
@@ -63946,7 +63946,7 @@
         <v>2</v>
       </c>
       <c r="H1083" s="67">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I1083" s="1">
         <v>1</v>
@@ -63999,7 +63999,7 @@
         <v>3</v>
       </c>
       <c r="H1084" s="67">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I1084" s="1">
         <v>1</v>
@@ -64052,7 +64052,7 @@
         <v>4</v>
       </c>
       <c r="H1085" s="67">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I1085" s="1">
         <v>2</v>
@@ -64105,7 +64105,7 @@
         <v>5</v>
       </c>
       <c r="H1086" s="67">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I1086" s="1">
         <v>2</v>
@@ -64158,7 +64158,7 @@
         <v>6</v>
       </c>
       <c r="H1087" s="67">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I1087" s="1">
         <v>2</v>
@@ -64317,7 +64317,7 @@
         <v>9</v>
       </c>
       <c r="H1090" s="67">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I1090" s="1">
         <v>3</v>
@@ -64370,7 +64370,7 @@
         <v>10</v>
       </c>
       <c r="H1091" s="67">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I1091" s="1">
         <v>3</v>
@@ -64476,7 +64476,7 @@
         <v>12</v>
       </c>
       <c r="H1093" s="67">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I1093" s="1">
         <v>4</v>
@@ -64582,7 +64582,7 @@
         <v>14</v>
       </c>
       <c r="H1095" s="67">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I1095" s="1">
         <v>4</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E80116-5012-4E70-A766-2AF05F830EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7547D406-6890-405F-B4A4-716AC99FD988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63893,7 +63893,7 @@
         <v>1</v>
       </c>
       <c r="H1082" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1082" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7547D406-6890-405F-B4A4-716AC99FD988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4028B409-4CA0-4612-A1E9-8D7FE8C49B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="829">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2595,9 +2595,6 @@
     <t>65,91,70,88,70,94,93,76</t>
   </si>
   <si>
-    <t>111105</t>
-  </si>
-  <si>
     <t>111105,111104</t>
   </si>
   <si>
@@ -2608,9 +2605,6 @@
   </si>
   <si>
     <t>111101,111101,111104</t>
-  </si>
-  <si>
-    <t>111102,111101,111104</t>
   </si>
   <si>
     <t>111105,111105,111105</t>
@@ -2627,6 +2621,16 @@
   <si>
     <t>10,13</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>111113</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>111105,111105,111104</t>
+  </si>
+  <si>
+    <t>111102,111105,111104</t>
   </si>
 </sst>
 </file>
@@ -63196,7 +63200,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>788</v>
+        <v>826</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -63220,7 +63224,7 @@
         <v>0</v>
       </c>
       <c r="R1068" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1069" spans="1:18" x14ac:dyDescent="0.2">
@@ -63899,7 +63903,7 @@
         <v>1</v>
       </c>
       <c r="J1082" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K1082" s="1">
         <v>60</v>
@@ -63914,7 +63918,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -63967,7 +63971,7 @@
         <v>0</v>
       </c>
       <c r="O1083" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="P1083" s="1">
         <v>0</v>
@@ -64058,7 +64062,7 @@
         <v>2</v>
       </c>
       <c r="J1085" s="2" t="s">
-        <v>817</v>
+        <v>795</v>
       </c>
       <c r="K1085" s="1">
         <v>60</v>
@@ -64111,7 +64115,7 @@
         <v>2</v>
       </c>
       <c r="J1086" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="K1086" s="1">
         <v>60</v>
@@ -64164,7 +64168,7 @@
         <v>2</v>
       </c>
       <c r="J1087" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="K1087" s="1">
         <v>60</v>
@@ -64323,7 +64327,7 @@
         <v>3</v>
       </c>
       <c r="J1090" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="K1090" s="1">
         <v>60</v>
@@ -64400,7 +64404,7 @@
         <v>0</v>
       </c>
       <c r="R1091" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1092" spans="1:18" x14ac:dyDescent="0.2">
@@ -64482,7 +64486,7 @@
         <v>4</v>
       </c>
       <c r="J1093" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="K1093" s="1">
         <v>60</v>
@@ -64535,7 +64539,7 @@
         <v>4</v>
       </c>
       <c r="J1094" s="2" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="K1094" s="1">
         <v>60</v>
@@ -64588,7 +64592,7 @@
         <v>4</v>
       </c>
       <c r="J1095" s="2" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="K1095" s="1">
         <v>60</v>
@@ -64747,7 +64751,7 @@
         <v>5</v>
       </c>
       <c r="J1098" s="2" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="K1098" s="1">
         <v>60</v>
@@ -64800,7 +64804,7 @@
         <v>5</v>
       </c>
       <c r="J1099" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="K1099" s="1">
         <v>60</v>
@@ -64824,7 +64828,7 @@
         <v>0</v>
       </c>
       <c r="R1099" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1100" spans="1:18" x14ac:dyDescent="0.2">
@@ -64853,7 +64857,7 @@
         <v>5</v>
       </c>
       <c r="J1100" s="2" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="K1100" s="1">
         <v>60</v>
@@ -64906,7 +64910,7 @@
         <v>5</v>
       </c>
       <c r="J1101" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="K1101" s="1">
         <v>60</v>
@@ -64959,7 +64963,7 @@
         <v>5</v>
       </c>
       <c r="J1102" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K1102" s="1">
         <v>60</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4028B409-4CA0-4612-A1E9-8D7FE8C49B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8C0F0A-C8F4-43B5-9B31-101B30DE80A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="829">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="843">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2631,6 +2631,48 @@
   </si>
   <si>
     <t>111102,111105,111104</t>
+  </si>
+  <si>
+    <t>112113</t>
+  </si>
+  <si>
+    <t>112101,112101,112101</t>
+  </si>
+  <si>
+    <t>112104,112104</t>
+  </si>
+  <si>
+    <t>112102,112101,112101</t>
+  </si>
+  <si>
+    <t>112105,112105</t>
+  </si>
+  <si>
+    <t>112105,112105,112105</t>
+  </si>
+  <si>
+    <t>50,66</t>
+  </si>
+  <si>
+    <t>50,85,20,56,80,56</t>
+  </si>
+  <si>
+    <t>11,98,22,98</t>
+  </si>
+  <si>
+    <t>98,55,98,42,98,68</t>
+  </si>
+  <si>
+    <t>17,45,17,35</t>
+  </si>
+  <si>
+    <t>2,55,2,42,2,68</t>
+  </si>
+  <si>
+    <t>78,98,89,98</t>
+  </si>
+  <si>
+    <t>83,48,83,40,83,32</t>
   </si>
 </sst>
 </file>
@@ -3446,7 +3488,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1102"/>
+  <dimension ref="A1:R1110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -63906,7 +63948,7 @@
         <v>824</v>
       </c>
       <c r="K1082" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1082" s="1">
         <v>30000</v>
@@ -63959,7 +64001,7 @@
         <v>796</v>
       </c>
       <c r="K1083" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1083" s="1">
         <v>30000</v>
@@ -64012,7 +64054,7 @@
         <v>795</v>
       </c>
       <c r="K1084" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1084" s="1">
         <v>30000</v>
@@ -64065,7 +64107,7 @@
         <v>795</v>
       </c>
       <c r="K1085" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1085" s="1">
         <v>30000</v>
@@ -64118,7 +64160,7 @@
         <v>817</v>
       </c>
       <c r="K1086" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1086" s="1">
         <v>30000</v>
@@ -64171,7 +64213,7 @@
         <v>818</v>
       </c>
       <c r="K1087" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1087" s="1">
         <v>30000</v>
@@ -64224,7 +64266,7 @@
         <v>795</v>
       </c>
       <c r="K1088" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1088" s="1">
         <v>30000</v>
@@ -64277,7 +64319,7 @@
         <v>796</v>
       </c>
       <c r="K1089" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1089" s="1">
         <v>30000</v>
@@ -64330,7 +64372,7 @@
         <v>819</v>
       </c>
       <c r="K1090" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1090" s="1">
         <v>30000</v>
@@ -64383,7 +64425,7 @@
         <v>797</v>
       </c>
       <c r="K1091" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1091" s="1">
         <v>30000</v>
@@ -64436,7 +64478,7 @@
         <v>797</v>
       </c>
       <c r="K1092" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1092" s="1">
         <v>30000</v>
@@ -64489,7 +64531,7 @@
         <v>819</v>
       </c>
       <c r="K1093" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1093" s="1">
         <v>30000</v>
@@ -64542,7 +64584,7 @@
         <v>827</v>
       </c>
       <c r="K1094" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1094" s="1">
         <v>30000</v>
@@ -64595,7 +64637,7 @@
         <v>828</v>
       </c>
       <c r="K1095" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1095" s="1">
         <v>30000</v>
@@ -64648,7 +64690,7 @@
         <v>797</v>
       </c>
       <c r="K1096" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1096" s="1">
         <v>30000</v>
@@ -64701,7 +64743,7 @@
         <v>796</v>
       </c>
       <c r="K1097" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1097" s="1">
         <v>30000</v>
@@ -64754,7 +64796,7 @@
         <v>828</v>
       </c>
       <c r="K1098" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1098" s="1">
         <v>30000</v>
@@ -64807,7 +64849,7 @@
         <v>821</v>
       </c>
       <c r="K1099" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1099" s="1">
         <v>30000</v>
@@ -64860,7 +64902,7 @@
         <v>828</v>
       </c>
       <c r="K1100" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1100" s="1">
         <v>30000</v>
@@ -64913,7 +64955,7 @@
         <v>820</v>
       </c>
       <c r="K1101" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1101" s="1">
         <v>30000</v>
@@ -64966,7 +65008,7 @@
         <v>822</v>
       </c>
       <c r="K1102" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L1102" s="1">
         <v>30000</v>
@@ -64987,6 +65029,430 @@
         <v>0</v>
       </c>
       <c r="R1102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1103" s="1">
+        <v>1120101</v>
+      </c>
+      <c r="B1103" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1103" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1103" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1103" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1103" s="1">
+        <v>1</v>
+      </c>
+      <c r="H1103" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1103" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1103" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="K1103" s="1">
+        <v>800</v>
+      </c>
+      <c r="L1103" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1103" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1103" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1103" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="P1103" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1103" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1103" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1104" s="1">
+        <v>1120102</v>
+      </c>
+      <c r="B1104" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1104" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1104" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1104" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1104" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1104" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1104" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1104" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="K1104" s="1">
+        <v>800</v>
+      </c>
+      <c r="L1104" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1104" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1104" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1104" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="P1104" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1104" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1104" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1105" s="1">
+        <v>1120103</v>
+      </c>
+      <c r="B1105" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1105" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1105" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1105" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1105" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1105" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1105" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1105" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="K1105" s="1">
+        <v>800</v>
+      </c>
+      <c r="L1105" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1105" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1105" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1105" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="P1105" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1105" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1105" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1106" s="1">
+        <v>1120104</v>
+      </c>
+      <c r="B1106" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1106" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1106" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1106" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1106" s="1">
+        <v>4</v>
+      </c>
+      <c r="H1106" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I1106" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1106" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="K1106" s="1">
+        <v>800</v>
+      </c>
+      <c r="L1106" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1106" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1106" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1106" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="P1106" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1106" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1106" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1107" s="1">
+        <v>1120105</v>
+      </c>
+      <c r="B1107" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1107" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1107" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1107" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1107" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1107" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1107" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1107" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="K1107" s="1">
+        <v>800</v>
+      </c>
+      <c r="L1107" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1107" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1107" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1107" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="P1107" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1107" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1107" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1108" s="1">
+        <v>1120106</v>
+      </c>
+      <c r="B1108" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1108" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1108" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1108" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1108" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1108" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1108" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1108" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="K1108" s="1">
+        <v>800</v>
+      </c>
+      <c r="L1108" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1108" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1108" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1108" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="P1108" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1108" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1108" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1109" s="1">
+        <v>1120107</v>
+      </c>
+      <c r="B1109" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1109" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1109" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1109" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1109" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1109" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1109" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1109" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="K1109" s="1">
+        <v>800</v>
+      </c>
+      <c r="L1109" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1109" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1109" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1109" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="P1109" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1109" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1109" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1110" s="1">
+        <v>1120108</v>
+      </c>
+      <c r="B1110" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1110" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1110" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1110" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1110" s="1">
+        <v>8</v>
+      </c>
+      <c r="H1110" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1110" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1110" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="K1110" s="1">
+        <v>800</v>
+      </c>
+      <c r="L1110" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1110" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1110" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1110" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="P1110" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1110" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1110" s="67">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8C0F0A-C8F4-43B5-9B31-101B30DE80A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63201E4-A206-4AC7-A390-DDC612F4F1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2583,9 +2583,6 @@
     <t>18,55,15,60,52,63</t>
   </si>
   <si>
-    <t>45,90,50,88,55,86</t>
-  </si>
-  <si>
     <t>58,91,65,94,93,92</t>
   </si>
   <si>
@@ -2673,6 +2670,9 @@
   </si>
   <si>
     <t>83,48,83,40,83,32</t>
+  </si>
+  <si>
+    <t>45,90,50,82,55,86</t>
   </si>
 </sst>
 </file>
@@ -63242,7 +63242,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -63945,7 +63945,7 @@
         <v>1</v>
       </c>
       <c r="J1082" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="K1082" s="1">
         <v>40</v>
@@ -63960,7 +63960,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -64013,7 +64013,7 @@
         <v>0</v>
       </c>
       <c r="O1083" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P1083" s="1">
         <v>0</v>
@@ -64157,7 +64157,7 @@
         <v>2</v>
       </c>
       <c r="J1086" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K1086" s="1">
         <v>40</v>
@@ -64210,7 +64210,7 @@
         <v>2</v>
       </c>
       <c r="J1087" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="K1087" s="1">
         <v>40</v>
@@ -64369,7 +64369,7 @@
         <v>3</v>
       </c>
       <c r="J1090" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="K1090" s="1">
         <v>40</v>
@@ -64528,7 +64528,7 @@
         <v>4</v>
       </c>
       <c r="J1093" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="K1093" s="1">
         <v>40</v>
@@ -64581,7 +64581,7 @@
         <v>4</v>
       </c>
       <c r="J1094" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K1094" s="1">
         <v>40</v>
@@ -64634,7 +64634,7 @@
         <v>4</v>
       </c>
       <c r="J1095" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="K1095" s="1">
         <v>40</v>
@@ -64793,7 +64793,7 @@
         <v>5</v>
       </c>
       <c r="J1098" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="K1098" s="1">
         <v>40</v>
@@ -64846,7 +64846,7 @@
         <v>5</v>
       </c>
       <c r="J1099" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="K1099" s="1">
         <v>40</v>
@@ -64861,7 +64861,7 @@
         <v>0</v>
       </c>
       <c r="O1099" s="1" t="s">
-        <v>813</v>
+        <v>842</v>
       </c>
       <c r="P1099" s="1">
         <v>0</v>
@@ -64899,7 +64899,7 @@
         <v>5</v>
       </c>
       <c r="J1100" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="K1100" s="1">
         <v>40</v>
@@ -64914,7 +64914,7 @@
         <v>0</v>
       </c>
       <c r="O1100" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="P1100" s="1">
         <v>0</v>
@@ -64952,7 +64952,7 @@
         <v>5</v>
       </c>
       <c r="J1101" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="K1101" s="1">
         <v>40</v>
@@ -64967,7 +64967,7 @@
         <v>0</v>
       </c>
       <c r="O1101" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="P1101" s="1">
         <v>0</v>
@@ -65005,7 +65005,7 @@
         <v>5</v>
       </c>
       <c r="J1102" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="K1102" s="1">
         <v>40</v>
@@ -65020,7 +65020,7 @@
         <v>0</v>
       </c>
       <c r="O1102" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="P1102" s="1">
         <v>0</v>
@@ -65058,7 +65058,7 @@
         <v>1</v>
       </c>
       <c r="J1103" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="K1103" s="1">
         <v>800</v>
@@ -65073,7 +65073,7 @@
         <v>1</v>
       </c>
       <c r="O1103" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="P1103" s="1">
         <v>0</v>
@@ -65111,7 +65111,7 @@
         <v>1</v>
       </c>
       <c r="J1104" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K1104" s="1">
         <v>800</v>
@@ -65126,7 +65126,7 @@
         <v>1</v>
       </c>
       <c r="O1104" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="P1104" s="1">
         <v>0</v>
@@ -65164,7 +65164,7 @@
         <v>1</v>
       </c>
       <c r="J1105" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="K1105" s="1">
         <v>800</v>
@@ -65179,7 +65179,7 @@
         <v>1</v>
       </c>
       <c r="O1105" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="P1105" s="1">
         <v>0</v>
@@ -65217,7 +65217,7 @@
         <v>1</v>
       </c>
       <c r="J1106" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="K1106" s="1">
         <v>800</v>
@@ -65232,7 +65232,7 @@
         <v>1</v>
       </c>
       <c r="O1106" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="P1106" s="1">
         <v>0</v>
@@ -65270,7 +65270,7 @@
         <v>1</v>
       </c>
       <c r="J1107" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K1107" s="1">
         <v>800</v>
@@ -65285,7 +65285,7 @@
         <v>1</v>
       </c>
       <c r="O1107" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P1107" s="1">
         <v>0</v>
@@ -65323,7 +65323,7 @@
         <v>1</v>
       </c>
       <c r="J1108" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="K1108" s="1">
         <v>800</v>
@@ -65338,7 +65338,7 @@
         <v>1</v>
       </c>
       <c r="O1108" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P1108" s="1">
         <v>0</v>
@@ -65376,7 +65376,7 @@
         <v>1</v>
       </c>
       <c r="J1109" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="K1109" s="1">
         <v>800</v>
@@ -65391,7 +65391,7 @@
         <v>1</v>
       </c>
       <c r="O1109" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="P1109" s="1">
         <v>0</v>
@@ -65429,7 +65429,7 @@
         <v>1</v>
       </c>
       <c r="J1110" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="K1110" s="1">
         <v>800</v>
@@ -65444,7 +65444,7 @@
         <v>1</v>
       </c>
       <c r="O1110" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P1110" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63201E4-A206-4AC7-A390-DDC612F4F1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBC1200-C20B-4EC2-A0F0-0D280FFD3AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2616,10 +2616,6 @@
     <t>111104</t>
   </si>
   <si>
-    <t>10,13</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>111113</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2654,15 +2650,9 @@
     <t>50,85,20,56,80,56</t>
   </si>
   <si>
-    <t>11,98,22,98</t>
-  </si>
-  <si>
     <t>98,55,98,42,98,68</t>
   </si>
   <si>
-    <t>17,45,17,35</t>
-  </si>
-  <si>
     <t>2,55,2,42,2,68</t>
   </si>
   <si>
@@ -2672,7 +2662,16 @@
     <t>83,48,83,40,83,32</t>
   </si>
   <si>
-    <t>45,90,50,82,55,86</t>
+    <t>10,13</t>
+  </si>
+  <si>
+    <t>45,90,50,80,55,86</t>
+  </si>
+  <si>
+    <t>83,45,83,35</t>
+  </si>
+  <si>
+    <t>98,44,98,54</t>
   </si>
 </sst>
 </file>
@@ -63242,7 +63241,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -63960,7 +63959,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -64581,7 +64580,7 @@
         <v>4</v>
       </c>
       <c r="J1094" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="K1094" s="1">
         <v>40</v>
@@ -64634,7 +64633,7 @@
         <v>4</v>
       </c>
       <c r="J1095" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K1095" s="1">
         <v>40</v>
@@ -64711,7 +64710,7 @@
         <v>0</v>
       </c>
       <c r="R1096" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1097" spans="1:18" x14ac:dyDescent="0.2">
@@ -64793,7 +64792,7 @@
         <v>5</v>
       </c>
       <c r="J1098" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K1098" s="1">
         <v>40</v>
@@ -64861,7 +64860,7 @@
         <v>0</v>
       </c>
       <c r="O1099" s="1" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="P1099" s="1">
         <v>0</v>
@@ -64870,7 +64869,7 @@
         <v>0</v>
       </c>
       <c r="R1099" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1100" spans="1:18" x14ac:dyDescent="0.2">
@@ -64899,7 +64898,7 @@
         <v>5</v>
       </c>
       <c r="J1100" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K1100" s="1">
         <v>40</v>
@@ -65058,7 +65057,7 @@
         <v>1</v>
       </c>
       <c r="J1103" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="K1103" s="1">
         <v>800</v>
@@ -65073,7 +65072,7 @@
         <v>1</v>
       </c>
       <c r="O1103" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="P1103" s="1">
         <v>0</v>
@@ -65111,7 +65110,7 @@
         <v>1</v>
       </c>
       <c r="J1104" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="K1104" s="1">
         <v>800</v>
@@ -65126,7 +65125,7 @@
         <v>1</v>
       </c>
       <c r="O1104" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="P1104" s="1">
         <v>0</v>
@@ -65164,7 +65163,7 @@
         <v>1</v>
       </c>
       <c r="J1105" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K1105" s="1">
         <v>800</v>
@@ -65179,7 +65178,7 @@
         <v>1</v>
       </c>
       <c r="O1105" s="1" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="P1105" s="1">
         <v>0</v>
@@ -65217,7 +65216,7 @@
         <v>1</v>
       </c>
       <c r="J1106" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="K1106" s="1">
         <v>800</v>
@@ -65232,7 +65231,7 @@
         <v>1</v>
       </c>
       <c r="O1106" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="P1106" s="1">
         <v>0</v>
@@ -65270,7 +65269,7 @@
         <v>1</v>
       </c>
       <c r="J1107" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="K1107" s="1">
         <v>800</v>
@@ -65285,7 +65284,7 @@
         <v>1</v>
       </c>
       <c r="O1107" s="1" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="P1107" s="1">
         <v>0</v>
@@ -65323,7 +65322,7 @@
         <v>1</v>
       </c>
       <c r="J1108" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="K1108" s="1">
         <v>800</v>
@@ -65338,7 +65337,7 @@
         <v>1</v>
       </c>
       <c r="O1108" s="1" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="P1108" s="1">
         <v>0</v>
@@ -65376,7 +65375,7 @@
         <v>1</v>
       </c>
       <c r="J1109" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K1109" s="1">
         <v>800</v>
@@ -65391,7 +65390,7 @@
         <v>1</v>
       </c>
       <c r="O1109" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="P1109" s="1">
         <v>0</v>
@@ -65400,7 +65399,7 @@
         <v>0</v>
       </c>
       <c r="R1109" s="67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1110" spans="1:18" x14ac:dyDescent="0.2">
@@ -65429,7 +65428,7 @@
         <v>1</v>
       </c>
       <c r="J1110" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K1110" s="1">
         <v>800</v>
@@ -65444,7 +65443,7 @@
         <v>1</v>
       </c>
       <c r="O1110" s="1" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="P1110" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBC1200-C20B-4EC2-A0F0-0D280FFD3AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEAE23E-2541-497F-A6AD-F740CC9188AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="863">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2644,34 +2644,94 @@
     <t>112105,112105,112105</t>
   </si>
   <si>
-    <t>50,66</t>
-  </si>
-  <si>
-    <t>50,85,20,56,80,56</t>
-  </si>
-  <si>
-    <t>98,55,98,42,98,68</t>
-  </si>
-  <si>
-    <t>2,55,2,42,2,68</t>
-  </si>
-  <si>
-    <t>78,98,89,98</t>
-  </si>
-  <si>
-    <t>83,48,83,40,83,32</t>
-  </si>
-  <si>
     <t>10,13</t>
   </si>
   <si>
     <t>45,90,50,80,55,86</t>
   </si>
   <si>
-    <t>83,45,83,35</t>
-  </si>
-  <si>
-    <t>98,44,98,54</t>
+    <t>112102,112104,112104</t>
+  </si>
+  <si>
+    <t>112101,112101,112104,112104</t>
+  </si>
+  <si>
+    <t>112101,112101,112101,112101</t>
+  </si>
+  <si>
+    <t>112105,112105,112105,112105</t>
+  </si>
+  <si>
+    <t>112102,112102,112104,112104</t>
+  </si>
+  <si>
+    <t>112105,112105,112105,112104,112104</t>
+  </si>
+  <si>
+    <t>112101,112101</t>
+  </si>
+  <si>
+    <t>50,60,40,55,60,55</t>
+  </si>
+  <si>
+    <t>50,60,62,78,72,73</t>
+  </si>
+  <si>
+    <t>72,50,75,40</t>
+  </si>
+  <si>
+    <t>30,75,35,80,40,85</t>
+  </si>
+  <si>
+    <t>67,55,80,50,70,40</t>
+  </si>
+  <si>
+    <t>65,40,55,35,85,45,75,35</t>
+  </si>
+  <si>
+    <t>33,35,45,35,25,45,25,55</t>
+  </si>
+  <si>
+    <t>40,55,25,32,32,25</t>
+  </si>
+  <si>
+    <t>60,80,65,75,60,70,55,65</t>
+  </si>
+  <si>
+    <t>40,55,20,40,20,20</t>
+  </si>
+  <si>
+    <t>40,80,35,75,40,70,45,65</t>
+  </si>
+  <si>
+    <t>40,80,47,75,53,75,60,80</t>
+  </si>
+  <si>
+    <t>45,40,55,40,45,30,55,30</t>
+  </si>
+  <si>
+    <t>42,40,50,40,58,40,38,30,62,30</t>
+  </si>
+  <si>
+    <t>50,40,32,35,68,35</t>
+  </si>
+  <si>
+    <t>38,40,45,40,55,40,62,40</t>
+  </si>
+  <si>
+    <t>80,85,90,75</t>
+  </si>
+  <si>
+    <t>85,90,95,80</t>
+  </si>
+  <si>
+    <t>40,75,35,80,35,70</t>
+  </si>
+  <si>
+    <t>85,65,85,60,85,55</t>
+  </si>
+  <si>
+    <t>45,75,40,80,40,70</t>
   </si>
 </sst>
 </file>
@@ -3487,7 +3547,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1110"/>
+  <dimension ref="A1:R1126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -63959,7 +64019,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -64498,7 +64558,7 @@
         <v>0</v>
       </c>
       <c r="R1092" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1093" spans="1:18" x14ac:dyDescent="0.2">
@@ -64710,7 +64770,7 @@
         <v>0</v>
       </c>
       <c r="R1096" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1097" spans="1:18" x14ac:dyDescent="0.2">
@@ -64860,7 +64920,7 @@
         <v>0</v>
       </c>
       <c r="O1099" s="1" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="P1099" s="1">
         <v>0</v>
@@ -65033,7 +65093,7 @@
     </row>
     <row r="1103" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1103" s="1">
-        <v>1120101</v>
+        <v>1120601</v>
       </c>
       <c r="B1103" s="1">
         <v>11</v>
@@ -65042,7 +65102,7 @@
         <v>2</v>
       </c>
       <c r="E1103" s="1">
-        <v>110001</v>
+        <v>110002</v>
       </c>
       <c r="F1103" s="1">
         <v>1</v>
@@ -65051,16 +65111,16 @@
         <v>1</v>
       </c>
       <c r="H1103" s="1">
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="I1103" s="1">
         <v>1</v>
       </c>
       <c r="J1103" s="2" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="K1103" s="1">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="L1103" s="1">
         <v>30000</v>
@@ -65069,10 +65129,10 @@
         <v>0</v>
       </c>
       <c r="N1103" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1103" s="1" t="s">
-        <v>833</v>
+        <v>842</v>
       </c>
       <c r="P1103" s="1">
         <v>0</v>
@@ -65081,12 +65141,12 @@
         <v>0</v>
       </c>
       <c r="R1103" s="67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1104" s="1">
-        <v>1120102</v>
+        <v>1120602</v>
       </c>
       <c r="B1104" s="1">
         <v>11</v>
@@ -65095,7 +65155,7 @@
         <v>2</v>
       </c>
       <c r="E1104" s="1">
-        <v>110001</v>
+        <v>110002</v>
       </c>
       <c r="F1104" s="1">
         <v>1</v>
@@ -65110,10 +65170,10 @@
         <v>1</v>
       </c>
       <c r="J1104" s="2" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="K1104" s="1">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="L1104" s="1">
         <v>30000</v>
@@ -65122,10 +65182,10 @@
         <v>0</v>
       </c>
       <c r="N1104" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1104" s="1" t="s">
-        <v>834</v>
+        <v>843</v>
       </c>
       <c r="P1104" s="1">
         <v>0</v>
@@ -65139,7 +65199,7 @@
     </row>
     <row r="1105" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1105" s="1">
-        <v>1120103</v>
+        <v>1120603</v>
       </c>
       <c r="B1105" s="1">
         <v>11</v>
@@ -65148,7 +65208,7 @@
         <v>2</v>
       </c>
       <c r="E1105" s="1">
-        <v>110001</v>
+        <v>110002</v>
       </c>
       <c r="F1105" s="1">
         <v>1</v>
@@ -65157,16 +65217,16 @@
         <v>3</v>
       </c>
       <c r="H1105" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I1105" s="1">
         <v>1</v>
       </c>
       <c r="J1105" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="K1105" s="1">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="L1105" s="1">
         <v>30000</v>
@@ -65175,10 +65235,10 @@
         <v>0</v>
       </c>
       <c r="N1105" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1105" s="1" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="P1105" s="1">
         <v>0</v>
@@ -65187,12 +65247,12 @@
         <v>0</v>
       </c>
       <c r="R1105" s="67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1106" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1106" s="1">
-        <v>1120104</v>
+        <v>1120604</v>
       </c>
       <c r="B1106" s="1">
         <v>11</v>
@@ -65201,7 +65261,7 @@
         <v>2</v>
       </c>
       <c r="E1106" s="1">
-        <v>110001</v>
+        <v>110002</v>
       </c>
       <c r="F1106" s="1">
         <v>1</v>
@@ -65210,16 +65270,16 @@
         <v>4</v>
       </c>
       <c r="H1106" s="1">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="I1106" s="1">
         <v>1</v>
       </c>
       <c r="J1106" s="2" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K1106" s="1">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="L1106" s="1">
         <v>30000</v>
@@ -65228,10 +65288,10 @@
         <v>0</v>
       </c>
       <c r="N1106" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1106" s="1" t="s">
-        <v>835</v>
+        <v>844</v>
       </c>
       <c r="P1106" s="1">
         <v>0</v>
@@ -65245,7 +65305,7 @@
     </row>
     <row r="1107" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1107" s="1">
-        <v>1120105</v>
+        <v>1120701</v>
       </c>
       <c r="B1107" s="1">
         <v>11</v>
@@ -65254,7 +65314,7 @@
         <v>2</v>
       </c>
       <c r="E1107" s="1">
-        <v>110001</v>
+        <v>110002</v>
       </c>
       <c r="F1107" s="1">
         <v>1</v>
@@ -65263,16 +65323,16 @@
         <v>5</v>
       </c>
       <c r="H1107" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I1107" s="1">
         <v>1</v>
       </c>
       <c r="J1107" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K1107" s="1">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="L1107" s="1">
         <v>30000</v>
@@ -65281,10 +65341,10 @@
         <v>0</v>
       </c>
       <c r="N1107" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1107" s="1" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="P1107" s="1">
         <v>0</v>
@@ -65293,12 +65353,12 @@
         <v>0</v>
       </c>
       <c r="R1107" s="67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1108" s="1">
-        <v>1120106</v>
+        <v>1120702</v>
       </c>
       <c r="B1108" s="1">
         <v>11</v>
@@ -65307,7 +65367,7 @@
         <v>2</v>
       </c>
       <c r="E1108" s="1">
-        <v>110001</v>
+        <v>110002</v>
       </c>
       <c r="F1108" s="1">
         <v>1</v>
@@ -65322,10 +65382,10 @@
         <v>1</v>
       </c>
       <c r="J1108" s="2" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="K1108" s="1">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="L1108" s="1">
         <v>30000</v>
@@ -65334,10 +65394,10 @@
         <v>0</v>
       </c>
       <c r="N1108" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1108" s="1" t="s">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="P1108" s="1">
         <v>0</v>
@@ -65351,7 +65411,7 @@
     </row>
     <row r="1109" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1109" s="1">
-        <v>1120107</v>
+        <v>1120703</v>
       </c>
       <c r="B1109" s="1">
         <v>11</v>
@@ -65360,7 +65420,7 @@
         <v>2</v>
       </c>
       <c r="E1109" s="1">
-        <v>110001</v>
+        <v>110002</v>
       </c>
       <c r="F1109" s="1">
         <v>1</v>
@@ -65369,16 +65429,16 @@
         <v>7</v>
       </c>
       <c r="H1109" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I1109" s="1">
         <v>1</v>
       </c>
       <c r="J1109" s="2" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="K1109" s="1">
-        <v>800</v>
+        <v>160</v>
       </c>
       <c r="L1109" s="1">
         <v>30000</v>
@@ -65387,10 +65447,10 @@
         <v>0</v>
       </c>
       <c r="N1109" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O1109" s="1" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="P1109" s="1">
         <v>0</v>
@@ -65404,7 +65464,7 @@
     </row>
     <row r="1110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1110" s="1">
-        <v>1120108</v>
+        <v>1120704</v>
       </c>
       <c r="B1110" s="1">
         <v>11</v>
@@ -65413,7 +65473,7 @@
         <v>2</v>
       </c>
       <c r="E1110" s="1">
-        <v>110001</v>
+        <v>110002</v>
       </c>
       <c r="F1110" s="1">
         <v>1</v>
@@ -65422,36 +65482,884 @@
         <v>8</v>
       </c>
       <c r="H1110" s="1">
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="I1110" s="1">
         <v>1</v>
       </c>
       <c r="J1110" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="K1110" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1110" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1110" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1110" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1110" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="P1110" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1110" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1110" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1111" s="1">
+        <v>1120801</v>
+      </c>
+      <c r="B1111" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1111" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1111" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1111" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1111" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1111" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1111" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1111" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="K1110" s="1">
-        <v>800</v>
-      </c>
-      <c r="L1110" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1110" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1110" s="1">
-        <v>1</v>
-      </c>
-      <c r="O1110" s="1" t="s">
+      <c r="K1111" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1111" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1111" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1111" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1111" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="P1111" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1111" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1111" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1112" s="1">
+        <v>1120802</v>
+      </c>
+      <c r="B1112" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1112" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1112" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1112" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1112" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1112" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1112" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1112" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="K1112" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1112" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1112" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1112" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1112" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="P1112" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1112" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1112" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1113" s="1">
+        <v>1120803</v>
+      </c>
+      <c r="B1113" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1113" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1113" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1113" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1113" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1113" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1113" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1113" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="P1110" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1110" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1110" s="67">
+      <c r="K1113" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1113" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1113" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1113" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1113" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="P1113" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1113" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1113" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1114" s="1">
+        <v>1120804</v>
+      </c>
+      <c r="B1114" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1114" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1114" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1114" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1114" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1114" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1114" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1114" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="K1114" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1114" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1114" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1114" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1114" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="P1114" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1114" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1114" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1115" s="1">
+        <v>1120805</v>
+      </c>
+      <c r="B1115" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1115" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1115" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1115" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1115" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1115" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1115" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1115" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="K1115" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1115" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1115" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1115" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1115" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="P1115" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1115" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1115" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1116" s="1">
+        <v>1120901</v>
+      </c>
+      <c r="B1116" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1116" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1116" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1116" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1116" s="1">
+        <v>14</v>
+      </c>
+      <c r="H1116" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1116" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1116" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="K1116" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1116" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1116" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1116" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1116" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="P1116" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1116" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1116" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1117" s="1">
+        <v>1120902</v>
+      </c>
+      <c r="B1117" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1117" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1117" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1117" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1117" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1117" s="1">
+        <v>3500</v>
+      </c>
+      <c r="I1117" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1117" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="K1117" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1117" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1117" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1117" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1117" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="P1117" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1117" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1117" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1118" s="1">
+        <v>1120903</v>
+      </c>
+      <c r="B1118" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1118" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1118" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1118" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1118" s="1">
+        <v>16</v>
+      </c>
+      <c r="H1118" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1118" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1118" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="K1118" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1118" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1118" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1118" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1118" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="P1118" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1118" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1118" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1119" s="1">
+        <v>1120904</v>
+      </c>
+      <c r="B1119" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1119" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1119" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1119" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1119" s="1">
+        <v>17</v>
+      </c>
+      <c r="H1119" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1119" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1119" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="K1119" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1119" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1119" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1119" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1119" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="P1119" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1119" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1119" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1120" s="1">
+        <v>1120905</v>
+      </c>
+      <c r="B1120" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1120" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1120" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1120" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1120" s="1">
+        <v>18</v>
+      </c>
+      <c r="H1120" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1120" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1120" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="K1120" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1120" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1120" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1120" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1120" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="P1120" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1120" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1120" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1121" s="1">
+        <v>1121001</v>
+      </c>
+      <c r="B1121" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1121" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1121" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1121" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1121" s="1">
+        <v>19</v>
+      </c>
+      <c r="H1121" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1121" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1121" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="K1121" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1121" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1121" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1121" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1121" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="P1121" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1121" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1121" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1122" s="1">
+        <v>1121002</v>
+      </c>
+      <c r="B1122" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1122" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1122" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1122" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1122" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1122" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1122" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1122" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="K1122" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1122" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1122" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1122" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1122" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="P1122" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1122" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1122" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1123" s="1">
+        <v>1121003</v>
+      </c>
+      <c r="B1123" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1123" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1123" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1123" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1123" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1123" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1123" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1123" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="K1123" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1123" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1123" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1123" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1123" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="P1123" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1123" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1123" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1124" s="1">
+        <v>1121004</v>
+      </c>
+      <c r="B1124" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1124" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1124" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1124" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1124" s="1">
+        <v>22</v>
+      </c>
+      <c r="H1124" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1124" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1124" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="K1124" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1124" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1124" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1124" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1124" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="P1124" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1124" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1124" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1125" s="1">
+        <v>1121005</v>
+      </c>
+      <c r="B1125" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1125" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1125" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1125" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1125" s="1">
+        <v>23</v>
+      </c>
+      <c r="H1125" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1125" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1125" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="K1125" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1125" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1125" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1125" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1125" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="P1125" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1125" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1125" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1126" s="1">
+        <v>1121006</v>
+      </c>
+      <c r="B1126" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1126" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1126" s="1">
+        <v>110002</v>
+      </c>
+      <c r="F1126" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1126" s="1">
+        <v>24</v>
+      </c>
+      <c r="H1126" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1126" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1126" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="K1126" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1126" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1126" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1126" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1126" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="P1126" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1126" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1126" s="67">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEAE23E-2541-497F-A6AD-F740CC9188AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB41FF9-A159-4C64-AC9C-3A843FFB6C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2574,22 +2574,10 @@
     <t>15,35,12,30,18,24</t>
   </si>
   <si>
-    <t>12,30,12,30</t>
-  </si>
-  <si>
     <t>12,47,12,67</t>
   </si>
   <si>
     <t>18,55,15,60,52,63</t>
-  </si>
-  <si>
-    <t>58,91,65,94,93,92</t>
-  </si>
-  <si>
-    <t>65,88,65,94,93,84</t>
-  </si>
-  <si>
-    <t>65,91,70,88,70,94,93,76</t>
   </si>
   <si>
     <t>111105,111104</t>
@@ -2732,6 +2720,18 @@
   </si>
   <si>
     <t>45,75,40,80,40,70</t>
+  </si>
+  <si>
+    <t>11,50,9,40</t>
+  </si>
+  <si>
+    <t>58,91,65,94,80,92</t>
+  </si>
+  <si>
+    <t>65,88,65,94,92,92</t>
+  </si>
+  <si>
+    <t>65,91,70,88,70,94,86,92</t>
   </si>
 </sst>
 </file>
@@ -63301,7 +63301,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -64004,7 +64004,7 @@
         <v>1</v>
       </c>
       <c r="J1082" s="2" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="K1082" s="1">
         <v>40</v>
@@ -64019,7 +64019,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -64072,7 +64072,7 @@
         <v>0</v>
       </c>
       <c r="O1083" s="1" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="P1083" s="1">
         <v>0</v>
@@ -64216,7 +64216,7 @@
         <v>2</v>
       </c>
       <c r="J1086" s="2" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="K1086" s="1">
         <v>40</v>
@@ -64269,7 +64269,7 @@
         <v>2</v>
       </c>
       <c r="J1087" s="2" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="K1087" s="1">
         <v>40</v>
@@ -64428,7 +64428,7 @@
         <v>3</v>
       </c>
       <c r="J1090" s="2" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="K1090" s="1">
         <v>40</v>
@@ -64587,7 +64587,7 @@
         <v>4</v>
       </c>
       <c r="J1093" s="2" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="K1093" s="1">
         <v>40</v>
@@ -64640,7 +64640,7 @@
         <v>4</v>
       </c>
       <c r="J1094" s="2" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="K1094" s="1">
         <v>40</v>
@@ -64693,7 +64693,7 @@
         <v>4</v>
       </c>
       <c r="J1095" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="K1095" s="1">
         <v>40</v>
@@ -64761,7 +64761,7 @@
         <v>0</v>
       </c>
       <c r="O1096" s="1" t="s">
-        <v>810</v>
+        <v>859</v>
       </c>
       <c r="P1096" s="1">
         <v>0</v>
@@ -64814,7 +64814,7 @@
         <v>0</v>
       </c>
       <c r="O1097" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="P1097" s="1">
         <v>0</v>
@@ -64852,7 +64852,7 @@
         <v>5</v>
       </c>
       <c r="J1098" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="K1098" s="1">
         <v>40</v>
@@ -64867,7 +64867,7 @@
         <v>0</v>
       </c>
       <c r="O1098" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="P1098" s="1">
         <v>0</v>
@@ -64905,7 +64905,7 @@
         <v>5</v>
       </c>
       <c r="J1099" s="2" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="K1099" s="1">
         <v>40</v>
@@ -64920,7 +64920,7 @@
         <v>0</v>
       </c>
       <c r="O1099" s="1" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="P1099" s="1">
         <v>0</v>
@@ -64958,7 +64958,7 @@
         <v>5</v>
       </c>
       <c r="J1100" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="K1100" s="1">
         <v>40</v>
@@ -64973,7 +64973,7 @@
         <v>0</v>
       </c>
       <c r="O1100" s="1" t="s">
-        <v>813</v>
+        <v>860</v>
       </c>
       <c r="P1100" s="1">
         <v>0</v>
@@ -65011,7 +65011,7 @@
         <v>5</v>
       </c>
       <c r="J1101" s="2" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="K1101" s="1">
         <v>40</v>
@@ -65026,7 +65026,7 @@
         <v>0</v>
       </c>
       <c r="O1101" s="1" t="s">
-        <v>814</v>
+        <v>861</v>
       </c>
       <c r="P1101" s="1">
         <v>0</v>
@@ -65064,7 +65064,7 @@
         <v>5</v>
       </c>
       <c r="J1102" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="K1102" s="1">
         <v>40</v>
@@ -65079,7 +65079,7 @@
         <v>0</v>
       </c>
       <c r="O1102" s="1" t="s">
-        <v>815</v>
+        <v>862</v>
       </c>
       <c r="P1102" s="1">
         <v>0</v>
@@ -65117,7 +65117,7 @@
         <v>1</v>
       </c>
       <c r="J1103" s="2" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="K1103" s="1">
         <v>160</v>
@@ -65132,7 +65132,7 @@
         <v>0</v>
       </c>
       <c r="O1103" s="1" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="P1103" s="1">
         <v>0</v>
@@ -65170,7 +65170,7 @@
         <v>1</v>
       </c>
       <c r="J1104" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K1104" s="1">
         <v>160</v>
@@ -65185,7 +65185,7 @@
         <v>0</v>
       </c>
       <c r="O1104" s="1" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="P1104" s="1">
         <v>0</v>
@@ -65223,7 +65223,7 @@
         <v>1</v>
       </c>
       <c r="J1105" s="2" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="K1105" s="1">
         <v>160</v>
@@ -65238,7 +65238,7 @@
         <v>0</v>
       </c>
       <c r="O1105" s="1" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="P1105" s="1">
         <v>0</v>
@@ -65276,7 +65276,7 @@
         <v>1</v>
       </c>
       <c r="J1106" s="2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="K1106" s="1">
         <v>160</v>
@@ -65291,7 +65291,7 @@
         <v>0</v>
       </c>
       <c r="O1106" s="1" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="P1106" s="1">
         <v>0</v>
@@ -65329,7 +65329,7 @@
         <v>1</v>
       </c>
       <c r="J1107" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="K1107" s="1">
         <v>160</v>
@@ -65344,7 +65344,7 @@
         <v>0</v>
       </c>
       <c r="O1107" s="1" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="P1107" s="1">
         <v>0</v>
@@ -65382,7 +65382,7 @@
         <v>1</v>
       </c>
       <c r="J1108" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K1108" s="1">
         <v>160</v>
@@ -65397,7 +65397,7 @@
         <v>0</v>
       </c>
       <c r="O1108" s="1" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="P1108" s="1">
         <v>0</v>
@@ -65435,7 +65435,7 @@
         <v>1</v>
       </c>
       <c r="J1109" s="2" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="K1109" s="1">
         <v>160</v>
@@ -65450,7 +65450,7 @@
         <v>0</v>
       </c>
       <c r="O1109" s="1" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="P1109" s="1">
         <v>0</v>
@@ -65488,7 +65488,7 @@
         <v>1</v>
       </c>
       <c r="J1110" s="2" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="K1110" s="1">
         <v>160</v>
@@ -65503,7 +65503,7 @@
         <v>0</v>
       </c>
       <c r="O1110" s="1" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="P1110" s="1">
         <v>0</v>
@@ -65541,7 +65541,7 @@
         <v>1</v>
       </c>
       <c r="J1111" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="K1111" s="1">
         <v>160</v>
@@ -65556,7 +65556,7 @@
         <v>0</v>
       </c>
       <c r="O1111" s="1" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="P1111" s="1">
         <v>0</v>
@@ -65594,7 +65594,7 @@
         <v>1</v>
       </c>
       <c r="J1112" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K1112" s="1">
         <v>160</v>
@@ -65609,7 +65609,7 @@
         <v>0</v>
       </c>
       <c r="O1112" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="P1112" s="1">
         <v>0</v>
@@ -65647,7 +65647,7 @@
         <v>1</v>
       </c>
       <c r="J1113" s="2" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="K1113" s="1">
         <v>160</v>
@@ -65662,7 +65662,7 @@
         <v>0</v>
       </c>
       <c r="O1113" s="1" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="P1113" s="1">
         <v>0</v>
@@ -65700,7 +65700,7 @@
         <v>1</v>
       </c>
       <c r="J1114" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K1114" s="1">
         <v>160</v>
@@ -65715,7 +65715,7 @@
         <v>0</v>
       </c>
       <c r="O1114" s="1" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="P1114" s="1">
         <v>0</v>
@@ -65753,7 +65753,7 @@
         <v>1</v>
       </c>
       <c r="J1115" s="2" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="K1115" s="1">
         <v>160</v>
@@ -65768,7 +65768,7 @@
         <v>0</v>
       </c>
       <c r="O1115" s="1" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="P1115" s="1">
         <v>0</v>
@@ -65806,7 +65806,7 @@
         <v>1</v>
       </c>
       <c r="J1116" s="2" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="K1116" s="1">
         <v>160</v>
@@ -65821,7 +65821,7 @@
         <v>0</v>
       </c>
       <c r="O1116" s="1" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="P1116" s="1">
         <v>0</v>
@@ -65859,7 +65859,7 @@
         <v>1</v>
       </c>
       <c r="J1117" s="2" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="K1117" s="1">
         <v>160</v>
@@ -65874,7 +65874,7 @@
         <v>0</v>
       </c>
       <c r="O1117" s="1" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="P1117" s="1">
         <v>0</v>
@@ -65912,7 +65912,7 @@
         <v>1</v>
       </c>
       <c r="J1118" s="2" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="K1118" s="1">
         <v>160</v>
@@ -65927,7 +65927,7 @@
         <v>0</v>
       </c>
       <c r="O1118" s="1" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="P1118" s="1">
         <v>0</v>
@@ -65965,7 +65965,7 @@
         <v>1</v>
       </c>
       <c r="J1119" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K1119" s="1">
         <v>160</v>
@@ -65980,7 +65980,7 @@
         <v>0</v>
       </c>
       <c r="O1119" s="1" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="P1119" s="1">
         <v>0</v>
@@ -66018,7 +66018,7 @@
         <v>1</v>
       </c>
       <c r="J1120" s="2" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="K1120" s="1">
         <v>160</v>
@@ -66033,7 +66033,7 @@
         <v>0</v>
       </c>
       <c r="O1120" s="1" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="P1120" s="1">
         <v>0</v>
@@ -66071,7 +66071,7 @@
         <v>1</v>
       </c>
       <c r="J1121" s="2" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="K1121" s="1">
         <v>160</v>
@@ -66124,7 +66124,7 @@
         <v>1</v>
       </c>
       <c r="J1122" s="2" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="K1122" s="1">
         <v>160</v>
@@ -66139,7 +66139,7 @@
         <v>0</v>
       </c>
       <c r="O1122" s="1" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="P1122" s="1">
         <v>0</v>
@@ -66177,7 +66177,7 @@
         <v>1</v>
       </c>
       <c r="J1123" s="2" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="K1123" s="1">
         <v>160</v>
@@ -66192,7 +66192,7 @@
         <v>0</v>
       </c>
       <c r="O1123" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="P1123" s="1">
         <v>0</v>
@@ -66230,7 +66230,7 @@
         <v>1</v>
       </c>
       <c r="J1124" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="K1124" s="1">
         <v>160</v>
@@ -66245,7 +66245,7 @@
         <v>0</v>
       </c>
       <c r="O1124" s="1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="P1124" s="1">
         <v>0</v>
@@ -66283,7 +66283,7 @@
         <v>1</v>
       </c>
       <c r="J1125" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="K1125" s="1">
         <v>160</v>
@@ -66298,7 +66298,7 @@
         <v>0</v>
       </c>
       <c r="O1125" s="1" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="P1125" s="1">
         <v>0</v>
@@ -66336,7 +66336,7 @@
         <v>1</v>
       </c>
       <c r="J1126" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="K1126" s="1">
         <v>160</v>
@@ -66351,7 +66351,7 @@
         <v>0</v>
       </c>
       <c r="O1126" s="1" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="P1126" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB41FF9-A159-4C64-AC9C-3A843FFB6C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A55EC5-2DD0-4E03-B6C9-5E80190951A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63998,7 +63998,7 @@
         <v>1</v>
       </c>
       <c r="H1082" s="67">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1082" s="1">
         <v>1</v>
@@ -64051,7 +64051,7 @@
         <v>2</v>
       </c>
       <c r="H1083" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1083" s="1">
         <v>1</v>
@@ -64104,7 +64104,7 @@
         <v>3</v>
       </c>
       <c r="H1084" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1084" s="1">
         <v>1</v>
@@ -64157,7 +64157,7 @@
         <v>4</v>
       </c>
       <c r="H1085" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1085" s="1">
         <v>2</v>
@@ -64210,7 +64210,7 @@
         <v>5</v>
       </c>
       <c r="H1086" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1086" s="1">
         <v>2</v>
@@ -64263,7 +64263,7 @@
         <v>6</v>
       </c>
       <c r="H1087" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1087" s="1">
         <v>2</v>
@@ -64316,7 +64316,7 @@
         <v>7</v>
       </c>
       <c r="H1088" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1088" s="1">
         <v>3</v>
@@ -64369,7 +64369,7 @@
         <v>8</v>
       </c>
       <c r="H1089" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1089" s="1">
         <v>3</v>
@@ -64422,7 +64422,7 @@
         <v>9</v>
       </c>
       <c r="H1090" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1090" s="1">
         <v>3</v>
@@ -64475,7 +64475,7 @@
         <v>10</v>
       </c>
       <c r="H1091" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1091" s="1">
         <v>3</v>
@@ -64528,7 +64528,7 @@
         <v>11</v>
       </c>
       <c r="H1092" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1092" s="1">
         <v>4</v>
@@ -64581,7 +64581,7 @@
         <v>12</v>
       </c>
       <c r="H1093" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1093" s="1">
         <v>4</v>
@@ -64634,7 +64634,7 @@
         <v>13</v>
       </c>
       <c r="H1094" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1094" s="1">
         <v>4</v>
@@ -64687,7 +64687,7 @@
         <v>14</v>
       </c>
       <c r="H1095" s="67">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I1095" s="1">
         <v>4</v>
@@ -64740,7 +64740,7 @@
         <v>15</v>
       </c>
       <c r="H1096" s="67">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I1096" s="1">
         <v>4</v>
@@ -64793,7 +64793,7 @@
         <v>16</v>
       </c>
       <c r="H1097" s="67">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1097" s="1">
         <v>5</v>
@@ -64846,7 +64846,7 @@
         <v>17</v>
       </c>
       <c r="H1098" s="67">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I1098" s="1">
         <v>5</v>
@@ -64899,7 +64899,7 @@
         <v>18</v>
       </c>
       <c r="H1099" s="67">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1099" s="1">
         <v>5</v>
@@ -64952,7 +64952,7 @@
         <v>19</v>
       </c>
       <c r="H1100" s="67">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I1100" s="1">
         <v>5</v>
@@ -65005,7 +65005,7 @@
         <v>20</v>
       </c>
       <c r="H1101" s="67">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1101" s="1">
         <v>5</v>
@@ -65111,10 +65111,10 @@
         <v>1</v>
       </c>
       <c r="H1103" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1103" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J1103" s="2" t="s">
         <v>824</v>
@@ -65164,10 +65164,10 @@
         <v>2</v>
       </c>
       <c r="H1104" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I1104" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J1104" s="2" t="s">
         <v>831</v>
@@ -65217,10 +65217,10 @@
         <v>3</v>
       </c>
       <c r="H1105" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1105" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J1105" s="2" t="s">
         <v>824</v>
@@ -65270,10 +65270,10 @@
         <v>4</v>
       </c>
       <c r="H1106" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1106" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J1106" s="2" t="s">
         <v>827</v>
@@ -65323,10 +65323,10 @@
         <v>5</v>
       </c>
       <c r="H1107" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1107" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1107" s="2" t="s">
         <v>828</v>
@@ -65376,10 +65376,10 @@
         <v>6</v>
       </c>
       <c r="H1108" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I1108" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1108" s="2" t="s">
         <v>831</v>
@@ -65429,10 +65429,10 @@
         <v>7</v>
       </c>
       <c r="H1109" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1109" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1109" s="2" t="s">
         <v>832</v>
@@ -65482,10 +65482,10 @@
         <v>8</v>
       </c>
       <c r="H1110" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1110" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1110" s="2" t="s">
         <v>833</v>
@@ -65535,10 +65535,10 @@
         <v>9</v>
       </c>
       <c r="H1111" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1111" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J1111" s="2" t="s">
         <v>828</v>
@@ -65588,10 +65588,10 @@
         <v>10</v>
       </c>
       <c r="H1112" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I1112" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J1112" s="2" t="s">
         <v>831</v>
@@ -65641,10 +65641,10 @@
         <v>11</v>
       </c>
       <c r="H1113" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1113" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J1113" s="2" t="s">
         <v>834</v>
@@ -65694,10 +65694,10 @@
         <v>12</v>
       </c>
       <c r="H1114" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I1114" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J1114" s="2" t="s">
         <v>831</v>
@@ -65747,10 +65747,10 @@
         <v>13</v>
       </c>
       <c r="H1115" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1115" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J1115" s="2" t="s">
         <v>833</v>
@@ -65800,10 +65800,10 @@
         <v>14</v>
       </c>
       <c r="H1116" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1116" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J1116" s="2" t="s">
         <v>833</v>
@@ -65853,10 +65853,10 @@
         <v>15</v>
       </c>
       <c r="H1117" s="1">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="I1117" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J1117" s="2" t="s">
         <v>835</v>
@@ -65906,10 +65906,10 @@
         <v>16</v>
       </c>
       <c r="H1118" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1118" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J1118" s="2" t="s">
         <v>836</v>
@@ -65959,10 +65959,10 @@
         <v>17</v>
       </c>
       <c r="H1119" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I1119" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J1119" s="2" t="s">
         <v>831</v>
@@ -66012,10 +66012,10 @@
         <v>18</v>
       </c>
       <c r="H1120" s="1">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1120" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J1120" s="2" t="s">
         <v>834</v>
@@ -66065,10 +66065,10 @@
         <v>19</v>
       </c>
       <c r="H1121" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="I1121" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J1121" s="2" t="s">
         <v>823</v>
@@ -66118,10 +66118,10 @@
         <v>20</v>
       </c>
       <c r="H1122" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I1122" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J1122" s="2" t="s">
         <v>837</v>
@@ -66171,10 +66171,10 @@
         <v>21</v>
       </c>
       <c r="H1123" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I1123" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J1123" s="2" t="s">
         <v>825</v>
@@ -66224,10 +66224,10 @@
         <v>22</v>
       </c>
       <c r="H1124" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I1124" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J1124" s="2" t="s">
         <v>826</v>
@@ -66277,10 +66277,10 @@
         <v>23</v>
       </c>
       <c r="H1125" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I1125" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J1125" s="2" t="s">
         <v>828</v>
@@ -66330,10 +66330,10 @@
         <v>24</v>
       </c>
       <c r="H1126" s="1">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="I1126" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J1126" s="2" t="s">
         <v>826</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A55EC5-2DD0-4E03-B6C9-5E80190951A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A817644-9283-42EE-B8D5-9B965B32E6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_brush_foe_v8" sheetId="2" r:id="rId1"/>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="864">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1330,13 +1330,6 @@
     <t>85,75,75,85,85,20,15,15,10,30,30,10</t>
   </si>
   <si>
-    <t>500107,500107,500107</t>
-  </si>
-  <si>
-    <t>500107,500107,500107</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>60,50,50,50,40,50</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2732,6 +2725,17 @@
   </si>
   <si>
     <t>65,91,70,88,70,94,86,92</t>
+  </si>
+  <si>
+    <t>999002,999002,999002</t>
+  </si>
+  <si>
+    <t>999002,999002,999002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>999001,999001,999001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3685,13 +3689,13 @@
         <v>148</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="Q3" s="8" t="s">
         <v>158</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3741,13 +3745,13 @@
         <v>151</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="Q4" s="10" t="s">
         <v>159</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -3779,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>399</v>
+        <v>862</v>
       </c>
       <c r="K5" s="12">
         <v>20</v>
@@ -3794,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P5" s="1">
         <v>0</v>
@@ -3835,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>399</v>
+        <v>863</v>
       </c>
       <c r="K6" s="14">
         <v>20</v>
@@ -3850,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -3891,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>398</v>
+        <v>861</v>
       </c>
       <c r="K7" s="14">
         <v>20</v>
@@ -3906,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -50035,7 +50039,7 @@
         <v>1</v>
       </c>
       <c r="J831" s="61" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K831" s="60">
         <v>16</v>
@@ -50050,7 +50054,7 @@
         <v>0</v>
       </c>
       <c r="O831" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="P831" s="1">
         <v>0</v>
@@ -50091,7 +50095,7 @@
         <v>1</v>
       </c>
       <c r="J832" s="61" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K832" s="60">
         <v>16</v>
@@ -50106,7 +50110,7 @@
         <v>0</v>
       </c>
       <c r="O832" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="P832" s="1">
         <v>0</v>
@@ -50147,7 +50151,7 @@
         <v>1</v>
       </c>
       <c r="J833" s="61" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K833" s="60">
         <v>16</v>
@@ -50162,7 +50166,7 @@
         <v>0</v>
       </c>
       <c r="O833" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P833" s="1">
         <v>0</v>
@@ -50203,7 +50207,7 @@
         <v>2</v>
       </c>
       <c r="J834" s="61" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K834" s="60">
         <v>16</v>
@@ -50218,7 +50222,7 @@
         <v>0</v>
       </c>
       <c r="O834" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="P834" s="1">
         <v>0</v>
@@ -50259,7 +50263,7 @@
         <v>2</v>
       </c>
       <c r="J835" s="61" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K835" s="60">
         <v>16</v>
@@ -50274,7 +50278,7 @@
         <v>0</v>
       </c>
       <c r="O835" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="P835" s="1">
         <v>0</v>
@@ -50315,7 +50319,7 @@
         <v>2</v>
       </c>
       <c r="J836" s="61" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K836" s="60">
         <v>16</v>
@@ -50330,7 +50334,7 @@
         <v>0</v>
       </c>
       <c r="O836" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="P836" s="1">
         <v>0</v>
@@ -50371,7 +50375,7 @@
         <v>2</v>
       </c>
       <c r="J837" s="61" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K837" s="60">
         <v>16</v>
@@ -50386,7 +50390,7 @@
         <v>0</v>
       </c>
       <c r="O837" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="P837" s="1">
         <v>0</v>
@@ -50427,7 +50431,7 @@
         <v>3</v>
       </c>
       <c r="J838" s="61" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K838" s="60">
         <v>16</v>
@@ -50442,7 +50446,7 @@
         <v>0</v>
       </c>
       <c r="O838" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="P838" s="1">
         <v>0</v>
@@ -50483,7 +50487,7 @@
         <v>3</v>
       </c>
       <c r="J839" s="61" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K839" s="60">
         <v>16</v>
@@ -50498,7 +50502,7 @@
         <v>0</v>
       </c>
       <c r="O839" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P839" s="1">
         <v>0</v>
@@ -50539,7 +50543,7 @@
         <v>3</v>
       </c>
       <c r="J840" s="61" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K840" s="60">
         <v>16</v>
@@ -50554,7 +50558,7 @@
         <v>0</v>
       </c>
       <c r="O840" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P840" s="1">
         <v>0</v>
@@ -50595,7 +50599,7 @@
         <v>3</v>
       </c>
       <c r="J841" s="61" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="K841" s="60">
         <v>16</v>
@@ -50610,7 +50614,7 @@
         <v>0</v>
       </c>
       <c r="O841" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="P841" s="1">
         <v>0</v>
@@ -50651,7 +50655,7 @@
         <v>3</v>
       </c>
       <c r="J842" s="61" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="K842" s="60">
         <v>16</v>
@@ -50666,7 +50670,7 @@
         <v>0</v>
       </c>
       <c r="O842" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="P842" s="1">
         <v>0</v>
@@ -50707,7 +50711,7 @@
         <v>3</v>
       </c>
       <c r="J843" s="61" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K843" s="60">
         <v>16</v>
@@ -50722,7 +50726,7 @@
         <v>0</v>
       </c>
       <c r="O843" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="P843" s="1">
         <v>0</v>
@@ -50763,7 +50767,7 @@
         <v>4</v>
       </c>
       <c r="J844" s="61" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K844" s="60">
         <v>16</v>
@@ -50778,7 +50782,7 @@
         <v>0</v>
       </c>
       <c r="O844" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P844" s="1">
         <v>0</v>
@@ -50819,7 +50823,7 @@
         <v>4</v>
       </c>
       <c r="J845" s="61" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K845" s="60">
         <v>16</v>
@@ -50834,7 +50838,7 @@
         <v>0</v>
       </c>
       <c r="O845" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="P845" s="1">
         <v>0</v>
@@ -50875,7 +50879,7 @@
         <v>4</v>
       </c>
       <c r="J846" s="61" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K846" s="60">
         <v>16</v>
@@ -50890,7 +50894,7 @@
         <v>0</v>
       </c>
       <c r="O846" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P846" s="1">
         <v>0</v>
@@ -50931,7 +50935,7 @@
         <v>4</v>
       </c>
       <c r="J847" s="61" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="K847" s="60">
         <v>16</v>
@@ -50946,7 +50950,7 @@
         <v>0</v>
       </c>
       <c r="O847" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="P847" s="1">
         <v>0</v>
@@ -50987,7 +50991,7 @@
         <v>4</v>
       </c>
       <c r="J848" s="61" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="K848" s="60">
         <v>16</v>
@@ -51002,7 +51006,7 @@
         <v>0</v>
       </c>
       <c r="O848" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="P848" s="1">
         <v>0</v>
@@ -51043,7 +51047,7 @@
         <v>4</v>
       </c>
       <c r="J849" s="61" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K849" s="60">
         <v>16</v>
@@ -51058,7 +51062,7 @@
         <v>0</v>
       </c>
       <c r="O849" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="P849" s="1">
         <v>0</v>
@@ -51099,7 +51103,7 @@
         <v>4</v>
       </c>
       <c r="J850" s="61" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K850" s="60">
         <v>16</v>
@@ -51114,7 +51118,7 @@
         <v>0</v>
       </c>
       <c r="O850" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="P850" s="1">
         <v>0</v>
@@ -51155,7 +51159,7 @@
         <v>4</v>
       </c>
       <c r="J851" s="61" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K851" s="60">
         <v>16</v>
@@ -51170,7 +51174,7 @@
         <v>0</v>
       </c>
       <c r="O851" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="P851" s="1">
         <v>0</v>
@@ -51211,7 +51215,7 @@
         <v>5</v>
       </c>
       <c r="J852" s="61" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K852" s="60">
         <v>16</v>
@@ -51226,7 +51230,7 @@
         <v>0</v>
       </c>
       <c r="O852" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P852" s="1">
         <v>0</v>
@@ -51267,7 +51271,7 @@
         <v>5</v>
       </c>
       <c r="J853" s="61" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="K853" s="60">
         <v>16</v>
@@ -51282,7 +51286,7 @@
         <v>0</v>
       </c>
       <c r="O853" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P853" s="1">
         <v>0</v>
@@ -51323,7 +51327,7 @@
         <v>5</v>
       </c>
       <c r="J854" s="61" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="K854" s="60">
         <v>16</v>
@@ -51338,7 +51342,7 @@
         <v>0</v>
       </c>
       <c r="O854" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P854" s="1">
         <v>0</v>
@@ -51379,7 +51383,7 @@
         <v>5</v>
       </c>
       <c r="J855" s="61" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="K855" s="60">
         <v>16</v>
@@ -51394,7 +51398,7 @@
         <v>0</v>
       </c>
       <c r="O855" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="P855" s="1">
         <v>0</v>
@@ -51435,7 +51439,7 @@
         <v>5</v>
       </c>
       <c r="J856" s="61" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="K856" s="60">
         <v>16</v>
@@ -51450,7 +51454,7 @@
         <v>0</v>
       </c>
       <c r="O856" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="P856" s="1">
         <v>0</v>
@@ -51491,7 +51495,7 @@
         <v>5</v>
       </c>
       <c r="J857" s="61" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K857" s="60">
         <v>16</v>
@@ -51506,7 +51510,7 @@
         <v>0</v>
       </c>
       <c r="O857" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="P857" s="1">
         <v>0</v>
@@ -51547,7 +51551,7 @@
         <v>5</v>
       </c>
       <c r="J858" s="61" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K858" s="60">
         <v>16</v>
@@ -51562,7 +51566,7 @@
         <v>0</v>
       </c>
       <c r="O858" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="P858" s="1">
         <v>0</v>
@@ -51603,7 +51607,7 @@
         <v>5</v>
       </c>
       <c r="J859" s="61" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="K859" s="60">
         <v>16</v>
@@ -51618,7 +51622,7 @@
         <v>0</v>
       </c>
       <c r="O859" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="P859" s="1">
         <v>0</v>
@@ -51659,7 +51663,7 @@
         <v>5</v>
       </c>
       <c r="J860" s="61" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K860" s="60">
         <v>16</v>
@@ -51674,7 +51678,7 @@
         <v>0</v>
       </c>
       <c r="O860" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="P860" s="1">
         <v>0</v>
@@ -51715,7 +51719,7 @@
         <v>5</v>
       </c>
       <c r="J861" s="61" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K861" s="60">
         <v>16</v>
@@ -51730,7 +51734,7 @@
         <v>0</v>
       </c>
       <c r="O861" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="P861" s="1">
         <v>0</v>
@@ -51771,7 +51775,7 @@
         <v>5</v>
       </c>
       <c r="J862" s="61" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="K862" s="60">
         <v>16</v>
@@ -51786,7 +51790,7 @@
         <v>0</v>
       </c>
       <c r="O862" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="P862" s="1">
         <v>0</v>
@@ -51827,7 +51831,7 @@
         <v>1</v>
       </c>
       <c r="J863" s="61" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="K863" s="60">
         <v>30</v>
@@ -51842,7 +51846,7 @@
         <v>1</v>
       </c>
       <c r="O863" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P863" s="1">
         <v>0</v>
@@ -51883,7 +51887,7 @@
         <v>1</v>
       </c>
       <c r="J864" s="61" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K864" s="60">
         <v>30</v>
@@ -51898,7 +51902,7 @@
         <v>1</v>
       </c>
       <c r="O864" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="P864" s="1">
         <v>0</v>
@@ -51939,7 +51943,7 @@
         <v>1</v>
       </c>
       <c r="J865" s="61" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="K865" s="60">
         <v>30</v>
@@ -51954,7 +51958,7 @@
         <v>1</v>
       </c>
       <c r="O865" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="P865" s="1">
         <v>0</v>
@@ -51995,7 +51999,7 @@
         <v>1</v>
       </c>
       <c r="J866" s="61" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K866" s="60">
         <v>30</v>
@@ -52010,7 +52014,7 @@
         <v>1</v>
       </c>
       <c r="O866" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="P866" s="1">
         <v>0</v>
@@ -52051,7 +52055,7 @@
         <v>2</v>
       </c>
       <c r="J867" s="61" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K867" s="60">
         <v>30</v>
@@ -52066,7 +52070,7 @@
         <v>1</v>
       </c>
       <c r="O867" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="P867" s="1">
         <v>0</v>
@@ -52107,7 +52111,7 @@
         <v>2</v>
       </c>
       <c r="J868" s="61" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="K868" s="60">
         <v>30</v>
@@ -52122,7 +52126,7 @@
         <v>1</v>
       </c>
       <c r="O868" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="P868" s="1">
         <v>0</v>
@@ -52163,7 +52167,7 @@
         <v>2</v>
       </c>
       <c r="J869" s="61" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K869" s="60">
         <v>30</v>
@@ -52178,7 +52182,7 @@
         <v>1</v>
       </c>
       <c r="O869" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="P869" s="1">
         <v>0</v>
@@ -52219,7 +52223,7 @@
         <v>2</v>
       </c>
       <c r="J870" s="61" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="K870" s="60">
         <v>30</v>
@@ -52234,7 +52238,7 @@
         <v>1</v>
       </c>
       <c r="O870" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P870" s="1">
         <v>0</v>
@@ -52275,7 +52279,7 @@
         <v>2</v>
       </c>
       <c r="J871" s="61" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K871" s="60">
         <v>30</v>
@@ -52290,7 +52294,7 @@
         <v>1</v>
       </c>
       <c r="O871" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="P871" s="1">
         <v>0</v>
@@ -52331,7 +52335,7 @@
         <v>2</v>
       </c>
       <c r="J872" s="61" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="K872" s="60">
         <v>30</v>
@@ -52346,7 +52350,7 @@
         <v>1</v>
       </c>
       <c r="O872" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P872" s="1">
         <v>0</v>
@@ -52387,7 +52391,7 @@
         <v>3</v>
       </c>
       <c r="J873" s="61" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K873" s="60">
         <v>30</v>
@@ -52402,7 +52406,7 @@
         <v>1</v>
       </c>
       <c r="O873" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P873" s="1">
         <v>0</v>
@@ -52443,7 +52447,7 @@
         <v>3</v>
       </c>
       <c r="J874" s="61" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K874" s="60">
         <v>30</v>
@@ -52458,7 +52462,7 @@
         <v>1</v>
       </c>
       <c r="O874" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="P874" s="1">
         <v>0</v>
@@ -52499,7 +52503,7 @@
         <v>3</v>
       </c>
       <c r="J875" s="61" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K875" s="60">
         <v>30</v>
@@ -52514,7 +52518,7 @@
         <v>1</v>
       </c>
       <c r="O875" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P875" s="1">
         <v>0</v>
@@ -52555,7 +52559,7 @@
         <v>3</v>
       </c>
       <c r="J876" s="61" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K876" s="60">
         <v>30</v>
@@ -52570,7 +52574,7 @@
         <v>1</v>
       </c>
       <c r="O876" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P876" s="1">
         <v>0</v>
@@ -52611,7 +52615,7 @@
         <v>3</v>
       </c>
       <c r="J877" s="61" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="K877" s="60">
         <v>30</v>
@@ -52626,7 +52630,7 @@
         <v>1</v>
       </c>
       <c r="O877" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P877" s="1">
         <v>0</v>
@@ -52667,7 +52671,7 @@
         <v>3</v>
       </c>
       <c r="J878" s="61" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K878" s="60">
         <v>30</v>
@@ -52682,7 +52686,7 @@
         <v>1</v>
       </c>
       <c r="O878" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P878" s="1">
         <v>0</v>
@@ -52723,7 +52727,7 @@
         <v>3</v>
       </c>
       <c r="J879" s="61" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K879" s="60">
         <v>30</v>
@@ -52738,7 +52742,7 @@
         <v>1</v>
       </c>
       <c r="O879" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="P879" s="1">
         <v>0</v>
@@ -52779,7 +52783,7 @@
         <v>3</v>
       </c>
       <c r="J880" s="61" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K880" s="60">
         <v>30</v>
@@ -52794,7 +52798,7 @@
         <v>1</v>
       </c>
       <c r="O880" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P880" s="1">
         <v>0</v>
@@ -52835,7 +52839,7 @@
         <v>4</v>
       </c>
       <c r="J881" s="61" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K881" s="60">
         <v>30</v>
@@ -52850,7 +52854,7 @@
         <v>1</v>
       </c>
       <c r="O881" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="P881" s="1">
         <v>0</v>
@@ -52891,7 +52895,7 @@
         <v>4</v>
       </c>
       <c r="J882" s="61" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="K882" s="60">
         <v>30</v>
@@ -52906,7 +52910,7 @@
         <v>1</v>
       </c>
       <c r="O882" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="P882" s="1">
         <v>0</v>
@@ -52947,7 +52951,7 @@
         <v>4</v>
       </c>
       <c r="J883" s="61" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K883" s="60">
         <v>30</v>
@@ -52962,7 +52966,7 @@
         <v>1</v>
       </c>
       <c r="O883" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="P883" s="1">
         <v>0</v>
@@ -53003,7 +53007,7 @@
         <v>4</v>
       </c>
       <c r="J884" s="61" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K884" s="60">
         <v>30</v>
@@ -53018,7 +53022,7 @@
         <v>1</v>
       </c>
       <c r="O884" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P884" s="1">
         <v>0</v>
@@ -53059,7 +53063,7 @@
         <v>4</v>
       </c>
       <c r="J885" s="61" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="K885" s="60">
         <v>30</v>
@@ -53074,7 +53078,7 @@
         <v>1</v>
       </c>
       <c r="O885" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="P885" s="1">
         <v>0</v>
@@ -53115,7 +53119,7 @@
         <v>4</v>
       </c>
       <c r="J886" s="61" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K886" s="60">
         <v>30</v>
@@ -53130,7 +53134,7 @@
         <v>1</v>
       </c>
       <c r="O886" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="P886" s="1">
         <v>0</v>
@@ -53171,7 +53175,7 @@
         <v>4</v>
       </c>
       <c r="J887" s="61" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K887" s="60">
         <v>30</v>
@@ -53186,7 +53190,7 @@
         <v>1</v>
       </c>
       <c r="O887" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P887" s="1">
         <v>0</v>
@@ -53227,7 +53231,7 @@
         <v>4</v>
       </c>
       <c r="J888" s="61" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="K888" s="60">
         <v>30</v>
@@ -53242,7 +53246,7 @@
         <v>1</v>
       </c>
       <c r="O888" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P888" s="1">
         <v>0</v>
@@ -53283,7 +53287,7 @@
         <v>4</v>
       </c>
       <c r="J889" s="61" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="K889" s="60">
         <v>30</v>
@@ -53298,7 +53302,7 @@
         <v>1</v>
       </c>
       <c r="O889" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="P889" s="1">
         <v>0</v>
@@ -53339,7 +53343,7 @@
         <v>4</v>
       </c>
       <c r="J890" s="61" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K890" s="60">
         <v>30</v>
@@ -53354,7 +53358,7 @@
         <v>1</v>
       </c>
       <c r="O890" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="P890" s="1">
         <v>0</v>
@@ -53395,7 +53399,7 @@
         <v>5</v>
       </c>
       <c r="J891" s="61" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="K891" s="60">
         <v>30</v>
@@ -53410,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="O891" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="P891" s="1">
         <v>0</v>
@@ -53451,7 +53455,7 @@
         <v>5</v>
       </c>
       <c r="J892" s="61" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="K892" s="60">
         <v>30</v>
@@ -53466,7 +53470,7 @@
         <v>1</v>
       </c>
       <c r="O892" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="P892" s="1">
         <v>0</v>
@@ -53507,7 +53511,7 @@
         <v>5</v>
       </c>
       <c r="J893" s="63" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="K893" s="60">
         <v>30</v>
@@ -53522,7 +53526,7 @@
         <v>1</v>
       </c>
       <c r="O893" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P893" s="1">
         <v>0</v>
@@ -53563,7 +53567,7 @@
         <v>5</v>
       </c>
       <c r="J894" s="63" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="K894" s="60">
         <v>30</v>
@@ -53578,7 +53582,7 @@
         <v>1</v>
       </c>
       <c r="O894" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="P894" s="1">
         <v>0</v>
@@ -53619,7 +53623,7 @@
         <v>5</v>
       </c>
       <c r="J895" s="63" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K895" s="60">
         <v>30</v>
@@ -53634,7 +53638,7 @@
         <v>1</v>
       </c>
       <c r="O895" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="P895" s="1">
         <v>0</v>
@@ -53675,7 +53679,7 @@
         <v>5</v>
       </c>
       <c r="J896" s="63" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="K896" s="60">
         <v>30</v>
@@ -53690,7 +53694,7 @@
         <v>1</v>
       </c>
       <c r="O896" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="P896" s="1">
         <v>0</v>
@@ -53731,7 +53735,7 @@
         <v>5</v>
       </c>
       <c r="J897" s="63" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="K897" s="60">
         <v>30</v>
@@ -53746,7 +53750,7 @@
         <v>1</v>
       </c>
       <c r="O897" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="P897" s="1">
         <v>0</v>
@@ -53787,7 +53791,7 @@
         <v>5</v>
       </c>
       <c r="J898" s="63" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="K898" s="60">
         <v>30</v>
@@ -53802,7 +53806,7 @@
         <v>1</v>
       </c>
       <c r="O898" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="P898" s="1">
         <v>0</v>
@@ -53843,7 +53847,7 @@
         <v>5</v>
       </c>
       <c r="J899" s="63" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K899" s="60">
         <v>30</v>
@@ -53858,7 +53862,7 @@
         <v>1</v>
       </c>
       <c r="O899" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="P899" s="1">
         <v>0</v>
@@ -53899,7 +53903,7 @@
         <v>5</v>
       </c>
       <c r="J900" s="63" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K900" s="60">
         <v>30</v>
@@ -53914,7 +53918,7 @@
         <v>1</v>
       </c>
       <c r="O900" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="P900" s="1">
         <v>0</v>
@@ -53955,7 +53959,7 @@
         <v>5</v>
       </c>
       <c r="J901" s="63" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="K901" s="60">
         <v>30</v>
@@ -53970,7 +53974,7 @@
         <v>1</v>
       </c>
       <c r="O901" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="P901" s="1">
         <v>0</v>
@@ -54011,7 +54015,7 @@
         <v>5</v>
       </c>
       <c r="J902" s="63" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="K902" s="60">
         <v>30</v>
@@ -54026,7 +54030,7 @@
         <v>1</v>
       </c>
       <c r="O902" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="P902" s="1">
         <v>0</v>
@@ -54067,7 +54071,7 @@
         <v>1</v>
       </c>
       <c r="J903" s="63" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="K903" s="62">
         <v>400</v>
@@ -54082,7 +54086,7 @@
         <v>2</v>
       </c>
       <c r="O903" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="P903" s="1">
         <v>0</v>
@@ -54123,7 +54127,7 @@
         <v>1</v>
       </c>
       <c r="J904" s="63" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K904" s="62">
         <v>400</v>
@@ -54138,7 +54142,7 @@
         <v>2</v>
       </c>
       <c r="O904" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="P904" s="1">
         <v>0</v>
@@ -54179,7 +54183,7 @@
         <v>1</v>
       </c>
       <c r="J905" s="63" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K905" s="62">
         <v>400</v>
@@ -54194,7 +54198,7 @@
         <v>2</v>
       </c>
       <c r="O905" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="P905" s="1">
         <v>0</v>
@@ -54235,7 +54239,7 @@
         <v>1</v>
       </c>
       <c r="J906" s="63" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K906" s="62">
         <v>400</v>
@@ -54250,7 +54254,7 @@
         <v>2</v>
       </c>
       <c r="O906" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="P906" s="1">
         <v>0</v>
@@ -54291,7 +54295,7 @@
         <v>1</v>
       </c>
       <c r="J907" s="63" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="K907" s="62">
         <v>400</v>
@@ -54306,7 +54310,7 @@
         <v>2</v>
       </c>
       <c r="O907" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="P907" s="1">
         <v>0</v>
@@ -54347,7 +54351,7 @@
         <v>1</v>
       </c>
       <c r="J908" s="63" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K908" s="62">
         <v>400</v>
@@ -54362,7 +54366,7 @@
         <v>2</v>
       </c>
       <c r="O908" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="P908" s="1">
         <v>0</v>
@@ -54403,7 +54407,7 @@
         <v>2</v>
       </c>
       <c r="J909" s="63" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="K909" s="62">
         <v>400</v>
@@ -54418,7 +54422,7 @@
         <v>2</v>
       </c>
       <c r="O909" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="P909" s="1">
         <v>0</v>
@@ -54459,7 +54463,7 @@
         <v>2</v>
       </c>
       <c r="J910" s="63" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K910" s="62">
         <v>400</v>
@@ -54474,7 +54478,7 @@
         <v>2</v>
       </c>
       <c r="O910" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="P910" s="1">
         <v>0</v>
@@ -54515,7 +54519,7 @@
         <v>2</v>
       </c>
       <c r="J911" s="63" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K911" s="62">
         <v>400</v>
@@ -54530,7 +54534,7 @@
         <v>2</v>
       </c>
       <c r="O911" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="P911" s="1">
         <v>0</v>
@@ -54571,7 +54575,7 @@
         <v>2</v>
       </c>
       <c r="J912" s="63" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="K912" s="62">
         <v>400</v>
@@ -54586,7 +54590,7 @@
         <v>2</v>
       </c>
       <c r="O912" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="P912" s="1">
         <v>0</v>
@@ -54627,7 +54631,7 @@
         <v>2</v>
       </c>
       <c r="J913" s="63" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K913" s="62">
         <v>400</v>
@@ -54642,7 +54646,7 @@
         <v>2</v>
       </c>
       <c r="O913" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="P913" s="1">
         <v>0</v>
@@ -54683,7 +54687,7 @@
         <v>2</v>
       </c>
       <c r="J914" s="63" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="K914" s="62">
         <v>400</v>
@@ -54698,7 +54702,7 @@
         <v>2</v>
       </c>
       <c r="O914" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="P914" s="1">
         <v>0</v>
@@ -54739,7 +54743,7 @@
         <v>2</v>
       </c>
       <c r="J915" s="63" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="K915" s="62">
         <v>400</v>
@@ -54754,7 +54758,7 @@
         <v>2</v>
       </c>
       <c r="O915" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="P915" s="1">
         <v>0</v>
@@ -54795,7 +54799,7 @@
         <v>2</v>
       </c>
       <c r="J916" s="63" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="K916" s="62">
         <v>400</v>
@@ -54810,7 +54814,7 @@
         <v>2</v>
       </c>
       <c r="O916" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="P916" s="1">
         <v>0</v>
@@ -54851,7 +54855,7 @@
         <v>3</v>
       </c>
       <c r="J917" s="63" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K917" s="62">
         <v>400</v>
@@ -54866,7 +54870,7 @@
         <v>2</v>
       </c>
       <c r="O917" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="P917" s="1">
         <v>0</v>
@@ -54907,7 +54911,7 @@
         <v>3</v>
       </c>
       <c r="J918" s="63" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K918" s="62">
         <v>400</v>
@@ -54922,7 +54926,7 @@
         <v>2</v>
       </c>
       <c r="O918" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="P918" s="1">
         <v>0</v>
@@ -54963,7 +54967,7 @@
         <v>3</v>
       </c>
       <c r="J919" s="63" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K919" s="62">
         <v>400</v>
@@ -54978,7 +54982,7 @@
         <v>2</v>
       </c>
       <c r="O919" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="P919" s="1">
         <v>0</v>
@@ -55019,7 +55023,7 @@
         <v>3</v>
       </c>
       <c r="J920" s="63" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K920" s="62">
         <v>400</v>
@@ -55034,7 +55038,7 @@
         <v>2</v>
       </c>
       <c r="O920" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="P920" s="1">
         <v>0</v>
@@ -55075,7 +55079,7 @@
         <v>3</v>
       </c>
       <c r="J921" s="63" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="K921" s="62">
         <v>400</v>
@@ -55090,7 +55094,7 @@
         <v>2</v>
       </c>
       <c r="O921" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="P921" s="1">
         <v>0</v>
@@ -55131,7 +55135,7 @@
         <v>3</v>
       </c>
       <c r="J922" s="63" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K922" s="62">
         <v>400</v>
@@ -55146,7 +55150,7 @@
         <v>2</v>
       </c>
       <c r="O922" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="P922" s="1">
         <v>0</v>
@@ -55187,7 +55191,7 @@
         <v>3</v>
       </c>
       <c r="J923" s="63" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="K923" s="62">
         <v>400</v>
@@ -55202,7 +55206,7 @@
         <v>2</v>
       </c>
       <c r="O923" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="P923" s="1">
         <v>0</v>
@@ -55243,7 +55247,7 @@
         <v>3</v>
       </c>
       <c r="J924" s="63" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="K924" s="62">
         <v>400</v>
@@ -55258,7 +55262,7 @@
         <v>2</v>
       </c>
       <c r="O924" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="P924" s="1">
         <v>0</v>
@@ -55299,7 +55303,7 @@
         <v>3</v>
       </c>
       <c r="J925" s="63" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="K925" s="62">
         <v>400</v>
@@ -55314,7 +55318,7 @@
         <v>2</v>
       </c>
       <c r="O925" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="P925" s="1">
         <v>0</v>
@@ -55355,7 +55359,7 @@
         <v>3</v>
       </c>
       <c r="J926" s="63" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K926" s="62">
         <v>400</v>
@@ -55370,7 +55374,7 @@
         <v>2</v>
       </c>
       <c r="O926" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="P926" s="1">
         <v>0</v>
@@ -55411,7 +55415,7 @@
         <v>4</v>
       </c>
       <c r="J927" s="63" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="K927" s="62">
         <v>400</v>
@@ -55426,7 +55430,7 @@
         <v>2</v>
       </c>
       <c r="O927" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="P927" s="1">
         <v>0</v>
@@ -55467,7 +55471,7 @@
         <v>4</v>
       </c>
       <c r="J928" s="63" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K928" s="62">
         <v>400</v>
@@ -55482,7 +55486,7 @@
         <v>2</v>
       </c>
       <c r="O928" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="P928" s="1">
         <v>0</v>
@@ -55523,7 +55527,7 @@
         <v>4</v>
       </c>
       <c r="J929" s="63" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="K929" s="62">
         <v>400</v>
@@ -55538,7 +55542,7 @@
         <v>2</v>
       </c>
       <c r="O929" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="P929" s="1">
         <v>0</v>
@@ -55579,7 +55583,7 @@
         <v>4</v>
       </c>
       <c r="J930" s="63" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="K930" s="62">
         <v>400</v>
@@ -55594,7 +55598,7 @@
         <v>2</v>
       </c>
       <c r="O930" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="P930" s="1">
         <v>0</v>
@@ -55635,7 +55639,7 @@
         <v>4</v>
       </c>
       <c r="J931" s="63" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K931" s="62">
         <v>400</v>
@@ -55650,7 +55654,7 @@
         <v>2</v>
       </c>
       <c r="O931" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="P931" s="1">
         <v>0</v>
@@ -55691,7 +55695,7 @@
         <v>4</v>
       </c>
       <c r="J932" s="63" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="K932" s="62">
         <v>400</v>
@@ -55706,7 +55710,7 @@
         <v>2</v>
       </c>
       <c r="O932" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="P932" s="1">
         <v>0</v>
@@ -55747,7 +55751,7 @@
         <v>4</v>
       </c>
       <c r="J933" s="63" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K933" s="62">
         <v>400</v>
@@ -55762,7 +55766,7 @@
         <v>2</v>
       </c>
       <c r="O933" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="P933" s="1">
         <v>0</v>
@@ -55803,7 +55807,7 @@
         <v>4</v>
       </c>
       <c r="J934" s="63" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="K934" s="62">
         <v>400</v>
@@ -55818,7 +55822,7 @@
         <v>2</v>
       </c>
       <c r="O934" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="P934" s="1">
         <v>0</v>
@@ -55859,7 +55863,7 @@
         <v>4</v>
       </c>
       <c r="J935" s="63" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="K935" s="62">
         <v>400</v>
@@ -55874,7 +55878,7 @@
         <v>2</v>
       </c>
       <c r="O935" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="P935" s="1">
         <v>0</v>
@@ -55915,7 +55919,7 @@
         <v>4</v>
       </c>
       <c r="J936" s="63" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="K936" s="62">
         <v>400</v>
@@ -55930,7 +55934,7 @@
         <v>2</v>
       </c>
       <c r="O936" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="P936" s="1">
         <v>0</v>
@@ -55971,7 +55975,7 @@
         <v>4</v>
       </c>
       <c r="J937" s="63" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="K937" s="62">
         <v>400</v>
@@ -55986,7 +55990,7 @@
         <v>2</v>
       </c>
       <c r="O937" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="P937" s="1">
         <v>0</v>
@@ -56027,7 +56031,7 @@
         <v>4</v>
       </c>
       <c r="J938" s="63" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K938" s="62">
         <v>400</v>
@@ -56042,7 +56046,7 @@
         <v>2</v>
       </c>
       <c r="O938" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="P938" s="1">
         <v>0</v>
@@ -56083,7 +56087,7 @@
         <v>5</v>
       </c>
       <c r="J939" s="63" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K939" s="62">
         <v>400</v>
@@ -56098,7 +56102,7 @@
         <v>2</v>
       </c>
       <c r="O939" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="P939" s="1">
         <v>0</v>
@@ -56139,7 +56143,7 @@
         <v>5</v>
       </c>
       <c r="J940" s="63" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K940" s="62">
         <v>400</v>
@@ -56154,7 +56158,7 @@
         <v>2</v>
       </c>
       <c r="O940" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="P940" s="1">
         <v>0</v>
@@ -56195,7 +56199,7 @@
         <v>5</v>
       </c>
       <c r="J941" s="63" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="K941" s="62">
         <v>400</v>
@@ -56210,7 +56214,7 @@
         <v>2</v>
       </c>
       <c r="O941" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="P941" s="1">
         <v>0</v>
@@ -56251,7 +56255,7 @@
         <v>5</v>
       </c>
       <c r="J942" s="63" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K942" s="62">
         <v>400</v>
@@ -56266,7 +56270,7 @@
         <v>2</v>
       </c>
       <c r="O942" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="P942" s="1">
         <v>0</v>
@@ -56307,7 +56311,7 @@
         <v>5</v>
       </c>
       <c r="J943" s="63" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K943" s="62">
         <v>400</v>
@@ -56322,7 +56326,7 @@
         <v>2</v>
       </c>
       <c r="O943" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="P943" s="1">
         <v>0</v>
@@ -56363,7 +56367,7 @@
         <v>5</v>
       </c>
       <c r="J944" s="63" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="K944" s="62">
         <v>400</v>
@@ -56378,7 +56382,7 @@
         <v>2</v>
       </c>
       <c r="O944" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="P944" s="1">
         <v>0</v>
@@ -56419,7 +56423,7 @@
         <v>5</v>
       </c>
       <c r="J945" s="63" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="K945" s="62">
         <v>400</v>
@@ -56434,7 +56438,7 @@
         <v>2</v>
       </c>
       <c r="O945" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="P945" s="1">
         <v>0</v>
@@ -56475,7 +56479,7 @@
         <v>5</v>
       </c>
       <c r="J946" s="63" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="K946" s="62">
         <v>400</v>
@@ -56490,7 +56494,7 @@
         <v>2</v>
       </c>
       <c r="O946" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="P946" s="1">
         <v>0</v>
@@ -56531,7 +56535,7 @@
         <v>5</v>
       </c>
       <c r="J947" s="63" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K947" s="62">
         <v>400</v>
@@ -56546,7 +56550,7 @@
         <v>2</v>
       </c>
       <c r="O947" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="P947" s="1">
         <v>0</v>
@@ -56587,7 +56591,7 @@
         <v>5</v>
       </c>
       <c r="J948" s="63" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K948" s="62">
         <v>400</v>
@@ -56602,7 +56606,7 @@
         <v>2</v>
       </c>
       <c r="O948" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="P948" s="1">
         <v>0</v>
@@ -56643,7 +56647,7 @@
         <v>5</v>
       </c>
       <c r="J949" s="63" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="K949" s="62">
         <v>400</v>
@@ -56658,7 +56662,7 @@
         <v>2</v>
       </c>
       <c r="O949" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="P949" s="1">
         <v>0</v>
@@ -56699,7 +56703,7 @@
         <v>5</v>
       </c>
       <c r="J950" s="63" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="K950" s="62">
         <v>400</v>
@@ -56714,7 +56718,7 @@
         <v>2</v>
       </c>
       <c r="O950" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="P950" s="1">
         <v>0</v>
@@ -56755,7 +56759,7 @@
         <v>5</v>
       </c>
       <c r="J951" s="63" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="K951" s="62">
         <v>400</v>
@@ -56770,7 +56774,7 @@
         <v>2</v>
       </c>
       <c r="O951" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="P951" s="1">
         <v>0</v>
@@ -56811,7 +56815,7 @@
         <v>5</v>
       </c>
       <c r="J952" s="63" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="K952" s="62">
         <v>400</v>
@@ -56826,7 +56830,7 @@
         <v>2</v>
       </c>
       <c r="O952" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P952" s="1">
         <v>0</v>
@@ -56867,7 +56871,7 @@
         <v>1</v>
       </c>
       <c r="J953" s="63" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="K953" s="62">
         <v>6000</v>
@@ -56882,7 +56886,7 @@
         <v>3</v>
       </c>
       <c r="O953" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="P953" s="1">
         <v>0</v>
@@ -56923,7 +56927,7 @@
         <v>1</v>
       </c>
       <c r="J954" s="63" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="K954" s="62">
         <v>6000</v>
@@ -56938,7 +56942,7 @@
         <v>3</v>
       </c>
       <c r="O954" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="P954" s="1">
         <v>0</v>
@@ -56979,7 +56983,7 @@
         <v>1</v>
       </c>
       <c r="J955" s="63" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="K955" s="62">
         <v>6000</v>
@@ -56994,7 +56998,7 @@
         <v>3</v>
       </c>
       <c r="O955" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="P955" s="1">
         <v>0</v>
@@ -57035,7 +57039,7 @@
         <v>1</v>
       </c>
       <c r="J956" s="63" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="K956" s="62">
         <v>6000</v>
@@ -57050,7 +57054,7 @@
         <v>3</v>
       </c>
       <c r="O956" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="P956" s="1">
         <v>0</v>
@@ -57091,7 +57095,7 @@
         <v>1</v>
       </c>
       <c r="J957" s="63" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="K957" s="62">
         <v>6000</v>
@@ -57106,7 +57110,7 @@
         <v>3</v>
       </c>
       <c r="O957" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="P957" s="1">
         <v>0</v>
@@ -57147,7 +57151,7 @@
         <v>1</v>
       </c>
       <c r="J958" s="63" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="K958" s="62">
         <v>6000</v>
@@ -57162,7 +57166,7 @@
         <v>3</v>
       </c>
       <c r="O958" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="P958" s="1">
         <v>0</v>
@@ -57203,7 +57207,7 @@
         <v>1</v>
       </c>
       <c r="J959" s="63" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="K959" s="62">
         <v>6000</v>
@@ -57218,7 +57222,7 @@
         <v>3</v>
       </c>
       <c r="O959" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="P959" s="1">
         <v>0</v>
@@ -57259,7 +57263,7 @@
         <v>1</v>
       </c>
       <c r="J960" s="63" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="K960" s="62">
         <v>6000</v>
@@ -57274,7 +57278,7 @@
         <v>3</v>
       </c>
       <c r="O960" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="P960" s="1">
         <v>0</v>
@@ -57315,7 +57319,7 @@
         <v>2</v>
       </c>
       <c r="J961" s="63" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="K961" s="62">
         <v>6000</v>
@@ -57330,7 +57334,7 @@
         <v>3</v>
       </c>
       <c r="O961" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="P961" s="1">
         <v>0</v>
@@ -57371,7 +57375,7 @@
         <v>2</v>
       </c>
       <c r="J962" s="63" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="K962" s="62">
         <v>6000</v>
@@ -57386,7 +57390,7 @@
         <v>3</v>
       </c>
       <c r="O962" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="P962" s="1">
         <v>0</v>
@@ -57427,7 +57431,7 @@
         <v>2</v>
       </c>
       <c r="J963" s="63" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="K963" s="62">
         <v>6000</v>
@@ -57442,7 +57446,7 @@
         <v>3</v>
       </c>
       <c r="O963" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="P963" s="1">
         <v>0</v>
@@ -57483,7 +57487,7 @@
         <v>2</v>
       </c>
       <c r="J964" s="63" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="K964" s="62">
         <v>6000</v>
@@ -57498,7 +57502,7 @@
         <v>3</v>
       </c>
       <c r="O964" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="P964" s="1">
         <v>0</v>
@@ -57539,7 +57543,7 @@
         <v>2</v>
       </c>
       <c r="J965" s="63" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="K965" s="62">
         <v>6000</v>
@@ -57554,7 +57558,7 @@
         <v>3</v>
       </c>
       <c r="O965" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="P965" s="1">
         <v>0</v>
@@ -57595,7 +57599,7 @@
         <v>2</v>
       </c>
       <c r="J966" s="63" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="K966" s="62">
         <v>6000</v>
@@ -57610,7 +57614,7 @@
         <v>3</v>
       </c>
       <c r="O966" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="P966" s="1">
         <v>0</v>
@@ -57651,7 +57655,7 @@
         <v>2</v>
       </c>
       <c r="J967" s="63" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="K967" s="62">
         <v>6000</v>
@@ -57666,7 +57670,7 @@
         <v>3</v>
       </c>
       <c r="O967" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="P967" s="1">
         <v>0</v>
@@ -57707,7 +57711,7 @@
         <v>2</v>
       </c>
       <c r="J968" s="63" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="K968" s="62">
         <v>6000</v>
@@ -57722,7 +57726,7 @@
         <v>3</v>
       </c>
       <c r="O968" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="P968" s="1">
         <v>0</v>
@@ -57763,7 +57767,7 @@
         <v>2</v>
       </c>
       <c r="J969" s="63" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="K969" s="62">
         <v>6000</v>
@@ -57778,7 +57782,7 @@
         <v>3</v>
       </c>
       <c r="O969" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="P969" s="1">
         <v>0</v>
@@ -57819,7 +57823,7 @@
         <v>2</v>
       </c>
       <c r="J970" s="63" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="K970" s="62">
         <v>6000</v>
@@ -57834,7 +57838,7 @@
         <v>3</v>
       </c>
       <c r="O970" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="P970" s="1">
         <v>0</v>
@@ -57875,7 +57879,7 @@
         <v>3</v>
       </c>
       <c r="J971" s="63" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K971" s="62">
         <v>6000</v>
@@ -57890,7 +57894,7 @@
         <v>3</v>
       </c>
       <c r="O971" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="P971" s="1">
         <v>0</v>
@@ -57931,7 +57935,7 @@
         <v>3</v>
       </c>
       <c r="J972" s="63" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="K972" s="62">
         <v>6000</v>
@@ -57946,7 +57950,7 @@
         <v>3</v>
       </c>
       <c r="O972" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="P972" s="1">
         <v>0</v>
@@ -57987,7 +57991,7 @@
         <v>3</v>
       </c>
       <c r="J973" s="63" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="K973" s="62">
         <v>6000</v>
@@ -58002,7 +58006,7 @@
         <v>3</v>
       </c>
       <c r="O973" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="P973" s="1">
         <v>0</v>
@@ -58043,7 +58047,7 @@
         <v>3</v>
       </c>
       <c r="J974" s="63" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="K974" s="62">
         <v>6000</v>
@@ -58058,7 +58062,7 @@
         <v>3</v>
       </c>
       <c r="O974" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="P974" s="1">
         <v>0</v>
@@ -58099,7 +58103,7 @@
         <v>3</v>
       </c>
       <c r="J975" s="63" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="K975" s="62">
         <v>6000</v>
@@ -58114,7 +58118,7 @@
         <v>3</v>
       </c>
       <c r="O975" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="P975" s="1">
         <v>0</v>
@@ -58155,7 +58159,7 @@
         <v>3</v>
       </c>
       <c r="J976" s="63" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="K976" s="62">
         <v>6000</v>
@@ -58170,7 +58174,7 @@
         <v>3</v>
       </c>
       <c r="O976" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="P976" s="1">
         <v>0</v>
@@ -58211,7 +58215,7 @@
         <v>3</v>
       </c>
       <c r="J977" s="63" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="K977" s="62">
         <v>6000</v>
@@ -58226,7 +58230,7 @@
         <v>3</v>
       </c>
       <c r="O977" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="P977" s="1">
         <v>0</v>
@@ -58267,7 +58271,7 @@
         <v>3</v>
       </c>
       <c r="J978" s="63" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="K978" s="62">
         <v>6000</v>
@@ -58282,7 +58286,7 @@
         <v>3</v>
       </c>
       <c r="O978" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="P978" s="1">
         <v>0</v>
@@ -58323,7 +58327,7 @@
         <v>3</v>
       </c>
       <c r="J979" s="63" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="K979" s="62">
         <v>6000</v>
@@ -58338,7 +58342,7 @@
         <v>3</v>
       </c>
       <c r="O979" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="P979" s="1">
         <v>0</v>
@@ -58379,7 +58383,7 @@
         <v>3</v>
       </c>
       <c r="J980" s="63" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="K980" s="62">
         <v>6000</v>
@@ -58394,7 +58398,7 @@
         <v>3</v>
       </c>
       <c r="O980" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="P980" s="1">
         <v>0</v>
@@ -58435,7 +58439,7 @@
         <v>3</v>
       </c>
       <c r="J981" s="63" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="K981" s="62">
         <v>6000</v>
@@ -58450,7 +58454,7 @@
         <v>3</v>
       </c>
       <c r="O981" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="P981" s="1">
         <v>0</v>
@@ -58491,7 +58495,7 @@
         <v>3</v>
       </c>
       <c r="J982" s="63" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="K982" s="62">
         <v>6000</v>
@@ -58506,7 +58510,7 @@
         <v>3</v>
       </c>
       <c r="O982" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="P982" s="1">
         <v>0</v>
@@ -58547,7 +58551,7 @@
         <v>4</v>
       </c>
       <c r="J983" s="63" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K983" s="62">
         <v>6000</v>
@@ -58562,7 +58566,7 @@
         <v>3</v>
       </c>
       <c r="O983" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="P983" s="1">
         <v>0</v>
@@ -58603,7 +58607,7 @@
         <v>4</v>
       </c>
       <c r="J984" s="63" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="K984" s="62">
         <v>6000</v>
@@ -58618,7 +58622,7 @@
         <v>3</v>
       </c>
       <c r="O984" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="P984" s="1">
         <v>0</v>
@@ -58659,7 +58663,7 @@
         <v>4</v>
       </c>
       <c r="J985" s="63" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="K985" s="62">
         <v>6000</v>
@@ -58674,7 +58678,7 @@
         <v>3</v>
       </c>
       <c r="O985" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="P985" s="1">
         <v>0</v>
@@ -58715,7 +58719,7 @@
         <v>4</v>
       </c>
       <c r="J986" s="63" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="K986" s="62">
         <v>6000</v>
@@ -58730,7 +58734,7 @@
         <v>3</v>
       </c>
       <c r="O986" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="P986" s="1">
         <v>0</v>
@@ -58771,7 +58775,7 @@
         <v>4</v>
       </c>
       <c r="J987" s="63" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K987" s="62">
         <v>6000</v>
@@ -58786,7 +58790,7 @@
         <v>3</v>
       </c>
       <c r="O987" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="P987" s="1">
         <v>0</v>
@@ -58827,7 +58831,7 @@
         <v>4</v>
       </c>
       <c r="J988" s="63" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="K988" s="62">
         <v>6000</v>
@@ -58842,7 +58846,7 @@
         <v>3</v>
       </c>
       <c r="O988" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="P988" s="1">
         <v>0</v>
@@ -58883,7 +58887,7 @@
         <v>4</v>
       </c>
       <c r="J989" s="63" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="K989" s="62">
         <v>6000</v>
@@ -58898,7 +58902,7 @@
         <v>3</v>
       </c>
       <c r="O989" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="P989" s="1">
         <v>0</v>
@@ -58939,7 +58943,7 @@
         <v>4</v>
       </c>
       <c r="J990" s="63" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="K990" s="62">
         <v>6000</v>
@@ -58954,7 +58958,7 @@
         <v>3</v>
       </c>
       <c r="O990" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="P990" s="1">
         <v>0</v>
@@ -58995,7 +58999,7 @@
         <v>4</v>
       </c>
       <c r="J991" s="63" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K991" s="62">
         <v>6000</v>
@@ -59010,7 +59014,7 @@
         <v>3</v>
       </c>
       <c r="O991" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="P991" s="1">
         <v>0</v>
@@ -59051,7 +59055,7 @@
         <v>4</v>
       </c>
       <c r="J992" s="63" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K992" s="62">
         <v>6000</v>
@@ -59066,7 +59070,7 @@
         <v>3</v>
       </c>
       <c r="O992" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="P992" s="1">
         <v>0</v>
@@ -59107,7 +59111,7 @@
         <v>4</v>
       </c>
       <c r="J993" s="63" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="K993" s="62">
         <v>6000</v>
@@ -59122,7 +59126,7 @@
         <v>3</v>
       </c>
       <c r="O993" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="P993" s="1">
         <v>0</v>
@@ -59163,7 +59167,7 @@
         <v>4</v>
       </c>
       <c r="J994" s="63" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="K994" s="62">
         <v>6000</v>
@@ -59178,7 +59182,7 @@
         <v>3</v>
       </c>
       <c r="O994" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="P994" s="1">
         <v>0</v>
@@ -59219,7 +59223,7 @@
         <v>4</v>
       </c>
       <c r="J995" s="63" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="K995" s="62">
         <v>6000</v>
@@ -59234,7 +59238,7 @@
         <v>3</v>
       </c>
       <c r="O995" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="P995" s="1">
         <v>0</v>
@@ -59275,7 +59279,7 @@
         <v>4</v>
       </c>
       <c r="J996" s="63" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="K996" s="62">
         <v>6000</v>
@@ -59290,7 +59294,7 @@
         <v>3</v>
       </c>
       <c r="O996" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="P996" s="1">
         <v>0</v>
@@ -59331,7 +59335,7 @@
         <v>5</v>
       </c>
       <c r="J997" s="63" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="K997" s="62">
         <v>6000</v>
@@ -59346,7 +59350,7 @@
         <v>3</v>
       </c>
       <c r="O997" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="P997" s="1">
         <v>0</v>
@@ -59387,7 +59391,7 @@
         <v>5</v>
       </c>
       <c r="J998" s="63" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="K998" s="62">
         <v>6000</v>
@@ -59402,7 +59406,7 @@
         <v>3</v>
       </c>
       <c r="O998" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="P998" s="1">
         <v>0</v>
@@ -59443,7 +59447,7 @@
         <v>5</v>
       </c>
       <c r="J999" s="63" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="K999" s="62">
         <v>6000</v>
@@ -59458,7 +59462,7 @@
         <v>3</v>
       </c>
       <c r="O999" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="P999" s="1">
         <v>0</v>
@@ -59499,7 +59503,7 @@
         <v>5</v>
       </c>
       <c r="J1000" s="63" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="K1000" s="62">
         <v>6000</v>
@@ -59514,7 +59518,7 @@
         <v>3</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="P1000" s="1">
         <v>0</v>
@@ -59555,7 +59559,7 @@
         <v>5</v>
       </c>
       <c r="J1001" s="63" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K1001" s="62">
         <v>6000</v>
@@ -59570,7 +59574,7 @@
         <v>3</v>
       </c>
       <c r="O1001" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="P1001" s="1">
         <v>0</v>
@@ -59611,7 +59615,7 @@
         <v>5</v>
       </c>
       <c r="J1002" s="63" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K1002" s="62">
         <v>6000</v>
@@ -59626,7 +59630,7 @@
         <v>3</v>
       </c>
       <c r="O1002" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="P1002" s="1">
         <v>0</v>
@@ -59667,7 +59671,7 @@
         <v>5</v>
       </c>
       <c r="J1003" s="63" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="K1003" s="62">
         <v>6000</v>
@@ -59682,7 +59686,7 @@
         <v>3</v>
       </c>
       <c r="O1003" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="P1003" s="1">
         <v>0</v>
@@ -59723,7 +59727,7 @@
         <v>5</v>
       </c>
       <c r="J1004" s="63" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K1004" s="62">
         <v>6000</v>
@@ -59738,7 +59742,7 @@
         <v>3</v>
       </c>
       <c r="O1004" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="P1004" s="1">
         <v>0</v>
@@ -59779,7 +59783,7 @@
         <v>5</v>
       </c>
       <c r="J1005" s="63" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K1005" s="62">
         <v>6000</v>
@@ -59794,7 +59798,7 @@
         <v>3</v>
       </c>
       <c r="O1005" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="P1005" s="1">
         <v>0</v>
@@ -59835,7 +59839,7 @@
         <v>5</v>
       </c>
       <c r="J1006" s="63" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="K1006" s="62">
         <v>6000</v>
@@ -59850,7 +59854,7 @@
         <v>3</v>
       </c>
       <c r="O1006" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="P1006" s="1">
         <v>0</v>
@@ -59891,7 +59895,7 @@
         <v>5</v>
       </c>
       <c r="J1007" s="63" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K1007" s="62">
         <v>6000</v>
@@ -59906,7 +59910,7 @@
         <v>3</v>
       </c>
       <c r="O1007" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="P1007" s="1">
         <v>0</v>
@@ -59947,7 +59951,7 @@
         <v>5</v>
       </c>
       <c r="J1008" s="63" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K1008" s="62">
         <v>6000</v>
@@ -59962,7 +59966,7 @@
         <v>3</v>
       </c>
       <c r="O1008" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="P1008" s="1">
         <v>0</v>
@@ -60003,7 +60007,7 @@
         <v>5</v>
       </c>
       <c r="J1009" s="63" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="K1009" s="62">
         <v>6000</v>
@@ -60018,7 +60022,7 @@
         <v>3</v>
       </c>
       <c r="O1009" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="P1009" s="1">
         <v>0</v>
@@ -60059,7 +60063,7 @@
         <v>5</v>
       </c>
       <c r="J1010" s="63" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="K1010" s="62">
         <v>6000</v>
@@ -60074,7 +60078,7 @@
         <v>3</v>
       </c>
       <c r="O1010" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="P1010" s="1">
         <v>0</v>
@@ -60115,7 +60119,7 @@
         <v>5</v>
       </c>
       <c r="J1011" s="63" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="K1011" s="62">
         <v>6000</v>
@@ -60130,7 +60134,7 @@
         <v>3</v>
       </c>
       <c r="O1011" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="P1011" s="1">
         <v>0</v>
@@ -60171,7 +60175,7 @@
         <v>5</v>
       </c>
       <c r="J1012" s="63" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="K1012" s="62">
         <v>6000</v>
@@ -60186,7 +60190,7 @@
         <v>3</v>
       </c>
       <c r="O1012" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="P1012" s="1">
         <v>0</v>
@@ -60227,7 +60231,7 @@
         <v>1</v>
       </c>
       <c r="J1013" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K1013" s="1">
         <v>120</v>
@@ -60242,7 +60246,7 @@
         <v>0</v>
       </c>
       <c r="O1013" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="P1013" s="1">
         <v>0</v>
@@ -60283,7 +60287,7 @@
         <v>1</v>
       </c>
       <c r="J1014" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K1014" s="1">
         <v>120</v>
@@ -60298,7 +60302,7 @@
         <v>0</v>
       </c>
       <c r="O1014" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="P1014" s="1">
         <v>0</v>
@@ -60339,7 +60343,7 @@
         <v>1</v>
       </c>
       <c r="J1015" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K1015" s="1">
         <v>120</v>
@@ -60354,7 +60358,7 @@
         <v>0</v>
       </c>
       <c r="O1015" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="P1015" s="1">
         <v>0</v>
@@ -60395,7 +60399,7 @@
         <v>2</v>
       </c>
       <c r="J1016" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K1016" s="1">
         <v>120</v>
@@ -60410,7 +60414,7 @@
         <v>0</v>
       </c>
       <c r="O1016" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="P1016" s="1">
         <v>0</v>
@@ -60451,7 +60455,7 @@
         <v>2</v>
       </c>
       <c r="J1017" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K1017" s="1">
         <v>120</v>
@@ -60466,7 +60470,7 @@
         <v>0</v>
       </c>
       <c r="O1017" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="P1017" s="1">
         <v>0</v>
@@ -60507,7 +60511,7 @@
         <v>2</v>
       </c>
       <c r="J1018" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K1018" s="1">
         <v>120</v>
@@ -60522,7 +60526,7 @@
         <v>0</v>
       </c>
       <c r="O1018" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="P1018" s="1">
         <v>0</v>
@@ -60563,7 +60567,7 @@
         <v>3</v>
       </c>
       <c r="J1019" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K1019" s="1">
         <v>120</v>
@@ -60578,7 +60582,7 @@
         <v>0</v>
       </c>
       <c r="O1019" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="P1019" s="1">
         <v>0</v>
@@ -60619,7 +60623,7 @@
         <v>3</v>
       </c>
       <c r="J1020" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K1020" s="1">
         <v>120</v>
@@ -60634,7 +60638,7 @@
         <v>0</v>
       </c>
       <c r="O1020" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="P1020" s="1">
         <v>0</v>
@@ -60675,7 +60679,7 @@
         <v>3</v>
       </c>
       <c r="J1021" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K1021" s="1">
         <v>120</v>
@@ -60690,7 +60694,7 @@
         <v>0</v>
       </c>
       <c r="O1021" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="P1021" s="1">
         <v>0</v>
@@ -60731,7 +60735,7 @@
         <v>3</v>
       </c>
       <c r="J1022" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="K1022" s="1">
         <v>120</v>
@@ -60746,7 +60750,7 @@
         <v>0</v>
       </c>
       <c r="O1022" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="P1022" s="1">
         <v>0</v>
@@ -60787,7 +60791,7 @@
         <v>4</v>
       </c>
       <c r="J1023" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K1023" s="1">
         <v>120</v>
@@ -60802,7 +60806,7 @@
         <v>0</v>
       </c>
       <c r="O1023" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="P1023" s="1">
         <v>0</v>
@@ -60843,7 +60847,7 @@
         <v>4</v>
       </c>
       <c r="J1024" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K1024" s="1">
         <v>120</v>
@@ -60858,7 +60862,7 @@
         <v>0</v>
       </c>
       <c r="O1024" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="P1024" s="1">
         <v>0</v>
@@ -60899,7 +60903,7 @@
         <v>4</v>
       </c>
       <c r="J1025" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K1025" s="1">
         <v>120</v>
@@ -60914,7 +60918,7 @@
         <v>0</v>
       </c>
       <c r="O1025" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="P1025" s="1">
         <v>0</v>
@@ -60955,7 +60959,7 @@
         <v>4</v>
       </c>
       <c r="J1026" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K1026" s="1">
         <v>120</v>
@@ -60970,7 +60974,7 @@
         <v>0</v>
       </c>
       <c r="O1026" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="P1026" s="1">
         <v>0</v>
@@ -61011,7 +61015,7 @@
         <v>5</v>
       </c>
       <c r="J1027" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="K1027" s="1">
         <v>120</v>
@@ -61026,7 +61030,7 @@
         <v>0</v>
       </c>
       <c r="O1027" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="P1027" s="1">
         <v>0</v>
@@ -61067,7 +61071,7 @@
         <v>5</v>
       </c>
       <c r="J1028" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="K1028" s="1">
         <v>120</v>
@@ -61082,7 +61086,7 @@
         <v>0</v>
       </c>
       <c r="O1028" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="P1028" s="1">
         <v>0</v>
@@ -61123,7 +61127,7 @@
         <v>5</v>
       </c>
       <c r="J1029" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K1029" s="1">
         <v>120</v>
@@ -61138,7 +61142,7 @@
         <v>0</v>
       </c>
       <c r="O1029" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="P1029" s="1">
         <v>0</v>
@@ -61179,7 +61183,7 @@
         <v>5</v>
       </c>
       <c r="J1030" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K1030" s="1">
         <v>120</v>
@@ -61194,7 +61198,7 @@
         <v>0</v>
       </c>
       <c r="O1030" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="P1030" s="1">
         <v>0</v>
@@ -61235,7 +61239,7 @@
         <v>6</v>
       </c>
       <c r="J1031" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K1031" s="1">
         <v>120</v>
@@ -61250,7 +61254,7 @@
         <v>0</v>
       </c>
       <c r="O1031" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="P1031" s="1">
         <v>0</v>
@@ -61291,7 +61295,7 @@
         <v>6</v>
       </c>
       <c r="J1032" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K1032" s="1">
         <v>120</v>
@@ -61306,7 +61310,7 @@
         <v>0</v>
       </c>
       <c r="O1032" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="P1032" s="1">
         <v>0</v>
@@ -61347,7 +61351,7 @@
         <v>6</v>
       </c>
       <c r="J1033" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K1033" s="1">
         <v>120</v>
@@ -61362,7 +61366,7 @@
         <v>0</v>
       </c>
       <c r="O1033" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="P1033" s="1">
         <v>0</v>
@@ -61403,7 +61407,7 @@
         <v>6</v>
       </c>
       <c r="J1034" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="K1034" s="1">
         <v>120</v>
@@ -61418,7 +61422,7 @@
         <v>0</v>
       </c>
       <c r="O1034" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="P1034" s="1">
         <v>0</v>
@@ -61459,7 +61463,7 @@
         <v>6</v>
       </c>
       <c r="J1035" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="K1035" s="1">
         <v>120</v>
@@ -61474,7 +61478,7 @@
         <v>0</v>
       </c>
       <c r="O1035" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="P1035" s="1">
         <v>0</v>
@@ -61515,7 +61519,7 @@
         <v>7</v>
       </c>
       <c r="J1036" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K1036" s="1">
         <v>120</v>
@@ -61530,7 +61534,7 @@
         <v>0</v>
       </c>
       <c r="O1036" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="P1036" s="1">
         <v>0</v>
@@ -61571,7 +61575,7 @@
         <v>7</v>
       </c>
       <c r="J1037" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K1037" s="1">
         <v>120</v>
@@ -61586,7 +61590,7 @@
         <v>0</v>
       </c>
       <c r="O1037" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="P1037" s="1">
         <v>0</v>
@@ -61627,7 +61631,7 @@
         <v>7</v>
       </c>
       <c r="J1038" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="K1038" s="1">
         <v>120</v>
@@ -61642,7 +61646,7 @@
         <v>0</v>
       </c>
       <c r="O1038" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="P1038" s="1">
         <v>0</v>
@@ -61683,7 +61687,7 @@
         <v>7</v>
       </c>
       <c r="J1039" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="K1039" s="1">
         <v>120</v>
@@ -61698,7 +61702,7 @@
         <v>0</v>
       </c>
       <c r="O1039" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="P1039" s="1">
         <v>0</v>
@@ -61739,7 +61743,7 @@
         <v>7</v>
       </c>
       <c r="J1040" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="K1040" s="1">
         <v>120</v>
@@ -61754,7 +61758,7 @@
         <v>0</v>
       </c>
       <c r="O1040" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="P1040" s="1">
         <v>0</v>
@@ -61795,7 +61799,7 @@
         <v>8</v>
       </c>
       <c r="J1041" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="K1041" s="1">
         <v>120</v>
@@ -61810,7 +61814,7 @@
         <v>0</v>
       </c>
       <c r="O1041" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="P1041" s="1">
         <v>0</v>
@@ -61851,7 +61855,7 @@
         <v>8</v>
       </c>
       <c r="J1042" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K1042" s="1">
         <v>120</v>
@@ -61866,7 +61870,7 @@
         <v>0</v>
       </c>
       <c r="O1042" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="P1042" s="1">
         <v>0</v>
@@ -61907,7 +61911,7 @@
         <v>8</v>
       </c>
       <c r="J1043" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="K1043" s="1">
         <v>120</v>
@@ -61922,7 +61926,7 @@
         <v>0</v>
       </c>
       <c r="O1043" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="P1043" s="1">
         <v>0</v>
@@ -61963,7 +61967,7 @@
         <v>8</v>
       </c>
       <c r="J1044" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="K1044" s="1">
         <v>120</v>
@@ -61978,7 +61982,7 @@
         <v>0</v>
       </c>
       <c r="O1044" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="P1044" s="1">
         <v>0</v>
@@ -62019,7 +62023,7 @@
         <v>8</v>
       </c>
       <c r="J1045" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="K1045" s="1">
         <v>120</v>
@@ -62034,7 +62038,7 @@
         <v>0</v>
       </c>
       <c r="O1045" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="P1045" s="1">
         <v>0</v>
@@ -62075,7 +62079,7 @@
         <v>8</v>
       </c>
       <c r="J1046" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K1046" s="1">
         <v>120</v>
@@ -62090,7 +62094,7 @@
         <v>0</v>
       </c>
       <c r="O1046" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="P1046" s="1">
         <v>0</v>
@@ -62131,7 +62135,7 @@
         <v>8</v>
       </c>
       <c r="J1047" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="K1047" s="1">
         <v>120</v>
@@ -62146,7 +62150,7 @@
         <v>0</v>
       </c>
       <c r="O1047" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="P1047" s="1">
         <v>0</v>
@@ -62187,7 +62191,7 @@
         <v>9</v>
       </c>
       <c r="J1048" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="K1048" s="1">
         <v>120</v>
@@ -62202,7 +62206,7 @@
         <v>0</v>
       </c>
       <c r="O1048" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="P1048" s="1">
         <v>0</v>
@@ -62243,7 +62247,7 @@
         <v>9</v>
       </c>
       <c r="J1049" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="K1049" s="1">
         <v>120</v>
@@ -62258,7 +62262,7 @@
         <v>0</v>
       </c>
       <c r="O1049" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="P1049" s="1">
         <v>0</v>
@@ -62299,7 +62303,7 @@
         <v>9</v>
       </c>
       <c r="J1050" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K1050" s="1">
         <v>120</v>
@@ -62314,7 +62318,7 @@
         <v>0</v>
       </c>
       <c r="O1050" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="P1050" s="1">
         <v>0</v>
@@ -62355,7 +62359,7 @@
         <v>9</v>
       </c>
       <c r="J1051" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="K1051" s="1">
         <v>120</v>
@@ -62370,7 +62374,7 @@
         <v>0</v>
       </c>
       <c r="O1051" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="P1051" s="1">
         <v>0</v>
@@ -62411,7 +62415,7 @@
         <v>9</v>
       </c>
       <c r="J1052" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="K1052" s="1">
         <v>120</v>
@@ -62426,7 +62430,7 @@
         <v>0</v>
       </c>
       <c r="O1052" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="P1052" s="1">
         <v>0</v>
@@ -62467,7 +62471,7 @@
         <v>9</v>
       </c>
       <c r="J1053" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="K1053" s="1">
         <v>120</v>
@@ -62482,7 +62486,7 @@
         <v>0</v>
       </c>
       <c r="O1053" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="P1053" s="1">
         <v>0</v>
@@ -62523,7 +62527,7 @@
         <v>9</v>
       </c>
       <c r="J1054" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="K1054" s="1">
         <v>120</v>
@@ -62538,7 +62542,7 @@
         <v>0</v>
       </c>
       <c r="O1054" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="P1054" s="1">
         <v>0</v>
@@ -62579,7 +62583,7 @@
         <v>9</v>
       </c>
       <c r="J1055" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="K1055" s="1">
         <v>120</v>
@@ -62594,7 +62598,7 @@
         <v>0</v>
       </c>
       <c r="O1055" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="P1055" s="1">
         <v>0</v>
@@ -62635,7 +62639,7 @@
         <v>9</v>
       </c>
       <c r="J1056" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="K1056" s="1">
         <v>120</v>
@@ -62650,7 +62654,7 @@
         <v>0</v>
       </c>
       <c r="O1056" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="P1056" s="1">
         <v>0</v>
@@ -62691,7 +62695,7 @@
         <v>10</v>
       </c>
       <c r="J1057" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="K1057" s="1">
         <v>120</v>
@@ -62706,7 +62710,7 @@
         <v>0</v>
       </c>
       <c r="O1057" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="P1057" s="1">
         <v>0</v>
@@ -62747,7 +62751,7 @@
         <v>10</v>
       </c>
       <c r="J1058" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="K1058" s="1">
         <v>120</v>
@@ -62762,7 +62766,7 @@
         <v>0</v>
       </c>
       <c r="O1058" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="P1058" s="1">
         <v>0</v>
@@ -62803,7 +62807,7 @@
         <v>10</v>
       </c>
       <c r="J1059" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="K1059" s="1">
         <v>120</v>
@@ -62818,7 +62822,7 @@
         <v>0</v>
       </c>
       <c r="O1059" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="P1059" s="1">
         <v>0</v>
@@ -62859,7 +62863,7 @@
         <v>10</v>
       </c>
       <c r="J1060" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="K1060" s="1">
         <v>120</v>
@@ -62874,7 +62878,7 @@
         <v>0</v>
       </c>
       <c r="O1060" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="P1060" s="1">
         <v>0</v>
@@ -62915,7 +62919,7 @@
         <v>10</v>
       </c>
       <c r="J1061" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="K1061" s="1">
         <v>120</v>
@@ -62930,7 +62934,7 @@
         <v>0</v>
       </c>
       <c r="O1061" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="P1061" s="1">
         <v>0</v>
@@ -62971,7 +62975,7 @@
         <v>10</v>
       </c>
       <c r="J1062" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="K1062" s="1">
         <v>120</v>
@@ -62986,7 +62990,7 @@
         <v>0</v>
       </c>
       <c r="O1062" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="P1062" s="1">
         <v>0</v>
@@ -63027,7 +63031,7 @@
         <v>10</v>
       </c>
       <c r="J1063" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="K1063" s="1">
         <v>120</v>
@@ -63042,7 +63046,7 @@
         <v>0</v>
       </c>
       <c r="O1063" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="P1063" s="1">
         <v>0</v>
@@ -63083,7 +63087,7 @@
         <v>10</v>
       </c>
       <c r="J1064" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="K1064" s="1">
         <v>120</v>
@@ -63098,7 +63102,7 @@
         <v>0</v>
       </c>
       <c r="O1064" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="P1064" s="1">
         <v>0</v>
@@ -63139,7 +63143,7 @@
         <v>10</v>
       </c>
       <c r="J1065" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="K1065" s="1">
         <v>120</v>
@@ -63154,7 +63158,7 @@
         <v>0</v>
       </c>
       <c r="O1065" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="P1065" s="1">
         <v>0</v>
@@ -63195,7 +63199,7 @@
         <v>10</v>
       </c>
       <c r="J1066" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K1066" s="1">
         <v>120</v>
@@ -63210,7 +63214,7 @@
         <v>0</v>
       </c>
       <c r="O1066" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="P1066" s="1">
         <v>0</v>
@@ -63251,7 +63255,7 @@
         <v>10</v>
       </c>
       <c r="J1067" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="K1067" s="1">
         <v>120</v>
@@ -63266,7 +63270,7 @@
         <v>0</v>
       </c>
       <c r="O1067" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="P1067" s="1">
         <v>0</v>
@@ -63301,7 +63305,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -63316,7 +63320,7 @@
         <v>0</v>
       </c>
       <c r="O1068" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="P1068" s="1">
         <v>0</v>
@@ -63351,7 +63355,7 @@
         <v>1</v>
       </c>
       <c r="J1069" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="K1069" s="1">
         <v>100</v>
@@ -63366,7 +63370,7 @@
         <v>0</v>
       </c>
       <c r="O1069" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="P1069" s="1">
         <v>0</v>
@@ -63401,7 +63405,7 @@
         <v>1</v>
       </c>
       <c r="J1070" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="K1070" s="1">
         <v>100</v>
@@ -63416,7 +63420,7 @@
         <v>0</v>
       </c>
       <c r="O1070" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="P1070" s="1">
         <v>0</v>
@@ -63451,7 +63455,7 @@
         <v>2</v>
       </c>
       <c r="J1071" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="K1071" s="1">
         <v>100</v>
@@ -63466,7 +63470,7 @@
         <v>0</v>
       </c>
       <c r="O1071" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="P1071" s="1">
         <v>0</v>
@@ -63501,7 +63505,7 @@
         <v>2</v>
       </c>
       <c r="J1072" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="K1072" s="1">
         <v>100</v>
@@ -63516,7 +63520,7 @@
         <v>0</v>
       </c>
       <c r="O1072" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="P1072" s="1">
         <v>0</v>
@@ -63551,7 +63555,7 @@
         <v>2</v>
       </c>
       <c r="J1073" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="K1073" s="1">
         <v>100</v>
@@ -63566,7 +63570,7 @@
         <v>0</v>
       </c>
       <c r="O1073" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="P1073" s="1">
         <v>0</v>
@@ -63601,7 +63605,7 @@
         <v>3</v>
       </c>
       <c r="J1074" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="K1074" s="1">
         <v>100</v>
@@ -63616,7 +63620,7 @@
         <v>1</v>
       </c>
       <c r="O1074" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="P1074" s="1">
         <v>0</v>
@@ -63651,7 +63655,7 @@
         <v>3</v>
       </c>
       <c r="J1075" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="K1075" s="1">
         <v>100</v>
@@ -63666,7 +63670,7 @@
         <v>1</v>
       </c>
       <c r="O1075" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="P1075" s="1">
         <v>0</v>
@@ -63701,7 +63705,7 @@
         <v>3</v>
       </c>
       <c r="J1076" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="K1076" s="1">
         <v>100</v>
@@ -63716,7 +63720,7 @@
         <v>1</v>
       </c>
       <c r="O1076" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="P1076" s="1">
         <v>0</v>
@@ -63751,7 +63755,7 @@
         <v>3</v>
       </c>
       <c r="J1077" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="K1077" s="1">
         <v>100</v>
@@ -63766,7 +63770,7 @@
         <v>1</v>
       </c>
       <c r="O1077" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="P1077" s="1">
         <v>0</v>
@@ -63801,7 +63805,7 @@
         <v>4</v>
       </c>
       <c r="J1078" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="K1078" s="1">
         <v>100</v>
@@ -63816,7 +63820,7 @@
         <v>1</v>
       </c>
       <c r="O1078" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="P1078" s="1">
         <v>0</v>
@@ -63851,7 +63855,7 @@
         <v>4</v>
       </c>
       <c r="J1079" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="K1079" s="1">
         <v>100</v>
@@ -63866,7 +63870,7 @@
         <v>1</v>
       </c>
       <c r="O1079" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="P1079" s="1">
         <v>0</v>
@@ -63901,7 +63905,7 @@
         <v>4</v>
       </c>
       <c r="J1080" s="2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="K1080" s="1">
         <v>100</v>
@@ -63916,7 +63920,7 @@
         <v>1</v>
       </c>
       <c r="O1080" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="P1080" s="1">
         <v>0</v>
@@ -63951,7 +63955,7 @@
         <v>4</v>
       </c>
       <c r="J1081" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="K1081" s="1">
         <v>100</v>
@@ -63966,7 +63970,7 @@
         <v>1</v>
       </c>
       <c r="O1081" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="P1081" s="1">
         <v>0</v>
@@ -64004,7 +64008,7 @@
         <v>1</v>
       </c>
       <c r="J1082" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="K1082" s="1">
         <v>40</v>
@@ -64019,7 +64023,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -64057,7 +64061,7 @@
         <v>1</v>
       </c>
       <c r="J1083" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="K1083" s="1">
         <v>40</v>
@@ -64072,7 +64076,7 @@
         <v>0</v>
       </c>
       <c r="O1083" s="1" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="P1083" s="1">
         <v>0</v>
@@ -64110,7 +64114,7 @@
         <v>1</v>
       </c>
       <c r="J1084" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="K1084" s="1">
         <v>40</v>
@@ -64125,7 +64129,7 @@
         <v>0</v>
       </c>
       <c r="O1084" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="P1084" s="1">
         <v>0</v>
@@ -64163,7 +64167,7 @@
         <v>2</v>
       </c>
       <c r="J1085" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="K1085" s="1">
         <v>40</v>
@@ -64178,7 +64182,7 @@
         <v>0</v>
       </c>
       <c r="O1085" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="P1085" s="1">
         <v>0</v>
@@ -64216,7 +64220,7 @@
         <v>2</v>
       </c>
       <c r="J1086" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="K1086" s="1">
         <v>40</v>
@@ -64231,7 +64235,7 @@
         <v>0</v>
       </c>
       <c r="O1086" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="P1086" s="1">
         <v>0</v>
@@ -64269,7 +64273,7 @@
         <v>2</v>
       </c>
       <c r="J1087" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="K1087" s="1">
         <v>40</v>
@@ -64284,7 +64288,7 @@
         <v>0</v>
       </c>
       <c r="O1087" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="P1087" s="1">
         <v>0</v>
@@ -64322,7 +64326,7 @@
         <v>3</v>
       </c>
       <c r="J1088" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="K1088" s="1">
         <v>40</v>
@@ -64337,7 +64341,7 @@
         <v>0</v>
       </c>
       <c r="O1088" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="P1088" s="1">
         <v>0</v>
@@ -64375,7 +64379,7 @@
         <v>3</v>
       </c>
       <c r="J1089" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="K1089" s="1">
         <v>40</v>
@@ -64390,7 +64394,7 @@
         <v>0</v>
       </c>
       <c r="O1089" s="1" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="P1089" s="1">
         <v>0</v>
@@ -64428,7 +64432,7 @@
         <v>3</v>
       </c>
       <c r="J1090" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="K1090" s="1">
         <v>40</v>
@@ -64443,7 +64447,7 @@
         <v>0</v>
       </c>
       <c r="O1090" s="1" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="P1090" s="1">
         <v>0</v>
@@ -64481,7 +64485,7 @@
         <v>3</v>
       </c>
       <c r="J1091" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="K1091" s="1">
         <v>40</v>
@@ -64496,7 +64500,7 @@
         <v>0</v>
       </c>
       <c r="O1091" s="1" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="P1091" s="1">
         <v>0</v>
@@ -64534,7 +64538,7 @@
         <v>4</v>
       </c>
       <c r="J1092" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="K1092" s="1">
         <v>40</v>
@@ -64549,7 +64553,7 @@
         <v>0</v>
       </c>
       <c r="O1092" s="1" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="P1092" s="1">
         <v>0</v>
@@ -64587,7 +64591,7 @@
         <v>4</v>
       </c>
       <c r="J1093" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="K1093" s="1">
         <v>40</v>
@@ -64602,7 +64606,7 @@
         <v>0</v>
       </c>
       <c r="O1093" s="1" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="P1093" s="1">
         <v>0</v>
@@ -64640,7 +64644,7 @@
         <v>4</v>
       </c>
       <c r="J1094" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="K1094" s="1">
         <v>40</v>
@@ -64655,7 +64659,7 @@
         <v>0</v>
       </c>
       <c r="O1094" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="P1094" s="1">
         <v>0</v>
@@ -64693,7 +64697,7 @@
         <v>4</v>
       </c>
       <c r="J1095" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="K1095" s="1">
         <v>40</v>
@@ -64708,7 +64712,7 @@
         <v>0</v>
       </c>
       <c r="O1095" s="1" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="P1095" s="1">
         <v>0</v>
@@ -64746,7 +64750,7 @@
         <v>4</v>
       </c>
       <c r="J1096" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="K1096" s="1">
         <v>40</v>
@@ -64761,7 +64765,7 @@
         <v>0</v>
       </c>
       <c r="O1096" s="1" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="P1096" s="1">
         <v>0</v>
@@ -64799,7 +64803,7 @@
         <v>5</v>
       </c>
       <c r="J1097" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="K1097" s="1">
         <v>40</v>
@@ -64814,7 +64818,7 @@
         <v>0</v>
       </c>
       <c r="O1097" s="1" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="P1097" s="1">
         <v>0</v>
@@ -64852,7 +64856,7 @@
         <v>5</v>
       </c>
       <c r="J1098" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="K1098" s="1">
         <v>40</v>
@@ -64867,7 +64871,7 @@
         <v>0</v>
       </c>
       <c r="O1098" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="P1098" s="1">
         <v>0</v>
@@ -64905,7 +64909,7 @@
         <v>5</v>
       </c>
       <c r="J1099" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="K1099" s="1">
         <v>40</v>
@@ -64920,7 +64924,7 @@
         <v>0</v>
       </c>
       <c r="O1099" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="P1099" s="1">
         <v>0</v>
@@ -64958,7 +64962,7 @@
         <v>5</v>
       </c>
       <c r="J1100" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="K1100" s="1">
         <v>40</v>
@@ -64973,7 +64977,7 @@
         <v>0</v>
       </c>
       <c r="O1100" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="P1100" s="1">
         <v>0</v>
@@ -65011,7 +65015,7 @@
         <v>5</v>
       </c>
       <c r="J1101" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="K1101" s="1">
         <v>40</v>
@@ -65026,7 +65030,7 @@
         <v>0</v>
       </c>
       <c r="O1101" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="P1101" s="1">
         <v>0</v>
@@ -65064,7 +65068,7 @@
         <v>5</v>
       </c>
       <c r="J1102" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="K1102" s="1">
         <v>40</v>
@@ -65079,7 +65083,7 @@
         <v>0</v>
       </c>
       <c r="O1102" s="1" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="P1102" s="1">
         <v>0</v>
@@ -65117,7 +65121,7 @@
         <v>6</v>
       </c>
       <c r="J1103" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K1103" s="1">
         <v>160</v>
@@ -65132,7 +65136,7 @@
         <v>0</v>
       </c>
       <c r="O1103" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="P1103" s="1">
         <v>0</v>
@@ -65170,7 +65174,7 @@
         <v>6</v>
       </c>
       <c r="J1104" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="K1104" s="1">
         <v>160</v>
@@ -65185,7 +65189,7 @@
         <v>0</v>
       </c>
       <c r="O1104" s="1" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="P1104" s="1">
         <v>0</v>
@@ -65223,7 +65227,7 @@
         <v>6</v>
       </c>
       <c r="J1105" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K1105" s="1">
         <v>160</v>
@@ -65238,7 +65242,7 @@
         <v>0</v>
       </c>
       <c r="O1105" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="P1105" s="1">
         <v>0</v>
@@ -65276,7 +65280,7 @@
         <v>6</v>
       </c>
       <c r="J1106" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="K1106" s="1">
         <v>160</v>
@@ -65291,7 +65295,7 @@
         <v>0</v>
       </c>
       <c r="O1106" s="1" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="P1106" s="1">
         <v>0</v>
@@ -65329,7 +65333,7 @@
         <v>7</v>
       </c>
       <c r="J1107" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="K1107" s="1">
         <v>160</v>
@@ -65344,7 +65348,7 @@
         <v>0</v>
       </c>
       <c r="O1107" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="P1107" s="1">
         <v>0</v>
@@ -65382,7 +65386,7 @@
         <v>7</v>
       </c>
       <c r="J1108" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="K1108" s="1">
         <v>160</v>
@@ -65397,7 +65401,7 @@
         <v>0</v>
       </c>
       <c r="O1108" s="1" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="P1108" s="1">
         <v>0</v>
@@ -65435,7 +65439,7 @@
         <v>7</v>
       </c>
       <c r="J1109" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="K1109" s="1">
         <v>160</v>
@@ -65450,7 +65454,7 @@
         <v>0</v>
       </c>
       <c r="O1109" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="P1109" s="1">
         <v>0</v>
@@ -65488,7 +65492,7 @@
         <v>7</v>
       </c>
       <c r="J1110" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="K1110" s="1">
         <v>160</v>
@@ -65503,7 +65507,7 @@
         <v>0</v>
       </c>
       <c r="O1110" s="1" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="P1110" s="1">
         <v>0</v>
@@ -65541,7 +65545,7 @@
         <v>8</v>
       </c>
       <c r="J1111" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="K1111" s="1">
         <v>160</v>
@@ -65556,7 +65560,7 @@
         <v>0</v>
       </c>
       <c r="O1111" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="P1111" s="1">
         <v>0</v>
@@ -65594,7 +65598,7 @@
         <v>8</v>
       </c>
       <c r="J1112" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="K1112" s="1">
         <v>160</v>
@@ -65609,7 +65613,7 @@
         <v>0</v>
       </c>
       <c r="O1112" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="P1112" s="1">
         <v>0</v>
@@ -65647,7 +65651,7 @@
         <v>8</v>
       </c>
       <c r="J1113" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="K1113" s="1">
         <v>160</v>
@@ -65662,7 +65666,7 @@
         <v>0</v>
       </c>
       <c r="O1113" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="P1113" s="1">
         <v>0</v>
@@ -65700,7 +65704,7 @@
         <v>8</v>
       </c>
       <c r="J1114" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="K1114" s="1">
         <v>160</v>
@@ -65715,7 +65719,7 @@
         <v>0</v>
       </c>
       <c r="O1114" s="1" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="P1114" s="1">
         <v>0</v>
@@ -65753,7 +65757,7 @@
         <v>8</v>
       </c>
       <c r="J1115" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="K1115" s="1">
         <v>160</v>
@@ -65768,7 +65772,7 @@
         <v>0</v>
       </c>
       <c r="O1115" s="1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="P1115" s="1">
         <v>0</v>
@@ -65806,7 +65810,7 @@
         <v>9</v>
       </c>
       <c r="J1116" s="2" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="K1116" s="1">
         <v>160</v>
@@ -65821,7 +65825,7 @@
         <v>0</v>
       </c>
       <c r="O1116" s="1" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="P1116" s="1">
         <v>0</v>
@@ -65859,7 +65863,7 @@
         <v>9</v>
       </c>
       <c r="J1117" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="K1117" s="1">
         <v>160</v>
@@ -65874,7 +65878,7 @@
         <v>0</v>
       </c>
       <c r="O1117" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="P1117" s="1">
         <v>0</v>
@@ -65912,7 +65916,7 @@
         <v>9</v>
       </c>
       <c r="J1118" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="K1118" s="1">
         <v>160</v>
@@ -65927,7 +65931,7 @@
         <v>0</v>
       </c>
       <c r="O1118" s="1" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="P1118" s="1">
         <v>0</v>
@@ -65965,7 +65969,7 @@
         <v>9</v>
       </c>
       <c r="J1119" s="2" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="K1119" s="1">
         <v>160</v>
@@ -65980,7 +65984,7 @@
         <v>0</v>
       </c>
       <c r="O1119" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="P1119" s="1">
         <v>0</v>
@@ -66018,7 +66022,7 @@
         <v>9</v>
       </c>
       <c r="J1120" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="K1120" s="1">
         <v>160</v>
@@ -66033,7 +66037,7 @@
         <v>0</v>
       </c>
       <c r="O1120" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="P1120" s="1">
         <v>0</v>
@@ -66071,7 +66075,7 @@
         <v>10</v>
       </c>
       <c r="J1121" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="K1121" s="1">
         <v>160</v>
@@ -66124,7 +66128,7 @@
         <v>10</v>
       </c>
       <c r="J1122" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="K1122" s="1">
         <v>160</v>
@@ -66139,7 +66143,7 @@
         <v>0</v>
       </c>
       <c r="O1122" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="P1122" s="1">
         <v>0</v>
@@ -66177,7 +66181,7 @@
         <v>10</v>
       </c>
       <c r="J1123" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="K1123" s="1">
         <v>160</v>
@@ -66192,7 +66196,7 @@
         <v>0</v>
       </c>
       <c r="O1123" s="1" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="P1123" s="1">
         <v>0</v>
@@ -66230,7 +66234,7 @@
         <v>10</v>
       </c>
       <c r="J1124" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K1124" s="1">
         <v>160</v>
@@ -66245,7 +66249,7 @@
         <v>0</v>
       </c>
       <c r="O1124" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="P1124" s="1">
         <v>0</v>
@@ -66283,7 +66287,7 @@
         <v>10</v>
       </c>
       <c r="J1125" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="K1125" s="1">
         <v>160</v>
@@ -66298,7 +66302,7 @@
         <v>0</v>
       </c>
       <c r="O1125" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="P1125" s="1">
         <v>0</v>
@@ -66336,7 +66340,7 @@
         <v>10</v>
       </c>
       <c r="J1126" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K1126" s="1">
         <v>160</v>
@@ -66351,7 +66355,7 @@
         <v>0</v>
       </c>
       <c r="O1126" s="1" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="P1126" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A817644-9283-42EE-B8D5-9B965B32E6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F751F30D-7272-4F78-9CAB-631AB4AEB463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64011,7 +64011,7 @@
         <v>817</v>
       </c>
       <c r="K1082" s="1">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="L1082" s="1">
         <v>30000</v>
@@ -64040,13 +64040,13 @@
         <v>1110102</v>
       </c>
       <c r="B1083" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1083" s="1">
         <v>1</v>
       </c>
       <c r="E1083" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1083" s="1">
         <v>1</v>
@@ -64093,13 +64093,13 @@
         <v>1110103</v>
       </c>
       <c r="B1084" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1084" s="1">
         <v>1</v>
       </c>
       <c r="E1084" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1084" s="1">
         <v>1</v>
@@ -64146,13 +64146,13 @@
         <v>1110201</v>
       </c>
       <c r="B1085" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1085" s="1">
         <v>1</v>
       </c>
       <c r="E1085" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1085" s="1">
         <v>1</v>
@@ -64199,13 +64199,13 @@
         <v>1110202</v>
       </c>
       <c r="B1086" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1086" s="1">
         <v>1</v>
       </c>
       <c r="E1086" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1086" s="1">
         <v>1</v>
@@ -64252,13 +64252,13 @@
         <v>1110203</v>
       </c>
       <c r="B1087" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1087" s="1">
         <v>1</v>
       </c>
       <c r="E1087" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1087" s="1">
         <v>1</v>
@@ -64305,13 +64305,13 @@
         <v>1110301</v>
       </c>
       <c r="B1088" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1088" s="1">
         <v>1</v>
       </c>
       <c r="E1088" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1088" s="1">
         <v>1</v>
@@ -64358,13 +64358,13 @@
         <v>1110302</v>
       </c>
       <c r="B1089" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1089" s="1">
         <v>1</v>
       </c>
       <c r="E1089" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1089" s="1">
         <v>1</v>
@@ -64411,13 +64411,13 @@
         <v>1110303</v>
       </c>
       <c r="B1090" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1090" s="1">
         <v>1</v>
       </c>
       <c r="E1090" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1090" s="1">
         <v>1</v>
@@ -64464,13 +64464,13 @@
         <v>1110304</v>
       </c>
       <c r="B1091" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1091" s="1">
         <v>1</v>
       </c>
       <c r="E1091" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1091" s="1">
         <v>1</v>
@@ -64517,13 +64517,13 @@
         <v>1110401</v>
       </c>
       <c r="B1092" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1092" s="1">
         <v>1</v>
       </c>
       <c r="E1092" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1092" s="1">
         <v>1</v>
@@ -64570,13 +64570,13 @@
         <v>1110402</v>
       </c>
       <c r="B1093" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1093" s="1">
         <v>1</v>
       </c>
       <c r="E1093" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1093" s="1">
         <v>1</v>
@@ -64623,13 +64623,13 @@
         <v>1110403</v>
       </c>
       <c r="B1094" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1094" s="1">
         <v>1</v>
       </c>
       <c r="E1094" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1094" s="1">
         <v>1</v>
@@ -64676,13 +64676,13 @@
         <v>1110404</v>
       </c>
       <c r="B1095" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1095" s="1">
         <v>1</v>
       </c>
       <c r="E1095" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1095" s="1">
         <v>1</v>
@@ -64729,13 +64729,13 @@
         <v>1110405</v>
       </c>
       <c r="B1096" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1096" s="1">
         <v>1</v>
       </c>
       <c r="E1096" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1096" s="1">
         <v>1</v>
@@ -64782,13 +64782,13 @@
         <v>1110501</v>
       </c>
       <c r="B1097" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1097" s="1">
         <v>1</v>
       </c>
       <c r="E1097" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1097" s="1">
         <v>1</v>
@@ -64835,13 +64835,13 @@
         <v>1110502</v>
       </c>
       <c r="B1098" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1098" s="1">
         <v>1</v>
       </c>
       <c r="E1098" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1098" s="1">
         <v>1</v>
@@ -64888,13 +64888,13 @@
         <v>1110503</v>
       </c>
       <c r="B1099" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1099" s="1">
         <v>1</v>
       </c>
       <c r="E1099" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1099" s="1">
         <v>1</v>
@@ -64941,13 +64941,13 @@
         <v>1110504</v>
       </c>
       <c r="B1100" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1100" s="1">
         <v>1</v>
       </c>
       <c r="E1100" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1100" s="1">
         <v>1</v>
@@ -64994,13 +64994,13 @@
         <v>1110505</v>
       </c>
       <c r="B1101" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1101" s="1">
         <v>1</v>
       </c>
       <c r="E1101" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1101" s="1">
         <v>1</v>
@@ -65047,13 +65047,13 @@
         <v>1110506</v>
       </c>
       <c r="B1102" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1102" s="1">
         <v>1</v>
       </c>
       <c r="E1102" s="1">
-        <v>110001</v>
+        <v>120001</v>
       </c>
       <c r="F1102" s="1">
         <v>1</v>
@@ -65124,7 +65124,7 @@
         <v>822</v>
       </c>
       <c r="K1103" s="1">
-        <v>160</v>
+        <v>800</v>
       </c>
       <c r="L1103" s="1">
         <v>30000</v>
@@ -65153,13 +65153,13 @@
         <v>1120602</v>
       </c>
       <c r="B1104" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1104" s="1">
         <v>2</v>
       </c>
       <c r="E1104" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1104" s="1">
         <v>1</v>
@@ -65206,13 +65206,13 @@
         <v>1120603</v>
       </c>
       <c r="B1105" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1105" s="1">
         <v>2</v>
       </c>
       <c r="E1105" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1105" s="1">
         <v>1</v>
@@ -65259,13 +65259,13 @@
         <v>1120604</v>
       </c>
       <c r="B1106" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1106" s="1">
         <v>2</v>
       </c>
       <c r="E1106" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1106" s="1">
         <v>1</v>
@@ -65312,13 +65312,13 @@
         <v>1120701</v>
       </c>
       <c r="B1107" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1107" s="1">
         <v>2</v>
       </c>
       <c r="E1107" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1107" s="1">
         <v>1</v>
@@ -65365,13 +65365,13 @@
         <v>1120702</v>
       </c>
       <c r="B1108" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1108" s="1">
         <v>2</v>
       </c>
       <c r="E1108" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1108" s="1">
         <v>1</v>
@@ -65418,13 +65418,13 @@
         <v>1120703</v>
       </c>
       <c r="B1109" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1109" s="1">
         <v>2</v>
       </c>
       <c r="E1109" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1109" s="1">
         <v>1</v>
@@ -65471,13 +65471,13 @@
         <v>1120704</v>
       </c>
       <c r="B1110" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1110" s="1">
         <v>2</v>
       </c>
       <c r="E1110" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1110" s="1">
         <v>1</v>
@@ -65524,13 +65524,13 @@
         <v>1120801</v>
       </c>
       <c r="B1111" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1111" s="1">
         <v>2</v>
       </c>
       <c r="E1111" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1111" s="1">
         <v>1</v>
@@ -65577,13 +65577,13 @@
         <v>1120802</v>
       </c>
       <c r="B1112" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1112" s="1">
         <v>2</v>
       </c>
       <c r="E1112" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1112" s="1">
         <v>1</v>
@@ -65630,13 +65630,13 @@
         <v>1120803</v>
       </c>
       <c r="B1113" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1113" s="1">
         <v>2</v>
       </c>
       <c r="E1113" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1113" s="1">
         <v>1</v>
@@ -65683,13 +65683,13 @@
         <v>1120804</v>
       </c>
       <c r="B1114" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1114" s="1">
         <v>2</v>
       </c>
       <c r="E1114" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1114" s="1">
         <v>1</v>
@@ -65736,13 +65736,13 @@
         <v>1120805</v>
       </c>
       <c r="B1115" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1115" s="1">
         <v>2</v>
       </c>
       <c r="E1115" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1115" s="1">
         <v>1</v>
@@ -65789,13 +65789,13 @@
         <v>1120901</v>
       </c>
       <c r="B1116" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1116" s="1">
         <v>2</v>
       </c>
       <c r="E1116" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1116" s="1">
         <v>1</v>
@@ -65842,13 +65842,13 @@
         <v>1120902</v>
       </c>
       <c r="B1117" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1117" s="1">
         <v>2</v>
       </c>
       <c r="E1117" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1117" s="1">
         <v>1</v>
@@ -65895,13 +65895,13 @@
         <v>1120903</v>
       </c>
       <c r="B1118" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1118" s="1">
         <v>2</v>
       </c>
       <c r="E1118" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1118" s="1">
         <v>1</v>
@@ -65948,13 +65948,13 @@
         <v>1120904</v>
       </c>
       <c r="B1119" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1119" s="1">
         <v>2</v>
       </c>
       <c r="E1119" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1119" s="1">
         <v>1</v>
@@ -66001,13 +66001,13 @@
         <v>1120905</v>
       </c>
       <c r="B1120" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1120" s="1">
         <v>2</v>
       </c>
       <c r="E1120" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1120" s="1">
         <v>1</v>
@@ -66054,13 +66054,13 @@
         <v>1121001</v>
       </c>
       <c r="B1121" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1121" s="1">
         <v>2</v>
       </c>
       <c r="E1121" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1121" s="1">
         <v>1</v>
@@ -66107,13 +66107,13 @@
         <v>1121002</v>
       </c>
       <c r="B1122" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1122" s="1">
         <v>2</v>
       </c>
       <c r="E1122" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1122" s="1">
         <v>1</v>
@@ -66160,13 +66160,13 @@
         <v>1121003</v>
       </c>
       <c r="B1123" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1123" s="1">
         <v>2</v>
       </c>
       <c r="E1123" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1123" s="1">
         <v>1</v>
@@ -66213,13 +66213,13 @@
         <v>1121004</v>
       </c>
       <c r="B1124" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1124" s="1">
         <v>2</v>
       </c>
       <c r="E1124" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1124" s="1">
         <v>1</v>
@@ -66266,13 +66266,13 @@
         <v>1121005</v>
       </c>
       <c r="B1125" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1125" s="1">
         <v>2</v>
       </c>
       <c r="E1125" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1125" s="1">
         <v>1</v>
@@ -66319,13 +66319,13 @@
         <v>1121006</v>
       </c>
       <c r="B1126" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1126" s="1">
         <v>2</v>
       </c>
       <c r="E1126" s="1">
-        <v>110002</v>
+        <v>120002</v>
       </c>
       <c r="F1126" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6597D898-D696-4D14-BC5B-9E1743F83708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1EBB5A-AE81-442C-8772-8004CEF492E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1298,10 +1298,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>80,20,80,10,80,30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>30,80,10,80,20,80</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2703,6 +2699,10 @@
   </si>
   <si>
     <t>999001,999001,999001</t>
+  </si>
+  <si>
+    <t>10,90,10,95,10,85</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3656,13 +3656,13 @@
         <v>146</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="Q3" s="8" t="s">
         <v>156</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3712,13 +3712,13 @@
         <v>149</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="Q4" s="10" t="s">
         <v>157</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -3750,7 +3750,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="K5" s="12">
         <v>20</v>
@@ -3806,7 +3806,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K6" s="14">
         <v>20</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>387</v>
+        <v>852</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K7" s="14">
         <v>20</v>
@@ -3877,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -3918,7 +3918,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K8" s="12">
         <v>20</v>
@@ -3974,7 +3974,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K9" s="14">
         <v>20</v>
@@ -4030,7 +4030,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K10" s="14">
         <v>20</v>
@@ -4086,7 +4086,7 @@
         <v>3</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K11" s="12">
         <v>20</v>
@@ -4142,7 +4142,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K12" s="14">
         <v>20</v>
@@ -4198,7 +4198,7 @@
         <v>3</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K13" s="14">
         <v>20</v>
@@ -4254,7 +4254,7 @@
         <v>3</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K14" s="16">
         <v>20</v>
@@ -4310,7 +4310,7 @@
         <v>4</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K15" s="14">
         <v>20</v>
@@ -4366,7 +4366,7 @@
         <v>4</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K16" s="14">
         <v>20</v>
@@ -4422,7 +4422,7 @@
         <v>4</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K17" s="14">
         <v>20</v>
@@ -4478,7 +4478,7 @@
         <v>4</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K18" s="16">
         <v>20</v>
@@ -4534,7 +4534,7 @@
         <v>5</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K19" s="14">
         <v>20</v>
@@ -4590,7 +4590,7 @@
         <v>5</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K20" s="14">
         <v>20</v>
@@ -4646,7 +4646,7 @@
         <v>5</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="K21" s="14">
         <v>20</v>
@@ -4702,7 +4702,7 @@
         <v>5</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="K22" s="16">
         <v>20</v>
@@ -50006,7 +50006,7 @@
         <v>1</v>
       </c>
       <c r="J831" s="61" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K831" s="60">
         <v>16</v>
@@ -50021,7 +50021,7 @@
         <v>0</v>
       </c>
       <c r="O831" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P831" s="1">
         <v>0</v>
@@ -50062,7 +50062,7 @@
         <v>1</v>
       </c>
       <c r="J832" s="61" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K832" s="60">
         <v>16</v>
@@ -50077,7 +50077,7 @@
         <v>0</v>
       </c>
       <c r="O832" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="P832" s="1">
         <v>0</v>
@@ -50118,7 +50118,7 @@
         <v>1</v>
       </c>
       <c r="J833" s="61" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K833" s="60">
         <v>16</v>
@@ -50133,7 +50133,7 @@
         <v>0</v>
       </c>
       <c r="O833" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P833" s="1">
         <v>0</v>
@@ -50174,7 +50174,7 @@
         <v>2</v>
       </c>
       <c r="J834" s="61" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K834" s="60">
         <v>16</v>
@@ -50189,7 +50189,7 @@
         <v>0</v>
       </c>
       <c r="O834" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P834" s="1">
         <v>0</v>
@@ -50230,7 +50230,7 @@
         <v>2</v>
       </c>
       <c r="J835" s="61" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K835" s="60">
         <v>16</v>
@@ -50245,7 +50245,7 @@
         <v>0</v>
       </c>
       <c r="O835" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P835" s="1">
         <v>0</v>
@@ -50286,7 +50286,7 @@
         <v>2</v>
       </c>
       <c r="J836" s="61" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K836" s="60">
         <v>16</v>
@@ -50301,7 +50301,7 @@
         <v>0</v>
       </c>
       <c r="O836" s="1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="P836" s="1">
         <v>0</v>
@@ -50342,7 +50342,7 @@
         <v>2</v>
       </c>
       <c r="J837" s="61" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K837" s="60">
         <v>16</v>
@@ -50357,7 +50357,7 @@
         <v>0</v>
       </c>
       <c r="O837" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="P837" s="1">
         <v>0</v>
@@ -50398,7 +50398,7 @@
         <v>3</v>
       </c>
       <c r="J838" s="61" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K838" s="60">
         <v>16</v>
@@ -50413,7 +50413,7 @@
         <v>0</v>
       </c>
       <c r="O838" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P838" s="1">
         <v>0</v>
@@ -50454,7 +50454,7 @@
         <v>3</v>
       </c>
       <c r="J839" s="61" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K839" s="60">
         <v>16</v>
@@ -50469,7 +50469,7 @@
         <v>0</v>
       </c>
       <c r="O839" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P839" s="1">
         <v>0</v>
@@ -50510,7 +50510,7 @@
         <v>3</v>
       </c>
       <c r="J840" s="61" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K840" s="60">
         <v>16</v>
@@ -50525,7 +50525,7 @@
         <v>0</v>
       </c>
       <c r="O840" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="P840" s="1">
         <v>0</v>
@@ -50566,7 +50566,7 @@
         <v>3</v>
       </c>
       <c r="J841" s="61" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K841" s="60">
         <v>16</v>
@@ -50581,7 +50581,7 @@
         <v>0</v>
       </c>
       <c r="O841" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P841" s="1">
         <v>0</v>
@@ -50622,7 +50622,7 @@
         <v>3</v>
       </c>
       <c r="J842" s="61" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K842" s="60">
         <v>16</v>
@@ -50637,7 +50637,7 @@
         <v>0</v>
       </c>
       <c r="O842" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P842" s="1">
         <v>0</v>
@@ -50678,7 +50678,7 @@
         <v>3</v>
       </c>
       <c r="J843" s="61" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K843" s="60">
         <v>16</v>
@@ -50693,7 +50693,7 @@
         <v>0</v>
       </c>
       <c r="O843" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P843" s="1">
         <v>0</v>
@@ -50734,7 +50734,7 @@
         <v>4</v>
       </c>
       <c r="J844" s="61" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K844" s="60">
         <v>16</v>
@@ -50749,7 +50749,7 @@
         <v>0</v>
       </c>
       <c r="O844" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P844" s="1">
         <v>0</v>
@@ -50790,7 +50790,7 @@
         <v>4</v>
       </c>
       <c r="J845" s="61" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K845" s="60">
         <v>16</v>
@@ -50805,7 +50805,7 @@
         <v>0</v>
       </c>
       <c r="O845" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="P845" s="1">
         <v>0</v>
@@ -50846,7 +50846,7 @@
         <v>4</v>
       </c>
       <c r="J846" s="61" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K846" s="60">
         <v>16</v>
@@ -50861,7 +50861,7 @@
         <v>0</v>
       </c>
       <c r="O846" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P846" s="1">
         <v>0</v>
@@ -50902,7 +50902,7 @@
         <v>4</v>
       </c>
       <c r="J847" s="61" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K847" s="60">
         <v>16</v>
@@ -50917,7 +50917,7 @@
         <v>0</v>
       </c>
       <c r="O847" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="P847" s="1">
         <v>0</v>
@@ -50958,7 +50958,7 @@
         <v>4</v>
       </c>
       <c r="J848" s="61" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="K848" s="60">
         <v>16</v>
@@ -50973,7 +50973,7 @@
         <v>0</v>
       </c>
       <c r="O848" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P848" s="1">
         <v>0</v>
@@ -51014,7 +51014,7 @@
         <v>4</v>
       </c>
       <c r="J849" s="61" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K849" s="60">
         <v>16</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="O849" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P849" s="1">
         <v>0</v>
@@ -51070,7 +51070,7 @@
         <v>4</v>
       </c>
       <c r="J850" s="61" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K850" s="60">
         <v>16</v>
@@ -51085,7 +51085,7 @@
         <v>0</v>
       </c>
       <c r="O850" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="P850" s="1">
         <v>0</v>
@@ -51126,7 +51126,7 @@
         <v>4</v>
       </c>
       <c r="J851" s="61" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K851" s="60">
         <v>16</v>
@@ -51141,7 +51141,7 @@
         <v>0</v>
       </c>
       <c r="O851" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="P851" s="1">
         <v>0</v>
@@ -51182,7 +51182,7 @@
         <v>5</v>
       </c>
       <c r="J852" s="61" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K852" s="60">
         <v>16</v>
@@ -51197,7 +51197,7 @@
         <v>0</v>
       </c>
       <c r="O852" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P852" s="1">
         <v>0</v>
@@ -51238,7 +51238,7 @@
         <v>5</v>
       </c>
       <c r="J853" s="61" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K853" s="60">
         <v>16</v>
@@ -51253,7 +51253,7 @@
         <v>0</v>
       </c>
       <c r="O853" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P853" s="1">
         <v>0</v>
@@ -51294,7 +51294,7 @@
         <v>5</v>
       </c>
       <c r="J854" s="61" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K854" s="60">
         <v>16</v>
@@ -51309,7 +51309,7 @@
         <v>0</v>
       </c>
       <c r="O854" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P854" s="1">
         <v>0</v>
@@ -51350,7 +51350,7 @@
         <v>5</v>
       </c>
       <c r="J855" s="61" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K855" s="60">
         <v>16</v>
@@ -51365,7 +51365,7 @@
         <v>0</v>
       </c>
       <c r="O855" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P855" s="1">
         <v>0</v>
@@ -51406,7 +51406,7 @@
         <v>5</v>
       </c>
       <c r="J856" s="61" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K856" s="60">
         <v>16</v>
@@ -51421,7 +51421,7 @@
         <v>0</v>
       </c>
       <c r="O856" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P856" s="1">
         <v>0</v>
@@ -51462,7 +51462,7 @@
         <v>5</v>
       </c>
       <c r="J857" s="61" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K857" s="60">
         <v>16</v>
@@ -51477,7 +51477,7 @@
         <v>0</v>
       </c>
       <c r="O857" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P857" s="1">
         <v>0</v>
@@ -51518,7 +51518,7 @@
         <v>5</v>
       </c>
       <c r="J858" s="61" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K858" s="60">
         <v>16</v>
@@ -51533,7 +51533,7 @@
         <v>0</v>
       </c>
       <c r="O858" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P858" s="1">
         <v>0</v>
@@ -51574,7 +51574,7 @@
         <v>5</v>
       </c>
       <c r="J859" s="61" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K859" s="60">
         <v>16</v>
@@ -51589,7 +51589,7 @@
         <v>0</v>
       </c>
       <c r="O859" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="P859" s="1">
         <v>0</v>
@@ -51630,7 +51630,7 @@
         <v>5</v>
       </c>
       <c r="J860" s="61" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K860" s="60">
         <v>16</v>
@@ -51645,7 +51645,7 @@
         <v>0</v>
       </c>
       <c r="O860" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="P860" s="1">
         <v>0</v>
@@ -51686,7 +51686,7 @@
         <v>5</v>
       </c>
       <c r="J861" s="61" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K861" s="60">
         <v>16</v>
@@ -51701,7 +51701,7 @@
         <v>0</v>
       </c>
       <c r="O861" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P861" s="1">
         <v>0</v>
@@ -51742,7 +51742,7 @@
         <v>5</v>
       </c>
       <c r="J862" s="61" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K862" s="60">
         <v>16</v>
@@ -51757,7 +51757,7 @@
         <v>0</v>
       </c>
       <c r="O862" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="P862" s="1">
         <v>0</v>
@@ -51798,7 +51798,7 @@
         <v>1</v>
       </c>
       <c r="J863" s="61" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K863" s="60">
         <v>30</v>
@@ -51813,7 +51813,7 @@
         <v>1</v>
       </c>
       <c r="O863" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="P863" s="1">
         <v>0</v>
@@ -51854,7 +51854,7 @@
         <v>1</v>
       </c>
       <c r="J864" s="61" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K864" s="60">
         <v>30</v>
@@ -51869,7 +51869,7 @@
         <v>1</v>
       </c>
       <c r="O864" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="P864" s="1">
         <v>0</v>
@@ -51910,7 +51910,7 @@
         <v>1</v>
       </c>
       <c r="J865" s="61" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K865" s="60">
         <v>30</v>
@@ -51925,7 +51925,7 @@
         <v>1</v>
       </c>
       <c r="O865" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="P865" s="1">
         <v>0</v>
@@ -51966,7 +51966,7 @@
         <v>1</v>
       </c>
       <c r="J866" s="61" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K866" s="60">
         <v>30</v>
@@ -51981,7 +51981,7 @@
         <v>1</v>
       </c>
       <c r="O866" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P866" s="1">
         <v>0</v>
@@ -52022,7 +52022,7 @@
         <v>2</v>
       </c>
       <c r="J867" s="61" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K867" s="60">
         <v>30</v>
@@ -52037,7 +52037,7 @@
         <v>1</v>
       </c>
       <c r="O867" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P867" s="1">
         <v>0</v>
@@ -52078,7 +52078,7 @@
         <v>2</v>
       </c>
       <c r="J868" s="61" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K868" s="60">
         <v>30</v>
@@ -52093,7 +52093,7 @@
         <v>1</v>
       </c>
       <c r="O868" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P868" s="1">
         <v>0</v>
@@ -52134,7 +52134,7 @@
         <v>2</v>
       </c>
       <c r="J869" s="61" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K869" s="60">
         <v>30</v>
@@ -52149,7 +52149,7 @@
         <v>1</v>
       </c>
       <c r="O869" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P869" s="1">
         <v>0</v>
@@ -52190,7 +52190,7 @@
         <v>2</v>
       </c>
       <c r="J870" s="61" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K870" s="60">
         <v>30</v>
@@ -52205,7 +52205,7 @@
         <v>1</v>
       </c>
       <c r="O870" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="P870" s="1">
         <v>0</v>
@@ -52246,7 +52246,7 @@
         <v>2</v>
       </c>
       <c r="J871" s="61" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K871" s="60">
         <v>30</v>
@@ -52261,7 +52261,7 @@
         <v>1</v>
       </c>
       <c r="O871" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="P871" s="1">
         <v>0</v>
@@ -52302,7 +52302,7 @@
         <v>2</v>
       </c>
       <c r="J872" s="61" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K872" s="60">
         <v>30</v>
@@ -52317,7 +52317,7 @@
         <v>1</v>
       </c>
       <c r="O872" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="P872" s="1">
         <v>0</v>
@@ -52358,7 +52358,7 @@
         <v>3</v>
       </c>
       <c r="J873" s="61" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K873" s="60">
         <v>30</v>
@@ -52373,7 +52373,7 @@
         <v>1</v>
       </c>
       <c r="O873" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P873" s="1">
         <v>0</v>
@@ -52414,7 +52414,7 @@
         <v>3</v>
       </c>
       <c r="J874" s="61" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K874" s="60">
         <v>30</v>
@@ -52429,7 +52429,7 @@
         <v>1</v>
       </c>
       <c r="O874" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="P874" s="1">
         <v>0</v>
@@ -52470,7 +52470,7 @@
         <v>3</v>
       </c>
       <c r="J875" s="61" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K875" s="60">
         <v>30</v>
@@ -52485,7 +52485,7 @@
         <v>1</v>
       </c>
       <c r="O875" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P875" s="1">
         <v>0</v>
@@ -52526,7 +52526,7 @@
         <v>3</v>
       </c>
       <c r="J876" s="61" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K876" s="60">
         <v>30</v>
@@ -52541,7 +52541,7 @@
         <v>1</v>
       </c>
       <c r="O876" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="P876" s="1">
         <v>0</v>
@@ -52582,7 +52582,7 @@
         <v>3</v>
       </c>
       <c r="J877" s="61" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K877" s="60">
         <v>30</v>
@@ -52597,7 +52597,7 @@
         <v>1</v>
       </c>
       <c r="O877" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P877" s="1">
         <v>0</v>
@@ -52638,7 +52638,7 @@
         <v>3</v>
       </c>
       <c r="J878" s="61" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K878" s="60">
         <v>30</v>
@@ -52653,7 +52653,7 @@
         <v>1</v>
       </c>
       <c r="O878" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P878" s="1">
         <v>0</v>
@@ -52694,7 +52694,7 @@
         <v>3</v>
       </c>
       <c r="J879" s="61" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K879" s="60">
         <v>30</v>
@@ -52709,7 +52709,7 @@
         <v>1</v>
       </c>
       <c r="O879" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="P879" s="1">
         <v>0</v>
@@ -52750,7 +52750,7 @@
         <v>3</v>
       </c>
       <c r="J880" s="61" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K880" s="60">
         <v>30</v>
@@ -52765,7 +52765,7 @@
         <v>1</v>
       </c>
       <c r="O880" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="P880" s="1">
         <v>0</v>
@@ -52806,7 +52806,7 @@
         <v>4</v>
       </c>
       <c r="J881" s="61" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K881" s="60">
         <v>30</v>
@@ -52821,7 +52821,7 @@
         <v>1</v>
       </c>
       <c r="O881" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="P881" s="1">
         <v>0</v>
@@ -52862,7 +52862,7 @@
         <v>4</v>
       </c>
       <c r="J882" s="61" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K882" s="60">
         <v>30</v>
@@ -52877,7 +52877,7 @@
         <v>1</v>
       </c>
       <c r="O882" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="P882" s="1">
         <v>0</v>
@@ -52918,7 +52918,7 @@
         <v>4</v>
       </c>
       <c r="J883" s="61" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K883" s="60">
         <v>30</v>
@@ -52933,7 +52933,7 @@
         <v>1</v>
       </c>
       <c r="O883" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="P883" s="1">
         <v>0</v>
@@ -52974,7 +52974,7 @@
         <v>4</v>
       </c>
       <c r="J884" s="61" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K884" s="60">
         <v>30</v>
@@ -52989,7 +52989,7 @@
         <v>1</v>
       </c>
       <c r="O884" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="P884" s="1">
         <v>0</v>
@@ -53030,7 +53030,7 @@
         <v>4</v>
       </c>
       <c r="J885" s="61" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K885" s="60">
         <v>30</v>
@@ -53045,7 +53045,7 @@
         <v>1</v>
       </c>
       <c r="O885" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P885" s="1">
         <v>0</v>
@@ -53086,7 +53086,7 @@
         <v>4</v>
       </c>
       <c r="J886" s="61" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K886" s="60">
         <v>30</v>
@@ -53101,7 +53101,7 @@
         <v>1</v>
       </c>
       <c r="O886" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="P886" s="1">
         <v>0</v>
@@ -53142,7 +53142,7 @@
         <v>4</v>
       </c>
       <c r="J887" s="61" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K887" s="60">
         <v>30</v>
@@ -53157,7 +53157,7 @@
         <v>1</v>
       </c>
       <c r="O887" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P887" s="1">
         <v>0</v>
@@ -53198,7 +53198,7 @@
         <v>4</v>
       </c>
       <c r="J888" s="61" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K888" s="60">
         <v>30</v>
@@ -53213,7 +53213,7 @@
         <v>1</v>
       </c>
       <c r="O888" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P888" s="1">
         <v>0</v>
@@ -53254,7 +53254,7 @@
         <v>4</v>
       </c>
       <c r="J889" s="61" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K889" s="60">
         <v>30</v>
@@ -53269,7 +53269,7 @@
         <v>1</v>
       </c>
       <c r="O889" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P889" s="1">
         <v>0</v>
@@ -53310,7 +53310,7 @@
         <v>4</v>
       </c>
       <c r="J890" s="61" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K890" s="60">
         <v>30</v>
@@ -53325,7 +53325,7 @@
         <v>1</v>
       </c>
       <c r="O890" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P890" s="1">
         <v>0</v>
@@ -53366,7 +53366,7 @@
         <v>5</v>
       </c>
       <c r="J891" s="61" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K891" s="60">
         <v>30</v>
@@ -53381,7 +53381,7 @@
         <v>1</v>
       </c>
       <c r="O891" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P891" s="1">
         <v>0</v>
@@ -53422,7 +53422,7 @@
         <v>5</v>
       </c>
       <c r="J892" s="61" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K892" s="60">
         <v>30</v>
@@ -53437,7 +53437,7 @@
         <v>1</v>
       </c>
       <c r="O892" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="P892" s="1">
         <v>0</v>
@@ -53478,7 +53478,7 @@
         <v>5</v>
       </c>
       <c r="J893" s="63" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K893" s="60">
         <v>30</v>
@@ -53493,7 +53493,7 @@
         <v>1</v>
       </c>
       <c r="O893" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="P893" s="1">
         <v>0</v>
@@ -53534,7 +53534,7 @@
         <v>5</v>
       </c>
       <c r="J894" s="63" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K894" s="60">
         <v>30</v>
@@ -53549,7 +53549,7 @@
         <v>1</v>
       </c>
       <c r="O894" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="P894" s="1">
         <v>0</v>
@@ -53590,7 +53590,7 @@
         <v>5</v>
       </c>
       <c r="J895" s="63" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K895" s="60">
         <v>30</v>
@@ -53605,7 +53605,7 @@
         <v>1</v>
       </c>
       <c r="O895" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P895" s="1">
         <v>0</v>
@@ -53646,7 +53646,7 @@
         <v>5</v>
       </c>
       <c r="J896" s="63" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K896" s="60">
         <v>30</v>
@@ -53661,7 +53661,7 @@
         <v>1</v>
       </c>
       <c r="O896" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="P896" s="1">
         <v>0</v>
@@ -53702,7 +53702,7 @@
         <v>5</v>
       </c>
       <c r="J897" s="63" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="K897" s="60">
         <v>30</v>
@@ -53717,7 +53717,7 @@
         <v>1</v>
       </c>
       <c r="O897" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="P897" s="1">
         <v>0</v>
@@ -53758,7 +53758,7 @@
         <v>5</v>
       </c>
       <c r="J898" s="63" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K898" s="60">
         <v>30</v>
@@ -53773,7 +53773,7 @@
         <v>1</v>
       </c>
       <c r="O898" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="P898" s="1">
         <v>0</v>
@@ -53814,7 +53814,7 @@
         <v>5</v>
       </c>
       <c r="J899" s="63" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K899" s="60">
         <v>30</v>
@@ -53829,7 +53829,7 @@
         <v>1</v>
       </c>
       <c r="O899" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="P899" s="1">
         <v>0</v>
@@ -53870,7 +53870,7 @@
         <v>5</v>
       </c>
       <c r="J900" s="63" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K900" s="60">
         <v>30</v>
@@ -53885,7 +53885,7 @@
         <v>1</v>
       </c>
       <c r="O900" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P900" s="1">
         <v>0</v>
@@ -53926,7 +53926,7 @@
         <v>5</v>
       </c>
       <c r="J901" s="63" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K901" s="60">
         <v>30</v>
@@ -53941,7 +53941,7 @@
         <v>1</v>
       </c>
       <c r="O901" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="P901" s="1">
         <v>0</v>
@@ -53982,7 +53982,7 @@
         <v>5</v>
       </c>
       <c r="J902" s="63" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K902" s="60">
         <v>30</v>
@@ -53997,7 +53997,7 @@
         <v>1</v>
       </c>
       <c r="O902" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="P902" s="1">
         <v>0</v>
@@ -54038,7 +54038,7 @@
         <v>1</v>
       </c>
       <c r="J903" s="63" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K903" s="62">
         <v>400</v>
@@ -54053,7 +54053,7 @@
         <v>2</v>
       </c>
       <c r="O903" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P903" s="1">
         <v>0</v>
@@ -54094,7 +54094,7 @@
         <v>1</v>
       </c>
       <c r="J904" s="63" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K904" s="62">
         <v>400</v>
@@ -54109,7 +54109,7 @@
         <v>2</v>
       </c>
       <c r="O904" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="P904" s="1">
         <v>0</v>
@@ -54150,7 +54150,7 @@
         <v>1</v>
       </c>
       <c r="J905" s="63" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K905" s="62">
         <v>400</v>
@@ -54165,7 +54165,7 @@
         <v>2</v>
       </c>
       <c r="O905" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P905" s="1">
         <v>0</v>
@@ -54206,7 +54206,7 @@
         <v>1</v>
       </c>
       <c r="J906" s="63" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K906" s="62">
         <v>400</v>
@@ -54221,7 +54221,7 @@
         <v>2</v>
       </c>
       <c r="O906" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P906" s="1">
         <v>0</v>
@@ -54262,7 +54262,7 @@
         <v>1</v>
       </c>
       <c r="J907" s="63" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K907" s="62">
         <v>400</v>
@@ -54277,7 +54277,7 @@
         <v>2</v>
       </c>
       <c r="O907" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="P907" s="1">
         <v>0</v>
@@ -54318,7 +54318,7 @@
         <v>1</v>
       </c>
       <c r="J908" s="63" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K908" s="62">
         <v>400</v>
@@ -54333,7 +54333,7 @@
         <v>2</v>
       </c>
       <c r="O908" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="P908" s="1">
         <v>0</v>
@@ -54374,7 +54374,7 @@
         <v>2</v>
       </c>
       <c r="J909" s="63" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K909" s="62">
         <v>400</v>
@@ -54389,7 +54389,7 @@
         <v>2</v>
       </c>
       <c r="O909" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P909" s="1">
         <v>0</v>
@@ -54430,7 +54430,7 @@
         <v>2</v>
       </c>
       <c r="J910" s="63" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K910" s="62">
         <v>400</v>
@@ -54445,7 +54445,7 @@
         <v>2</v>
       </c>
       <c r="O910" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="P910" s="1">
         <v>0</v>
@@ -54486,7 +54486,7 @@
         <v>2</v>
       </c>
       <c r="J911" s="63" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K911" s="62">
         <v>400</v>
@@ -54501,7 +54501,7 @@
         <v>2</v>
       </c>
       <c r="O911" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P911" s="1">
         <v>0</v>
@@ -54542,7 +54542,7 @@
         <v>2</v>
       </c>
       <c r="J912" s="63" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K912" s="62">
         <v>400</v>
@@ -54557,7 +54557,7 @@
         <v>2</v>
       </c>
       <c r="O912" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="P912" s="1">
         <v>0</v>
@@ -54598,7 +54598,7 @@
         <v>2</v>
       </c>
       <c r="J913" s="63" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K913" s="62">
         <v>400</v>
@@ -54613,7 +54613,7 @@
         <v>2</v>
       </c>
       <c r="O913" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="P913" s="1">
         <v>0</v>
@@ -54654,7 +54654,7 @@
         <v>2</v>
       </c>
       <c r="J914" s="63" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K914" s="62">
         <v>400</v>
@@ -54669,7 +54669,7 @@
         <v>2</v>
       </c>
       <c r="O914" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="P914" s="1">
         <v>0</v>
@@ -54710,7 +54710,7 @@
         <v>2</v>
       </c>
       <c r="J915" s="63" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K915" s="62">
         <v>400</v>
@@ -54725,7 +54725,7 @@
         <v>2</v>
       </c>
       <c r="O915" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="P915" s="1">
         <v>0</v>
@@ -54766,7 +54766,7 @@
         <v>2</v>
       </c>
       <c r="J916" s="63" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K916" s="62">
         <v>400</v>
@@ -54781,7 +54781,7 @@
         <v>2</v>
       </c>
       <c r="O916" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="P916" s="1">
         <v>0</v>
@@ -54822,7 +54822,7 @@
         <v>3</v>
       </c>
       <c r="J917" s="63" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K917" s="62">
         <v>400</v>
@@ -54837,7 +54837,7 @@
         <v>2</v>
       </c>
       <c r="O917" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="P917" s="1">
         <v>0</v>
@@ -54878,7 +54878,7 @@
         <v>3</v>
       </c>
       <c r="J918" s="63" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K918" s="62">
         <v>400</v>
@@ -54893,7 +54893,7 @@
         <v>2</v>
       </c>
       <c r="O918" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="P918" s="1">
         <v>0</v>
@@ -54934,7 +54934,7 @@
         <v>3</v>
       </c>
       <c r="J919" s="63" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K919" s="62">
         <v>400</v>
@@ -54949,7 +54949,7 @@
         <v>2</v>
       </c>
       <c r="O919" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="P919" s="1">
         <v>0</v>
@@ -54990,7 +54990,7 @@
         <v>3</v>
       </c>
       <c r="J920" s="63" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K920" s="62">
         <v>400</v>
@@ -55005,7 +55005,7 @@
         <v>2</v>
       </c>
       <c r="O920" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="P920" s="1">
         <v>0</v>
@@ -55046,7 +55046,7 @@
         <v>3</v>
       </c>
       <c r="J921" s="63" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K921" s="62">
         <v>400</v>
@@ -55061,7 +55061,7 @@
         <v>2</v>
       </c>
       <c r="O921" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P921" s="1">
         <v>0</v>
@@ -55102,7 +55102,7 @@
         <v>3</v>
       </c>
       <c r="J922" s="63" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K922" s="62">
         <v>400</v>
@@ -55117,7 +55117,7 @@
         <v>2</v>
       </c>
       <c r="O922" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="P922" s="1">
         <v>0</v>
@@ -55158,7 +55158,7 @@
         <v>3</v>
       </c>
       <c r="J923" s="63" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K923" s="62">
         <v>400</v>
@@ -55173,7 +55173,7 @@
         <v>2</v>
       </c>
       <c r="O923" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="P923" s="1">
         <v>0</v>
@@ -55214,7 +55214,7 @@
         <v>3</v>
       </c>
       <c r="J924" s="63" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K924" s="62">
         <v>400</v>
@@ -55229,7 +55229,7 @@
         <v>2</v>
       </c>
       <c r="O924" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="P924" s="1">
         <v>0</v>
@@ -55270,7 +55270,7 @@
         <v>3</v>
       </c>
       <c r="J925" s="63" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K925" s="62">
         <v>400</v>
@@ -55285,7 +55285,7 @@
         <v>2</v>
       </c>
       <c r="O925" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="P925" s="1">
         <v>0</v>
@@ -55326,7 +55326,7 @@
         <v>3</v>
       </c>
       <c r="J926" s="63" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K926" s="62">
         <v>400</v>
@@ -55341,7 +55341,7 @@
         <v>2</v>
       </c>
       <c r="O926" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="P926" s="1">
         <v>0</v>
@@ -55382,7 +55382,7 @@
         <v>4</v>
       </c>
       <c r="J927" s="63" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K927" s="62">
         <v>400</v>
@@ -55397,7 +55397,7 @@
         <v>2</v>
       </c>
       <c r="O927" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P927" s="1">
         <v>0</v>
@@ -55438,7 +55438,7 @@
         <v>4</v>
       </c>
       <c r="J928" s="63" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K928" s="62">
         <v>400</v>
@@ -55453,7 +55453,7 @@
         <v>2</v>
       </c>
       <c r="O928" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="P928" s="1">
         <v>0</v>
@@ -55494,7 +55494,7 @@
         <v>4</v>
       </c>
       <c r="J929" s="63" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K929" s="62">
         <v>400</v>
@@ -55509,7 +55509,7 @@
         <v>2</v>
       </c>
       <c r="O929" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="P929" s="1">
         <v>0</v>
@@ -55550,7 +55550,7 @@
         <v>4</v>
       </c>
       <c r="J930" s="63" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K930" s="62">
         <v>400</v>
@@ -55565,7 +55565,7 @@
         <v>2</v>
       </c>
       <c r="O930" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="P930" s="1">
         <v>0</v>
@@ -55606,7 +55606,7 @@
         <v>4</v>
       </c>
       <c r="J931" s="63" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K931" s="62">
         <v>400</v>
@@ -55621,7 +55621,7 @@
         <v>2</v>
       </c>
       <c r="O931" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="P931" s="1">
         <v>0</v>
@@ -55662,7 +55662,7 @@
         <v>4</v>
       </c>
       <c r="J932" s="63" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K932" s="62">
         <v>400</v>
@@ -55677,7 +55677,7 @@
         <v>2</v>
       </c>
       <c r="O932" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="P932" s="1">
         <v>0</v>
@@ -55718,7 +55718,7 @@
         <v>4</v>
       </c>
       <c r="J933" s="63" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K933" s="62">
         <v>400</v>
@@ -55733,7 +55733,7 @@
         <v>2</v>
       </c>
       <c r="O933" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="P933" s="1">
         <v>0</v>
@@ -55774,7 +55774,7 @@
         <v>4</v>
       </c>
       <c r="J934" s="63" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K934" s="62">
         <v>400</v>
@@ -55789,7 +55789,7 @@
         <v>2</v>
       </c>
       <c r="O934" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="P934" s="1">
         <v>0</v>
@@ -55830,7 +55830,7 @@
         <v>4</v>
       </c>
       <c r="J935" s="63" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K935" s="62">
         <v>400</v>
@@ -55845,7 +55845,7 @@
         <v>2</v>
       </c>
       <c r="O935" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="P935" s="1">
         <v>0</v>
@@ -55886,7 +55886,7 @@
         <v>4</v>
       </c>
       <c r="J936" s="63" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K936" s="62">
         <v>400</v>
@@ -55901,7 +55901,7 @@
         <v>2</v>
       </c>
       <c r="O936" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="P936" s="1">
         <v>0</v>
@@ -55942,7 +55942,7 @@
         <v>4</v>
       </c>
       <c r="J937" s="63" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="K937" s="62">
         <v>400</v>
@@ -55957,7 +55957,7 @@
         <v>2</v>
       </c>
       <c r="O937" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="P937" s="1">
         <v>0</v>
@@ -55998,7 +55998,7 @@
         <v>4</v>
       </c>
       <c r="J938" s="63" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K938" s="62">
         <v>400</v>
@@ -56013,7 +56013,7 @@
         <v>2</v>
       </c>
       <c r="O938" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="P938" s="1">
         <v>0</v>
@@ -56054,7 +56054,7 @@
         <v>5</v>
       </c>
       <c r="J939" s="63" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K939" s="62">
         <v>400</v>
@@ -56069,7 +56069,7 @@
         <v>2</v>
       </c>
       <c r="O939" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="P939" s="1">
         <v>0</v>
@@ -56110,7 +56110,7 @@
         <v>5</v>
       </c>
       <c r="J940" s="63" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K940" s="62">
         <v>400</v>
@@ -56125,7 +56125,7 @@
         <v>2</v>
       </c>
       <c r="O940" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="P940" s="1">
         <v>0</v>
@@ -56166,7 +56166,7 @@
         <v>5</v>
       </c>
       <c r="J941" s="63" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="K941" s="62">
         <v>400</v>
@@ -56181,7 +56181,7 @@
         <v>2</v>
       </c>
       <c r="O941" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="P941" s="1">
         <v>0</v>
@@ -56222,7 +56222,7 @@
         <v>5</v>
       </c>
       <c r="J942" s="63" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="K942" s="62">
         <v>400</v>
@@ -56237,7 +56237,7 @@
         <v>2</v>
       </c>
       <c r="O942" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="P942" s="1">
         <v>0</v>
@@ -56278,7 +56278,7 @@
         <v>5</v>
       </c>
       <c r="J943" s="63" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K943" s="62">
         <v>400</v>
@@ -56293,7 +56293,7 @@
         <v>2</v>
       </c>
       <c r="O943" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="P943" s="1">
         <v>0</v>
@@ -56334,7 +56334,7 @@
         <v>5</v>
       </c>
       <c r="J944" s="63" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K944" s="62">
         <v>400</v>
@@ -56349,7 +56349,7 @@
         <v>2</v>
       </c>
       <c r="O944" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="P944" s="1">
         <v>0</v>
@@ -56390,7 +56390,7 @@
         <v>5</v>
       </c>
       <c r="J945" s="63" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K945" s="62">
         <v>400</v>
@@ -56405,7 +56405,7 @@
         <v>2</v>
       </c>
       <c r="O945" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="P945" s="1">
         <v>0</v>
@@ -56446,7 +56446,7 @@
         <v>5</v>
       </c>
       <c r="J946" s="63" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="K946" s="62">
         <v>400</v>
@@ -56461,7 +56461,7 @@
         <v>2</v>
       </c>
       <c r="O946" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="P946" s="1">
         <v>0</v>
@@ -56502,7 +56502,7 @@
         <v>5</v>
       </c>
       <c r="J947" s="63" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K947" s="62">
         <v>400</v>
@@ -56517,7 +56517,7 @@
         <v>2</v>
       </c>
       <c r="O947" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="P947" s="1">
         <v>0</v>
@@ -56558,7 +56558,7 @@
         <v>5</v>
       </c>
       <c r="J948" s="63" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K948" s="62">
         <v>400</v>
@@ -56573,7 +56573,7 @@
         <v>2</v>
       </c>
       <c r="O948" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="P948" s="1">
         <v>0</v>
@@ -56614,7 +56614,7 @@
         <v>5</v>
       </c>
       <c r="J949" s="63" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K949" s="62">
         <v>400</v>
@@ -56629,7 +56629,7 @@
         <v>2</v>
       </c>
       <c r="O949" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="P949" s="1">
         <v>0</v>
@@ -56670,7 +56670,7 @@
         <v>5</v>
       </c>
       <c r="J950" s="63" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K950" s="62">
         <v>400</v>
@@ -56685,7 +56685,7 @@
         <v>2</v>
       </c>
       <c r="O950" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="P950" s="1">
         <v>0</v>
@@ -56726,7 +56726,7 @@
         <v>5</v>
       </c>
       <c r="J951" s="63" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K951" s="62">
         <v>400</v>
@@ -56741,7 +56741,7 @@
         <v>2</v>
       </c>
       <c r="O951" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="P951" s="1">
         <v>0</v>
@@ -56782,7 +56782,7 @@
         <v>5</v>
       </c>
       <c r="J952" s="63" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K952" s="62">
         <v>400</v>
@@ -56797,7 +56797,7 @@
         <v>2</v>
       </c>
       <c r="O952" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="P952" s="1">
         <v>0</v>
@@ -56838,7 +56838,7 @@
         <v>1</v>
       </c>
       <c r="J953" s="63" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K953" s="62">
         <v>6000</v>
@@ -56853,7 +56853,7 @@
         <v>3</v>
       </c>
       <c r="O953" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="P953" s="1">
         <v>0</v>
@@ -56894,7 +56894,7 @@
         <v>1</v>
       </c>
       <c r="J954" s="63" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K954" s="62">
         <v>6000</v>
@@ -56909,7 +56909,7 @@
         <v>3</v>
       </c>
       <c r="O954" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="P954" s="1">
         <v>0</v>
@@ -56950,7 +56950,7 @@
         <v>1</v>
       </c>
       <c r="J955" s="63" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K955" s="62">
         <v>6000</v>
@@ -56965,7 +56965,7 @@
         <v>3</v>
       </c>
       <c r="O955" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="P955" s="1">
         <v>0</v>
@@ -57006,7 +57006,7 @@
         <v>1</v>
       </c>
       <c r="J956" s="63" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K956" s="62">
         <v>6000</v>
@@ -57021,7 +57021,7 @@
         <v>3</v>
       </c>
       <c r="O956" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P956" s="1">
         <v>0</v>
@@ -57062,7 +57062,7 @@
         <v>1</v>
       </c>
       <c r="J957" s="63" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K957" s="62">
         <v>6000</v>
@@ -57077,7 +57077,7 @@
         <v>3</v>
       </c>
       <c r="O957" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P957" s="1">
         <v>0</v>
@@ -57118,7 +57118,7 @@
         <v>1</v>
       </c>
       <c r="J958" s="63" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K958" s="62">
         <v>6000</v>
@@ -57133,7 +57133,7 @@
         <v>3</v>
       </c>
       <c r="O958" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P958" s="1">
         <v>0</v>
@@ -57174,7 +57174,7 @@
         <v>1</v>
       </c>
       <c r="J959" s="63" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K959" s="62">
         <v>6000</v>
@@ -57189,7 +57189,7 @@
         <v>3</v>
       </c>
       <c r="O959" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P959" s="1">
         <v>0</v>
@@ -57230,7 +57230,7 @@
         <v>1</v>
       </c>
       <c r="J960" s="63" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K960" s="62">
         <v>6000</v>
@@ -57245,7 +57245,7 @@
         <v>3</v>
       </c>
       <c r="O960" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="P960" s="1">
         <v>0</v>
@@ -57286,7 +57286,7 @@
         <v>2</v>
       </c>
       <c r="J961" s="63" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K961" s="62">
         <v>6000</v>
@@ -57301,7 +57301,7 @@
         <v>3</v>
       </c>
       <c r="O961" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="P961" s="1">
         <v>0</v>
@@ -57342,7 +57342,7 @@
         <v>2</v>
       </c>
       <c r="J962" s="63" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K962" s="62">
         <v>6000</v>
@@ -57357,7 +57357,7 @@
         <v>3</v>
       </c>
       <c r="O962" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="P962" s="1">
         <v>0</v>
@@ -57398,7 +57398,7 @@
         <v>2</v>
       </c>
       <c r="J963" s="63" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K963" s="62">
         <v>6000</v>
@@ -57413,7 +57413,7 @@
         <v>3</v>
       </c>
       <c r="O963" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="P963" s="1">
         <v>0</v>
@@ -57454,7 +57454,7 @@
         <v>2</v>
       </c>
       <c r="J964" s="63" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K964" s="62">
         <v>6000</v>
@@ -57469,7 +57469,7 @@
         <v>3</v>
       </c>
       <c r="O964" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="P964" s="1">
         <v>0</v>
@@ -57510,7 +57510,7 @@
         <v>2</v>
       </c>
       <c r="J965" s="63" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="K965" s="62">
         <v>6000</v>
@@ -57525,7 +57525,7 @@
         <v>3</v>
       </c>
       <c r="O965" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="P965" s="1">
         <v>0</v>
@@ -57566,7 +57566,7 @@
         <v>2</v>
       </c>
       <c r="J966" s="63" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K966" s="62">
         <v>6000</v>
@@ -57581,7 +57581,7 @@
         <v>3</v>
       </c>
       <c r="O966" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="P966" s="1">
         <v>0</v>
@@ -57622,7 +57622,7 @@
         <v>2</v>
       </c>
       <c r="J967" s="63" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="K967" s="62">
         <v>6000</v>
@@ -57637,7 +57637,7 @@
         <v>3</v>
       </c>
       <c r="O967" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="P967" s="1">
         <v>0</v>
@@ -57678,7 +57678,7 @@
         <v>2</v>
       </c>
       <c r="J968" s="63" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="K968" s="62">
         <v>6000</v>
@@ -57693,7 +57693,7 @@
         <v>3</v>
       </c>
       <c r="O968" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="P968" s="1">
         <v>0</v>
@@ -57734,7 +57734,7 @@
         <v>2</v>
       </c>
       <c r="J969" s="63" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="K969" s="62">
         <v>6000</v>
@@ -57749,7 +57749,7 @@
         <v>3</v>
       </c>
       <c r="O969" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P969" s="1">
         <v>0</v>
@@ -57790,7 +57790,7 @@
         <v>2</v>
       </c>
       <c r="J970" s="63" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K970" s="62">
         <v>6000</v>
@@ -57805,7 +57805,7 @@
         <v>3</v>
       </c>
       <c r="O970" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="P970" s="1">
         <v>0</v>
@@ -57846,7 +57846,7 @@
         <v>3</v>
       </c>
       <c r="J971" s="63" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K971" s="62">
         <v>6000</v>
@@ -57861,7 +57861,7 @@
         <v>3</v>
       </c>
       <c r="O971" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="P971" s="1">
         <v>0</v>
@@ -57902,7 +57902,7 @@
         <v>3</v>
       </c>
       <c r="J972" s="63" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K972" s="62">
         <v>6000</v>
@@ -57917,7 +57917,7 @@
         <v>3</v>
       </c>
       <c r="O972" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="P972" s="1">
         <v>0</v>
@@ -57958,7 +57958,7 @@
         <v>3</v>
       </c>
       <c r="J973" s="63" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K973" s="62">
         <v>6000</v>
@@ -57973,7 +57973,7 @@
         <v>3</v>
       </c>
       <c r="O973" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P973" s="1">
         <v>0</v>
@@ -58014,7 +58014,7 @@
         <v>3</v>
       </c>
       <c r="J974" s="63" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K974" s="62">
         <v>6000</v>
@@ -58029,7 +58029,7 @@
         <v>3</v>
       </c>
       <c r="O974" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="P974" s="1">
         <v>0</v>
@@ -58070,7 +58070,7 @@
         <v>3</v>
       </c>
       <c r="J975" s="63" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K975" s="62">
         <v>6000</v>
@@ -58085,7 +58085,7 @@
         <v>3</v>
       </c>
       <c r="O975" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="P975" s="1">
         <v>0</v>
@@ -58126,7 +58126,7 @@
         <v>3</v>
       </c>
       <c r="J976" s="63" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K976" s="62">
         <v>6000</v>
@@ -58141,7 +58141,7 @@
         <v>3</v>
       </c>
       <c r="O976" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="P976" s="1">
         <v>0</v>
@@ -58182,7 +58182,7 @@
         <v>3</v>
       </c>
       <c r="J977" s="63" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K977" s="62">
         <v>6000</v>
@@ -58197,7 +58197,7 @@
         <v>3</v>
       </c>
       <c r="O977" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="P977" s="1">
         <v>0</v>
@@ -58238,7 +58238,7 @@
         <v>3</v>
       </c>
       <c r="J978" s="63" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K978" s="62">
         <v>6000</v>
@@ -58253,7 +58253,7 @@
         <v>3</v>
       </c>
       <c r="O978" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="P978" s="1">
         <v>0</v>
@@ -58294,7 +58294,7 @@
         <v>3</v>
       </c>
       <c r="J979" s="63" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="K979" s="62">
         <v>6000</v>
@@ -58309,7 +58309,7 @@
         <v>3</v>
       </c>
       <c r="O979" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="P979" s="1">
         <v>0</v>
@@ -58350,7 +58350,7 @@
         <v>3</v>
       </c>
       <c r="J980" s="63" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K980" s="62">
         <v>6000</v>
@@ -58365,7 +58365,7 @@
         <v>3</v>
       </c>
       <c r="O980" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="P980" s="1">
         <v>0</v>
@@ -58406,7 +58406,7 @@
         <v>3</v>
       </c>
       <c r="J981" s="63" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="K981" s="62">
         <v>6000</v>
@@ -58421,7 +58421,7 @@
         <v>3</v>
       </c>
       <c r="O981" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="P981" s="1">
         <v>0</v>
@@ -58462,7 +58462,7 @@
         <v>3</v>
       </c>
       <c r="J982" s="63" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="K982" s="62">
         <v>6000</v>
@@ -58477,7 +58477,7 @@
         <v>3</v>
       </c>
       <c r="O982" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="P982" s="1">
         <v>0</v>
@@ -58518,7 +58518,7 @@
         <v>4</v>
       </c>
       <c r="J983" s="63" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K983" s="62">
         <v>6000</v>
@@ -58533,7 +58533,7 @@
         <v>3</v>
       </c>
       <c r="O983" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="P983" s="1">
         <v>0</v>
@@ -58574,7 +58574,7 @@
         <v>4</v>
       </c>
       <c r="J984" s="63" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="K984" s="62">
         <v>6000</v>
@@ -58589,7 +58589,7 @@
         <v>3</v>
       </c>
       <c r="O984" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="P984" s="1">
         <v>0</v>
@@ -58630,7 +58630,7 @@
         <v>4</v>
       </c>
       <c r="J985" s="63" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="K985" s="62">
         <v>6000</v>
@@ -58645,7 +58645,7 @@
         <v>3</v>
       </c>
       <c r="O985" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="P985" s="1">
         <v>0</v>
@@ -58686,7 +58686,7 @@
         <v>4</v>
       </c>
       <c r="J986" s="63" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="K986" s="62">
         <v>6000</v>
@@ -58701,7 +58701,7 @@
         <v>3</v>
       </c>
       <c r="O986" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="P986" s="1">
         <v>0</v>
@@ -58742,7 +58742,7 @@
         <v>4</v>
       </c>
       <c r="J987" s="63" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K987" s="62">
         <v>6000</v>
@@ -58757,7 +58757,7 @@
         <v>3</v>
       </c>
       <c r="O987" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="P987" s="1">
         <v>0</v>
@@ -58798,7 +58798,7 @@
         <v>4</v>
       </c>
       <c r="J988" s="63" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="K988" s="62">
         <v>6000</v>
@@ -58813,7 +58813,7 @@
         <v>3</v>
       </c>
       <c r="O988" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="P988" s="1">
         <v>0</v>
@@ -58854,7 +58854,7 @@
         <v>4</v>
       </c>
       <c r="J989" s="63" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="K989" s="62">
         <v>6000</v>
@@ -58869,7 +58869,7 @@
         <v>3</v>
       </c>
       <c r="O989" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="P989" s="1">
         <v>0</v>
@@ -58910,7 +58910,7 @@
         <v>4</v>
       </c>
       <c r="J990" s="63" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K990" s="62">
         <v>6000</v>
@@ -58925,7 +58925,7 @@
         <v>3</v>
       </c>
       <c r="O990" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="P990" s="1">
         <v>0</v>
@@ -58966,7 +58966,7 @@
         <v>4</v>
       </c>
       <c r="J991" s="63" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K991" s="62">
         <v>6000</v>
@@ -58981,7 +58981,7 @@
         <v>3</v>
       </c>
       <c r="O991" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="P991" s="1">
         <v>0</v>
@@ -59022,7 +59022,7 @@
         <v>4</v>
       </c>
       <c r="J992" s="63" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="K992" s="62">
         <v>6000</v>
@@ -59037,7 +59037,7 @@
         <v>3</v>
       </c>
       <c r="O992" s="1" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="P992" s="1">
         <v>0</v>
@@ -59078,7 +59078,7 @@
         <v>4</v>
       </c>
       <c r="J993" s="63" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="K993" s="62">
         <v>6000</v>
@@ -59093,7 +59093,7 @@
         <v>3</v>
       </c>
       <c r="O993" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="P993" s="1">
         <v>0</v>
@@ -59134,7 +59134,7 @@
         <v>4</v>
       </c>
       <c r="J994" s="63" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="K994" s="62">
         <v>6000</v>
@@ -59149,7 +59149,7 @@
         <v>3</v>
       </c>
       <c r="O994" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="P994" s="1">
         <v>0</v>
@@ -59190,7 +59190,7 @@
         <v>4</v>
       </c>
       <c r="J995" s="63" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="K995" s="62">
         <v>6000</v>
@@ -59205,7 +59205,7 @@
         <v>3</v>
       </c>
       <c r="O995" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="P995" s="1">
         <v>0</v>
@@ -59246,7 +59246,7 @@
         <v>4</v>
       </c>
       <c r="J996" s="63" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="K996" s="62">
         <v>6000</v>
@@ -59261,7 +59261,7 @@
         <v>3</v>
       </c>
       <c r="O996" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="P996" s="1">
         <v>0</v>
@@ -59302,7 +59302,7 @@
         <v>5</v>
       </c>
       <c r="J997" s="63" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K997" s="62">
         <v>6000</v>
@@ -59317,7 +59317,7 @@
         <v>3</v>
       </c>
       <c r="O997" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="P997" s="1">
         <v>0</v>
@@ -59358,7 +59358,7 @@
         <v>5</v>
       </c>
       <c r="J998" s="63" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="K998" s="62">
         <v>6000</v>
@@ -59373,7 +59373,7 @@
         <v>3</v>
       </c>
       <c r="O998" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="P998" s="1">
         <v>0</v>
@@ -59414,7 +59414,7 @@
         <v>5</v>
       </c>
       <c r="J999" s="63" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="K999" s="62">
         <v>6000</v>
@@ -59429,7 +59429,7 @@
         <v>3</v>
       </c>
       <c r="O999" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="P999" s="1">
         <v>0</v>
@@ -59470,7 +59470,7 @@
         <v>5</v>
       </c>
       <c r="J1000" s="63" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K1000" s="62">
         <v>6000</v>
@@ -59485,7 +59485,7 @@
         <v>3</v>
       </c>
       <c r="O1000" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="P1000" s="1">
         <v>0</v>
@@ -59526,7 +59526,7 @@
         <v>5</v>
       </c>
       <c r="J1001" s="63" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K1001" s="62">
         <v>6000</v>
@@ -59541,7 +59541,7 @@
         <v>3</v>
       </c>
       <c r="O1001" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="P1001" s="1">
         <v>0</v>
@@ -59582,7 +59582,7 @@
         <v>5</v>
       </c>
       <c r="J1002" s="63" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K1002" s="62">
         <v>6000</v>
@@ -59597,7 +59597,7 @@
         <v>3</v>
       </c>
       <c r="O1002" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="P1002" s="1">
         <v>0</v>
@@ -59638,7 +59638,7 @@
         <v>5</v>
       </c>
       <c r="J1003" s="63" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K1003" s="62">
         <v>6000</v>
@@ -59653,7 +59653,7 @@
         <v>3</v>
       </c>
       <c r="O1003" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="P1003" s="1">
         <v>0</v>
@@ -59694,7 +59694,7 @@
         <v>5</v>
       </c>
       <c r="J1004" s="63" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K1004" s="62">
         <v>6000</v>
@@ -59709,7 +59709,7 @@
         <v>3</v>
       </c>
       <c r="O1004" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="P1004" s="1">
         <v>0</v>
@@ -59750,7 +59750,7 @@
         <v>5</v>
       </c>
       <c r="J1005" s="63" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K1005" s="62">
         <v>6000</v>
@@ -59765,7 +59765,7 @@
         <v>3</v>
       </c>
       <c r="O1005" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="P1005" s="1">
         <v>0</v>
@@ -59806,7 +59806,7 @@
         <v>5</v>
       </c>
       <c r="J1006" s="63" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K1006" s="62">
         <v>6000</v>
@@ -59821,7 +59821,7 @@
         <v>3</v>
       </c>
       <c r="O1006" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="P1006" s="1">
         <v>0</v>
@@ -59862,7 +59862,7 @@
         <v>5</v>
       </c>
       <c r="J1007" s="63" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K1007" s="62">
         <v>6000</v>
@@ -59877,7 +59877,7 @@
         <v>3</v>
       </c>
       <c r="O1007" s="1" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="P1007" s="1">
         <v>0</v>
@@ -59918,7 +59918,7 @@
         <v>5</v>
       </c>
       <c r="J1008" s="63" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K1008" s="62">
         <v>6000</v>
@@ -59933,7 +59933,7 @@
         <v>3</v>
       </c>
       <c r="O1008" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="P1008" s="1">
         <v>0</v>
@@ -59974,7 +59974,7 @@
         <v>5</v>
       </c>
       <c r="J1009" s="63" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K1009" s="62">
         <v>6000</v>
@@ -59989,7 +59989,7 @@
         <v>3</v>
       </c>
       <c r="O1009" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="P1009" s="1">
         <v>0</v>
@@ -60030,7 +60030,7 @@
         <v>5</v>
       </c>
       <c r="J1010" s="63" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K1010" s="62">
         <v>6000</v>
@@ -60045,7 +60045,7 @@
         <v>3</v>
       </c>
       <c r="O1010" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P1010" s="1">
         <v>0</v>
@@ -60086,7 +60086,7 @@
         <v>5</v>
       </c>
       <c r="J1011" s="63" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K1011" s="62">
         <v>6000</v>
@@ -60101,7 +60101,7 @@
         <v>3</v>
       </c>
       <c r="O1011" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="P1011" s="1">
         <v>0</v>
@@ -60142,7 +60142,7 @@
         <v>5</v>
       </c>
       <c r="J1012" s="63" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K1012" s="62">
         <v>6000</v>
@@ -60157,7 +60157,7 @@
         <v>3</v>
       </c>
       <c r="O1012" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="P1012" s="1">
         <v>0</v>
@@ -60198,7 +60198,7 @@
         <v>1</v>
       </c>
       <c r="J1013" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K1013" s="1">
         <v>120</v>
@@ -60213,7 +60213,7 @@
         <v>0</v>
       </c>
       <c r="O1013" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="P1013" s="1">
         <v>0</v>
@@ -60254,7 +60254,7 @@
         <v>1</v>
       </c>
       <c r="J1014" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K1014" s="1">
         <v>120</v>
@@ -60269,7 +60269,7 @@
         <v>0</v>
       </c>
       <c r="O1014" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="P1014" s="1">
         <v>0</v>
@@ -60310,7 +60310,7 @@
         <v>1</v>
       </c>
       <c r="J1015" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K1015" s="1">
         <v>120</v>
@@ -60325,7 +60325,7 @@
         <v>0</v>
       </c>
       <c r="O1015" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="P1015" s="1">
         <v>0</v>
@@ -60366,7 +60366,7 @@
         <v>2</v>
       </c>
       <c r="J1016" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K1016" s="1">
         <v>120</v>
@@ -60381,7 +60381,7 @@
         <v>0</v>
       </c>
       <c r="O1016" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="P1016" s="1">
         <v>0</v>
@@ -60422,7 +60422,7 @@
         <v>2</v>
       </c>
       <c r="J1017" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K1017" s="1">
         <v>120</v>
@@ -60437,7 +60437,7 @@
         <v>0</v>
       </c>
       <c r="O1017" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="P1017" s="1">
         <v>0</v>
@@ -60478,7 +60478,7 @@
         <v>2</v>
       </c>
       <c r="J1018" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K1018" s="1">
         <v>120</v>
@@ -60493,7 +60493,7 @@
         <v>0</v>
       </c>
       <c r="O1018" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P1018" s="1">
         <v>0</v>
@@ -60534,7 +60534,7 @@
         <v>3</v>
       </c>
       <c r="J1019" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="K1019" s="1">
         <v>120</v>
@@ -60549,7 +60549,7 @@
         <v>0</v>
       </c>
       <c r="O1019" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="P1019" s="1">
         <v>0</v>
@@ -60590,7 +60590,7 @@
         <v>3</v>
       </c>
       <c r="J1020" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K1020" s="1">
         <v>120</v>
@@ -60605,7 +60605,7 @@
         <v>0</v>
       </c>
       <c r="O1020" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="P1020" s="1">
         <v>0</v>
@@ -60646,7 +60646,7 @@
         <v>3</v>
       </c>
       <c r="J1021" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="K1021" s="1">
         <v>120</v>
@@ -60661,7 +60661,7 @@
         <v>0</v>
       </c>
       <c r="O1021" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="P1021" s="1">
         <v>0</v>
@@ -60702,7 +60702,7 @@
         <v>3</v>
       </c>
       <c r="J1022" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="K1022" s="1">
         <v>120</v>
@@ -60717,7 +60717,7 @@
         <v>0</v>
       </c>
       <c r="O1022" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P1022" s="1">
         <v>0</v>
@@ -60758,7 +60758,7 @@
         <v>4</v>
       </c>
       <c r="J1023" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K1023" s="1">
         <v>120</v>
@@ -60773,7 +60773,7 @@
         <v>0</v>
       </c>
       <c r="O1023" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P1023" s="1">
         <v>0</v>
@@ -60814,7 +60814,7 @@
         <v>4</v>
       </c>
       <c r="J1024" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K1024" s="1">
         <v>120</v>
@@ -60829,7 +60829,7 @@
         <v>0</v>
       </c>
       <c r="O1024" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="P1024" s="1">
         <v>0</v>
@@ -60870,7 +60870,7 @@
         <v>4</v>
       </c>
       <c r="J1025" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="K1025" s="1">
         <v>120</v>
@@ -60885,7 +60885,7 @@
         <v>0</v>
       </c>
       <c r="O1025" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="P1025" s="1">
         <v>0</v>
@@ -60926,7 +60926,7 @@
         <v>4</v>
       </c>
       <c r="J1026" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K1026" s="1">
         <v>120</v>
@@ -60941,7 +60941,7 @@
         <v>0</v>
       </c>
       <c r="O1026" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="P1026" s="1">
         <v>0</v>
@@ -60982,7 +60982,7 @@
         <v>5</v>
       </c>
       <c r="J1027" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K1027" s="1">
         <v>120</v>
@@ -60997,7 +60997,7 @@
         <v>0</v>
       </c>
       <c r="O1027" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P1027" s="1">
         <v>0</v>
@@ -61038,7 +61038,7 @@
         <v>5</v>
       </c>
       <c r="J1028" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="K1028" s="1">
         <v>120</v>
@@ -61053,7 +61053,7 @@
         <v>0</v>
       </c>
       <c r="O1028" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="P1028" s="1">
         <v>0</v>
@@ -61094,7 +61094,7 @@
         <v>5</v>
       </c>
       <c r="J1029" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K1029" s="1">
         <v>120</v>
@@ -61109,7 +61109,7 @@
         <v>0</v>
       </c>
       <c r="O1029" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="P1029" s="1">
         <v>0</v>
@@ -61150,7 +61150,7 @@
         <v>5</v>
       </c>
       <c r="J1030" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="K1030" s="1">
         <v>120</v>
@@ -61165,7 +61165,7 @@
         <v>0</v>
       </c>
       <c r="O1030" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="P1030" s="1">
         <v>0</v>
@@ -61206,7 +61206,7 @@
         <v>6</v>
       </c>
       <c r="J1031" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K1031" s="1">
         <v>120</v>
@@ -61221,7 +61221,7 @@
         <v>0</v>
       </c>
       <c r="O1031" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="P1031" s="1">
         <v>0</v>
@@ -61262,7 +61262,7 @@
         <v>6</v>
       </c>
       <c r="J1032" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K1032" s="1">
         <v>120</v>
@@ -61277,7 +61277,7 @@
         <v>0</v>
       </c>
       <c r="O1032" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="P1032" s="1">
         <v>0</v>
@@ -61318,7 +61318,7 @@
         <v>6</v>
       </c>
       <c r="J1033" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="K1033" s="1">
         <v>120</v>
@@ -61333,7 +61333,7 @@
         <v>0</v>
       </c>
       <c r="O1033" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="P1033" s="1">
         <v>0</v>
@@ -61374,7 +61374,7 @@
         <v>6</v>
       </c>
       <c r="J1034" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K1034" s="1">
         <v>120</v>
@@ -61389,7 +61389,7 @@
         <v>0</v>
       </c>
       <c r="O1034" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="P1034" s="1">
         <v>0</v>
@@ -61430,7 +61430,7 @@
         <v>6</v>
       </c>
       <c r="J1035" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K1035" s="1">
         <v>120</v>
@@ -61445,7 +61445,7 @@
         <v>0</v>
       </c>
       <c r="O1035" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="P1035" s="1">
         <v>0</v>
@@ -61486,7 +61486,7 @@
         <v>7</v>
       </c>
       <c r="J1036" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K1036" s="1">
         <v>120</v>
@@ -61501,7 +61501,7 @@
         <v>0</v>
       </c>
       <c r="O1036" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P1036" s="1">
         <v>0</v>
@@ -61542,7 +61542,7 @@
         <v>7</v>
       </c>
       <c r="J1037" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="K1037" s="1">
         <v>120</v>
@@ -61557,7 +61557,7 @@
         <v>0</v>
       </c>
       <c r="O1037" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="P1037" s="1">
         <v>0</v>
@@ -61598,7 +61598,7 @@
         <v>7</v>
       </c>
       <c r="J1038" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="K1038" s="1">
         <v>120</v>
@@ -61613,7 +61613,7 @@
         <v>0</v>
       </c>
       <c r="O1038" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="P1038" s="1">
         <v>0</v>
@@ -61654,7 +61654,7 @@
         <v>7</v>
       </c>
       <c r="J1039" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="K1039" s="1">
         <v>120</v>
@@ -61669,7 +61669,7 @@
         <v>0</v>
       </c>
       <c r="O1039" s="1" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="P1039" s="1">
         <v>0</v>
@@ -61710,7 +61710,7 @@
         <v>7</v>
       </c>
       <c r="J1040" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="K1040" s="1">
         <v>120</v>
@@ -61725,7 +61725,7 @@
         <v>0</v>
       </c>
       <c r="O1040" s="1" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="P1040" s="1">
         <v>0</v>
@@ -61766,7 +61766,7 @@
         <v>8</v>
       </c>
       <c r="J1041" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K1041" s="1">
         <v>120</v>
@@ -61781,7 +61781,7 @@
         <v>0</v>
       </c>
       <c r="O1041" s="1" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P1041" s="1">
         <v>0</v>
@@ -61822,7 +61822,7 @@
         <v>8</v>
       </c>
       <c r="J1042" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K1042" s="1">
         <v>120</v>
@@ -61837,7 +61837,7 @@
         <v>0</v>
       </c>
       <c r="O1042" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="P1042" s="1">
         <v>0</v>
@@ -61878,7 +61878,7 @@
         <v>8</v>
       </c>
       <c r="J1043" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="K1043" s="1">
         <v>120</v>
@@ -61893,7 +61893,7 @@
         <v>0</v>
       </c>
       <c r="O1043" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="P1043" s="1">
         <v>0</v>
@@ -61934,7 +61934,7 @@
         <v>8</v>
       </c>
       <c r="J1044" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="K1044" s="1">
         <v>120</v>
@@ -61949,7 +61949,7 @@
         <v>0</v>
       </c>
       <c r="O1044" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="P1044" s="1">
         <v>0</v>
@@ -61990,7 +61990,7 @@
         <v>8</v>
       </c>
       <c r="J1045" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="K1045" s="1">
         <v>120</v>
@@ -62005,7 +62005,7 @@
         <v>0</v>
       </c>
       <c r="O1045" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="P1045" s="1">
         <v>0</v>
@@ -62046,7 +62046,7 @@
         <v>8</v>
       </c>
       <c r="J1046" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="K1046" s="1">
         <v>120</v>
@@ -62061,7 +62061,7 @@
         <v>0</v>
       </c>
       <c r="O1046" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="P1046" s="1">
         <v>0</v>
@@ -62102,7 +62102,7 @@
         <v>8</v>
       </c>
       <c r="J1047" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="K1047" s="1">
         <v>120</v>
@@ -62117,7 +62117,7 @@
         <v>0</v>
       </c>
       <c r="O1047" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="P1047" s="1">
         <v>0</v>
@@ -62158,7 +62158,7 @@
         <v>9</v>
       </c>
       <c r="J1048" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="K1048" s="1">
         <v>120</v>
@@ -62173,7 +62173,7 @@
         <v>0</v>
       </c>
       <c r="O1048" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="P1048" s="1">
         <v>0</v>
@@ -62214,7 +62214,7 @@
         <v>9</v>
       </c>
       <c r="J1049" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="K1049" s="1">
         <v>120</v>
@@ -62229,7 +62229,7 @@
         <v>0</v>
       </c>
       <c r="O1049" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="P1049" s="1">
         <v>0</v>
@@ -62270,7 +62270,7 @@
         <v>9</v>
       </c>
       <c r="J1050" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K1050" s="1">
         <v>120</v>
@@ -62285,7 +62285,7 @@
         <v>0</v>
       </c>
       <c r="O1050" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="P1050" s="1">
         <v>0</v>
@@ -62326,7 +62326,7 @@
         <v>9</v>
       </c>
       <c r="J1051" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="K1051" s="1">
         <v>120</v>
@@ -62341,7 +62341,7 @@
         <v>0</v>
       </c>
       <c r="O1051" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="P1051" s="1">
         <v>0</v>
@@ -62382,7 +62382,7 @@
         <v>9</v>
       </c>
       <c r="J1052" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K1052" s="1">
         <v>120</v>
@@ -62397,7 +62397,7 @@
         <v>0</v>
       </c>
       <c r="O1052" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="P1052" s="1">
         <v>0</v>
@@ -62438,7 +62438,7 @@
         <v>9</v>
       </c>
       <c r="J1053" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="K1053" s="1">
         <v>120</v>
@@ -62453,7 +62453,7 @@
         <v>0</v>
       </c>
       <c r="O1053" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="P1053" s="1">
         <v>0</v>
@@ -62494,7 +62494,7 @@
         <v>9</v>
       </c>
       <c r="J1054" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K1054" s="1">
         <v>120</v>
@@ -62509,7 +62509,7 @@
         <v>0</v>
       </c>
       <c r="O1054" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="P1054" s="1">
         <v>0</v>
@@ -62550,7 +62550,7 @@
         <v>9</v>
       </c>
       <c r="J1055" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="K1055" s="1">
         <v>120</v>
@@ -62565,7 +62565,7 @@
         <v>0</v>
       </c>
       <c r="O1055" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="P1055" s="1">
         <v>0</v>
@@ -62606,7 +62606,7 @@
         <v>9</v>
       </c>
       <c r="J1056" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K1056" s="1">
         <v>120</v>
@@ -62621,7 +62621,7 @@
         <v>0</v>
       </c>
       <c r="O1056" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="P1056" s="1">
         <v>0</v>
@@ -62662,7 +62662,7 @@
         <v>10</v>
       </c>
       <c r="J1057" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K1057" s="1">
         <v>120</v>
@@ -62677,7 +62677,7 @@
         <v>0</v>
       </c>
       <c r="O1057" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="P1057" s="1">
         <v>0</v>
@@ -62718,7 +62718,7 @@
         <v>10</v>
       </c>
       <c r="J1058" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="K1058" s="1">
         <v>120</v>
@@ -62733,7 +62733,7 @@
         <v>0</v>
       </c>
       <c r="O1058" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="P1058" s="1">
         <v>0</v>
@@ -62774,7 +62774,7 @@
         <v>10</v>
       </c>
       <c r="J1059" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="K1059" s="1">
         <v>120</v>
@@ -62789,7 +62789,7 @@
         <v>0</v>
       </c>
       <c r="O1059" s="1" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="P1059" s="1">
         <v>0</v>
@@ -62830,7 +62830,7 @@
         <v>10</v>
       </c>
       <c r="J1060" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K1060" s="1">
         <v>120</v>
@@ -62845,7 +62845,7 @@
         <v>0</v>
       </c>
       <c r="O1060" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="P1060" s="1">
         <v>0</v>
@@ -62886,7 +62886,7 @@
         <v>10</v>
       </c>
       <c r="J1061" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="K1061" s="1">
         <v>120</v>
@@ -62901,7 +62901,7 @@
         <v>0</v>
       </c>
       <c r="O1061" s="1" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="P1061" s="1">
         <v>0</v>
@@ -62942,7 +62942,7 @@
         <v>10</v>
       </c>
       <c r="J1062" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="K1062" s="1">
         <v>120</v>
@@ -62957,7 +62957,7 @@
         <v>0</v>
       </c>
       <c r="O1062" s="1" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="P1062" s="1">
         <v>0</v>
@@ -62998,7 +62998,7 @@
         <v>10</v>
       </c>
       <c r="J1063" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="K1063" s="1">
         <v>120</v>
@@ -63013,7 +63013,7 @@
         <v>0</v>
       </c>
       <c r="O1063" s="1" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="P1063" s="1">
         <v>0</v>
@@ -63054,7 +63054,7 @@
         <v>10</v>
       </c>
       <c r="J1064" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K1064" s="1">
         <v>120</v>
@@ -63069,7 +63069,7 @@
         <v>0</v>
       </c>
       <c r="O1064" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P1064" s="1">
         <v>0</v>
@@ -63110,7 +63110,7 @@
         <v>10</v>
       </c>
       <c r="J1065" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="K1065" s="1">
         <v>120</v>
@@ -63125,7 +63125,7 @@
         <v>0</v>
       </c>
       <c r="O1065" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="P1065" s="1">
         <v>0</v>
@@ -63166,7 +63166,7 @@
         <v>10</v>
       </c>
       <c r="J1066" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="K1066" s="1">
         <v>120</v>
@@ -63181,7 +63181,7 @@
         <v>0</v>
       </c>
       <c r="O1066" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="P1066" s="1">
         <v>0</v>
@@ -63222,7 +63222,7 @@
         <v>10</v>
       </c>
       <c r="J1067" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="K1067" s="1">
         <v>120</v>
@@ -63237,7 +63237,7 @@
         <v>0</v>
       </c>
       <c r="O1067" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="P1067" s="1">
         <v>0</v>
@@ -63272,7 +63272,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -63287,7 +63287,7 @@
         <v>0</v>
       </c>
       <c r="O1068" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="P1068" s="1">
         <v>0</v>
@@ -63322,7 +63322,7 @@
         <v>1</v>
       </c>
       <c r="J1069" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K1069" s="1">
         <v>100</v>
@@ -63337,7 +63337,7 @@
         <v>0</v>
       </c>
       <c r="O1069" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="P1069" s="1">
         <v>0</v>
@@ -63372,7 +63372,7 @@
         <v>1</v>
       </c>
       <c r="J1070" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K1070" s="1">
         <v>100</v>
@@ -63387,7 +63387,7 @@
         <v>0</v>
       </c>
       <c r="O1070" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P1070" s="1">
         <v>0</v>
@@ -63422,7 +63422,7 @@
         <v>2</v>
       </c>
       <c r="J1071" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K1071" s="1">
         <v>100</v>
@@ -63437,7 +63437,7 @@
         <v>0</v>
       </c>
       <c r="O1071" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P1071" s="1">
         <v>0</v>
@@ -63472,7 +63472,7 @@
         <v>2</v>
       </c>
       <c r="J1072" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K1072" s="1">
         <v>100</v>
@@ -63487,7 +63487,7 @@
         <v>0</v>
       </c>
       <c r="O1072" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="P1072" s="1">
         <v>0</v>
@@ -63522,7 +63522,7 @@
         <v>2</v>
       </c>
       <c r="J1073" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K1073" s="1">
         <v>100</v>
@@ -63537,7 +63537,7 @@
         <v>0</v>
       </c>
       <c r="O1073" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P1073" s="1">
         <v>0</v>
@@ -63572,7 +63572,7 @@
         <v>3</v>
       </c>
       <c r="J1074" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="K1074" s="1">
         <v>100</v>
@@ -63587,7 +63587,7 @@
         <v>1</v>
       </c>
       <c r="O1074" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="P1074" s="1">
         <v>0</v>
@@ -63622,7 +63622,7 @@
         <v>3</v>
       </c>
       <c r="J1075" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="K1075" s="1">
         <v>100</v>
@@ -63637,7 +63637,7 @@
         <v>1</v>
       </c>
       <c r="O1075" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="P1075" s="1">
         <v>0</v>
@@ -63672,7 +63672,7 @@
         <v>3</v>
       </c>
       <c r="J1076" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K1076" s="1">
         <v>100</v>
@@ -63687,7 +63687,7 @@
         <v>1</v>
       </c>
       <c r="O1076" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P1076" s="1">
         <v>0</v>
@@ -63722,7 +63722,7 @@
         <v>3</v>
       </c>
       <c r="J1077" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K1077" s="1">
         <v>100</v>
@@ -63737,7 +63737,7 @@
         <v>1</v>
       </c>
       <c r="O1077" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="P1077" s="1">
         <v>0</v>
@@ -63772,7 +63772,7 @@
         <v>4</v>
       </c>
       <c r="J1078" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K1078" s="1">
         <v>100</v>
@@ -63787,7 +63787,7 @@
         <v>1</v>
       </c>
       <c r="O1078" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="P1078" s="1">
         <v>0</v>
@@ -63822,7 +63822,7 @@
         <v>4</v>
       </c>
       <c r="J1079" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K1079" s="1">
         <v>100</v>
@@ -63837,7 +63837,7 @@
         <v>1</v>
       </c>
       <c r="O1079" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="P1079" s="1">
         <v>0</v>
@@ -63872,7 +63872,7 @@
         <v>4</v>
       </c>
       <c r="J1080" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K1080" s="1">
         <v>100</v>
@@ -63887,7 +63887,7 @@
         <v>1</v>
       </c>
       <c r="O1080" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="P1080" s="1">
         <v>0</v>
@@ -63922,7 +63922,7 @@
         <v>4</v>
       </c>
       <c r="J1081" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K1081" s="1">
         <v>100</v>
@@ -63937,7 +63937,7 @@
         <v>1</v>
       </c>
       <c r="O1081" s="1" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="P1081" s="1">
         <v>0</v>
@@ -63975,7 +63975,7 @@
         <v>1</v>
       </c>
       <c r="J1082" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="K1082" s="1">
         <v>200</v>
@@ -63990,7 +63990,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -64028,7 +64028,7 @@
         <v>1</v>
       </c>
       <c r="J1083" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K1083" s="1">
         <v>40</v>
@@ -64043,7 +64043,7 @@
         <v>0</v>
       </c>
       <c r="O1083" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="P1083" s="1">
         <v>0</v>
@@ -64081,7 +64081,7 @@
         <v>1</v>
       </c>
       <c r="J1084" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K1084" s="1">
         <v>40</v>
@@ -64096,7 +64096,7 @@
         <v>0</v>
       </c>
       <c r="O1084" s="1" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P1084" s="1">
         <v>0</v>
@@ -64134,7 +64134,7 @@
         <v>2</v>
       </c>
       <c r="J1085" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K1085" s="1">
         <v>40</v>
@@ -64149,7 +64149,7 @@
         <v>0</v>
       </c>
       <c r="O1085" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P1085" s="1">
         <v>0</v>
@@ -64187,7 +64187,7 @@
         <v>2</v>
       </c>
       <c r="J1086" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K1086" s="1">
         <v>40</v>
@@ -64202,7 +64202,7 @@
         <v>0</v>
       </c>
       <c r="O1086" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="P1086" s="1">
         <v>0</v>
@@ -64240,7 +64240,7 @@
         <v>2</v>
       </c>
       <c r="J1087" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="K1087" s="1">
         <v>40</v>
@@ -64255,7 +64255,7 @@
         <v>0</v>
       </c>
       <c r="O1087" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="P1087" s="1">
         <v>0</v>
@@ -64293,7 +64293,7 @@
         <v>3</v>
       </c>
       <c r="J1088" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K1088" s="1">
         <v>40</v>
@@ -64308,7 +64308,7 @@
         <v>0</v>
       </c>
       <c r="O1088" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="P1088" s="1">
         <v>0</v>
@@ -64346,7 +64346,7 @@
         <v>3</v>
       </c>
       <c r="J1089" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K1089" s="1">
         <v>40</v>
@@ -64361,7 +64361,7 @@
         <v>0</v>
       </c>
       <c r="O1089" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="P1089" s="1">
         <v>0</v>
@@ -64399,7 +64399,7 @@
         <v>3</v>
       </c>
       <c r="J1090" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K1090" s="1">
         <v>40</v>
@@ -64414,7 +64414,7 @@
         <v>0</v>
       </c>
       <c r="O1090" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P1090" s="1">
         <v>0</v>
@@ -64452,7 +64452,7 @@
         <v>3</v>
       </c>
       <c r="J1091" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="K1091" s="1">
         <v>40</v>
@@ -64467,7 +64467,7 @@
         <v>0</v>
       </c>
       <c r="O1091" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P1091" s="1">
         <v>0</v>
@@ -64505,7 +64505,7 @@
         <v>4</v>
       </c>
       <c r="J1092" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="K1092" s="1">
         <v>40</v>
@@ -64520,7 +64520,7 @@
         <v>0</v>
       </c>
       <c r="O1092" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="P1092" s="1">
         <v>0</v>
@@ -64558,7 +64558,7 @@
         <v>4</v>
       </c>
       <c r="J1093" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K1093" s="1">
         <v>40</v>
@@ -64573,7 +64573,7 @@
         <v>0</v>
       </c>
       <c r="O1093" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="P1093" s="1">
         <v>0</v>
@@ -64611,7 +64611,7 @@
         <v>4</v>
       </c>
       <c r="J1094" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="K1094" s="1">
         <v>40</v>
@@ -64626,7 +64626,7 @@
         <v>0</v>
       </c>
       <c r="O1094" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="P1094" s="1">
         <v>0</v>
@@ -64664,7 +64664,7 @@
         <v>4</v>
       </c>
       <c r="J1095" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K1095" s="1">
         <v>40</v>
@@ -64679,7 +64679,7 @@
         <v>0</v>
       </c>
       <c r="O1095" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="P1095" s="1">
         <v>0</v>
@@ -64717,7 +64717,7 @@
         <v>4</v>
       </c>
       <c r="J1096" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="K1096" s="1">
         <v>40</v>
@@ -64732,7 +64732,7 @@
         <v>0</v>
       </c>
       <c r="O1096" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="P1096" s="1">
         <v>0</v>
@@ -64770,7 +64770,7 @@
         <v>5</v>
       </c>
       <c r="J1097" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K1097" s="1">
         <v>40</v>
@@ -64785,7 +64785,7 @@
         <v>0</v>
       </c>
       <c r="O1097" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="P1097" s="1">
         <v>0</v>
@@ -64823,7 +64823,7 @@
         <v>5</v>
       </c>
       <c r="J1098" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K1098" s="1">
         <v>40</v>
@@ -64838,7 +64838,7 @@
         <v>0</v>
       </c>
       <c r="O1098" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P1098" s="1">
         <v>0</v>
@@ -64876,7 +64876,7 @@
         <v>5</v>
       </c>
       <c r="J1099" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="K1099" s="1">
         <v>40</v>
@@ -64891,7 +64891,7 @@
         <v>0</v>
       </c>
       <c r="O1099" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="P1099" s="1">
         <v>0</v>
@@ -64929,7 +64929,7 @@
         <v>5</v>
       </c>
       <c r="J1100" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K1100" s="1">
         <v>40</v>
@@ -64944,7 +64944,7 @@
         <v>0</v>
       </c>
       <c r="O1100" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="P1100" s="1">
         <v>0</v>
@@ -64982,7 +64982,7 @@
         <v>5</v>
       </c>
       <c r="J1101" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K1101" s="1">
         <v>40</v>
@@ -64997,7 +64997,7 @@
         <v>0</v>
       </c>
       <c r="O1101" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="P1101" s="1">
         <v>0</v>
@@ -65035,7 +65035,7 @@
         <v>5</v>
       </c>
       <c r="J1102" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K1102" s="1">
         <v>40</v>
@@ -65050,7 +65050,7 @@
         <v>0</v>
       </c>
       <c r="O1102" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="P1102" s="1">
         <v>0</v>
@@ -65088,7 +65088,7 @@
         <v>6</v>
       </c>
       <c r="J1103" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K1103" s="1">
         <v>800</v>
@@ -65103,7 +65103,7 @@
         <v>0</v>
       </c>
       <c r="O1103" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="P1103" s="1">
         <v>0</v>
@@ -65141,7 +65141,7 @@
         <v>6</v>
       </c>
       <c r="J1104" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K1104" s="1">
         <v>160</v>
@@ -65156,7 +65156,7 @@
         <v>0</v>
       </c>
       <c r="O1104" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="P1104" s="1">
         <v>0</v>
@@ -65194,7 +65194,7 @@
         <v>6</v>
       </c>
       <c r="J1105" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K1105" s="1">
         <v>160</v>
@@ -65209,7 +65209,7 @@
         <v>0</v>
       </c>
       <c r="O1105" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="P1105" s="1">
         <v>0</v>
@@ -65247,7 +65247,7 @@
         <v>6</v>
       </c>
       <c r="J1106" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="K1106" s="1">
         <v>160</v>
@@ -65262,7 +65262,7 @@
         <v>0</v>
       </c>
       <c r="O1106" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="P1106" s="1">
         <v>0</v>
@@ -65300,7 +65300,7 @@
         <v>7</v>
       </c>
       <c r="J1107" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="K1107" s="1">
         <v>160</v>
@@ -65315,7 +65315,7 @@
         <v>0</v>
       </c>
       <c r="O1107" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="P1107" s="1">
         <v>0</v>
@@ -65353,7 +65353,7 @@
         <v>7</v>
       </c>
       <c r="J1108" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K1108" s="1">
         <v>160</v>
@@ -65368,7 +65368,7 @@
         <v>0</v>
       </c>
       <c r="O1108" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="P1108" s="1">
         <v>0</v>
@@ -65406,7 +65406,7 @@
         <v>7</v>
       </c>
       <c r="J1109" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="K1109" s="1">
         <v>160</v>
@@ -65421,7 +65421,7 @@
         <v>0</v>
       </c>
       <c r="O1109" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="P1109" s="1">
         <v>0</v>
@@ -65459,7 +65459,7 @@
         <v>7</v>
       </c>
       <c r="J1110" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="K1110" s="1">
         <v>160</v>
@@ -65474,7 +65474,7 @@
         <v>0</v>
       </c>
       <c r="O1110" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="P1110" s="1">
         <v>0</v>
@@ -65512,7 +65512,7 @@
         <v>8</v>
       </c>
       <c r="J1111" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="K1111" s="1">
         <v>160</v>
@@ -65527,7 +65527,7 @@
         <v>0</v>
       </c>
       <c r="O1111" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="P1111" s="1">
         <v>0</v>
@@ -65565,7 +65565,7 @@
         <v>8</v>
       </c>
       <c r="J1112" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K1112" s="1">
         <v>160</v>
@@ -65580,7 +65580,7 @@
         <v>0</v>
       </c>
       <c r="O1112" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="P1112" s="1">
         <v>0</v>
@@ -65618,7 +65618,7 @@
         <v>8</v>
       </c>
       <c r="J1113" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="K1113" s="1">
         <v>160</v>
@@ -65633,7 +65633,7 @@
         <v>0</v>
       </c>
       <c r="O1113" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P1113" s="1">
         <v>0</v>
@@ -65671,7 +65671,7 @@
         <v>8</v>
       </c>
       <c r="J1114" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K1114" s="1">
         <v>160</v>
@@ -65686,7 +65686,7 @@
         <v>0</v>
       </c>
       <c r="O1114" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="P1114" s="1">
         <v>0</v>
@@ -65724,7 +65724,7 @@
         <v>8</v>
       </c>
       <c r="J1115" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="K1115" s="1">
         <v>160</v>
@@ -65739,7 +65739,7 @@
         <v>0</v>
       </c>
       <c r="O1115" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="P1115" s="1">
         <v>0</v>
@@ -65777,7 +65777,7 @@
         <v>9</v>
       </c>
       <c r="J1116" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="K1116" s="1">
         <v>160</v>
@@ -65792,7 +65792,7 @@
         <v>0</v>
       </c>
       <c r="O1116" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="P1116" s="1">
         <v>0</v>
@@ -65830,7 +65830,7 @@
         <v>9</v>
       </c>
       <c r="J1117" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="K1117" s="1">
         <v>160</v>
@@ -65845,7 +65845,7 @@
         <v>0</v>
       </c>
       <c r="O1117" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="P1117" s="1">
         <v>0</v>
@@ -65883,7 +65883,7 @@
         <v>9</v>
       </c>
       <c r="J1118" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="K1118" s="1">
         <v>160</v>
@@ -65898,7 +65898,7 @@
         <v>0</v>
       </c>
       <c r="O1118" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="P1118" s="1">
         <v>0</v>
@@ -65936,7 +65936,7 @@
         <v>9</v>
       </c>
       <c r="J1119" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K1119" s="1">
         <v>160</v>
@@ -65951,7 +65951,7 @@
         <v>0</v>
       </c>
       <c r="O1119" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="P1119" s="1">
         <v>0</v>
@@ -65989,7 +65989,7 @@
         <v>9</v>
       </c>
       <c r="J1120" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="K1120" s="1">
         <v>160</v>
@@ -66004,7 +66004,7 @@
         <v>0</v>
       </c>
       <c r="O1120" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="P1120" s="1">
         <v>0</v>
@@ -66042,7 +66042,7 @@
         <v>10</v>
       </c>
       <c r="J1121" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="K1121" s="1">
         <v>160</v>
@@ -66095,7 +66095,7 @@
         <v>10</v>
       </c>
       <c r="J1122" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="K1122" s="1">
         <v>160</v>
@@ -66110,7 +66110,7 @@
         <v>0</v>
       </c>
       <c r="O1122" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P1122" s="1">
         <v>0</v>
@@ -66148,7 +66148,7 @@
         <v>10</v>
       </c>
       <c r="J1123" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K1123" s="1">
         <v>160</v>
@@ -66163,7 +66163,7 @@
         <v>0</v>
       </c>
       <c r="O1123" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="P1123" s="1">
         <v>0</v>
@@ -66201,7 +66201,7 @@
         <v>10</v>
       </c>
       <c r="J1124" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="K1124" s="1">
         <v>160</v>
@@ -66216,7 +66216,7 @@
         <v>0</v>
       </c>
       <c r="O1124" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P1124" s="1">
         <v>0</v>
@@ -66254,7 +66254,7 @@
         <v>10</v>
       </c>
       <c r="J1125" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="K1125" s="1">
         <v>160</v>
@@ -66269,7 +66269,7 @@
         <v>0</v>
       </c>
       <c r="O1125" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="P1125" s="1">
         <v>0</v>
@@ -66307,7 +66307,7 @@
         <v>10</v>
       </c>
       <c r="J1126" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="K1126" s="1">
         <v>160</v>
@@ -66322,7 +66322,7 @@
         <v>0</v>
       </c>
       <c r="O1126" s="1" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="P1126" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1EBB5A-AE81-442C-8772-8004CEF492E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0155EC-DC0B-4359-A504-BB7565B2EC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_brush_foe_v8" sheetId="2" r:id="rId1"/>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2299" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="1066">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2703,6 +2703,645 @@
   <si>
     <t>10,90,10,95,10,85</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>55,22</t>
+  </si>
+  <si>
+    <t>55,22,73,22</t>
+  </si>
+  <si>
+    <t>45,2</t>
+  </si>
+  <si>
+    <t>65,65</t>
+  </si>
+  <si>
+    <t>60,70,50,90</t>
+  </si>
+  <si>
+    <t>60,70,65,75</t>
+  </si>
+  <si>
+    <t>55,95</t>
+  </si>
+  <si>
+    <t>55,35,60,35</t>
+  </si>
+  <si>
+    <t>55,35,50,15</t>
+  </si>
+  <si>
+    <t>46,66,46,51</t>
+  </si>
+  <si>
+    <t>60,35,60,15</t>
+  </si>
+  <si>
+    <t>55,65,60,65</t>
+  </si>
+  <si>
+    <t>55,65,80,85,90,85</t>
+  </si>
+  <si>
+    <t>55,65,60,65,65,65</t>
+  </si>
+  <si>
+    <t>55,70,60,70,65,70</t>
+  </si>
+  <si>
+    <t>55,35,60,35,50,15</t>
+  </si>
+  <si>
+    <t>55,35,60,35,60,15</t>
+  </si>
+  <si>
+    <t>55,30,60,30,55,15</t>
+  </si>
+  <si>
+    <t>55,30,60,30,65,30</t>
+  </si>
+  <si>
+    <t>55,65,60,65,80,85,90,85</t>
+  </si>
+  <si>
+    <t>55,70,60,70,85,85,95,85</t>
+  </si>
+  <si>
+    <t>55,70,60,70,65,30</t>
+  </si>
+  <si>
+    <t>55,35,60,35,50,35,65,35</t>
+  </si>
+  <si>
+    <t>55,35,60,35,50,15,45,15</t>
+  </si>
+  <si>
+    <t>55,35,60,35,65,35</t>
+  </si>
+  <si>
+    <t>55,30,60,30,60,15,55,15</t>
+  </si>
+  <si>
+    <t>55,30,60,30,65,30,55,30</t>
+  </si>
+  <si>
+    <t>60,70,55,70,65,70</t>
+  </si>
+  <si>
+    <t>55,70,60,70,80,85,90,85</t>
+  </si>
+  <si>
+    <t>55,75,60,75,65,75,50,75</t>
+  </si>
+  <si>
+    <t>55,35,60,35,50,35,65,35,70,35</t>
+  </si>
+  <si>
+    <t>55,35,60,35,50,35,50,15,45,15</t>
+  </si>
+  <si>
+    <t>55,35,60,35,65,35,50,35</t>
+  </si>
+  <si>
+    <t>55,30,60,30,65,30,55,15,55,10</t>
+  </si>
+  <si>
+    <t>55,30,60,30,65,30,50,30</t>
+  </si>
+  <si>
+    <t>55,25,60,25,65,25,50,25</t>
+  </si>
+  <si>
+    <t>55,65,60,65,50,65,65,65,70,65</t>
+  </si>
+  <si>
+    <t>55,65,60,65,50,65,80,85,90,85</t>
+  </si>
+  <si>
+    <t>55,65,60,65,65,65,50,65</t>
+  </si>
+  <si>
+    <t>55,70,60,70,60,70,80,85,90,85</t>
+  </si>
+  <si>
+    <t>55,70,60,70,65,70,50,70,70,70</t>
+  </si>
+  <si>
+    <t>55,75,60,75,65,75,50,75,70,75</t>
+  </si>
+  <si>
+    <t>55,35,60,35,65,35,50,35,70,35</t>
+  </si>
+  <si>
+    <t>55,30,60,30,65,30,50,30,70,30</t>
+  </si>
+  <si>
+    <t>55,25,60,25,65,25,50,10,45,10</t>
+  </si>
+  <si>
+    <t>55,20,60,20,50,20,65,20,70,20</t>
+  </si>
+  <si>
+    <t>55,65,60,65,50,65,62,60,57,60,52,60</t>
+  </si>
+  <si>
+    <t>55,65,60,65,65,65,80,85,90,85</t>
+  </si>
+  <si>
+    <t>55,70,60,70,65,70,50,65,60,65,55,65</t>
+  </si>
+  <si>
+    <t>55,70,60,70,65,70,85,85,95,85</t>
+  </si>
+  <si>
+    <t>55,75,60,75,65,75,50,80,55,80,60,80</t>
+  </si>
+  <si>
+    <t>55,70,60,70,65,70,80,90,85,95</t>
+  </si>
+  <si>
+    <t>55,35,60,35,50,35,65,35,70,30,45,30</t>
+  </si>
+  <si>
+    <t>55,35,60,35,65,35,50,35,70,30,45,30</t>
+  </si>
+  <si>
+    <t>55,30,60,30,65,30,50,30,70,30,45,30</t>
+  </si>
+  <si>
+    <t>55,20,60,20,50,20,65,20,70,20,45,20</t>
+  </si>
+  <si>
+    <t>55,65,60,65,65,65,50,65,80,85,90,85</t>
+  </si>
+  <si>
+    <t>55,80,60,80,65,80,50,85,55,85,60,85</t>
+  </si>
+  <si>
+    <t>55,35,60,35,50,35,65,35,50,15,45,15</t>
+  </si>
+  <si>
+    <t>55,30,60,30,65,30,50,30,55,15,55,10</t>
+  </si>
+  <si>
+    <t>55,25,60,25,65,25,50,10,50,10,45,10</t>
+  </si>
+  <si>
+    <t>55,70,60,70,65,70,50,70,85,85,95,85</t>
+  </si>
+  <si>
+    <t>55,70,60,70,65,70,50,70,80,90,85,95</t>
+  </si>
+  <si>
+    <t>113101</t>
+  </si>
+  <si>
+    <t>113101,113104</t>
+  </si>
+  <si>
+    <t>113101,113101</t>
+  </si>
+  <si>
+    <t>113104</t>
+  </si>
+  <si>
+    <t>113105,113104,113104</t>
+  </si>
+  <si>
+    <t>113101,113101,113101</t>
+  </si>
+  <si>
+    <t>113105,113101,113101</t>
+  </si>
+  <si>
+    <t>113105,113105,113104</t>
+  </si>
+  <si>
+    <t>113101,113101,113104</t>
+  </si>
+  <si>
+    <t>113105,113105,113105</t>
+  </si>
+  <si>
+    <t>113105,113105,113104,113104</t>
+  </si>
+  <si>
+    <t>113105,113105,113101,113101</t>
+  </si>
+  <si>
+    <t>113101,113101,113101,113101</t>
+  </si>
+  <si>
+    <t>113101,113101,113104,113104</t>
+  </si>
+  <si>
+    <t>113102,113101,113101</t>
+  </si>
+  <si>
+    <t>113105,113105,113105,113105</t>
+  </si>
+  <si>
+    <t>113105,113105,113105,113101,113101</t>
+  </si>
+  <si>
+    <t>113105,113105,113105,113104,113104</t>
+  </si>
+  <si>
+    <t>113102,113101,113101,113101</t>
+  </si>
+  <si>
+    <t>113101,113101,113101,113104,113104</t>
+  </si>
+  <si>
+    <t>113105,113105,113105,113105,113105</t>
+  </si>
+  <si>
+    <t>113102,113101,113101,113104,113104</t>
+  </si>
+  <si>
+    <t>113102,113105,113105,113104,113104</t>
+  </si>
+  <si>
+    <t>113105,113105,113105,113105,113105,113105</t>
+  </si>
+  <si>
+    <t>113102,113105,113105,113105,113105,113105</t>
+  </si>
+  <si>
+    <t>113102,113105,113105,113105,113104,113104</t>
+  </si>
+  <si>
+    <t>113102,113102,113105,113105,113105,113105</t>
+  </si>
+  <si>
+    <t>1130101</t>
+  </si>
+  <si>
+    <t>1130102</t>
+  </si>
+  <si>
+    <t>1130103</t>
+  </si>
+  <si>
+    <t>1130201</t>
+  </si>
+  <si>
+    <t>1130202</t>
+  </si>
+  <si>
+    <t>1130203</t>
+  </si>
+  <si>
+    <t>1130204</t>
+  </si>
+  <si>
+    <t>1130301</t>
+  </si>
+  <si>
+    <t>1130302</t>
+  </si>
+  <si>
+    <t>1130303</t>
+  </si>
+  <si>
+    <t>1130304</t>
+  </si>
+  <si>
+    <t>1130401</t>
+  </si>
+  <si>
+    <t>1130402</t>
+  </si>
+  <si>
+    <t>1130403</t>
+  </si>
+  <si>
+    <t>1130404</t>
+  </si>
+  <si>
+    <t>1130501</t>
+  </si>
+  <si>
+    <t>1130502</t>
+  </si>
+  <si>
+    <t>1130503</t>
+  </si>
+  <si>
+    <t>1130504</t>
+  </si>
+  <si>
+    <t>1130505</t>
+  </si>
+  <si>
+    <t>1130601</t>
+  </si>
+  <si>
+    <t>1130602</t>
+  </si>
+  <si>
+    <t>1130603</t>
+  </si>
+  <si>
+    <t>1130604</t>
+  </si>
+  <si>
+    <t>1130605</t>
+  </si>
+  <si>
+    <t>1130701</t>
+  </si>
+  <si>
+    <t>1130702</t>
+  </si>
+  <si>
+    <t>1130703</t>
+  </si>
+  <si>
+    <t>1130704</t>
+  </si>
+  <si>
+    <t>1130705</t>
+  </si>
+  <si>
+    <t>1130801</t>
+  </si>
+  <si>
+    <t>1130802</t>
+  </si>
+  <si>
+    <t>1130803</t>
+  </si>
+  <si>
+    <t>1130804</t>
+  </si>
+  <si>
+    <t>1130805</t>
+  </si>
+  <si>
+    <t>1130806</t>
+  </si>
+  <si>
+    <t>1130901</t>
+  </si>
+  <si>
+    <t>1130902</t>
+  </si>
+  <si>
+    <t>1130903</t>
+  </si>
+  <si>
+    <t>1130904</t>
+  </si>
+  <si>
+    <t>1130905</t>
+  </si>
+  <si>
+    <t>1130906</t>
+  </si>
+  <si>
+    <t>1131001</t>
+  </si>
+  <si>
+    <t>1131002</t>
+  </si>
+  <si>
+    <t>1131003</t>
+  </si>
+  <si>
+    <t>1131004</t>
+  </si>
+  <si>
+    <t>1131005</t>
+  </si>
+  <si>
+    <t>1131006</t>
+  </si>
+  <si>
+    <t>1131101</t>
+  </si>
+  <si>
+    <t>1131102</t>
+  </si>
+  <si>
+    <t>1131103</t>
+  </si>
+  <si>
+    <t>1131104</t>
+  </si>
+  <si>
+    <t>1131105</t>
+  </si>
+  <si>
+    <t>1131106</t>
+  </si>
+  <si>
+    <t>1131107</t>
+  </si>
+  <si>
+    <t>1131201</t>
+  </si>
+  <si>
+    <t>1131202</t>
+  </si>
+  <si>
+    <t>1131203</t>
+  </si>
+  <si>
+    <t>1131204</t>
+  </si>
+  <si>
+    <t>1131205</t>
+  </si>
+  <si>
+    <t>1131206</t>
+  </si>
+  <si>
+    <t>1131207</t>
+  </si>
+  <si>
+    <t>1131301</t>
+  </si>
+  <si>
+    <t>1131302</t>
+  </si>
+  <si>
+    <t>1131303</t>
+  </si>
+  <si>
+    <t>1131304</t>
+  </si>
+  <si>
+    <t>1131305</t>
+  </si>
+  <si>
+    <t>1131306</t>
+  </si>
+  <si>
+    <t>1131307</t>
+  </si>
+  <si>
+    <t>1131401</t>
+  </si>
+  <si>
+    <t>1131402</t>
+  </si>
+  <si>
+    <t>1131403</t>
+  </si>
+  <si>
+    <t>1131404</t>
+  </si>
+  <si>
+    <t>1131405</t>
+  </si>
+  <si>
+    <t>1131406</t>
+  </si>
+  <si>
+    <t>1131407</t>
+  </si>
+  <si>
+    <t>1131501</t>
+  </si>
+  <si>
+    <t>1131502</t>
+  </si>
+  <si>
+    <t>1131503</t>
+  </si>
+  <si>
+    <t>1131504</t>
+  </si>
+  <si>
+    <t>1131505</t>
+  </si>
+  <si>
+    <t>1131506</t>
+  </si>
+  <si>
+    <t>1131507</t>
+  </si>
+  <si>
+    <t>1131601</t>
+  </si>
+  <si>
+    <t>1131602</t>
+  </si>
+  <si>
+    <t>1131603</t>
+  </si>
+  <si>
+    <t>1131604</t>
+  </si>
+  <si>
+    <t>1131605</t>
+  </si>
+  <si>
+    <t>1131606</t>
+  </si>
+  <si>
+    <t>1131607</t>
+  </si>
+  <si>
+    <t>1131608</t>
+  </si>
+  <si>
+    <t>1131701</t>
+  </si>
+  <si>
+    <t>1131702</t>
+  </si>
+  <si>
+    <t>1131703</t>
+  </si>
+  <si>
+    <t>1131704</t>
+  </si>
+  <si>
+    <t>1131705</t>
+  </si>
+  <si>
+    <t>1131706</t>
+  </si>
+  <si>
+    <t>1131707</t>
+  </si>
+  <si>
+    <t>1131708</t>
+  </si>
+  <si>
+    <t>1131801</t>
+  </si>
+  <si>
+    <t>1131802</t>
+  </si>
+  <si>
+    <t>1131803</t>
+  </si>
+  <si>
+    <t>1131804</t>
+  </si>
+  <si>
+    <t>1131805</t>
+  </si>
+  <si>
+    <t>1131806</t>
+  </si>
+  <si>
+    <t>1131807</t>
+  </si>
+  <si>
+    <t>1131808</t>
+  </si>
+  <si>
+    <t>1131901</t>
+  </si>
+  <si>
+    <t>1131902</t>
+  </si>
+  <si>
+    <t>1131903</t>
+  </si>
+  <si>
+    <t>1131904</t>
+  </si>
+  <si>
+    <t>1131905</t>
+  </si>
+  <si>
+    <t>1131906</t>
+  </si>
+  <si>
+    <t>1131907</t>
+  </si>
+  <si>
+    <t>1131908</t>
+  </si>
+  <si>
+    <t>1132001</t>
+  </si>
+  <si>
+    <t>1132002</t>
+  </si>
+  <si>
+    <t>1132003</t>
+  </si>
+  <si>
+    <t>1132004</t>
+  </si>
+  <si>
+    <t>1132005</t>
+  </si>
+  <si>
+    <t>1132006</t>
+  </si>
+  <si>
+    <t>1132007</t>
+  </si>
+  <si>
+    <t>1132008</t>
   </si>
 </sst>
 </file>
@@ -3518,7 +4157,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1126"/>
+  <dimension ref="A1:R1249"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -66334,6 +66973,6525 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1127" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1127" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="B1127" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1127" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1127" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1127" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1127" s="1">
+        <v>1</v>
+      </c>
+      <c r="H1127" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1127" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1127" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="K1127" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1127" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1127" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1127" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1127" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="P1127" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1127" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1128" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="B1128" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1128" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1128" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1128" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1128" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1128" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1128" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1128" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="K1128" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1128" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1128" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1128" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1128" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="P1128" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1128" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1129" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="B1129" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1129" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1129" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1129" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1129" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1129" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1129" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1129" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="K1129" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1129" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1129" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1129" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1129" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="P1129" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1129" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1129" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1130" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="B1130" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1130" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1130" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1130" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1130" s="1">
+        <v>4</v>
+      </c>
+      <c r="H1130" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1130" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1130" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="K1130" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1130" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1130" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1130" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1130" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="P1130" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1130" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1131" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B1131" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1131" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1131" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1131" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1131" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1131" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1131" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1131" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="K1131" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1131" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1131" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1131" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1131" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="P1131" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1131" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1132" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="B1132" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1132" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1132" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1132" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1132" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1132" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1132" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1132" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1132" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1132" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1132" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1132" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1132" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="P1132" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1132" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1132" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1133" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B1133" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1133" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1133" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1133" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1133" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1133" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1133" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1133" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1133" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1133" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1133" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1133" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1133" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="P1133" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1133" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1134" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="B1134" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1134" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1134" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1134" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1134" s="1">
+        <v>8</v>
+      </c>
+      <c r="H1134" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1134" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1134" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1134" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1134" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1134" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1134" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1134" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="P1134" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1134" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1135" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="B1135" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1135" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1135" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1135" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1135" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1135" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1135" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1135" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="K1135" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1135" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1135" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1135" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1135" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="P1135" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1135" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1136" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="B1136" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1136" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1136" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1136" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1136" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1136" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1136" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1136" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1136" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1136" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1136" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1136" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1136" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="P1136" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1136" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1136" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1137" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="B1137" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1137" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1137" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1137" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1137" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1137" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1137" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1137" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="K1137" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1137" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1137" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1137" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1137" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="P1137" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1137" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1138" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="B1138" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1138" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1138" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1138" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1138" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1138" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1138" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1138" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1138" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1138" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1138" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1138" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1138" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="P1138" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1138" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1139" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B1139" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1139" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1139" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1139" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1139" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1139" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1139" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1139" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="K1139" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1139" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1139" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1139" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1139" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="P1139" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1139" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1140" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="B1140" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1140" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1140" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1140" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1140" s="1">
+        <v>14</v>
+      </c>
+      <c r="H1140" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1140" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1140" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="K1140" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1140" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1140" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1140" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1140" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="P1140" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1140" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1141" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="B1141" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1141" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1141" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1141" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1141" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1141" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1141" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1141" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="K1141" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1141" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1141" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1141" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1141" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="P1141" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1141" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1142" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B1142" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1142" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1142" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1142" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1142" s="1">
+        <v>16</v>
+      </c>
+      <c r="H1142" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1142" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1142" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1142" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1142" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1142" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1142" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1142" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="P1142" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1142" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1143" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B1143" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1143" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1143" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1143" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1143" s="1">
+        <v>17</v>
+      </c>
+      <c r="H1143" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1143" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1143" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="K1143" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1143" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1143" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1143" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1143" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="P1143" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1143" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1144" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B1144" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1144" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1144" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1144" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1144" s="1">
+        <v>18</v>
+      </c>
+      <c r="H1144" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1144" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1144" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="K1144" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1144" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1144" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1144" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1144" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="P1144" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1144" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1145" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B1145" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1145" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1145" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1145" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1145" s="1">
+        <v>19</v>
+      </c>
+      <c r="H1145" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1145" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1145" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="K1145" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1145" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1145" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1145" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1145" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="P1145" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1145" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1146" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B1146" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1146" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1146" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1146" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1146" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1146" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1146" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1146" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="K1146" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1146" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1146" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1146" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1146" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="P1146" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1146" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1146" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1147" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="B1147" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1147" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1147" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1147" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1147" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1147" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1147" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1147" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="K1147" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1147" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1147" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1147" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1147" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="P1147" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1147" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1148" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="B1148" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1148" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1148" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1148" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1148" s="1">
+        <v>22</v>
+      </c>
+      <c r="H1148" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1148" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1148" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="K1148" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1148" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1148" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1148" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1148" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="P1148" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1148" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1149" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="B1149" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1149" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1149" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1149" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1149" s="1">
+        <v>23</v>
+      </c>
+      <c r="H1149" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1149" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1149" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="K1149" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1149" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1149" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1149" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1149" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="P1149" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1149" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1150" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="B1150" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1150" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1150" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1150" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1150" s="1">
+        <v>24</v>
+      </c>
+      <c r="H1150" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1150" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1150" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="K1150" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1150" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1150" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1150" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1150" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="P1150" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1150" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1150" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1151" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B1151" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1151" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1151" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1151" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1151" s="1">
+        <v>25</v>
+      </c>
+      <c r="H1151" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1151" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1151" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="K1151" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1151" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1151" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1151" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1151" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="P1151" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1151" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1152" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B1152" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1152" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1152" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1152" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1152" s="1">
+        <v>26</v>
+      </c>
+      <c r="H1152" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1152" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1152" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="K1152" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1152" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1152" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1152" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1152" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="P1152" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1152" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1153" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="B1153" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1153" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1153" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1153" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1153" s="1">
+        <v>27</v>
+      </c>
+      <c r="H1153" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1153" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1153" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="K1153" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1153" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1153" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1153" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1153" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="P1153" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1153" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1154" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B1154" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1154" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1154" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1154" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1154" s="1">
+        <v>28</v>
+      </c>
+      <c r="H1154" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1154" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1154" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="K1154" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1154" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1154" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1154" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1154" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="P1154" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1154" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1154" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1155" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="B1155" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1155" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1155" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1155" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1155" s="1">
+        <v>29</v>
+      </c>
+      <c r="H1155" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1155" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1155" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="K1155" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1155" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1155" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1155" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1155" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="P1155" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1155" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1155" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1156" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B1156" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1156" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1156" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1156" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1156" s="1">
+        <v>30</v>
+      </c>
+      <c r="H1156" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1156" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1156" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="K1156" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1156" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1156" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1156" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1156" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="P1156" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1156" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1157" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B1157" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1157" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1157" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1157" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1157" s="1">
+        <v>31</v>
+      </c>
+      <c r="H1157" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1157" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1157" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="K1157" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1157" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1157" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1157" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1157" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="P1157" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1157" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1158" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B1158" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1158" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1158" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1158" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1158" s="1">
+        <v>32</v>
+      </c>
+      <c r="H1158" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1158" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1158" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="K1158" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1158" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1158" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1158" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1158" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="P1158" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1158" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1159" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="B1159" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1159" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1159" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1159" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1159" s="1">
+        <v>33</v>
+      </c>
+      <c r="H1159" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1159" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1159" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="K1159" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1159" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1159" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1159" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1159" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="P1159" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1159" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1160" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B1160" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1160" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1160" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1160" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1160" s="1">
+        <v>34</v>
+      </c>
+      <c r="H1160" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1160" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1160" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="K1160" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1160" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1160" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1160" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1160" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="P1160" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1160" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1161" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B1161" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1161" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1161" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1161" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1161" s="1">
+        <v>35</v>
+      </c>
+      <c r="H1161" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1161" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1161" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="K1161" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1161" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1161" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1161" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1161" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="P1161" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1161" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1162" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B1162" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1162" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1162" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1162" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1162" s="1">
+        <v>36</v>
+      </c>
+      <c r="H1162" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1162" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1162" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="K1162" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1162" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1162" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1162" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1162" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="P1162" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1162" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1162" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1163" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B1163" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1163" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1163" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1163" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1163" s="1">
+        <v>37</v>
+      </c>
+      <c r="H1163" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1163" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1163" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="K1163" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1163" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1163" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1163" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1163" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="P1163" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1163" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1164" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B1164" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1164" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1164" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1164" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1164" s="1">
+        <v>38</v>
+      </c>
+      <c r="H1164" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1164" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1164" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="K1164" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1164" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1164" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1164" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1164" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="P1164" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1164" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1164" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1165" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B1165" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1165" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1165" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1165" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1165" s="1">
+        <v>39</v>
+      </c>
+      <c r="H1165" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1165" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1165" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="K1165" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1165" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1165" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1165" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1165" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="P1165" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1165" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1166" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B1166" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1166" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1166" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1166" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1166" s="1">
+        <v>40</v>
+      </c>
+      <c r="H1166" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1166" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1166" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="K1166" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1166" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1166" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1166" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1166" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="P1166" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1166" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1167" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B1167" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1167" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1167" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1167" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1167" s="1">
+        <v>41</v>
+      </c>
+      <c r="H1167" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1167" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1167" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="K1167" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1167" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1167" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1167" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1167" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="P1167" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1167" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1167" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1168" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="B1168" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1168" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1168" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1168" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1168" s="1">
+        <v>42</v>
+      </c>
+      <c r="H1168" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1168" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1168" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="K1168" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1168" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1168" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1168" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1168" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="P1168" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1168" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1168" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1169" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B1169" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1169" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1169" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1169" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1169" s="1">
+        <v>43</v>
+      </c>
+      <c r="H1169" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1169" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1169" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="K1169" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1169" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1169" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1169" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1169" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="P1169" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1169" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1169" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1170" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B1170" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1170" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1170" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1170" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1170" s="1">
+        <v>44</v>
+      </c>
+      <c r="H1170" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1170" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1170" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="K1170" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1170" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1170" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1170" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1170" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="P1170" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1170" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1170" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1171" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B1171" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1171" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1171" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1171" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1171" s="1">
+        <v>45</v>
+      </c>
+      <c r="H1171" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1171" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1171" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="K1171" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1171" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1171" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1171" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1171" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="P1171" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1171" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1171" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1172" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1172" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1172" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1172" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1172" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1172" s="1">
+        <v>46</v>
+      </c>
+      <c r="H1172" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1172" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1172" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="K1172" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1172" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1172" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1172" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1172" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="P1172" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1172" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1173" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B1173" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1173" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1173" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1173" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1173" s="1">
+        <v>47</v>
+      </c>
+      <c r="H1173" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1173" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1173" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="K1173" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1173" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1173" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1173" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1173" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="P1173" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1173" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1173" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1174" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="B1174" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1174" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1174" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1174" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1174" s="1">
+        <v>48</v>
+      </c>
+      <c r="H1174" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1174" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1174" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="K1174" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1174" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1174" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1174" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1174" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="P1174" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1174" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1174" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1175" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1175" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1175" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1175" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1175" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1175" s="1">
+        <v>49</v>
+      </c>
+      <c r="H1175" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1175" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1175" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="K1175" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1175" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1175" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1175" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1175" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="P1175" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1175" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1175" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1176" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B1176" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1176" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1176" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1176" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1176" s="1">
+        <v>50</v>
+      </c>
+      <c r="H1176" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1176" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1176" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1176" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1176" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1176" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1176" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1176" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="P1176" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1176" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1176" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1177" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="B1177" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1177" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1177" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1177" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1177" s="1">
+        <v>51</v>
+      </c>
+      <c r="H1177" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1177" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1177" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="K1177" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1177" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1177" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1177" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1177" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="P1177" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1177" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1177" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1178" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="B1178" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1178" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1178" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1178" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1178" s="1">
+        <v>52</v>
+      </c>
+      <c r="H1178" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1178" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1178" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1178" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1178" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1178" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1178" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1178" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="P1178" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1178" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1178" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1179" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B1179" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1179" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1179" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1179" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1179" s="1">
+        <v>53</v>
+      </c>
+      <c r="H1179" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1179" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1179" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="K1179" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1179" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1179" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1179" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1179" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="P1179" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1179" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1179" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1180" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="B1180" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1180" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1180" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1180" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1180" s="1">
+        <v>54</v>
+      </c>
+      <c r="H1180" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1180" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1180" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1180" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1180" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1180" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1180" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1180" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="P1180" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1180" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1180" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1181" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B1181" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1181" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1181" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1181" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1181" s="1">
+        <v>55</v>
+      </c>
+      <c r="H1181" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1181" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1181" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="K1181" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1181" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1181" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1181" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1181" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="P1181" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1181" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1181" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1182" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="B1182" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1182" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1182" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1182" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1182" s="1">
+        <v>56</v>
+      </c>
+      <c r="H1182" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1182" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1182" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1182" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1182" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1182" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1182" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1182" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="P1182" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1182" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1182" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1183" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="B1183" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1183" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1183" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1183" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1183" s="1">
+        <v>57</v>
+      </c>
+      <c r="H1183" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1183" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1183" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1183" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1183" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1183" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1183" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1183" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="P1183" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1183" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1183" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1184" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B1184" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1184" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1184" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1184" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1184" s="1">
+        <v>58</v>
+      </c>
+      <c r="H1184" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1184" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1184" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1184" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1184" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1184" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1184" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1184" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="P1184" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1184" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1184" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1185" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B1185" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1185" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1185" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1185" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1185" s="1">
+        <v>59</v>
+      </c>
+      <c r="H1185" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1185" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1185" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1185" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1185" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1185" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1185" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1185" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="P1185" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1185" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1185" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1186" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B1186" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1186" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1186" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1186" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1186" s="1">
+        <v>60</v>
+      </c>
+      <c r="H1186" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1186" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1186" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1186" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1186" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1186" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1186" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1186" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1186" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1186" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1186" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1187" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1187" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1187" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1187" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1187" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1187" s="1">
+        <v>61</v>
+      </c>
+      <c r="H1187" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1187" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1187" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1187" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1187" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1187" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1187" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1187" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="P1187" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1187" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1187" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1188" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B1188" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1188" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1188" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1188" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1188" s="1">
+        <v>62</v>
+      </c>
+      <c r="H1188" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1188" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1188" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1188" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1188" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1188" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1188" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1188" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1188" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1188" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1188" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1189" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1189" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1189" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1189" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1189" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1189" s="1">
+        <v>63</v>
+      </c>
+      <c r="H1189" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1189" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1189" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1189" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1189" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1189" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1189" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1189" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="P1189" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1189" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1189" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1190" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B1190" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1190" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1190" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1190" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1190" s="1">
+        <v>64</v>
+      </c>
+      <c r="H1190" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1190" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1190" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1190" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1190" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1190" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1190" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1190" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="P1190" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1190" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1190" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1191" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B1191" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1191" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1191" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1191" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1191" s="1">
+        <v>65</v>
+      </c>
+      <c r="H1191" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1191" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1191" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1191" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1191" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1191" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1191" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1191" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="P1191" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1191" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1191" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1192" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B1192" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1192" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1192" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1192" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1192" s="1">
+        <v>66</v>
+      </c>
+      <c r="H1192" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1192" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1192" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1192" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1192" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1192" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1192" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1192" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="P1192" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1192" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1192" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1193" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B1193" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1193" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1193" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1193" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1193" s="1">
+        <v>67</v>
+      </c>
+      <c r="H1193" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1193" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1193" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1193" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1193" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1193" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1193" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1193" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="P1193" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1193" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1193" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1194" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B1194" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1194" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1194" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1194" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1194" s="1">
+        <v>68</v>
+      </c>
+      <c r="H1194" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1194" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1194" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1194" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1194" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1194" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1194" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1194" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="P1194" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1194" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1194" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1195" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B1195" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1195" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1195" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1195" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1195" s="1">
+        <v>69</v>
+      </c>
+      <c r="H1195" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1195" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1195" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1195" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1195" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1195" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1195" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1195" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="P1195" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1195" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1195" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1196" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B1196" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1196" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1196" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1196" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1196" s="1">
+        <v>70</v>
+      </c>
+      <c r="H1196" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1196" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1196" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1196" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1196" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1196" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1196" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1196" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="P1196" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1196" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1196" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1197" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1197" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1197" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1197" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1197" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1197" s="1">
+        <v>71</v>
+      </c>
+      <c r="H1197" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1197" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1197" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1197" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1197" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1197" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1197" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1197" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="P1197" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1197" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1197" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1198" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B1198" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1198" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1198" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1198" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1198" s="1">
+        <v>72</v>
+      </c>
+      <c r="H1198" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1198" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1198" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1198" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1198" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1198" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1198" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1198" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="P1198" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1198" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1198" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1199" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B1199" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1199" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1199" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1199" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1199" s="1">
+        <v>73</v>
+      </c>
+      <c r="H1199" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1199" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1199" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1199" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1199" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1199" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1199" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1199" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="P1199" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1199" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1199" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1200" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B1200" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1200" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1200" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1200" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1200" s="1">
+        <v>74</v>
+      </c>
+      <c r="H1200" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1200" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1200" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1200" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1200" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1200" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1200" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1200" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1200" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1200" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1200" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1201" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B1201" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1201" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1201" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1201" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1201" s="1">
+        <v>75</v>
+      </c>
+      <c r="H1201" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1201" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1201" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1201" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1201" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1201" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1201" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1201" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="P1201" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1201" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1201" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1202" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B1202" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1202" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1202" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1202" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1202" s="1">
+        <v>76</v>
+      </c>
+      <c r="H1202" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1202" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1202" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1202" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1202" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1202" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1202" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1202" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1202" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1202" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1202" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1203" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B1203" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1203" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1203" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1203" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1203" s="1">
+        <v>77</v>
+      </c>
+      <c r="H1203" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1203" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1203" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="K1203" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1203" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1203" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1203" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1203" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="P1203" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1203" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1203" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1204" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B1204" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1204" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1204" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1204" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1204" s="1">
+        <v>78</v>
+      </c>
+      <c r="H1204" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1204" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1204" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1204" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1204" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1204" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1204" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1204" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="P1204" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1204" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1204" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1205" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B1205" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1205" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1205" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1205" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1205" s="1">
+        <v>79</v>
+      </c>
+      <c r="H1205" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1205" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1205" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1205" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1205" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1205" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1205" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1205" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="P1205" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1205" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1205" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1206" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B1206" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1206" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1206" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1206" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1206" s="1">
+        <v>80</v>
+      </c>
+      <c r="H1206" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1206" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1206" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1206" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1206" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1206" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1206" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1206" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="P1206" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1206" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1206" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1207" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B1207" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1207" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1207" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1207" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1207" s="1">
+        <v>81</v>
+      </c>
+      <c r="H1207" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1207" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1207" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1207" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1207" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1207" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1207" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1207" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="P1207" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1207" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1207" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1208" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B1208" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1208" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1208" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1208" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1208" s="1">
+        <v>82</v>
+      </c>
+      <c r="H1208" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1208" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1208" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1208" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1208" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1208" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1208" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1208" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="P1208" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1208" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1208" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1209" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B1209" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1209" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1209" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1209" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1209" s="1">
+        <v>83</v>
+      </c>
+      <c r="H1209" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1209" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1209" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1209" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1209" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1209" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1209" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1209" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="P1209" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1209" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1209" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1210" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B1210" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1210" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1210" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1210" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1210" s="1">
+        <v>84</v>
+      </c>
+      <c r="H1210" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1210" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1210" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1210" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1210" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1210" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1210" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1210" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="P1210" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1210" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1210" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1211" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B1211" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1211" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1211" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1211" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1211" s="1">
+        <v>85</v>
+      </c>
+      <c r="H1211" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1211" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1211" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1211" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1211" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1211" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1211" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1211" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="P1211" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1211" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1211" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1212" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B1212" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1212" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1212" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1212" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1212" s="1">
+        <v>86</v>
+      </c>
+      <c r="H1212" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1212" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1212" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1212" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1212" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1212" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1212" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1212" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="P1212" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1212" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1212" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1213" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B1213" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1213" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1213" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1213" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1213" s="1">
+        <v>87</v>
+      </c>
+      <c r="H1213" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1213" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1213" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1213" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1213" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1213" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1213" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1213" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="P1213" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1213" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1213" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1214" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B1214" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1214" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1214" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1214" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1214" s="1">
+        <v>88</v>
+      </c>
+      <c r="H1214" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1214" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1214" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1214" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1214" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1214" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1214" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1214" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1214" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1214" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1214" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1215" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B1215" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1215" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1215" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1215" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1215" s="1">
+        <v>89</v>
+      </c>
+      <c r="H1215" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1215" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1215" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="K1215" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1215" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1215" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1215" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1215" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="P1215" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1215" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1215" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1216" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B1216" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1216" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1216" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1216" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1216" s="1">
+        <v>90</v>
+      </c>
+      <c r="H1216" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1216" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1216" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1216" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1216" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1216" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1216" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1216" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1216" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1216" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1216" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1217" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B1217" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1217" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1217" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1217" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1217" s="1">
+        <v>91</v>
+      </c>
+      <c r="H1217" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1217" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1217" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1217" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1217" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1217" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1217" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1217" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="P1217" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1217" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1217" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1218" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B1218" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1218" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1218" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1218" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1218" s="1">
+        <v>92</v>
+      </c>
+      <c r="H1218" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1218" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1218" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1218" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1218" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1218" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1218" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1218" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="P1218" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1218" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1218" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1219" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B1219" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1219" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1219" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1219" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1219" s="1">
+        <v>93</v>
+      </c>
+      <c r="H1219" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1219" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1219" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1219" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1219" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1219" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1219" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1219" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="P1219" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1219" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1219" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1220" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B1220" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1220" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1220" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1220" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1220" s="1">
+        <v>94</v>
+      </c>
+      <c r="H1220" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1220" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1220" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1220" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1220" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1220" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1220" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1220" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="P1220" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1220" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1220" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1221" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B1221" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1221" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1221" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1221" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1221" s="1">
+        <v>95</v>
+      </c>
+      <c r="H1221" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1221" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1221" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1221" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1221" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1221" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1221" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1221" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="P1221" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1221" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1221" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1222" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B1222" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1222" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1222" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1222" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1222" s="1">
+        <v>96</v>
+      </c>
+      <c r="H1222" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1222" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1222" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1222" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1222" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1222" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1222" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1222" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="P1222" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1222" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1222" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1223" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B1223" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1223" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1223" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1223" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1223" s="1">
+        <v>97</v>
+      </c>
+      <c r="H1223" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1223" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1223" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1223" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1223" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1223" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1223" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1223" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="P1223" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1223" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1223" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1224" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B1224" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1224" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1224" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1224" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1224" s="1">
+        <v>98</v>
+      </c>
+      <c r="H1224" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1224" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1224" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1224" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1224" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1224" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1224" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1224" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="P1224" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1224" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1224" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1225" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B1225" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1225" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1225" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1225" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1225" s="1">
+        <v>99</v>
+      </c>
+      <c r="H1225" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1225" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1225" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1225" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1225" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1225" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1225" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1225" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="P1225" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1225" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1225" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1226" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B1226" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1226" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1226" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1226" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1226" s="1">
+        <v>100</v>
+      </c>
+      <c r="H1226" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1226" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1226" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1226" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1226" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1226" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1226" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1226" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="P1226" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1226" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1226" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1227" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B1227" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1227" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1227" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1227" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1227" s="1">
+        <v>101</v>
+      </c>
+      <c r="H1227" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1227" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1227" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1227" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1227" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1227" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1227" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1227" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="P1227" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1227" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1227" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1228" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B1228" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1228" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1228" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1228" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1228" s="1">
+        <v>102</v>
+      </c>
+      <c r="H1228" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1228" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1228" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1228" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1228" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1228" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1228" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1228" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="P1228" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1228" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1228" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1229" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B1229" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1229" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1229" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1229" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1229" s="1">
+        <v>103</v>
+      </c>
+      <c r="H1229" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1229" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1229" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1229" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1229" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1229" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1229" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1229" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="P1229" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1229" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1229" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1230" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B1230" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1230" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1230" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1230" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1230" s="1">
+        <v>104</v>
+      </c>
+      <c r="H1230" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1230" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1230" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1230" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1230" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1230" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1230" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1230" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1230" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1230" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1230" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1231" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B1231" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1231" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1231" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1231" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1231" s="1">
+        <v>105</v>
+      </c>
+      <c r="H1231" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1231" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1231" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1231" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1231" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1231" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1231" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1231" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="P1231" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1231" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1231" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1232" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B1232" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1232" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1232" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1232" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1232" s="1">
+        <v>106</v>
+      </c>
+      <c r="H1232" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1232" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1232" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1232" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1232" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1232" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1232" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1232" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1232" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1232" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1232" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1233" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B1233" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1233" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1233" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1233" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1233" s="1">
+        <v>107</v>
+      </c>
+      <c r="H1233" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1233" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1233" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1233" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1233" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1233" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1233" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1233" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="P1233" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1233" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1233" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1234" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B1234" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1234" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1234" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1234" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1234" s="1">
+        <v>108</v>
+      </c>
+      <c r="H1234" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1234" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1234" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1234" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1234" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1234" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1234" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1234" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="P1234" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1234" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1234" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1235" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B1235" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1235" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1235" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1235" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1235" s="1">
+        <v>109</v>
+      </c>
+      <c r="H1235" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1235" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1235" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1235" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1235" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1235" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1235" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1235" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="P1235" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1235" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1235" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1236" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B1236" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1236" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1236" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1236" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1236" s="1">
+        <v>110</v>
+      </c>
+      <c r="H1236" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1236" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1236" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1236" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1236" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1236" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1236" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1236" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="P1236" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1236" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1236" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1237" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B1237" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1237" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1237" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1237" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1237" s="1">
+        <v>111</v>
+      </c>
+      <c r="H1237" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1237" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1237" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1237" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1237" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1237" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1237" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1237" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="P1237" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1237" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1237" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1238" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B1238" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1238" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1238" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1238" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1238" s="1">
+        <v>112</v>
+      </c>
+      <c r="H1238" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1238" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1238" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1238" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1238" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1238" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1238" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1238" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="P1238" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1238" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1238" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1239" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B1239" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1239" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1239" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1239" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1239" s="1">
+        <v>113</v>
+      </c>
+      <c r="H1239" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1239" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1239" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1239" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1239" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1239" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1239" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1239" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="P1239" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1239" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1239" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1240" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B1240" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1240" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1240" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1240" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1240" s="1">
+        <v>114</v>
+      </c>
+      <c r="H1240" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1240" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1240" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1240" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1240" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1240" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1240" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1240" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="P1240" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1240" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1240" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1241" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B1241" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1241" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1241" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1241" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1241" s="1">
+        <v>115</v>
+      </c>
+      <c r="H1241" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1241" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1241" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1241" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1241" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1241" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1241" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1241" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="P1241" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1241" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1241" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1242" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B1242" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1242" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1242" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1242" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1242" s="1">
+        <v>116</v>
+      </c>
+      <c r="H1242" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1242" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1242" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1242" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1242" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1242" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1242" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1242" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="P1242" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1242" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1242" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1243" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B1243" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1243" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1243" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1243" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1243" s="1">
+        <v>117</v>
+      </c>
+      <c r="H1243" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1243" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1243" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1243" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1243" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1243" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1243" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1243" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="P1243" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1243" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1243" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1244" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B1244" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1244" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1244" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1244" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1244" s="1">
+        <v>118</v>
+      </c>
+      <c r="H1244" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1244" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1244" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1244" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1244" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1244" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1244" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1244" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="P1244" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1244" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1244" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1245" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B1245" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1245" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1245" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1245" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1245" s="1">
+        <v>119</v>
+      </c>
+      <c r="H1245" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1245" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1245" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1245" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1245" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1245" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1245" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1245" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="P1245" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1245" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1245" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1246" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B1246" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1246" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1246" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1246" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1246" s="1">
+        <v>120</v>
+      </c>
+      <c r="H1246" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1246" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1246" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1246" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1246" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1246" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1246" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1246" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1246" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1246" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1246" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1247" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B1247" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1247" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1247" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1247" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1247" s="1">
+        <v>121</v>
+      </c>
+      <c r="H1247" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1247" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1247" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="K1247" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1247" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1247" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1247" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1247" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="P1247" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1247" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1247" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1248" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B1248" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1248" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1248" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1248" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1248" s="1">
+        <v>122</v>
+      </c>
+      <c r="H1248" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1248" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1248" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1248" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1248" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1248" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1248" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1248" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="P1248" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1248" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1248" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1249" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B1249" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1249" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1249" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1249" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1249" s="1">
+        <v>123</v>
+      </c>
+      <c r="H1249" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1249" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1249" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="K1249" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1249" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1249" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1249" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1249" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="P1249" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1249" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1249" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2:A1012">

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0155EC-DC0B-4359-A504-BB7565B2EC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A2570B-982D-4CD6-81C5-37BA0F600D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2743" uniqueCount="1117">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2491,57 +2491,12 @@
     <t>111105,111105</t>
   </si>
   <si>
-    <t>3,25</t>
-  </si>
-  <si>
-    <t>12,45</t>
-  </si>
-  <si>
-    <t>25,57,18,65</t>
-  </si>
-  <si>
-    <t>2,50,33,50</t>
-  </si>
-  <si>
-    <t>40,67</t>
-  </si>
-  <si>
-    <t>40,58,57,62</t>
-  </si>
-  <si>
-    <t>40,67,52,72</t>
-  </si>
-  <si>
-    <t>42,70,42,62</t>
-  </si>
-  <si>
-    <t>15,70,15,60</t>
-  </si>
-  <si>
-    <t>44,35,44,25</t>
-  </si>
-  <si>
-    <t>12,35,18,35,27,24</t>
-  </si>
-  <si>
-    <t>15,35,12,30,18,24</t>
-  </si>
-  <si>
-    <t>12,47,12,67</t>
-  </si>
-  <si>
-    <t>18,55,15,60,52,63</t>
-  </si>
-  <si>
     <t>111105,111104</t>
   </si>
   <si>
     <t>111101,111101</t>
   </si>
   <si>
-    <t>111102,111104</t>
-  </si>
-  <si>
     <t>111101,111101,111104</t>
   </si>
   <si>
@@ -2549,9 +2504,6 @@
   </si>
   <si>
     <t>111102,111105,111105,111104</t>
-  </si>
-  <si>
-    <t>25,27,12,40</t>
   </si>
   <si>
     <t>111104</t>
@@ -2564,9 +2516,6 @@
     <t>111105,111105,111104</t>
   </si>
   <si>
-    <t>111102,111105,111104</t>
-  </si>
-  <si>
     <t>112113</t>
   </si>
   <si>
@@ -2585,12 +2534,6 @@
     <t>112105,112105,112105</t>
   </si>
   <si>
-    <t>10,13</t>
-  </si>
-  <si>
-    <t>45,90,50,80,55,86</t>
-  </si>
-  <si>
     <t>112102,112104,112104</t>
   </si>
   <si>
@@ -2673,18 +2616,6 @@
   </si>
   <si>
     <t>45,75,40,80,40,70</t>
-  </si>
-  <si>
-    <t>11,50,9,40</t>
-  </si>
-  <si>
-    <t>58,91,65,94,80,92</t>
-  </si>
-  <si>
-    <t>65,88,65,94,92,92</t>
-  </si>
-  <si>
-    <t>65,91,70,88,70,94,86,92</t>
   </si>
   <si>
     <t>999002,999002,999002</t>
@@ -3342,6 +3273,228 @@
   </si>
   <si>
     <t>1132008</t>
+  </si>
+  <si>
+    <t>1110102</t>
+  </si>
+  <si>
+    <t>1110103</t>
+  </si>
+  <si>
+    <t>1110201</t>
+  </si>
+  <si>
+    <t>1110202</t>
+  </si>
+  <si>
+    <t>1110203</t>
+  </si>
+  <si>
+    <t>1110301</t>
+  </si>
+  <si>
+    <t>1110302</t>
+  </si>
+  <si>
+    <t>1110303</t>
+  </si>
+  <si>
+    <t>1110401</t>
+  </si>
+  <si>
+    <t>1110402</t>
+  </si>
+  <si>
+    <t>1110403</t>
+  </si>
+  <si>
+    <t>1110501</t>
+  </si>
+  <si>
+    <t>1110502</t>
+  </si>
+  <si>
+    <t>1110503</t>
+  </si>
+  <si>
+    <t>1110504</t>
+  </si>
+  <si>
+    <t>1110601</t>
+  </si>
+  <si>
+    <t>1110602</t>
+  </si>
+  <si>
+    <t>1110603</t>
+  </si>
+  <si>
+    <t>1110604</t>
+  </si>
+  <si>
+    <t>1110701</t>
+  </si>
+  <si>
+    <t>1110702</t>
+  </si>
+  <si>
+    <t>1110703</t>
+  </si>
+  <si>
+    <t>1110704</t>
+  </si>
+  <si>
+    <t>1110801</t>
+  </si>
+  <si>
+    <t>1110802</t>
+  </si>
+  <si>
+    <t>1110803</t>
+  </si>
+  <si>
+    <t>1110804</t>
+  </si>
+  <si>
+    <t>1110901</t>
+  </si>
+  <si>
+    <t>1110902</t>
+  </si>
+  <si>
+    <t>1110903</t>
+  </si>
+  <si>
+    <t>1110904</t>
+  </si>
+  <si>
+    <t>1110905</t>
+  </si>
+  <si>
+    <t>1111001</t>
+  </si>
+  <si>
+    <t>1111002</t>
+  </si>
+  <si>
+    <t>1111003</t>
+  </si>
+  <si>
+    <t>1111004</t>
+  </si>
+  <si>
+    <t>1111005</t>
+  </si>
+  <si>
+    <t>1111006</t>
+  </si>
+  <si>
+    <t>1110101</t>
+  </si>
+  <si>
+    <t>15,7</t>
+  </si>
+  <si>
+    <t>2,30,2,45</t>
+  </si>
+  <si>
+    <t>15,35</t>
+  </si>
+  <si>
+    <t>45,60</t>
+  </si>
+  <si>
+    <t>55,45,55,35</t>
+  </si>
+  <si>
+    <t>35,45,45,45</t>
+  </si>
+  <si>
+    <t>35,75,50,75</t>
+  </si>
+  <si>
+    <t>42,75,45,90</t>
+  </si>
+  <si>
+    <t>42,80,55,90</t>
+  </si>
+  <si>
+    <t>35,45,50,45</t>
+  </si>
+  <si>
+    <t>42,45,20,30</t>
+  </si>
+  <si>
+    <t>35,40,50,40,35,30</t>
+  </si>
+  <si>
+    <t>37,75,48,75,45,90</t>
+  </si>
+  <si>
+    <t>37,80,48,80,55,90</t>
+  </si>
+  <si>
+    <t>35,80,45,80</t>
+  </si>
+  <si>
+    <t>38,45,47,45,20,30</t>
+  </si>
+  <si>
+    <t>20,35,30,35,40,35</t>
+  </si>
+  <si>
+    <t>35,75,50,75,45,90</t>
+  </si>
+  <si>
+    <t>37,75,48,75,55,90</t>
+  </si>
+  <si>
+    <t>45,80,50,80,40,80,45,85</t>
+  </si>
+  <si>
+    <t>50,80,40,80,45,80</t>
+  </si>
+  <si>
+    <t>35,45,50,45,30,30</t>
+  </si>
+  <si>
+    <t>38,45,47,45,25,30,35,30</t>
+  </si>
+  <si>
+    <t>40,40,35,40,45,40,50,40</t>
+  </si>
+  <si>
+    <t>20,35,30,35,25,35,35,35</t>
+  </si>
+  <si>
+    <t>37,75,40,75,48,75,55,90</t>
+  </si>
+  <si>
+    <t>45,80,50,80,40,85,45,85</t>
+  </si>
+  <si>
+    <t>45,80,50,80,40,80,35,80</t>
+  </si>
+  <si>
+    <t>45,80,50,80,40,80</t>
+  </si>
+  <si>
+    <t>40,40,35,40,40,30,40,25</t>
+  </si>
+  <si>
+    <t>30,35,20,35,25,35,35,35</t>
+  </si>
+  <si>
+    <t>111102,111101,111101,111101</t>
+  </si>
+  <si>
+    <t>111105,111105,111104,111104</t>
+  </si>
+  <si>
+    <t>111105,111105,111105,111105</t>
+  </si>
+  <si>
+    <t>111102,111105,111105,111105</t>
   </si>
 </sst>
 </file>
@@ -4157,7 +4310,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1249"/>
+  <dimension ref="A1:R1267"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -4389,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>849</v>
+        <v>826</v>
       </c>
       <c r="K5" s="12">
         <v>20</v>
@@ -4445,7 +4598,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="K6" s="14">
         <v>20</v>
@@ -4460,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>852</v>
+        <v>829</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -4501,7 +4654,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="K7" s="14">
         <v>20</v>
@@ -4557,7 +4710,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="K8" s="12">
         <v>20</v>
@@ -4613,7 +4766,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="K9" s="14">
         <v>20</v>
@@ -4669,7 +4822,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="K10" s="14">
         <v>20</v>
@@ -4725,7 +4878,7 @@
         <v>3</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="K11" s="12">
         <v>20</v>
@@ -4781,7 +4934,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="K12" s="14">
         <v>20</v>
@@ -4837,7 +4990,7 @@
         <v>3</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="K13" s="14">
         <v>20</v>
@@ -4893,7 +5046,7 @@
         <v>3</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="K14" s="16">
         <v>20</v>
@@ -4949,7 +5102,7 @@
         <v>4</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="K15" s="14">
         <v>20</v>
@@ -5005,7 +5158,7 @@
         <v>4</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="K16" s="14">
         <v>20</v>
@@ -5061,7 +5214,7 @@
         <v>4</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="K17" s="14">
         <v>20</v>
@@ -5117,7 +5270,7 @@
         <v>4</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="K18" s="16">
         <v>20</v>
@@ -5173,7 +5326,7 @@
         <v>5</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="K19" s="14">
         <v>20</v>
@@ -5229,7 +5382,7 @@
         <v>5</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="K20" s="14">
         <v>20</v>
@@ -5285,7 +5438,7 @@
         <v>5</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="K21" s="14">
         <v>20</v>
@@ -5341,7 +5494,7 @@
         <v>5</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="K22" s="16">
         <v>20</v>
@@ -63911,7 +64064,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -64589,8 +64742,8 @@
       </c>
     </row>
     <row r="1082" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1082" s="1">
-        <v>1110101</v>
+      <c r="A1082" s="1" t="s">
+        <v>1081</v>
       </c>
       <c r="B1082" s="1">
         <v>11</v>
@@ -64614,10 +64767,10 @@
         <v>1</v>
       </c>
       <c r="J1082" s="2" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="K1082" s="1">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="L1082" s="1">
         <v>30000</v>
@@ -64629,7 +64782,7 @@
         <v>0</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>814</v>
+        <v>1082</v>
       </c>
       <c r="P1082" s="1">
         <v>0</v>
@@ -64642,17 +64795,17 @@
       </c>
     </row>
     <row r="1083" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1083" s="1">
-        <v>1110102</v>
+      <c r="A1083" s="1" t="s">
+        <v>1043</v>
       </c>
       <c r="B1083" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1083" s="1">
         <v>1</v>
       </c>
       <c r="E1083" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1083" s="1">
         <v>1</v>
@@ -64661,7 +64814,7 @@
         <v>2</v>
       </c>
       <c r="H1083" s="67">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1083" s="1">
         <v>1</v>
@@ -64670,7 +64823,7 @@
         <v>781</v>
       </c>
       <c r="K1083" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1083" s="1">
         <v>30000</v>
@@ -64682,7 +64835,7 @@
         <v>0</v>
       </c>
       <c r="O1083" s="1" t="s">
-        <v>803</v>
+        <v>1083</v>
       </c>
       <c r="P1083" s="1">
         <v>0</v>
@@ -64691,21 +64844,21 @@
         <v>0</v>
       </c>
       <c r="R1083" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1084" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1084" s="1">
-        <v>1110103</v>
+      <c r="A1084" s="1" t="s">
+        <v>1044</v>
       </c>
       <c r="B1084" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1084" s="1">
         <v>1</v>
       </c>
       <c r="E1084" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1084" s="1">
         <v>1</v>
@@ -64714,7 +64867,7 @@
         <v>3</v>
       </c>
       <c r="H1084" s="67">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1084" s="1">
         <v>1</v>
@@ -64723,7 +64876,7 @@
         <v>780</v>
       </c>
       <c r="K1084" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1084" s="1">
         <v>30000</v>
@@ -64735,7 +64888,7 @@
         <v>0</v>
       </c>
       <c r="O1084" s="1" t="s">
-        <v>783</v>
+        <v>1084</v>
       </c>
       <c r="P1084" s="1">
         <v>0</v>
@@ -64744,21 +64897,21 @@
         <v>0</v>
       </c>
       <c r="R1084" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1085" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1085" s="1">
-        <v>1110201</v>
+      <c r="A1085" s="1" t="s">
+        <v>1045</v>
       </c>
       <c r="B1085" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1085" s="1">
         <v>1</v>
       </c>
       <c r="E1085" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1085" s="1">
         <v>1</v>
@@ -64776,7 +64929,7 @@
         <v>780</v>
       </c>
       <c r="K1085" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1085" s="1">
         <v>30000</v>
@@ -64788,7 +64941,7 @@
         <v>0</v>
       </c>
       <c r="O1085" s="1" t="s">
-        <v>784</v>
+        <v>1085</v>
       </c>
       <c r="P1085" s="1">
         <v>0</v>
@@ -64801,17 +64954,17 @@
       </c>
     </row>
     <row r="1086" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1086" s="1">
-        <v>1110202</v>
+      <c r="A1086" s="1" t="s">
+        <v>1046</v>
       </c>
       <c r="B1086" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1086" s="1">
         <v>1</v>
       </c>
       <c r="E1086" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1086" s="1">
         <v>1</v>
@@ -64820,16 +64973,16 @@
         <v>5</v>
       </c>
       <c r="H1086" s="67">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1086" s="1">
         <v>2</v>
       </c>
       <c r="J1086" s="2" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="K1086" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1086" s="1">
         <v>30000</v>
@@ -64841,7 +64994,7 @@
         <v>0</v>
       </c>
       <c r="O1086" s="1" t="s">
-        <v>785</v>
+        <v>1086</v>
       </c>
       <c r="P1086" s="1">
         <v>0</v>
@@ -64850,21 +65003,21 @@
         <v>0</v>
       </c>
       <c r="R1086" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1087" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1087" s="1">
-        <v>1110203</v>
+      <c r="A1087" s="1" t="s">
+        <v>1047</v>
       </c>
       <c r="B1087" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1087" s="1">
         <v>1</v>
       </c>
       <c r="E1087" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1087" s="1">
         <v>1</v>
@@ -64873,16 +65026,16 @@
         <v>6</v>
       </c>
       <c r="H1087" s="67">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1087" s="1">
         <v>2</v>
       </c>
       <c r="J1087" s="2" t="s">
-        <v>798</v>
+        <v>784</v>
       </c>
       <c r="K1087" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1087" s="1">
         <v>30000</v>
@@ -64894,7 +65047,7 @@
         <v>0</v>
       </c>
       <c r="O1087" s="1" t="s">
-        <v>786</v>
+        <v>1087</v>
       </c>
       <c r="P1087" s="1">
         <v>0</v>
@@ -64903,21 +65056,21 @@
         <v>0</v>
       </c>
       <c r="R1087" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1088" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1088" s="1">
-        <v>1110301</v>
+      <c r="A1088" s="1" t="s">
+        <v>1048</v>
       </c>
       <c r="B1088" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1088" s="1">
         <v>1</v>
       </c>
       <c r="E1088" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1088" s="1">
         <v>1</v>
@@ -64932,10 +65085,10 @@
         <v>3</v>
       </c>
       <c r="J1088" s="2" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="K1088" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1088" s="1">
         <v>30000</v>
@@ -64947,7 +65100,7 @@
         <v>0</v>
       </c>
       <c r="O1088" s="1" t="s">
-        <v>787</v>
+        <v>1088</v>
       </c>
       <c r="P1088" s="1">
         <v>0</v>
@@ -64960,17 +65113,17 @@
       </c>
     </row>
     <row r="1089" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1089" s="1">
-        <v>1110302</v>
+      <c r="A1089" s="1" t="s">
+        <v>1049</v>
       </c>
       <c r="B1089" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1089" s="1">
         <v>1</v>
       </c>
       <c r="E1089" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1089" s="1">
         <v>1</v>
@@ -64988,7 +65141,7 @@
         <v>781</v>
       </c>
       <c r="K1089" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1089" s="1">
         <v>30000</v>
@@ -65000,7 +65153,7 @@
         <v>0</v>
       </c>
       <c r="O1089" s="1" t="s">
-        <v>788</v>
+        <v>1089</v>
       </c>
       <c r="P1089" s="1">
         <v>0</v>
@@ -65009,21 +65162,21 @@
         <v>0</v>
       </c>
       <c r="R1089" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1090" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1090" s="1">
-        <v>1110303</v>
+      <c r="A1090" s="1" t="s">
+        <v>1050</v>
       </c>
       <c r="B1090" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1090" s="1">
         <v>1</v>
       </c>
       <c r="E1090" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1090" s="1">
         <v>1</v>
@@ -65032,16 +65185,16 @@
         <v>9</v>
       </c>
       <c r="H1090" s="67">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I1090" s="1">
         <v>3</v>
       </c>
       <c r="J1090" s="2" t="s">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="K1090" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1090" s="1">
         <v>30000</v>
@@ -65053,7 +65206,7 @@
         <v>0</v>
       </c>
       <c r="O1090" s="1" t="s">
-        <v>789</v>
+        <v>1090</v>
       </c>
       <c r="P1090" s="1">
         <v>0</v>
@@ -65066,17 +65219,17 @@
       </c>
     </row>
     <row r="1091" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1091" s="1">
-        <v>1110304</v>
+      <c r="A1091" s="1" t="s">
+        <v>1051</v>
       </c>
       <c r="B1091" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1091" s="1">
         <v>1</v>
       </c>
       <c r="E1091" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1091" s="1">
         <v>1</v>
@@ -65085,16 +65238,16 @@
         <v>10</v>
       </c>
       <c r="H1091" s="67">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I1091" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J1091" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="K1091" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1091" s="1">
         <v>30000</v>
@@ -65106,7 +65259,7 @@
         <v>0</v>
       </c>
       <c r="O1091" s="1" t="s">
-        <v>790</v>
+        <v>1091</v>
       </c>
       <c r="P1091" s="1">
         <v>0</v>
@@ -65115,21 +65268,21 @@
         <v>0</v>
       </c>
       <c r="R1091" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1092" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1092" s="1">
-        <v>1110401</v>
+      <c r="A1092" s="1" t="s">
+        <v>1052</v>
       </c>
       <c r="B1092" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1092" s="1">
         <v>1</v>
       </c>
       <c r="E1092" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1092" s="1">
         <v>1</v>
@@ -65138,16 +65291,16 @@
         <v>11</v>
       </c>
       <c r="H1092" s="67">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I1092" s="1">
         <v>4</v>
       </c>
       <c r="J1092" s="2" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="K1092" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1092" s="1">
         <v>30000</v>
@@ -65159,7 +65312,7 @@
         <v>0</v>
       </c>
       <c r="O1092" s="1" t="s">
-        <v>791</v>
+        <v>1092</v>
       </c>
       <c r="P1092" s="1">
         <v>0</v>
@@ -65168,21 +65321,21 @@
         <v>0</v>
       </c>
       <c r="R1092" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1093" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1093" s="1">
-        <v>1110402</v>
+      <c r="A1093" s="1" t="s">
+        <v>1053</v>
       </c>
       <c r="B1093" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1093" s="1">
         <v>1</v>
       </c>
       <c r="E1093" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1093" s="1">
         <v>1</v>
@@ -65191,16 +65344,16 @@
         <v>12</v>
       </c>
       <c r="H1093" s="67">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="I1093" s="1">
         <v>4</v>
       </c>
       <c r="J1093" s="2" t="s">
-        <v>799</v>
+        <v>785</v>
       </c>
       <c r="K1093" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1093" s="1">
         <v>30000</v>
@@ -65212,7 +65365,7 @@
         <v>0</v>
       </c>
       <c r="O1093" s="1" t="s">
-        <v>792</v>
+        <v>1093</v>
       </c>
       <c r="P1093" s="1">
         <v>0</v>
@@ -65221,21 +65374,21 @@
         <v>0</v>
       </c>
       <c r="R1093" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1094" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1094" s="1">
-        <v>1110403</v>
+      <c r="A1094" s="1" t="s">
+        <v>1054</v>
       </c>
       <c r="B1094" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1094" s="1">
         <v>1</v>
       </c>
       <c r="E1094" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1094" s="1">
         <v>1</v>
@@ -65244,16 +65397,16 @@
         <v>13</v>
       </c>
       <c r="H1094" s="67">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I1094" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1094" s="2" t="s">
-        <v>806</v>
+        <v>784</v>
       </c>
       <c r="K1094" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1094" s="1">
         <v>30000</v>
@@ -65265,7 +65418,7 @@
         <v>0</v>
       </c>
       <c r="O1094" s="1" t="s">
-        <v>793</v>
+        <v>1088</v>
       </c>
       <c r="P1094" s="1">
         <v>0</v>
@@ -65278,17 +65431,17 @@
       </c>
     </row>
     <row r="1095" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1095" s="1">
-        <v>1110404</v>
+      <c r="A1095" s="1" t="s">
+        <v>1055</v>
       </c>
       <c r="B1095" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1095" s="1">
         <v>1</v>
       </c>
       <c r="E1095" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1095" s="1">
         <v>1</v>
@@ -65297,16 +65450,16 @@
         <v>14</v>
       </c>
       <c r="H1095" s="67">
-        <v>2500</v>
+        <v>1800</v>
       </c>
       <c r="I1095" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1095" s="2" t="s">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="K1095" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1095" s="1">
         <v>30000</v>
@@ -65318,7 +65471,7 @@
         <v>0</v>
       </c>
       <c r="O1095" s="1" t="s">
-        <v>794</v>
+        <v>1094</v>
       </c>
       <c r="P1095" s="1">
         <v>0</v>
@@ -65331,17 +65484,17 @@
       </c>
     </row>
     <row r="1096" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1096" s="1">
-        <v>1110405</v>
+      <c r="A1096" s="1" t="s">
+        <v>1056</v>
       </c>
       <c r="B1096" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1096" s="1">
         <v>1</v>
       </c>
       <c r="E1096" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1096" s="1">
         <v>1</v>
@@ -65350,16 +65503,16 @@
         <v>15</v>
       </c>
       <c r="H1096" s="67">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I1096" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J1096" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="K1096" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1096" s="1">
         <v>30000</v>
@@ -65371,7 +65524,7 @@
         <v>0</v>
       </c>
       <c r="O1096" s="1" t="s">
-        <v>844</v>
+        <v>1095</v>
       </c>
       <c r="P1096" s="1">
         <v>0</v>
@@ -65384,17 +65537,17 @@
       </c>
     </row>
     <row r="1097" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1097" s="1">
-        <v>1110501</v>
+      <c r="A1097" s="1" t="s">
+        <v>1057</v>
       </c>
       <c r="B1097" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1097" s="1">
         <v>1</v>
       </c>
       <c r="E1097" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1097" s="1">
         <v>1</v>
@@ -65403,16 +65556,16 @@
         <v>16</v>
       </c>
       <c r="H1097" s="67">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I1097" s="1">
         <v>5</v>
       </c>
       <c r="J1097" s="2" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K1097" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1097" s="1">
         <v>30000</v>
@@ -65424,7 +65577,7 @@
         <v>0</v>
       </c>
       <c r="O1097" s="1" t="s">
-        <v>795</v>
+        <v>1096</v>
       </c>
       <c r="P1097" s="1">
         <v>0</v>
@@ -65433,21 +65586,21 @@
         <v>0</v>
       </c>
       <c r="R1097" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1098" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1098" s="1">
-        <v>1110502</v>
+      <c r="A1098" s="1" t="s">
+        <v>1058</v>
       </c>
       <c r="B1098" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1098" s="1">
         <v>1</v>
       </c>
       <c r="E1098" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1098" s="1">
         <v>1</v>
@@ -65456,16 +65609,16 @@
         <v>17</v>
       </c>
       <c r="H1098" s="67">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="I1098" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1098" s="2" t="s">
-        <v>807</v>
+        <v>784</v>
       </c>
       <c r="K1098" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1098" s="1">
         <v>30000</v>
@@ -65477,7 +65630,7 @@
         <v>0</v>
       </c>
       <c r="O1098" s="1" t="s">
-        <v>796</v>
+        <v>1091</v>
       </c>
       <c r="P1098" s="1">
         <v>0</v>
@@ -65490,17 +65643,17 @@
       </c>
     </row>
     <row r="1099" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1099" s="1">
-        <v>1110503</v>
+      <c r="A1099" s="1" t="s">
+        <v>1059</v>
       </c>
       <c r="B1099" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1099" s="1">
         <v>1</v>
       </c>
       <c r="E1099" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1099" s="1">
         <v>1</v>
@@ -65509,16 +65662,16 @@
         <v>18</v>
       </c>
       <c r="H1099" s="67">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I1099" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1099" s="2" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="K1099" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1099" s="1">
         <v>30000</v>
@@ -65530,7 +65683,7 @@
         <v>0</v>
       </c>
       <c r="O1099" s="1" t="s">
-        <v>815</v>
+        <v>1097</v>
       </c>
       <c r="P1099" s="1">
         <v>0</v>
@@ -65543,17 +65696,17 @@
       </c>
     </row>
     <row r="1100" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1100" s="1">
-        <v>1110504</v>
+      <c r="A1100" s="1" t="s">
+        <v>1060</v>
       </c>
       <c r="B1100" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1100" s="1">
         <v>1</v>
       </c>
       <c r="E1100" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1100" s="1">
         <v>1</v>
@@ -65562,16 +65715,16 @@
         <v>19</v>
       </c>
       <c r="H1100" s="67">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="I1100" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1100" s="2" t="s">
-        <v>807</v>
+        <v>785</v>
       </c>
       <c r="K1100" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1100" s="1">
         <v>30000</v>
@@ -65583,7 +65736,7 @@
         <v>0</v>
       </c>
       <c r="O1100" s="1" t="s">
-        <v>845</v>
+        <v>1093</v>
       </c>
       <c r="P1100" s="1">
         <v>0</v>
@@ -65596,17 +65749,17 @@
       </c>
     </row>
     <row r="1101" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1101" s="1">
-        <v>1110505</v>
+      <c r="A1101" s="1" t="s">
+        <v>1061</v>
       </c>
       <c r="B1101" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1101" s="1">
         <v>1</v>
       </c>
       <c r="E1101" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1101" s="1">
         <v>1</v>
@@ -65615,16 +65768,16 @@
         <v>20</v>
       </c>
       <c r="H1101" s="67">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I1101" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J1101" s="2" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="K1101" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1101" s="1">
         <v>30000</v>
@@ -65636,7 +65789,7 @@
         <v>0</v>
       </c>
       <c r="O1101" s="1" t="s">
-        <v>846</v>
+        <v>1098</v>
       </c>
       <c r="P1101" s="1">
         <v>0</v>
@@ -65645,21 +65798,21 @@
         <v>0</v>
       </c>
       <c r="R1101" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1102" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1102" s="1">
-        <v>1110506</v>
+      <c r="A1102" s="1" t="s">
+        <v>1062</v>
       </c>
       <c r="B1102" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1102" s="1">
         <v>1</v>
       </c>
       <c r="E1102" s="1">
-        <v>120001</v>
+        <v>110001</v>
       </c>
       <c r="F1102" s="1">
         <v>1</v>
@@ -65668,16 +65821,16 @@
         <v>21</v>
       </c>
       <c r="H1102" s="67">
-        <v>1</v>
+        <v>1800</v>
       </c>
       <c r="I1102" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J1102" s="2" t="s">
-        <v>802</v>
+        <v>785</v>
       </c>
       <c r="K1102" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L1102" s="1">
         <v>30000</v>
@@ -65689,7 +65842,7 @@
         <v>0</v>
       </c>
       <c r="O1102" s="1" t="s">
-        <v>847</v>
+        <v>1099</v>
       </c>
       <c r="P1102" s="1">
         <v>0</v>
@@ -65702,35 +65855,35 @@
       </c>
     </row>
     <row r="1103" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1103" s="1">
-        <v>1120601</v>
+      <c r="A1103" s="1" t="s">
+        <v>1063</v>
       </c>
       <c r="B1103" s="1">
         <v>11</v>
       </c>
       <c r="D1103" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1103" s="1">
-        <v>110002</v>
+        <v>110001</v>
       </c>
       <c r="F1103" s="1">
         <v>1</v>
       </c>
       <c r="G1103" s="1">
-        <v>1</v>
-      </c>
-      <c r="H1103" s="1">
-        <v>2000</v>
+        <v>22</v>
+      </c>
+      <c r="H1103" s="67">
+        <v>1800</v>
       </c>
       <c r="I1103" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1103" s="2" t="s">
-        <v>809</v>
+        <v>790</v>
       </c>
       <c r="K1103" s="1">
-        <v>800</v>
+        <v>20</v>
       </c>
       <c r="L1103" s="1">
         <v>30000</v>
@@ -65742,7 +65895,7 @@
         <v>0</v>
       </c>
       <c r="O1103" s="1" t="s">
-        <v>823</v>
+        <v>1100</v>
       </c>
       <c r="P1103" s="1">
         <v>0</v>
@@ -65750,40 +65903,40 @@
       <c r="Q1103" s="1">
         <v>0</v>
       </c>
-      <c r="R1103" s="67">
+      <c r="R1103" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1104" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1104" s="1">
-        <v>1120602</v>
+      <c r="A1104" s="1" t="s">
+        <v>1064</v>
       </c>
       <c r="B1104" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1104" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1104" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1104" s="1">
         <v>1</v>
       </c>
       <c r="G1104" s="1">
-        <v>2</v>
-      </c>
-      <c r="H1104" s="1">
-        <v>2500</v>
+        <v>23</v>
+      </c>
+      <c r="H1104" s="67">
+        <v>1800</v>
       </c>
       <c r="I1104" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1104" s="2" t="s">
-        <v>816</v>
+        <v>1113</v>
       </c>
       <c r="K1104" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1104" s="1">
         <v>30000</v>
@@ -65795,7 +65948,7 @@
         <v>0</v>
       </c>
       <c r="O1104" s="1" t="s">
-        <v>824</v>
+        <v>1101</v>
       </c>
       <c r="P1104" s="1">
         <v>0</v>
@@ -65803,40 +65956,40 @@
       <c r="Q1104" s="1">
         <v>0</v>
       </c>
-      <c r="R1104" s="67">
+      <c r="R1104" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1105" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1105" s="1">
-        <v>1120603</v>
+      <c r="A1105" s="1" t="s">
+        <v>1065</v>
       </c>
       <c r="B1105" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1105" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1105" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1105" s="1">
         <v>1</v>
       </c>
       <c r="G1105" s="1">
-        <v>3</v>
-      </c>
-      <c r="H1105" s="1">
-        <v>2000</v>
+        <v>24</v>
+      </c>
+      <c r="H1105" s="67">
+        <v>1800</v>
       </c>
       <c r="I1105" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1105" s="2" t="s">
-        <v>809</v>
+        <v>786</v>
       </c>
       <c r="K1105" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1105" s="1">
         <v>30000</v>
@@ -65848,7 +66001,7 @@
         <v>0</v>
       </c>
       <c r="O1105" s="1" t="s">
-        <v>823</v>
+        <v>1102</v>
       </c>
       <c r="P1105" s="1">
         <v>0</v>
@@ -65856,40 +66009,40 @@
       <c r="Q1105" s="1">
         <v>0</v>
       </c>
-      <c r="R1105" s="67">
+      <c r="R1105" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1106" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1106" s="1">
-        <v>1120604</v>
+      <c r="A1106" s="1" t="s">
+        <v>1066</v>
       </c>
       <c r="B1106" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1106" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1106" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1106" s="1">
         <v>1</v>
       </c>
       <c r="G1106" s="1">
-        <v>4</v>
-      </c>
-      <c r="H1106" s="1">
-        <v>2000</v>
+        <v>25</v>
+      </c>
+      <c r="H1106" s="67">
+        <v>1600</v>
       </c>
       <c r="I1106" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1106" s="2" t="s">
-        <v>812</v>
+        <v>785</v>
       </c>
       <c r="K1106" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1106" s="1">
         <v>30000</v>
@@ -65901,7 +66054,7 @@
         <v>0</v>
       </c>
       <c r="O1106" s="1" t="s">
-        <v>825</v>
+        <v>1103</v>
       </c>
       <c r="P1106" s="1">
         <v>0</v>
@@ -65909,40 +66062,40 @@
       <c r="Q1106" s="1">
         <v>0</v>
       </c>
-      <c r="R1106" s="67">
-        <v>1</v>
+      <c r="R1106" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="1107" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1107" s="1">
-        <v>1120701</v>
+      <c r="A1107" s="1" t="s">
+        <v>1067</v>
       </c>
       <c r="B1107" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1107" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1107" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1107" s="1">
         <v>1</v>
       </c>
       <c r="G1107" s="1">
-        <v>5</v>
-      </c>
-      <c r="H1107" s="1">
-        <v>2000</v>
+        <v>26</v>
+      </c>
+      <c r="H1107" s="67">
+        <v>1600</v>
       </c>
       <c r="I1107" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1107" s="2" t="s">
-        <v>813</v>
+        <v>1114</v>
       </c>
       <c r="K1107" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1107" s="1">
         <v>30000</v>
@@ -65954,7 +66107,7 @@
         <v>0</v>
       </c>
       <c r="O1107" s="1" t="s">
-        <v>826</v>
+        <v>1104</v>
       </c>
       <c r="P1107" s="1">
         <v>0</v>
@@ -65962,40 +66115,40 @@
       <c r="Q1107" s="1">
         <v>0</v>
       </c>
-      <c r="R1107" s="67">
+      <c r="R1107" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1108" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1108" s="1">
-        <v>1120702</v>
+      <c r="A1108" s="1" t="s">
+        <v>1068</v>
       </c>
       <c r="B1108" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1108" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1108" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1108" s="1">
         <v>1</v>
       </c>
       <c r="G1108" s="1">
-        <v>6</v>
-      </c>
-      <c r="H1108" s="1">
-        <v>2500</v>
+        <v>27</v>
+      </c>
+      <c r="H1108" s="67">
+        <v>1600</v>
       </c>
       <c r="I1108" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1108" s="2" t="s">
-        <v>816</v>
+        <v>1113</v>
       </c>
       <c r="K1108" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1108" s="1">
         <v>30000</v>
@@ -66007,7 +66160,7 @@
         <v>0</v>
       </c>
       <c r="O1108" s="1" t="s">
-        <v>827</v>
+        <v>1105</v>
       </c>
       <c r="P1108" s="1">
         <v>0</v>
@@ -66015,40 +66168,40 @@
       <c r="Q1108" s="1">
         <v>0</v>
       </c>
-      <c r="R1108" s="67">
+      <c r="R1108" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1109" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1109" s="1">
-        <v>1120703</v>
+      <c r="A1109" s="1" t="s">
+        <v>1069</v>
       </c>
       <c r="B1109" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1109" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1109" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1109" s="1">
         <v>1</v>
       </c>
       <c r="G1109" s="1">
-        <v>7</v>
-      </c>
-      <c r="H1109" s="1">
-        <v>2000</v>
+        <v>28</v>
+      </c>
+      <c r="H1109" s="67">
+        <v>1600</v>
       </c>
       <c r="I1109" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1109" s="2" t="s">
-        <v>817</v>
+        <v>1115</v>
       </c>
       <c r="K1109" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1109" s="1">
         <v>30000</v>
@@ -66060,7 +66213,7 @@
         <v>0</v>
       </c>
       <c r="O1109" s="1" t="s">
-        <v>828</v>
+        <v>1106</v>
       </c>
       <c r="P1109" s="1">
         <v>0</v>
@@ -66068,40 +66221,40 @@
       <c r="Q1109" s="1">
         <v>0</v>
       </c>
-      <c r="R1109" s="67">
+      <c r="R1109" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1110" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1110" s="1">
-        <v>1120704</v>
+      <c r="A1110" s="1" t="s">
+        <v>1070</v>
       </c>
       <c r="B1110" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1110" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1110" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1110" s="1">
         <v>1</v>
       </c>
       <c r="G1110" s="1">
-        <v>8</v>
-      </c>
-      <c r="H1110" s="1">
-        <v>2000</v>
+        <v>29</v>
+      </c>
+      <c r="H1110" s="67">
+        <v>1600</v>
       </c>
       <c r="I1110" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J1110" s="2" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="K1110" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1110" s="1">
         <v>30000</v>
@@ -66113,7 +66266,7 @@
         <v>0</v>
       </c>
       <c r="O1110" s="1" t="s">
-        <v>829</v>
+        <v>1099</v>
       </c>
       <c r="P1110" s="1">
         <v>0</v>
@@ -66121,40 +66274,40 @@
       <c r="Q1110" s="1">
         <v>0</v>
       </c>
-      <c r="R1110" s="67">
+      <c r="R1110" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1111" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1111" s="1">
-        <v>1120801</v>
+      <c r="A1111" s="1" t="s">
+        <v>1071</v>
       </c>
       <c r="B1111" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1111" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1111" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1111" s="1">
         <v>1</v>
       </c>
       <c r="G1111" s="1">
+        <v>30</v>
+      </c>
+      <c r="H1111" s="67">
+        <v>1600</v>
+      </c>
+      <c r="I1111" s="1">
         <v>9</v>
       </c>
-      <c r="H1111" s="1">
-        <v>2000</v>
-      </c>
-      <c r="I1111" s="1">
-        <v>8</v>
-      </c>
       <c r="J1111" s="2" t="s">
-        <v>813</v>
+        <v>787</v>
       </c>
       <c r="K1111" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1111" s="1">
         <v>30000</v>
@@ -66166,7 +66319,7 @@
         <v>0</v>
       </c>
       <c r="O1111" s="1" t="s">
-        <v>826</v>
+        <v>1107</v>
       </c>
       <c r="P1111" s="1">
         <v>0</v>
@@ -66174,252 +66327,252 @@
       <c r="Q1111" s="1">
         <v>0</v>
       </c>
-      <c r="R1111" s="67">
-        <v>1</v>
+      <c r="R1111" s="1">
+        <v>0</v>
       </c>
     </row>
     <row r="1112" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1112" s="1">
-        <v>1120802</v>
+      <c r="A1112" s="1" t="s">
+        <v>1072</v>
       </c>
       <c r="B1112" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1112" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1112" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1112" s="1">
         <v>1</v>
       </c>
       <c r="G1112" s="1">
+        <v>31</v>
+      </c>
+      <c r="H1112" s="67">
+        <v>1600</v>
+      </c>
+      <c r="I1112" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1112" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="K1112" s="1">
+        <v>20</v>
+      </c>
+      <c r="L1112" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1112" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1112" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1112" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="P1112" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1112" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1113" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B1113" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1113" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1113" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1113" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1113" s="1">
+        <v>32</v>
+      </c>
+      <c r="H1113" s="67">
+        <v>1600</v>
+      </c>
+      <c r="I1113" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1113" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K1113" s="1">
+        <v>20</v>
+      </c>
+      <c r="L1113" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1113" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1113" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1113" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="P1113" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1113" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1114" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B1114" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1114" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1114" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1114" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1114" s="1">
+        <v>33</v>
+      </c>
+      <c r="H1114" s="67">
+        <v>1600</v>
+      </c>
+      <c r="I1114" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1114" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="K1114" s="1">
+        <v>20</v>
+      </c>
+      <c r="L1114" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1114" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1114" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1114" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="P1114" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1114" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1114" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1115" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B1115" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1115" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1115" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1115" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1115" s="1">
+        <v>34</v>
+      </c>
+      <c r="H1115" s="67">
+        <v>1600</v>
+      </c>
+      <c r="I1115" s="1">
         <v>10</v>
       </c>
-      <c r="H1112" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I1112" s="1">
-        <v>8</v>
-      </c>
-      <c r="J1112" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="K1112" s="1">
-        <v>160</v>
-      </c>
-      <c r="L1112" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1112" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1112" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1112" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="P1112" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1112" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1112" s="67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1113" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1113" s="1">
-        <v>1120803</v>
-      </c>
-      <c r="B1113" s="1">
-        <v>12</v>
-      </c>
-      <c r="D1113" s="1">
-        <v>2</v>
-      </c>
-      <c r="E1113" s="1">
-        <v>120002</v>
-      </c>
-      <c r="F1113" s="1">
-        <v>1</v>
-      </c>
-      <c r="G1113" s="1">
+      <c r="J1115" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="K1115" s="1">
+        <v>20</v>
+      </c>
+      <c r="L1115" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1115" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1115" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1115" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="P1115" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1115" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1115" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1116" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B1116" s="1">
         <v>11</v>
       </c>
-      <c r="H1113" s="1">
-        <v>2000</v>
-      </c>
-      <c r="I1113" s="1">
-        <v>8</v>
-      </c>
-      <c r="J1113" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="K1113" s="1">
-        <v>160</v>
-      </c>
-      <c r="L1113" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1113" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1113" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1113" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="P1113" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1113" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1113" s="67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1114" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1114" s="1">
-        <v>1120804</v>
-      </c>
-      <c r="B1114" s="1">
-        <v>12</v>
-      </c>
-      <c r="D1114" s="1">
-        <v>2</v>
-      </c>
-      <c r="E1114" s="1">
-        <v>120002</v>
-      </c>
-      <c r="F1114" s="1">
-        <v>1</v>
-      </c>
-      <c r="G1114" s="1">
-        <v>12</v>
-      </c>
-      <c r="H1114" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I1114" s="1">
-        <v>8</v>
-      </c>
-      <c r="J1114" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="K1114" s="1">
-        <v>160</v>
-      </c>
-      <c r="L1114" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1114" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1114" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1114" s="1" t="s">
-        <v>832</v>
-      </c>
-      <c r="P1114" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1114" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1114" s="67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1115" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1115" s="1">
-        <v>1120805</v>
-      </c>
-      <c r="B1115" s="1">
-        <v>12</v>
-      </c>
-      <c r="D1115" s="1">
-        <v>2</v>
-      </c>
-      <c r="E1115" s="1">
-        <v>120002</v>
-      </c>
-      <c r="F1115" s="1">
-        <v>1</v>
-      </c>
-      <c r="G1115" s="1">
-        <v>13</v>
-      </c>
-      <c r="H1115" s="1">
-        <v>2000</v>
-      </c>
-      <c r="I1115" s="1">
-        <v>8</v>
-      </c>
-      <c r="J1115" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="K1115" s="1">
-        <v>160</v>
-      </c>
-      <c r="L1115" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1115" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1115" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1115" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="P1115" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1115" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1115" s="67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1116" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1116" s="1">
-        <v>1120901</v>
-      </c>
-      <c r="B1116" s="1">
-        <v>12</v>
-      </c>
       <c r="D1116" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1116" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1116" s="1">
         <v>1</v>
       </c>
       <c r="G1116" s="1">
-        <v>14</v>
-      </c>
-      <c r="H1116" s="1">
-        <v>2000</v>
+        <v>35</v>
+      </c>
+      <c r="H1116" s="67">
+        <v>1600</v>
       </c>
       <c r="I1116" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J1116" s="2" t="s">
-        <v>818</v>
+        <v>787</v>
       </c>
       <c r="K1116" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1116" s="1">
         <v>30000</v>
@@ -66431,7 +66584,7 @@
         <v>0</v>
       </c>
       <c r="O1116" s="1" t="s">
-        <v>834</v>
+        <v>1104</v>
       </c>
       <c r="P1116" s="1">
         <v>0</v>
@@ -66439,40 +66592,40 @@
       <c r="Q1116" s="1">
         <v>0</v>
       </c>
-      <c r="R1116" s="67">
+      <c r="R1116" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1117" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1117" s="1">
-        <v>1120902</v>
+      <c r="A1117" s="1" t="s">
+        <v>1077</v>
       </c>
       <c r="B1117" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1117" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1117" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1117" s="1">
         <v>1</v>
       </c>
       <c r="G1117" s="1">
-        <v>15</v>
-      </c>
-      <c r="H1117" s="1">
-        <v>3000</v>
+        <v>36</v>
+      </c>
+      <c r="H1117" s="67">
+        <v>1600</v>
       </c>
       <c r="I1117" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J1117" s="2" t="s">
-        <v>820</v>
+        <v>1114</v>
       </c>
       <c r="K1117" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1117" s="1">
         <v>30000</v>
@@ -66484,7 +66637,7 @@
         <v>0</v>
       </c>
       <c r="O1117" s="1" t="s">
-        <v>835</v>
+        <v>1111</v>
       </c>
       <c r="P1117" s="1">
         <v>0</v>
@@ -66492,40 +66645,40 @@
       <c r="Q1117" s="1">
         <v>0</v>
       </c>
-      <c r="R1117" s="67">
+      <c r="R1117" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1118" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1118" s="1">
-        <v>1120903</v>
+      <c r="A1118" s="1" t="s">
+        <v>1078</v>
       </c>
       <c r="B1118" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1118" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1118" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1118" s="1">
         <v>1</v>
       </c>
       <c r="G1118" s="1">
-        <v>16</v>
-      </c>
-      <c r="H1118" s="1">
-        <v>2000</v>
+        <v>37</v>
+      </c>
+      <c r="H1118" s="67">
+        <v>1600</v>
       </c>
       <c r="I1118" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J1118" s="2" t="s">
-        <v>821</v>
+        <v>1116</v>
       </c>
       <c r="K1118" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1118" s="1">
         <v>30000</v>
@@ -66537,7 +66690,7 @@
         <v>0</v>
       </c>
       <c r="O1118" s="1" t="s">
-        <v>836</v>
+        <v>1112</v>
       </c>
       <c r="P1118" s="1">
         <v>0</v>
@@ -66545,40 +66698,40 @@
       <c r="Q1118" s="1">
         <v>0</v>
       </c>
-      <c r="R1118" s="67">
+      <c r="R1118" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1119" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1119" s="1">
-        <v>1120904</v>
+      <c r="A1119" s="1" t="s">
+        <v>1079</v>
       </c>
       <c r="B1119" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1119" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1119" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1119" s="1">
         <v>1</v>
       </c>
       <c r="G1119" s="1">
-        <v>17</v>
-      </c>
-      <c r="H1119" s="1">
-        <v>2500</v>
+        <v>38</v>
+      </c>
+      <c r="H1119" s="67">
+        <v>1600</v>
       </c>
       <c r="I1119" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J1119" s="2" t="s">
-        <v>816</v>
+        <v>1116</v>
       </c>
       <c r="K1119" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1119" s="1">
         <v>30000</v>
@@ -66590,7 +66743,7 @@
         <v>0</v>
       </c>
       <c r="O1119" s="1" t="s">
-        <v>837</v>
+        <v>1112</v>
       </c>
       <c r="P1119" s="1">
         <v>0</v>
@@ -66598,40 +66751,40 @@
       <c r="Q1119" s="1">
         <v>0</v>
       </c>
-      <c r="R1119" s="67">
+      <c r="R1119" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1120" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1120" s="1">
-        <v>1120905</v>
+      <c r="A1120" s="1" t="s">
+        <v>1080</v>
       </c>
       <c r="B1120" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1120" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1120" s="1">
-        <v>120002</v>
+        <v>110001</v>
       </c>
       <c r="F1120" s="1">
         <v>1</v>
       </c>
       <c r="G1120" s="1">
-        <v>18</v>
-      </c>
-      <c r="H1120" s="1">
-        <v>2000</v>
+        <v>39</v>
+      </c>
+      <c r="H1120" s="67">
+        <v>1</v>
       </c>
       <c r="I1120" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J1120" s="2" t="s">
-        <v>819</v>
+        <v>1116</v>
       </c>
       <c r="K1120" s="1">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="L1120" s="1">
         <v>30000</v>
@@ -66643,7 +66796,7 @@
         <v>0</v>
       </c>
       <c r="O1120" s="1" t="s">
-        <v>838</v>
+        <v>1112</v>
       </c>
       <c r="P1120" s="1">
         <v>0</v>
@@ -66651,40 +66804,40 @@
       <c r="Q1120" s="1">
         <v>0</v>
       </c>
-      <c r="R1120" s="67">
+      <c r="R1120" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="1121" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1121" s="1">
-        <v>1121001</v>
+        <v>1120601</v>
       </c>
       <c r="B1121" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1121" s="1">
         <v>2</v>
       </c>
       <c r="E1121" s="1">
-        <v>120002</v>
+        <v>110002</v>
       </c>
       <c r="F1121" s="1">
         <v>1</v>
       </c>
       <c r="G1121" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H1121" s="1">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="I1121" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J1121" s="2" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="K1121" s="1">
-        <v>160</v>
+        <v>800</v>
       </c>
       <c r="L1121" s="1">
         <v>30000</v>
@@ -66696,7 +66849,7 @@
         <v>0</v>
       </c>
       <c r="O1121" s="1" t="s">
-        <v>153</v>
+        <v>804</v>
       </c>
       <c r="P1121" s="1">
         <v>0</v>
@@ -66705,12 +66858,12 @@
         <v>0</v>
       </c>
       <c r="R1121" s="67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1122" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1122" s="1">
-        <v>1121002</v>
+        <v>1120602</v>
       </c>
       <c r="B1122" s="1">
         <v>12</v>
@@ -66725,16 +66878,16 @@
         <v>1</v>
       </c>
       <c r="G1122" s="1">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H1122" s="1">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="I1122" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J1122" s="2" t="s">
-        <v>822</v>
+        <v>797</v>
       </c>
       <c r="K1122" s="1">
         <v>160</v>
@@ -66749,7 +66902,7 @@
         <v>0</v>
       </c>
       <c r="O1122" s="1" t="s">
-        <v>839</v>
+        <v>805</v>
       </c>
       <c r="P1122" s="1">
         <v>0</v>
@@ -66763,7 +66916,7 @@
     </row>
     <row r="1123" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1123" s="1">
-        <v>1121003</v>
+        <v>1120603</v>
       </c>
       <c r="B1123" s="1">
         <v>12</v>
@@ -66778,16 +66931,16 @@
         <v>1</v>
       </c>
       <c r="G1123" s="1">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1123" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1123" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J1123" s="2" t="s">
-        <v>810</v>
+        <v>792</v>
       </c>
       <c r="K1123" s="1">
         <v>160</v>
@@ -66802,7 +66955,7 @@
         <v>0</v>
       </c>
       <c r="O1123" s="1" t="s">
-        <v>840</v>
+        <v>804</v>
       </c>
       <c r="P1123" s="1">
         <v>0</v>
@@ -66816,7 +66969,7 @@
     </row>
     <row r="1124" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1124" s="1">
-        <v>1121004</v>
+        <v>1120604</v>
       </c>
       <c r="B1124" s="1">
         <v>12</v>
@@ -66831,16 +66984,16 @@
         <v>1</v>
       </c>
       <c r="G1124" s="1">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H1124" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1124" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J1124" s="2" t="s">
-        <v>811</v>
+        <v>795</v>
       </c>
       <c r="K1124" s="1">
         <v>160</v>
@@ -66855,7 +67008,7 @@
         <v>0</v>
       </c>
       <c r="O1124" s="1" t="s">
-        <v>841</v>
+        <v>806</v>
       </c>
       <c r="P1124" s="1">
         <v>0</v>
@@ -66869,7 +67022,7 @@
     </row>
     <row r="1125" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1125" s="1">
-        <v>1121005</v>
+        <v>1120701</v>
       </c>
       <c r="B1125" s="1">
         <v>12</v>
@@ -66884,16 +67037,16 @@
         <v>1</v>
       </c>
       <c r="G1125" s="1">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H1125" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1125" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J1125" s="2" t="s">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="K1125" s="1">
         <v>160</v>
@@ -66908,7 +67061,7 @@
         <v>0</v>
       </c>
       <c r="O1125" s="1" t="s">
-        <v>842</v>
+        <v>807</v>
       </c>
       <c r="P1125" s="1">
         <v>0</v>
@@ -66922,7 +67075,7 @@
     </row>
     <row r="1126" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1126" s="1">
-        <v>1121006</v>
+        <v>1120702</v>
       </c>
       <c r="B1126" s="1">
         <v>12</v>
@@ -66937,16 +67090,16 @@
         <v>1</v>
       </c>
       <c r="G1126" s="1">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H1126" s="1">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="I1126" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J1126" s="2" t="s">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="K1126" s="1">
         <v>160</v>
@@ -66961,7 +67114,7 @@
         <v>0</v>
       </c>
       <c r="O1126" s="1" t="s">
-        <v>843</v>
+        <v>808</v>
       </c>
       <c r="P1126" s="1">
         <v>0</v>
@@ -66974,35 +67127,35 @@
       </c>
     </row>
     <row r="1127" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1127" s="1" t="s">
-        <v>943</v>
+      <c r="A1127" s="1">
+        <v>1120703</v>
       </c>
       <c r="B1127" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1127" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1127" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1127" s="1">
         <v>1</v>
       </c>
       <c r="G1127" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1127" s="1">
         <v>2000</v>
       </c>
       <c r="I1127" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1127" s="2" t="s">
-        <v>916</v>
+        <v>798</v>
       </c>
       <c r="K1127" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1127" s="1">
         <v>30000</v>
@@ -67014,7 +67167,7 @@
         <v>0</v>
       </c>
       <c r="O1127" s="1" t="s">
-        <v>853</v>
+        <v>809</v>
       </c>
       <c r="P1127" s="1">
         <v>0</v>
@@ -67022,40 +67175,40 @@
       <c r="Q1127" s="1">
         <v>0</v>
       </c>
-      <c r="R1127" s="1">
+      <c r="R1127" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1128" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1128" s="1" t="s">
-        <v>944</v>
+      <c r="A1128" s="1">
+        <v>1120704</v>
       </c>
       <c r="B1128" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1128" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1128" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1128" s="1">
         <v>1</v>
       </c>
       <c r="G1128" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H1128" s="1">
         <v>2000</v>
       </c>
       <c r="I1128" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1128" s="2" t="s">
-        <v>917</v>
+        <v>799</v>
       </c>
       <c r="K1128" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1128" s="1">
         <v>30000</v>
@@ -67067,7 +67220,7 @@
         <v>0</v>
       </c>
       <c r="O1128" s="1" t="s">
-        <v>854</v>
+        <v>810</v>
       </c>
       <c r="P1128" s="1">
         <v>0</v>
@@ -67075,40 +67228,40 @@
       <c r="Q1128" s="1">
         <v>0</v>
       </c>
-      <c r="R1128" s="1">
+      <c r="R1128" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1129" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1129" s="1" t="s">
-        <v>945</v>
+      <c r="A1129" s="1">
+        <v>1120801</v>
       </c>
       <c r="B1129" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1129" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1129" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1129" s="1">
         <v>1</v>
       </c>
       <c r="G1129" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H1129" s="1">
         <v>2000</v>
       </c>
       <c r="I1129" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J1129" s="2" t="s">
-        <v>916</v>
+        <v>796</v>
       </c>
       <c r="K1129" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1129" s="1">
         <v>30000</v>
@@ -67120,7 +67273,7 @@
         <v>0</v>
       </c>
       <c r="O1129" s="1" t="s">
-        <v>855</v>
+        <v>807</v>
       </c>
       <c r="P1129" s="1">
         <v>0</v>
@@ -67128,252 +67281,252 @@
       <c r="Q1129" s="1">
         <v>0</v>
       </c>
-      <c r="R1129" s="1">
-        <v>1</v>
+      <c r="R1129" s="67">
+        <v>0</v>
       </c>
     </row>
     <row r="1130" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1130" s="1" t="s">
-        <v>946</v>
+      <c r="A1130" s="1">
+        <v>1120802</v>
       </c>
       <c r="B1130" s="1">
+        <v>12</v>
+      </c>
+      <c r="D1130" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1130" s="1">
+        <v>120002</v>
+      </c>
+      <c r="F1130" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1130" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1130" s="1">
+        <v>2500</v>
+      </c>
+      <c r="I1130" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1130" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="K1130" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1130" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1130" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1130" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1130" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="P1130" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1130" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1130" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1131" s="1">
+        <v>1120803</v>
+      </c>
+      <c r="B1131" s="1">
+        <v>12</v>
+      </c>
+      <c r="D1131" s="1">
+        <v>2</v>
+      </c>
+      <c r="E1131" s="1">
+        <v>120002</v>
+      </c>
+      <c r="F1131" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1131" s="1">
         <v>11</v>
-      </c>
-      <c r="D1130" s="1">
-        <v>3</v>
-      </c>
-      <c r="E1130" s="1">
-        <v>110003</v>
-      </c>
-      <c r="F1130" s="1">
-        <v>1</v>
-      </c>
-      <c r="G1130" s="1">
-        <v>4</v>
-      </c>
-      <c r="H1130" s="1">
-        <v>2000</v>
-      </c>
-      <c r="I1130" s="1">
-        <v>2</v>
-      </c>
-      <c r="J1130" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="K1130" s="1">
-        <v>150</v>
-      </c>
-      <c r="L1130" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1130" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1130" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1130" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="P1130" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1130" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1130" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1131" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1131" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="B1131" s="1">
-        <v>11</v>
-      </c>
-      <c r="D1131" s="1">
-        <v>3</v>
-      </c>
-      <c r="E1131" s="1">
-        <v>110003</v>
-      </c>
-      <c r="F1131" s="1">
-        <v>1</v>
-      </c>
-      <c r="G1131" s="1">
-        <v>5</v>
       </c>
       <c r="H1131" s="1">
         <v>2000</v>
       </c>
       <c r="I1131" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1131" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="K1131" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1131" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1131" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1131" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1131" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="P1131" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1131" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1131" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1132" s="1">
+        <v>1120804</v>
+      </c>
+      <c r="B1132" s="1">
+        <v>12</v>
+      </c>
+      <c r="D1132" s="1">
         <v>2</v>
       </c>
-      <c r="J1131" s="2" t="s">
-        <v>917</v>
-      </c>
-      <c r="K1131" s="1">
-        <v>150</v>
-      </c>
-      <c r="L1131" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1131" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1131" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1131" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="P1131" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1131" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1131" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1132" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1132" s="1" t="s">
-        <v>948</v>
-      </c>
-      <c r="B1132" s="1">
-        <v>11</v>
-      </c>
-      <c r="D1132" s="1">
-        <v>3</v>
-      </c>
       <c r="E1132" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1132" s="1">
         <v>1</v>
       </c>
       <c r="G1132" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H1132" s="1">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I1132" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1132" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="K1132" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1132" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1132" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1132" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1132" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="P1132" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1132" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1132" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1133" s="1">
+        <v>1120805</v>
+      </c>
+      <c r="B1133" s="1">
+        <v>12</v>
+      </c>
+      <c r="D1133" s="1">
         <v>2</v>
       </c>
-      <c r="J1132" s="2" t="s">
-        <v>918</v>
-      </c>
-      <c r="K1132" s="1">
-        <v>150</v>
-      </c>
-      <c r="L1132" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1132" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1132" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1132" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="P1132" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1132" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1132" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1133" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1133" s="1" t="s">
-        <v>949</v>
-      </c>
-      <c r="B1133" s="1">
-        <v>11</v>
-      </c>
-      <c r="D1133" s="1">
-        <v>3</v>
-      </c>
       <c r="E1133" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1133" s="1">
         <v>1</v>
       </c>
       <c r="G1133" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1133" s="1">
         <v>2000</v>
       </c>
       <c r="I1133" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1133" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="K1133" s="1">
+        <v>160</v>
+      </c>
+      <c r="L1133" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1133" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1133" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1133" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="P1133" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1133" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1133" s="67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1134" s="1">
+        <v>1120901</v>
+      </c>
+      <c r="B1134" s="1">
+        <v>12</v>
+      </c>
+      <c r="D1134" s="1">
         <v>2</v>
       </c>
-      <c r="J1133" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="K1133" s="1">
-        <v>150</v>
-      </c>
-      <c r="L1133" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1133" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1133" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1133" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="P1133" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1133" s="1">
-        <v>0</v>
-      </c>
-      <c r="R1133" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1134" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1134" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="B1134" s="1">
-        <v>11</v>
-      </c>
-      <c r="D1134" s="1">
-        <v>3</v>
-      </c>
       <c r="E1134" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1134" s="1">
         <v>1</v>
       </c>
       <c r="G1134" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H1134" s="1">
         <v>2000</v>
       </c>
       <c r="I1134" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J1134" s="2" t="s">
-        <v>918</v>
+        <v>799</v>
       </c>
       <c r="K1134" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1134" s="1">
         <v>30000</v>
@@ -67385,7 +67538,7 @@
         <v>0</v>
       </c>
       <c r="O1134" s="1" t="s">
-        <v>860</v>
+        <v>815</v>
       </c>
       <c r="P1134" s="1">
         <v>0</v>
@@ -67393,40 +67546,40 @@
       <c r="Q1134" s="1">
         <v>0</v>
       </c>
-      <c r="R1134" s="1">
+      <c r="R1134" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1135" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1135" s="1" t="s">
-        <v>951</v>
+      <c r="A1135" s="1">
+        <v>1120902</v>
       </c>
       <c r="B1135" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1135" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1135" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1135" s="1">
         <v>1</v>
       </c>
       <c r="G1135" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1135" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I1135" s="1">
         <v>9</v>
       </c>
-      <c r="H1135" s="1">
-        <v>2000</v>
-      </c>
-      <c r="I1135" s="1">
-        <v>3</v>
-      </c>
       <c r="J1135" s="2" t="s">
-        <v>917</v>
+        <v>801</v>
       </c>
       <c r="K1135" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1135" s="1">
         <v>30000</v>
@@ -67438,7 +67591,7 @@
         <v>0</v>
       </c>
       <c r="O1135" s="1" t="s">
-        <v>861</v>
+        <v>816</v>
       </c>
       <c r="P1135" s="1">
         <v>0</v>
@@ -67446,40 +67599,40 @@
       <c r="Q1135" s="1">
         <v>0</v>
       </c>
-      <c r="R1135" s="1">
+      <c r="R1135" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1136" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1136" s="1" t="s">
-        <v>952</v>
+      <c r="A1136" s="1">
+        <v>1120903</v>
       </c>
       <c r="B1136" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1136" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1136" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1136" s="1">
         <v>1</v>
       </c>
       <c r="G1136" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H1136" s="1">
         <v>2000</v>
       </c>
       <c r="I1136" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J1136" s="2" t="s">
-        <v>918</v>
+        <v>802</v>
       </c>
       <c r="K1136" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1136" s="1">
         <v>30000</v>
@@ -67491,7 +67644,7 @@
         <v>0</v>
       </c>
       <c r="O1136" s="1" t="s">
-        <v>862</v>
+        <v>817</v>
       </c>
       <c r="P1136" s="1">
         <v>0</v>
@@ -67499,40 +67652,40 @@
       <c r="Q1136" s="1">
         <v>0</v>
       </c>
-      <c r="R1136" s="1">
-        <v>1</v>
+      <c r="R1136" s="67">
+        <v>0</v>
       </c>
     </row>
     <row r="1137" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1137" s="1" t="s">
-        <v>953</v>
+      <c r="A1137" s="1">
+        <v>1120904</v>
       </c>
       <c r="B1137" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1137" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1137" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1137" s="1">
         <v>1</v>
       </c>
       <c r="G1137" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H1137" s="1">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="I1137" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J1137" s="2" t="s">
-        <v>917</v>
+        <v>797</v>
       </c>
       <c r="K1137" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1137" s="1">
         <v>30000</v>
@@ -67544,7 +67697,7 @@
         <v>0</v>
       </c>
       <c r="O1137" s="1" t="s">
-        <v>863</v>
+        <v>818</v>
       </c>
       <c r="P1137" s="1">
         <v>0</v>
@@ -67552,40 +67705,40 @@
       <c r="Q1137" s="1">
         <v>0</v>
       </c>
-      <c r="R1137" s="1">
+      <c r="R1137" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1138" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1138" s="1" t="s">
-        <v>954</v>
+      <c r="A1138" s="1">
+        <v>1120905</v>
       </c>
       <c r="B1138" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1138" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1138" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1138" s="1">
         <v>1</v>
       </c>
       <c r="G1138" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H1138" s="1">
         <v>2000</v>
       </c>
       <c r="I1138" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J1138" s="2" t="s">
-        <v>918</v>
+        <v>800</v>
       </c>
       <c r="K1138" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1138" s="1">
         <v>30000</v>
@@ -67597,7 +67750,7 @@
         <v>0</v>
       </c>
       <c r="O1138" s="1" t="s">
-        <v>864</v>
+        <v>819</v>
       </c>
       <c r="P1138" s="1">
         <v>0</v>
@@ -67605,40 +67758,40 @@
       <c r="Q1138" s="1">
         <v>0</v>
       </c>
-      <c r="R1138" s="1">
+      <c r="R1138" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1139" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1139" s="1" t="s">
-        <v>955</v>
+      <c r="A1139" s="1">
+        <v>1121001</v>
       </c>
       <c r="B1139" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1139" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1139" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1139" s="1">
         <v>1</v>
       </c>
       <c r="G1139" s="1">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H1139" s="1">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="I1139" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J1139" s="2" t="s">
-        <v>920</v>
+        <v>791</v>
       </c>
       <c r="K1139" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1139" s="1">
         <v>30000</v>
@@ -67650,7 +67803,7 @@
         <v>0</v>
       </c>
       <c r="O1139" s="1" t="s">
-        <v>865</v>
+        <v>153</v>
       </c>
       <c r="P1139" s="1">
         <v>0</v>
@@ -67658,40 +67811,40 @@
       <c r="Q1139" s="1">
         <v>0</v>
       </c>
-      <c r="R1139" s="1">
-        <v>0</v>
+      <c r="R1139" s="67">
+        <v>1</v>
       </c>
     </row>
     <row r="1140" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1140" s="1" t="s">
-        <v>956</v>
+      <c r="A1140" s="1">
+        <v>1121002</v>
       </c>
       <c r="B1140" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1140" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1140" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1140" s="1">
         <v>1</v>
       </c>
       <c r="G1140" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H1140" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1140" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J1140" s="2" t="s">
-        <v>921</v>
+        <v>803</v>
       </c>
       <c r="K1140" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1140" s="1">
         <v>30000</v>
@@ -67703,7 +67856,7 @@
         <v>0</v>
       </c>
       <c r="O1140" s="1" t="s">
-        <v>866</v>
+        <v>820</v>
       </c>
       <c r="P1140" s="1">
         <v>0</v>
@@ -67711,40 +67864,40 @@
       <c r="Q1140" s="1">
         <v>0</v>
       </c>
-      <c r="R1140" s="1">
+      <c r="R1140" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1141" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1141" s="1" t="s">
-        <v>957</v>
+      <c r="A1141" s="1">
+        <v>1121003</v>
       </c>
       <c r="B1141" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1141" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1141" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1141" s="1">
         <v>1</v>
       </c>
       <c r="G1141" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H1141" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1141" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J1141" s="2" t="s">
-        <v>922</v>
+        <v>793</v>
       </c>
       <c r="K1141" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1141" s="1">
         <v>30000</v>
@@ -67756,7 +67909,7 @@
         <v>0</v>
       </c>
       <c r="O1141" s="1" t="s">
-        <v>867</v>
+        <v>821</v>
       </c>
       <c r="P1141" s="1">
         <v>0</v>
@@ -67764,40 +67917,40 @@
       <c r="Q1141" s="1">
         <v>0</v>
       </c>
-      <c r="R1141" s="1">
+      <c r="R1141" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1142" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1142" s="1" t="s">
-        <v>958</v>
+      <c r="A1142" s="1">
+        <v>1121004</v>
       </c>
       <c r="B1142" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1142" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1142" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1142" s="1">
         <v>1</v>
       </c>
       <c r="G1142" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H1142" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1142" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J1142" s="2" t="s">
-        <v>918</v>
+        <v>794</v>
       </c>
       <c r="K1142" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1142" s="1">
         <v>30000</v>
@@ -67809,7 +67962,7 @@
         <v>0</v>
       </c>
       <c r="O1142" s="1" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
       <c r="P1142" s="1">
         <v>0</v>
@@ -67817,40 +67970,40 @@
       <c r="Q1142" s="1">
         <v>0</v>
       </c>
-      <c r="R1142" s="1">
+      <c r="R1142" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1143" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1143" s="1" t="s">
-        <v>959</v>
+      <c r="A1143" s="1">
+        <v>1121005</v>
       </c>
       <c r="B1143" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1143" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1143" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1143" s="1">
         <v>1</v>
       </c>
       <c r="G1143" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H1143" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1143" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J1143" s="2" t="s">
-        <v>923</v>
+        <v>796</v>
       </c>
       <c r="K1143" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1143" s="1">
         <v>30000</v>
@@ -67862,7 +68015,7 @@
         <v>0</v>
       </c>
       <c r="O1143" s="1" t="s">
-        <v>868</v>
+        <v>823</v>
       </c>
       <c r="P1143" s="1">
         <v>0</v>
@@ -67870,40 +68023,40 @@
       <c r="Q1143" s="1">
         <v>0</v>
       </c>
-      <c r="R1143" s="1">
+      <c r="R1143" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1144" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1144" s="1" t="s">
-        <v>960</v>
+      <c r="A1144" s="1">
+        <v>1121006</v>
       </c>
       <c r="B1144" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1144" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1144" s="1">
-        <v>110003</v>
+        <v>120002</v>
       </c>
       <c r="F1144" s="1">
         <v>1</v>
       </c>
       <c r="G1144" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H1144" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1144" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J1144" s="2" t="s">
-        <v>924</v>
+        <v>794</v>
       </c>
       <c r="K1144" s="1">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L1144" s="1">
         <v>30000</v>
@@ -67915,7 +68068,7 @@
         <v>0</v>
       </c>
       <c r="O1144" s="1" t="s">
-        <v>869</v>
+        <v>824</v>
       </c>
       <c r="P1144" s="1">
         <v>0</v>
@@ -67923,13 +68076,13 @@
       <c r="Q1144" s="1">
         <v>0</v>
       </c>
-      <c r="R1144" s="1">
+      <c r="R1144" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="1145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1145" s="1" t="s">
-        <v>961</v>
+        <v>920</v>
       </c>
       <c r="B1145" s="1">
         <v>11</v>
@@ -67944,16 +68097,16 @@
         <v>1</v>
       </c>
       <c r="G1145" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H1145" s="1">
         <v>2000</v>
       </c>
       <c r="I1145" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J1145" s="2" t="s">
-        <v>924</v>
+        <v>893</v>
       </c>
       <c r="K1145" s="1">
         <v>150</v>
@@ -67968,7 +68121,7 @@
         <v>0</v>
       </c>
       <c r="O1145" s="1" t="s">
-        <v>870</v>
+        <v>830</v>
       </c>
       <c r="P1145" s="1">
         <v>0</v>
@@ -67982,7 +68135,7 @@
     </row>
     <row r="1146" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1146" s="1" t="s">
-        <v>962</v>
+        <v>921</v>
       </c>
       <c r="B1146" s="1">
         <v>11</v>
@@ -67997,16 +68150,16 @@
         <v>1</v>
       </c>
       <c r="G1146" s="1">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H1146" s="1">
         <v>2000</v>
       </c>
       <c r="I1146" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J1146" s="2" t="s">
-        <v>925</v>
+        <v>894</v>
       </c>
       <c r="K1146" s="1">
         <v>150</v>
@@ -68021,7 +68174,7 @@
         <v>0</v>
       </c>
       <c r="O1146" s="1" t="s">
-        <v>871</v>
+        <v>831</v>
       </c>
       <c r="P1146" s="1">
         <v>0</v>
@@ -68030,12 +68183,12 @@
         <v>0</v>
       </c>
       <c r="R1146" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1147" s="1" t="s">
-        <v>963</v>
+        <v>922</v>
       </c>
       <c r="B1147" s="1">
         <v>11</v>
@@ -68050,16 +68203,16 @@
         <v>1</v>
       </c>
       <c r="G1147" s="1">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H1147" s="1">
         <v>2000</v>
       </c>
       <c r="I1147" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J1147" s="2" t="s">
-        <v>921</v>
+        <v>893</v>
       </c>
       <c r="K1147" s="1">
         <v>150</v>
@@ -68074,7 +68227,7 @@
         <v>0</v>
       </c>
       <c r="O1147" s="1" t="s">
-        <v>866</v>
+        <v>832</v>
       </c>
       <c r="P1147" s="1">
         <v>0</v>
@@ -68083,12 +68236,12 @@
         <v>0</v>
       </c>
       <c r="R1147" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1148" s="1" t="s">
-        <v>964</v>
+        <v>923</v>
       </c>
       <c r="B1148" s="1">
         <v>11</v>
@@ -68103,16 +68256,16 @@
         <v>1</v>
       </c>
       <c r="G1148" s="1">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H1148" s="1">
         <v>2000</v>
       </c>
       <c r="I1148" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1148" s="2" t="s">
-        <v>926</v>
+        <v>893</v>
       </c>
       <c r="K1148" s="1">
         <v>150</v>
@@ -68127,7 +68280,7 @@
         <v>0</v>
       </c>
       <c r="O1148" s="1" t="s">
-        <v>872</v>
+        <v>833</v>
       </c>
       <c r="P1148" s="1">
         <v>0</v>
@@ -68141,7 +68294,7 @@
     </row>
     <row r="1149" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1149" s="1" t="s">
-        <v>965</v>
+        <v>924</v>
       </c>
       <c r="B1149" s="1">
         <v>11</v>
@@ -68156,16 +68309,16 @@
         <v>1</v>
       </c>
       <c r="G1149" s="1">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H1149" s="1">
         <v>2000</v>
       </c>
       <c r="I1149" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1149" s="2" t="s">
-        <v>921</v>
+        <v>894</v>
       </c>
       <c r="K1149" s="1">
         <v>150</v>
@@ -68180,7 +68333,7 @@
         <v>0</v>
       </c>
       <c r="O1149" s="1" t="s">
-        <v>866</v>
+        <v>834</v>
       </c>
       <c r="P1149" s="1">
         <v>0</v>
@@ -68194,7 +68347,7 @@
     </row>
     <row r="1150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1150" s="1" t="s">
-        <v>966</v>
+        <v>925</v>
       </c>
       <c r="B1150" s="1">
         <v>11</v>
@@ -68209,16 +68362,16 @@
         <v>1</v>
       </c>
       <c r="G1150" s="1">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H1150" s="1">
         <v>2000</v>
       </c>
       <c r="I1150" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1150" s="2" t="s">
-        <v>926</v>
+        <v>895</v>
       </c>
       <c r="K1150" s="1">
         <v>150</v>
@@ -68233,7 +68386,7 @@
         <v>0</v>
       </c>
       <c r="O1150" s="1" t="s">
-        <v>873</v>
+        <v>835</v>
       </c>
       <c r="P1150" s="1">
         <v>0</v>
@@ -68247,7 +68400,7 @@
     </row>
     <row r="1151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1151" s="1" t="s">
-        <v>967</v>
+        <v>926</v>
       </c>
       <c r="B1151" s="1">
         <v>11</v>
@@ -68262,16 +68415,16 @@
         <v>1</v>
       </c>
       <c r="G1151" s="1">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="H1151" s="1">
         <v>2000</v>
       </c>
       <c r="I1151" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J1151" s="2" t="s">
-        <v>921</v>
+        <v>896</v>
       </c>
       <c r="K1151" s="1">
         <v>150</v>
@@ -68286,7 +68439,7 @@
         <v>0</v>
       </c>
       <c r="O1151" s="1" t="s">
-        <v>874</v>
+        <v>836</v>
       </c>
       <c r="P1151" s="1">
         <v>0</v>
@@ -68300,7 +68453,7 @@
     </row>
     <row r="1152" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1152" s="1" t="s">
-        <v>968</v>
+        <v>927</v>
       </c>
       <c r="B1152" s="1">
         <v>11</v>
@@ -68315,16 +68468,16 @@
         <v>1</v>
       </c>
       <c r="G1152" s="1">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="H1152" s="1">
         <v>2000</v>
       </c>
       <c r="I1152" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J1152" s="2" t="s">
-        <v>927</v>
+        <v>895</v>
       </c>
       <c r="K1152" s="1">
         <v>150</v>
@@ -68339,7 +68492,7 @@
         <v>0</v>
       </c>
       <c r="O1152" s="1" t="s">
-        <v>875</v>
+        <v>837</v>
       </c>
       <c r="P1152" s="1">
         <v>0</v>
@@ -68353,7 +68506,7 @@
     </row>
     <row r="1153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1153" s="1" t="s">
-        <v>969</v>
+        <v>928</v>
       </c>
       <c r="B1153" s="1">
         <v>11</v>
@@ -68368,16 +68521,16 @@
         <v>1</v>
       </c>
       <c r="G1153" s="1">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H1153" s="1">
         <v>2000</v>
       </c>
       <c r="I1153" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J1153" s="2" t="s">
-        <v>926</v>
+        <v>894</v>
       </c>
       <c r="K1153" s="1">
         <v>150</v>
@@ -68392,7 +68545,7 @@
         <v>0</v>
       </c>
       <c r="O1153" s="1" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
       <c r="P1153" s="1">
         <v>0</v>
@@ -68406,7 +68559,7 @@
     </row>
     <row r="1154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1154" s="1" t="s">
-        <v>970</v>
+        <v>929</v>
       </c>
       <c r="B1154" s="1">
         <v>11</v>
@@ -68421,16 +68574,16 @@
         <v>1</v>
       </c>
       <c r="G1154" s="1">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H1154" s="1">
         <v>2000</v>
       </c>
       <c r="I1154" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J1154" s="2" t="s">
-        <v>925</v>
+        <v>895</v>
       </c>
       <c r="K1154" s="1">
         <v>150</v>
@@ -68445,7 +68598,7 @@
         <v>0</v>
       </c>
       <c r="O1154" s="1" t="s">
-        <v>877</v>
+        <v>839</v>
       </c>
       <c r="P1154" s="1">
         <v>0</v>
@@ -68454,12 +68607,12 @@
         <v>0</v>
       </c>
       <c r="R1154" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1155" s="1" t="s">
-        <v>971</v>
+        <v>930</v>
       </c>
       <c r="B1155" s="1">
         <v>11</v>
@@ -68474,16 +68627,16 @@
         <v>1</v>
       </c>
       <c r="G1155" s="1">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H1155" s="1">
         <v>2000</v>
       </c>
       <c r="I1155" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J1155" s="2" t="s">
-        <v>926</v>
+        <v>894</v>
       </c>
       <c r="K1155" s="1">
         <v>150</v>
@@ -68498,7 +68651,7 @@
         <v>0</v>
       </c>
       <c r="O1155" s="1" t="s">
-        <v>878</v>
+        <v>840</v>
       </c>
       <c r="P1155" s="1">
         <v>0</v>
@@ -68512,7 +68665,7 @@
     </row>
     <row r="1156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1156" s="1" t="s">
-        <v>972</v>
+        <v>931</v>
       </c>
       <c r="B1156" s="1">
         <v>11</v>
@@ -68527,16 +68680,16 @@
         <v>1</v>
       </c>
       <c r="G1156" s="1">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H1156" s="1">
         <v>2000</v>
       </c>
       <c r="I1156" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J1156" s="2" t="s">
-        <v>928</v>
+        <v>895</v>
       </c>
       <c r="K1156" s="1">
         <v>150</v>
@@ -68551,7 +68704,7 @@
         <v>0</v>
       </c>
       <c r="O1156" s="1" t="s">
-        <v>879</v>
+        <v>841</v>
       </c>
       <c r="P1156" s="1">
         <v>0</v>
@@ -68565,7 +68718,7 @@
     </row>
     <row r="1157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1157" s="1" t="s">
-        <v>973</v>
+        <v>932</v>
       </c>
       <c r="B1157" s="1">
         <v>11</v>
@@ -68580,16 +68733,16 @@
         <v>1</v>
       </c>
       <c r="G1157" s="1">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H1157" s="1">
         <v>2000</v>
       </c>
       <c r="I1157" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J1157" s="2" t="s">
-        <v>925</v>
+        <v>897</v>
       </c>
       <c r="K1157" s="1">
         <v>150</v>
@@ -68604,7 +68757,7 @@
         <v>0</v>
       </c>
       <c r="O1157" s="1" t="s">
-        <v>866</v>
+        <v>842</v>
       </c>
       <c r="P1157" s="1">
         <v>0</v>
@@ -68618,7 +68771,7 @@
     </row>
     <row r="1158" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1158" s="1" t="s">
-        <v>974</v>
+        <v>933</v>
       </c>
       <c r="B1158" s="1">
         <v>11</v>
@@ -68633,16 +68786,16 @@
         <v>1</v>
       </c>
       <c r="G1158" s="1">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="H1158" s="1">
         <v>2000</v>
       </c>
       <c r="I1158" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J1158" s="2" t="s">
-        <v>929</v>
+        <v>898</v>
       </c>
       <c r="K1158" s="1">
         <v>150</v>
@@ -68657,7 +68810,7 @@
         <v>0</v>
       </c>
       <c r="O1158" s="1" t="s">
-        <v>872</v>
+        <v>843</v>
       </c>
       <c r="P1158" s="1">
         <v>0</v>
@@ -68671,7 +68824,7 @@
     </row>
     <row r="1159" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1159" s="1" t="s">
-        <v>975</v>
+        <v>934</v>
       </c>
       <c r="B1159" s="1">
         <v>11</v>
@@ -68686,16 +68839,16 @@
         <v>1</v>
       </c>
       <c r="G1159" s="1">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H1159" s="1">
         <v>2000</v>
       </c>
       <c r="I1159" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J1159" s="2" t="s">
-        <v>925</v>
+        <v>899</v>
       </c>
       <c r="K1159" s="1">
         <v>150</v>
@@ -68710,7 +68863,7 @@
         <v>0</v>
       </c>
       <c r="O1159" s="1" t="s">
-        <v>866</v>
+        <v>844</v>
       </c>
       <c r="P1159" s="1">
         <v>0</v>
@@ -68724,7 +68877,7 @@
     </row>
     <row r="1160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1160" s="1" t="s">
-        <v>976</v>
+        <v>935</v>
       </c>
       <c r="B1160" s="1">
         <v>11</v>
@@ -68739,16 +68892,16 @@
         <v>1</v>
       </c>
       <c r="G1160" s="1">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H1160" s="1">
         <v>2000</v>
       </c>
       <c r="I1160" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J1160" s="2" t="s">
-        <v>930</v>
+        <v>895</v>
       </c>
       <c r="K1160" s="1">
         <v>150</v>
@@ -68763,7 +68916,7 @@
         <v>0</v>
       </c>
       <c r="O1160" s="1" t="s">
-        <v>880</v>
+        <v>837</v>
       </c>
       <c r="P1160" s="1">
         <v>0</v>
@@ -68777,7 +68930,7 @@
     </row>
     <row r="1161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1161" s="1" t="s">
-        <v>977</v>
+        <v>936</v>
       </c>
       <c r="B1161" s="1">
         <v>11</v>
@@ -68792,16 +68945,16 @@
         <v>1</v>
       </c>
       <c r="G1161" s="1">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H1161" s="1">
         <v>2000</v>
       </c>
       <c r="I1161" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J1161" s="2" t="s">
-        <v>929</v>
+        <v>900</v>
       </c>
       <c r="K1161" s="1">
         <v>150</v>
@@ -68816,7 +68969,7 @@
         <v>0</v>
       </c>
       <c r="O1161" s="1" t="s">
-        <v>881</v>
+        <v>845</v>
       </c>
       <c r="P1161" s="1">
         <v>0</v>
@@ -68830,7 +68983,7 @@
     </row>
     <row r="1162" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1162" s="1" t="s">
-        <v>978</v>
+        <v>937</v>
       </c>
       <c r="B1162" s="1">
         <v>11</v>
@@ -68845,16 +68998,16 @@
         <v>1</v>
       </c>
       <c r="G1162" s="1">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H1162" s="1">
         <v>2000</v>
       </c>
       <c r="I1162" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J1162" s="2" t="s">
-        <v>931</v>
+        <v>901</v>
       </c>
       <c r="K1162" s="1">
         <v>150</v>
@@ -68869,7 +69022,7 @@
         <v>0</v>
       </c>
       <c r="O1162" s="1" t="s">
-        <v>882</v>
+        <v>846</v>
       </c>
       <c r="P1162" s="1">
         <v>0</v>
@@ -68883,7 +69036,7 @@
     </row>
     <row r="1163" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1163" s="1" t="s">
-        <v>979</v>
+        <v>938</v>
       </c>
       <c r="B1163" s="1">
         <v>11</v>
@@ -68898,16 +69051,16 @@
         <v>1</v>
       </c>
       <c r="G1163" s="1">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H1163" s="1">
         <v>2000</v>
       </c>
       <c r="I1163" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J1163" s="2" t="s">
-        <v>932</v>
+        <v>901</v>
       </c>
       <c r="K1163" s="1">
         <v>150</v>
@@ -68922,7 +69075,7 @@
         <v>0</v>
       </c>
       <c r="O1163" s="1" t="s">
-        <v>883</v>
+        <v>847</v>
       </c>
       <c r="P1163" s="1">
         <v>0</v>
@@ -68936,7 +69089,7 @@
     </row>
     <row r="1164" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1164" s="1" t="s">
-        <v>980</v>
+        <v>939</v>
       </c>
       <c r="B1164" s="1">
         <v>11</v>
@@ -68951,16 +69104,16 @@
         <v>1</v>
       </c>
       <c r="G1164" s="1">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="H1164" s="1">
         <v>2000</v>
       </c>
       <c r="I1164" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J1164" s="2" t="s">
-        <v>933</v>
+        <v>902</v>
       </c>
       <c r="K1164" s="1">
         <v>150</v>
@@ -68975,7 +69128,7 @@
         <v>0</v>
       </c>
       <c r="O1164" s="1" t="s">
-        <v>884</v>
+        <v>848</v>
       </c>
       <c r="P1164" s="1">
         <v>0</v>
@@ -68984,12 +69137,12 @@
         <v>0</v>
       </c>
       <c r="R1164" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1165" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1165" s="1" t="s">
-        <v>981</v>
+        <v>940</v>
       </c>
       <c r="B1165" s="1">
         <v>11</v>
@@ -69004,16 +69157,16 @@
         <v>1</v>
       </c>
       <c r="G1165" s="1">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H1165" s="1">
         <v>2000</v>
       </c>
       <c r="I1165" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J1165" s="2" t="s">
-        <v>934</v>
+        <v>898</v>
       </c>
       <c r="K1165" s="1">
         <v>150</v>
@@ -69028,7 +69181,7 @@
         <v>0</v>
       </c>
       <c r="O1165" s="1" t="s">
-        <v>885</v>
+        <v>843</v>
       </c>
       <c r="P1165" s="1">
         <v>0</v>
@@ -69042,7 +69195,7 @@
     </row>
     <row r="1166" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1166" s="1" t="s">
-        <v>982</v>
+        <v>941</v>
       </c>
       <c r="B1166" s="1">
         <v>11</v>
@@ -69057,16 +69210,16 @@
         <v>1</v>
       </c>
       <c r="G1166" s="1">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H1166" s="1">
         <v>2000</v>
       </c>
       <c r="I1166" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J1166" s="2" t="s">
-        <v>935</v>
+        <v>903</v>
       </c>
       <c r="K1166" s="1">
         <v>150</v>
@@ -69081,7 +69234,7 @@
         <v>0</v>
       </c>
       <c r="O1166" s="1" t="s">
-        <v>886</v>
+        <v>849</v>
       </c>
       <c r="P1166" s="1">
         <v>0</v>
@@ -69095,7 +69248,7 @@
     </row>
     <row r="1167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1167" s="1" t="s">
-        <v>983</v>
+        <v>942</v>
       </c>
       <c r="B1167" s="1">
         <v>11</v>
@@ -69110,16 +69263,16 @@
         <v>1</v>
       </c>
       <c r="G1167" s="1">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="H1167" s="1">
         <v>2000</v>
       </c>
       <c r="I1167" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J1167" s="2" t="s">
-        <v>931</v>
+        <v>898</v>
       </c>
       <c r="K1167" s="1">
         <v>150</v>
@@ -69134,7 +69287,7 @@
         <v>0</v>
       </c>
       <c r="O1167" s="1" t="s">
-        <v>887</v>
+        <v>843</v>
       </c>
       <c r="P1167" s="1">
         <v>0</v>
@@ -69148,7 +69301,7 @@
     </row>
     <row r="1168" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1168" s="1" t="s">
-        <v>984</v>
+        <v>943</v>
       </c>
       <c r="B1168" s="1">
         <v>11</v>
@@ -69163,16 +69316,16 @@
         <v>1</v>
       </c>
       <c r="G1168" s="1">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H1168" s="1">
         <v>2000</v>
       </c>
       <c r="I1168" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J1168" s="2" t="s">
-        <v>931</v>
+        <v>903</v>
       </c>
       <c r="K1168" s="1">
         <v>150</v>
@@ -69187,7 +69340,7 @@
         <v>0</v>
       </c>
       <c r="O1168" s="1" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
       <c r="P1168" s="1">
         <v>0</v>
@@ -69201,7 +69354,7 @@
     </row>
     <row r="1169" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1169" s="1" t="s">
-        <v>985</v>
+        <v>944</v>
       </c>
       <c r="B1169" s="1">
         <v>11</v>
@@ -69216,16 +69369,16 @@
         <v>1</v>
       </c>
       <c r="G1169" s="1">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H1169" s="1">
         <v>2000</v>
       </c>
       <c r="I1169" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J1169" s="2" t="s">
-        <v>936</v>
+        <v>898</v>
       </c>
       <c r="K1169" s="1">
         <v>150</v>
@@ -69240,7 +69393,7 @@
         <v>0</v>
       </c>
       <c r="O1169" s="1" t="s">
-        <v>889</v>
+        <v>851</v>
       </c>
       <c r="P1169" s="1">
         <v>0</v>
@@ -69254,7 +69407,7 @@
     </row>
     <row r="1170" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1170" s="1" t="s">
-        <v>986</v>
+        <v>945</v>
       </c>
       <c r="B1170" s="1">
         <v>11</v>
@@ -69269,16 +69422,16 @@
         <v>1</v>
       </c>
       <c r="G1170" s="1">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H1170" s="1">
         <v>2000</v>
       </c>
       <c r="I1170" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J1170" s="2" t="s">
-        <v>933</v>
+        <v>904</v>
       </c>
       <c r="K1170" s="1">
         <v>150</v>
@@ -69293,7 +69446,7 @@
         <v>0</v>
       </c>
       <c r="O1170" s="1" t="s">
-        <v>890</v>
+        <v>852</v>
       </c>
       <c r="P1170" s="1">
         <v>0</v>
@@ -69307,7 +69460,7 @@
     </row>
     <row r="1171" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1171" s="1" t="s">
-        <v>987</v>
+        <v>946</v>
       </c>
       <c r="B1171" s="1">
         <v>11</v>
@@ -69322,16 +69475,16 @@
         <v>1</v>
       </c>
       <c r="G1171" s="1">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H1171" s="1">
         <v>2000</v>
       </c>
       <c r="I1171" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J1171" s="2" t="s">
-        <v>934</v>
+        <v>903</v>
       </c>
       <c r="K1171" s="1">
         <v>150</v>
@@ -69346,7 +69499,7 @@
         <v>0</v>
       </c>
       <c r="O1171" s="1" t="s">
-        <v>891</v>
+        <v>853</v>
       </c>
       <c r="P1171" s="1">
         <v>0</v>
@@ -69360,7 +69513,7 @@
     </row>
     <row r="1172" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1172" s="1" t="s">
-        <v>988</v>
+        <v>947</v>
       </c>
       <c r="B1172" s="1">
         <v>11</v>
@@ -69375,16 +69528,16 @@
         <v>1</v>
       </c>
       <c r="G1172" s="1">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H1172" s="1">
         <v>2000</v>
       </c>
       <c r="I1172" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J1172" s="2" t="s">
-        <v>936</v>
+        <v>902</v>
       </c>
       <c r="K1172" s="1">
         <v>150</v>
@@ -69399,7 +69552,7 @@
         <v>0</v>
       </c>
       <c r="O1172" s="1" t="s">
-        <v>892</v>
+        <v>854</v>
       </c>
       <c r="P1172" s="1">
         <v>0</v>
@@ -69413,7 +69566,7 @@
     </row>
     <row r="1173" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1173" s="1" t="s">
-        <v>989</v>
+        <v>948</v>
       </c>
       <c r="B1173" s="1">
         <v>11</v>
@@ -69428,16 +69581,16 @@
         <v>1</v>
       </c>
       <c r="G1173" s="1">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="H1173" s="1">
         <v>2000</v>
       </c>
       <c r="I1173" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J1173" s="2" t="s">
-        <v>937</v>
+        <v>903</v>
       </c>
       <c r="K1173" s="1">
         <v>150</v>
@@ -69452,7 +69605,7 @@
         <v>0</v>
       </c>
       <c r="O1173" s="1" t="s">
-        <v>893</v>
+        <v>855</v>
       </c>
       <c r="P1173" s="1">
         <v>0</v>
@@ -69466,7 +69619,7 @@
     </row>
     <row r="1174" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1174" s="1" t="s">
-        <v>990</v>
+        <v>949</v>
       </c>
       <c r="B1174" s="1">
         <v>11</v>
@@ -69481,16 +69634,16 @@
         <v>1</v>
       </c>
       <c r="G1174" s="1">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H1174" s="1">
         <v>2000</v>
       </c>
       <c r="I1174" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J1174" s="2" t="s">
-        <v>936</v>
+        <v>905</v>
       </c>
       <c r="K1174" s="1">
         <v>150</v>
@@ -69505,7 +69658,7 @@
         <v>0</v>
       </c>
       <c r="O1174" s="1" t="s">
-        <v>894</v>
+        <v>856</v>
       </c>
       <c r="P1174" s="1">
         <v>0</v>
@@ -69519,7 +69672,7 @@
     </row>
     <row r="1175" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1175" s="1" t="s">
-        <v>991</v>
+        <v>950</v>
       </c>
       <c r="B1175" s="1">
         <v>11</v>
@@ -69534,16 +69687,16 @@
         <v>1</v>
       </c>
       <c r="G1175" s="1">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H1175" s="1">
         <v>2000</v>
       </c>
       <c r="I1175" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J1175" s="2" t="s">
-        <v>936</v>
+        <v>902</v>
       </c>
       <c r="K1175" s="1">
         <v>150</v>
@@ -69558,7 +69711,7 @@
         <v>0</v>
       </c>
       <c r="O1175" s="1" t="s">
-        <v>883</v>
+        <v>843</v>
       </c>
       <c r="P1175" s="1">
         <v>0</v>
@@ -69572,7 +69725,7 @@
     </row>
     <row r="1176" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1176" s="1" t="s">
-        <v>992</v>
+        <v>951</v>
       </c>
       <c r="B1176" s="1">
         <v>11</v>
@@ -69587,16 +69740,16 @@
         <v>1</v>
       </c>
       <c r="G1176" s="1">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="H1176" s="1">
         <v>2000</v>
       </c>
       <c r="I1176" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J1176" s="2" t="s">
-        <v>938</v>
+        <v>906</v>
       </c>
       <c r="K1176" s="1">
         <v>150</v>
@@ -69611,7 +69764,7 @@
         <v>0</v>
       </c>
       <c r="O1176" s="1" t="s">
-        <v>884</v>
+        <v>849</v>
       </c>
       <c r="P1176" s="1">
         <v>0</v>
@@ -69625,7 +69778,7 @@
     </row>
     <row r="1177" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1177" s="1" t="s">
-        <v>993</v>
+        <v>952</v>
       </c>
       <c r="B1177" s="1">
         <v>11</v>
@@ -69640,16 +69793,16 @@
         <v>1</v>
       </c>
       <c r="G1177" s="1">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H1177" s="1">
         <v>2000</v>
       </c>
       <c r="I1177" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J1177" s="2" t="s">
-        <v>936</v>
+        <v>902</v>
       </c>
       <c r="K1177" s="1">
         <v>150</v>
@@ -69664,7 +69817,7 @@
         <v>0</v>
       </c>
       <c r="O1177" s="1" t="s">
-        <v>895</v>
+        <v>843</v>
       </c>
       <c r="P1177" s="1">
         <v>0</v>
@@ -69678,7 +69831,7 @@
     </row>
     <row r="1178" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1178" s="1" t="s">
-        <v>994</v>
+        <v>953</v>
       </c>
       <c r="B1178" s="1">
         <v>11</v>
@@ -69693,16 +69846,16 @@
         <v>1</v>
       </c>
       <c r="G1178" s="1">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="H1178" s="1">
         <v>2000</v>
       </c>
       <c r="I1178" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J1178" s="2" t="s">
-        <v>938</v>
+        <v>907</v>
       </c>
       <c r="K1178" s="1">
         <v>150</v>
@@ -69717,7 +69870,7 @@
         <v>0</v>
       </c>
       <c r="O1178" s="1" t="s">
-        <v>886</v>
+        <v>857</v>
       </c>
       <c r="P1178" s="1">
         <v>0</v>
@@ -69731,7 +69884,7 @@
     </row>
     <row r="1179" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1179" s="1" t="s">
-        <v>995</v>
+        <v>954</v>
       </c>
       <c r="B1179" s="1">
         <v>11</v>
@@ -69746,16 +69899,16 @@
         <v>1</v>
       </c>
       <c r="G1179" s="1">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="H1179" s="1">
         <v>2000</v>
       </c>
       <c r="I1179" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J1179" s="2" t="s">
-        <v>936</v>
+        <v>906</v>
       </c>
       <c r="K1179" s="1">
         <v>150</v>
@@ -69770,7 +69923,7 @@
         <v>0</v>
       </c>
       <c r="O1179" s="1" t="s">
-        <v>896</v>
+        <v>858</v>
       </c>
       <c r="P1179" s="1">
         <v>0</v>
@@ -69784,7 +69937,7 @@
     </row>
     <row r="1180" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1180" s="1" t="s">
-        <v>996</v>
+        <v>955</v>
       </c>
       <c r="B1180" s="1">
         <v>11</v>
@@ -69799,16 +69952,16 @@
         <v>1</v>
       </c>
       <c r="G1180" s="1">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H1180" s="1">
         <v>2000</v>
       </c>
       <c r="I1180" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J1180" s="2" t="s">
-        <v>938</v>
+        <v>908</v>
       </c>
       <c r="K1180" s="1">
         <v>150</v>
@@ -69823,7 +69976,7 @@
         <v>0</v>
       </c>
       <c r="O1180" s="1" t="s">
-        <v>897</v>
+        <v>859</v>
       </c>
       <c r="P1180" s="1">
         <v>0</v>
@@ -69837,7 +69990,7 @@
     </row>
     <row r="1181" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1181" s="1" t="s">
-        <v>997</v>
+        <v>956</v>
       </c>
       <c r="B1181" s="1">
         <v>11</v>
@@ -69852,16 +70005,16 @@
         <v>1</v>
       </c>
       <c r="G1181" s="1">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H1181" s="1">
         <v>2000</v>
       </c>
       <c r="I1181" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J1181" s="2" t="s">
-        <v>936</v>
+        <v>909</v>
       </c>
       <c r="K1181" s="1">
         <v>150</v>
@@ -69876,7 +70029,7 @@
         <v>0</v>
       </c>
       <c r="O1181" s="1" t="s">
-        <v>898</v>
+        <v>860</v>
       </c>
       <c r="P1181" s="1">
         <v>0</v>
@@ -69890,7 +70043,7 @@
     </row>
     <row r="1182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1182" s="1" t="s">
-        <v>998</v>
+        <v>957</v>
       </c>
       <c r="B1182" s="1">
         <v>11</v>
@@ -69905,16 +70058,16 @@
         <v>1</v>
       </c>
       <c r="G1182" s="1">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="H1182" s="1">
         <v>2000</v>
       </c>
       <c r="I1182" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J1182" s="2" t="s">
-        <v>939</v>
+        <v>910</v>
       </c>
       <c r="K1182" s="1">
         <v>150</v>
@@ -69929,7 +70082,7 @@
         <v>0</v>
       </c>
       <c r="O1182" s="1" t="s">
-        <v>899</v>
+        <v>861</v>
       </c>
       <c r="P1182" s="1">
         <v>0</v>
@@ -69943,7 +70096,7 @@
     </row>
     <row r="1183" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1183" s="1" t="s">
-        <v>999</v>
+        <v>958</v>
       </c>
       <c r="B1183" s="1">
         <v>11</v>
@@ -69958,16 +70111,16 @@
         <v>1</v>
       </c>
       <c r="G1183" s="1">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H1183" s="1">
         <v>2000</v>
       </c>
       <c r="I1183" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J1183" s="2" t="s">
-        <v>938</v>
+        <v>911</v>
       </c>
       <c r="K1183" s="1">
         <v>150</v>
@@ -69982,7 +70135,7 @@
         <v>0</v>
       </c>
       <c r="O1183" s="1" t="s">
-        <v>900</v>
+        <v>862</v>
       </c>
       <c r="P1183" s="1">
         <v>0</v>
@@ -69996,7 +70149,7 @@
     </row>
     <row r="1184" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1184" s="1" t="s">
-        <v>1000</v>
+        <v>959</v>
       </c>
       <c r="B1184" s="1">
         <v>11</v>
@@ -70011,16 +70164,16 @@
         <v>1</v>
       </c>
       <c r="G1184" s="1">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H1184" s="1">
         <v>2000</v>
       </c>
       <c r="I1184" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J1184" s="2" t="s">
-        <v>939</v>
+        <v>912</v>
       </c>
       <c r="K1184" s="1">
         <v>150</v>
@@ -70035,7 +70188,7 @@
         <v>0</v>
       </c>
       <c r="O1184" s="1" t="s">
-        <v>901</v>
+        <v>863</v>
       </c>
       <c r="P1184" s="1">
         <v>0</v>
@@ -70049,7 +70202,7 @@
     </row>
     <row r="1185" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1185" s="1" t="s">
-        <v>1001</v>
+        <v>960</v>
       </c>
       <c r="B1185" s="1">
         <v>11</v>
@@ -70064,16 +70217,16 @@
         <v>1</v>
       </c>
       <c r="G1185" s="1">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="H1185" s="1">
         <v>2000</v>
       </c>
       <c r="I1185" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J1185" s="2" t="s">
-        <v>938</v>
+        <v>908</v>
       </c>
       <c r="K1185" s="1">
         <v>150</v>
@@ -70088,7 +70241,7 @@
         <v>0</v>
       </c>
       <c r="O1185" s="1" t="s">
-        <v>902</v>
+        <v>864</v>
       </c>
       <c r="P1185" s="1">
         <v>0</v>
@@ -70102,7 +70255,7 @@
     </row>
     <row r="1186" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1186" s="1" t="s">
-        <v>1002</v>
+        <v>961</v>
       </c>
       <c r="B1186" s="1">
         <v>11</v>
@@ -70117,16 +70270,16 @@
         <v>1</v>
       </c>
       <c r="G1186" s="1">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H1186" s="1">
         <v>2000</v>
       </c>
       <c r="I1186" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J1186" s="2" t="s">
-        <v>939</v>
+        <v>908</v>
       </c>
       <c r="K1186" s="1">
         <v>150</v>
@@ -70141,7 +70294,7 @@
         <v>0</v>
       </c>
       <c r="O1186" s="1" t="s">
-        <v>903</v>
+        <v>865</v>
       </c>
       <c r="P1186" s="1">
         <v>0</v>
@@ -70155,7 +70308,7 @@
     </row>
     <row r="1187" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1187" s="1" t="s">
-        <v>1003</v>
+        <v>962</v>
       </c>
       <c r="B1187" s="1">
         <v>11</v>
@@ -70170,16 +70323,16 @@
         <v>1</v>
       </c>
       <c r="G1187" s="1">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="H1187" s="1">
         <v>2000</v>
       </c>
       <c r="I1187" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J1187" s="2" t="s">
-        <v>938</v>
+        <v>913</v>
       </c>
       <c r="K1187" s="1">
         <v>150</v>
@@ -70194,7 +70347,7 @@
         <v>0</v>
       </c>
       <c r="O1187" s="1" t="s">
-        <v>904</v>
+        <v>866</v>
       </c>
       <c r="P1187" s="1">
         <v>0</v>
@@ -70208,7 +70361,7 @@
     </row>
     <row r="1188" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1188" s="1" t="s">
-        <v>1004</v>
+        <v>963</v>
       </c>
       <c r="B1188" s="1">
         <v>11</v>
@@ -70223,16 +70376,16 @@
         <v>1</v>
       </c>
       <c r="G1188" s="1">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H1188" s="1">
         <v>2000</v>
       </c>
       <c r="I1188" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J1188" s="2" t="s">
-        <v>939</v>
+        <v>910</v>
       </c>
       <c r="K1188" s="1">
         <v>150</v>
@@ -70247,7 +70400,7 @@
         <v>0</v>
       </c>
       <c r="O1188" s="1" t="s">
-        <v>903</v>
+        <v>867</v>
       </c>
       <c r="P1188" s="1">
         <v>0</v>
@@ -70261,7 +70414,7 @@
     </row>
     <row r="1189" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1189" s="1" t="s">
-        <v>1005</v>
+        <v>964</v>
       </c>
       <c r="B1189" s="1">
         <v>11</v>
@@ -70276,16 +70429,16 @@
         <v>1</v>
       </c>
       <c r="G1189" s="1">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H1189" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1189" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J1189" s="2" t="s">
-        <v>939</v>
+        <v>911</v>
       </c>
       <c r="K1189" s="1">
         <v>150</v>
@@ -70300,7 +70453,7 @@
         <v>0</v>
       </c>
       <c r="O1189" s="1" t="s">
-        <v>905</v>
+        <v>868</v>
       </c>
       <c r="P1189" s="1">
         <v>0</v>
@@ -70314,7 +70467,7 @@
     </row>
     <row r="1190" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1190" s="1" t="s">
-        <v>1006</v>
+        <v>965</v>
       </c>
       <c r="B1190" s="1">
         <v>11</v>
@@ -70329,16 +70482,16 @@
         <v>1</v>
       </c>
       <c r="G1190" s="1">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="H1190" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1190" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J1190" s="2" t="s">
-        <v>938</v>
+        <v>913</v>
       </c>
       <c r="K1190" s="1">
         <v>150</v>
@@ -70353,7 +70506,7 @@
         <v>0</v>
       </c>
       <c r="O1190" s="1" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="P1190" s="1">
         <v>0</v>
@@ -70367,7 +70520,7 @@
     </row>
     <row r="1191" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1191" s="1" t="s">
-        <v>1007</v>
+        <v>966</v>
       </c>
       <c r="B1191" s="1">
         <v>11</v>
@@ -70382,16 +70535,16 @@
         <v>1</v>
       </c>
       <c r="G1191" s="1">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="H1191" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1191" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J1191" s="2" t="s">
-        <v>939</v>
+        <v>914</v>
       </c>
       <c r="K1191" s="1">
         <v>150</v>
@@ -70406,7 +70559,7 @@
         <v>0</v>
       </c>
       <c r="O1191" s="1" t="s">
-        <v>906</v>
+        <v>870</v>
       </c>
       <c r="P1191" s="1">
         <v>0</v>
@@ -70420,7 +70573,7 @@
     </row>
     <row r="1192" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1192" s="1" t="s">
-        <v>1008</v>
+        <v>967</v>
       </c>
       <c r="B1192" s="1">
         <v>11</v>
@@ -70435,16 +70588,16 @@
         <v>1</v>
       </c>
       <c r="G1192" s="1">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H1192" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1192" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J1192" s="2" t="s">
-        <v>938</v>
+        <v>913</v>
       </c>
       <c r="K1192" s="1">
         <v>150</v>
@@ -70459,7 +70612,7 @@
         <v>0</v>
       </c>
       <c r="O1192" s="1" t="s">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="P1192" s="1">
         <v>0</v>
@@ -70473,7 +70626,7 @@
     </row>
     <row r="1193" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1193" s="1" t="s">
-        <v>1009</v>
+        <v>968</v>
       </c>
       <c r="B1193" s="1">
         <v>11</v>
@@ -70488,16 +70641,16 @@
         <v>1</v>
       </c>
       <c r="G1193" s="1">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H1193" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1193" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J1193" s="2" t="s">
-        <v>939</v>
+        <v>913</v>
       </c>
       <c r="K1193" s="1">
         <v>150</v>
@@ -70512,7 +70665,7 @@
         <v>0</v>
       </c>
       <c r="O1193" s="1" t="s">
-        <v>907</v>
+        <v>860</v>
       </c>
       <c r="P1193" s="1">
         <v>0</v>
@@ -70526,7 +70679,7 @@
     </row>
     <row r="1194" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1194" s="1" t="s">
-        <v>1010</v>
+        <v>969</v>
       </c>
       <c r="B1194" s="1">
         <v>11</v>
@@ -70541,16 +70694,16 @@
         <v>1</v>
       </c>
       <c r="G1194" s="1">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="H1194" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1194" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J1194" s="2" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="K1194" s="1">
         <v>150</v>
@@ -70565,7 +70718,7 @@
         <v>0</v>
       </c>
       <c r="O1194" s="1" t="s">
-        <v>897</v>
+        <v>861</v>
       </c>
       <c r="P1194" s="1">
         <v>0</v>
@@ -70579,7 +70732,7 @@
     </row>
     <row r="1195" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1195" s="1" t="s">
-        <v>1011</v>
+        <v>970</v>
       </c>
       <c r="B1195" s="1">
         <v>11</v>
@@ -70594,16 +70747,16 @@
         <v>1</v>
       </c>
       <c r="G1195" s="1">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H1195" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1195" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J1195" s="2" t="s">
-        <v>940</v>
+        <v>913</v>
       </c>
       <c r="K1195" s="1">
         <v>150</v>
@@ -70618,7 +70771,7 @@
         <v>0</v>
       </c>
       <c r="O1195" s="1" t="s">
-        <v>908</v>
+        <v>872</v>
       </c>
       <c r="P1195" s="1">
         <v>0</v>
@@ -70632,7 +70785,7 @@
     </row>
     <row r="1196" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1196" s="1" t="s">
-        <v>1012</v>
+        <v>971</v>
       </c>
       <c r="B1196" s="1">
         <v>11</v>
@@ -70647,16 +70800,16 @@
         <v>1</v>
       </c>
       <c r="G1196" s="1">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="H1196" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1196" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J1196" s="2" t="s">
-        <v>939</v>
+        <v>915</v>
       </c>
       <c r="K1196" s="1">
         <v>150</v>
@@ -70671,7 +70824,7 @@
         <v>0</v>
       </c>
       <c r="O1196" s="1" t="s">
-        <v>899</v>
+        <v>863</v>
       </c>
       <c r="P1196" s="1">
         <v>0</v>
@@ -70685,7 +70838,7 @@
     </row>
     <row r="1197" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1197" s="1" t="s">
-        <v>1013</v>
+        <v>972</v>
       </c>
       <c r="B1197" s="1">
         <v>11</v>
@@ -70700,16 +70853,16 @@
         <v>1</v>
       </c>
       <c r="G1197" s="1">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H1197" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1197" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J1197" s="2" t="s">
-        <v>938</v>
+        <v>913</v>
       </c>
       <c r="K1197" s="1">
         <v>150</v>
@@ -70724,7 +70877,7 @@
         <v>0</v>
       </c>
       <c r="O1197" s="1" t="s">
-        <v>900</v>
+        <v>873</v>
       </c>
       <c r="P1197" s="1">
         <v>0</v>
@@ -70738,7 +70891,7 @@
     </row>
     <row r="1198" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1198" s="1" t="s">
-        <v>1014</v>
+        <v>973</v>
       </c>
       <c r="B1198" s="1">
         <v>11</v>
@@ -70753,16 +70906,16 @@
         <v>1</v>
       </c>
       <c r="G1198" s="1">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H1198" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1198" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J1198" s="2" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="K1198" s="1">
         <v>150</v>
@@ -70777,7 +70930,7 @@
         <v>0</v>
       </c>
       <c r="O1198" s="1" t="s">
-        <v>901</v>
+        <v>874</v>
       </c>
       <c r="P1198" s="1">
         <v>0</v>
@@ -70791,7 +70944,7 @@
     </row>
     <row r="1199" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1199" s="1" t="s">
-        <v>1015</v>
+        <v>974</v>
       </c>
       <c r="B1199" s="1">
         <v>11</v>
@@ -70806,16 +70959,16 @@
         <v>1</v>
       </c>
       <c r="G1199" s="1">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H1199" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1199" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J1199" s="2" t="s">
-        <v>938</v>
+        <v>913</v>
       </c>
       <c r="K1199" s="1">
         <v>150</v>
@@ -70830,7 +70983,7 @@
         <v>0</v>
       </c>
       <c r="O1199" s="1" t="s">
-        <v>902</v>
+        <v>875</v>
       </c>
       <c r="P1199" s="1">
         <v>0</v>
@@ -70844,7 +70997,7 @@
     </row>
     <row r="1200" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1200" s="1" t="s">
-        <v>1016</v>
+        <v>975</v>
       </c>
       <c r="B1200" s="1">
         <v>11</v>
@@ -70859,16 +71012,16 @@
         <v>1</v>
       </c>
       <c r="G1200" s="1">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="H1200" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1200" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J1200" s="2" t="s">
-        <v>939</v>
+        <v>916</v>
       </c>
       <c r="K1200" s="1">
         <v>150</v>
@@ -70883,7 +71036,7 @@
         <v>0</v>
       </c>
       <c r="O1200" s="1" t="s">
-        <v>903</v>
+        <v>876</v>
       </c>
       <c r="P1200" s="1">
         <v>0</v>
@@ -70897,7 +71050,7 @@
     </row>
     <row r="1201" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1201" s="1" t="s">
-        <v>1017</v>
+        <v>976</v>
       </c>
       <c r="B1201" s="1">
         <v>11</v>
@@ -70912,16 +71065,16 @@
         <v>1</v>
       </c>
       <c r="G1201" s="1">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="H1201" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1201" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J1201" s="2" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="K1201" s="1">
         <v>150</v>
@@ -70936,7 +71089,7 @@
         <v>0</v>
       </c>
       <c r="O1201" s="1" t="s">
-        <v>904</v>
+        <v>877</v>
       </c>
       <c r="P1201" s="1">
         <v>0</v>
@@ -70950,7 +71103,7 @@
     </row>
     <row r="1202" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1202" s="1" t="s">
-        <v>1018</v>
+        <v>977</v>
       </c>
       <c r="B1202" s="1">
         <v>11</v>
@@ -70965,16 +71118,16 @@
         <v>1</v>
       </c>
       <c r="G1202" s="1">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="H1202" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1202" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J1202" s="2" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="K1202" s="1">
         <v>150</v>
@@ -70989,7 +71142,7 @@
         <v>0</v>
       </c>
       <c r="O1202" s="1" t="s">
-        <v>903</v>
+        <v>878</v>
       </c>
       <c r="P1202" s="1">
         <v>0</v>
@@ -71003,7 +71156,7 @@
     </row>
     <row r="1203" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1203" s="1" t="s">
-        <v>1019</v>
+        <v>978</v>
       </c>
       <c r="B1203" s="1">
         <v>11</v>
@@ -71018,16 +71171,16 @@
         <v>1</v>
       </c>
       <c r="G1203" s="1">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="H1203" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1203" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J1203" s="2" t="s">
-        <v>939</v>
+        <v>915</v>
       </c>
       <c r="K1203" s="1">
         <v>150</v>
@@ -71042,7 +71195,7 @@
         <v>0</v>
       </c>
       <c r="O1203" s="1" t="s">
-        <v>905</v>
+        <v>879</v>
       </c>
       <c r="P1203" s="1">
         <v>0</v>
@@ -71056,7 +71209,7 @@
     </row>
     <row r="1204" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1204" s="1" t="s">
-        <v>1020</v>
+        <v>979</v>
       </c>
       <c r="B1204" s="1">
         <v>11</v>
@@ -71071,16 +71224,16 @@
         <v>1</v>
       </c>
       <c r="G1204" s="1">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H1204" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1204" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J1204" s="2" t="s">
-        <v>938</v>
+        <v>916</v>
       </c>
       <c r="K1204" s="1">
         <v>150</v>
@@ -71095,7 +71248,7 @@
         <v>0</v>
       </c>
       <c r="O1204" s="1" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="P1204" s="1">
         <v>0</v>
@@ -71109,7 +71262,7 @@
     </row>
     <row r="1205" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1205" s="1" t="s">
-        <v>1021</v>
+        <v>980</v>
       </c>
       <c r="B1205" s="1">
         <v>11</v>
@@ -71124,16 +71277,16 @@
         <v>1</v>
       </c>
       <c r="G1205" s="1">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="H1205" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1205" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J1205" s="2" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="K1205" s="1">
         <v>150</v>
@@ -71148,7 +71301,7 @@
         <v>0</v>
       </c>
       <c r="O1205" s="1" t="s">
-        <v>906</v>
+        <v>881</v>
       </c>
       <c r="P1205" s="1">
         <v>0</v>
@@ -71162,7 +71315,7 @@
     </row>
     <row r="1206" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1206" s="1" t="s">
-        <v>1022</v>
+        <v>981</v>
       </c>
       <c r="B1206" s="1">
         <v>11</v>
@@ -71177,16 +71330,16 @@
         <v>1</v>
       </c>
       <c r="G1206" s="1">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="H1206" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1206" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J1206" s="2" t="s">
-        <v>938</v>
+        <v>916</v>
       </c>
       <c r="K1206" s="1">
         <v>150</v>
@@ -71201,7 +71354,7 @@
         <v>0</v>
       </c>
       <c r="O1206" s="1" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="P1206" s="1">
         <v>0</v>
@@ -71215,7 +71368,7 @@
     </row>
     <row r="1207" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1207" s="1" t="s">
-        <v>1023</v>
+        <v>982</v>
       </c>
       <c r="B1207" s="1">
         <v>11</v>
@@ -71230,16 +71383,16 @@
         <v>1</v>
       </c>
       <c r="G1207" s="1">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="H1207" s="1">
         <v>1500</v>
       </c>
       <c r="I1207" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J1207" s="2" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="K1207" s="1">
         <v>150</v>
@@ -71254,7 +71407,7 @@
         <v>0</v>
       </c>
       <c r="O1207" s="1" t="s">
-        <v>907</v>
+        <v>882</v>
       </c>
       <c r="P1207" s="1">
         <v>0</v>
@@ -71268,7 +71421,7 @@
     </row>
     <row r="1208" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1208" s="1" t="s">
-        <v>1024</v>
+        <v>983</v>
       </c>
       <c r="B1208" s="1">
         <v>11</v>
@@ -71283,16 +71436,16 @@
         <v>1</v>
       </c>
       <c r="G1208" s="1">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H1208" s="1">
         <v>1500</v>
       </c>
       <c r="I1208" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J1208" s="2" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="K1208" s="1">
         <v>150</v>
@@ -71307,7 +71460,7 @@
         <v>0</v>
       </c>
       <c r="O1208" s="1" t="s">
-        <v>897</v>
+        <v>861</v>
       </c>
       <c r="P1208" s="1">
         <v>0</v>
@@ -71321,7 +71474,7 @@
     </row>
     <row r="1209" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1209" s="1" t="s">
-        <v>1025</v>
+        <v>984</v>
       </c>
       <c r="B1209" s="1">
         <v>11</v>
@@ -71336,16 +71489,16 @@
         <v>1</v>
       </c>
       <c r="G1209" s="1">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="H1209" s="1">
         <v>1500</v>
       </c>
       <c r="I1209" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J1209" s="2" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="K1209" s="1">
         <v>150</v>
@@ -71360,7 +71513,7 @@
         <v>0</v>
       </c>
       <c r="O1209" s="1" t="s">
-        <v>908</v>
+        <v>883</v>
       </c>
       <c r="P1209" s="1">
         <v>0</v>
@@ -71374,7 +71527,7 @@
     </row>
     <row r="1210" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1210" s="1" t="s">
-        <v>1026</v>
+        <v>985</v>
       </c>
       <c r="B1210" s="1">
         <v>11</v>
@@ -71389,16 +71542,16 @@
         <v>1</v>
       </c>
       <c r="G1210" s="1">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H1210" s="1">
         <v>1500</v>
       </c>
       <c r="I1210" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J1210" s="2" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="K1210" s="1">
         <v>150</v>
@@ -71413,7 +71566,7 @@
         <v>0</v>
       </c>
       <c r="O1210" s="1" t="s">
-        <v>899</v>
+        <v>863</v>
       </c>
       <c r="P1210" s="1">
         <v>0</v>
@@ -71427,7 +71580,7 @@
     </row>
     <row r="1211" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1211" s="1" t="s">
-        <v>1027</v>
+        <v>986</v>
       </c>
       <c r="B1211" s="1">
         <v>11</v>
@@ -71442,16 +71595,16 @@
         <v>1</v>
       </c>
       <c r="G1211" s="1">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="H1211" s="1">
         <v>1500</v>
       </c>
       <c r="I1211" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J1211" s="2" t="s">
-        <v>941</v>
+        <v>916</v>
       </c>
       <c r="K1211" s="1">
         <v>150</v>
@@ -71466,7 +71619,7 @@
         <v>0</v>
       </c>
       <c r="O1211" s="1" t="s">
-        <v>909</v>
+        <v>884</v>
       </c>
       <c r="P1211" s="1">
         <v>0</v>
@@ -71480,7 +71633,7 @@
     </row>
     <row r="1212" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1212" s="1" t="s">
-        <v>1028</v>
+        <v>987</v>
       </c>
       <c r="B1212" s="1">
         <v>11</v>
@@ -71495,16 +71648,16 @@
         <v>1</v>
       </c>
       <c r="G1212" s="1">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="H1212" s="1">
         <v>1500</v>
       </c>
       <c r="I1212" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J1212" s="2" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="K1212" s="1">
         <v>150</v>
@@ -71519,7 +71672,7 @@
         <v>0</v>
       </c>
       <c r="O1212" s="1" t="s">
-        <v>901</v>
+        <v>874</v>
       </c>
       <c r="P1212" s="1">
         <v>0</v>
@@ -71533,7 +71686,7 @@
     </row>
     <row r="1213" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1213" s="1" t="s">
-        <v>1029</v>
+        <v>988</v>
       </c>
       <c r="B1213" s="1">
         <v>11</v>
@@ -71548,16 +71701,16 @@
         <v>1</v>
       </c>
       <c r="G1213" s="1">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H1213" s="1">
         <v>1500</v>
       </c>
       <c r="I1213" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J1213" s="2" t="s">
-        <v>938</v>
+        <v>917</v>
       </c>
       <c r="K1213" s="1">
         <v>150</v>
@@ -71572,7 +71725,7 @@
         <v>0</v>
       </c>
       <c r="O1213" s="1" t="s">
-        <v>902</v>
+        <v>885</v>
       </c>
       <c r="P1213" s="1">
         <v>0</v>
@@ -71586,7 +71739,7 @@
     </row>
     <row r="1214" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1214" s="1" t="s">
-        <v>1030</v>
+        <v>989</v>
       </c>
       <c r="B1214" s="1">
         <v>11</v>
@@ -71601,16 +71754,16 @@
         <v>1</v>
       </c>
       <c r="G1214" s="1">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="H1214" s="1">
         <v>1500</v>
       </c>
       <c r="I1214" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J1214" s="2" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="K1214" s="1">
         <v>150</v>
@@ -71625,7 +71778,7 @@
         <v>0</v>
       </c>
       <c r="O1214" s="1" t="s">
-        <v>903</v>
+        <v>876</v>
       </c>
       <c r="P1214" s="1">
         <v>0</v>
@@ -71639,7 +71792,7 @@
     </row>
     <row r="1215" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1215" s="1" t="s">
-        <v>1031</v>
+        <v>990</v>
       </c>
       <c r="B1215" s="1">
         <v>11</v>
@@ -71654,16 +71807,16 @@
         <v>1</v>
       </c>
       <c r="G1215" s="1">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="H1215" s="1">
         <v>1500</v>
       </c>
       <c r="I1215" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J1215" s="2" t="s">
-        <v>938</v>
+        <v>915</v>
       </c>
       <c r="K1215" s="1">
         <v>150</v>
@@ -71678,7 +71831,7 @@
         <v>0</v>
       </c>
       <c r="O1215" s="1" t="s">
-        <v>904</v>
+        <v>877</v>
       </c>
       <c r="P1215" s="1">
         <v>0</v>
@@ -71692,7 +71845,7 @@
     </row>
     <row r="1216" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1216" s="1" t="s">
-        <v>1032</v>
+        <v>991</v>
       </c>
       <c r="B1216" s="1">
         <v>11</v>
@@ -71707,16 +71860,16 @@
         <v>1</v>
       </c>
       <c r="G1216" s="1">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H1216" s="1">
         <v>1500</v>
       </c>
       <c r="I1216" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J1216" s="2" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
       <c r="K1216" s="1">
         <v>150</v>
@@ -71731,7 +71884,7 @@
         <v>0</v>
       </c>
       <c r="O1216" s="1" t="s">
-        <v>903</v>
+        <v>878</v>
       </c>
       <c r="P1216" s="1">
         <v>0</v>
@@ -71745,7 +71898,7 @@
     </row>
     <row r="1217" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1217" s="1" t="s">
-        <v>1033</v>
+        <v>992</v>
       </c>
       <c r="B1217" s="1">
         <v>11</v>
@@ -71760,16 +71913,16 @@
         <v>1</v>
       </c>
       <c r="G1217" s="1">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="H1217" s="1">
         <v>1500</v>
       </c>
       <c r="I1217" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J1217" s="2" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="K1217" s="1">
         <v>150</v>
@@ -71784,7 +71937,7 @@
         <v>0</v>
       </c>
       <c r="O1217" s="1" t="s">
-        <v>910</v>
+        <v>879</v>
       </c>
       <c r="P1217" s="1">
         <v>0</v>
@@ -71798,7 +71951,7 @@
     </row>
     <row r="1218" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1218" s="1" t="s">
-        <v>1034</v>
+        <v>993</v>
       </c>
       <c r="B1218" s="1">
         <v>11</v>
@@ -71813,16 +71966,16 @@
         <v>1</v>
       </c>
       <c r="G1218" s="1">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="H1218" s="1">
         <v>1500</v>
       </c>
       <c r="I1218" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J1218" s="2" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="K1218" s="1">
         <v>150</v>
@@ -71837,7 +71990,7 @@
         <v>0</v>
       </c>
       <c r="O1218" s="1" t="s">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="P1218" s="1">
         <v>0</v>
@@ -71851,7 +72004,7 @@
     </row>
     <row r="1219" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1219" s="1" t="s">
-        <v>1035</v>
+        <v>994</v>
       </c>
       <c r="B1219" s="1">
         <v>11</v>
@@ -71866,16 +72019,16 @@
         <v>1</v>
       </c>
       <c r="G1219" s="1">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="H1219" s="1">
         <v>1500</v>
       </c>
       <c r="I1219" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J1219" s="2" t="s">
-        <v>941</v>
+        <v>915</v>
       </c>
       <c r="K1219" s="1">
         <v>150</v>
@@ -71890,7 +72043,7 @@
         <v>0</v>
       </c>
       <c r="O1219" s="1" t="s">
-        <v>911</v>
+        <v>881</v>
       </c>
       <c r="P1219" s="1">
         <v>0</v>
@@ -71904,7 +72057,7 @@
     </row>
     <row r="1220" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1220" s="1" t="s">
-        <v>1036</v>
+        <v>995</v>
       </c>
       <c r="B1220" s="1">
         <v>11</v>
@@ -71919,16 +72072,16 @@
         <v>1</v>
       </c>
       <c r="G1220" s="1">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="H1220" s="1">
         <v>1500</v>
       </c>
       <c r="I1220" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J1220" s="2" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
       <c r="K1220" s="1">
         <v>150</v>
@@ -71943,7 +72096,7 @@
         <v>0</v>
       </c>
       <c r="O1220" s="1" t="s">
-        <v>906</v>
+        <v>880</v>
       </c>
       <c r="P1220" s="1">
         <v>0</v>
@@ -71957,7 +72110,7 @@
     </row>
     <row r="1221" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1221" s="1" t="s">
-        <v>1037</v>
+        <v>996</v>
       </c>
       <c r="B1221" s="1">
         <v>11</v>
@@ -71972,16 +72125,16 @@
         <v>1</v>
       </c>
       <c r="G1221" s="1">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="H1221" s="1">
         <v>1500</v>
       </c>
       <c r="I1221" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J1221" s="2" t="s">
-        <v>941</v>
+        <v>916</v>
       </c>
       <c r="K1221" s="1">
         <v>150</v>
@@ -71996,7 +72149,7 @@
         <v>0</v>
       </c>
       <c r="O1221" s="1" t="s">
-        <v>912</v>
+        <v>882</v>
       </c>
       <c r="P1221" s="1">
         <v>0</v>
@@ -72010,7 +72163,7 @@
     </row>
     <row r="1222" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1222" s="1" t="s">
-        <v>1038</v>
+        <v>997</v>
       </c>
       <c r="B1222" s="1">
         <v>11</v>
@@ -72025,16 +72178,16 @@
         <v>1</v>
       </c>
       <c r="G1222" s="1">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H1222" s="1">
         <v>1500</v>
       </c>
       <c r="I1222" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J1222" s="2" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="K1222" s="1">
         <v>150</v>
@@ -72049,7 +72202,7 @@
         <v>0</v>
       </c>
       <c r="O1222" s="1" t="s">
-        <v>907</v>
+        <v>861</v>
       </c>
       <c r="P1222" s="1">
         <v>0</v>
@@ -72063,7 +72216,7 @@
     </row>
     <row r="1223" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1223" s="1" t="s">
-        <v>1039</v>
+        <v>998</v>
       </c>
       <c r="B1223" s="1">
         <v>11</v>
@@ -72078,16 +72231,16 @@
         <v>1</v>
       </c>
       <c r="G1223" s="1">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="H1223" s="1">
         <v>1500</v>
       </c>
       <c r="I1223" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J1223" s="2" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
       <c r="K1223" s="1">
         <v>150</v>
@@ -72102,7 +72255,7 @@
         <v>0</v>
       </c>
       <c r="O1223" s="1" t="s">
-        <v>913</v>
+        <v>883</v>
       </c>
       <c r="P1223" s="1">
         <v>0</v>
@@ -72116,7 +72269,7 @@
     </row>
     <row r="1224" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1224" s="1" t="s">
-        <v>1040</v>
+        <v>999</v>
       </c>
       <c r="B1224" s="1">
         <v>11</v>
@@ -72131,16 +72284,16 @@
         <v>1</v>
       </c>
       <c r="G1224" s="1">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H1224" s="1">
         <v>1500</v>
       </c>
       <c r="I1224" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J1224" s="2" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="K1224" s="1">
         <v>150</v>
@@ -72155,7 +72308,7 @@
         <v>0</v>
       </c>
       <c r="O1224" s="1" t="s">
-        <v>908</v>
+        <v>863</v>
       </c>
       <c r="P1224" s="1">
         <v>0</v>
@@ -72169,7 +72322,7 @@
     </row>
     <row r="1225" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1225" s="1" t="s">
-        <v>1041</v>
+        <v>1000</v>
       </c>
       <c r="B1225" s="1">
         <v>11</v>
@@ -72184,16 +72337,16 @@
         <v>1</v>
       </c>
       <c r="G1225" s="1">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="H1225" s="1">
         <v>1500</v>
       </c>
       <c r="I1225" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J1225" s="2" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
       <c r="K1225" s="1">
         <v>150</v>
@@ -72208,7 +72361,7 @@
         <v>0</v>
       </c>
       <c r="O1225" s="1" t="s">
-        <v>908</v>
+        <v>884</v>
       </c>
       <c r="P1225" s="1">
         <v>0</v>
@@ -72222,7 +72375,7 @@
     </row>
     <row r="1226" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1226" s="1" t="s">
-        <v>1042</v>
+        <v>1001</v>
       </c>
       <c r="B1226" s="1">
         <v>11</v>
@@ -72237,16 +72390,16 @@
         <v>1</v>
       </c>
       <c r="G1226" s="1">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="H1226" s="1">
         <v>1500</v>
       </c>
       <c r="I1226" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J1226" s="2" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="K1226" s="1">
         <v>150</v>
@@ -72261,7 +72414,7 @@
         <v>0</v>
       </c>
       <c r="O1226" s="1" t="s">
-        <v>899</v>
+        <v>874</v>
       </c>
       <c r="P1226" s="1">
         <v>0</v>
@@ -72275,7 +72428,7 @@
     </row>
     <row r="1227" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1227" s="1" t="s">
-        <v>1043</v>
+        <v>1002</v>
       </c>
       <c r="B1227" s="1">
         <v>11</v>
@@ -72290,16 +72443,16 @@
         <v>1</v>
       </c>
       <c r="G1227" s="1">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H1227" s="1">
         <v>1500</v>
       </c>
       <c r="I1227" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J1227" s="2" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
       <c r="K1227" s="1">
         <v>150</v>
@@ -72314,7 +72467,7 @@
         <v>0</v>
       </c>
       <c r="O1227" s="1" t="s">
-        <v>909</v>
+        <v>885</v>
       </c>
       <c r="P1227" s="1">
         <v>0</v>
@@ -72328,7 +72481,7 @@
     </row>
     <row r="1228" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1228" s="1" t="s">
-        <v>1044</v>
+        <v>1003</v>
       </c>
       <c r="B1228" s="1">
         <v>11</v>
@@ -72343,16 +72496,16 @@
         <v>1</v>
       </c>
       <c r="G1228" s="1">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H1228" s="1">
         <v>1500</v>
       </c>
       <c r="I1228" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J1228" s="2" t="s">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="K1228" s="1">
         <v>150</v>
@@ -72367,7 +72520,7 @@
         <v>0</v>
       </c>
       <c r="O1228" s="1" t="s">
-        <v>901</v>
+        <v>876</v>
       </c>
       <c r="P1228" s="1">
         <v>0</v>
@@ -72381,7 +72534,7 @@
     </row>
     <row r="1229" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1229" s="1" t="s">
-        <v>1045</v>
+        <v>1004</v>
       </c>
       <c r="B1229" s="1">
         <v>11</v>
@@ -72396,16 +72549,16 @@
         <v>1</v>
       </c>
       <c r="G1229" s="1">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="H1229" s="1">
         <v>1500</v>
       </c>
       <c r="I1229" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J1229" s="2" t="s">
-        <v>941</v>
+        <v>918</v>
       </c>
       <c r="K1229" s="1">
         <v>150</v>
@@ -72420,7 +72573,7 @@
         <v>0</v>
       </c>
       <c r="O1229" s="1" t="s">
-        <v>914</v>
+        <v>886</v>
       </c>
       <c r="P1229" s="1">
         <v>0</v>
@@ -72434,7 +72587,7 @@
     </row>
     <row r="1230" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1230" s="1" t="s">
-        <v>1046</v>
+        <v>1005</v>
       </c>
       <c r="B1230" s="1">
         <v>11</v>
@@ -72449,16 +72602,16 @@
         <v>1</v>
       </c>
       <c r="G1230" s="1">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="H1230" s="1">
         <v>1500</v>
       </c>
       <c r="I1230" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J1230" s="2" t="s">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="K1230" s="1">
         <v>150</v>
@@ -72473,7 +72626,7 @@
         <v>0</v>
       </c>
       <c r="O1230" s="1" t="s">
-        <v>903</v>
+        <v>878</v>
       </c>
       <c r="P1230" s="1">
         <v>0</v>
@@ -72487,7 +72640,7 @@
     </row>
     <row r="1231" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1231" s="1" t="s">
-        <v>1047</v>
+        <v>1006</v>
       </c>
       <c r="B1231" s="1">
         <v>11</v>
@@ -72502,16 +72655,16 @@
         <v>1</v>
       </c>
       <c r="G1231" s="1">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="H1231" s="1">
         <v>1500</v>
       </c>
       <c r="I1231" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J1231" s="2" t="s">
-        <v>941</v>
+        <v>915</v>
       </c>
       <c r="K1231" s="1">
         <v>150</v>
@@ -72526,7 +72679,7 @@
         <v>0</v>
       </c>
       <c r="O1231" s="1" t="s">
-        <v>915</v>
+        <v>879</v>
       </c>
       <c r="P1231" s="1">
         <v>0</v>
@@ -72540,7 +72693,7 @@
     </row>
     <row r="1232" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1232" s="1" t="s">
-        <v>1048</v>
+        <v>1007</v>
       </c>
       <c r="B1232" s="1">
         <v>11</v>
@@ -72555,16 +72708,16 @@
         <v>1</v>
       </c>
       <c r="G1232" s="1">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="H1232" s="1">
         <v>1500</v>
       </c>
       <c r="I1232" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J1232" s="2" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
       <c r="K1232" s="1">
         <v>150</v>
@@ -72579,7 +72732,7 @@
         <v>0</v>
       </c>
       <c r="O1232" s="1" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="P1232" s="1">
         <v>0</v>
@@ -72593,7 +72746,7 @@
     </row>
     <row r="1233" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1233" s="1" t="s">
-        <v>1049</v>
+        <v>1008</v>
       </c>
       <c r="B1233" s="1">
         <v>11</v>
@@ -72608,16 +72761,16 @@
         <v>1</v>
       </c>
       <c r="G1233" s="1">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="H1233" s="1">
         <v>1500</v>
       </c>
       <c r="I1233" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J1233" s="2" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="K1233" s="1">
         <v>150</v>
@@ -72632,7 +72785,7 @@
         <v>0</v>
       </c>
       <c r="O1233" s="1" t="s">
-        <v>910</v>
+        <v>881</v>
       </c>
       <c r="P1233" s="1">
         <v>0</v>
@@ -72646,7 +72799,7 @@
     </row>
     <row r="1234" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1234" s="1" t="s">
-        <v>1050</v>
+        <v>1009</v>
       </c>
       <c r="B1234" s="1">
         <v>11</v>
@@ -72661,16 +72814,16 @@
         <v>1</v>
       </c>
       <c r="G1234" s="1">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H1234" s="1">
         <v>1500</v>
       </c>
       <c r="I1234" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J1234" s="2" t="s">
-        <v>940</v>
+        <v>917</v>
       </c>
       <c r="K1234" s="1">
         <v>150</v>
@@ -72685,7 +72838,7 @@
         <v>0</v>
       </c>
       <c r="O1234" s="1" t="s">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="P1234" s="1">
         <v>0</v>
@@ -72699,7 +72852,7 @@
     </row>
     <row r="1235" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1235" s="1" t="s">
-        <v>1051</v>
+        <v>1010</v>
       </c>
       <c r="B1235" s="1">
         <v>11</v>
@@ -72714,16 +72867,16 @@
         <v>1</v>
       </c>
       <c r="G1235" s="1">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H1235" s="1">
         <v>1500</v>
       </c>
       <c r="I1235" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J1235" s="2" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
       <c r="K1235" s="1">
         <v>150</v>
@@ -72738,7 +72891,7 @@
         <v>0</v>
       </c>
       <c r="O1235" s="1" t="s">
-        <v>911</v>
+        <v>887</v>
       </c>
       <c r="P1235" s="1">
         <v>0</v>
@@ -72752,7 +72905,7 @@
     </row>
     <row r="1236" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1236" s="1" t="s">
-        <v>1052</v>
+        <v>1011</v>
       </c>
       <c r="B1236" s="1">
         <v>11</v>
@@ -72767,16 +72920,16 @@
         <v>1</v>
       </c>
       <c r="G1236" s="1">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="H1236" s="1">
         <v>1500</v>
       </c>
       <c r="I1236" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J1236" s="2" t="s">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="K1236" s="1">
         <v>150</v>
@@ -72791,7 +72944,7 @@
         <v>0</v>
       </c>
       <c r="O1236" s="1" t="s">
-        <v>906</v>
+        <v>882</v>
       </c>
       <c r="P1236" s="1">
         <v>0</v>
@@ -72805,7 +72958,7 @@
     </row>
     <row r="1237" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1237" s="1" t="s">
-        <v>1053</v>
+        <v>1012</v>
       </c>
       <c r="B1237" s="1">
         <v>11</v>
@@ -72820,16 +72973,16 @@
         <v>1</v>
       </c>
       <c r="G1237" s="1">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H1237" s="1">
         <v>1500</v>
       </c>
       <c r="I1237" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J1237" s="2" t="s">
-        <v>941</v>
+        <v>918</v>
       </c>
       <c r="K1237" s="1">
         <v>150</v>
@@ -72844,7 +72997,7 @@
         <v>0</v>
       </c>
       <c r="O1237" s="1" t="s">
-        <v>912</v>
+        <v>888</v>
       </c>
       <c r="P1237" s="1">
         <v>0</v>
@@ -72858,7 +73011,7 @@
     </row>
     <row r="1238" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1238" s="1" t="s">
-        <v>1054</v>
+        <v>1013</v>
       </c>
       <c r="B1238" s="1">
         <v>11</v>
@@ -72873,16 +73026,16 @@
         <v>1</v>
       </c>
       <c r="G1238" s="1">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="H1238" s="1">
         <v>1500</v>
       </c>
       <c r="I1238" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J1238" s="2" t="s">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="K1238" s="1">
         <v>150</v>
@@ -72897,7 +73050,7 @@
         <v>0</v>
       </c>
       <c r="O1238" s="1" t="s">
-        <v>907</v>
+        <v>883</v>
       </c>
       <c r="P1238" s="1">
         <v>0</v>
@@ -72911,7 +73064,7 @@
     </row>
     <row r="1239" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1239" s="1" t="s">
-        <v>1055</v>
+        <v>1014</v>
       </c>
       <c r="B1239" s="1">
         <v>11</v>
@@ -72926,16 +73079,16 @@
         <v>1</v>
       </c>
       <c r="G1239" s="1">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H1239" s="1">
         <v>1500</v>
       </c>
       <c r="I1239" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J1239" s="2" t="s">
-        <v>941</v>
+        <v>918</v>
       </c>
       <c r="K1239" s="1">
         <v>150</v>
@@ -72950,7 +73103,7 @@
         <v>0</v>
       </c>
       <c r="O1239" s="1" t="s">
-        <v>913</v>
+        <v>889</v>
       </c>
       <c r="P1239" s="1">
         <v>0</v>
@@ -72964,7 +73117,7 @@
     </row>
     <row r="1240" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1240" s="1" t="s">
-        <v>1056</v>
+        <v>1015</v>
       </c>
       <c r="B1240" s="1">
         <v>11</v>
@@ -72979,16 +73132,16 @@
         <v>1</v>
       </c>
       <c r="G1240" s="1">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="H1240" s="1">
         <v>1500</v>
       </c>
       <c r="I1240" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J1240" s="2" t="s">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="K1240" s="1">
         <v>150</v>
@@ -73003,7 +73156,7 @@
         <v>0</v>
       </c>
       <c r="O1240" s="1" t="s">
-        <v>908</v>
+        <v>884</v>
       </c>
       <c r="P1240" s="1">
         <v>0</v>
@@ -73017,7 +73170,7 @@
     </row>
     <row r="1241" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1241" s="1" t="s">
-        <v>1057</v>
+        <v>1016</v>
       </c>
       <c r="B1241" s="1">
         <v>11</v>
@@ -73032,16 +73185,16 @@
         <v>1</v>
       </c>
       <c r="G1241" s="1">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H1241" s="1">
         <v>1500</v>
       </c>
       <c r="I1241" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J1241" s="2" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="K1241" s="1">
         <v>150</v>
@@ -73056,7 +73209,7 @@
         <v>0</v>
       </c>
       <c r="O1241" s="1" t="s">
-        <v>908</v>
+        <v>890</v>
       </c>
       <c r="P1241" s="1">
         <v>0</v>
@@ -73070,7 +73223,7 @@
     </row>
     <row r="1242" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1242" s="1" t="s">
-        <v>1058</v>
+        <v>1017</v>
       </c>
       <c r="B1242" s="1">
         <v>11</v>
@@ -73085,16 +73238,16 @@
         <v>1</v>
       </c>
       <c r="G1242" s="1">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="H1242" s="1">
         <v>1500</v>
       </c>
       <c r="I1242" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J1242" s="2" t="s">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="K1242" s="1">
         <v>150</v>
@@ -73109,7 +73262,7 @@
         <v>0</v>
       </c>
       <c r="O1242" s="1" t="s">
-        <v>899</v>
+        <v>885</v>
       </c>
       <c r="P1242" s="1">
         <v>0</v>
@@ -73123,7 +73276,7 @@
     </row>
     <row r="1243" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1243" s="1" t="s">
-        <v>1059</v>
+        <v>1018</v>
       </c>
       <c r="B1243" s="1">
         <v>11</v>
@@ -73138,16 +73291,16 @@
         <v>1</v>
       </c>
       <c r="G1243" s="1">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="H1243" s="1">
         <v>1500</v>
       </c>
       <c r="I1243" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J1243" s="2" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
       <c r="K1243" s="1">
         <v>150</v>
@@ -73162,7 +73315,7 @@
         <v>0</v>
       </c>
       <c r="O1243" s="1" t="s">
-        <v>909</v>
+        <v>885</v>
       </c>
       <c r="P1243" s="1">
         <v>0</v>
@@ -73176,7 +73329,7 @@
     </row>
     <row r="1244" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1244" s="1" t="s">
-        <v>1060</v>
+        <v>1019</v>
       </c>
       <c r="B1244" s="1">
         <v>11</v>
@@ -73191,16 +73344,16 @@
         <v>1</v>
       </c>
       <c r="G1244" s="1">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="H1244" s="1">
         <v>1500</v>
       </c>
       <c r="I1244" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1244" s="2" t="s">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="K1244" s="1">
         <v>150</v>
@@ -73215,7 +73368,7 @@
         <v>0</v>
       </c>
       <c r="O1244" s="1" t="s">
-        <v>901</v>
+        <v>876</v>
       </c>
       <c r="P1244" s="1">
         <v>0</v>
@@ -73229,7 +73382,7 @@
     </row>
     <row r="1245" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1245" s="1" t="s">
-        <v>1061</v>
+        <v>1020</v>
       </c>
       <c r="B1245" s="1">
         <v>11</v>
@@ -73244,16 +73397,16 @@
         <v>1</v>
       </c>
       <c r="G1245" s="1">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="H1245" s="1">
         <v>1500</v>
       </c>
       <c r="I1245" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1245" s="2" t="s">
-        <v>941</v>
+        <v>918</v>
       </c>
       <c r="K1245" s="1">
         <v>150</v>
@@ -73268,7 +73421,7 @@
         <v>0</v>
       </c>
       <c r="O1245" s="1" t="s">
-        <v>914</v>
+        <v>886</v>
       </c>
       <c r="P1245" s="1">
         <v>0</v>
@@ -73282,7 +73435,7 @@
     </row>
     <row r="1246" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1246" s="1" t="s">
-        <v>1062</v>
+        <v>1021</v>
       </c>
       <c r="B1246" s="1">
         <v>11</v>
@@ -73297,16 +73450,16 @@
         <v>1</v>
       </c>
       <c r="G1246" s="1">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="H1246" s="1">
         <v>1500</v>
       </c>
       <c r="I1246" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1246" s="2" t="s">
-        <v>942</v>
+        <v>919</v>
       </c>
       <c r="K1246" s="1">
         <v>150</v>
@@ -73321,7 +73474,7 @@
         <v>0</v>
       </c>
       <c r="O1246" s="1" t="s">
-        <v>903</v>
+        <v>878</v>
       </c>
       <c r="P1246" s="1">
         <v>0</v>
@@ -73335,7 +73488,7 @@
     </row>
     <row r="1247" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1247" s="1" t="s">
-        <v>1063</v>
+        <v>1022</v>
       </c>
       <c r="B1247" s="1">
         <v>11</v>
@@ -73350,16 +73503,16 @@
         <v>1</v>
       </c>
       <c r="G1247" s="1">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="H1247" s="1">
         <v>1500</v>
       </c>
       <c r="I1247" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1247" s="2" t="s">
-        <v>941</v>
+        <v>918</v>
       </c>
       <c r="K1247" s="1">
         <v>150</v>
@@ -73374,7 +73527,7 @@
         <v>0</v>
       </c>
       <c r="O1247" s="1" t="s">
-        <v>915</v>
+        <v>891</v>
       </c>
       <c r="P1247" s="1">
         <v>0</v>
@@ -73388,7 +73541,7 @@
     </row>
     <row r="1248" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1248" s="1" t="s">
-        <v>1064</v>
+        <v>1023</v>
       </c>
       <c r="B1248" s="1">
         <v>11</v>
@@ -73403,16 +73556,16 @@
         <v>1</v>
       </c>
       <c r="G1248" s="1">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="H1248" s="1">
         <v>1500</v>
       </c>
       <c r="I1248" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1248" s="2" t="s">
-        <v>942</v>
+        <v>919</v>
       </c>
       <c r="K1248" s="1">
         <v>150</v>
@@ -73427,7 +73580,7 @@
         <v>0</v>
       </c>
       <c r="O1248" s="1" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="P1248" s="1">
         <v>0</v>
@@ -73441,7 +73594,7 @@
     </row>
     <row r="1249" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1249" s="1" t="s">
-        <v>1065</v>
+        <v>1024</v>
       </c>
       <c r="B1249" s="1">
         <v>11</v>
@@ -73456,16 +73609,16 @@
         <v>1</v>
       </c>
       <c r="G1249" s="1">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="H1249" s="1">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="I1249" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J1249" s="2" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="K1249" s="1">
         <v>150</v>
@@ -73480,7 +73633,7 @@
         <v>0</v>
       </c>
       <c r="O1249" s="1" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="P1249" s="1">
         <v>0</v>
@@ -73489,6 +73642,960 @@
         <v>0</v>
       </c>
       <c r="R1249" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1250" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B1250" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1250" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1250" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1250" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1250" s="1">
+        <v>106</v>
+      </c>
+      <c r="H1250" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1250" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1250" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="K1250" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1250" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1250" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1250" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1250" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="P1250" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1250" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1250" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1251" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B1251" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1251" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1251" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1251" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1251" s="1">
+        <v>107</v>
+      </c>
+      <c r="H1251" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1251" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1251" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="K1251" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1251" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1251" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1251" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1251" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="P1251" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1251" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1251" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1252" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B1252" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1252" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1252" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1252" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1252" s="1">
+        <v>108</v>
+      </c>
+      <c r="H1252" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1252" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1252" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="K1252" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1252" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1252" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1252" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1252" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="P1252" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1252" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1252" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1253" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B1253" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1253" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1253" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1253" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1253" s="1">
+        <v>109</v>
+      </c>
+      <c r="H1253" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1253" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1253" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1253" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1253" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1253" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1253" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1253" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="P1253" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1253" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1253" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1254" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B1254" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1254" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1254" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1254" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1254" s="1">
+        <v>110</v>
+      </c>
+      <c r="H1254" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1254" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1254" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1254" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1254" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1254" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1254" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1254" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="P1254" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1254" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1254" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1255" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B1255" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1255" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1255" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1255" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1255" s="1">
+        <v>111</v>
+      </c>
+      <c r="H1255" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1255" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1255" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1255" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1255" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1255" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1255" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1255" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="P1255" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1255" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1255" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1256" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B1256" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1256" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1256" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1256" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1256" s="1">
+        <v>112</v>
+      </c>
+      <c r="H1256" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1256" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1256" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1256" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1256" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1256" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1256" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1256" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="P1256" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1256" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1256" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1257" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B1257" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1257" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1257" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1257" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1257" s="1">
+        <v>113</v>
+      </c>
+      <c r="H1257" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1257" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1257" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1257" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1257" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1257" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1257" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1257" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="P1257" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1257" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1257" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1258" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B1258" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1258" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1258" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1258" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1258" s="1">
+        <v>114</v>
+      </c>
+      <c r="H1258" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1258" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1258" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1258" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1258" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1258" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1258" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1258" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="P1258" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1258" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1258" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1259" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B1259" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1259" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1259" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1259" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1259" s="1">
+        <v>115</v>
+      </c>
+      <c r="H1259" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1259" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1259" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1259" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1259" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1259" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1259" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1259" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="P1259" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1259" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1259" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1260" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B1260" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1260" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1260" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1260" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1260" s="1">
+        <v>116</v>
+      </c>
+      <c r="H1260" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1260" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1260" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1260" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1260" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1260" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1260" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1260" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="P1260" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1260" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1260" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1261" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B1261" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1261" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1261" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1261" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1261" s="1">
+        <v>117</v>
+      </c>
+      <c r="H1261" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1261" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1261" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1261" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1261" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1261" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1261" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1261" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="P1261" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1261" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1261" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1262" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B1262" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1262" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1262" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1262" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1262" s="1">
+        <v>118</v>
+      </c>
+      <c r="H1262" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1262" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1262" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1262" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1262" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1262" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1262" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1262" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="P1262" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1262" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1262" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1263" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B1263" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1263" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1263" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1263" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1263" s="1">
+        <v>119</v>
+      </c>
+      <c r="H1263" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1263" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1263" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1263" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1263" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1263" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1263" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1263" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="P1263" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1263" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1263" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1264" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B1264" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1264" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1264" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1264" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1264" s="1">
+        <v>120</v>
+      </c>
+      <c r="H1264" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1264" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1264" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1264" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1264" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1264" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1264" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1264" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="P1264" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1264" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1264" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1265" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B1265" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1265" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1265" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1265" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1265" s="1">
+        <v>121</v>
+      </c>
+      <c r="H1265" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1265" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1265" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="K1265" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1265" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1265" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1265" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1265" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="P1265" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1265" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1265" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1266" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B1266" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1266" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1266" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1266" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1266" s="1">
+        <v>122</v>
+      </c>
+      <c r="H1266" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1266" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1266" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1266" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1266" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1266" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1266" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1266" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="P1266" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1266" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1266" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1267" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B1267" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1267" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1267" s="1">
+        <v>110003</v>
+      </c>
+      <c r="F1267" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1267" s="1">
+        <v>123</v>
+      </c>
+      <c r="H1267" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1267" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1267" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="K1267" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1267" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1267" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1267" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1267" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="P1267" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1267" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1267" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA7F1D6-C9AD-48A9-9D75-6C5CDEC4209E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A569381C-2D43-4737-AAC6-3A36A0E8DF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2902" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3148" uniqueCount="1309">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -3804,6 +3804,273 @@
   </si>
   <si>
     <t>50,45,60,45,55,45,45,45,65,45,40,45</t>
+  </si>
+  <si>
+    <t>114101</t>
+  </si>
+  <si>
+    <t>114101,114104</t>
+  </si>
+  <si>
+    <t>114101,114101</t>
+  </si>
+  <si>
+    <t>114104</t>
+  </si>
+  <si>
+    <t>114105,114104,114104</t>
+  </si>
+  <si>
+    <t>114101,114101,114101</t>
+  </si>
+  <si>
+    <t>114105,114101,114101</t>
+  </si>
+  <si>
+    <t>114105,114105,114104</t>
+  </si>
+  <si>
+    <t>114101,114101,114104</t>
+  </si>
+  <si>
+    <t>114105,114105,114105</t>
+  </si>
+  <si>
+    <t>114105,114105,114104,114104</t>
+  </si>
+  <si>
+    <t>114105,114105,114101,114101</t>
+  </si>
+  <si>
+    <t>114101,114101,114101,114101</t>
+  </si>
+  <si>
+    <t>114101,114101,114104,114104</t>
+  </si>
+  <si>
+    <t>114102,114101,114101</t>
+  </si>
+  <si>
+    <t>114105,114105,114105,114105</t>
+  </si>
+  <si>
+    <t>114105,114105,114105,114101,114101</t>
+  </si>
+  <si>
+    <t>114105,114105,114105,114104,114104</t>
+  </si>
+  <si>
+    <t>114102,114101,114101,114101</t>
+  </si>
+  <si>
+    <t>114101,114101,114101,114104,114104</t>
+  </si>
+  <si>
+    <t>114105,114105,114105,114105,114105</t>
+  </si>
+  <si>
+    <t>114102,114101,114101,114104,114104</t>
+  </si>
+  <si>
+    <t>114102,114105,114105,114104,114104</t>
+  </si>
+  <si>
+    <t>114105,114105,114105,114105,114105,114105</t>
+  </si>
+  <si>
+    <t>114102,114105,114105,114105,114105,114105</t>
+  </si>
+  <si>
+    <t>114102,114105,114105,114105,114104,114104</t>
+  </si>
+  <si>
+    <t>114102,114102,114105,114105,114105,114105</t>
+  </si>
+  <si>
+    <t>70,50</t>
+  </si>
+  <si>
+    <t>98,20,98,10</t>
+  </si>
+  <si>
+    <t>65,25</t>
+  </si>
+  <si>
+    <t>65,50</t>
+  </si>
+  <si>
+    <t>65,55,60,90</t>
+  </si>
+  <si>
+    <t>70,60,65,60</t>
+  </si>
+  <si>
+    <t>70,90</t>
+  </si>
+  <si>
+    <t>65,50,75,50</t>
+  </si>
+  <si>
+    <t>65,45,60,10</t>
+  </si>
+  <si>
+    <t>60,40,70,40</t>
+  </si>
+  <si>
+    <t>65,40,70,10</t>
+  </si>
+  <si>
+    <t>65,55,60,90,70,90</t>
+  </si>
+  <si>
+    <t>70,55,65,55,60,55</t>
+  </si>
+  <si>
+    <t>70,60,65,60,60,60</t>
+  </si>
+  <si>
+    <t>65,45,75,45,60,10</t>
+  </si>
+  <si>
+    <t>60,45,70,45,70,10</t>
+  </si>
+  <si>
+    <t>65,40,75,40,80,10</t>
+  </si>
+  <si>
+    <t>65,40,70,40,75,40</t>
+  </si>
+  <si>
+    <t>65,50,75,50,70,50</t>
+  </si>
+  <si>
+    <t>60,55,70,55,60,90,70,90</t>
+  </si>
+  <si>
+    <t>70,60,65,60,65,95,75,95</t>
+  </si>
+  <si>
+    <t>70,60,65,60,75,60</t>
+  </si>
+  <si>
+    <t>65,50,75,50,60,50,70,50</t>
+  </si>
+  <si>
+    <t>65,45,75,45,60,10,70,10</t>
+  </si>
+  <si>
+    <t>60,45,70,45,65,45</t>
+  </si>
+  <si>
+    <t>65,40,75,40,80,10,90,10</t>
+  </si>
+  <si>
+    <t>65,40,70,40,75,40,80,40</t>
+  </si>
+  <si>
+    <t>70,60,65,60,75,60,80,60</t>
+  </si>
+  <si>
+    <t>65,50,75,50,60,50,70,50,80,50</t>
+  </si>
+  <si>
+    <t>65,50,75,50,70,50,60,10,70,10</t>
+  </si>
+  <si>
+    <t>60,45,70,45,65,45,75,45</t>
+  </si>
+  <si>
+    <t>65,45,75,45,70,45,80,10,90,10</t>
+  </si>
+  <si>
+    <t>65,50,75,50,70,50,60,50,80,50</t>
+  </si>
+  <si>
+    <t>60,50,70,50,65,50,60,90,70,90</t>
+  </si>
+  <si>
+    <t>70,55,65,55,60,55,75,55</t>
+  </si>
+  <si>
+    <t>70,55,65,55,75,55,80,55,60,55</t>
+  </si>
+  <si>
+    <t>70,60,65,60,75,60,65,95,75,95</t>
+  </si>
+  <si>
+    <t>70,60,65,60,75,60,80,60,60,60</t>
+  </si>
+  <si>
+    <t>60,45,70,45,65,45,75,45,80,45</t>
+  </si>
+  <si>
+    <t>65,40,70,40,75,40,80,40,60,40</t>
+  </si>
+  <si>
+    <t>65,40,70,40,75,40,75,5,85,5</t>
+  </si>
+  <si>
+    <t>65,35,70,35,75,35,80,35,60,35</t>
+  </si>
+  <si>
+    <t>65,50,75,50,70,50,60,50,80,50,55,50</t>
+  </si>
+  <si>
+    <t>70,55,65,55,60,55,75,55,80,55,55,55</t>
+  </si>
+  <si>
+    <t>70,60,65,60,75,60,80,60,85,60,55,60</t>
+  </si>
+  <si>
+    <t>70,60,65,60,75,60,65,90,75,90</t>
+  </si>
+  <si>
+    <t>70,65,65,65,75,65,80,65,85,65,55,65</t>
+  </si>
+  <si>
+    <t>65,50,75,50,60,50,70,50,80,50,55,50</t>
+  </si>
+  <si>
+    <t>60,45,70,45,65,45,75,45,80,45,55,45</t>
+  </si>
+  <si>
+    <t>65,40,70,40,75,40,80,40,60,40,55,40</t>
+  </si>
+  <si>
+    <t>65,35,70,35,75,35,80,35,60,35,55,35</t>
+  </si>
+  <si>
+    <t>60,50,70,50,65,50,75,50,60,90,70,90</t>
+  </si>
+  <si>
+    <t>70,55,65,55,75,55,80,90,60,90</t>
+  </si>
+  <si>
+    <t>65,50,75,50,70,50,80,50,60,10,70,10</t>
+  </si>
+  <si>
+    <t>65,45,75,45,70,45,80,45,80,10,90,10</t>
+  </si>
+  <si>
+    <t>65,40,70,40,75,40,80,40,75,5,85,5</t>
+  </si>
+  <si>
+    <t>60,50,70,50,65,50,75,50,80,50,55,50</t>
+  </si>
+  <si>
+    <t>70,55,65,55,60,55,75,55,80,90,60,90</t>
+  </si>
+  <si>
+    <t>70,55,65,55,75,55,80,55,60,55,55,55</t>
+  </si>
+  <si>
+    <t>70,60,65,60,75,60,80,60,65,90,70,90</t>
+  </si>
+  <si>
+    <t>70,60,65,60,75,60,80,60,60,60,55,60</t>
+  </si>
+  <si>
+    <t>70,65,65,65,75,65,80,65,65,95,50,95</t>
   </si>
 </sst>
 </file>
@@ -4619,7 +4886,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1312"/>
+  <dimension ref="A1:R1435"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -77293,6 +77560,6525 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1313" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1313" s="1">
+        <v>1140101</v>
+      </c>
+      <c r="B1313" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1313" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1313" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1313" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1313" s="1">
+        <v>1</v>
+      </c>
+      <c r="H1313" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1313" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1313" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="K1313" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1313" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1313" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1313" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1313" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="P1313" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1313" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1313" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1314" s="1">
+        <v>1140102</v>
+      </c>
+      <c r="B1314" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1314" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1314" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1314" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1314" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1314" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1314" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1314" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="K1314" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1314" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1314" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1314" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1314" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="P1314" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1314" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1314" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1315" s="1">
+        <v>1140103</v>
+      </c>
+      <c r="B1315" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1315" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1315" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1315" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1315" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1315" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1315" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1315" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="K1315" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1315" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1315" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1315" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1315" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="P1315" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1315" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1315" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1316" s="1">
+        <v>1140201</v>
+      </c>
+      <c r="B1316" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1316" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1316" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1316" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1316" s="1">
+        <v>4</v>
+      </c>
+      <c r="H1316" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1316" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1316" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="K1316" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1316" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1316" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1316" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1316" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="P1316" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1316" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1316" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1317" s="1">
+        <v>1140202</v>
+      </c>
+      <c r="B1317" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1317" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1317" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1317" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1317" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1317" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1317" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1317" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="K1317" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1317" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1317" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1317" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1317" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="P1317" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1317" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1317" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1318" s="1">
+        <v>1140203</v>
+      </c>
+      <c r="B1318" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1318" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1318" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1318" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1318" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1318" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1318" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1318" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K1318" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1318" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1318" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1318" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1318" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="P1318" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1318" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1318" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1319" s="1">
+        <v>1140204</v>
+      </c>
+      <c r="B1319" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1319" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1319" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1319" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1319" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1319" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1319" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1319" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K1319" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1319" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1319" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1319" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1319" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="P1319" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1319" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1319" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1320" s="1">
+        <v>1140301</v>
+      </c>
+      <c r="B1320" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1320" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1320" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1320" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1320" s="1">
+        <v>8</v>
+      </c>
+      <c r="H1320" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1320" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1320" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K1320" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1320" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1320" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1320" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1320" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="P1320" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1320" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1320" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1321" s="1">
+        <v>1140302</v>
+      </c>
+      <c r="B1321" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1321" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1321" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1321" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1321" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1321" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1321" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1321" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="K1321" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1321" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1321" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1321" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1321" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="P1321" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1321" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1321" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1322" s="1">
+        <v>1140303</v>
+      </c>
+      <c r="B1322" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1322" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1322" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1322" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1322" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1322" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1322" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1322" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K1322" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1322" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1322" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1322" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1322" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="P1322" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1322" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1322" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1323" s="1">
+        <v>1140304</v>
+      </c>
+      <c r="B1323" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1323" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1323" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1323" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1323" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1323" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1323" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1323" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="K1323" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1323" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1323" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1323" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1323" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="P1323" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1323" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1323" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1324" s="1">
+        <v>1140401</v>
+      </c>
+      <c r="B1324" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1324" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1324" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1324" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1324" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1324" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1324" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1324" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K1324" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1324" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1324" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1324" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1324" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="P1324" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1324" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1324" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1325" s="1">
+        <v>1140402</v>
+      </c>
+      <c r="B1325" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1325" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1325" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1325" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1325" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1325" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1325" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1325" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="K1325" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1325" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1325" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1325" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1325" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="P1325" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1325" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1325" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1326" s="1">
+        <v>1140403</v>
+      </c>
+      <c r="B1326" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1326" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1326" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1326" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1326" s="1">
+        <v>14</v>
+      </c>
+      <c r="H1326" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1326" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1326" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="K1326" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1326" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1326" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1326" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1326" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="P1326" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1326" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1326" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1327" s="1">
+        <v>1140404</v>
+      </c>
+      <c r="B1327" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1327" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1327" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1327" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1327" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1327" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1327" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1327" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="K1327" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1327" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1327" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1327" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1327" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="P1327" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1327" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1327" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1328" s="1">
+        <v>1140501</v>
+      </c>
+      <c r="B1328" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1328" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1328" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1328" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1328" s="1">
+        <v>16</v>
+      </c>
+      <c r="H1328" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1328" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1328" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K1328" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1328" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1328" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1328" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1328" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="P1328" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1328" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1328" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1329" s="1">
+        <v>1140502</v>
+      </c>
+      <c r="B1329" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1329" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1329" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1329" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1329" s="1">
+        <v>17</v>
+      </c>
+      <c r="H1329" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1329" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1329" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="K1329" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1329" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1329" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1329" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1329" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="P1329" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1329" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1329" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1330" s="1">
+        <v>1140503</v>
+      </c>
+      <c r="B1330" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1330" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1330" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1330" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1330" s="1">
+        <v>18</v>
+      </c>
+      <c r="H1330" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1330" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1330" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K1330" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1330" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1330" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1330" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1330" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="P1330" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1330" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1330" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1331" s="1">
+        <v>1140504</v>
+      </c>
+      <c r="B1331" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1331" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1331" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1331" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1331" s="1">
+        <v>19</v>
+      </c>
+      <c r="H1331" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1331" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1331" s="2" t="s">
+        <v>1228</v>
+      </c>
+      <c r="K1331" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1331" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1331" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1331" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1331" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="P1331" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1331" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1331" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1332" s="1">
+        <v>1140505</v>
+      </c>
+      <c r="B1332" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1332" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1332" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1332" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1332" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1332" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1332" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1332" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K1332" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1332" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1332" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1332" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1332" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="P1332" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1332" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1332" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1333" s="1">
+        <v>1140601</v>
+      </c>
+      <c r="B1333" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1333" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1333" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1333" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1333" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1333" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1333" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1333" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="K1333" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1333" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1333" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1333" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1333" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P1333" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1333" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1333" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1334" s="1">
+        <v>1140602</v>
+      </c>
+      <c r="B1334" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1334" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1334" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1334" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1334" s="1">
+        <v>22</v>
+      </c>
+      <c r="H1334" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1334" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1334" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K1334" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1334" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1334" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1334" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1334" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="P1334" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1334" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1334" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1335" s="1">
+        <v>1140603</v>
+      </c>
+      <c r="B1335" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1335" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1335" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1335" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1335" s="1">
+        <v>23</v>
+      </c>
+      <c r="H1335" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1335" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1335" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="K1335" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1335" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1335" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1335" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1335" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="P1335" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1335" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1335" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1336" s="1">
+        <v>1140604</v>
+      </c>
+      <c r="B1336" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1336" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1336" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1336" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1336" s="1">
+        <v>24</v>
+      </c>
+      <c r="H1336" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1336" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1336" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K1336" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1336" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1336" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1336" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1336" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="P1336" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1336" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1336" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1337" s="1">
+        <v>1140605</v>
+      </c>
+      <c r="B1337" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1337" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1337" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1337" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1337" s="1">
+        <v>25</v>
+      </c>
+      <c r="H1337" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1337" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1337" s="2" t="s">
+        <v>1225</v>
+      </c>
+      <c r="K1337" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1337" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1337" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1337" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1337" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P1337" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1337" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1337" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1338" s="1">
+        <v>1140701</v>
+      </c>
+      <c r="B1338" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1338" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1338" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1338" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1338" s="1">
+        <v>26</v>
+      </c>
+      <c r="H1338" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1338" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1338" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="K1338" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1338" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1338" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1338" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1338" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="P1338" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1338" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1338" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1339" s="1">
+        <v>1140702</v>
+      </c>
+      <c r="B1339" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1339" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1339" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1339" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1339" s="1">
+        <v>27</v>
+      </c>
+      <c r="H1339" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1339" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1339" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K1339" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1339" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1339" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1339" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1339" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="P1339" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1339" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1339" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1340" s="1">
+        <v>1140703</v>
+      </c>
+      <c r="B1340" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1340" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1340" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1340" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1340" s="1">
+        <v>28</v>
+      </c>
+      <c r="H1340" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1340" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1340" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K1340" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1340" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1340" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1340" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1340" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="P1340" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1340" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1340" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1341" s="1">
+        <v>1140704</v>
+      </c>
+      <c r="B1341" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1341" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1341" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1341" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1341" s="1">
+        <v>29</v>
+      </c>
+      <c r="H1341" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1341" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1341" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="K1341" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1341" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1341" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1341" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1341" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="P1341" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1341" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1341" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1342" s="1">
+        <v>1140705</v>
+      </c>
+      <c r="B1342" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1342" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1342" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1342" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1342" s="1">
+        <v>30</v>
+      </c>
+      <c r="H1342" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1342" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1342" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="K1342" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1342" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1342" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1342" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1342" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="P1342" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1342" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1342" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1343" s="1">
+        <v>1140801</v>
+      </c>
+      <c r="B1343" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1343" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1343" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1343" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1343" s="1">
+        <v>31</v>
+      </c>
+      <c r="H1343" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1343" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1343" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K1343" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1343" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1343" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1343" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1343" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="P1343" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1343" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1343" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1344" s="1">
+        <v>1140802</v>
+      </c>
+      <c r="B1344" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1344" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1344" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1344" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1344" s="1">
+        <v>32</v>
+      </c>
+      <c r="H1344" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1344" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1344" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="K1344" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1344" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1344" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1344" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1344" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="P1344" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1344" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1344" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1345" s="1">
+        <v>1140803</v>
+      </c>
+      <c r="B1345" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1345" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1345" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1345" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1345" s="1">
+        <v>33</v>
+      </c>
+      <c r="H1345" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1345" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1345" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="K1345" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1345" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1345" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1345" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1345" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="P1345" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1345" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1345" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1346" s="1">
+        <v>1140804</v>
+      </c>
+      <c r="B1346" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1346" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1346" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1346" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1346" s="1">
+        <v>34</v>
+      </c>
+      <c r="H1346" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1346" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1346" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="K1346" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1346" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1346" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1346" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1346" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P1346" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1346" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1346" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1347" s="1">
+        <v>1140805</v>
+      </c>
+      <c r="B1347" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1347" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1347" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1347" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1347" s="1">
+        <v>35</v>
+      </c>
+      <c r="H1347" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1347" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1347" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="K1347" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1347" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1347" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1347" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1347" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="P1347" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1347" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1347" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1348" s="1">
+        <v>1140806</v>
+      </c>
+      <c r="B1348" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1348" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1348" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1348" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1348" s="1">
+        <v>36</v>
+      </c>
+      <c r="H1348" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1348" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1348" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K1348" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1348" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1348" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1348" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1348" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="P1348" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1348" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1348" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1349" s="1">
+        <v>1140901</v>
+      </c>
+      <c r="B1349" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1349" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1349" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1349" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1349" s="1">
+        <v>37</v>
+      </c>
+      <c r="H1349" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1349" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1349" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="K1349" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1349" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1349" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1349" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1349" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="P1349" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1349" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1349" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1350" s="1">
+        <v>1140902</v>
+      </c>
+      <c r="B1350" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1350" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1350" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1350" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1350" s="1">
+        <v>38</v>
+      </c>
+      <c r="H1350" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1350" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1350" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="K1350" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1350" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1350" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1350" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1350" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="P1350" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1350" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1350" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1351" s="1">
+        <v>1140903</v>
+      </c>
+      <c r="B1351" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1351" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1351" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1351" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1351" s="1">
+        <v>39</v>
+      </c>
+      <c r="H1351" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1351" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1351" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="K1351" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1351" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1351" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1351" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1351" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="P1351" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1351" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1351" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1352" s="1">
+        <v>1140904</v>
+      </c>
+      <c r="B1352" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1352" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1352" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1352" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1352" s="1">
+        <v>40</v>
+      </c>
+      <c r="H1352" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1352" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1352" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="K1352" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1352" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1352" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1352" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1352" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="P1352" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1352" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1352" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1353" s="1">
+        <v>1140905</v>
+      </c>
+      <c r="B1353" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1353" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1353" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1353" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1353" s="1">
+        <v>41</v>
+      </c>
+      <c r="H1353" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1353" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1353" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K1353" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1353" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1353" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1353" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1353" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="P1353" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1353" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1353" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1354" s="1">
+        <v>1140906</v>
+      </c>
+      <c r="B1354" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1354" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1354" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1354" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1354" s="1">
+        <v>42</v>
+      </c>
+      <c r="H1354" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1354" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1354" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="K1354" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1354" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1354" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1354" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1354" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="P1354" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1354" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1354" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1355" s="1">
+        <v>1141001</v>
+      </c>
+      <c r="B1355" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1355" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1355" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1355" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1355" s="1">
+        <v>43</v>
+      </c>
+      <c r="H1355" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1355" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1355" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K1355" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1355" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1355" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1355" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1355" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="P1355" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1355" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1355" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1356" s="1">
+        <v>1141002</v>
+      </c>
+      <c r="B1356" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1356" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1356" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1356" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1356" s="1">
+        <v>44</v>
+      </c>
+      <c r="H1356" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1356" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1356" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="K1356" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1356" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1356" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1356" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1356" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="P1356" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1356" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1356" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1357" s="1">
+        <v>1141003</v>
+      </c>
+      <c r="B1357" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1357" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1357" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1357" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1357" s="1">
+        <v>45</v>
+      </c>
+      <c r="H1357" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1357" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1357" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="K1357" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1357" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1357" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1357" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1357" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="P1357" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1357" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1357" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1358" s="1">
+        <v>1141004</v>
+      </c>
+      <c r="B1358" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1358" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1358" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1358" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1358" s="1">
+        <v>46</v>
+      </c>
+      <c r="H1358" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1358" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1358" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K1358" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1358" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1358" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1358" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1358" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="P1358" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1358" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1358" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1359" s="1">
+        <v>1141005</v>
+      </c>
+      <c r="B1359" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1359" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1359" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1359" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1359" s="1">
+        <v>47</v>
+      </c>
+      <c r="H1359" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1359" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1359" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="K1359" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1359" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1359" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1359" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1359" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="P1359" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1359" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1359" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1360" s="1">
+        <v>1141006</v>
+      </c>
+      <c r="B1360" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1360" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1360" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1360" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1360" s="1">
+        <v>48</v>
+      </c>
+      <c r="H1360" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1360" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1360" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K1360" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1360" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1360" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1360" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1360" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="P1360" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1360" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1360" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1361" s="1">
+        <v>1141101</v>
+      </c>
+      <c r="B1361" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1361" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1361" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1361" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1361" s="1">
+        <v>49</v>
+      </c>
+      <c r="H1361" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1361" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1361" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K1361" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1361" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1361" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1361" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1361" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="P1361" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1361" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1361" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1362" s="1">
+        <v>1141102</v>
+      </c>
+      <c r="B1362" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1362" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1362" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1362" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1362" s="1">
+        <v>50</v>
+      </c>
+      <c r="H1362" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1362" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1362" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1362" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1362" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1362" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1362" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1362" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="P1362" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1362" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1362" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1363" s="1">
+        <v>1141103</v>
+      </c>
+      <c r="B1363" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1363" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1363" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1363" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1363" s="1">
+        <v>51</v>
+      </c>
+      <c r="H1363" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1363" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1363" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K1363" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1363" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1363" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1363" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1363" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="P1363" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1363" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1363" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1364" s="1">
+        <v>1141104</v>
+      </c>
+      <c r="B1364" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1364" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1364" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1364" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1364" s="1">
+        <v>52</v>
+      </c>
+      <c r="H1364" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1364" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1364" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1364" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1364" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1364" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1364" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1364" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="P1364" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1364" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1364" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1365" s="1">
+        <v>1141105</v>
+      </c>
+      <c r="B1365" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1365" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1365" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1365" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1365" s="1">
+        <v>53</v>
+      </c>
+      <c r="H1365" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1365" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1365" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K1365" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1365" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1365" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1365" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1365" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="P1365" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1365" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1365" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1366" s="1">
+        <v>1141106</v>
+      </c>
+      <c r="B1366" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1366" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1366" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1366" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1366" s="1">
+        <v>54</v>
+      </c>
+      <c r="H1366" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1366" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1366" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1366" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1366" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1366" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1366" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1366" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="P1366" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1366" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1366" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1367" s="1">
+        <v>1141107</v>
+      </c>
+      <c r="B1367" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1367" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1367" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1367" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1367" s="1">
+        <v>55</v>
+      </c>
+      <c r="H1367" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1367" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1367" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="K1367" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1367" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1367" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1367" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1367" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="P1367" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1367" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1367" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1368" s="1">
+        <v>1141201</v>
+      </c>
+      <c r="B1368" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1368" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1368" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1368" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1368" s="1">
+        <v>56</v>
+      </c>
+      <c r="H1368" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1368" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1368" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1368" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1368" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1368" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1368" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1368" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="P1368" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1368" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1368" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1369" s="1">
+        <v>1141202</v>
+      </c>
+      <c r="B1369" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1369" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1369" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1369" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1369" s="1">
+        <v>57</v>
+      </c>
+      <c r="H1369" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1369" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1369" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1369" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1369" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1369" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1369" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1369" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="P1369" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1369" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1369" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1370" s="1">
+        <v>1141203</v>
+      </c>
+      <c r="B1370" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1370" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1370" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1370" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1370" s="1">
+        <v>58</v>
+      </c>
+      <c r="H1370" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1370" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1370" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1370" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1370" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1370" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1370" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1370" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="P1370" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1370" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1370" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1371" s="1">
+        <v>1141204</v>
+      </c>
+      <c r="B1371" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1371" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1371" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1371" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1371" s="1">
+        <v>59</v>
+      </c>
+      <c r="H1371" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1371" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1371" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1371" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1371" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1371" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1371" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1371" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="P1371" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1371" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1371" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1372" s="1">
+        <v>1141205</v>
+      </c>
+      <c r="B1372" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1372" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1372" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1372" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1372" s="1">
+        <v>60</v>
+      </c>
+      <c r="H1372" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1372" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1372" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1372" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1372" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1372" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1372" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1372" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="P1372" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1372" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1372" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1373" s="1">
+        <v>1141206</v>
+      </c>
+      <c r="B1373" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1373" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1373" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1373" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1373" s="1">
+        <v>61</v>
+      </c>
+      <c r="H1373" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1373" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1373" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1373" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1373" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1373" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1373" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1373" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="P1373" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1373" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1373" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1374" s="1">
+        <v>1141207</v>
+      </c>
+      <c r="B1374" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1374" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1374" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1374" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1374" s="1">
+        <v>62</v>
+      </c>
+      <c r="H1374" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1374" s="1">
+        <v>12</v>
+      </c>
+      <c r="J1374" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1374" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1374" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1374" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1374" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1374" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P1374" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1374" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1374" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1375" s="1">
+        <v>1141301</v>
+      </c>
+      <c r="B1375" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1375" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1375" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1375" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1375" s="1">
+        <v>63</v>
+      </c>
+      <c r="H1375" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1375" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1375" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1375" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1375" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1375" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1375" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1375" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="P1375" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1375" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1375" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1376" s="1">
+        <v>1141302</v>
+      </c>
+      <c r="B1376" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1376" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1376" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1376" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1376" s="1">
+        <v>64</v>
+      </c>
+      <c r="H1376" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1376" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1376" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1376" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1376" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1376" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1376" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1376" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="P1376" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1376" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1376" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1377" s="1">
+        <v>1141303</v>
+      </c>
+      <c r="B1377" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1377" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1377" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1377" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1377" s="1">
+        <v>65</v>
+      </c>
+      <c r="H1377" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1377" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1377" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1377" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1377" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1377" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1377" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1377" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P1377" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1377" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1377" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1378" s="1">
+        <v>1141304</v>
+      </c>
+      <c r="B1378" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1378" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1378" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1378" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1378" s="1">
+        <v>66</v>
+      </c>
+      <c r="H1378" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1378" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1378" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1378" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1378" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1378" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1378" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1378" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="P1378" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1378" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1378" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1379" s="1">
+        <v>1141305</v>
+      </c>
+      <c r="B1379" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1379" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1379" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1379" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1379" s="1">
+        <v>67</v>
+      </c>
+      <c r="H1379" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1379" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1379" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1379" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1379" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1379" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1379" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1379" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="P1379" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1379" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1379" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1380" s="1">
+        <v>1141306</v>
+      </c>
+      <c r="B1380" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1380" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1380" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1380" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1380" s="1">
+        <v>68</v>
+      </c>
+      <c r="H1380" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1380" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1380" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1380" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1380" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1380" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1380" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1380" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="P1380" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1380" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1380" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1381" s="1">
+        <v>1141307</v>
+      </c>
+      <c r="B1381" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1381" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1381" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1381" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1381" s="1">
+        <v>69</v>
+      </c>
+      <c r="H1381" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1381" s="1">
+        <v>13</v>
+      </c>
+      <c r="J1381" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1381" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1381" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1381" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1381" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1381" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="P1381" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1381" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1381" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1382" s="1">
+        <v>1141401</v>
+      </c>
+      <c r="B1382" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1382" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1382" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1382" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1382" s="1">
+        <v>70</v>
+      </c>
+      <c r="H1382" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1382" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1382" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1382" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1382" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1382" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1382" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1382" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="P1382" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1382" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1382" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1383" s="1">
+        <v>1141402</v>
+      </c>
+      <c r="B1383" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1383" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1383" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1383" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1383" s="1">
+        <v>71</v>
+      </c>
+      <c r="H1383" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1383" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1383" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1383" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1383" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1383" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1383" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1383" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="P1383" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1383" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1383" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1384" s="1">
+        <v>1141403</v>
+      </c>
+      <c r="B1384" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1384" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1384" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1384" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1384" s="1">
+        <v>72</v>
+      </c>
+      <c r="H1384" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1384" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1384" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1384" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1384" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1384" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1384" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1384" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="P1384" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1384" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1384" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1385" s="1">
+        <v>1141404</v>
+      </c>
+      <c r="B1385" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1385" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1385" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1385" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1385" s="1">
+        <v>73</v>
+      </c>
+      <c r="H1385" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1385" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1385" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1385" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1385" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1385" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1385" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1385" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="P1385" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1385" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1385" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1386" s="1">
+        <v>1141405</v>
+      </c>
+      <c r="B1386" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1386" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1386" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1386" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1386" s="1">
+        <v>74</v>
+      </c>
+      <c r="H1386" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1386" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1386" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1386" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1386" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1386" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1386" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1386" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="P1386" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1386" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1386" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1387" s="1">
+        <v>1141406</v>
+      </c>
+      <c r="B1387" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1387" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1387" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1387" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1387" s="1">
+        <v>75</v>
+      </c>
+      <c r="H1387" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1387" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1387" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1387" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1387" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1387" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1387" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1387" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="P1387" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1387" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1387" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1388" s="1">
+        <v>1141407</v>
+      </c>
+      <c r="B1388" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1388" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1388" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1388" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1388" s="1">
+        <v>76</v>
+      </c>
+      <c r="H1388" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1388" s="1">
+        <v>14</v>
+      </c>
+      <c r="J1388" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1388" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1388" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1388" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1388" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1388" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P1388" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1388" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1388" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1389" s="1">
+        <v>1141501</v>
+      </c>
+      <c r="B1389" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1389" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1389" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1389" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1389" s="1">
+        <v>77</v>
+      </c>
+      <c r="H1389" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1389" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1389" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K1389" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1389" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1389" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1389" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1389" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="P1389" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1389" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1389" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1390" s="1">
+        <v>1141502</v>
+      </c>
+      <c r="B1390" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1390" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1390" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1390" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1390" s="1">
+        <v>78</v>
+      </c>
+      <c r="H1390" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1390" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1390" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1390" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1390" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1390" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1390" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1390" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="P1390" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1390" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1390" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1391" s="1">
+        <v>1141503</v>
+      </c>
+      <c r="B1391" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1391" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1391" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1391" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1391" s="1">
+        <v>79</v>
+      </c>
+      <c r="H1391" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1391" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1391" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1391" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1391" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1391" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1391" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1391" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P1391" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1391" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1391" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1392" s="1">
+        <v>1141504</v>
+      </c>
+      <c r="B1392" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1392" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1392" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1392" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1392" s="1">
+        <v>80</v>
+      </c>
+      <c r="H1392" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1392" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1392" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1392" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1392" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1392" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1392" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1392" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="P1392" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1392" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1392" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1393" s="1">
+        <v>1141505</v>
+      </c>
+      <c r="B1393" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1393" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1393" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1393" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1393" s="1">
+        <v>81</v>
+      </c>
+      <c r="H1393" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1393" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1393" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1393" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1393" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1393" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1393" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1393" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="P1393" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1393" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1393" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1394" s="1">
+        <v>1141506</v>
+      </c>
+      <c r="B1394" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1394" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1394" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1394" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1394" s="1">
+        <v>82</v>
+      </c>
+      <c r="H1394" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1394" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1394" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1394" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1394" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1394" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1394" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1394" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="P1394" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1394" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1394" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1395" s="1">
+        <v>1141507</v>
+      </c>
+      <c r="B1395" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1395" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1395" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1395" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1395" s="1">
+        <v>83</v>
+      </c>
+      <c r="H1395" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1395" s="1">
+        <v>15</v>
+      </c>
+      <c r="J1395" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1395" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1395" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1395" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1395" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1395" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="P1395" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1395" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1395" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1396" s="1">
+        <v>1141601</v>
+      </c>
+      <c r="B1396" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1396" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1396" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1396" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1396" s="1">
+        <v>84</v>
+      </c>
+      <c r="H1396" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1396" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1396" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1396" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1396" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1396" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1396" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1396" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="P1396" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1396" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1396" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1397" s="1">
+        <v>1141602</v>
+      </c>
+      <c r="B1397" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1397" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1397" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1397" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1397" s="1">
+        <v>85</v>
+      </c>
+      <c r="H1397" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1397" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1397" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1397" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1397" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1397" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1397" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1397" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="P1397" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1397" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1397" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1398" s="1">
+        <v>1141603</v>
+      </c>
+      <c r="B1398" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1398" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1398" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1398" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1398" s="1">
+        <v>86</v>
+      </c>
+      <c r="H1398" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1398" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1398" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1398" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1398" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1398" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1398" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1398" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="P1398" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1398" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1398" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1399" s="1">
+        <v>1141604</v>
+      </c>
+      <c r="B1399" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1399" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1399" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1399" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1399" s="1">
+        <v>87</v>
+      </c>
+      <c r="H1399" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1399" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1399" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1399" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1399" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1399" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1399" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1399" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="P1399" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1399" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1399" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1400" s="1">
+        <v>1141605</v>
+      </c>
+      <c r="B1400" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1400" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1400" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1400" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1400" s="1">
+        <v>88</v>
+      </c>
+      <c r="H1400" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1400" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1400" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1400" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1400" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1400" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1400" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1400" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="P1400" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1400" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1400" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1401" s="1">
+        <v>1141606</v>
+      </c>
+      <c r="B1401" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1401" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1401" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1401" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1401" s="1">
+        <v>89</v>
+      </c>
+      <c r="H1401" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1401" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1401" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K1401" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1401" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1401" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1401" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1401" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="P1401" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1401" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1401" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1402" s="1">
+        <v>1141607</v>
+      </c>
+      <c r="B1402" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1402" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1402" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1402" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1402" s="1">
+        <v>90</v>
+      </c>
+      <c r="H1402" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1402" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1402" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1402" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1402" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1402" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1402" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1402" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P1402" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1402" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1402" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1403" s="1">
+        <v>1141608</v>
+      </c>
+      <c r="B1403" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1403" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1403" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1403" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1403" s="1">
+        <v>91</v>
+      </c>
+      <c r="H1403" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1403" s="1">
+        <v>16</v>
+      </c>
+      <c r="J1403" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1403" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1403" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1403" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1403" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1403" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P1403" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1403" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1403" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1404" s="1">
+        <v>1141701</v>
+      </c>
+      <c r="B1404" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1404" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1404" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1404" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1404" s="1">
+        <v>92</v>
+      </c>
+      <c r="H1404" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1404" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1404" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1404" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1404" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1404" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1404" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1404" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="P1404" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1404" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1404" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1405" s="1">
+        <v>1141702</v>
+      </c>
+      <c r="B1405" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1405" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1405" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1405" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1405" s="1">
+        <v>93</v>
+      </c>
+      <c r="H1405" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1405" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1405" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1405" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1405" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1405" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1405" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1405" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="P1405" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1405" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1405" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1406" s="1">
+        <v>1141703</v>
+      </c>
+      <c r="B1406" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1406" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1406" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1406" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1406" s="1">
+        <v>94</v>
+      </c>
+      <c r="H1406" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1406" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1406" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1406" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1406" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1406" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1406" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1406" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P1406" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1406" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1406" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1407" s="1">
+        <v>1141704</v>
+      </c>
+      <c r="B1407" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1407" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1407" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1407" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1407" s="1">
+        <v>95</v>
+      </c>
+      <c r="H1407" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1407" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1407" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1407" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1407" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1407" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1407" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1407" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="P1407" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1407" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1407" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1408" s="1">
+        <v>1141705</v>
+      </c>
+      <c r="B1408" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1408" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1408" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1408" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1408" s="1">
+        <v>96</v>
+      </c>
+      <c r="H1408" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1408" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1408" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1408" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1408" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1408" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1408" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1408" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="P1408" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1408" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1408" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1409" s="1">
+        <v>1141706</v>
+      </c>
+      <c r="B1409" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1409" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1409" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1409" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1409" s="1">
+        <v>97</v>
+      </c>
+      <c r="H1409" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1409" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1409" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1409" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1409" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1409" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1409" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1409" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P1409" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1409" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1409" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1410" s="1">
+        <v>1141707</v>
+      </c>
+      <c r="B1410" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1410" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1410" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1410" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1410" s="1">
+        <v>98</v>
+      </c>
+      <c r="H1410" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1410" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1410" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1410" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1410" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1410" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1410" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1410" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="P1410" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1410" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1410" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1411" s="1">
+        <v>1141708</v>
+      </c>
+      <c r="B1411" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1411" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1411" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1411" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1411" s="1">
+        <v>99</v>
+      </c>
+      <c r="H1411" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1411" s="1">
+        <v>17</v>
+      </c>
+      <c r="J1411" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1411" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1411" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1411" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1411" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1411" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="P1411" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1411" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1411" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1412" s="1">
+        <v>1141801</v>
+      </c>
+      <c r="B1412" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1412" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1412" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1412" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1412" s="1">
+        <v>100</v>
+      </c>
+      <c r="H1412" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1412" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1412" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1412" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1412" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1412" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1412" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1412" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="P1412" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1412" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1412" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1413" s="1">
+        <v>1141802</v>
+      </c>
+      <c r="B1413" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1413" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1413" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1413" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1413" s="1">
+        <v>101</v>
+      </c>
+      <c r="H1413" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1413" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1413" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1413" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1413" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1413" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1413" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1413" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="P1413" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1413" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1413" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1414" s="1">
+        <v>1141803</v>
+      </c>
+      <c r="B1414" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1414" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1414" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1414" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1414" s="1">
+        <v>102</v>
+      </c>
+      <c r="H1414" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1414" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1414" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1414" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1414" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1414" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1414" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1414" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="P1414" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1414" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1414" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1415" s="1">
+        <v>1141804</v>
+      </c>
+      <c r="B1415" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1415" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1415" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1415" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1415" s="1">
+        <v>103</v>
+      </c>
+      <c r="H1415" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1415" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1415" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1415" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1415" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1415" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1415" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1415" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="P1415" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1415" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1415" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1416" s="1">
+        <v>1141805</v>
+      </c>
+      <c r="B1416" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1416" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1416" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1416" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1416" s="1">
+        <v>104</v>
+      </c>
+      <c r="H1416" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1416" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1416" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1416" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1416" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1416" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1416" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1416" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="P1416" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1416" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1416" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1417" s="1">
+        <v>1141806</v>
+      </c>
+      <c r="B1417" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1417" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1417" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1417" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1417" s="1">
+        <v>105</v>
+      </c>
+      <c r="H1417" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1417" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1417" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1417" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1417" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1417" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1417" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1417" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="P1417" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1417" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1417" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1418" s="1">
+        <v>1141807</v>
+      </c>
+      <c r="B1418" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1418" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1418" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1418" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1418" s="1">
+        <v>106</v>
+      </c>
+      <c r="H1418" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1418" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1418" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1418" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1418" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1418" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1418" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1418" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P1418" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1418" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1418" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1419" s="1">
+        <v>1141808</v>
+      </c>
+      <c r="B1419" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1419" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1419" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1419" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1419" s="1">
+        <v>107</v>
+      </c>
+      <c r="H1419" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1419" s="1">
+        <v>18</v>
+      </c>
+      <c r="J1419" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1419" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1419" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1419" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1419" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1419" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P1419" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1419" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1419" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1420" s="1">
+        <v>1141901</v>
+      </c>
+      <c r="B1420" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1420" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1420" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1420" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1420" s="1">
+        <v>108</v>
+      </c>
+      <c r="H1420" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1420" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1420" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K1420" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1420" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1420" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1420" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1420" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="P1420" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1420" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1420" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1421" s="1">
+        <v>1141902</v>
+      </c>
+      <c r="B1421" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1421" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1421" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1421" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1421" s="1">
+        <v>109</v>
+      </c>
+      <c r="H1421" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1421" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1421" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1421" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1421" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1421" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1421" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1421" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="P1421" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1421" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1421" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1422" s="1">
+        <v>1141903</v>
+      </c>
+      <c r="B1422" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1422" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1422" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1422" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1422" s="1">
+        <v>110</v>
+      </c>
+      <c r="H1422" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1422" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1422" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1422" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1422" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1422" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1422" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1422" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="P1422" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1422" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1422" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1423" s="1">
+        <v>1141904</v>
+      </c>
+      <c r="B1423" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1423" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1423" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1423" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1423" s="1">
+        <v>111</v>
+      </c>
+      <c r="H1423" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1423" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1423" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1423" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1423" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1423" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1423" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1423" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="P1423" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1423" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1423" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1424" s="1">
+        <v>1141905</v>
+      </c>
+      <c r="B1424" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1424" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1424" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1424" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1424" s="1">
+        <v>112</v>
+      </c>
+      <c r="H1424" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1424" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1424" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1424" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1424" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1424" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1424" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1424" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="P1424" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1424" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1424" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1425" s="1">
+        <v>1141906</v>
+      </c>
+      <c r="B1425" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1425" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1425" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1425" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1425" s="1">
+        <v>113</v>
+      </c>
+      <c r="H1425" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1425" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1425" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1425" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1425" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1425" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1425" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1425" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="P1425" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1425" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1425" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1426" s="1">
+        <v>1141907</v>
+      </c>
+      <c r="B1426" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1426" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1426" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1426" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1426" s="1">
+        <v>114</v>
+      </c>
+      <c r="H1426" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1426" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1426" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1426" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1426" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1426" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1426" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1426" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="P1426" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1426" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1426" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1427" s="1">
+        <v>1141908</v>
+      </c>
+      <c r="B1427" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1427" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1427" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1427" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1427" s="1">
+        <v>115</v>
+      </c>
+      <c r="H1427" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1427" s="1">
+        <v>19</v>
+      </c>
+      <c r="J1427" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1427" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1427" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1427" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1427" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1427" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="P1427" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1427" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1427" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1428" s="1">
+        <v>1142001</v>
+      </c>
+      <c r="B1428" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1428" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1428" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1428" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1428" s="1">
+        <v>116</v>
+      </c>
+      <c r="H1428" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1428" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1428" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1428" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1428" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1428" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1428" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1428" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="P1428" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1428" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1428" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1429" s="1">
+        <v>1142002</v>
+      </c>
+      <c r="B1429" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1429" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1429" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1429" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1429" s="1">
+        <v>117</v>
+      </c>
+      <c r="H1429" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1429" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1429" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1429" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1429" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1429" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1429" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1429" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="P1429" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1429" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1429" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1430" s="1">
+        <v>1142003</v>
+      </c>
+      <c r="B1430" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1430" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1430" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1430" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1430" s="1">
+        <v>118</v>
+      </c>
+      <c r="H1430" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1430" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1430" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1430" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1430" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1430" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1430" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1430" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="P1430" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1430" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1430" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1431" s="1">
+        <v>1142004</v>
+      </c>
+      <c r="B1431" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1431" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1431" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1431" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1431" s="1">
+        <v>119</v>
+      </c>
+      <c r="H1431" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1431" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1431" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1431" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1431" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1431" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1431" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1431" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="P1431" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1431" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1431" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1432" s="1">
+        <v>1142005</v>
+      </c>
+      <c r="B1432" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1432" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1432" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1432" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1432" s="1">
+        <v>120</v>
+      </c>
+      <c r="H1432" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1432" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1432" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1432" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1432" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1432" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1432" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1432" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="P1432" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1432" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1432" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1433" s="1">
+        <v>1142006</v>
+      </c>
+      <c r="B1433" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1433" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1433" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1433" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1433" s="1">
+        <v>121</v>
+      </c>
+      <c r="H1433" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1433" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1433" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="K1433" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1433" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1433" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1433" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1433" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="P1433" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1433" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1433" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1434" s="1">
+        <v>1142007</v>
+      </c>
+      <c r="B1434" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1434" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1434" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1434" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1434" s="1">
+        <v>122</v>
+      </c>
+      <c r="H1434" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1434" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1434" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1434" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1434" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1434" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1434" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1434" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P1434" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1434" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1434" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1435" s="1">
+        <v>1142008</v>
+      </c>
+      <c r="B1435" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1435" s="1">
+        <v>4</v>
+      </c>
+      <c r="E1435" s="1">
+        <v>110004</v>
+      </c>
+      <c r="F1435" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1435" s="1">
+        <v>123</v>
+      </c>
+      <c r="H1435" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1435" s="1">
+        <v>20</v>
+      </c>
+      <c r="J1435" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="K1435" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1435" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1435" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1435" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1435" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="P1435" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1435" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1435" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2:A1012">

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FE8F3A-8E17-45B4-A2D2-6BC8CA43C0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC79BC1-9023-4A70-B7F9-BE3D6DBE8D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65480,7 +65480,7 @@
         <v>786</v>
       </c>
       <c r="K1082" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1082" s="1">
         <v>30000</v>
@@ -65533,7 +65533,7 @@
         <v>779</v>
       </c>
       <c r="K1083" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1083" s="1">
         <v>30000</v>
@@ -65586,7 +65586,7 @@
         <v>778</v>
       </c>
       <c r="K1084" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1084" s="1">
         <v>30000</v>
@@ -65639,7 +65639,7 @@
         <v>778</v>
       </c>
       <c r="K1085" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1085" s="1">
         <v>30000</v>
@@ -65692,7 +65692,7 @@
         <v>779</v>
       </c>
       <c r="K1086" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1086" s="1">
         <v>30000</v>
@@ -65745,7 +65745,7 @@
         <v>782</v>
       </c>
       <c r="K1087" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1087" s="1">
         <v>30000</v>
@@ -65798,7 +65798,7 @@
         <v>782</v>
       </c>
       <c r="K1088" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1088" s="1">
         <v>30000</v>
@@ -65851,7 +65851,7 @@
         <v>779</v>
       </c>
       <c r="K1089" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1089" s="1">
         <v>30000</v>
@@ -65904,7 +65904,7 @@
         <v>779</v>
       </c>
       <c r="K1090" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1090" s="1">
         <v>30000</v>
@@ -65957,7 +65957,7 @@
         <v>782</v>
       </c>
       <c r="K1091" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1091" s="1">
         <v>30000</v>
@@ -66010,7 +66010,7 @@
         <v>781</v>
       </c>
       <c r="K1092" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1092" s="1">
         <v>30000</v>
@@ -66063,7 +66063,7 @@
         <v>783</v>
       </c>
       <c r="K1093" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1093" s="1">
         <v>30000</v>
@@ -66116,7 +66116,7 @@
         <v>782</v>
       </c>
       <c r="K1094" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1094" s="1">
         <v>30000</v>
@@ -66169,7 +66169,7 @@
         <v>788</v>
       </c>
       <c r="K1095" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1095" s="1">
         <v>30000</v>
@@ -66222,7 +66222,7 @@
         <v>783</v>
       </c>
       <c r="K1096" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1096" s="1">
         <v>30000</v>
@@ -66275,7 +66275,7 @@
         <v>780</v>
       </c>
       <c r="K1097" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1097" s="1">
         <v>30000</v>
@@ -66328,7 +66328,7 @@
         <v>782</v>
       </c>
       <c r="K1098" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1098" s="1">
         <v>30000</v>
@@ -66381,7 +66381,7 @@
         <v>788</v>
       </c>
       <c r="K1099" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1099" s="1">
         <v>30000</v>
@@ -66434,7 +66434,7 @@
         <v>783</v>
       </c>
       <c r="K1100" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1100" s="1">
         <v>30000</v>
@@ -66487,7 +66487,7 @@
         <v>784</v>
       </c>
       <c r="K1101" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1101" s="1">
         <v>30000</v>
@@ -66540,7 +66540,7 @@
         <v>783</v>
       </c>
       <c r="K1102" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1102" s="1">
         <v>30000</v>
@@ -66593,7 +66593,7 @@
         <v>788</v>
       </c>
       <c r="K1103" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1103" s="1">
         <v>30000</v>
@@ -66646,7 +66646,7 @@
         <v>1305</v>
       </c>
       <c r="K1104" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1104" s="1">
         <v>30000</v>
@@ -66699,7 +66699,7 @@
         <v>784</v>
       </c>
       <c r="K1105" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1105" s="1">
         <v>30000</v>
@@ -66752,7 +66752,7 @@
         <v>783</v>
       </c>
       <c r="K1106" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1106" s="1">
         <v>30000</v>
@@ -66805,7 +66805,7 @@
         <v>1076</v>
       </c>
       <c r="K1107" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1107" s="1">
         <v>30000</v>
@@ -66858,7 +66858,7 @@
         <v>1305</v>
       </c>
       <c r="K1108" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1108" s="1">
         <v>30000</v>
@@ -66911,7 +66911,7 @@
         <v>1077</v>
       </c>
       <c r="K1109" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1109" s="1">
         <v>30000</v>
@@ -66964,7 +66964,7 @@
         <v>783</v>
       </c>
       <c r="K1110" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1110" s="1">
         <v>30000</v>
@@ -67017,7 +67017,7 @@
         <v>785</v>
       </c>
       <c r="K1111" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1111" s="1">
         <v>30000</v>
@@ -67070,7 +67070,7 @@
         <v>1076</v>
       </c>
       <c r="K1112" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1112" s="1">
         <v>30000</v>
@@ -67123,7 +67123,7 @@
         <v>1077</v>
       </c>
       <c r="K1113" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1113" s="1">
         <v>30000</v>
@@ -67176,7 +67176,7 @@
         <v>784</v>
       </c>
       <c r="K1114" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1114" s="1">
         <v>30000</v>
@@ -67229,7 +67229,7 @@
         <v>783</v>
       </c>
       <c r="K1115" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1115" s="1">
         <v>30000</v>
@@ -67282,7 +67282,7 @@
         <v>785</v>
       </c>
       <c r="K1116" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1116" s="1">
         <v>30000</v>
@@ -67335,7 +67335,7 @@
         <v>1076</v>
       </c>
       <c r="K1117" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1117" s="1">
         <v>30000</v>
@@ -67388,7 +67388,7 @@
         <v>1077</v>
       </c>
       <c r="K1118" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1118" s="1">
         <v>30000</v>
@@ -67441,7 +67441,7 @@
         <v>1078</v>
       </c>
       <c r="K1119" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1119" s="1">
         <v>30000</v>
@@ -67494,7 +67494,7 @@
         <v>1078</v>
       </c>
       <c r="K1120" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1120" s="1">
         <v>30000</v>
@@ -67547,7 +67547,7 @@
         <v>1306</v>
       </c>
       <c r="K1121" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1121" s="1">
         <v>30000</v>
@@ -67600,7 +67600,7 @@
         <v>1307</v>
       </c>
       <c r="K1122" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1122" s="1">
         <v>30000</v>
@@ -67653,7 +67653,7 @@
         <v>1076</v>
       </c>
       <c r="K1123" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1123" s="1">
         <v>30000</v>
@@ -67706,7 +67706,7 @@
         <v>1078</v>
       </c>
       <c r="K1124" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1124" s="1">
         <v>30000</v>
@@ -67759,7 +67759,7 @@
         <v>1077</v>
       </c>
       <c r="K1125" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1125" s="1">
         <v>30000</v>
@@ -67812,7 +67812,7 @@
         <v>1078</v>
       </c>
       <c r="K1126" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1126" s="1">
         <v>30000</v>
@@ -67865,7 +67865,7 @@
         <v>1306</v>
       </c>
       <c r="K1127" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1127" s="1">
         <v>30000</v>
@@ -67918,7 +67918,7 @@
         <v>1307</v>
       </c>
       <c r="K1128" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1128" s="1">
         <v>30000</v>
@@ -67971,7 +67971,7 @@
         <v>1076</v>
       </c>
       <c r="K1129" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1129" s="1">
         <v>30000</v>
@@ -68024,7 +68024,7 @@
         <v>1308</v>
       </c>
       <c r="K1130" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1130" s="1">
         <v>30000</v>
@@ -68077,7 +68077,7 @@
         <v>1309</v>
       </c>
       <c r="K1131" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1131" s="1">
         <v>30000</v>
@@ -68130,7 +68130,7 @@
         <v>1078</v>
       </c>
       <c r="K1132" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1132" s="1">
         <v>30000</v>
@@ -68183,7 +68183,7 @@
         <v>1310</v>
       </c>
       <c r="K1133" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1133" s="1">
         <v>30000</v>
@@ -68236,7 +68236,7 @@
         <v>1307</v>
       </c>
       <c r="K1134" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1134" s="1">
         <v>30000</v>
@@ -68289,7 +68289,7 @@
         <v>1076</v>
       </c>
       <c r="K1135" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1135" s="1">
         <v>30000</v>
@@ -68342,7 +68342,7 @@
         <v>1308</v>
       </c>
       <c r="K1136" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1136" s="1">
         <v>30000</v>
@@ -68395,7 +68395,7 @@
         <v>1308</v>
       </c>
       <c r="K1137" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1137" s="1">
         <v>30000</v>
@@ -68448,7 +68448,7 @@
         <v>1309</v>
       </c>
       <c r="K1138" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1138" s="1">
         <v>30000</v>
@@ -68501,7 +68501,7 @@
         <v>1310</v>
       </c>
       <c r="K1139" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1139" s="1">
         <v>30000</v>
@@ -68554,7 +68554,7 @@
         <v>1307</v>
       </c>
       <c r="K1140" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1140" s="1">
         <v>30000</v>
@@ -68607,7 +68607,7 @@
         <v>1311</v>
       </c>
       <c r="K1141" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1141" s="1">
         <v>30000</v>
@@ -68660,7 +68660,7 @@
         <v>1308</v>
       </c>
       <c r="K1142" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1142" s="1">
         <v>30000</v>
@@ -68713,7 +68713,7 @@
         <v>1308</v>
       </c>
       <c r="K1143" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1143" s="1">
         <v>30000</v>
@@ -68766,7 +68766,7 @@
         <v>1309</v>
       </c>
       <c r="K1144" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1144" s="1">
         <v>30000</v>
@@ -68819,7 +68819,7 @@
         <v>1310</v>
       </c>
       <c r="K1145" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1145" s="1">
         <v>30000</v>
@@ -68872,7 +68872,7 @@
         <v>1307</v>
       </c>
       <c r="K1146" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1146" s="1">
         <v>30000</v>
@@ -68925,7 +68925,7 @@
         <v>1311</v>
       </c>
       <c r="K1147" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1147" s="1">
         <v>30000</v>
@@ -68978,7 +68978,7 @@
         <v>1308</v>
       </c>
       <c r="K1148" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1148" s="1">
         <v>30000</v>
@@ -69031,7 +69031,7 @@
         <v>1312</v>
       </c>
       <c r="K1149" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1149" s="1">
         <v>30000</v>
@@ -69084,7 +69084,7 @@
         <v>1312</v>
       </c>
       <c r="K1150" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1150" s="1">
         <v>30000</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF3128C-01AE-4BA2-96E3-D2C55AAD814F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082D056E-229B-4432-BAE5-6C218227AEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3310" uniqueCount="1381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3332" uniqueCount="1394">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -4286,6 +4286,45 @@
   </si>
   <si>
     <t>1121015</t>
+  </si>
+  <si>
+    <t>88,88</t>
+  </si>
+  <si>
+    <t>88,75,91,70,94,65</t>
+  </si>
+  <si>
+    <t>60,75,55,75</t>
+  </si>
+  <si>
+    <t>60,80,55,80</t>
+  </si>
+  <si>
+    <t>15,75,20,75</t>
+  </si>
+  <si>
+    <t>15,50,15,45</t>
+  </si>
+  <si>
+    <t>80,55,85,60,85,50</t>
+  </si>
+  <si>
+    <t>50,80,45,80</t>
+  </si>
+  <si>
+    <t>115113</t>
+  </si>
+  <si>
+    <t>115101,115101,115101</t>
+  </si>
+  <si>
+    <t>115105,115105</t>
+  </si>
+  <si>
+    <t>115104,115104</t>
+  </si>
+  <si>
+    <t>115102,115101,115101</t>
   </si>
 </sst>
 </file>
@@ -5101,7 +5140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1489"/>
+  <dimension ref="A1:R1500"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -87156,6 +87195,589 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1490" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1490" s="1">
+        <v>1151001</v>
+      </c>
+      <c r="B1490" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1490" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1490" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1490" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1490" s="1">
+        <v>1</v>
+      </c>
+      <c r="H1490" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1490" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1490" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="K1490" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1490" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1490" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1490" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1490" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="P1490" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1490" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1490" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1491" s="1">
+        <v>1151002</v>
+      </c>
+      <c r="B1491" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1491" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1491" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1491" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1491" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1491" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1491" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1491" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="K1491" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1491" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1491" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1491" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1491" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="P1491" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1491" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1491" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1492" s="1">
+        <v>1151003</v>
+      </c>
+      <c r="B1492" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1492" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1492" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1492" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1492" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1492" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1492" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1492" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K1492" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1492" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1492" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1492" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1492" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="P1492" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1492" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1492" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1493" s="1">
+        <v>1151004</v>
+      </c>
+      <c r="B1493" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1493" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1493" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1493" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1493" s="1">
+        <v>4</v>
+      </c>
+      <c r="H1493" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1493" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1493" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="K1493" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1493" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1493" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1493" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1493" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="P1493" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1493" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1493" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1494" s="1">
+        <v>1151005</v>
+      </c>
+      <c r="B1494" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1494" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1494" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1494" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1494" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1494" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1494" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1494" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K1494" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1494" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1494" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1494" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1494" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P1494" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1494" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1494" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1495" s="1">
+        <v>1151006</v>
+      </c>
+      <c r="B1495" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1495" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1495" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1495" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1495" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1495" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1495" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1495" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K1495" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1495" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1495" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1495" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1495" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="P1495" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1495" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1495" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1496" s="1">
+        <v>1151007</v>
+      </c>
+      <c r="B1496" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1496" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1496" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1496" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1496" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1496" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1496" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1496" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="K1496" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1496" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1496" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1496" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1496" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="P1496" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1496" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1496" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1497" s="1">
+        <v>1151008</v>
+      </c>
+      <c r="B1497" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1497" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1497" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1497" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1497" s="1">
+        <v>8</v>
+      </c>
+      <c r="H1497" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1497" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1497" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="K1497" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1497" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1497" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1497" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1497" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="P1497" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1497" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1497" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1498" s="1">
+        <v>1151009</v>
+      </c>
+      <c r="B1498" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1498" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1498" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1498" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1498" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1498" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1498" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1498" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K1498" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1498" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1498" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1498" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1498" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P1498" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1498" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1498" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1499" s="1">
+        <v>1151010</v>
+      </c>
+      <c r="B1499" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1499" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1499" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1499" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1499" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1499" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1499" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1499" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K1499" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1499" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1499" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1499" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1499" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="P1499" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1499" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1499" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1500" s="1">
+        <v>1151011</v>
+      </c>
+      <c r="B1500" s="1">
+        <v>11</v>
+      </c>
+      <c r="D1500" s="1">
+        <v>5</v>
+      </c>
+      <c r="E1500" s="1">
+        <v>110005</v>
+      </c>
+      <c r="F1500" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1500" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1500" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1500" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1500" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="K1500" s="1">
+        <v>5000</v>
+      </c>
+      <c r="L1500" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1500" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1500" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1500" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="P1500" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1500" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1500" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A2:A1012">

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C7BC58-B2A4-4EDF-AC4D-0E701EC8825B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE14BCB-E626-4F76-90DC-5396C110F7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3335" uniqueCount="1405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3521" uniqueCount="1499">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -4355,10 +4355,293 @@
     <t>LIST&lt;INT&gt;_S_C</t>
   </si>
   <si>
+    <t>立即刷怪前置条件波次</t>
+  </si>
+  <si>
     <t>front_group_order</t>
-  </si>
-  <si>
-    <t>立即刷怪前置条件波次</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>121101</t>
+  </si>
+  <si>
+    <t>121101,121101</t>
+  </si>
+  <si>
+    <t>65,75,1500</t>
+  </si>
+  <si>
+    <t>35,75,1500</t>
+  </si>
+  <si>
+    <t>122101,122101,122101</t>
+  </si>
+  <si>
+    <t>0,5500,1500</t>
+  </si>
+  <si>
+    <t>90,5500,1500</t>
+  </si>
+  <si>
+    <t>122101,122101</t>
+  </si>
+  <si>
+    <t>270,5500,1500</t>
+  </si>
+  <si>
+    <t>123101,123101,123101</t>
+  </si>
+  <si>
+    <t>45,5500,1500</t>
+  </si>
+  <si>
+    <t>135,5500,1500</t>
+  </si>
+  <si>
+    <t>123105,123101,123101</t>
+  </si>
+  <si>
+    <t>225,5500,1500</t>
+  </si>
+  <si>
+    <t>123101,123101</t>
+  </si>
+  <si>
+    <t>315,5500,1500</t>
+  </si>
+  <si>
+    <t>124101,124101,124101,124101</t>
+  </si>
+  <si>
+    <t>30,5500,1500</t>
+  </si>
+  <si>
+    <t>124101,124101,124104</t>
+  </si>
+  <si>
+    <t>102,6500,1500</t>
+  </si>
+  <si>
+    <t>124105,124101,124101</t>
+  </si>
+  <si>
+    <t>174,5500,1500</t>
+  </si>
+  <si>
+    <t>246,5500,1500</t>
+  </si>
+  <si>
+    <t>318,5500,1500</t>
+  </si>
+  <si>
+    <t>125101,125101,125101,125101</t>
+  </si>
+  <si>
+    <t>70,5500,1500</t>
+  </si>
+  <si>
+    <t>125101,125101,125101,125104</t>
+  </si>
+  <si>
+    <t>142,6500,1500</t>
+  </si>
+  <si>
+    <t>125105,125101,125101,125101</t>
+  </si>
+  <si>
+    <t>214,5500,1500</t>
+  </si>
+  <si>
+    <t>125105,125105</t>
+  </si>
+  <si>
+    <t>75,55,75,45</t>
+  </si>
+  <si>
+    <t>125105,125101,125101,125101,125101</t>
+  </si>
+  <si>
+    <t>286,5500,1500</t>
+  </si>
+  <si>
+    <t>358,5500,1500</t>
+  </si>
+  <si>
+    <t>126105,126101,126101,126101</t>
+  </si>
+  <si>
+    <t>50,5500,1500</t>
+  </si>
+  <si>
+    <t>126105,126101,126101,126104</t>
+  </si>
+  <si>
+    <t>110,6500,1500</t>
+  </si>
+  <si>
+    <t>170,5500,1500</t>
+  </si>
+  <si>
+    <t>126105,126105,126105</t>
+  </si>
+  <si>
+    <t>35,75,30,70,25,65</t>
+  </si>
+  <si>
+    <t>230,5500,1500</t>
+  </si>
+  <si>
+    <t>126105,126105,126101,126101,126101</t>
+  </si>
+  <si>
+    <t>290,5500,1500</t>
+  </si>
+  <si>
+    <t>350,5500,1500</t>
+  </si>
+  <si>
+    <t>127105,127105,127101,127101</t>
+  </si>
+  <si>
+    <t>204,5500,1500</t>
+  </si>
+  <si>
+    <t>127105,127105,127104,127104</t>
+  </si>
+  <si>
+    <t>256,6500,1500</t>
+  </si>
+  <si>
+    <t>127105,127105,127101,127101,127101</t>
+  </si>
+  <si>
+    <t>308,5500,1500</t>
+  </si>
+  <si>
+    <t>127102,127101,127101,127101,127101</t>
+  </si>
+  <si>
+    <t>127105,127105,127105,127101,127101</t>
+  </si>
+  <si>
+    <t>52,5500,1500</t>
+  </si>
+  <si>
+    <t>104,5500,1500</t>
+  </si>
+  <si>
+    <t>156,5500,1500</t>
+  </si>
+  <si>
+    <t>128105,128105,128105,128101,128101</t>
+  </si>
+  <si>
+    <t>25,5500,1500</t>
+  </si>
+  <si>
+    <t>128102,128101,128101,128101,128101</t>
+  </si>
+  <si>
+    <t>128105,128105,128105,128104,128104</t>
+  </si>
+  <si>
+    <t>115,6500,1500</t>
+  </si>
+  <si>
+    <t>160,5500,1500</t>
+  </si>
+  <si>
+    <t>128102,128105,128105,128105</t>
+  </si>
+  <si>
+    <t>205,5500,1500</t>
+  </si>
+  <si>
+    <t>128105,128105,128105,128105</t>
+  </si>
+  <si>
+    <t>250,5500,1500</t>
+  </si>
+  <si>
+    <t>295,5500,1500</t>
+  </si>
+  <si>
+    <t>128102,128105,128105,128101,128101</t>
+  </si>
+  <si>
+    <t>340,5500,1500</t>
+  </si>
+  <si>
+    <t>129105,129105,129105,129101,129101</t>
+  </si>
+  <si>
+    <t>15,5500,1500</t>
+  </si>
+  <si>
+    <t>129102,129102,129101,129101,129101</t>
+  </si>
+  <si>
+    <t>55,5500,1500</t>
+  </si>
+  <si>
+    <t>95,5500,1500</t>
+  </si>
+  <si>
+    <t>129105,129105,129105,129104,129104</t>
+  </si>
+  <si>
+    <t>135,6500,1500</t>
+  </si>
+  <si>
+    <t>129102,129105,129105,129105</t>
+  </si>
+  <si>
+    <t>175,5500,1500</t>
+  </si>
+  <si>
+    <t>129105,129105,129105,129105</t>
+  </si>
+  <si>
+    <t>215,5500,1500</t>
+  </si>
+  <si>
+    <t>255,5500,1500</t>
+  </si>
+  <si>
+    <t>129105,129105,129105,129105,129105</t>
+  </si>
+  <si>
+    <t>129102,129102,129105,129105</t>
+  </si>
+  <si>
+    <t>335,5500,1500</t>
+  </si>
+  <si>
+    <t>1210113</t>
+  </si>
+  <si>
+    <t>1210105,1210105,1210105</t>
+  </si>
+  <si>
+    <t>95,95,1500</t>
+  </si>
+  <si>
+    <t>1210104,1210104</t>
+  </si>
+  <si>
+    <t>45,6500,1500</t>
+  </si>
+  <si>
+    <t>1210102,1210102</t>
+  </si>
+  <si>
+    <t>180,5500,1500</t>
+  </si>
+  <si>
+    <t>225,6500,1500</t>
   </si>
 </sst>
 </file>
@@ -4663,7 +4946,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4873,6 +5156,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5193,7 +5479,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S1500"/>
+  <dimension ref="A1:S1562"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -5342,7 +5628,7 @@
         <v>1399</v>
       </c>
       <c r="R3" s="69" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="S3" s="8" t="s">
         <v>751</v>
@@ -5401,7 +5687,7 @@
         <v>1400</v>
       </c>
       <c r="R4" s="70" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="S4" s="10" t="s">
         <v>752</v>
@@ -92327,6 +92613,3664 @@
         <v>0</v>
       </c>
       <c r="S1500" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1501" s="71">
+        <v>1210101</v>
+      </c>
+      <c r="B1501" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1501" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1501" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1501" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1501" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1501" s="1">
+        <v>1</v>
+      </c>
+      <c r="H1501" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I1501" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1501" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K1501" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1501" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1501" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1501" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1501" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="P1501" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1501" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1501" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1501" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1502" s="71">
+        <v>1210102</v>
+      </c>
+      <c r="B1502" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1502" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1502" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1502" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1502" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1502" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1502" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1502" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1502" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K1502" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1502" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1502" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1502" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1502" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1502" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="Q1502" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1502" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1502" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1503" s="71">
+        <v>1210103</v>
+      </c>
+      <c r="B1503" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1503" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1503" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1503" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1503" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1503" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1503" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1503" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1503" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K1503" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1503" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1503" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1503" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1503" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1503" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="Q1503" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1503" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1503" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1504" s="71">
+        <v>1210201</v>
+      </c>
+      <c r="B1504" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1504" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1504" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1504" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1504" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1504" s="1">
+        <v>4</v>
+      </c>
+      <c r="H1504" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1504" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1504" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="K1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1504" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1504" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="R1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1504" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1505" s="71">
+        <v>1210202</v>
+      </c>
+      <c r="B1505" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1505" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1505" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1505" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1505" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1505" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1505" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1505" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1505" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="K1505" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1505" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1505" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1505" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1505" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1505" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1505" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="R1505" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1505" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1506" s="71">
+        <v>1210203</v>
+      </c>
+      <c r="B1506" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1506" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1506" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1506" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1506" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1506" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1506" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1506" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1506" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="K1506" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1506" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1506" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1506" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1506" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1506" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1506" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="R1506" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1506" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1507" s="71">
+        <v>1210301</v>
+      </c>
+      <c r="B1507" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1507" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1507" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1507" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1507" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1507" s="1">
+        <v>7</v>
+      </c>
+      <c r="H1507" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1507" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1507" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K1507" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1507" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1507" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1507" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1507" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1507" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1507" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="R1507" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1507" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1508" s="71">
+        <v>1210302</v>
+      </c>
+      <c r="B1508" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1508" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1508" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1508" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1508" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1508" s="1">
+        <v>8</v>
+      </c>
+      <c r="H1508" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1508" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1508" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K1508" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1508" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1508" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1508" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1508" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1508" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1508" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="R1508" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1508" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1509" s="71">
+        <v>1210303</v>
+      </c>
+      <c r="B1509" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1509" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1509" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1509" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1509" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1509" s="1">
+        <v>9</v>
+      </c>
+      <c r="H1509" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1509" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1509" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="K1509" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1509" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1509" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1509" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1509" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1509" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1509" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="R1509" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1509" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1510" s="71">
+        <v>1210304</v>
+      </c>
+      <c r="B1510" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1510" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1510" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1510" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1510" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1510" s="1">
+        <v>10</v>
+      </c>
+      <c r="H1510" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1510" s="1">
+        <v>3</v>
+      </c>
+      <c r="J1510" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="K1510" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1510" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1510" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1510" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1510" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1510" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1510" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="R1510" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1510" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1511" s="71">
+        <v>1210401</v>
+      </c>
+      <c r="B1511" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1511" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1511" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1511" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1511" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1511" s="1">
+        <v>11</v>
+      </c>
+      <c r="H1511" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1511" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1511" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="K1511" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1511" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1511" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1511" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1511" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1511" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1511" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="R1511" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1511" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1512" s="71">
+        <v>1210402</v>
+      </c>
+      <c r="B1512" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1512" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1512" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1512" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1512" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1512" s="1">
+        <v>12</v>
+      </c>
+      <c r="H1512" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1512" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1512" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="K1512" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1512" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1512" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1512" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1512" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1512" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1512" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="R1512" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1512" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1513" s="71">
+        <v>1210403</v>
+      </c>
+      <c r="B1513" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1513" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1513" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1513" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1513" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1513" s="1">
+        <v>13</v>
+      </c>
+      <c r="H1513" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1513" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1513" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1513" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1513" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="R1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1513" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1514" s="71">
+        <v>1210404</v>
+      </c>
+      <c r="B1514" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1514" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1514" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1514" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1514" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1514" s="1">
+        <v>14</v>
+      </c>
+      <c r="H1514" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1514" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1514" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1514" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1514" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="R1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1514" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1515" s="71">
+        <v>1210405</v>
+      </c>
+      <c r="B1515" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1515" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1515" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1515" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1515" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1515" s="1">
+        <v>15</v>
+      </c>
+      <c r="H1515" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1515" s="1">
+        <v>4</v>
+      </c>
+      <c r="J1515" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K1515" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1515" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1515" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1515" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1515" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1515" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1515" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="R1515" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1515" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1516" s="71">
+        <v>1210501</v>
+      </c>
+      <c r="B1516" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1516" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1516" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1516" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1516" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1516" s="1">
+        <v>16</v>
+      </c>
+      <c r="H1516" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1516" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1516" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="K1516" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1516" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1516" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1516" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1516" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1516" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1516" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="R1516" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1516" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1517" s="71">
+        <v>1210502</v>
+      </c>
+      <c r="B1517" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1517" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1517" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1517" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1517" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1517" s="1">
+        <v>17</v>
+      </c>
+      <c r="H1517" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1517" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1517" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="K1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1517" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1517" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="R1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1517" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1518" s="71">
+        <v>1210503</v>
+      </c>
+      <c r="B1518" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1518" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1518" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1518" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1518" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1518" s="1">
+        <v>18</v>
+      </c>
+      <c r="H1518" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1518" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1518" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="K1518" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1518" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1518" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1518" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1518" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1518" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1518" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="R1518" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1518" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1519" s="71">
+        <v>1210504</v>
+      </c>
+      <c r="B1519" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1519" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1519" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1519" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1519" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1519" s="1">
+        <v>19</v>
+      </c>
+      <c r="H1519" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1519" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1519" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="K1519" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1519" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1519" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1519" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1519" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="P1519" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1519" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1519" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1519" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1520" s="71">
+        <v>1210505</v>
+      </c>
+      <c r="B1520" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1520" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1520" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1520" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1520" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1520" s="1">
+        <v>20</v>
+      </c>
+      <c r="H1520" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1520" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1520" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="K1520" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1520" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1520" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1520" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1520" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1520" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1520" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="R1520" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1520" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1521" s="71">
+        <v>1210506</v>
+      </c>
+      <c r="B1521" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1521" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1521" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1521" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1521" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1521" s="1">
+        <v>21</v>
+      </c>
+      <c r="H1521" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I1521" s="1">
+        <v>5</v>
+      </c>
+      <c r="J1521" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="K1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1521" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1521" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="R1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1521" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1522" s="71">
+        <v>1210601</v>
+      </c>
+      <c r="B1522" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1522" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1522" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1522" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1522" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1522" s="1">
+        <v>22</v>
+      </c>
+      <c r="H1522" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1522" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1522" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="K1522" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1522" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1522" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1522" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1522" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1522" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1522" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="R1522" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1522" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1523" s="71">
+        <v>1210602</v>
+      </c>
+      <c r="B1523" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1523" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1523" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1523" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1523" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1523" s="1">
+        <v>23</v>
+      </c>
+      <c r="H1523" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1523" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1523" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="K1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1523" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1523" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="R1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1523" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1524" s="71">
+        <v>1210603</v>
+      </c>
+      <c r="B1524" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1524" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1524" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1524" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1524" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1524" s="1">
+        <v>24</v>
+      </c>
+      <c r="H1524" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1524" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1524" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="K1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1524" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1524" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="R1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1524" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1525" s="71">
+        <v>1210604</v>
+      </c>
+      <c r="B1525" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1525" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1525" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1525" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1525" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1525" s="1">
+        <v>25</v>
+      </c>
+      <c r="H1525" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1525" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1525" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="K1525" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1525" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1525" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1525" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1525" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="P1525" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1525" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1525" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1525" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1526" s="71">
+        <v>1210605</v>
+      </c>
+      <c r="B1526" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1526" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1526" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1526" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1526" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1526" s="1">
+        <v>26</v>
+      </c>
+      <c r="H1526" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1526" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1526" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="K1526" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1526" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1526" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1526" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1526" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1526" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1526" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="R1526" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1526" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1527" s="71">
+        <v>1210606</v>
+      </c>
+      <c r="B1527" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1527" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1527" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1527" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1527" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1527" s="1">
+        <v>27</v>
+      </c>
+      <c r="H1527" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1527" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1527" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="K1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1527" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1527" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="R1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1527" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1528" s="71">
+        <v>1210607</v>
+      </c>
+      <c r="B1528" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1528" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1528" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1528" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1528" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1528" s="1">
+        <v>28</v>
+      </c>
+      <c r="H1528" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1528" s="1">
+        <v>6</v>
+      </c>
+      <c r="J1528" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="K1528" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1528" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1528" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1528" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1528" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1528" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1528" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="R1528" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1528" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1529" s="71">
+        <v>1210701</v>
+      </c>
+      <c r="B1529" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1529" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1529" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1529" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1529" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1529" s="1">
+        <v>29</v>
+      </c>
+      <c r="H1529" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1529" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1529" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="K1529" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1529" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1529" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1529" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1529" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1529" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1529" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="R1529" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1529" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1530" s="71">
+        <v>1210702</v>
+      </c>
+      <c r="B1530" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1530" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1530" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1530" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1530" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1530" s="1">
+        <v>30</v>
+      </c>
+      <c r="H1530" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1530" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1530" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="K1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1530" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1530" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="R1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1530" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1531" s="71">
+        <v>1210703</v>
+      </c>
+      <c r="B1531" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1531" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1531" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1531" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1531" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1531" s="1">
+        <v>31</v>
+      </c>
+      <c r="H1531" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1531" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1531" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="K1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1531" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1531" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="R1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1531" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1532" s="71">
+        <v>1210704</v>
+      </c>
+      <c r="B1532" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1532" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1532" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1532" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1532" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1532" s="1">
+        <v>32</v>
+      </c>
+      <c r="H1532" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1532" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1532" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K1532" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1532" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1532" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1532" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1532" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1532" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1532" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="R1532" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1532" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1533" s="71">
+        <v>1210705</v>
+      </c>
+      <c r="B1533" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1533" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1533" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1533" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1533" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1533" s="1">
+        <v>33</v>
+      </c>
+      <c r="H1533" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1533" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1533" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="K1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1533" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1533" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="R1533" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1533" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1534" s="71">
+        <v>1210706</v>
+      </c>
+      <c r="B1534" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1534" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1534" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1534" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1534" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1534" s="1">
+        <v>34</v>
+      </c>
+      <c r="H1534" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1534" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1534" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="K1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1534" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1534" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="R1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1534" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1535" s="71">
+        <v>1210707</v>
+      </c>
+      <c r="B1535" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1535" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1535" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1535" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1535" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1535" s="1">
+        <v>35</v>
+      </c>
+      <c r="H1535" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1535" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1535" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="K1535" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1535" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1535" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1535" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1535" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1535" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1535" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="R1535" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1535" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1536" s="71">
+        <v>1210801</v>
+      </c>
+      <c r="B1536" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1536" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1536" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1536" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1536" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1536" s="1">
+        <v>36</v>
+      </c>
+      <c r="H1536" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1536" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1536" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="K1536" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1536" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1536" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1536" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1536" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1536" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1536" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="R1536" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1536" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1537" s="71">
+        <v>1210802</v>
+      </c>
+      <c r="B1537" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1537" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1537" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1537" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1537" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1537" s="1">
+        <v>37</v>
+      </c>
+      <c r="H1537" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1537" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1537" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="K1537" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1537" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1537" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1537" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1537" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1537" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1537" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="R1537" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1537" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1538" s="71">
+        <v>1210803</v>
+      </c>
+      <c r="B1538" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1538" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1538" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1538" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1538" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1538" s="1">
+        <v>38</v>
+      </c>
+      <c r="H1538" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1538" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1538" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="K1538" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1538" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1538" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1538" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1538" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1538" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1538" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="R1538" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1538" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1539" s="71">
+        <v>1210804</v>
+      </c>
+      <c r="B1539" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1539" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1539" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1539" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1539" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1539" s="1">
+        <v>39</v>
+      </c>
+      <c r="H1539" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1539" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1539" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="K1539" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1539" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1539" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1539" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1539" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1539" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1539" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="R1539" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1539" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1540" s="71">
+        <v>1210805</v>
+      </c>
+      <c r="B1540" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1540" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1540" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1540" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1540" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1540" s="1">
+        <v>40</v>
+      </c>
+      <c r="H1540" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1540" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1540" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="K1540" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1540" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1540" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1540" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1540" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1540" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1540" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="R1540" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1540" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1541" s="71">
+        <v>1210806</v>
+      </c>
+      <c r="B1541" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1541" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1541" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1541" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1541" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1541" s="1">
+        <v>41</v>
+      </c>
+      <c r="H1541" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1541" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1541" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1541" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1541" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="R1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1541" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1542" s="71">
+        <v>1210807</v>
+      </c>
+      <c r="B1542" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1542" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1542" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1542" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1542" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1542" s="1">
+        <v>42</v>
+      </c>
+      <c r="H1542" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1542" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1542" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="K1542" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1542" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1542" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1542" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1542" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1542" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1542" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="R1542" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1542" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1543" s="71">
+        <v>1210808</v>
+      </c>
+      <c r="B1543" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1543" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1543" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1543" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1543" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1543" s="1">
+        <v>43</v>
+      </c>
+      <c r="H1543" s="1">
+        <v>1800</v>
+      </c>
+      <c r="I1543" s="1">
+        <v>8</v>
+      </c>
+      <c r="J1543" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="K1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1543" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1543" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="R1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1543" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1544" s="71">
+        <v>1210901</v>
+      </c>
+      <c r="B1544" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1544" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1544" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1544" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1544" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1544" s="1">
+        <v>44</v>
+      </c>
+      <c r="H1544" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I1544" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1544" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="K1544" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1544" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1544" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1544" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1544" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1544" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1544" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="R1544" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1544" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1545" s="71">
+        <v>1210902</v>
+      </c>
+      <c r="B1545" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1545" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1545" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1545" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1545" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1545" s="1">
+        <v>45</v>
+      </c>
+      <c r="H1545" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I1545" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1545" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="K1545" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1545" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1545" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1545" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1545" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1545" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1545" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="R1545" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1545" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1546" s="71">
+        <v>1210903</v>
+      </c>
+      <c r="B1546" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1546" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1546" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1546" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1546" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1546" s="1">
+        <v>46</v>
+      </c>
+      <c r="H1546" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I1546" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1546" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="K1546" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1546" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1546" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1546" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1546" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1546" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1546" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="R1546" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1546" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1547" s="71">
+        <v>1210904</v>
+      </c>
+      <c r="B1547" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1547" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1547" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1547" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1547" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1547" s="1">
+        <v>47</v>
+      </c>
+      <c r="H1547" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I1547" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1547" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="K1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1547" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1547" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="R1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1547" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1548" s="71">
+        <v>1210905</v>
+      </c>
+      <c r="B1548" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1548" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1548" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1548" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1548" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1548" s="1">
+        <v>48</v>
+      </c>
+      <c r="H1548" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I1548" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1548" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="K1548" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1548" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1548" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1548" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1548" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1548" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1548" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="R1548" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1548" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1549" s="71">
+        <v>1210906</v>
+      </c>
+      <c r="B1549" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1549" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1549" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1549" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1549" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1549" s="1">
+        <v>49</v>
+      </c>
+      <c r="H1549" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I1549" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1549" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="K1549" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1549" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1549" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1549" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1549" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1549" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1549" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="R1549" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1549" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1550" s="71">
+        <v>1210907</v>
+      </c>
+      <c r="B1550" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1550" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1550" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1550" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1550" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1550" s="1">
+        <v>50</v>
+      </c>
+      <c r="H1550" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I1550" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1550" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="K1550" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1550" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1550" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1550" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1550" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1550" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1550" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="R1550" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1550" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1551" s="71">
+        <v>1210908</v>
+      </c>
+      <c r="B1551" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1551" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1551" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1551" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1551" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1551" s="1">
+        <v>51</v>
+      </c>
+      <c r="H1551" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I1551" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1551" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="K1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1551" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1551" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="R1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1551" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1552" s="71">
+        <v>1210909</v>
+      </c>
+      <c r="B1552" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1552" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1552" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1552" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1552" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1552" s="1">
+        <v>52</v>
+      </c>
+      <c r="H1552" s="1">
+        <v>1600</v>
+      </c>
+      <c r="I1552" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1552" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="K1552" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1552" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1552" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1552" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1552" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1552" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1552" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="R1552" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1552" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1553" s="71">
+        <v>1211001</v>
+      </c>
+      <c r="B1553" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1553" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1553" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1553" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1553" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1553" s="1">
+        <v>53</v>
+      </c>
+      <c r="H1553" s="1">
+        <v>500</v>
+      </c>
+      <c r="I1553" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1553" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="K1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1553" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1553" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1553" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1554" s="71">
+        <v>1211002</v>
+      </c>
+      <c r="B1554" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1554" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1554" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1554" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1554" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1554" s="1">
+        <v>54</v>
+      </c>
+      <c r="H1554" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1554" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1554" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K1554" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1554" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1554" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1554" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1554" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1554" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="Q1554" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1554" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1554" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1555" s="71">
+        <v>1211003</v>
+      </c>
+      <c r="B1555" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1555" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1555" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1555" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1555" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1555" s="1">
+        <v>55</v>
+      </c>
+      <c r="H1555" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1555" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1555" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1555" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1555" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="R1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1555" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1556" s="71">
+        <v>1211004</v>
+      </c>
+      <c r="B1556" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1556" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1556" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1556" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1556" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1556" s="1">
+        <v>56</v>
+      </c>
+      <c r="H1556" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1556" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1556" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="K1556" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1556" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1556" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1556" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1556" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1556" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1556" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="R1556" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1556" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1557" s="71">
+        <v>1211005</v>
+      </c>
+      <c r="B1557" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1557" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1557" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1557" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1557" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1557" s="1">
+        <v>57</v>
+      </c>
+      <c r="H1557" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1557" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1557" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K1557" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1557" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1557" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1557" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1557" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1557" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1557" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="R1557" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1557" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1558" s="71">
+        <v>1211006</v>
+      </c>
+      <c r="B1558" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1558" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1558" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1558" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1558" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1558" s="1">
+        <v>58</v>
+      </c>
+      <c r="H1558" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1558" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1558" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="K1558" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1558" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1558" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1558" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1558" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1558" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1558" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="R1558" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1558" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1559" s="71">
+        <v>1211007</v>
+      </c>
+      <c r="B1559" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1559" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1559" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1559" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1559" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1559" s="1">
+        <v>59</v>
+      </c>
+      <c r="H1559" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1559" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1559" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1559" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1559" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="R1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1559" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1560" s="71">
+        <v>1211008</v>
+      </c>
+      <c r="B1560" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1560" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1560" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1560" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1560" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1560" s="1">
+        <v>60</v>
+      </c>
+      <c r="H1560" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1560" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1560" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="K1560" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1560" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1560" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1560" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1560" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1560" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1560" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="R1560" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1560" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1561" s="71">
+        <v>1211009</v>
+      </c>
+      <c r="B1561" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1561" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1561" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1561" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1561" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1561" s="1">
+        <v>61</v>
+      </c>
+      <c r="H1561" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1561" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1561" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1561" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1561" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="R1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1561" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1562" s="71">
+        <v>1211010</v>
+      </c>
+      <c r="B1562" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1562" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1562" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1562" s="71">
+        <v>120001</v>
+      </c>
+      <c r="F1562" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1562" s="1">
+        <v>62</v>
+      </c>
+      <c r="H1562" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1562" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1562" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="K1562" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1562" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1562" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1562" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1562" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1562" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1562" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="R1562" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1562" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE14BCB-E626-4F76-90DC-5396C110F7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DA6E2F-478D-44EA-A775-93A367F9FFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3521" uniqueCount="1499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3521" uniqueCount="1485">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -4377,57 +4377,33 @@
     <t>35,75,1500</t>
   </si>
   <si>
-    <t>122101,122101,122101</t>
-  </si>
-  <si>
     <t>0,5500,1500</t>
   </si>
   <si>
     <t>90,5500,1500</t>
   </si>
   <si>
-    <t>122101,122101</t>
-  </si>
-  <si>
     <t>270,5500,1500</t>
   </si>
   <si>
-    <t>123101,123101,123101</t>
-  </si>
-  <si>
     <t>45,5500,1500</t>
   </si>
   <si>
     <t>135,5500,1500</t>
   </si>
   <si>
-    <t>123105,123101,123101</t>
-  </si>
-  <si>
     <t>225,5500,1500</t>
   </si>
   <si>
-    <t>123101,123101</t>
-  </si>
-  <si>
     <t>315,5500,1500</t>
   </si>
   <si>
-    <t>124101,124101,124101,124101</t>
-  </si>
-  <si>
     <t>30,5500,1500</t>
   </si>
   <si>
-    <t>124101,124101,124104</t>
-  </si>
-  <si>
     <t>102,6500,1500</t>
   </si>
   <si>
-    <t>124105,124101,124101</t>
-  </si>
-  <si>
     <t>174,5500,1500</t>
   </si>
   <si>
@@ -4437,96 +4413,54 @@
     <t>318,5500,1500</t>
   </si>
   <si>
-    <t>125101,125101,125101,125101</t>
-  </si>
-  <si>
     <t>70,5500,1500</t>
   </si>
   <si>
-    <t>125101,125101,125101,125104</t>
-  </si>
-  <si>
     <t>142,6500,1500</t>
   </si>
   <si>
-    <t>125105,125101,125101,125101</t>
-  </si>
-  <si>
     <t>214,5500,1500</t>
   </si>
   <si>
-    <t>125105,125105</t>
-  </si>
-  <si>
     <t>75,55,75,45</t>
   </si>
   <si>
-    <t>125105,125101,125101,125101,125101</t>
-  </si>
-  <si>
     <t>286,5500,1500</t>
   </si>
   <si>
     <t>358,5500,1500</t>
   </si>
   <si>
-    <t>126105,126101,126101,126101</t>
-  </si>
-  <si>
     <t>50,5500,1500</t>
   </si>
   <si>
-    <t>126105,126101,126101,126104</t>
-  </si>
-  <si>
     <t>110,6500,1500</t>
   </si>
   <si>
     <t>170,5500,1500</t>
   </si>
   <si>
-    <t>126105,126105,126105</t>
-  </si>
-  <si>
     <t>35,75,30,70,25,65</t>
   </si>
   <si>
     <t>230,5500,1500</t>
   </si>
   <si>
-    <t>126105,126105,126101,126101,126101</t>
-  </si>
-  <si>
     <t>290,5500,1500</t>
   </si>
   <si>
     <t>350,5500,1500</t>
   </si>
   <si>
-    <t>127105,127105,127101,127101</t>
-  </si>
-  <si>
     <t>204,5500,1500</t>
   </si>
   <si>
-    <t>127105,127105,127104,127104</t>
-  </si>
-  <si>
     <t>256,6500,1500</t>
   </si>
   <si>
-    <t>127105,127105,127101,127101,127101</t>
-  </si>
-  <si>
     <t>308,5500,1500</t>
   </si>
   <si>
-    <t>127102,127101,127101,127101,127101</t>
-  </si>
-  <si>
-    <t>127105,127105,127105,127101,127101</t>
-  </si>
-  <si>
     <t>52,5500,1500</t>
   </si>
   <si>
@@ -4536,112 +4470,136 @@
     <t>156,5500,1500</t>
   </si>
   <si>
-    <t>128105,128105,128105,128101,128101</t>
-  </si>
-  <si>
     <t>25,5500,1500</t>
   </si>
   <si>
-    <t>128102,128101,128101,128101,128101</t>
-  </si>
-  <si>
-    <t>128105,128105,128105,128104,128104</t>
-  </si>
-  <si>
     <t>115,6500,1500</t>
   </si>
   <si>
     <t>160,5500,1500</t>
   </si>
   <si>
-    <t>128102,128105,128105,128105</t>
-  </si>
-  <si>
     <t>205,5500,1500</t>
   </si>
   <si>
-    <t>128105,128105,128105,128105</t>
-  </si>
-  <si>
     <t>250,5500,1500</t>
   </si>
   <si>
     <t>295,5500,1500</t>
   </si>
   <si>
-    <t>128102,128105,128105,128101,128101</t>
-  </si>
-  <si>
     <t>340,5500,1500</t>
   </si>
   <si>
-    <t>129105,129105,129105,129101,129101</t>
-  </si>
-  <si>
     <t>15,5500,1500</t>
   </si>
   <si>
-    <t>129102,129102,129101,129101,129101</t>
-  </si>
-  <si>
     <t>55,5500,1500</t>
   </si>
   <si>
     <t>95,5500,1500</t>
   </si>
   <si>
-    <t>129105,129105,129105,129104,129104</t>
-  </si>
-  <si>
     <t>135,6500,1500</t>
   </si>
   <si>
-    <t>129102,129105,129105,129105</t>
-  </si>
-  <si>
     <t>175,5500,1500</t>
   </si>
   <si>
-    <t>129105,129105,129105,129105</t>
-  </si>
-  <si>
     <t>215,5500,1500</t>
   </si>
   <si>
     <t>255,5500,1500</t>
   </si>
   <si>
-    <t>129105,129105,129105,129105,129105</t>
-  </si>
-  <si>
-    <t>129102,129102,129105,129105</t>
-  </si>
-  <si>
     <t>335,5500,1500</t>
   </si>
   <si>
-    <t>1210113</t>
-  </si>
-  <si>
-    <t>1210105,1210105,1210105</t>
-  </si>
-  <si>
     <t>95,95,1500</t>
   </si>
   <si>
-    <t>1210104,1210104</t>
-  </si>
-  <si>
     <t>45,6500,1500</t>
   </si>
   <si>
-    <t>1210102,1210102</t>
-  </si>
-  <si>
     <t>180,5500,1500</t>
   </si>
   <si>
     <t>225,6500,1500</t>
+  </si>
+  <si>
+    <t>121101,121101,121101</t>
+  </si>
+  <si>
+    <t>121105,121101,121101</t>
+  </si>
+  <si>
+    <t>121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>121101,121101,121104</t>
+  </si>
+  <si>
+    <t>121101,121101,121101,121104</t>
+  </si>
+  <si>
+    <t>121105,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>121105,121105</t>
+  </si>
+  <si>
+    <t>121105,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>121105,121101,121101,121104</t>
+  </si>
+  <si>
+    <t>121105,121105,121105</t>
+  </si>
+  <si>
+    <t>121105,121105,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>121105,121105,121101,121101</t>
+  </si>
+  <si>
+    <t>121105,121105,121104,121104</t>
+  </si>
+  <si>
+    <t>121102,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121101,121101</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121104,121104</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121105</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121101,121101</t>
+  </si>
+  <si>
+    <t>121102,121102,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121105</t>
+  </si>
+  <si>
+    <t>121102,121102,121105,121105</t>
+  </si>
+  <si>
+    <t>121113</t>
+  </si>
+  <si>
+    <t>121104,121104</t>
+  </si>
+  <si>
+    <t>121102,121102</t>
   </si>
 </sst>
 </file>
@@ -4946,7 +4904,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5156,9 +5114,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -92617,7 +92572,7 @@
       </c>
     </row>
     <row r="1501" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1501" s="71">
+      <c r="A1501" s="1">
         <v>1210101</v>
       </c>
       <c r="B1501" s="1">
@@ -92629,7 +92584,7 @@
       <c r="D1501" s="1">
         <v>1</v>
       </c>
-      <c r="E1501" s="71">
+      <c r="E1501" s="1">
         <v>120001</v>
       </c>
       <c r="F1501" s="1">
@@ -92676,7 +92631,7 @@
       </c>
     </row>
     <row r="1502" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1502" s="71">
+      <c r="A1502" s="1">
         <v>1210102</v>
       </c>
       <c r="B1502" s="1">
@@ -92688,7 +92643,7 @@
       <c r="D1502" s="1">
         <v>1</v>
       </c>
-      <c r="E1502" s="71">
+      <c r="E1502" s="1">
         <v>120001</v>
       </c>
       <c r="F1502" s="1">
@@ -92735,7 +92690,7 @@
       </c>
     </row>
     <row r="1503" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1503" s="71">
+      <c r="A1503" s="1">
         <v>1210103</v>
       </c>
       <c r="B1503" s="1">
@@ -92747,7 +92702,7 @@
       <c r="D1503" s="1">
         <v>1</v>
       </c>
-      <c r="E1503" s="71">
+      <c r="E1503" s="1">
         <v>120001</v>
       </c>
       <c r="F1503" s="1">
@@ -92794,7 +92749,7 @@
       </c>
     </row>
     <row r="1504" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1504" s="71">
+      <c r="A1504" s="1">
         <v>1210201</v>
       </c>
       <c r="B1504" s="1">
@@ -92806,7 +92761,7 @@
       <c r="D1504" s="1">
         <v>1</v>
       </c>
-      <c r="E1504" s="71">
+      <c r="E1504" s="1">
         <v>120001</v>
       </c>
       <c r="F1504" s="1">
@@ -92822,29 +92777,29 @@
         <v>2</v>
       </c>
       <c r="J1504" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="K1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1504" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1504" s="1" t="s">
         <v>1410</v>
       </c>
-      <c r="K1504" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1504" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1504" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1504" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1504" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1504" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1504" s="1" t="s">
-        <v>1411</v>
-      </c>
       <c r="R1504" s="1">
         <v>0</v>
       </c>
@@ -92853,7 +92808,7 @@
       </c>
     </row>
     <row r="1505" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1505" s="71">
+      <c r="A1505" s="1">
         <v>1210202</v>
       </c>
       <c r="B1505" s="1">
@@ -92865,7 +92820,7 @@
       <c r="D1505" s="1">
         <v>1</v>
       </c>
-      <c r="E1505" s="71">
+      <c r="E1505" s="1">
         <v>120001</v>
       </c>
       <c r="F1505" s="1">
@@ -92881,7 +92836,7 @@
         <v>2</v>
       </c>
       <c r="J1505" s="2" t="s">
-        <v>1410</v>
+        <v>1460</v>
       </c>
       <c r="K1505" s="1">
         <v>0</v>
@@ -92902,7 +92857,7 @@
         <v>0</v>
       </c>
       <c r="Q1505" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="R1505" s="1">
         <v>0</v>
@@ -92912,7 +92867,7 @@
       </c>
     </row>
     <row r="1506" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1506" s="71">
+      <c r="A1506" s="1">
         <v>1210203</v>
       </c>
       <c r="B1506" s="1">
@@ -92924,7 +92879,7 @@
       <c r="D1506" s="1">
         <v>1</v>
       </c>
-      <c r="E1506" s="71">
+      <c r="E1506" s="1">
         <v>120001</v>
       </c>
       <c r="F1506" s="1">
@@ -92940,7 +92895,7 @@
         <v>2</v>
       </c>
       <c r="J1506" s="2" t="s">
-        <v>1413</v>
+        <v>1407</v>
       </c>
       <c r="K1506" s="1">
         <v>0</v>
@@ -92961,7 +92916,7 @@
         <v>0</v>
       </c>
       <c r="Q1506" s="1" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="R1506" s="1">
         <v>0</v>
@@ -92971,7 +92926,7 @@
       </c>
     </row>
     <row r="1507" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1507" s="71">
+      <c r="A1507" s="1">
         <v>1210301</v>
       </c>
       <c r="B1507" s="1">
@@ -92983,7 +92938,7 @@
       <c r="D1507" s="1">
         <v>1</v>
       </c>
-      <c r="E1507" s="71">
+      <c r="E1507" s="1">
         <v>120001</v>
       </c>
       <c r="F1507" s="1">
@@ -92999,7 +92954,7 @@
         <v>3</v>
       </c>
       <c r="J1507" s="2" t="s">
-        <v>1415</v>
+        <v>1460</v>
       </c>
       <c r="K1507" s="1">
         <v>0</v>
@@ -93020,7 +92975,7 @@
         <v>0</v>
       </c>
       <c r="Q1507" s="1" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="R1507" s="1">
         <v>0</v>
@@ -93030,7 +92985,7 @@
       </c>
     </row>
     <row r="1508" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1508" s="71">
+      <c r="A1508" s="1">
         <v>1210302</v>
       </c>
       <c r="B1508" s="1">
@@ -93042,7 +92997,7 @@
       <c r="D1508" s="1">
         <v>1</v>
       </c>
-      <c r="E1508" s="71">
+      <c r="E1508" s="1">
         <v>120001</v>
       </c>
       <c r="F1508" s="1">
@@ -93058,7 +93013,7 @@
         <v>3</v>
       </c>
       <c r="J1508" s="2" t="s">
-        <v>1415</v>
+        <v>1460</v>
       </c>
       <c r="K1508" s="1">
         <v>0</v>
@@ -93079,7 +93034,7 @@
         <v>0</v>
       </c>
       <c r="Q1508" s="1" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="R1508" s="1">
         <v>0</v>
@@ -93089,7 +93044,7 @@
       </c>
     </row>
     <row r="1509" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1509" s="71">
+      <c r="A1509" s="1">
         <v>1210303</v>
       </c>
       <c r="B1509" s="1">
@@ -93101,7 +93056,7 @@
       <c r="D1509" s="1">
         <v>1</v>
       </c>
-      <c r="E1509" s="71">
+      <c r="E1509" s="1">
         <v>120001</v>
       </c>
       <c r="F1509" s="1">
@@ -93117,7 +93072,7 @@
         <v>3</v>
       </c>
       <c r="J1509" s="2" t="s">
-        <v>1418</v>
+        <v>1461</v>
       </c>
       <c r="K1509" s="1">
         <v>0</v>
@@ -93138,7 +93093,7 @@
         <v>0</v>
       </c>
       <c r="Q1509" s="1" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="R1509" s="1">
         <v>0</v>
@@ -93148,7 +93103,7 @@
       </c>
     </row>
     <row r="1510" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1510" s="71">
+      <c r="A1510" s="1">
         <v>1210304</v>
       </c>
       <c r="B1510" s="1">
@@ -93160,7 +93115,7 @@
       <c r="D1510" s="1">
         <v>1</v>
       </c>
-      <c r="E1510" s="71">
+      <c r="E1510" s="1">
         <v>120001</v>
       </c>
       <c r="F1510" s="1">
@@ -93176,7 +93131,7 @@
         <v>3</v>
       </c>
       <c r="J1510" s="2" t="s">
-        <v>1420</v>
+        <v>1407</v>
       </c>
       <c r="K1510" s="1">
         <v>0</v>
@@ -93197,7 +93152,7 @@
         <v>0</v>
       </c>
       <c r="Q1510" s="1" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="R1510" s="1">
         <v>0</v>
@@ -93207,7 +93162,7 @@
       </c>
     </row>
     <row r="1511" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1511" s="71">
+      <c r="A1511" s="1">
         <v>1210401</v>
       </c>
       <c r="B1511" s="1">
@@ -93219,7 +93174,7 @@
       <c r="D1511" s="1">
         <v>1</v>
       </c>
-      <c r="E1511" s="71">
+      <c r="E1511" s="1">
         <v>120001</v>
       </c>
       <c r="F1511" s="1">
@@ -93235,7 +93190,7 @@
         <v>4</v>
       </c>
       <c r="J1511" s="2" t="s">
-        <v>1422</v>
+        <v>1462</v>
       </c>
       <c r="K1511" s="1">
         <v>0</v>
@@ -93256,7 +93211,7 @@
         <v>0</v>
       </c>
       <c r="Q1511" s="1" t="s">
-        <v>1423</v>
+        <v>1417</v>
       </c>
       <c r="R1511" s="1">
         <v>0</v>
@@ -93266,7 +93221,7 @@
       </c>
     </row>
     <row r="1512" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1512" s="71">
+      <c r="A1512" s="1">
         <v>1210402</v>
       </c>
       <c r="B1512" s="1">
@@ -93278,7 +93233,7 @@
       <c r="D1512" s="1">
         <v>1</v>
       </c>
-      <c r="E1512" s="71">
+      <c r="E1512" s="1">
         <v>120001</v>
       </c>
       <c r="F1512" s="1">
@@ -93294,7 +93249,7 @@
         <v>4</v>
       </c>
       <c r="J1512" s="2" t="s">
-        <v>1424</v>
+        <v>1463</v>
       </c>
       <c r="K1512" s="1">
         <v>0</v>
@@ -93315,7 +93270,7 @@
         <v>0</v>
       </c>
       <c r="Q1512" s="1" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="R1512" s="1">
         <v>0</v>
@@ -93325,7 +93280,7 @@
       </c>
     </row>
     <row r="1513" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1513" s="71">
+      <c r="A1513" s="1">
         <v>1210403</v>
       </c>
       <c r="B1513" s="1">
@@ -93337,7 +93292,7 @@
       <c r="D1513" s="1">
         <v>1</v>
       </c>
-      <c r="E1513" s="71">
+      <c r="E1513" s="1">
         <v>120001</v>
       </c>
       <c r="F1513" s="1">
@@ -93353,7 +93308,7 @@
         <v>4</v>
       </c>
       <c r="J1513" s="2" t="s">
-        <v>1426</v>
+        <v>1461</v>
       </c>
       <c r="K1513" s="1">
         <v>0</v>
@@ -93374,7 +93329,7 @@
         <v>0</v>
       </c>
       <c r="Q1513" s="1" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
       <c r="R1513" s="1">
         <v>0</v>
@@ -93384,7 +93339,7 @@
       </c>
     </row>
     <row r="1514" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1514" s="71">
+      <c r="A1514" s="1">
         <v>1210404</v>
       </c>
       <c r="B1514" s="1">
@@ -93396,7 +93351,7 @@
       <c r="D1514" s="1">
         <v>1</v>
       </c>
-      <c r="E1514" s="71">
+      <c r="E1514" s="1">
         <v>120001</v>
       </c>
       <c r="F1514" s="1">
@@ -93412,7 +93367,7 @@
         <v>4</v>
       </c>
       <c r="J1514" s="2" t="s">
-        <v>1426</v>
+        <v>1461</v>
       </c>
       <c r="K1514" s="1">
         <v>0</v>
@@ -93433,7 +93388,7 @@
         <v>0</v>
       </c>
       <c r="Q1514" s="1" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="R1514" s="1">
         <v>0</v>
@@ -93443,7 +93398,7 @@
       </c>
     </row>
     <row r="1515" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1515" s="71">
+      <c r="A1515" s="1">
         <v>1210405</v>
       </c>
       <c r="B1515" s="1">
@@ -93455,7 +93410,7 @@
       <c r="D1515" s="1">
         <v>1</v>
       </c>
-      <c r="E1515" s="71">
+      <c r="E1515" s="1">
         <v>120001</v>
       </c>
       <c r="F1515" s="1">
@@ -93471,7 +93426,7 @@
         <v>4</v>
       </c>
       <c r="J1515" s="2" t="s">
-        <v>1426</v>
+        <v>1461</v>
       </c>
       <c r="K1515" s="1">
         <v>0</v>
@@ -93492,7 +93447,7 @@
         <v>0</v>
       </c>
       <c r="Q1515" s="1" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
       <c r="R1515" s="1">
         <v>0</v>
@@ -93502,7 +93457,7 @@
       </c>
     </row>
     <row r="1516" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1516" s="71">
+      <c r="A1516" s="1">
         <v>1210501</v>
       </c>
       <c r="B1516" s="1">
@@ -93514,7 +93469,7 @@
       <c r="D1516" s="1">
         <v>1</v>
       </c>
-      <c r="E1516" s="71">
+      <c r="E1516" s="1">
         <v>120001</v>
       </c>
       <c r="F1516" s="1">
@@ -93530,7 +93485,7 @@
         <v>5</v>
       </c>
       <c r="J1516" s="2" t="s">
-        <v>1430</v>
+        <v>1462</v>
       </c>
       <c r="K1516" s="1">
         <v>0</v>
@@ -93551,7 +93506,7 @@
         <v>0</v>
       </c>
       <c r="Q1516" s="1" t="s">
-        <v>1431</v>
+        <v>1422</v>
       </c>
       <c r="R1516" s="1">
         <v>0</v>
@@ -93561,7 +93516,7 @@
       </c>
     </row>
     <row r="1517" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1517" s="71">
+      <c r="A1517" s="1">
         <v>1210502</v>
       </c>
       <c r="B1517" s="1">
@@ -93573,7 +93528,7 @@
       <c r="D1517" s="1">
         <v>1</v>
       </c>
-      <c r="E1517" s="71">
+      <c r="E1517" s="1">
         <v>120001</v>
       </c>
       <c r="F1517" s="1">
@@ -93589,7 +93544,7 @@
         <v>5</v>
       </c>
       <c r="J1517" s="2" t="s">
-        <v>1432</v>
+        <v>1464</v>
       </c>
       <c r="K1517" s="1">
         <v>0</v>
@@ -93610,7 +93565,7 @@
         <v>0</v>
       </c>
       <c r="Q1517" s="1" t="s">
-        <v>1433</v>
+        <v>1423</v>
       </c>
       <c r="R1517" s="1">
         <v>0</v>
@@ -93620,7 +93575,7 @@
       </c>
     </row>
     <row r="1518" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1518" s="71">
+      <c r="A1518" s="1">
         <v>1210503</v>
       </c>
       <c r="B1518" s="1">
@@ -93632,7 +93587,7 @@
       <c r="D1518" s="1">
         <v>1</v>
       </c>
-      <c r="E1518" s="71">
+      <c r="E1518" s="1">
         <v>120001</v>
       </c>
       <c r="F1518" s="1">
@@ -93648,7 +93603,7 @@
         <v>5</v>
       </c>
       <c r="J1518" s="2" t="s">
-        <v>1434</v>
+        <v>1465</v>
       </c>
       <c r="K1518" s="1">
         <v>0</v>
@@ -93669,7 +93624,7 @@
         <v>0</v>
       </c>
       <c r="Q1518" s="1" t="s">
-        <v>1435</v>
+        <v>1424</v>
       </c>
       <c r="R1518" s="1">
         <v>0</v>
@@ -93679,7 +93634,7 @@
       </c>
     </row>
     <row r="1519" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1519" s="71">
+      <c r="A1519" s="1">
         <v>1210504</v>
       </c>
       <c r="B1519" s="1">
@@ -93691,7 +93646,7 @@
       <c r="D1519" s="1">
         <v>1</v>
       </c>
-      <c r="E1519" s="71">
+      <c r="E1519" s="1">
         <v>120001</v>
       </c>
       <c r="F1519" s="1">
@@ -93707,7 +93662,7 @@
         <v>5</v>
       </c>
       <c r="J1519" s="2" t="s">
-        <v>1436</v>
+        <v>1466</v>
       </c>
       <c r="K1519" s="1">
         <v>0</v>
@@ -93722,7 +93677,7 @@
         <v>0</v>
       </c>
       <c r="O1519" s="1" t="s">
-        <v>1437</v>
+        <v>1425</v>
       </c>
       <c r="P1519" s="1">
         <v>0</v>
@@ -93738,7 +93693,7 @@
       </c>
     </row>
     <row r="1520" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1520" s="71">
+      <c r="A1520" s="1">
         <v>1210505</v>
       </c>
       <c r="B1520" s="1">
@@ -93750,7 +93705,7 @@
       <c r="D1520" s="1">
         <v>1</v>
       </c>
-      <c r="E1520" s="71">
+      <c r="E1520" s="1">
         <v>120001</v>
       </c>
       <c r="F1520" s="1">
@@ -93766,7 +93721,7 @@
         <v>5</v>
       </c>
       <c r="J1520" s="2" t="s">
-        <v>1438</v>
+        <v>1467</v>
       </c>
       <c r="K1520" s="1">
         <v>0</v>
@@ -93787,7 +93742,7 @@
         <v>0</v>
       </c>
       <c r="Q1520" s="1" t="s">
-        <v>1439</v>
+        <v>1426</v>
       </c>
       <c r="R1520" s="1">
         <v>0</v>
@@ -93797,7 +93752,7 @@
       </c>
     </row>
     <row r="1521" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1521" s="71">
+      <c r="A1521" s="1">
         <v>1210506</v>
       </c>
       <c r="B1521" s="1">
@@ -93809,7 +93764,7 @@
       <c r="D1521" s="1">
         <v>1</v>
       </c>
-      <c r="E1521" s="71">
+      <c r="E1521" s="1">
         <v>120001</v>
       </c>
       <c r="F1521" s="1">
@@ -93825,7 +93780,7 @@
         <v>5</v>
       </c>
       <c r="J1521" s="2" t="s">
-        <v>1434</v>
+        <v>1465</v>
       </c>
       <c r="K1521" s="1">
         <v>0</v>
@@ -93846,7 +93801,7 @@
         <v>0</v>
       </c>
       <c r="Q1521" s="1" t="s">
-        <v>1440</v>
+        <v>1427</v>
       </c>
       <c r="R1521" s="1">
         <v>0</v>
@@ -93856,7 +93811,7 @@
       </c>
     </row>
     <row r="1522" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1522" s="71">
+      <c r="A1522" s="1">
         <v>1210601</v>
       </c>
       <c r="B1522" s="1">
@@ -93868,7 +93823,7 @@
       <c r="D1522" s="1">
         <v>1</v>
       </c>
-      <c r="E1522" s="71">
+      <c r="E1522" s="1">
         <v>120001</v>
       </c>
       <c r="F1522" s="1">
@@ -93884,7 +93839,7 @@
         <v>6</v>
       </c>
       <c r="J1522" s="2" t="s">
-        <v>1441</v>
+        <v>1465</v>
       </c>
       <c r="K1522" s="1">
         <v>0</v>
@@ -93905,7 +93860,7 @@
         <v>0</v>
       </c>
       <c r="Q1522" s="1" t="s">
-        <v>1442</v>
+        <v>1428</v>
       </c>
       <c r="R1522" s="1">
         <v>0</v>
@@ -93915,7 +93870,7 @@
       </c>
     </row>
     <row r="1523" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1523" s="71">
+      <c r="A1523" s="1">
         <v>1210602</v>
       </c>
       <c r="B1523" s="1">
@@ -93927,7 +93882,7 @@
       <c r="D1523" s="1">
         <v>1</v>
       </c>
-      <c r="E1523" s="71">
+      <c r="E1523" s="1">
         <v>120001</v>
       </c>
       <c r="F1523" s="1">
@@ -93943,7 +93898,7 @@
         <v>6</v>
       </c>
       <c r="J1523" s="2" t="s">
-        <v>1443</v>
+        <v>1468</v>
       </c>
       <c r="K1523" s="1">
         <v>0</v>
@@ -93964,7 +93919,7 @@
         <v>0</v>
       </c>
       <c r="Q1523" s="1" t="s">
-        <v>1444</v>
+        <v>1429</v>
       </c>
       <c r="R1523" s="1">
         <v>0</v>
@@ -93974,7 +93929,7 @@
       </c>
     </row>
     <row r="1524" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1524" s="71">
+      <c r="A1524" s="1">
         <v>1210603</v>
       </c>
       <c r="B1524" s="1">
@@ -93986,7 +93941,7 @@
       <c r="D1524" s="1">
         <v>1</v>
       </c>
-      <c r="E1524" s="71">
+      <c r="E1524" s="1">
         <v>120001</v>
       </c>
       <c r="F1524" s="1">
@@ -94002,7 +93957,7 @@
         <v>6</v>
       </c>
       <c r="J1524" s="2" t="s">
-        <v>1441</v>
+        <v>1465</v>
       </c>
       <c r="K1524" s="1">
         <v>0</v>
@@ -94023,7 +93978,7 @@
         <v>0</v>
       </c>
       <c r="Q1524" s="1" t="s">
-        <v>1445</v>
+        <v>1430</v>
       </c>
       <c r="R1524" s="1">
         <v>0</v>
@@ -94033,7 +93988,7 @@
       </c>
     </row>
     <row r="1525" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1525" s="71">
+      <c r="A1525" s="1">
         <v>1210604</v>
       </c>
       <c r="B1525" s="1">
@@ -94045,7 +94000,7 @@
       <c r="D1525" s="1">
         <v>1</v>
       </c>
-      <c r="E1525" s="71">
+      <c r="E1525" s="1">
         <v>120001</v>
       </c>
       <c r="F1525" s="1">
@@ -94061,7 +94016,7 @@
         <v>6</v>
       </c>
       <c r="J1525" s="2" t="s">
-        <v>1446</v>
+        <v>1469</v>
       </c>
       <c r="K1525" s="1">
         <v>0</v>
@@ -94076,7 +94031,7 @@
         <v>0</v>
       </c>
       <c r="O1525" s="1" t="s">
-        <v>1447</v>
+        <v>1431</v>
       </c>
       <c r="P1525" s="1">
         <v>0</v>
@@ -94092,7 +94047,7 @@
       </c>
     </row>
     <row r="1526" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1526" s="71">
+      <c r="A1526" s="1">
         <v>1210605</v>
       </c>
       <c r="B1526" s="1">
@@ -94104,7 +94059,7 @@
       <c r="D1526" s="1">
         <v>1</v>
       </c>
-      <c r="E1526" s="71">
+      <c r="E1526" s="1">
         <v>120001</v>
       </c>
       <c r="F1526" s="1">
@@ -94120,7 +94075,7 @@
         <v>6</v>
       </c>
       <c r="J1526" s="2" t="s">
-        <v>1441</v>
+        <v>1465</v>
       </c>
       <c r="K1526" s="1">
         <v>0</v>
@@ -94141,7 +94096,7 @@
         <v>0</v>
       </c>
       <c r="Q1526" s="1" t="s">
-        <v>1448</v>
+        <v>1432</v>
       </c>
       <c r="R1526" s="1">
         <v>0</v>
@@ -94151,7 +94106,7 @@
       </c>
     </row>
     <row r="1527" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1527" s="71">
+      <c r="A1527" s="1">
         <v>1210606</v>
       </c>
       <c r="B1527" s="1">
@@ -94163,7 +94118,7 @@
       <c r="D1527" s="1">
         <v>1</v>
       </c>
-      <c r="E1527" s="71">
+      <c r="E1527" s="1">
         <v>120001</v>
       </c>
       <c r="F1527" s="1">
@@ -94179,7 +94134,7 @@
         <v>6</v>
       </c>
       <c r="J1527" s="2" t="s">
-        <v>1449</v>
+        <v>1470</v>
       </c>
       <c r="K1527" s="1">
         <v>0</v>
@@ -94200,7 +94155,7 @@
         <v>0</v>
       </c>
       <c r="Q1527" s="1" t="s">
-        <v>1450</v>
+        <v>1433</v>
       </c>
       <c r="R1527" s="1">
         <v>0</v>
@@ -94210,7 +94165,7 @@
       </c>
     </row>
     <row r="1528" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1528" s="71">
+      <c r="A1528" s="1">
         <v>1210607</v>
       </c>
       <c r="B1528" s="1">
@@ -94222,7 +94177,7 @@
       <c r="D1528" s="1">
         <v>1</v>
       </c>
-      <c r="E1528" s="71">
+      <c r="E1528" s="1">
         <v>120001</v>
       </c>
       <c r="F1528" s="1">
@@ -94238,7 +94193,7 @@
         <v>6</v>
       </c>
       <c r="J1528" s="2" t="s">
-        <v>1449</v>
+        <v>1470</v>
       </c>
       <c r="K1528" s="1">
         <v>0</v>
@@ -94259,7 +94214,7 @@
         <v>0</v>
       </c>
       <c r="Q1528" s="1" t="s">
-        <v>1451</v>
+        <v>1434</v>
       </c>
       <c r="R1528" s="1">
         <v>0</v>
@@ -94269,7 +94224,7 @@
       </c>
     </row>
     <row r="1529" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1529" s="71">
+      <c r="A1529" s="1">
         <v>1210701</v>
       </c>
       <c r="B1529" s="1">
@@ -94281,7 +94236,7 @@
       <c r="D1529" s="1">
         <v>1</v>
       </c>
-      <c r="E1529" s="71">
+      <c r="E1529" s="1">
         <v>120001</v>
       </c>
       <c r="F1529" s="1">
@@ -94297,7 +94252,7 @@
         <v>7</v>
       </c>
       <c r="J1529" s="2" t="s">
-        <v>1452</v>
+        <v>1471</v>
       </c>
       <c r="K1529" s="1">
         <v>0</v>
@@ -94318,7 +94273,7 @@
         <v>0</v>
       </c>
       <c r="Q1529" s="1" t="s">
-        <v>1453</v>
+        <v>1435</v>
       </c>
       <c r="R1529" s="1">
         <v>0</v>
@@ -94328,7 +94283,7 @@
       </c>
     </row>
     <row r="1530" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1530" s="71">
+      <c r="A1530" s="1">
         <v>1210702</v>
       </c>
       <c r="B1530" s="1">
@@ -94340,7 +94295,7 @@
       <c r="D1530" s="1">
         <v>1</v>
       </c>
-      <c r="E1530" s="71">
+      <c r="E1530" s="1">
         <v>120001</v>
       </c>
       <c r="F1530" s="1">
@@ -94356,7 +94311,7 @@
         <v>7</v>
       </c>
       <c r="J1530" s="2" t="s">
-        <v>1454</v>
+        <v>1472</v>
       </c>
       <c r="K1530" s="1">
         <v>0</v>
@@ -94377,7 +94332,7 @@
         <v>0</v>
       </c>
       <c r="Q1530" s="1" t="s">
-        <v>1455</v>
+        <v>1436</v>
       </c>
       <c r="R1530" s="1">
         <v>0</v>
@@ -94387,7 +94342,7 @@
       </c>
     </row>
     <row r="1531" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1531" s="71">
+      <c r="A1531" s="1">
         <v>1210703</v>
       </c>
       <c r="B1531" s="1">
@@ -94399,7 +94354,7 @@
       <c r="D1531" s="1">
         <v>1</v>
       </c>
-      <c r="E1531" s="71">
+      <c r="E1531" s="1">
         <v>120001</v>
       </c>
       <c r="F1531" s="1">
@@ -94415,7 +94370,7 @@
         <v>7</v>
       </c>
       <c r="J1531" s="2" t="s">
-        <v>1456</v>
+        <v>1470</v>
       </c>
       <c r="K1531" s="1">
         <v>0</v>
@@ -94436,7 +94391,7 @@
         <v>0</v>
       </c>
       <c r="Q1531" s="1" t="s">
-        <v>1457</v>
+        <v>1437</v>
       </c>
       <c r="R1531" s="1">
         <v>0</v>
@@ -94446,7 +94401,7 @@
       </c>
     </row>
     <row r="1532" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1532" s="71">
+      <c r="A1532" s="1">
         <v>1210704</v>
       </c>
       <c r="B1532" s="1">
@@ -94458,7 +94413,7 @@
       <c r="D1532" s="1">
         <v>1</v>
       </c>
-      <c r="E1532" s="71">
+      <c r="E1532" s="1">
         <v>120001</v>
       </c>
       <c r="F1532" s="1">
@@ -94474,7 +94429,7 @@
         <v>7</v>
       </c>
       <c r="J1532" s="2" t="s">
-        <v>1458</v>
+        <v>1473</v>
       </c>
       <c r="K1532" s="1">
         <v>0</v>
@@ -94495,7 +94450,7 @@
         <v>0</v>
       </c>
       <c r="Q1532" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="R1532" s="1">
         <v>0</v>
@@ -94505,7 +94460,7 @@
       </c>
     </row>
     <row r="1533" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1533" s="71">
+      <c r="A1533" s="1">
         <v>1210705</v>
       </c>
       <c r="B1533" s="1">
@@ -94517,7 +94472,7 @@
       <c r="D1533" s="1">
         <v>1</v>
       </c>
-      <c r="E1533" s="71">
+      <c r="E1533" s="1">
         <v>120001</v>
       </c>
       <c r="F1533" s="1">
@@ -94533,7 +94488,7 @@
         <v>7</v>
       </c>
       <c r="J1533" s="2" t="s">
-        <v>1459</v>
+        <v>1474</v>
       </c>
       <c r="K1533" s="1">
         <v>0</v>
@@ -94554,7 +94509,7 @@
         <v>0</v>
       </c>
       <c r="Q1533" s="1" t="s">
-        <v>1460</v>
+        <v>1438</v>
       </c>
       <c r="R1533" s="1">
         <v>0</v>
@@ -94564,7 +94519,7 @@
       </c>
     </row>
     <row r="1534" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1534" s="71">
+      <c r="A1534" s="1">
         <v>1210706</v>
       </c>
       <c r="B1534" s="1">
@@ -94576,7 +94531,7 @@
       <c r="D1534" s="1">
         <v>1</v>
       </c>
-      <c r="E1534" s="71">
+      <c r="E1534" s="1">
         <v>120001</v>
       </c>
       <c r="F1534" s="1">
@@ -94592,7 +94547,7 @@
         <v>7</v>
       </c>
       <c r="J1534" s="2" t="s">
-        <v>1459</v>
+        <v>1474</v>
       </c>
       <c r="K1534" s="1">
         <v>0</v>
@@ -94613,7 +94568,7 @@
         <v>0</v>
       </c>
       <c r="Q1534" s="1" t="s">
-        <v>1461</v>
+        <v>1439</v>
       </c>
       <c r="R1534" s="1">
         <v>0</v>
@@ -94623,7 +94578,7 @@
       </c>
     </row>
     <row r="1535" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1535" s="71">
+      <c r="A1535" s="1">
         <v>1210707</v>
       </c>
       <c r="B1535" s="1">
@@ -94635,7 +94590,7 @@
       <c r="D1535" s="1">
         <v>1</v>
       </c>
-      <c r="E1535" s="71">
+      <c r="E1535" s="1">
         <v>120001</v>
       </c>
       <c r="F1535" s="1">
@@ -94651,7 +94606,7 @@
         <v>7</v>
       </c>
       <c r="J1535" s="2" t="s">
-        <v>1459</v>
+        <v>1474</v>
       </c>
       <c r="K1535" s="1">
         <v>0</v>
@@ -94672,7 +94627,7 @@
         <v>0</v>
       </c>
       <c r="Q1535" s="1" t="s">
-        <v>1462</v>
+        <v>1440</v>
       </c>
       <c r="R1535" s="1">
         <v>0</v>
@@ -94682,7 +94637,7 @@
       </c>
     </row>
     <row r="1536" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1536" s="71">
+      <c r="A1536" s="1">
         <v>1210801</v>
       </c>
       <c r="B1536" s="1">
@@ -94694,7 +94649,7 @@
       <c r="D1536" s="1">
         <v>1</v>
       </c>
-      <c r="E1536" s="71">
+      <c r="E1536" s="1">
         <v>120001</v>
       </c>
       <c r="F1536" s="1">
@@ -94710,7 +94665,7 @@
         <v>8</v>
       </c>
       <c r="J1536" s="2" t="s">
-        <v>1463</v>
+        <v>1474</v>
       </c>
       <c r="K1536" s="1">
         <v>0</v>
@@ -94731,7 +94686,7 @@
         <v>0</v>
       </c>
       <c r="Q1536" s="1" t="s">
-        <v>1464</v>
+        <v>1441</v>
       </c>
       <c r="R1536" s="1">
         <v>0</v>
@@ -94741,7 +94696,7 @@
       </c>
     </row>
     <row r="1537" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1537" s="71">
+      <c r="A1537" s="1">
         <v>1210802</v>
       </c>
       <c r="B1537" s="1">
@@ -94753,7 +94708,7 @@
       <c r="D1537" s="1">
         <v>1</v>
       </c>
-      <c r="E1537" s="71">
+      <c r="E1537" s="1">
         <v>120001</v>
       </c>
       <c r="F1537" s="1">
@@ -94769,7 +94724,7 @@
         <v>8</v>
       </c>
       <c r="J1537" s="2" t="s">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="K1537" s="1">
         <v>0</v>
@@ -94790,7 +94745,7 @@
         <v>0</v>
       </c>
       <c r="Q1537" s="1" t="s">
-        <v>1431</v>
+        <v>1422</v>
       </c>
       <c r="R1537" s="1">
         <v>0</v>
@@ -94800,7 +94755,7 @@
       </c>
     </row>
     <row r="1538" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1538" s="71">
+      <c r="A1538" s="1">
         <v>1210803</v>
       </c>
       <c r="B1538" s="1">
@@ -94812,7 +94767,7 @@
       <c r="D1538" s="1">
         <v>1</v>
       </c>
-      <c r="E1538" s="71">
+      <c r="E1538" s="1">
         <v>120001</v>
       </c>
       <c r="F1538" s="1">
@@ -94828,7 +94783,7 @@
         <v>8</v>
       </c>
       <c r="J1538" s="2" t="s">
-        <v>1466</v>
+        <v>1475</v>
       </c>
       <c r="K1538" s="1">
         <v>0</v>
@@ -94849,7 +94804,7 @@
         <v>0</v>
       </c>
       <c r="Q1538" s="1" t="s">
-        <v>1467</v>
+        <v>1442</v>
       </c>
       <c r="R1538" s="1">
         <v>0</v>
@@ -94859,7 +94814,7 @@
       </c>
     </row>
     <row r="1539" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1539" s="71">
+      <c r="A1539" s="1">
         <v>1210804</v>
       </c>
       <c r="B1539" s="1">
@@ -94871,7 +94826,7 @@
       <c r="D1539" s="1">
         <v>1</v>
       </c>
-      <c r="E1539" s="71">
+      <c r="E1539" s="1">
         <v>120001</v>
       </c>
       <c r="F1539" s="1">
@@ -94887,7 +94842,7 @@
         <v>8</v>
       </c>
       <c r="J1539" s="2" t="s">
-        <v>1463</v>
+        <v>1474</v>
       </c>
       <c r="K1539" s="1">
         <v>0</v>
@@ -94908,7 +94863,7 @@
         <v>0</v>
       </c>
       <c r="Q1539" s="1" t="s">
-        <v>1468</v>
+        <v>1443</v>
       </c>
       <c r="R1539" s="1">
         <v>0</v>
@@ -94918,7 +94873,7 @@
       </c>
     </row>
     <row r="1540" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1540" s="71">
+      <c r="A1540" s="1">
         <v>1210805</v>
       </c>
       <c r="B1540" s="1">
@@ -94930,7 +94885,7 @@
       <c r="D1540" s="1">
         <v>1</v>
       </c>
-      <c r="E1540" s="71">
+      <c r="E1540" s="1">
         <v>120001</v>
       </c>
       <c r="F1540" s="1">
@@ -94946,7 +94901,7 @@
         <v>8</v>
       </c>
       <c r="J1540" s="2" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="K1540" s="1">
         <v>0</v>
@@ -94967,7 +94922,7 @@
         <v>0</v>
       </c>
       <c r="Q1540" s="1" t="s">
-        <v>1470</v>
+        <v>1444</v>
       </c>
       <c r="R1540" s="1">
         <v>0</v>
@@ -94977,7 +94932,7 @@
       </c>
     </row>
     <row r="1541" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1541" s="71">
+      <c r="A1541" s="1">
         <v>1210806</v>
       </c>
       <c r="B1541" s="1">
@@ -94989,7 +94944,7 @@
       <c r="D1541" s="1">
         <v>1</v>
       </c>
-      <c r="E1541" s="71">
+      <c r="E1541" s="1">
         <v>120001</v>
       </c>
       <c r="F1541" s="1">
@@ -95005,7 +94960,7 @@
         <v>8</v>
       </c>
       <c r="J1541" s="2" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="K1541" s="1">
         <v>0</v>
@@ -95026,7 +94981,7 @@
         <v>0</v>
       </c>
       <c r="Q1541" s="1" t="s">
-        <v>1472</v>
+        <v>1445</v>
       </c>
       <c r="R1541" s="1">
         <v>0</v>
@@ -95036,7 +94991,7 @@
       </c>
     </row>
     <row r="1542" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1542" s="71">
+      <c r="A1542" s="1">
         <v>1210807</v>
       </c>
       <c r="B1542" s="1">
@@ -95048,7 +95003,7 @@
       <c r="D1542" s="1">
         <v>1</v>
       </c>
-      <c r="E1542" s="71">
+      <c r="E1542" s="1">
         <v>120001</v>
       </c>
       <c r="F1542" s="1">
@@ -95064,7 +95019,7 @@
         <v>8</v>
       </c>
       <c r="J1542" s="2" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="K1542" s="1">
         <v>0</v>
@@ -95085,7 +95040,7 @@
         <v>0</v>
       </c>
       <c r="Q1542" s="1" t="s">
-        <v>1473</v>
+        <v>1446</v>
       </c>
       <c r="R1542" s="1">
         <v>0</v>
@@ -95095,7 +95050,7 @@
       </c>
     </row>
     <row r="1543" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1543" s="71">
+      <c r="A1543" s="1">
         <v>1210808</v>
       </c>
       <c r="B1543" s="1">
@@ -95107,7 +95062,7 @@
       <c r="D1543" s="1">
         <v>1</v>
       </c>
-      <c r="E1543" s="71">
+      <c r="E1543" s="1">
         <v>120001</v>
       </c>
       <c r="F1543" s="1">
@@ -95123,7 +95078,7 @@
         <v>8</v>
       </c>
       <c r="J1543" s="2" t="s">
-        <v>1474</v>
+        <v>1478</v>
       </c>
       <c r="K1543" s="1">
         <v>0</v>
@@ -95144,7 +95099,7 @@
         <v>0</v>
       </c>
       <c r="Q1543" s="1" t="s">
-        <v>1475</v>
+        <v>1447</v>
       </c>
       <c r="R1543" s="1">
         <v>0</v>
@@ -95154,7 +95109,7 @@
       </c>
     </row>
     <row r="1544" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1544" s="71">
+      <c r="A1544" s="1">
         <v>1210901</v>
       </c>
       <c r="B1544" s="1">
@@ -95166,7 +95121,7 @@
       <c r="D1544" s="1">
         <v>1</v>
       </c>
-      <c r="E1544" s="71">
+      <c r="E1544" s="1">
         <v>120001</v>
       </c>
       <c r="F1544" s="1">
@@ -95182,7 +95137,7 @@
         <v>9</v>
       </c>
       <c r="J1544" s="2" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="K1544" s="1">
         <v>0</v>
@@ -95203,7 +95158,7 @@
         <v>0</v>
       </c>
       <c r="Q1544" s="1" t="s">
-        <v>1477</v>
+        <v>1448</v>
       </c>
       <c r="R1544" s="1">
         <v>0</v>
@@ -95213,7 +95168,7 @@
       </c>
     </row>
     <row r="1545" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1545" s="71">
+      <c r="A1545" s="1">
         <v>1210902</v>
       </c>
       <c r="B1545" s="1">
@@ -95225,7 +95180,7 @@
       <c r="D1545" s="1">
         <v>1</v>
       </c>
-      <c r="E1545" s="71">
+      <c r="E1545" s="1">
         <v>120001</v>
       </c>
       <c r="F1545" s="1">
@@ -95241,7 +95196,7 @@
         <v>9</v>
       </c>
       <c r="J1545" s="2" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="K1545" s="1">
         <v>0</v>
@@ -95262,7 +95217,7 @@
         <v>0</v>
       </c>
       <c r="Q1545" s="1" t="s">
-        <v>1479</v>
+        <v>1449</v>
       </c>
       <c r="R1545" s="1">
         <v>0</v>
@@ -95272,7 +95227,7 @@
       </c>
     </row>
     <row r="1546" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1546" s="71">
+      <c r="A1546" s="1">
         <v>1210903</v>
       </c>
       <c r="B1546" s="1">
@@ -95284,7 +95239,7 @@
       <c r="D1546" s="1">
         <v>1</v>
       </c>
-      <c r="E1546" s="71">
+      <c r="E1546" s="1">
         <v>120001</v>
       </c>
       <c r="F1546" s="1">
@@ -95300,7 +95255,7 @@
         <v>9</v>
       </c>
       <c r="J1546" s="2" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="K1546" s="1">
         <v>0</v>
@@ -95321,7 +95276,7 @@
         <v>0</v>
       </c>
       <c r="Q1546" s="1" t="s">
-        <v>1480</v>
+        <v>1450</v>
       </c>
       <c r="R1546" s="1">
         <v>0</v>
@@ -95331,7 +95286,7 @@
       </c>
     </row>
     <row r="1547" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1547" s="71">
+      <c r="A1547" s="1">
         <v>1210904</v>
       </c>
       <c r="B1547" s="1">
@@ -95343,7 +95298,7 @@
       <c r="D1547" s="1">
         <v>1</v>
       </c>
-      <c r="E1547" s="71">
+      <c r="E1547" s="1">
         <v>120001</v>
       </c>
       <c r="F1547" s="1">
@@ -95359,7 +95314,7 @@
         <v>9</v>
       </c>
       <c r="J1547" s="2" t="s">
-        <v>1481</v>
+        <v>1475</v>
       </c>
       <c r="K1547" s="1">
         <v>0</v>
@@ -95380,7 +95335,7 @@
         <v>0</v>
       </c>
       <c r="Q1547" s="1" t="s">
-        <v>1482</v>
+        <v>1451</v>
       </c>
       <c r="R1547" s="1">
         <v>0</v>
@@ -95390,7 +95345,7 @@
       </c>
     </row>
     <row r="1548" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1548" s="71">
+      <c r="A1548" s="1">
         <v>1210905</v>
       </c>
       <c r="B1548" s="1">
@@ -95402,7 +95357,7 @@
       <c r="D1548" s="1">
         <v>1</v>
       </c>
-      <c r="E1548" s="71">
+      <c r="E1548" s="1">
         <v>120001</v>
       </c>
       <c r="F1548" s="1">
@@ -95418,7 +95373,7 @@
         <v>9</v>
       </c>
       <c r="J1548" s="2" t="s">
-        <v>1483</v>
+        <v>1476</v>
       </c>
       <c r="K1548" s="1">
         <v>0</v>
@@ -95439,7 +95394,7 @@
         <v>0</v>
       </c>
       <c r="Q1548" s="1" t="s">
-        <v>1484</v>
+        <v>1452</v>
       </c>
       <c r="R1548" s="1">
         <v>0</v>
@@ -95449,7 +95404,7 @@
       </c>
     </row>
     <row r="1549" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1549" s="71">
+      <c r="A1549" s="1">
         <v>1210906</v>
       </c>
       <c r="B1549" s="1">
@@ -95461,7 +95416,7 @@
       <c r="D1549" s="1">
         <v>1</v>
       </c>
-      <c r="E1549" s="71">
+      <c r="E1549" s="1">
         <v>120001</v>
       </c>
       <c r="F1549" s="1">
@@ -95477,7 +95432,7 @@
         <v>9</v>
       </c>
       <c r="J1549" s="2" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
       <c r="K1549" s="1">
         <v>0</v>
@@ -95498,7 +95453,7 @@
         <v>0</v>
       </c>
       <c r="Q1549" s="1" t="s">
-        <v>1486</v>
+        <v>1453</v>
       </c>
       <c r="R1549" s="1">
         <v>0</v>
@@ -95508,7 +95463,7 @@
       </c>
     </row>
     <row r="1550" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1550" s="71">
+      <c r="A1550" s="1">
         <v>1210907</v>
       </c>
       <c r="B1550" s="1">
@@ -95520,7 +95475,7 @@
       <c r="D1550" s="1">
         <v>1</v>
       </c>
-      <c r="E1550" s="71">
+      <c r="E1550" s="1">
         <v>120001</v>
       </c>
       <c r="F1550" s="1">
@@ -95536,7 +95491,7 @@
         <v>9</v>
       </c>
       <c r="J1550" s="2" t="s">
-        <v>1483</v>
+        <v>1476</v>
       </c>
       <c r="K1550" s="1">
         <v>0</v>
@@ -95557,7 +95512,7 @@
         <v>0</v>
       </c>
       <c r="Q1550" s="1" t="s">
-        <v>1487</v>
+        <v>1454</v>
       </c>
       <c r="R1550" s="1">
         <v>0</v>
@@ -95567,7 +95522,7 @@
       </c>
     </row>
     <row r="1551" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1551" s="71">
+      <c r="A1551" s="1">
         <v>1210908</v>
       </c>
       <c r="B1551" s="1">
@@ -95579,7 +95534,7 @@
       <c r="D1551" s="1">
         <v>1</v>
       </c>
-      <c r="E1551" s="71">
+      <c r="E1551" s="1">
         <v>120001</v>
       </c>
       <c r="F1551" s="1">
@@ -95595,7 +95550,7 @@
         <v>9</v>
       </c>
       <c r="J1551" s="2" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
       <c r="K1551" s="1">
         <v>0</v>
@@ -95616,7 +95571,7 @@
         <v>0</v>
       </c>
       <c r="Q1551" s="1" t="s">
-        <v>1473</v>
+        <v>1446</v>
       </c>
       <c r="R1551" s="1">
         <v>0</v>
@@ -95626,7 +95581,7 @@
       </c>
     </row>
     <row r="1552" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1552" s="71">
+      <c r="A1552" s="1">
         <v>1210909</v>
       </c>
       <c r="B1552" s="1">
@@ -95638,7 +95593,7 @@
       <c r="D1552" s="1">
         <v>1</v>
       </c>
-      <c r="E1552" s="71">
+      <c r="E1552" s="1">
         <v>120001</v>
       </c>
       <c r="F1552" s="1">
@@ -95654,7 +95609,7 @@
         <v>9</v>
       </c>
       <c r="J1552" s="2" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="K1552" s="1">
         <v>0</v>
@@ -95675,7 +95630,7 @@
         <v>0</v>
       </c>
       <c r="Q1552" s="1" t="s">
-        <v>1490</v>
+        <v>1455</v>
       </c>
       <c r="R1552" s="1">
         <v>0</v>
@@ -95685,7 +95640,7 @@
       </c>
     </row>
     <row r="1553" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1553" s="71">
+      <c r="A1553" s="1">
         <v>1211001</v>
       </c>
       <c r="B1553" s="1">
@@ -95697,7 +95652,7 @@
       <c r="D1553" s="1">
         <v>1</v>
       </c>
-      <c r="E1553" s="71">
+      <c r="E1553" s="1">
         <v>120001</v>
       </c>
       <c r="F1553" s="1">
@@ -95713,7 +95668,7 @@
         <v>10</v>
       </c>
       <c r="J1553" s="2" t="s">
-        <v>1491</v>
+        <v>1482</v>
       </c>
       <c r="K1553" s="1">
         <v>0</v>
@@ -95744,7 +95699,7 @@
       </c>
     </row>
     <row r="1554" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1554" s="71">
+      <c r="A1554" s="1">
         <v>1211002</v>
       </c>
       <c r="B1554" s="1">
@@ -95756,7 +95711,7 @@
       <c r="D1554" s="1">
         <v>1</v>
       </c>
-      <c r="E1554" s="71">
+      <c r="E1554" s="1">
         <v>120001</v>
       </c>
       <c r="F1554" s="1">
@@ -95772,7 +95727,7 @@
         <v>10</v>
       </c>
       <c r="J1554" s="2" t="s">
-        <v>1492</v>
+        <v>1469</v>
       </c>
       <c r="K1554" s="1">
         <v>0</v>
@@ -95790,7 +95745,7 @@
         <v>0</v>
       </c>
       <c r="P1554" s="1" t="s">
-        <v>1493</v>
+        <v>1456</v>
       </c>
       <c r="Q1554" s="1">
         <v>0</v>
@@ -95803,7 +95758,7 @@
       </c>
     </row>
     <row r="1555" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1555" s="71">
+      <c r="A1555" s="1">
         <v>1211003</v>
       </c>
       <c r="B1555" s="1">
@@ -95815,7 +95770,7 @@
       <c r="D1555" s="1">
         <v>1</v>
       </c>
-      <c r="E1555" s="71">
+      <c r="E1555" s="1">
         <v>120001</v>
       </c>
       <c r="F1555" s="1">
@@ -95831,7 +95786,7 @@
         <v>10</v>
       </c>
       <c r="J1555" s="2" t="s">
-        <v>1492</v>
+        <v>1469</v>
       </c>
       <c r="K1555" s="1">
         <v>0</v>
@@ -95852,7 +95807,7 @@
         <v>0</v>
       </c>
       <c r="Q1555" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="R1555" s="1">
         <v>0</v>
@@ -95862,7 +95817,7 @@
       </c>
     </row>
     <row r="1556" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1556" s="71">
+      <c r="A1556" s="1">
         <v>1211004</v>
       </c>
       <c r="B1556" s="1">
@@ -95874,7 +95829,7 @@
       <c r="D1556" s="1">
         <v>1</v>
       </c>
-      <c r="E1556" s="71">
+      <c r="E1556" s="1">
         <v>120001</v>
       </c>
       <c r="F1556" s="1">
@@ -95890,7 +95845,7 @@
         <v>10</v>
       </c>
       <c r="J1556" s="2" t="s">
-        <v>1494</v>
+        <v>1483</v>
       </c>
       <c r="K1556" s="1">
         <v>0</v>
@@ -95911,7 +95866,7 @@
         <v>0</v>
       </c>
       <c r="Q1556" s="1" t="s">
-        <v>1495</v>
+        <v>1457</v>
       </c>
       <c r="R1556" s="1">
         <v>0</v>
@@ -95921,7 +95876,7 @@
       </c>
     </row>
     <row r="1557" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1557" s="71">
+      <c r="A1557" s="1">
         <v>1211005</v>
       </c>
       <c r="B1557" s="1">
@@ -95933,7 +95888,7 @@
       <c r="D1557" s="1">
         <v>1</v>
       </c>
-      <c r="E1557" s="71">
+      <c r="E1557" s="1">
         <v>120001</v>
       </c>
       <c r="F1557" s="1">
@@ -95949,7 +95904,7 @@
         <v>10</v>
       </c>
       <c r="J1557" s="2" t="s">
-        <v>1492</v>
+        <v>1469</v>
       </c>
       <c r="K1557" s="1">
         <v>0</v>
@@ -95970,7 +95925,7 @@
         <v>0</v>
       </c>
       <c r="Q1557" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="R1557" s="1">
         <v>0</v>
@@ -95980,7 +95935,7 @@
       </c>
     </row>
     <row r="1558" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1558" s="71">
+      <c r="A1558" s="1">
         <v>1211006</v>
       </c>
       <c r="B1558" s="1">
@@ -95992,7 +95947,7 @@
       <c r="D1558" s="1">
         <v>1</v>
       </c>
-      <c r="E1558" s="71">
+      <c r="E1558" s="1">
         <v>120001</v>
       </c>
       <c r="F1558" s="1">
@@ -96008,7 +95963,7 @@
         <v>10</v>
       </c>
       <c r="J1558" s="2" t="s">
-        <v>1496</v>
+        <v>1484</v>
       </c>
       <c r="K1558" s="1">
         <v>0</v>
@@ -96029,7 +95984,7 @@
         <v>0</v>
       </c>
       <c r="Q1558" s="1" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="R1558" s="1">
         <v>0</v>
@@ -96039,7 +95994,7 @@
       </c>
     </row>
     <row r="1559" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1559" s="71">
+      <c r="A1559" s="1">
         <v>1211007</v>
       </c>
       <c r="B1559" s="1">
@@ -96051,7 +96006,7 @@
       <c r="D1559" s="1">
         <v>1</v>
       </c>
-      <c r="E1559" s="71">
+      <c r="E1559" s="1">
         <v>120001</v>
       </c>
       <c r="F1559" s="1">
@@ -96067,7 +96022,7 @@
         <v>10</v>
       </c>
       <c r="J1559" s="2" t="s">
-        <v>1492</v>
+        <v>1469</v>
       </c>
       <c r="K1559" s="1">
         <v>0</v>
@@ -96088,7 +96043,7 @@
         <v>0</v>
       </c>
       <c r="Q1559" s="1" t="s">
-        <v>1497</v>
+        <v>1458</v>
       </c>
       <c r="R1559" s="1">
         <v>0</v>
@@ -96098,7 +96053,7 @@
       </c>
     </row>
     <row r="1560" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1560" s="71">
+      <c r="A1560" s="1">
         <v>1211008</v>
       </c>
       <c r="B1560" s="1">
@@ -96110,7 +96065,7 @@
       <c r="D1560" s="1">
         <v>1</v>
       </c>
-      <c r="E1560" s="71">
+      <c r="E1560" s="1">
         <v>120001</v>
       </c>
       <c r="F1560" s="1">
@@ -96126,7 +96081,7 @@
         <v>10</v>
       </c>
       <c r="J1560" s="2" t="s">
-        <v>1494</v>
+        <v>1483</v>
       </c>
       <c r="K1560" s="1">
         <v>0</v>
@@ -96147,7 +96102,7 @@
         <v>0</v>
       </c>
       <c r="Q1560" s="1" t="s">
-        <v>1498</v>
+        <v>1459</v>
       </c>
       <c r="R1560" s="1">
         <v>0</v>
@@ -96157,7 +96112,7 @@
       </c>
     </row>
     <row r="1561" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1561" s="71">
+      <c r="A1561" s="1">
         <v>1211009</v>
       </c>
       <c r="B1561" s="1">
@@ -96169,7 +96124,7 @@
       <c r="D1561" s="1">
         <v>1</v>
       </c>
-      <c r="E1561" s="71">
+      <c r="E1561" s="1">
         <v>120001</v>
       </c>
       <c r="F1561" s="1">
@@ -96185,7 +96140,7 @@
         <v>10</v>
       </c>
       <c r="J1561" s="2" t="s">
-        <v>1492</v>
+        <v>1469</v>
       </c>
       <c r="K1561" s="1">
         <v>0</v>
@@ -96206,7 +96161,7 @@
         <v>0</v>
       </c>
       <c r="Q1561" s="1" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="R1561" s="1">
         <v>0</v>
@@ -96216,7 +96171,7 @@
       </c>
     </row>
     <row r="1562" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1562" s="71">
+      <c r="A1562" s="1">
         <v>1211010</v>
       </c>
       <c r="B1562" s="1">
@@ -96228,7 +96183,7 @@
       <c r="D1562" s="1">
         <v>1</v>
       </c>
-      <c r="E1562" s="71">
+      <c r="E1562" s="1">
         <v>120001</v>
       </c>
       <c r="F1562" s="1">
@@ -96244,7 +96199,7 @@
         <v>10</v>
       </c>
       <c r="J1562" s="2" t="s">
-        <v>1492</v>
+        <v>1469</v>
       </c>
       <c r="K1562" s="1">
         <v>0</v>
@@ -96265,7 +96220,7 @@
         <v>0</v>
       </c>
       <c r="Q1562" s="1" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="R1562" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DA6E2F-478D-44EA-A775-93A367F9FFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8FDDFF-4515-4D6E-AC4F-1CF25571028D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3521" uniqueCount="1485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3713" uniqueCount="1558">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -4371,177 +4371,21 @@
     <t>121101,121101</t>
   </si>
   <si>
-    <t>65,75,1500</t>
-  </si>
-  <si>
-    <t>35,75,1500</t>
-  </si>
-  <si>
-    <t>0,5500,1500</t>
-  </si>
-  <si>
-    <t>90,5500,1500</t>
-  </si>
-  <si>
-    <t>270,5500,1500</t>
-  </si>
-  <si>
-    <t>45,5500,1500</t>
-  </si>
-  <si>
-    <t>135,5500,1500</t>
-  </si>
-  <si>
-    <t>225,5500,1500</t>
-  </si>
-  <si>
-    <t>315,5500,1500</t>
-  </si>
-  <si>
-    <t>30,5500,1500</t>
-  </si>
-  <si>
-    <t>102,6500,1500</t>
-  </si>
-  <si>
-    <t>174,5500,1500</t>
-  </si>
-  <si>
-    <t>246,5500,1500</t>
-  </si>
-  <si>
-    <t>318,5500,1500</t>
-  </si>
-  <si>
-    <t>70,5500,1500</t>
-  </si>
-  <si>
-    <t>142,6500,1500</t>
-  </si>
-  <si>
-    <t>214,5500,1500</t>
-  </si>
-  <si>
     <t>75,55,75,45</t>
   </si>
   <si>
-    <t>286,5500,1500</t>
-  </si>
-  <si>
-    <t>358,5500,1500</t>
-  </si>
-  <si>
-    <t>50,5500,1500</t>
-  </si>
-  <si>
-    <t>110,6500,1500</t>
-  </si>
-  <si>
-    <t>170,5500,1500</t>
-  </si>
-  <si>
     <t>35,75,30,70,25,65</t>
   </si>
   <si>
-    <t>230,5500,1500</t>
-  </si>
-  <si>
-    <t>290,5500,1500</t>
-  </si>
-  <si>
-    <t>350,5500,1500</t>
-  </si>
-  <si>
-    <t>204,5500,1500</t>
-  </si>
-  <si>
-    <t>256,6500,1500</t>
-  </si>
-  <si>
-    <t>308,5500,1500</t>
-  </si>
-  <si>
-    <t>52,5500,1500</t>
-  </si>
-  <si>
-    <t>104,5500,1500</t>
-  </si>
-  <si>
-    <t>156,5500,1500</t>
-  </si>
-  <si>
-    <t>25,5500,1500</t>
-  </si>
-  <si>
-    <t>115,6500,1500</t>
-  </si>
-  <si>
-    <t>160,5500,1500</t>
-  </si>
-  <si>
-    <t>205,5500,1500</t>
-  </si>
-  <si>
-    <t>250,5500,1500</t>
-  </si>
-  <si>
-    <t>295,5500,1500</t>
-  </si>
-  <si>
-    <t>340,5500,1500</t>
-  </si>
-  <si>
-    <t>15,5500,1500</t>
-  </si>
-  <si>
-    <t>55,5500,1500</t>
-  </si>
-  <si>
-    <t>95,5500,1500</t>
-  </si>
-  <si>
-    <t>135,6500,1500</t>
-  </si>
-  <si>
-    <t>175,5500,1500</t>
-  </si>
-  <si>
-    <t>215,5500,1500</t>
-  </si>
-  <si>
-    <t>255,5500,1500</t>
-  </si>
-  <si>
-    <t>335,5500,1500</t>
-  </si>
-  <si>
     <t>95,95,1500</t>
   </si>
   <si>
-    <t>45,6500,1500</t>
-  </si>
-  <si>
-    <t>180,5500,1500</t>
-  </si>
-  <si>
-    <t>225,6500,1500</t>
-  </si>
-  <si>
     <t>121101,121101,121101</t>
   </si>
   <si>
-    <t>121105,121101,121101</t>
-  </si>
-  <si>
     <t>121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>121101,121101,121104</t>
-  </si>
-  <si>
-    <t>121101,121101,121101,121104</t>
-  </si>
-  <si>
     <t>121105,121101,121101,121101</t>
   </si>
   <si>
@@ -4551,55 +4395,430 @@
     <t>121105,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>121105,121101,121101,121104</t>
-  </si>
-  <si>
     <t>121105,121105,121105</t>
   </si>
   <si>
-    <t>121105,121105,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>121105,121105,121101,121101</t>
-  </si>
-  <si>
-    <t>121105,121105,121104,121104</t>
-  </si>
-  <si>
-    <t>121102,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>121105,121105,121105,121101,121101</t>
-  </si>
-  <si>
-    <t>121105,121105,121105,121104,121104</t>
-  </si>
-  <si>
-    <t>121102,121105,121105,121105</t>
-  </si>
-  <si>
-    <t>121105,121105,121105,121105</t>
-  </si>
-  <si>
-    <t>121102,121105,121105,121101,121101</t>
-  </si>
-  <si>
-    <t>121102,121102,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>121105,121105,121105,121105,121105</t>
-  </si>
-  <si>
-    <t>121102,121102,121105,121105</t>
-  </si>
-  <si>
     <t>121113</t>
   </si>
   <si>
-    <t>121104,121104</t>
-  </si>
-  <si>
     <t>121102,121102</t>
+  </si>
+  <si>
+    <t>1210101</t>
+  </si>
+  <si>
+    <t>120001</t>
+  </si>
+  <si>
+    <t>1210102</t>
+  </si>
+  <si>
+    <t>65,60,1500</t>
+  </si>
+  <si>
+    <t>1210103</t>
+  </si>
+  <si>
+    <t>35,60,1500</t>
+  </si>
+  <si>
+    <t>1210201</t>
+  </si>
+  <si>
+    <t>1210202</t>
+  </si>
+  <si>
+    <t>0,4500,1200</t>
+  </si>
+  <si>
+    <t>1210203</t>
+  </si>
+  <si>
+    <t>90,4500,1200</t>
+  </si>
+  <si>
+    <t>1210204</t>
+  </si>
+  <si>
+    <t>270,4500,1200</t>
+  </si>
+  <si>
+    <t>1210301</t>
+  </si>
+  <si>
+    <t>45,4500,1200</t>
+  </si>
+  <si>
+    <t>1210302</t>
+  </si>
+  <si>
+    <t>135,4500,1200</t>
+  </si>
+  <si>
+    <t>1210303</t>
+  </si>
+  <si>
+    <t>225,4500,1200</t>
+  </si>
+  <si>
+    <t>1210304</t>
+  </si>
+  <si>
+    <t>315,4500,1200</t>
+  </si>
+  <si>
+    <t>1210401</t>
+  </si>
+  <si>
+    <t>30,4500,1200</t>
+  </si>
+  <si>
+    <t>1210402</t>
+  </si>
+  <si>
+    <t>121101,121101,121101,121101,121104</t>
+  </si>
+  <si>
+    <t>102,5500,1200</t>
+  </si>
+  <si>
+    <t>1210403</t>
+  </si>
+  <si>
+    <t>174,4500,1200</t>
+  </si>
+  <si>
+    <t>1210404</t>
+  </si>
+  <si>
+    <t>246,4500,1200</t>
+  </si>
+  <si>
+    <t>1210405</t>
+  </si>
+  <si>
+    <t>318,4500,1200</t>
+  </si>
+  <si>
+    <t>1210501</t>
+  </si>
+  <si>
+    <t>121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>70,4500,1200</t>
+  </si>
+  <si>
+    <t>1210502</t>
+  </si>
+  <si>
+    <t>121101,121101,121101,121101,121101,121104</t>
+  </si>
+  <si>
+    <t>142,5500,1200</t>
+  </si>
+  <si>
+    <t>1210503</t>
+  </si>
+  <si>
+    <t>121105,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>214,4500,1200</t>
+  </si>
+  <si>
+    <t>1210504</t>
+  </si>
+  <si>
+    <t>1210505</t>
+  </si>
+  <si>
+    <t>121105,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>286,4500,1200</t>
+  </si>
+  <si>
+    <t>1210506</t>
+  </si>
+  <si>
+    <t>121105,121105,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>358,4500,1200</t>
+  </si>
+  <si>
+    <t>1210601</t>
+  </si>
+  <si>
+    <t>50,4500,1200</t>
+  </si>
+  <si>
+    <t>1210602</t>
+  </si>
+  <si>
+    <t>121105,121105,121101,121101,121101,121101,121104</t>
+  </si>
+  <si>
+    <t>110,5500,1200</t>
+  </si>
+  <si>
+    <t>1210603</t>
+  </si>
+  <si>
+    <t>170,4500,1200</t>
+  </si>
+  <si>
+    <t>1210604</t>
+  </si>
+  <si>
+    <t>1210605</t>
+  </si>
+  <si>
+    <t>121105,121105,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>230,4500,1200</t>
+  </si>
+  <si>
+    <t>1210606</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>290,4500,1200</t>
+  </si>
+  <si>
+    <t>1210607</t>
+  </si>
+  <si>
+    <t>350,4500,1200</t>
+  </si>
+  <si>
+    <t>1210701</t>
+  </si>
+  <si>
+    <t>204,4500,1200</t>
+  </si>
+  <si>
+    <t>1210702</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121101,121101,121101,121104,121104</t>
+  </si>
+  <si>
+    <t>256,5500,1200</t>
+  </si>
+  <si>
+    <t>1210703</t>
+  </si>
+  <si>
+    <t>308,4500,1200</t>
+  </si>
+  <si>
+    <t>1210704</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>1210705</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121105,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>52,4500,1200</t>
+  </si>
+  <si>
+    <t>1210706</t>
+  </si>
+  <si>
+    <t>104,4500,1200</t>
+  </si>
+  <si>
+    <t>1210707</t>
+  </si>
+  <si>
+    <t>156,4500,1200</t>
+  </si>
+  <si>
+    <t>1210801</t>
+  </si>
+  <si>
+    <t>25,4500,1200</t>
+  </si>
+  <si>
+    <t>1210802</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>1210803</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121101,121101,121101,121101,121104,121104</t>
+  </si>
+  <si>
+    <t>115,5500,1200</t>
+  </si>
+  <si>
+    <t>1210804</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>160,4500,1200</t>
+  </si>
+  <si>
+    <t>1210805</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121105,121105,121105,121105,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>205,4500,1200</t>
+  </si>
+  <si>
+    <t>1210806</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121105,121105,121105,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>250,4500,1200</t>
+  </si>
+  <si>
+    <t>1210807</t>
+  </si>
+  <si>
+    <t>295,4500,1200</t>
+  </si>
+  <si>
+    <t>1210808</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121105,121105,121105,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>340,4500,1200</t>
+  </si>
+  <si>
+    <t>1210901</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121105,121105,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>15,4500,1200</t>
+  </si>
+  <si>
+    <t>1210902</t>
+  </si>
+  <si>
+    <t>121102,121102,121101,121101,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>55,4500,1200</t>
+  </si>
+  <si>
+    <t>1210903</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>95,4500,1200</t>
+  </si>
+  <si>
+    <t>1210904</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121104,121104</t>
+  </si>
+  <si>
+    <t>135,5500,1200</t>
+  </si>
+  <si>
+    <t>1210905</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>175,4500,1200</t>
+  </si>
+  <si>
+    <t>1210906</t>
+  </si>
+  <si>
+    <t>215,4500,1200</t>
+  </si>
+  <si>
+    <t>1210907</t>
+  </si>
+  <si>
+    <t>255,4500,1200</t>
+  </si>
+  <si>
+    <t>1210908</t>
+  </si>
+  <si>
+    <t>1210909</t>
+  </si>
+  <si>
+    <t>121102,121102,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>335,4500,1200</t>
+  </si>
+  <si>
+    <t>1211001</t>
+  </si>
+  <si>
+    <t>1211002</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121105,121105</t>
+  </si>
+  <si>
+    <t>1211003</t>
+  </si>
+  <si>
+    <t>1211004</t>
+  </si>
+  <si>
+    <t>121104,121104,121105,121105</t>
+  </si>
+  <si>
+    <t>45,5500,1200</t>
+  </si>
+  <si>
+    <t>1211005</t>
+  </si>
+  <si>
+    <t>1211006</t>
+  </si>
+  <si>
+    <t>1211007</t>
+  </si>
+  <si>
+    <t>180,4500,1200</t>
+  </si>
+  <si>
+    <t>1211008</t>
+  </si>
+  <si>
+    <t>225,5500,1200</t>
+  </si>
+  <si>
+    <t>1211009</t>
+  </si>
+  <si>
+    <t>1211010</t>
   </si>
 </sst>
 </file>
@@ -5434,7 +5653,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S1562"/>
+  <dimension ref="A1:S1563"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -92572,8 +92791,8 @@
       </c>
     </row>
     <row r="1501" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1501" s="1">
-        <v>1210101</v>
+      <c r="A1501" s="1" t="s">
+        <v>1419</v>
       </c>
       <c r="B1501" s="1">
         <v>12</v>
@@ -92581,11 +92800,11 @@
       <c r="C1501" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1501" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1501" s="1">
-        <v>120001</v>
+      <c r="D1501" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1501" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1501" s="1">
         <v>1</v>
@@ -92631,8 +92850,8 @@
       </c>
     </row>
     <row r="1502" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1502" s="1">
-        <v>1210102</v>
+      <c r="A1502" s="1" t="s">
+        <v>1421</v>
       </c>
       <c r="B1502" s="1">
         <v>12</v>
@@ -92640,11 +92859,11 @@
       <c r="C1502" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1502" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1502" s="1">
-        <v>120001</v>
+      <c r="D1502" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1502" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1502" s="1">
         <v>1</v>
@@ -92653,7 +92872,7 @@
         <v>2</v>
       </c>
       <c r="H1502" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1502" s="1">
         <v>1</v>
@@ -92677,7 +92896,7 @@
         <v>0</v>
       </c>
       <c r="P1502" s="1" t="s">
-        <v>1408</v>
+        <v>1422</v>
       </c>
       <c r="Q1502" s="1">
         <v>0</v>
@@ -92690,8 +92909,8 @@
       </c>
     </row>
     <row r="1503" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1503" s="1">
-        <v>1210103</v>
+      <c r="A1503" s="1" t="s">
+        <v>1423</v>
       </c>
       <c r="B1503" s="1">
         <v>12</v>
@@ -92699,11 +92918,11 @@
       <c r="C1503" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1503" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1503" s="1">
-        <v>120001</v>
+      <c r="D1503" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1503" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1503" s="1">
         <v>1</v>
@@ -92712,7 +92931,7 @@
         <v>3</v>
       </c>
       <c r="H1503" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1503" s="1">
         <v>1</v>
@@ -92736,7 +92955,7 @@
         <v>0</v>
       </c>
       <c r="P1503" s="1" t="s">
-        <v>1409</v>
+        <v>1424</v>
       </c>
       <c r="Q1503" s="1">
         <v>0</v>
@@ -92749,8 +92968,8 @@
       </c>
     </row>
     <row r="1504" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1504" s="1">
-        <v>1210201</v>
+      <c r="A1504" s="1" t="s">
+        <v>1425</v>
       </c>
       <c r="B1504" s="1">
         <v>12</v>
@@ -92758,11 +92977,11 @@
       <c r="C1504" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1504" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1504" s="1">
-        <v>120001</v>
+      <c r="D1504" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1504" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1504" s="1">
         <v>1</v>
@@ -92771,13 +92990,13 @@
         <v>4</v>
       </c>
       <c r="H1504" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1504" s="1">
         <v>2</v>
       </c>
       <c r="J1504" s="2" t="s">
-        <v>1460</v>
+        <v>1407</v>
       </c>
       <c r="K1504" s="1">
         <v>0</v>
@@ -92794,11 +93013,11 @@
       <c r="O1504" s="1">
         <v>0</v>
       </c>
-      <c r="P1504" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1504" s="1" t="s">
-        <v>1410</v>
+      <c r="P1504" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="Q1504" s="1">
+        <v>0</v>
       </c>
       <c r="R1504" s="1">
         <v>0</v>
@@ -92808,8 +93027,8 @@
       </c>
     </row>
     <row r="1505" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1505" s="1">
-        <v>1210202</v>
+      <c r="A1505" s="1" t="s">
+        <v>1426</v>
       </c>
       <c r="B1505" s="1">
         <v>12</v>
@@ -92817,11 +93036,11 @@
       <c r="C1505" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1505" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1505" s="1">
-        <v>120001</v>
+      <c r="D1505" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1505" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1505" s="1">
         <v>1</v>
@@ -92830,13 +93049,13 @@
         <v>5</v>
       </c>
       <c r="H1505" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1505" s="1">
         <v>2</v>
       </c>
       <c r="J1505" s="2" t="s">
-        <v>1460</v>
+        <v>1411</v>
       </c>
       <c r="K1505" s="1">
         <v>0</v>
@@ -92857,7 +93076,7 @@
         <v>0</v>
       </c>
       <c r="Q1505" s="1" t="s">
-        <v>1411</v>
+        <v>1427</v>
       </c>
       <c r="R1505" s="1">
         <v>0</v>
@@ -92867,8 +93086,8 @@
       </c>
     </row>
     <row r="1506" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1506" s="1">
-        <v>1210203</v>
+      <c r="A1506" s="1" t="s">
+        <v>1428</v>
       </c>
       <c r="B1506" s="1">
         <v>12</v>
@@ -92876,11 +93095,11 @@
       <c r="C1506" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1506" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1506" s="1">
-        <v>120001</v>
+      <c r="D1506" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1506" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1506" s="1">
         <v>1</v>
@@ -92889,13 +93108,13 @@
         <v>6</v>
       </c>
       <c r="H1506" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1506" s="1">
         <v>2</v>
       </c>
       <c r="J1506" s="2" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="K1506" s="1">
         <v>0</v>
@@ -92916,7 +93135,7 @@
         <v>0</v>
       </c>
       <c r="Q1506" s="1" t="s">
-        <v>1412</v>
+        <v>1429</v>
       </c>
       <c r="R1506" s="1">
         <v>0</v>
@@ -92926,8 +93145,8 @@
       </c>
     </row>
     <row r="1507" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1507" s="1">
-        <v>1210301</v>
+      <c r="A1507" s="1" t="s">
+        <v>1430</v>
       </c>
       <c r="B1507" s="1">
         <v>12</v>
@@ -92935,11 +93154,11 @@
       <c r="C1507" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1507" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1507" s="1">
-        <v>120001</v>
+      <c r="D1507" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1507" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1507" s="1">
         <v>1</v>
@@ -92948,13 +93167,13 @@
         <v>7</v>
       </c>
       <c r="H1507" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1507" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1507" s="2" t="s">
-        <v>1460</v>
+        <v>1411</v>
       </c>
       <c r="K1507" s="1">
         <v>0</v>
@@ -92975,7 +93194,7 @@
         <v>0</v>
       </c>
       <c r="Q1507" s="1" t="s">
-        <v>1413</v>
+        <v>1431</v>
       </c>
       <c r="R1507" s="1">
         <v>0</v>
@@ -92985,8 +93204,8 @@
       </c>
     </row>
     <row r="1508" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1508" s="1">
-        <v>1210302</v>
+      <c r="A1508" s="1" t="s">
+        <v>1432</v>
       </c>
       <c r="B1508" s="1">
         <v>12</v>
@@ -92994,11 +93213,11 @@
       <c r="C1508" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1508" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1508" s="1">
-        <v>120001</v>
+      <c r="D1508" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1508" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1508" s="1">
         <v>1</v>
@@ -93007,13 +93226,13 @@
         <v>8</v>
       </c>
       <c r="H1508" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1508" s="1">
         <v>3</v>
       </c>
       <c r="J1508" s="2" t="s">
-        <v>1460</v>
+        <v>1412</v>
       </c>
       <c r="K1508" s="1">
         <v>0</v>
@@ -93034,7 +93253,7 @@
         <v>0</v>
       </c>
       <c r="Q1508" s="1" t="s">
-        <v>1414</v>
+        <v>1433</v>
       </c>
       <c r="R1508" s="1">
         <v>0</v>
@@ -93044,8 +93263,8 @@
       </c>
     </row>
     <row r="1509" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1509" s="1">
-        <v>1210303</v>
+      <c r="A1509" s="1" t="s">
+        <v>1434</v>
       </c>
       <c r="B1509" s="1">
         <v>12</v>
@@ -93053,11 +93272,11 @@
       <c r="C1509" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1509" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1509" s="1">
-        <v>120001</v>
+      <c r="D1509" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1509" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1509" s="1">
         <v>1</v>
@@ -93066,13 +93285,13 @@
         <v>9</v>
       </c>
       <c r="H1509" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1509" s="1">
         <v>3</v>
       </c>
       <c r="J1509" s="2" t="s">
-        <v>1461</v>
+        <v>1412</v>
       </c>
       <c r="K1509" s="1">
         <v>0</v>
@@ -93093,7 +93312,7 @@
         <v>0</v>
       </c>
       <c r="Q1509" s="1" t="s">
-        <v>1415</v>
+        <v>1435</v>
       </c>
       <c r="R1509" s="1">
         <v>0</v>
@@ -93103,8 +93322,8 @@
       </c>
     </row>
     <row r="1510" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1510" s="1">
-        <v>1210304</v>
+      <c r="A1510" s="1" t="s">
+        <v>1436</v>
       </c>
       <c r="B1510" s="1">
         <v>12</v>
@@ -93112,11 +93331,11 @@
       <c r="C1510" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1510" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1510" s="1">
-        <v>120001</v>
+      <c r="D1510" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1510" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1510" s="1">
         <v>1</v>
@@ -93125,13 +93344,13 @@
         <v>10</v>
       </c>
       <c r="H1510" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1510" s="1">
         <v>3</v>
       </c>
       <c r="J1510" s="2" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="K1510" s="1">
         <v>0</v>
@@ -93152,7 +93371,7 @@
         <v>0</v>
       </c>
       <c r="Q1510" s="1" t="s">
-        <v>1416</v>
+        <v>1437</v>
       </c>
       <c r="R1510" s="1">
         <v>0</v>
@@ -93162,8 +93381,8 @@
       </c>
     </row>
     <row r="1511" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1511" s="1">
-        <v>1210401</v>
+      <c r="A1511" s="1" t="s">
+        <v>1438</v>
       </c>
       <c r="B1511" s="1">
         <v>12</v>
@@ -93171,11 +93390,11 @@
       <c r="C1511" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1511" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1511" s="1">
-        <v>120001</v>
+      <c r="D1511" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1511" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1511" s="1">
         <v>1</v>
@@ -93184,13 +93403,13 @@
         <v>11</v>
       </c>
       <c r="H1511" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1511" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J1511" s="2" t="s">
-        <v>1462</v>
+        <v>1412</v>
       </c>
       <c r="K1511" s="1">
         <v>0</v>
@@ -93211,7 +93430,7 @@
         <v>0</v>
       </c>
       <c r="Q1511" s="1" t="s">
-        <v>1417</v>
+        <v>1439</v>
       </c>
       <c r="R1511" s="1">
         <v>0</v>
@@ -93221,8 +93440,8 @@
       </c>
     </row>
     <row r="1512" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1512" s="1">
-        <v>1210402</v>
+      <c r="A1512" s="1" t="s">
+        <v>1440</v>
       </c>
       <c r="B1512" s="1">
         <v>12</v>
@@ -93230,11 +93449,11 @@
       <c r="C1512" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1512" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1512" s="1">
-        <v>120001</v>
+      <c r="D1512" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1512" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1512" s="1">
         <v>1</v>
@@ -93243,13 +93462,13 @@
         <v>12</v>
       </c>
       <c r="H1512" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1512" s="1">
         <v>4</v>
       </c>
       <c r="J1512" s="2" t="s">
-        <v>1463</v>
+        <v>1412</v>
       </c>
       <c r="K1512" s="1">
         <v>0</v>
@@ -93270,7 +93489,7 @@
         <v>0</v>
       </c>
       <c r="Q1512" s="1" t="s">
-        <v>1418</v>
+        <v>1441</v>
       </c>
       <c r="R1512" s="1">
         <v>0</v>
@@ -93280,8 +93499,8 @@
       </c>
     </row>
     <row r="1513" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1513" s="1">
-        <v>1210403</v>
+      <c r="A1513" s="1" t="s">
+        <v>1442</v>
       </c>
       <c r="B1513" s="1">
         <v>12</v>
@@ -93289,11 +93508,11 @@
       <c r="C1513" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1513" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1513" s="1">
-        <v>120001</v>
+      <c r="D1513" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1513" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1513" s="1">
         <v>1</v>
@@ -93302,13 +93521,13 @@
         <v>13</v>
       </c>
       <c r="H1513" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1513" s="1">
         <v>4</v>
       </c>
       <c r="J1513" s="2" t="s">
-        <v>1461</v>
+        <v>1443</v>
       </c>
       <c r="K1513" s="1">
         <v>0</v>
@@ -93329,7 +93548,7 @@
         <v>0</v>
       </c>
       <c r="Q1513" s="1" t="s">
-        <v>1419</v>
+        <v>1444</v>
       </c>
       <c r="R1513" s="1">
         <v>0</v>
@@ -93339,8 +93558,8 @@
       </c>
     </row>
     <row r="1514" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1514" s="1">
-        <v>1210404</v>
+      <c r="A1514" s="1" t="s">
+        <v>1445</v>
       </c>
       <c r="B1514" s="1">
         <v>12</v>
@@ -93348,11 +93567,11 @@
       <c r="C1514" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1514" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1514" s="1">
-        <v>120001</v>
+      <c r="D1514" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1514" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1514" s="1">
         <v>1</v>
@@ -93361,13 +93580,13 @@
         <v>14</v>
       </c>
       <c r="H1514" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1514" s="1">
         <v>4</v>
       </c>
       <c r="J1514" s="2" t="s">
-        <v>1461</v>
+        <v>1415</v>
       </c>
       <c r="K1514" s="1">
         <v>0</v>
@@ -93388,7 +93607,7 @@
         <v>0</v>
       </c>
       <c r="Q1514" s="1" t="s">
-        <v>1420</v>
+        <v>1446</v>
       </c>
       <c r="R1514" s="1">
         <v>0</v>
@@ -93398,8 +93617,8 @@
       </c>
     </row>
     <row r="1515" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1515" s="1">
-        <v>1210405</v>
+      <c r="A1515" s="1" t="s">
+        <v>1447</v>
       </c>
       <c r="B1515" s="1">
         <v>12</v>
@@ -93407,11 +93626,11 @@
       <c r="C1515" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1515" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1515" s="1">
-        <v>120001</v>
+      <c r="D1515" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1515" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1515" s="1">
         <v>1</v>
@@ -93420,13 +93639,13 @@
         <v>15</v>
       </c>
       <c r="H1515" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1515" s="1">
         <v>4</v>
       </c>
       <c r="J1515" s="2" t="s">
-        <v>1461</v>
+        <v>1415</v>
       </c>
       <c r="K1515" s="1">
         <v>0</v>
@@ -93447,7 +93666,7 @@
         <v>0</v>
       </c>
       <c r="Q1515" s="1" t="s">
-        <v>1421</v>
+        <v>1448</v>
       </c>
       <c r="R1515" s="1">
         <v>0</v>
@@ -93457,8 +93676,8 @@
       </c>
     </row>
     <row r="1516" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1516" s="1">
-        <v>1210501</v>
+      <c r="A1516" s="1" t="s">
+        <v>1449</v>
       </c>
       <c r="B1516" s="1">
         <v>12</v>
@@ -93466,11 +93685,11 @@
       <c r="C1516" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1516" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1516" s="1">
-        <v>120001</v>
+      <c r="D1516" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1516" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1516" s="1">
         <v>1</v>
@@ -93479,13 +93698,13 @@
         <v>16</v>
       </c>
       <c r="H1516" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1516" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1516" s="2" t="s">
-        <v>1462</v>
+        <v>1415</v>
       </c>
       <c r="K1516" s="1">
         <v>0</v>
@@ -93506,7 +93725,7 @@
         <v>0</v>
       </c>
       <c r="Q1516" s="1" t="s">
-        <v>1422</v>
+        <v>1450</v>
       </c>
       <c r="R1516" s="1">
         <v>0</v>
@@ -93516,8 +93735,8 @@
       </c>
     </row>
     <row r="1517" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1517" s="1">
-        <v>1210502</v>
+      <c r="A1517" s="1" t="s">
+        <v>1451</v>
       </c>
       <c r="B1517" s="1">
         <v>12</v>
@@ -93525,11 +93744,11 @@
       <c r="C1517" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1517" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1517" s="1">
-        <v>120001</v>
+      <c r="D1517" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1517" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1517" s="1">
         <v>1</v>
@@ -93538,13 +93757,13 @@
         <v>17</v>
       </c>
       <c r="H1517" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1517" s="1">
         <v>5</v>
       </c>
       <c r="J1517" s="2" t="s">
-        <v>1464</v>
+        <v>1452</v>
       </c>
       <c r="K1517" s="1">
         <v>0</v>
@@ -93565,7 +93784,7 @@
         <v>0</v>
       </c>
       <c r="Q1517" s="1" t="s">
-        <v>1423</v>
+        <v>1453</v>
       </c>
       <c r="R1517" s="1">
         <v>0</v>
@@ -93575,8 +93794,8 @@
       </c>
     </row>
     <row r="1518" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1518" s="1">
-        <v>1210503</v>
+      <c r="A1518" s="1" t="s">
+        <v>1454</v>
       </c>
       <c r="B1518" s="1">
         <v>12</v>
@@ -93584,11 +93803,11 @@
       <c r="C1518" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1518" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1518" s="1">
-        <v>120001</v>
+      <c r="D1518" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1518" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1518" s="1">
         <v>1</v>
@@ -93597,13 +93816,13 @@
         <v>18</v>
       </c>
       <c r="H1518" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1518" s="1">
         <v>5</v>
       </c>
       <c r="J1518" s="2" t="s">
-        <v>1465</v>
+        <v>1455</v>
       </c>
       <c r="K1518" s="1">
         <v>0</v>
@@ -93624,7 +93843,7 @@
         <v>0</v>
       </c>
       <c r="Q1518" s="1" t="s">
-        <v>1424</v>
+        <v>1456</v>
       </c>
       <c r="R1518" s="1">
         <v>0</v>
@@ -93634,8 +93853,8 @@
       </c>
     </row>
     <row r="1519" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1519" s="1">
-        <v>1210504</v>
+      <c r="A1519" s="1" t="s">
+        <v>1457</v>
       </c>
       <c r="B1519" s="1">
         <v>12</v>
@@ -93643,11 +93862,11 @@
       <c r="C1519" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1519" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1519" s="1">
-        <v>120001</v>
+      <c r="D1519" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1519" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1519" s="1">
         <v>1</v>
@@ -93656,13 +93875,13 @@
         <v>19</v>
       </c>
       <c r="H1519" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1519" s="1">
         <v>5</v>
       </c>
       <c r="J1519" s="2" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
       <c r="K1519" s="1">
         <v>0</v>
@@ -93676,25 +93895,25 @@
       <c r="N1519" s="1">
         <v>0</v>
       </c>
-      <c r="O1519" s="1" t="s">
-        <v>1425</v>
+      <c r="O1519" s="1">
+        <v>0</v>
       </c>
       <c r="P1519" s="1">
         <v>0</v>
       </c>
-      <c r="Q1519" s="1">
-        <v>0</v>
+      <c r="Q1519" s="1" t="s">
+        <v>1459</v>
       </c>
       <c r="R1519" s="1">
         <v>0</v>
       </c>
       <c r="S1519" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1520" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1520" s="1">
-        <v>1210505</v>
+      <c r="A1520" s="1" t="s">
+        <v>1460</v>
       </c>
       <c r="B1520" s="1">
         <v>12</v>
@@ -93702,11 +93921,11 @@
       <c r="C1520" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1520" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1520" s="1">
-        <v>120001</v>
+      <c r="D1520" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1520" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1520" s="1">
         <v>1</v>
@@ -93715,13 +93934,13 @@
         <v>20</v>
       </c>
       <c r="H1520" s="1">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="I1520" s="1">
         <v>5</v>
       </c>
       <c r="J1520" s="2" t="s">
-        <v>1467</v>
+        <v>1414</v>
       </c>
       <c r="K1520" s="1">
         <v>0</v>
@@ -93735,25 +93954,25 @@
       <c r="N1520" s="1">
         <v>0</v>
       </c>
-      <c r="O1520" s="1">
-        <v>0</v>
+      <c r="O1520" s="1" t="s">
+        <v>1408</v>
       </c>
       <c r="P1520" s="1">
         <v>0</v>
       </c>
-      <c r="Q1520" s="1" t="s">
-        <v>1426</v>
+      <c r="Q1520" s="1">
+        <v>0</v>
       </c>
       <c r="R1520" s="1">
         <v>0</v>
       </c>
       <c r="S1520" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1521" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1521" s="1">
-        <v>1210506</v>
+      <c r="A1521" s="1" t="s">
+        <v>1461</v>
       </c>
       <c r="B1521" s="1">
         <v>12</v>
@@ -93761,11 +93980,11 @@
       <c r="C1521" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1521" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1521" s="1">
-        <v>120001</v>
+      <c r="D1521" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1521" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1521" s="1">
         <v>1</v>
@@ -93774,13 +93993,13 @@
         <v>21</v>
       </c>
       <c r="H1521" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I1521" s="1">
         <v>5</v>
       </c>
       <c r="J1521" s="2" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="K1521" s="1">
         <v>0</v>
@@ -93801,7 +94020,7 @@
         <v>0</v>
       </c>
       <c r="Q1521" s="1" t="s">
-        <v>1427</v>
+        <v>1463</v>
       </c>
       <c r="R1521" s="1">
         <v>0</v>
@@ -93811,8 +94030,8 @@
       </c>
     </row>
     <row r="1522" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1522" s="1">
-        <v>1210601</v>
+      <c r="A1522" s="1" t="s">
+        <v>1464</v>
       </c>
       <c r="B1522" s="1">
         <v>12</v>
@@ -93820,11 +94039,11 @@
       <c r="C1522" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1522" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1522" s="1">
-        <v>120001</v>
+      <c r="D1522" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1522" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1522" s="1">
         <v>1</v>
@@ -93833,10 +94052,10 @@
         <v>22</v>
       </c>
       <c r="H1522" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1522" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J1522" s="2" t="s">
         <v>1465</v>
@@ -93860,7 +94079,7 @@
         <v>0</v>
       </c>
       <c r="Q1522" s="1" t="s">
-        <v>1428</v>
+        <v>1466</v>
       </c>
       <c r="R1522" s="1">
         <v>0</v>
@@ -93870,8 +94089,8 @@
       </c>
     </row>
     <row r="1523" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1523" s="1">
-        <v>1210602</v>
+      <c r="A1523" s="1" t="s">
+        <v>1467</v>
       </c>
       <c r="B1523" s="1">
         <v>12</v>
@@ -93879,11 +94098,11 @@
       <c r="C1523" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1523" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1523" s="1">
-        <v>120001</v>
+      <c r="D1523" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1523" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1523" s="1">
         <v>1</v>
@@ -93892,35 +94111,35 @@
         <v>23</v>
       </c>
       <c r="H1523" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1523" s="1">
         <v>6</v>
       </c>
       <c r="J1523" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="K1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1523" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1523" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1523" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="K1523" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1523" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1523" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1523" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1523" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1523" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1523" s="1" t="s">
-        <v>1429</v>
-      </c>
       <c r="R1523" s="1">
         <v>0</v>
       </c>
@@ -93929,8 +94148,8 @@
       </c>
     </row>
     <row r="1524" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1524" s="1">
-        <v>1210603</v>
+      <c r="A1524" s="1" t="s">
+        <v>1469</v>
       </c>
       <c r="B1524" s="1">
         <v>12</v>
@@ -93938,11 +94157,11 @@
       <c r="C1524" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1524" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1524" s="1">
-        <v>120001</v>
+      <c r="D1524" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1524" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1524" s="1">
         <v>1</v>
@@ -93951,13 +94170,13 @@
         <v>24</v>
       </c>
       <c r="H1524" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1524" s="1">
         <v>6</v>
       </c>
       <c r="J1524" s="2" t="s">
-        <v>1465</v>
+        <v>1470</v>
       </c>
       <c r="K1524" s="1">
         <v>0</v>
@@ -93978,7 +94197,7 @@
         <v>0</v>
       </c>
       <c r="Q1524" s="1" t="s">
-        <v>1430</v>
+        <v>1471</v>
       </c>
       <c r="R1524" s="1">
         <v>0</v>
@@ -93988,8 +94207,8 @@
       </c>
     </row>
     <row r="1525" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1525" s="1">
-        <v>1210604</v>
+      <c r="A1525" s="1" t="s">
+        <v>1472</v>
       </c>
       <c r="B1525" s="1">
         <v>12</v>
@@ -93997,11 +94216,11 @@
       <c r="C1525" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1525" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1525" s="1">
-        <v>120001</v>
+      <c r="D1525" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1525" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1525" s="1">
         <v>1</v>
@@ -94010,13 +94229,13 @@
         <v>25</v>
       </c>
       <c r="H1525" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1525" s="1">
         <v>6</v>
       </c>
       <c r="J1525" s="2" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="K1525" s="1">
         <v>0</v>
@@ -94030,25 +94249,25 @@
       <c r="N1525" s="1">
         <v>0</v>
       </c>
-      <c r="O1525" s="1" t="s">
-        <v>1431</v>
+      <c r="O1525" s="1">
+        <v>0</v>
       </c>
       <c r="P1525" s="1">
         <v>0</v>
       </c>
-      <c r="Q1525" s="1">
-        <v>0</v>
+      <c r="Q1525" s="1" t="s">
+        <v>1473</v>
       </c>
       <c r="R1525" s="1">
         <v>0</v>
       </c>
       <c r="S1525" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1526" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1526" s="1">
-        <v>1210605</v>
+      <c r="A1526" s="1" t="s">
+        <v>1474</v>
       </c>
       <c r="B1526" s="1">
         <v>12</v>
@@ -94056,11 +94275,11 @@
       <c r="C1526" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1526" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1526" s="1">
-        <v>120001</v>
+      <c r="D1526" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1526" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1526" s="1">
         <v>1</v>
@@ -94069,13 +94288,13 @@
         <v>26</v>
       </c>
       <c r="H1526" s="1">
-        <v>1800</v>
+        <v>500</v>
       </c>
       <c r="I1526" s="1">
         <v>6</v>
       </c>
       <c r="J1526" s="2" t="s">
-        <v>1465</v>
+        <v>1416</v>
       </c>
       <c r="K1526" s="1">
         <v>0</v>
@@ -94089,25 +94308,25 @@
       <c r="N1526" s="1">
         <v>0</v>
       </c>
-      <c r="O1526" s="1">
-        <v>0</v>
+      <c r="O1526" s="1" t="s">
+        <v>1409</v>
       </c>
       <c r="P1526" s="1">
         <v>0</v>
       </c>
-      <c r="Q1526" s="1" t="s">
-        <v>1432</v>
+      <c r="Q1526" s="1">
+        <v>0</v>
       </c>
       <c r="R1526" s="1">
         <v>0</v>
       </c>
       <c r="S1526" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1527" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1527" s="1">
-        <v>1210606</v>
+      <c r="A1527" s="1" t="s">
+        <v>1475</v>
       </c>
       <c r="B1527" s="1">
         <v>12</v>
@@ -94115,11 +94334,11 @@
       <c r="C1527" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1527" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1527" s="1">
-        <v>120001</v>
+      <c r="D1527" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1527" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1527" s="1">
         <v>1</v>
@@ -94128,13 +94347,13 @@
         <v>27</v>
       </c>
       <c r="H1527" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1527" s="1">
         <v>6</v>
       </c>
       <c r="J1527" s="2" t="s">
-        <v>1470</v>
+        <v>1476</v>
       </c>
       <c r="K1527" s="1">
         <v>0</v>
@@ -94155,7 +94374,7 @@
         <v>0</v>
       </c>
       <c r="Q1527" s="1" t="s">
-        <v>1433</v>
+        <v>1477</v>
       </c>
       <c r="R1527" s="1">
         <v>0</v>
@@ -94165,8 +94384,8 @@
       </c>
     </row>
     <row r="1528" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1528" s="1">
-        <v>1210607</v>
+      <c r="A1528" s="1" t="s">
+        <v>1478</v>
       </c>
       <c r="B1528" s="1">
         <v>12</v>
@@ -94174,11 +94393,11 @@
       <c r="C1528" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1528" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1528" s="1">
-        <v>120001</v>
+      <c r="D1528" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1528" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1528" s="1">
         <v>1</v>
@@ -94187,13 +94406,13 @@
         <v>28</v>
       </c>
       <c r="H1528" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1528" s="1">
         <v>6</v>
       </c>
       <c r="J1528" s="2" t="s">
-        <v>1470</v>
+        <v>1479</v>
       </c>
       <c r="K1528" s="1">
         <v>0</v>
@@ -94214,7 +94433,7 @@
         <v>0</v>
       </c>
       <c r="Q1528" s="1" t="s">
-        <v>1434</v>
+        <v>1480</v>
       </c>
       <c r="R1528" s="1">
         <v>0</v>
@@ -94224,8 +94443,8 @@
       </c>
     </row>
     <row r="1529" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1529" s="1">
-        <v>1210701</v>
+      <c r="A1529" s="1" t="s">
+        <v>1481</v>
       </c>
       <c r="B1529" s="1">
         <v>12</v>
@@ -94233,11 +94452,11 @@
       <c r="C1529" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1529" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1529" s="1">
-        <v>120001</v>
+      <c r="D1529" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1529" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1529" s="1">
         <v>1</v>
@@ -94246,13 +94465,13 @@
         <v>29</v>
       </c>
       <c r="H1529" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1529" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J1529" s="2" t="s">
-        <v>1471</v>
+        <v>1479</v>
       </c>
       <c r="K1529" s="1">
         <v>0</v>
@@ -94273,7 +94492,7 @@
         <v>0</v>
       </c>
       <c r="Q1529" s="1" t="s">
-        <v>1435</v>
+        <v>1482</v>
       </c>
       <c r="R1529" s="1">
         <v>0</v>
@@ -94283,8 +94502,8 @@
       </c>
     </row>
     <row r="1530" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1530" s="1">
-        <v>1210702</v>
+      <c r="A1530" s="1" t="s">
+        <v>1483</v>
       </c>
       <c r="B1530" s="1">
         <v>12</v>
@@ -94292,11 +94511,11 @@
       <c r="C1530" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1530" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1530" s="1">
-        <v>120001</v>
+      <c r="D1530" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1530" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1530" s="1">
         <v>1</v>
@@ -94305,13 +94524,13 @@
         <v>30</v>
       </c>
       <c r="H1530" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1530" s="1">
         <v>7</v>
       </c>
       <c r="J1530" s="2" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
       <c r="K1530" s="1">
         <v>0</v>
@@ -94332,7 +94551,7 @@
         <v>0</v>
       </c>
       <c r="Q1530" s="1" t="s">
-        <v>1436</v>
+        <v>1484</v>
       </c>
       <c r="R1530" s="1">
         <v>0</v>
@@ -94342,8 +94561,8 @@
       </c>
     </row>
     <row r="1531" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1531" s="1">
-        <v>1210703</v>
+      <c r="A1531" s="1" t="s">
+        <v>1485</v>
       </c>
       <c r="B1531" s="1">
         <v>12</v>
@@ -94351,11 +94570,11 @@
       <c r="C1531" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1531" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1531" s="1">
-        <v>120001</v>
+      <c r="D1531" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1531" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1531" s="1">
         <v>1</v>
@@ -94364,13 +94583,13 @@
         <v>31</v>
       </c>
       <c r="H1531" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1531" s="1">
         <v>7</v>
       </c>
       <c r="J1531" s="2" t="s">
-        <v>1470</v>
+        <v>1486</v>
       </c>
       <c r="K1531" s="1">
         <v>0</v>
@@ -94391,7 +94610,7 @@
         <v>0</v>
       </c>
       <c r="Q1531" s="1" t="s">
-        <v>1437</v>
+        <v>1487</v>
       </c>
       <c r="R1531" s="1">
         <v>0</v>
@@ -94401,8 +94620,8 @@
       </c>
     </row>
     <row r="1532" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1532" s="1">
-        <v>1210704</v>
+      <c r="A1532" s="1" t="s">
+        <v>1488</v>
       </c>
       <c r="B1532" s="1">
         <v>12</v>
@@ -94410,11 +94629,11 @@
       <c r="C1532" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1532" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1532" s="1">
-        <v>120001</v>
+      <c r="D1532" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1532" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1532" s="1">
         <v>1</v>
@@ -94423,13 +94642,13 @@
         <v>32</v>
       </c>
       <c r="H1532" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1532" s="1">
         <v>7</v>
       </c>
       <c r="J1532" s="2" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="K1532" s="1">
         <v>0</v>
@@ -94450,7 +94669,7 @@
         <v>0</v>
       </c>
       <c r="Q1532" s="1" t="s">
-        <v>1410</v>
+        <v>1489</v>
       </c>
       <c r="R1532" s="1">
         <v>0</v>
@@ -94460,8 +94679,8 @@
       </c>
     </row>
     <row r="1533" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1533" s="1">
-        <v>1210705</v>
+      <c r="A1533" s="1" t="s">
+        <v>1490</v>
       </c>
       <c r="B1533" s="1">
         <v>12</v>
@@ -94469,11 +94688,11 @@
       <c r="C1533" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1533" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1533" s="1">
-        <v>120001</v>
+      <c r="D1533" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1533" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1533" s="1">
         <v>1</v>
@@ -94482,13 +94701,13 @@
         <v>33</v>
       </c>
       <c r="H1533" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1533" s="1">
         <v>7</v>
       </c>
       <c r="J1533" s="2" t="s">
-        <v>1474</v>
+        <v>1491</v>
       </c>
       <c r="K1533" s="1">
         <v>0</v>
@@ -94509,7 +94728,7 @@
         <v>0</v>
       </c>
       <c r="Q1533" s="1" t="s">
-        <v>1438</v>
+        <v>1427</v>
       </c>
       <c r="R1533" s="1">
         <v>0</v>
@@ -94519,8 +94738,8 @@
       </c>
     </row>
     <row r="1534" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1534" s="1">
-        <v>1210706</v>
+      <c r="A1534" s="1" t="s">
+        <v>1492</v>
       </c>
       <c r="B1534" s="1">
         <v>12</v>
@@ -94528,11 +94747,11 @@
       <c r="C1534" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1534" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1534" s="1">
-        <v>120001</v>
+      <c r="D1534" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1534" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1534" s="1">
         <v>1</v>
@@ -94541,13 +94760,13 @@
         <v>34</v>
       </c>
       <c r="H1534" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1534" s="1">
         <v>7</v>
       </c>
       <c r="J1534" s="2" t="s">
-        <v>1474</v>
+        <v>1493</v>
       </c>
       <c r="K1534" s="1">
         <v>0</v>
@@ -94568,7 +94787,7 @@
         <v>0</v>
       </c>
       <c r="Q1534" s="1" t="s">
-        <v>1439</v>
+        <v>1494</v>
       </c>
       <c r="R1534" s="1">
         <v>0</v>
@@ -94578,8 +94797,8 @@
       </c>
     </row>
     <row r="1535" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1535" s="1">
-        <v>1210707</v>
+      <c r="A1535" s="1" t="s">
+        <v>1495</v>
       </c>
       <c r="B1535" s="1">
         <v>12</v>
@@ -94587,11 +94806,11 @@
       <c r="C1535" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1535" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1535" s="1">
-        <v>120001</v>
+      <c r="D1535" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1535" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1535" s="1">
         <v>1</v>
@@ -94600,13 +94819,13 @@
         <v>35</v>
       </c>
       <c r="H1535" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1535" s="1">
         <v>7</v>
       </c>
       <c r="J1535" s="2" t="s">
-        <v>1474</v>
+        <v>1493</v>
       </c>
       <c r="K1535" s="1">
         <v>0</v>
@@ -94627,7 +94846,7 @@
         <v>0</v>
       </c>
       <c r="Q1535" s="1" t="s">
-        <v>1440</v>
+        <v>1496</v>
       </c>
       <c r="R1535" s="1">
         <v>0</v>
@@ -94637,8 +94856,8 @@
       </c>
     </row>
     <row r="1536" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1536" s="1">
-        <v>1210801</v>
+      <c r="A1536" s="1" t="s">
+        <v>1497</v>
       </c>
       <c r="B1536" s="1">
         <v>12</v>
@@ -94646,11 +94865,11 @@
       <c r="C1536" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1536" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1536" s="1">
-        <v>120001</v>
+      <c r="D1536" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1536" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1536" s="1">
         <v>1</v>
@@ -94659,13 +94878,13 @@
         <v>36</v>
       </c>
       <c r="H1536" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1536" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J1536" s="2" t="s">
-        <v>1474</v>
+        <v>1493</v>
       </c>
       <c r="K1536" s="1">
         <v>0</v>
@@ -94686,7 +94905,7 @@
         <v>0</v>
       </c>
       <c r="Q1536" s="1" t="s">
-        <v>1441</v>
+        <v>1498</v>
       </c>
       <c r="R1536" s="1">
         <v>0</v>
@@ -94696,8 +94915,8 @@
       </c>
     </row>
     <row r="1537" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1537" s="1">
-        <v>1210802</v>
+      <c r="A1537" s="1" t="s">
+        <v>1499</v>
       </c>
       <c r="B1537" s="1">
         <v>12</v>
@@ -94705,11 +94924,11 @@
       <c r="C1537" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1537" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1537" s="1">
-        <v>120001</v>
+      <c r="D1537" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1537" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1537" s="1">
         <v>1</v>
@@ -94718,13 +94937,13 @@
         <v>37</v>
       </c>
       <c r="H1537" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1537" s="1">
         <v>8</v>
       </c>
       <c r="J1537" s="2" t="s">
-        <v>1473</v>
+        <v>1493</v>
       </c>
       <c r="K1537" s="1">
         <v>0</v>
@@ -94745,7 +94964,7 @@
         <v>0</v>
       </c>
       <c r="Q1537" s="1" t="s">
-        <v>1422</v>
+        <v>1500</v>
       </c>
       <c r="R1537" s="1">
         <v>0</v>
@@ -94755,8 +94974,8 @@
       </c>
     </row>
     <row r="1538" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1538" s="1">
-        <v>1210803</v>
+      <c r="A1538" s="1" t="s">
+        <v>1501</v>
       </c>
       <c r="B1538" s="1">
         <v>12</v>
@@ -94764,11 +94983,11 @@
       <c r="C1538" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1538" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1538" s="1">
-        <v>120001</v>
+      <c r="D1538" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1538" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1538" s="1">
         <v>1</v>
@@ -94777,13 +94996,13 @@
         <v>38</v>
       </c>
       <c r="H1538" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1538" s="1">
         <v>8</v>
       </c>
       <c r="J1538" s="2" t="s">
-        <v>1475</v>
+        <v>1502</v>
       </c>
       <c r="K1538" s="1">
         <v>0</v>
@@ -94804,7 +95023,7 @@
         <v>0</v>
       </c>
       <c r="Q1538" s="1" t="s">
-        <v>1442</v>
+        <v>1453</v>
       </c>
       <c r="R1538" s="1">
         <v>0</v>
@@ -94814,8 +95033,8 @@
       </c>
     </row>
     <row r="1539" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1539" s="1">
-        <v>1210804</v>
+      <c r="A1539" s="1" t="s">
+        <v>1503</v>
       </c>
       <c r="B1539" s="1">
         <v>12</v>
@@ -94823,11 +95042,11 @@
       <c r="C1539" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1539" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1539" s="1">
-        <v>120001</v>
+      <c r="D1539" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1539" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1539" s="1">
         <v>1</v>
@@ -94836,13 +95055,13 @@
         <v>39</v>
       </c>
       <c r="H1539" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1539" s="1">
         <v>8</v>
       </c>
       <c r="J1539" s="2" t="s">
-        <v>1474</v>
+        <v>1504</v>
       </c>
       <c r="K1539" s="1">
         <v>0</v>
@@ -94863,7 +95082,7 @@
         <v>0</v>
       </c>
       <c r="Q1539" s="1" t="s">
-        <v>1443</v>
+        <v>1505</v>
       </c>
       <c r="R1539" s="1">
         <v>0</v>
@@ -94873,8 +95092,8 @@
       </c>
     </row>
     <row r="1540" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1540" s="1">
-        <v>1210805</v>
+      <c r="A1540" s="1" t="s">
+        <v>1506</v>
       </c>
       <c r="B1540" s="1">
         <v>12</v>
@@ -94882,11 +95101,11 @@
       <c r="C1540" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1540" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1540" s="1">
-        <v>120001</v>
+      <c r="D1540" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1540" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1540" s="1">
         <v>1</v>
@@ -94895,13 +95114,13 @@
         <v>40</v>
       </c>
       <c r="H1540" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1540" s="1">
         <v>8</v>
       </c>
       <c r="J1540" s="2" t="s">
-        <v>1476</v>
+        <v>1507</v>
       </c>
       <c r="K1540" s="1">
         <v>0</v>
@@ -94922,7 +95141,7 @@
         <v>0</v>
       </c>
       <c r="Q1540" s="1" t="s">
-        <v>1444</v>
+        <v>1508</v>
       </c>
       <c r="R1540" s="1">
         <v>0</v>
@@ -94932,8 +95151,8 @@
       </c>
     </row>
     <row r="1541" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1541" s="1">
-        <v>1210806</v>
+      <c r="A1541" s="1" t="s">
+        <v>1509</v>
       </c>
       <c r="B1541" s="1">
         <v>12</v>
@@ -94941,11 +95160,11 @@
       <c r="C1541" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1541" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1541" s="1">
-        <v>120001</v>
+      <c r="D1541" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1541" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1541" s="1">
         <v>1</v>
@@ -94954,13 +95173,13 @@
         <v>41</v>
       </c>
       <c r="H1541" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1541" s="1">
         <v>8</v>
       </c>
       <c r="J1541" s="2" t="s">
-        <v>1477</v>
+        <v>1510</v>
       </c>
       <c r="K1541" s="1">
         <v>0</v>
@@ -94981,7 +95200,7 @@
         <v>0</v>
       </c>
       <c r="Q1541" s="1" t="s">
-        <v>1445</v>
+        <v>1511</v>
       </c>
       <c r="R1541" s="1">
         <v>0</v>
@@ -94991,8 +95210,8 @@
       </c>
     </row>
     <row r="1542" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1542" s="1">
-        <v>1210807</v>
+      <c r="A1542" s="1" t="s">
+        <v>1512</v>
       </c>
       <c r="B1542" s="1">
         <v>12</v>
@@ -95000,11 +95219,11 @@
       <c r="C1542" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1542" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1542" s="1">
-        <v>120001</v>
+      <c r="D1542" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1542" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1542" s="1">
         <v>1</v>
@@ -95013,13 +95232,13 @@
         <v>42</v>
       </c>
       <c r="H1542" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1542" s="1">
         <v>8</v>
       </c>
       <c r="J1542" s="2" t="s">
-        <v>1477</v>
+        <v>1513</v>
       </c>
       <c r="K1542" s="1">
         <v>0</v>
@@ -95040,7 +95259,7 @@
         <v>0</v>
       </c>
       <c r="Q1542" s="1" t="s">
-        <v>1446</v>
+        <v>1514</v>
       </c>
       <c r="R1542" s="1">
         <v>0</v>
@@ -95050,8 +95269,8 @@
       </c>
     </row>
     <row r="1543" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1543" s="1">
-        <v>1210808</v>
+      <c r="A1543" s="1" t="s">
+        <v>1515</v>
       </c>
       <c r="B1543" s="1">
         <v>12</v>
@@ -95059,11 +95278,11 @@
       <c r="C1543" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1543" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1543" s="1">
-        <v>120001</v>
+      <c r="D1543" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1543" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1543" s="1">
         <v>1</v>
@@ -95072,13 +95291,13 @@
         <v>43</v>
       </c>
       <c r="H1543" s="1">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="I1543" s="1">
         <v>8</v>
       </c>
       <c r="J1543" s="2" t="s">
-        <v>1478</v>
+        <v>1513</v>
       </c>
       <c r="K1543" s="1">
         <v>0</v>
@@ -95099,7 +95318,7 @@
         <v>0</v>
       </c>
       <c r="Q1543" s="1" t="s">
-        <v>1447</v>
+        <v>1516</v>
       </c>
       <c r="R1543" s="1">
         <v>0</v>
@@ -95109,8 +95328,8 @@
       </c>
     </row>
     <row r="1544" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1544" s="1">
-        <v>1210901</v>
+      <c r="A1544" s="1" t="s">
+        <v>1517</v>
       </c>
       <c r="B1544" s="1">
         <v>12</v>
@@ -95118,11 +95337,11 @@
       <c r="C1544" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1544" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1544" s="1">
-        <v>120001</v>
+      <c r="D1544" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1544" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1544" s="1">
         <v>1</v>
@@ -95131,13 +95350,13 @@
         <v>44</v>
       </c>
       <c r="H1544" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I1544" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1544" s="2" t="s">
-        <v>1474</v>
+        <v>1518</v>
       </c>
       <c r="K1544" s="1">
         <v>0</v>
@@ -95158,7 +95377,7 @@
         <v>0</v>
       </c>
       <c r="Q1544" s="1" t="s">
-        <v>1448</v>
+        <v>1519</v>
       </c>
       <c r="R1544" s="1">
         <v>0</v>
@@ -95168,8 +95387,8 @@
       </c>
     </row>
     <row r="1545" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1545" s="1">
-        <v>1210902</v>
+      <c r="A1545" s="1" t="s">
+        <v>1520</v>
       </c>
       <c r="B1545" s="1">
         <v>12</v>
@@ -95177,11 +95396,11 @@
       <c r="C1545" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1545" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1545" s="1">
-        <v>120001</v>
+      <c r="D1545" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1545" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1545" s="1">
         <v>1</v>
@@ -95190,13 +95409,13 @@
         <v>45</v>
       </c>
       <c r="H1545" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I1545" s="1">
         <v>9</v>
       </c>
       <c r="J1545" s="2" t="s">
-        <v>1479</v>
+        <v>1521</v>
       </c>
       <c r="K1545" s="1">
         <v>0</v>
@@ -95217,7 +95436,7 @@
         <v>0</v>
       </c>
       <c r="Q1545" s="1" t="s">
-        <v>1449</v>
+        <v>1522</v>
       </c>
       <c r="R1545" s="1">
         <v>0</v>
@@ -95227,8 +95446,8 @@
       </c>
     </row>
     <row r="1546" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1546" s="1">
-        <v>1210903</v>
+      <c r="A1546" s="1" t="s">
+        <v>1523</v>
       </c>
       <c r="B1546" s="1">
         <v>12</v>
@@ -95236,11 +95455,11 @@
       <c r="C1546" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1546" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1546" s="1">
-        <v>120001</v>
+      <c r="D1546" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1546" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1546" s="1">
         <v>1</v>
@@ -95249,13 +95468,13 @@
         <v>46</v>
       </c>
       <c r="H1546" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I1546" s="1">
         <v>9</v>
       </c>
       <c r="J1546" s="2" t="s">
-        <v>1474</v>
+        <v>1524</v>
       </c>
       <c r="K1546" s="1">
         <v>0</v>
@@ -95276,7 +95495,7 @@
         <v>0</v>
       </c>
       <c r="Q1546" s="1" t="s">
-        <v>1450</v>
+        <v>1525</v>
       </c>
       <c r="R1546" s="1">
         <v>0</v>
@@ -95286,8 +95505,8 @@
       </c>
     </row>
     <row r="1547" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1547" s="1">
-        <v>1210904</v>
+      <c r="A1547" s="1" t="s">
+        <v>1526</v>
       </c>
       <c r="B1547" s="1">
         <v>12</v>
@@ -95295,11 +95514,11 @@
       <c r="C1547" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1547" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1547" s="1">
-        <v>120001</v>
+      <c r="D1547" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1547" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1547" s="1">
         <v>1</v>
@@ -95308,13 +95527,13 @@
         <v>47</v>
       </c>
       <c r="H1547" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I1547" s="1">
         <v>9</v>
       </c>
       <c r="J1547" s="2" t="s">
-        <v>1475</v>
+        <v>1527</v>
       </c>
       <c r="K1547" s="1">
         <v>0</v>
@@ -95335,7 +95554,7 @@
         <v>0</v>
       </c>
       <c r="Q1547" s="1" t="s">
-        <v>1451</v>
+        <v>1528</v>
       </c>
       <c r="R1547" s="1">
         <v>0</v>
@@ -95345,8 +95564,8 @@
       </c>
     </row>
     <row r="1548" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1548" s="1">
-        <v>1210905</v>
+      <c r="A1548" s="1" t="s">
+        <v>1529</v>
       </c>
       <c r="B1548" s="1">
         <v>12</v>
@@ -95354,11 +95573,11 @@
       <c r="C1548" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1548" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1548" s="1">
-        <v>120001</v>
+      <c r="D1548" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1548" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1548" s="1">
         <v>1</v>
@@ -95367,13 +95586,13 @@
         <v>48</v>
       </c>
       <c r="H1548" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I1548" s="1">
         <v>9</v>
       </c>
       <c r="J1548" s="2" t="s">
-        <v>1476</v>
+        <v>1530</v>
       </c>
       <c r="K1548" s="1">
         <v>0</v>
@@ -95394,7 +95613,7 @@
         <v>0</v>
       </c>
       <c r="Q1548" s="1" t="s">
-        <v>1452</v>
+        <v>1531</v>
       </c>
       <c r="R1548" s="1">
         <v>0</v>
@@ -95404,8 +95623,8 @@
       </c>
     </row>
     <row r="1549" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1549" s="1">
-        <v>1210906</v>
+      <c r="A1549" s="1" t="s">
+        <v>1532</v>
       </c>
       <c r="B1549" s="1">
         <v>12</v>
@@ -95413,11 +95632,11 @@
       <c r="C1549" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1549" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1549" s="1">
-        <v>120001</v>
+      <c r="D1549" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1549" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1549" s="1">
         <v>1</v>
@@ -95426,13 +95645,13 @@
         <v>49</v>
       </c>
       <c r="H1549" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I1549" s="1">
         <v>9</v>
       </c>
       <c r="J1549" s="2" t="s">
-        <v>1477</v>
+        <v>1533</v>
       </c>
       <c r="K1549" s="1">
         <v>0</v>
@@ -95453,7 +95672,7 @@
         <v>0</v>
       </c>
       <c r="Q1549" s="1" t="s">
-        <v>1453</v>
+        <v>1534</v>
       </c>
       <c r="R1549" s="1">
         <v>0</v>
@@ -95463,8 +95682,8 @@
       </c>
     </row>
     <row r="1550" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1550" s="1">
-        <v>1210907</v>
+      <c r="A1550" s="1" t="s">
+        <v>1535</v>
       </c>
       <c r="B1550" s="1">
         <v>12</v>
@@ -95472,11 +95691,11 @@
       <c r="C1550" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1550" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1550" s="1">
-        <v>120001</v>
+      <c r="D1550" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1550" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1550" s="1">
         <v>1</v>
@@ -95485,13 +95704,13 @@
         <v>50</v>
       </c>
       <c r="H1550" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I1550" s="1">
         <v>9</v>
       </c>
       <c r="J1550" s="2" t="s">
-        <v>1476</v>
+        <v>1527</v>
       </c>
       <c r="K1550" s="1">
         <v>0</v>
@@ -95512,7 +95731,7 @@
         <v>0</v>
       </c>
       <c r="Q1550" s="1" t="s">
-        <v>1454</v>
+        <v>1536</v>
       </c>
       <c r="R1550" s="1">
         <v>0</v>
@@ -95522,8 +95741,8 @@
       </c>
     </row>
     <row r="1551" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1551" s="1">
-        <v>1210908</v>
+      <c r="A1551" s="1" t="s">
+        <v>1537</v>
       </c>
       <c r="B1551" s="1">
         <v>12</v>
@@ -95531,11 +95750,11 @@
       <c r="C1551" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1551" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1551" s="1">
-        <v>120001</v>
+      <c r="D1551" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1551" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1551" s="1">
         <v>1</v>
@@ -95544,13 +95763,13 @@
         <v>51</v>
       </c>
       <c r="H1551" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I1551" s="1">
         <v>9</v>
       </c>
       <c r="J1551" s="2" t="s">
-        <v>1480</v>
+        <v>1533</v>
       </c>
       <c r="K1551" s="1">
         <v>0</v>
@@ -95571,7 +95790,7 @@
         <v>0</v>
       </c>
       <c r="Q1551" s="1" t="s">
-        <v>1446</v>
+        <v>1538</v>
       </c>
       <c r="R1551" s="1">
         <v>0</v>
@@ -95581,8 +95800,8 @@
       </c>
     </row>
     <row r="1552" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1552" s="1">
-        <v>1210909</v>
+      <c r="A1552" s="1" t="s">
+        <v>1539</v>
       </c>
       <c r="B1552" s="1">
         <v>12</v>
@@ -95590,11 +95809,11 @@
       <c r="C1552" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1552" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1552" s="1">
-        <v>120001</v>
+      <c r="D1552" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1552" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1552" s="1">
         <v>1</v>
@@ -95603,13 +95822,13 @@
         <v>52</v>
       </c>
       <c r="H1552" s="1">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I1552" s="1">
         <v>9</v>
       </c>
       <c r="J1552" s="2" t="s">
-        <v>1481</v>
+        <v>1527</v>
       </c>
       <c r="K1552" s="1">
         <v>0</v>
@@ -95630,7 +95849,7 @@
         <v>0</v>
       </c>
       <c r="Q1552" s="1" t="s">
-        <v>1455</v>
+        <v>1516</v>
       </c>
       <c r="R1552" s="1">
         <v>0</v>
@@ -95640,8 +95859,8 @@
       </c>
     </row>
     <row r="1553" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1553" s="1">
-        <v>1211001</v>
+      <c r="A1553" s="1" t="s">
+        <v>1540</v>
       </c>
       <c r="B1553" s="1">
         <v>12</v>
@@ -95649,11 +95868,11 @@
       <c r="C1553" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1553" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1553" s="1">
-        <v>120001</v>
+      <c r="D1553" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1553" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1553" s="1">
         <v>1</v>
@@ -95662,13 +95881,13 @@
         <v>53</v>
       </c>
       <c r="H1553" s="1">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="I1553" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1553" s="2" t="s">
-        <v>1482</v>
+        <v>1541</v>
       </c>
       <c r="K1553" s="1">
         <v>0</v>
@@ -95682,25 +95901,25 @@
       <c r="N1553" s="1">
         <v>0</v>
       </c>
-      <c r="O1553" s="1" t="s">
-        <v>153</v>
+      <c r="O1553" s="1">
+        <v>0</v>
       </c>
       <c r="P1553" s="1">
         <v>0</v>
       </c>
-      <c r="Q1553" s="1">
-        <v>0</v>
+      <c r="Q1553" s="1" t="s">
+        <v>1542</v>
       </c>
       <c r="R1553" s="1">
         <v>0</v>
       </c>
       <c r="S1553" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1554" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1554" s="1">
-        <v>1211002</v>
+      <c r="A1554" s="1" t="s">
+        <v>1543</v>
       </c>
       <c r="B1554" s="1">
         <v>12</v>
@@ -95708,11 +95927,11 @@
       <c r="C1554" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1554" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1554" s="1">
-        <v>120001</v>
+      <c r="D1554" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1554" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1554" s="1">
         <v>1</v>
@@ -95721,13 +95940,13 @@
         <v>54</v>
       </c>
       <c r="H1554" s="1">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="I1554" s="1">
         <v>10</v>
       </c>
       <c r="J1554" s="2" t="s">
-        <v>1469</v>
+        <v>1417</v>
       </c>
       <c r="K1554" s="1">
         <v>0</v>
@@ -95741,11 +95960,11 @@
       <c r="N1554" s="1">
         <v>0</v>
       </c>
-      <c r="O1554" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1554" s="1" t="s">
-        <v>1456</v>
+      <c r="O1554" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1554" s="1">
+        <v>0</v>
       </c>
       <c r="Q1554" s="1">
         <v>0</v>
@@ -95754,12 +95973,12 @@
         <v>0</v>
       </c>
       <c r="S1554" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1555" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1555" s="1">
-        <v>1211003</v>
+      <c r="A1555" s="1" t="s">
+        <v>1544</v>
       </c>
       <c r="B1555" s="1">
         <v>12</v>
@@ -95767,11 +95986,11 @@
       <c r="C1555" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1555" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1555" s="1">
-        <v>120001</v>
+      <c r="D1555" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1555" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1555" s="1">
         <v>1</v>
@@ -95786,7 +96005,7 @@
         <v>10</v>
       </c>
       <c r="J1555" s="2" t="s">
-        <v>1469</v>
+        <v>1545</v>
       </c>
       <c r="K1555" s="1">
         <v>0</v>
@@ -95803,12 +96022,12 @@
       <c r="O1555" s="1">
         <v>0</v>
       </c>
-      <c r="P1555" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1555" s="1" t="s">
+      <c r="P1555" s="1" t="s">
         <v>1410</v>
       </c>
+      <c r="Q1555" s="1">
+        <v>0</v>
+      </c>
       <c r="R1555" s="1">
         <v>0</v>
       </c>
@@ -95817,8 +96036,8 @@
       </c>
     </row>
     <row r="1556" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1556" s="1">
-        <v>1211004</v>
+      <c r="A1556" s="1" t="s">
+        <v>1546</v>
       </c>
       <c r="B1556" s="1">
         <v>12</v>
@@ -95826,11 +96045,11 @@
       <c r="C1556" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1556" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1556" s="1">
-        <v>120001</v>
+      <c r="D1556" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1556" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1556" s="1">
         <v>1</v>
@@ -95845,7 +96064,7 @@
         <v>10</v>
       </c>
       <c r="J1556" s="2" t="s">
-        <v>1483</v>
+        <v>1545</v>
       </c>
       <c r="K1556" s="1">
         <v>0</v>
@@ -95866,7 +96085,7 @@
         <v>0</v>
       </c>
       <c r="Q1556" s="1" t="s">
-        <v>1457</v>
+        <v>1427</v>
       </c>
       <c r="R1556" s="1">
         <v>0</v>
@@ -95876,8 +96095,8 @@
       </c>
     </row>
     <row r="1557" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1557" s="1">
-        <v>1211005</v>
+      <c r="A1557" s="1" t="s">
+        <v>1547</v>
       </c>
       <c r="B1557" s="1">
         <v>12</v>
@@ -95885,11 +96104,11 @@
       <c r="C1557" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1557" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1557" s="1">
-        <v>120001</v>
+      <c r="D1557" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1557" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1557" s="1">
         <v>1</v>
@@ -95904,7 +96123,7 @@
         <v>10</v>
       </c>
       <c r="J1557" s="2" t="s">
-        <v>1469</v>
+        <v>1548</v>
       </c>
       <c r="K1557" s="1">
         <v>0</v>
@@ -95925,7 +96144,7 @@
         <v>0</v>
       </c>
       <c r="Q1557" s="1" t="s">
-        <v>1411</v>
+        <v>1549</v>
       </c>
       <c r="R1557" s="1">
         <v>0</v>
@@ -95935,8 +96154,8 @@
       </c>
     </row>
     <row r="1558" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1558" s="1">
-        <v>1211006</v>
+      <c r="A1558" s="1" t="s">
+        <v>1550</v>
       </c>
       <c r="B1558" s="1">
         <v>12</v>
@@ -95944,11 +96163,11 @@
       <c r="C1558" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1558" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1558" s="1">
-        <v>120001</v>
+      <c r="D1558" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1558" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1558" s="1">
         <v>1</v>
@@ -95963,7 +96182,7 @@
         <v>10</v>
       </c>
       <c r="J1558" s="2" t="s">
-        <v>1484</v>
+        <v>1545</v>
       </c>
       <c r="K1558" s="1">
         <v>0</v>
@@ -95984,7 +96203,7 @@
         <v>0</v>
       </c>
       <c r="Q1558" s="1" t="s">
-        <v>1414</v>
+        <v>1429</v>
       </c>
       <c r="R1558" s="1">
         <v>0</v>
@@ -95994,8 +96213,8 @@
       </c>
     </row>
     <row r="1559" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1559" s="1">
-        <v>1211007</v>
+      <c r="A1559" s="1" t="s">
+        <v>1551</v>
       </c>
       <c r="B1559" s="1">
         <v>12</v>
@@ -96003,11 +96222,11 @@
       <c r="C1559" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1559" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1559" s="1">
-        <v>120001</v>
+      <c r="D1559" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1559" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1559" s="1">
         <v>1</v>
@@ -96022,7 +96241,7 @@
         <v>10</v>
       </c>
       <c r="J1559" s="2" t="s">
-        <v>1469</v>
+        <v>1418</v>
       </c>
       <c r="K1559" s="1">
         <v>0</v>
@@ -96043,7 +96262,7 @@
         <v>0</v>
       </c>
       <c r="Q1559" s="1" t="s">
-        <v>1458</v>
+        <v>1435</v>
       </c>
       <c r="R1559" s="1">
         <v>0</v>
@@ -96053,8 +96272,8 @@
       </c>
     </row>
     <row r="1560" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1560" s="1">
-        <v>1211008</v>
+      <c r="A1560" s="1" t="s">
+        <v>1552</v>
       </c>
       <c r="B1560" s="1">
         <v>12</v>
@@ -96062,11 +96281,11 @@
       <c r="C1560" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1560" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1560" s="1">
-        <v>120001</v>
+      <c r="D1560" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1560" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1560" s="1">
         <v>1</v>
@@ -96081,7 +96300,7 @@
         <v>10</v>
       </c>
       <c r="J1560" s="2" t="s">
-        <v>1483</v>
+        <v>1545</v>
       </c>
       <c r="K1560" s="1">
         <v>0</v>
@@ -96102,7 +96321,7 @@
         <v>0</v>
       </c>
       <c r="Q1560" s="1" t="s">
-        <v>1459</v>
+        <v>1553</v>
       </c>
       <c r="R1560" s="1">
         <v>0</v>
@@ -96112,8 +96331,8 @@
       </c>
     </row>
     <row r="1561" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1561" s="1">
-        <v>1211009</v>
+      <c r="A1561" s="1" t="s">
+        <v>1554</v>
       </c>
       <c r="B1561" s="1">
         <v>12</v>
@@ -96121,11 +96340,11 @@
       <c r="C1561" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1561" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1561" s="1">
-        <v>120001</v>
+      <c r="D1561" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1561" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1561" s="1">
         <v>1</v>
@@ -96140,7 +96359,7 @@
         <v>10</v>
       </c>
       <c r="J1561" s="2" t="s">
-        <v>1469</v>
+        <v>1548</v>
       </c>
       <c r="K1561" s="1">
         <v>0</v>
@@ -96161,7 +96380,7 @@
         <v>0</v>
       </c>
       <c r="Q1561" s="1" t="s">
-        <v>1412</v>
+        <v>1555</v>
       </c>
       <c r="R1561" s="1">
         <v>0</v>
@@ -96171,8 +96390,8 @@
       </c>
     </row>
     <row r="1562" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1562" s="1">
-        <v>1211010</v>
+      <c r="A1562" s="1" t="s">
+        <v>1556</v>
       </c>
       <c r="B1562" s="1">
         <v>12</v>
@@ -96180,11 +96399,11 @@
       <c r="C1562" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="D1562" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1562" s="1">
-        <v>120001</v>
+      <c r="D1562" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1562" s="1" t="s">
+        <v>1420</v>
       </c>
       <c r="F1562" s="1">
         <v>1</v>
@@ -96193,13 +96412,13 @@
         <v>62</v>
       </c>
       <c r="H1562" s="1">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="I1562" s="1">
         <v>10</v>
       </c>
       <c r="J1562" s="2" t="s">
-        <v>1469</v>
+        <v>1545</v>
       </c>
       <c r="K1562" s="1">
         <v>0</v>
@@ -96220,12 +96439,71 @@
         <v>0</v>
       </c>
       <c r="Q1562" s="1" t="s">
-        <v>1416</v>
+        <v>1431</v>
       </c>
       <c r="R1562" s="1">
         <v>0</v>
       </c>
       <c r="S1562" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1563" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B1563" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1563" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1563" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1563" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="F1563" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1563" s="1">
+        <v>63</v>
+      </c>
+      <c r="H1563" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1563" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1563" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="K1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1563" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1563" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="R1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1563" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8FDDFF-4515-4D6E-AC4F-1CF25571028D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECAE0A0-4B84-45F6-8B5F-FE2FBDDABADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92872,7 +92872,7 @@
         <v>2</v>
       </c>
       <c r="H1502" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1502" s="1">
         <v>1</v>
@@ -92931,7 +92931,7 @@
         <v>3</v>
       </c>
       <c r="H1503" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1503" s="1">
         <v>1</v>
@@ -92990,7 +92990,7 @@
         <v>4</v>
       </c>
       <c r="H1504" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1504" s="1">
         <v>2</v>
@@ -93049,7 +93049,7 @@
         <v>5</v>
       </c>
       <c r="H1505" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1505" s="1">
         <v>2</v>
@@ -93108,7 +93108,7 @@
         <v>6</v>
       </c>
       <c r="H1506" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1506" s="1">
         <v>2</v>
@@ -93167,7 +93167,7 @@
         <v>7</v>
       </c>
       <c r="H1507" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1507" s="1">
         <v>2</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECAE0A0-4B84-45F6-8B5F-FE2FBDDABADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F1002A-96B9-4430-B4FD-0C8A61623F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3713" uniqueCount="1558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3815" uniqueCount="1584">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -4392,18 +4392,12 @@
     <t>121105,121105</t>
   </si>
   <si>
-    <t>121105,121101,121101,121101,121101</t>
-  </si>
-  <si>
     <t>121105,121105,121105</t>
   </si>
   <si>
     <t>121113</t>
   </si>
   <si>
-    <t>121102,121102</t>
-  </si>
-  <si>
     <t>1210101</t>
   </si>
   <si>
@@ -4428,375 +4422,171 @@
     <t>1210202</t>
   </si>
   <si>
-    <t>0,4500,1200</t>
-  </si>
-  <si>
     <t>1210203</t>
   </si>
   <si>
-    <t>90,4500,1200</t>
-  </si>
-  <si>
     <t>1210204</t>
   </si>
   <si>
-    <t>270,4500,1200</t>
-  </si>
-  <si>
     <t>1210301</t>
   </si>
   <si>
-    <t>45,4500,1200</t>
-  </si>
-  <si>
     <t>1210302</t>
   </si>
   <si>
-    <t>135,4500,1200</t>
-  </si>
-  <si>
     <t>1210303</t>
   </si>
   <si>
-    <t>225,4500,1200</t>
-  </si>
-  <si>
     <t>1210304</t>
   </si>
   <si>
-    <t>315,4500,1200</t>
-  </si>
-  <si>
     <t>1210401</t>
   </si>
   <si>
-    <t>30,4500,1200</t>
-  </si>
-  <si>
     <t>1210402</t>
   </si>
   <si>
-    <t>121101,121101,121101,121101,121104</t>
-  </si>
-  <si>
-    <t>102,5500,1200</t>
-  </si>
-  <si>
     <t>1210403</t>
   </si>
   <si>
-    <t>174,4500,1200</t>
-  </si>
-  <si>
     <t>1210404</t>
   </si>
   <si>
-    <t>246,4500,1200</t>
-  </si>
-  <si>
     <t>1210405</t>
   </si>
   <si>
-    <t>318,4500,1200</t>
-  </si>
-  <si>
     <t>1210501</t>
   </si>
   <si>
     <t>121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>70,4500,1200</t>
-  </si>
-  <si>
     <t>1210502</t>
   </si>
   <si>
     <t>121101,121101,121101,121101,121101,121104</t>
   </si>
   <si>
-    <t>142,5500,1200</t>
-  </si>
-  <si>
     <t>1210503</t>
   </si>
   <si>
-    <t>121105,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>214,4500,1200</t>
-  </si>
-  <si>
     <t>1210504</t>
   </si>
   <si>
     <t>1210505</t>
   </si>
   <si>
-    <t>121105,121101,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>286,4500,1200</t>
-  </si>
-  <si>
     <t>1210506</t>
   </si>
   <si>
     <t>121105,121105,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>358,4500,1200</t>
-  </si>
-  <si>
     <t>1210601</t>
   </si>
   <si>
-    <t>50,4500,1200</t>
-  </si>
-  <si>
     <t>1210602</t>
   </si>
   <si>
-    <t>121105,121105,121101,121101,121101,121101,121104</t>
-  </si>
-  <si>
-    <t>110,5500,1200</t>
-  </si>
-  <si>
     <t>1210603</t>
   </si>
   <si>
-    <t>170,4500,1200</t>
-  </si>
-  <si>
     <t>1210604</t>
   </si>
   <si>
     <t>1210605</t>
   </si>
   <si>
-    <t>121105,121105,121101,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>230,4500,1200</t>
-  </si>
-  <si>
     <t>1210606</t>
   </si>
   <si>
-    <t>121105,121105,121105,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>290,4500,1200</t>
-  </si>
-  <si>
     <t>1210607</t>
   </si>
   <si>
-    <t>350,4500,1200</t>
-  </si>
-  <si>
     <t>1210701</t>
   </si>
   <si>
-    <t>204,4500,1200</t>
-  </si>
-  <si>
     <t>1210702</t>
   </si>
   <si>
-    <t>121105,121105,121105,121101,121101,121101,121104,121104</t>
-  </si>
-  <si>
-    <t>256,5500,1200</t>
-  </si>
-  <si>
     <t>1210703</t>
   </si>
   <si>
-    <t>308,4500,1200</t>
-  </si>
-  <si>
     <t>1210704</t>
   </si>
   <si>
-    <t>121102,121105,121105,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
     <t>1210705</t>
   </si>
   <si>
-    <t>121105,121105,121105,121105,121105,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>52,4500,1200</t>
-  </si>
-  <si>
     <t>1210706</t>
   </si>
   <si>
-    <t>104,4500,1200</t>
-  </si>
-  <si>
     <t>1210707</t>
   </si>
   <si>
-    <t>156,4500,1200</t>
-  </si>
-  <si>
     <t>1210801</t>
   </si>
   <si>
-    <t>25,4500,1200</t>
-  </si>
-  <si>
     <t>1210802</t>
   </si>
   <si>
-    <t>121102,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
     <t>1210803</t>
   </si>
   <si>
-    <t>121105,121105,121105,121105,121101,121101,121101,121101,121104,121104</t>
-  </si>
-  <si>
-    <t>115,5500,1200</t>
-  </si>
-  <si>
     <t>1210804</t>
   </si>
   <si>
-    <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>160,4500,1200</t>
-  </si>
-  <si>
     <t>1210805</t>
   </si>
   <si>
-    <t>121102,121105,121105,121105,121105,121105,121105,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>205,4500,1200</t>
-  </si>
-  <si>
     <t>1210806</t>
   </si>
   <si>
-    <t>121105,121105,121105,121105,121105,121105,121105,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>250,4500,1200</t>
-  </si>
-  <si>
     <t>1210807</t>
   </si>
   <si>
-    <t>295,4500,1200</t>
-  </si>
-  <si>
     <t>1210808</t>
   </si>
   <si>
-    <t>121102,121105,121105,121105,121105,121105,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>340,4500,1200</t>
-  </si>
-  <si>
     <t>1210901</t>
   </si>
   <si>
-    <t>121105,121105,121105,121105,121105,121105,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>15,4500,1200</t>
-  </si>
-  <si>
     <t>1210902</t>
   </si>
   <si>
-    <t>121102,121102,121101,121101,121101,121101,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>55,4500,1200</t>
-  </si>
-  <si>
     <t>1210903</t>
   </si>
   <si>
-    <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>95,4500,1200</t>
-  </si>
-  <si>
     <t>1210904</t>
   </si>
   <si>
-    <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121104,121104</t>
-  </si>
-  <si>
-    <t>135,5500,1200</t>
-  </si>
-  <si>
     <t>1210905</t>
   </si>
   <si>
-    <t>121102,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>175,4500,1200</t>
-  </si>
-  <si>
     <t>1210906</t>
   </si>
   <si>
-    <t>215,4500,1200</t>
-  </si>
-  <si>
     <t>1210907</t>
   </si>
   <si>
-    <t>255,4500,1200</t>
-  </si>
-  <si>
     <t>1210908</t>
   </si>
   <si>
     <t>1210909</t>
   </si>
   <si>
-    <t>121102,121102,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
-  </si>
-  <si>
-    <t>335,4500,1200</t>
-  </si>
-  <si>
     <t>1211001</t>
   </si>
   <si>
     <t>1211002</t>
   </si>
   <si>
-    <t>121105,121105,121105,121105,121105,121105</t>
-  </si>
-  <si>
     <t>1211003</t>
   </si>
   <si>
     <t>1211004</t>
   </si>
   <si>
-    <t>121104,121104,121105,121105</t>
-  </si>
-  <si>
-    <t>45,5500,1200</t>
-  </si>
-  <si>
     <t>1211005</t>
   </si>
   <si>
@@ -4806,19 +4596,307 @@
     <t>1211007</t>
   </si>
   <si>
-    <t>180,4500,1200</t>
-  </si>
-  <si>
     <t>1211008</t>
   </si>
   <si>
-    <t>225,5500,1200</t>
-  </si>
-  <si>
     <t>1211009</t>
   </si>
   <si>
     <t>1211010</t>
+  </si>
+  <si>
+    <t>0,4500,1800</t>
+  </si>
+  <si>
+    <t>90,4500,1800</t>
+  </si>
+  <si>
+    <t>270,4500,1800</t>
+  </si>
+  <si>
+    <t>45,4500,1800</t>
+  </si>
+  <si>
+    <t>135,4500,1800</t>
+  </si>
+  <si>
+    <t>225,4500,1800</t>
+  </si>
+  <si>
+    <t>315,4500,1800</t>
+  </si>
+  <si>
+    <t>30,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121101,121101,121101,121101,121104</t>
+  </si>
+  <si>
+    <t>102,5500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>174,4500,1800</t>
+  </si>
+  <si>
+    <t>246,4500,1800</t>
+  </si>
+  <si>
+    <t>318,4500,1800</t>
+  </si>
+  <si>
+    <t>121101,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>70,4500,1800</t>
+  </si>
+  <si>
+    <t>142,5500,1800</t>
+  </si>
+  <si>
+    <t>214,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>286,4500,1800</t>
+  </si>
+  <si>
+    <t>358,4500,1800</t>
+  </si>
+  <si>
+    <t>50,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121101,121101,121101,121101,121104,121101,121104</t>
+  </si>
+  <si>
+    <t>110,5500,1800</t>
+  </si>
+  <si>
+    <t>170,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>230,4500,1800</t>
+  </si>
+  <si>
+    <t>290,4500,1800</t>
+  </si>
+  <si>
+    <t>350,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>204,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121101,121101,121101,121104,121104,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>256,5500,1800</t>
+  </si>
+  <si>
+    <t>308,4500,1800</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>52,4500,1800</t>
+  </si>
+  <si>
+    <t>104,4500,1800</t>
+  </si>
+  <si>
+    <t>156,4500,1800</t>
+  </si>
+  <si>
+    <t>25,4500,1800</t>
+  </si>
+  <si>
+    <t>205,4500,1800</t>
+  </si>
+  <si>
+    <t>250,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121101,121101,121101,121101,121104,121104,121101,121101</t>
+  </si>
+  <si>
+    <t>115,5500,1800</t>
+  </si>
+  <si>
+    <t>295,5500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>160,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>1210809</t>
+  </si>
+  <si>
+    <t>121105,121105,121101,121101,121101,121101,121105,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>1210810</t>
+  </si>
+  <si>
+    <t>1210811</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121105,121105,121105,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>1210812</t>
+  </si>
+  <si>
+    <t>1210813</t>
+  </si>
+  <si>
+    <t>295,4500,1800</t>
+  </si>
+  <si>
+    <t>1210814</t>
+  </si>
+  <si>
+    <t>115,4500,1800</t>
+  </si>
+  <si>
+    <t>1210815</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121105,121105,121105,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>340,4500,1800</t>
+  </si>
+  <si>
+    <t>1210816</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121105,121105,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>15,4500,1800</t>
+  </si>
+  <si>
+    <t>195,4500,1800</t>
+  </si>
+  <si>
+    <t>121102,121102,121101,121101,121101,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>55,4500,1800</t>
+  </si>
+  <si>
+    <t>235,4500,1800</t>
+  </si>
+  <si>
+    <t>95,4500,1800</t>
+  </si>
+  <si>
+    <t>275,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121104,121104,121101</t>
+  </si>
+  <si>
+    <t>135,5500,1800</t>
+  </si>
+  <si>
+    <t>315,5500,1800</t>
+  </si>
+  <si>
+    <t>121102,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>175,4500,1800</t>
+  </si>
+  <si>
+    <t>1210910</t>
+  </si>
+  <si>
+    <t>355,4500,1800</t>
+  </si>
+  <si>
+    <t>1210911</t>
+  </si>
+  <si>
+    <t>215,4500,1800</t>
+  </si>
+  <si>
+    <t>1210912</t>
+  </si>
+  <si>
+    <t>35,4500,1800</t>
+  </si>
+  <si>
+    <t>1210913</t>
+  </si>
+  <si>
+    <t>255,4500,1800</t>
+  </si>
+  <si>
+    <t>1210914</t>
+  </si>
+  <si>
+    <t>75,4500,1800</t>
+  </si>
+  <si>
+    <t>1210915</t>
+  </si>
+  <si>
+    <t>1210916</t>
+  </si>
+  <si>
+    <t>1210917</t>
+  </si>
+  <si>
+    <t>121102,121102,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>335,4500,1800</t>
+  </si>
+  <si>
+    <t>1210918</t>
+  </si>
+  <si>
+    <t>155,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121105,121105,121105,121105,121105,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>121104,121104,121105,121105,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>45,5500,1800</t>
+  </si>
+  <si>
+    <t>121102,121102,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>180,4500,1800</t>
+  </si>
+  <si>
+    <t>225,5500,1800</t>
   </si>
 </sst>
 </file>
@@ -5653,7 +5731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S1563"/>
+  <dimension ref="A1:S1580"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -92792,7 +92870,7 @@
     </row>
     <row r="1501" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1501" s="1" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B1501" s="1">
         <v>12</v>
@@ -92804,7 +92882,7 @@
         <v>1405</v>
       </c>
       <c r="E1501" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1501" s="1">
         <v>1</v>
@@ -92851,7 +92929,7 @@
     </row>
     <row r="1502" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1502" s="1" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B1502" s="1">
         <v>12</v>
@@ -92863,7 +92941,7 @@
         <v>1405</v>
       </c>
       <c r="E1502" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1502" s="1">
         <v>1</v>
@@ -92896,7 +92974,7 @@
         <v>0</v>
       </c>
       <c r="P1502" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="Q1502" s="1">
         <v>0</v>
@@ -92910,7 +92988,7 @@
     </row>
     <row r="1503" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1503" s="1" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B1503" s="1">
         <v>12</v>
@@ -92922,7 +93000,7 @@
         <v>1405</v>
       </c>
       <c r="E1503" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1503" s="1">
         <v>1</v>
@@ -92955,7 +93033,7 @@
         <v>0</v>
       </c>
       <c r="P1503" s="1" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="Q1503" s="1">
         <v>0</v>
@@ -92969,7 +93047,7 @@
     </row>
     <row r="1504" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1504" s="1" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B1504" s="1">
         <v>12</v>
@@ -92981,7 +93059,7 @@
         <v>1405</v>
       </c>
       <c r="E1504" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1504" s="1">
         <v>1</v>
@@ -93014,7 +93092,7 @@
         <v>0</v>
       </c>
       <c r="P1504" s="1" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="Q1504" s="1">
         <v>0</v>
@@ -93028,7 +93106,7 @@
     </row>
     <row r="1505" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1505" s="1" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="B1505" s="1">
         <v>12</v>
@@ -93040,7 +93118,7 @@
         <v>1405</v>
       </c>
       <c r="E1505" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1505" s="1">
         <v>1</v>
@@ -93076,7 +93154,7 @@
         <v>0</v>
       </c>
       <c r="Q1505" s="1" t="s">
-        <v>1427</v>
+        <v>1486</v>
       </c>
       <c r="R1505" s="1">
         <v>0</v>
@@ -93087,7 +93165,7 @@
     </row>
     <row r="1506" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1506" s="1" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="B1506" s="1">
         <v>12</v>
@@ -93099,7 +93177,7 @@
         <v>1405</v>
       </c>
       <c r="E1506" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1506" s="1">
         <v>1</v>
@@ -93135,7 +93213,7 @@
         <v>0</v>
       </c>
       <c r="Q1506" s="1" t="s">
-        <v>1429</v>
+        <v>1487</v>
       </c>
       <c r="R1506" s="1">
         <v>0</v>
@@ -93146,7 +93224,7 @@
     </row>
     <row r="1507" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1507" s="1" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="B1507" s="1">
         <v>12</v>
@@ -93158,7 +93236,7 @@
         <v>1405</v>
       </c>
       <c r="E1507" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1507" s="1">
         <v>1</v>
@@ -93194,7 +93272,7 @@
         <v>0</v>
       </c>
       <c r="Q1507" s="1" t="s">
-        <v>1431</v>
+        <v>1488</v>
       </c>
       <c r="R1507" s="1">
         <v>0</v>
@@ -93205,7 +93283,7 @@
     </row>
     <row r="1508" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1508" s="1" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="B1508" s="1">
         <v>12</v>
@@ -93217,7 +93295,7 @@
         <v>1405</v>
       </c>
       <c r="E1508" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1508" s="1">
         <v>1</v>
@@ -93253,7 +93331,7 @@
         <v>0</v>
       </c>
       <c r="Q1508" s="1" t="s">
-        <v>1433</v>
+        <v>1489</v>
       </c>
       <c r="R1508" s="1">
         <v>0</v>
@@ -93264,7 +93342,7 @@
     </row>
     <row r="1509" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1509" s="1" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="B1509" s="1">
         <v>12</v>
@@ -93276,7 +93354,7 @@
         <v>1405</v>
       </c>
       <c r="E1509" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1509" s="1">
         <v>1</v>
@@ -93312,7 +93390,7 @@
         <v>0</v>
       </c>
       <c r="Q1509" s="1" t="s">
-        <v>1435</v>
+        <v>1490</v>
       </c>
       <c r="R1509" s="1">
         <v>0</v>
@@ -93323,7 +93401,7 @@
     </row>
     <row r="1510" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1510" s="1" t="s">
-        <v>1436</v>
+        <v>1429</v>
       </c>
       <c r="B1510" s="1">
         <v>12</v>
@@ -93335,7 +93413,7 @@
         <v>1405</v>
       </c>
       <c r="E1510" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1510" s="1">
         <v>1</v>
@@ -93371,7 +93449,7 @@
         <v>0</v>
       </c>
       <c r="Q1510" s="1" t="s">
-        <v>1437</v>
+        <v>1491</v>
       </c>
       <c r="R1510" s="1">
         <v>0</v>
@@ -93382,7 +93460,7 @@
     </row>
     <row r="1511" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1511" s="1" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
       <c r="B1511" s="1">
         <v>12</v>
@@ -93394,7 +93472,7 @@
         <v>1405</v>
       </c>
       <c r="E1511" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1511" s="1">
         <v>1</v>
@@ -93430,7 +93508,7 @@
         <v>0</v>
       </c>
       <c r="Q1511" s="1" t="s">
-        <v>1439</v>
+        <v>1492</v>
       </c>
       <c r="R1511" s="1">
         <v>0</v>
@@ -93441,7 +93519,7 @@
     </row>
     <row r="1512" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1512" s="1" t="s">
-        <v>1440</v>
+        <v>1431</v>
       </c>
       <c r="B1512" s="1">
         <v>12</v>
@@ -93453,7 +93531,7 @@
         <v>1405</v>
       </c>
       <c r="E1512" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1512" s="1">
         <v>1</v>
@@ -93489,7 +93567,7 @@
         <v>0</v>
       </c>
       <c r="Q1512" s="1" t="s">
-        <v>1441</v>
+        <v>1493</v>
       </c>
       <c r="R1512" s="1">
         <v>0</v>
@@ -93500,7 +93578,7 @@
     </row>
     <row r="1513" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1513" s="1" t="s">
-        <v>1442</v>
+        <v>1432</v>
       </c>
       <c r="B1513" s="1">
         <v>12</v>
@@ -93512,7 +93590,7 @@
         <v>1405</v>
       </c>
       <c r="E1513" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1513" s="1">
         <v>1</v>
@@ -93527,7 +93605,7 @@
         <v>4</v>
       </c>
       <c r="J1513" s="2" t="s">
-        <v>1443</v>
+        <v>1494</v>
       </c>
       <c r="K1513" s="1">
         <v>0</v>
@@ -93548,7 +93626,7 @@
         <v>0</v>
       </c>
       <c r="Q1513" s="1" t="s">
-        <v>1444</v>
+        <v>1495</v>
       </c>
       <c r="R1513" s="1">
         <v>0</v>
@@ -93559,7 +93637,7 @@
     </row>
     <row r="1514" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1514" s="1" t="s">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="B1514" s="1">
         <v>12</v>
@@ -93571,7 +93649,7 @@
         <v>1405</v>
       </c>
       <c r="E1514" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1514" s="1">
         <v>1</v>
@@ -93586,7 +93664,7 @@
         <v>4</v>
       </c>
       <c r="J1514" s="2" t="s">
-        <v>1415</v>
+        <v>1496</v>
       </c>
       <c r="K1514" s="1">
         <v>0</v>
@@ -93607,7 +93685,7 @@
         <v>0</v>
       </c>
       <c r="Q1514" s="1" t="s">
-        <v>1446</v>
+        <v>1497</v>
       </c>
       <c r="R1514" s="1">
         <v>0</v>
@@ -93618,7 +93696,7 @@
     </row>
     <row r="1515" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1515" s="1" t="s">
-        <v>1447</v>
+        <v>1434</v>
       </c>
       <c r="B1515" s="1">
         <v>12</v>
@@ -93630,7 +93708,7 @@
         <v>1405</v>
       </c>
       <c r="E1515" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1515" s="1">
         <v>1</v>
@@ -93645,7 +93723,7 @@
         <v>4</v>
       </c>
       <c r="J1515" s="2" t="s">
-        <v>1415</v>
+        <v>1496</v>
       </c>
       <c r="K1515" s="1">
         <v>0</v>
@@ -93666,7 +93744,7 @@
         <v>0</v>
       </c>
       <c r="Q1515" s="1" t="s">
-        <v>1448</v>
+        <v>1498</v>
       </c>
       <c r="R1515" s="1">
         <v>0</v>
@@ -93677,7 +93755,7 @@
     </row>
     <row r="1516" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1516" s="1" t="s">
-        <v>1449</v>
+        <v>1435</v>
       </c>
       <c r="B1516" s="1">
         <v>12</v>
@@ -93689,7 +93767,7 @@
         <v>1405</v>
       </c>
       <c r="E1516" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1516" s="1">
         <v>1</v>
@@ -93704,7 +93782,7 @@
         <v>4</v>
       </c>
       <c r="J1516" s="2" t="s">
-        <v>1415</v>
+        <v>1496</v>
       </c>
       <c r="K1516" s="1">
         <v>0</v>
@@ -93725,7 +93803,7 @@
         <v>0</v>
       </c>
       <c r="Q1516" s="1" t="s">
-        <v>1450</v>
+        <v>1499</v>
       </c>
       <c r="R1516" s="1">
         <v>0</v>
@@ -93736,7 +93814,7 @@
     </row>
     <row r="1517" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1517" s="1" t="s">
-        <v>1451</v>
+        <v>1436</v>
       </c>
       <c r="B1517" s="1">
         <v>12</v>
@@ -93748,7 +93826,7 @@
         <v>1405</v>
       </c>
       <c r="E1517" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1517" s="1">
         <v>1</v>
@@ -93763,7 +93841,7 @@
         <v>5</v>
       </c>
       <c r="J1517" s="2" t="s">
-        <v>1452</v>
+        <v>1500</v>
       </c>
       <c r="K1517" s="1">
         <v>0</v>
@@ -93784,7 +93862,7 @@
         <v>0</v>
       </c>
       <c r="Q1517" s="1" t="s">
-        <v>1453</v>
+        <v>1501</v>
       </c>
       <c r="R1517" s="1">
         <v>0</v>
@@ -93795,7 +93873,7 @@
     </row>
     <row r="1518" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1518" s="1" t="s">
-        <v>1454</v>
+        <v>1438</v>
       </c>
       <c r="B1518" s="1">
         <v>12</v>
@@ -93807,7 +93885,7 @@
         <v>1405</v>
       </c>
       <c r="E1518" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1518" s="1">
         <v>1</v>
@@ -93822,7 +93900,7 @@
         <v>5</v>
       </c>
       <c r="J1518" s="2" t="s">
-        <v>1455</v>
+        <v>1439</v>
       </c>
       <c r="K1518" s="1">
         <v>0</v>
@@ -93843,7 +93921,7 @@
         <v>0</v>
       </c>
       <c r="Q1518" s="1" t="s">
-        <v>1456</v>
+        <v>1502</v>
       </c>
       <c r="R1518" s="1">
         <v>0</v>
@@ -93854,7 +93932,7 @@
     </row>
     <row r="1519" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1519" s="1" t="s">
-        <v>1457</v>
+        <v>1440</v>
       </c>
       <c r="B1519" s="1">
         <v>12</v>
@@ -93866,7 +93944,7 @@
         <v>1405</v>
       </c>
       <c r="E1519" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1519" s="1">
         <v>1</v>
@@ -93881,7 +93959,7 @@
         <v>5</v>
       </c>
       <c r="J1519" s="2" t="s">
-        <v>1458</v>
+        <v>1444</v>
       </c>
       <c r="K1519" s="1">
         <v>0</v>
@@ -93902,7 +93980,7 @@
         <v>0</v>
       </c>
       <c r="Q1519" s="1" t="s">
-        <v>1459</v>
+        <v>1503</v>
       </c>
       <c r="R1519" s="1">
         <v>0</v>
@@ -93913,7 +93991,7 @@
     </row>
     <row r="1520" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1520" s="1" t="s">
-        <v>1460</v>
+        <v>1441</v>
       </c>
       <c r="B1520" s="1">
         <v>12</v>
@@ -93925,7 +94003,7 @@
         <v>1405</v>
       </c>
       <c r="E1520" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1520" s="1">
         <v>1</v>
@@ -93972,7 +94050,7 @@
     </row>
     <row r="1521" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1521" s="1" t="s">
-        <v>1461</v>
+        <v>1442</v>
       </c>
       <c r="B1521" s="1">
         <v>12</v>
@@ -93984,7 +94062,7 @@
         <v>1405</v>
       </c>
       <c r="E1521" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1521" s="1">
         <v>1</v>
@@ -93999,7 +94077,7 @@
         <v>5</v>
       </c>
       <c r="J1521" s="2" t="s">
-        <v>1462</v>
+        <v>1504</v>
       </c>
       <c r="K1521" s="1">
         <v>0</v>
@@ -94020,7 +94098,7 @@
         <v>0</v>
       </c>
       <c r="Q1521" s="1" t="s">
-        <v>1463</v>
+        <v>1505</v>
       </c>
       <c r="R1521" s="1">
         <v>0</v>
@@ -94031,7 +94109,7 @@
     </row>
     <row r="1522" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1522" s="1" t="s">
-        <v>1464</v>
+        <v>1443</v>
       </c>
       <c r="B1522" s="1">
         <v>12</v>
@@ -94043,7 +94121,7 @@
         <v>1405</v>
       </c>
       <c r="E1522" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1522" s="1">
         <v>1</v>
@@ -94058,7 +94136,7 @@
         <v>5</v>
       </c>
       <c r="J1522" s="2" t="s">
-        <v>1465</v>
+        <v>1504</v>
       </c>
       <c r="K1522" s="1">
         <v>0</v>
@@ -94079,7 +94157,7 @@
         <v>0</v>
       </c>
       <c r="Q1522" s="1" t="s">
-        <v>1466</v>
+        <v>1506</v>
       </c>
       <c r="R1522" s="1">
         <v>0</v>
@@ -94090,7 +94168,7 @@
     </row>
     <row r="1523" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1523" s="1" t="s">
-        <v>1467</v>
+        <v>1445</v>
       </c>
       <c r="B1523" s="1">
         <v>12</v>
@@ -94102,7 +94180,7 @@
         <v>1405</v>
       </c>
       <c r="E1523" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1523" s="1">
         <v>1</v>
@@ -94111,13 +94189,13 @@
         <v>23</v>
       </c>
       <c r="H1523" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1523" s="1">
         <v>6</v>
       </c>
       <c r="J1523" s="2" t="s">
-        <v>1465</v>
+        <v>1504</v>
       </c>
       <c r="K1523" s="1">
         <v>0</v>
@@ -94138,7 +94216,7 @@
         <v>0</v>
       </c>
       <c r="Q1523" s="1" t="s">
-        <v>1468</v>
+        <v>1507</v>
       </c>
       <c r="R1523" s="1">
         <v>0</v>
@@ -94149,7 +94227,7 @@
     </row>
     <row r="1524" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1524" s="1" t="s">
-        <v>1469</v>
+        <v>1446</v>
       </c>
       <c r="B1524" s="1">
         <v>12</v>
@@ -94161,7 +94239,7 @@
         <v>1405</v>
       </c>
       <c r="E1524" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1524" s="1">
         <v>1</v>
@@ -94170,13 +94248,13 @@
         <v>24</v>
       </c>
       <c r="H1524" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1524" s="1">
         <v>6</v>
       </c>
       <c r="J1524" s="2" t="s">
-        <v>1470</v>
+        <v>1508</v>
       </c>
       <c r="K1524" s="1">
         <v>0</v>
@@ -94197,7 +94275,7 @@
         <v>0</v>
       </c>
       <c r="Q1524" s="1" t="s">
-        <v>1471</v>
+        <v>1509</v>
       </c>
       <c r="R1524" s="1">
         <v>0</v>
@@ -94208,7 +94286,7 @@
     </row>
     <row r="1525" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1525" s="1" t="s">
-        <v>1472</v>
+        <v>1447</v>
       </c>
       <c r="B1525" s="1">
         <v>12</v>
@@ -94220,7 +94298,7 @@
         <v>1405</v>
       </c>
       <c r="E1525" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1525" s="1">
         <v>1</v>
@@ -94229,13 +94307,13 @@
         <v>25</v>
       </c>
       <c r="H1525" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1525" s="1">
         <v>6</v>
       </c>
       <c r="J1525" s="2" t="s">
-        <v>1465</v>
+        <v>1504</v>
       </c>
       <c r="K1525" s="1">
         <v>0</v>
@@ -94256,7 +94334,7 @@
         <v>0</v>
       </c>
       <c r="Q1525" s="1" t="s">
-        <v>1473</v>
+        <v>1510</v>
       </c>
       <c r="R1525" s="1">
         <v>0</v>
@@ -94267,7 +94345,7 @@
     </row>
     <row r="1526" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1526" s="1" t="s">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="B1526" s="1">
         <v>12</v>
@@ -94279,7 +94357,7 @@
         <v>1405</v>
       </c>
       <c r="E1526" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1526" s="1">
         <v>1</v>
@@ -94294,7 +94372,7 @@
         <v>6</v>
       </c>
       <c r="J1526" s="2" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="K1526" s="1">
         <v>0</v>
@@ -94326,7 +94404,7 @@
     </row>
     <row r="1527" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1527" s="1" t="s">
-        <v>1475</v>
+        <v>1449</v>
       </c>
       <c r="B1527" s="1">
         <v>12</v>
@@ -94338,7 +94416,7 @@
         <v>1405</v>
       </c>
       <c r="E1527" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1527" s="1">
         <v>1</v>
@@ -94347,13 +94425,13 @@
         <v>27</v>
       </c>
       <c r="H1527" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1527" s="1">
         <v>6</v>
       </c>
       <c r="J1527" s="2" t="s">
-        <v>1476</v>
+        <v>1511</v>
       </c>
       <c r="K1527" s="1">
         <v>0</v>
@@ -94374,7 +94452,7 @@
         <v>0</v>
       </c>
       <c r="Q1527" s="1" t="s">
-        <v>1477</v>
+        <v>1512</v>
       </c>
       <c r="R1527" s="1">
         <v>0</v>
@@ -94385,7 +94463,7 @@
     </row>
     <row r="1528" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1528" s="1" t="s">
-        <v>1478</v>
+        <v>1450</v>
       </c>
       <c r="B1528" s="1">
         <v>12</v>
@@ -94397,7 +94475,7 @@
         <v>1405</v>
       </c>
       <c r="E1528" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1528" s="1">
         <v>1</v>
@@ -94406,13 +94484,13 @@
         <v>28</v>
       </c>
       <c r="H1528" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1528" s="1">
         <v>6</v>
       </c>
       <c r="J1528" s="2" t="s">
-        <v>1479</v>
+        <v>1511</v>
       </c>
       <c r="K1528" s="1">
         <v>0</v>
@@ -94433,7 +94511,7 @@
         <v>0</v>
       </c>
       <c r="Q1528" s="1" t="s">
-        <v>1480</v>
+        <v>1513</v>
       </c>
       <c r="R1528" s="1">
         <v>0</v>
@@ -94444,7 +94522,7 @@
     </row>
     <row r="1529" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1529" s="1" t="s">
-        <v>1481</v>
+        <v>1451</v>
       </c>
       <c r="B1529" s="1">
         <v>12</v>
@@ -94456,7 +94534,7 @@
         <v>1405</v>
       </c>
       <c r="E1529" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1529" s="1">
         <v>1</v>
@@ -94465,13 +94543,13 @@
         <v>29</v>
       </c>
       <c r="H1529" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1529" s="1">
         <v>6</v>
       </c>
       <c r="J1529" s="2" t="s">
-        <v>1479</v>
+        <v>1511</v>
       </c>
       <c r="K1529" s="1">
         <v>0</v>
@@ -94492,7 +94570,7 @@
         <v>0</v>
       </c>
       <c r="Q1529" s="1" t="s">
-        <v>1482</v>
+        <v>1514</v>
       </c>
       <c r="R1529" s="1">
         <v>0</v>
@@ -94503,7 +94581,7 @@
     </row>
     <row r="1530" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1530" s="1" t="s">
-        <v>1483</v>
+        <v>1452</v>
       </c>
       <c r="B1530" s="1">
         <v>12</v>
@@ -94515,7 +94593,7 @@
         <v>1405</v>
       </c>
       <c r="E1530" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1530" s="1">
         <v>1</v>
@@ -94524,13 +94602,13 @@
         <v>30</v>
       </c>
       <c r="H1530" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1530" s="1">
         <v>7</v>
       </c>
       <c r="J1530" s="2" t="s">
-        <v>1479</v>
+        <v>1515</v>
       </c>
       <c r="K1530" s="1">
         <v>0</v>
@@ -94551,7 +94629,7 @@
         <v>0</v>
       </c>
       <c r="Q1530" s="1" t="s">
-        <v>1484</v>
+        <v>1516</v>
       </c>
       <c r="R1530" s="1">
         <v>0</v>
@@ -94562,7 +94640,7 @@
     </row>
     <row r="1531" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1531" s="1" t="s">
-        <v>1485</v>
+        <v>1453</v>
       </c>
       <c r="B1531" s="1">
         <v>12</v>
@@ -94574,7 +94652,7 @@
         <v>1405</v>
       </c>
       <c r="E1531" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1531" s="1">
         <v>1</v>
@@ -94583,13 +94661,13 @@
         <v>31</v>
       </c>
       <c r="H1531" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1531" s="1">
         <v>7</v>
       </c>
       <c r="J1531" s="2" t="s">
-        <v>1486</v>
+        <v>1517</v>
       </c>
       <c r="K1531" s="1">
         <v>0</v>
@@ -94610,7 +94688,7 @@
         <v>0</v>
       </c>
       <c r="Q1531" s="1" t="s">
-        <v>1487</v>
+        <v>1518</v>
       </c>
       <c r="R1531" s="1">
         <v>0</v>
@@ -94621,7 +94699,7 @@
     </row>
     <row r="1532" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1532" s="1" t="s">
-        <v>1488</v>
+        <v>1454</v>
       </c>
       <c r="B1532" s="1">
         <v>12</v>
@@ -94633,7 +94711,7 @@
         <v>1405</v>
       </c>
       <c r="E1532" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1532" s="1">
         <v>1</v>
@@ -94642,13 +94720,13 @@
         <v>32</v>
       </c>
       <c r="H1532" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1532" s="1">
         <v>7</v>
       </c>
       <c r="J1532" s="2" t="s">
-        <v>1479</v>
+        <v>1515</v>
       </c>
       <c r="K1532" s="1">
         <v>0</v>
@@ -94669,7 +94747,7 @@
         <v>0</v>
       </c>
       <c r="Q1532" s="1" t="s">
-        <v>1489</v>
+        <v>1519</v>
       </c>
       <c r="R1532" s="1">
         <v>0</v>
@@ -94680,7 +94758,7 @@
     </row>
     <row r="1533" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1533" s="1" t="s">
-        <v>1490</v>
+        <v>1455</v>
       </c>
       <c r="B1533" s="1">
         <v>12</v>
@@ -94692,7 +94770,7 @@
         <v>1405</v>
       </c>
       <c r="E1533" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1533" s="1">
         <v>1</v>
@@ -94701,13 +94779,13 @@
         <v>33</v>
       </c>
       <c r="H1533" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1533" s="1">
         <v>7</v>
       </c>
       <c r="J1533" s="2" t="s">
-        <v>1491</v>
+        <v>1520</v>
       </c>
       <c r="K1533" s="1">
         <v>0</v>
@@ -94728,7 +94806,7 @@
         <v>0</v>
       </c>
       <c r="Q1533" s="1" t="s">
-        <v>1427</v>
+        <v>1486</v>
       </c>
       <c r="R1533" s="1">
         <v>0</v>
@@ -94739,7 +94817,7 @@
     </row>
     <row r="1534" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1534" s="1" t="s">
-        <v>1492</v>
+        <v>1456</v>
       </c>
       <c r="B1534" s="1">
         <v>12</v>
@@ -94751,7 +94829,7 @@
         <v>1405</v>
       </c>
       <c r="E1534" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1534" s="1">
         <v>1</v>
@@ -94760,13 +94838,13 @@
         <v>34</v>
       </c>
       <c r="H1534" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1534" s="1">
         <v>7</v>
       </c>
       <c r="J1534" s="2" t="s">
-        <v>1493</v>
+        <v>1521</v>
       </c>
       <c r="K1534" s="1">
         <v>0</v>
@@ -94787,7 +94865,7 @@
         <v>0</v>
       </c>
       <c r="Q1534" s="1" t="s">
-        <v>1494</v>
+        <v>1522</v>
       </c>
       <c r="R1534" s="1">
         <v>0</v>
@@ -94798,7 +94876,7 @@
     </row>
     <row r="1535" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1535" s="1" t="s">
-        <v>1495</v>
+        <v>1457</v>
       </c>
       <c r="B1535" s="1">
         <v>12</v>
@@ -94810,7 +94888,7 @@
         <v>1405</v>
       </c>
       <c r="E1535" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1535" s="1">
         <v>1</v>
@@ -94819,13 +94897,13 @@
         <v>35</v>
       </c>
       <c r="H1535" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1535" s="1">
         <v>7</v>
       </c>
       <c r="J1535" s="2" t="s">
-        <v>1493</v>
+        <v>1521</v>
       </c>
       <c r="K1535" s="1">
         <v>0</v>
@@ -94846,7 +94924,7 @@
         <v>0</v>
       </c>
       <c r="Q1535" s="1" t="s">
-        <v>1496</v>
+        <v>1523</v>
       </c>
       <c r="R1535" s="1">
         <v>0</v>
@@ -94857,7 +94935,7 @@
     </row>
     <row r="1536" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1536" s="1" t="s">
-        <v>1497</v>
+        <v>1458</v>
       </c>
       <c r="B1536" s="1">
         <v>12</v>
@@ -94869,7 +94947,7 @@
         <v>1405</v>
       </c>
       <c r="E1536" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1536" s="1">
         <v>1</v>
@@ -94878,13 +94956,13 @@
         <v>36</v>
       </c>
       <c r="H1536" s="1">
-        <v>1500</v>
+        <v>1350</v>
       </c>
       <c r="I1536" s="1">
         <v>7</v>
       </c>
       <c r="J1536" s="2" t="s">
-        <v>1493</v>
+        <v>1521</v>
       </c>
       <c r="K1536" s="1">
         <v>0</v>
@@ -94905,7 +94983,7 @@
         <v>0</v>
       </c>
       <c r="Q1536" s="1" t="s">
-        <v>1498</v>
+        <v>1524</v>
       </c>
       <c r="R1536" s="1">
         <v>0</v>
@@ -94916,7 +94994,7 @@
     </row>
     <row r="1537" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1537" s="1" t="s">
-        <v>1499</v>
+        <v>1459</v>
       </c>
       <c r="B1537" s="1">
         <v>12</v>
@@ -94928,7 +95006,7 @@
         <v>1405</v>
       </c>
       <c r="E1537" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1537" s="1">
         <v>1</v>
@@ -94937,13 +95015,13 @@
         <v>37</v>
       </c>
       <c r="H1537" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1537" s="1">
         <v>8</v>
       </c>
       <c r="J1537" s="2" t="s">
-        <v>1493</v>
+        <v>1521</v>
       </c>
       <c r="K1537" s="1">
         <v>0</v>
@@ -94964,7 +95042,7 @@
         <v>0</v>
       </c>
       <c r="Q1537" s="1" t="s">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="R1537" s="1">
         <v>0</v>
@@ -94975,7 +95053,7 @@
     </row>
     <row r="1538" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1538" s="1" t="s">
-        <v>1501</v>
+        <v>1460</v>
       </c>
       <c r="B1538" s="1">
         <v>12</v>
@@ -94987,7 +95065,7 @@
         <v>1405</v>
       </c>
       <c r="E1538" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1538" s="1">
         <v>1</v>
@@ -94996,13 +95074,13 @@
         <v>38</v>
       </c>
       <c r="H1538" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1538" s="1">
         <v>8</v>
       </c>
       <c r="J1538" s="2" t="s">
-        <v>1502</v>
+        <v>1437</v>
       </c>
       <c r="K1538" s="1">
         <v>0</v>
@@ -95023,7 +95101,7 @@
         <v>0</v>
       </c>
       <c r="Q1538" s="1" t="s">
-        <v>1453</v>
+        <v>1526</v>
       </c>
       <c r="R1538" s="1">
         <v>0</v>
@@ -95034,7 +95112,7 @@
     </row>
     <row r="1539" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1539" s="1" t="s">
-        <v>1503</v>
+        <v>1461</v>
       </c>
       <c r="B1539" s="1">
         <v>12</v>
@@ -95046,7 +95124,7 @@
         <v>1405</v>
       </c>
       <c r="E1539" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1539" s="1">
         <v>1</v>
@@ -95055,13 +95133,13 @@
         <v>39</v>
       </c>
       <c r="H1539" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1539" s="1">
         <v>8</v>
       </c>
       <c r="J1539" s="2" t="s">
-        <v>1504</v>
+        <v>1520</v>
       </c>
       <c r="K1539" s="1">
         <v>0</v>
@@ -95082,7 +95160,7 @@
         <v>0</v>
       </c>
       <c r="Q1539" s="1" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="R1539" s="1">
         <v>0</v>
@@ -95093,7 +95171,7 @@
     </row>
     <row r="1540" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1540" s="1" t="s">
-        <v>1506</v>
+        <v>1462</v>
       </c>
       <c r="B1540" s="1">
         <v>12</v>
@@ -95105,7 +95183,7 @@
         <v>1405</v>
       </c>
       <c r="E1540" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1540" s="1">
         <v>1</v>
@@ -95114,13 +95192,13 @@
         <v>40</v>
       </c>
       <c r="H1540" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1540" s="1">
         <v>8</v>
       </c>
       <c r="J1540" s="2" t="s">
-        <v>1507</v>
+        <v>1437</v>
       </c>
       <c r="K1540" s="1">
         <v>0</v>
@@ -95141,7 +95219,7 @@
         <v>0</v>
       </c>
       <c r="Q1540" s="1" t="s">
-        <v>1508</v>
+        <v>1527</v>
       </c>
       <c r="R1540" s="1">
         <v>0</v>
@@ -95152,7 +95230,7 @@
     </row>
     <row r="1541" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1541" s="1" t="s">
-        <v>1509</v>
+        <v>1463</v>
       </c>
       <c r="B1541" s="1">
         <v>12</v>
@@ -95164,7 +95242,7 @@
         <v>1405</v>
       </c>
       <c r="E1541" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1541" s="1">
         <v>1</v>
@@ -95173,13 +95251,13 @@
         <v>41</v>
       </c>
       <c r="H1541" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1541" s="1">
         <v>8</v>
       </c>
       <c r="J1541" s="2" t="s">
-        <v>1510</v>
+        <v>1528</v>
       </c>
       <c r="K1541" s="1">
         <v>0</v>
@@ -95200,7 +95278,7 @@
         <v>0</v>
       </c>
       <c r="Q1541" s="1" t="s">
-        <v>1511</v>
+        <v>1529</v>
       </c>
       <c r="R1541" s="1">
         <v>0</v>
@@ -95211,7 +95289,7 @@
     </row>
     <row r="1542" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1542" s="1" t="s">
-        <v>1512</v>
+        <v>1464</v>
       </c>
       <c r="B1542" s="1">
         <v>12</v>
@@ -95223,7 +95301,7 @@
         <v>1405</v>
       </c>
       <c r="E1542" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1542" s="1">
         <v>1</v>
@@ -95232,13 +95310,13 @@
         <v>42</v>
       </c>
       <c r="H1542" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1542" s="1">
         <v>8</v>
       </c>
       <c r="J1542" s="2" t="s">
-        <v>1513</v>
+        <v>1437</v>
       </c>
       <c r="K1542" s="1">
         <v>0</v>
@@ -95259,7 +95337,7 @@
         <v>0</v>
       </c>
       <c r="Q1542" s="1" t="s">
-        <v>1514</v>
+        <v>1530</v>
       </c>
       <c r="R1542" s="1">
         <v>0</v>
@@ -95270,7 +95348,7 @@
     </row>
     <row r="1543" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1543" s="1" t="s">
-        <v>1515</v>
+        <v>1465</v>
       </c>
       <c r="B1543" s="1">
         <v>12</v>
@@ -95282,7 +95360,7 @@
         <v>1405</v>
       </c>
       <c r="E1543" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1543" s="1">
         <v>1</v>
@@ -95291,13 +95369,13 @@
         <v>43</v>
       </c>
       <c r="H1543" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1543" s="1">
         <v>8</v>
       </c>
       <c r="J1543" s="2" t="s">
-        <v>1513</v>
+        <v>1531</v>
       </c>
       <c r="K1543" s="1">
         <v>0</v>
@@ -95318,7 +95396,7 @@
         <v>0</v>
       </c>
       <c r="Q1543" s="1" t="s">
-        <v>1516</v>
+        <v>1532</v>
       </c>
       <c r="R1543" s="1">
         <v>0</v>
@@ -95329,7 +95407,7 @@
     </row>
     <row r="1544" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1544" s="1" t="s">
-        <v>1517</v>
+        <v>1466</v>
       </c>
       <c r="B1544" s="1">
         <v>12</v>
@@ -95341,7 +95419,7 @@
         <v>1405</v>
       </c>
       <c r="E1544" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1544" s="1">
         <v>1</v>
@@ -95350,13 +95428,13 @@
         <v>44</v>
       </c>
       <c r="H1544" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1544" s="1">
         <v>8</v>
       </c>
       <c r="J1544" s="2" t="s">
-        <v>1518</v>
+        <v>1533</v>
       </c>
       <c r="K1544" s="1">
         <v>0</v>
@@ -95377,7 +95455,7 @@
         <v>0</v>
       </c>
       <c r="Q1544" s="1" t="s">
-        <v>1519</v>
+        <v>1526</v>
       </c>
       <c r="R1544" s="1">
         <v>0</v>
@@ -95388,7 +95466,7 @@
     </row>
     <row r="1545" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1545" s="1" t="s">
-        <v>1520</v>
+        <v>1534</v>
       </c>
       <c r="B1545" s="1">
         <v>12</v>
@@ -95400,7 +95478,7 @@
         <v>1405</v>
       </c>
       <c r="E1545" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1545" s="1">
         <v>1</v>
@@ -95409,13 +95487,13 @@
         <v>45</v>
       </c>
       <c r="H1545" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1545" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1545" s="2" t="s">
-        <v>1521</v>
+        <v>1535</v>
       </c>
       <c r="K1545" s="1">
         <v>0</v>
@@ -95436,7 +95514,7 @@
         <v>0</v>
       </c>
       <c r="Q1545" s="1" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="R1545" s="1">
         <v>0</v>
@@ -95447,7 +95525,7 @@
     </row>
     <row r="1546" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1546" s="1" t="s">
-        <v>1523</v>
+        <v>1536</v>
       </c>
       <c r="B1546" s="1">
         <v>12</v>
@@ -95459,7 +95537,7 @@
         <v>1405</v>
       </c>
       <c r="E1546" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1546" s="1">
         <v>1</v>
@@ -95468,13 +95546,13 @@
         <v>46</v>
       </c>
       <c r="H1546" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1546" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1546" s="2" t="s">
-        <v>1524</v>
+        <v>1437</v>
       </c>
       <c r="K1546" s="1">
         <v>0</v>
@@ -95495,7 +95573,7 @@
         <v>0</v>
       </c>
       <c r="Q1546" s="1" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="R1546" s="1">
         <v>0</v>
@@ -95506,7 +95584,7 @@
     </row>
     <row r="1547" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1547" s="1" t="s">
-        <v>1526</v>
+        <v>1537</v>
       </c>
       <c r="B1547" s="1">
         <v>12</v>
@@ -95518,7 +95596,7 @@
         <v>1405</v>
       </c>
       <c r="E1547" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1547" s="1">
         <v>1</v>
@@ -95527,34 +95605,34 @@
         <v>47</v>
       </c>
       <c r="H1547" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1547" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1547" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="K1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1547" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1547" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1547" s="1" t="s">
         <v>1527</v>
-      </c>
-      <c r="K1547" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1547" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1547" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1547" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1547" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1547" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1547" s="1" t="s">
-        <v>1528</v>
       </c>
       <c r="R1547" s="1">
         <v>0</v>
@@ -95565,7 +95643,7 @@
     </row>
     <row r="1548" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1548" s="1" t="s">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="B1548" s="1">
         <v>12</v>
@@ -95577,7 +95655,7 @@
         <v>1405</v>
       </c>
       <c r="E1548" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1548" s="1">
         <v>1</v>
@@ -95586,13 +95664,13 @@
         <v>48</v>
       </c>
       <c r="H1548" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1548" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1548" s="2" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="K1548" s="1">
         <v>0</v>
@@ -95613,7 +95691,7 @@
         <v>0</v>
       </c>
       <c r="Q1548" s="1" t="s">
-        <v>1531</v>
+        <v>1501</v>
       </c>
       <c r="R1548" s="1">
         <v>0</v>
@@ -95624,7 +95702,7 @@
     </row>
     <row r="1549" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1549" s="1" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
       <c r="B1549" s="1">
         <v>12</v>
@@ -95636,7 +95714,7 @@
         <v>1405</v>
       </c>
       <c r="E1549" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1549" s="1">
         <v>1</v>
@@ -95645,13 +95723,13 @@
         <v>49</v>
       </c>
       <c r="H1549" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1549" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1549" s="2" t="s">
-        <v>1533</v>
+        <v>1538</v>
       </c>
       <c r="K1549" s="1">
         <v>0</v>
@@ -95672,7 +95750,7 @@
         <v>0</v>
       </c>
       <c r="Q1549" s="1" t="s">
-        <v>1534</v>
+        <v>1541</v>
       </c>
       <c r="R1549" s="1">
         <v>0</v>
@@ -95683,7 +95761,7 @@
     </row>
     <row r="1550" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1550" s="1" t="s">
-        <v>1535</v>
+        <v>1542</v>
       </c>
       <c r="B1550" s="1">
         <v>12</v>
@@ -95695,7 +95773,7 @@
         <v>1405</v>
       </c>
       <c r="E1550" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1550" s="1">
         <v>1</v>
@@ -95704,13 +95782,13 @@
         <v>50</v>
       </c>
       <c r="H1550" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1550" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1550" s="2" t="s">
-        <v>1527</v>
+        <v>1437</v>
       </c>
       <c r="K1550" s="1">
         <v>0</v>
@@ -95731,7 +95809,7 @@
         <v>0</v>
       </c>
       <c r="Q1550" s="1" t="s">
-        <v>1536</v>
+        <v>1543</v>
       </c>
       <c r="R1550" s="1">
         <v>0</v>
@@ -95742,7 +95820,7 @@
     </row>
     <row r="1551" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1551" s="1" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="B1551" s="1">
         <v>12</v>
@@ -95754,7 +95832,7 @@
         <v>1405</v>
       </c>
       <c r="E1551" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1551" s="1">
         <v>1</v>
@@ -95763,13 +95841,13 @@
         <v>51</v>
       </c>
       <c r="H1551" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1551" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1551" s="2" t="s">
-        <v>1533</v>
+        <v>1545</v>
       </c>
       <c r="K1551" s="1">
         <v>0</v>
@@ -95790,7 +95868,7 @@
         <v>0</v>
       </c>
       <c r="Q1551" s="1" t="s">
-        <v>1538</v>
+        <v>1546</v>
       </c>
       <c r="R1551" s="1">
         <v>0</v>
@@ -95801,7 +95879,7 @@
     </row>
     <row r="1552" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1552" s="1" t="s">
-        <v>1539</v>
+        <v>1547</v>
       </c>
       <c r="B1552" s="1">
         <v>12</v>
@@ -95813,7 +95891,7 @@
         <v>1405</v>
       </c>
       <c r="E1552" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1552" s="1">
         <v>1</v>
@@ -95822,13 +95900,13 @@
         <v>52</v>
       </c>
       <c r="H1552" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1552" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1552" s="2" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="K1552" s="1">
         <v>0</v>
@@ -95849,7 +95927,7 @@
         <v>0</v>
       </c>
       <c r="Q1552" s="1" t="s">
-        <v>1516</v>
+        <v>1532</v>
       </c>
       <c r="R1552" s="1">
         <v>0</v>
@@ -95860,7 +95938,7 @@
     </row>
     <row r="1553" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1553" s="1" t="s">
-        <v>1540</v>
+        <v>1467</v>
       </c>
       <c r="B1553" s="1">
         <v>12</v>
@@ -95872,7 +95950,7 @@
         <v>1405</v>
       </c>
       <c r="E1553" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1553" s="1">
         <v>1</v>
@@ -95881,13 +95959,13 @@
         <v>53</v>
       </c>
       <c r="H1553" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1553" s="1">
         <v>9</v>
       </c>
       <c r="J1553" s="2" t="s">
-        <v>1541</v>
+        <v>1548</v>
       </c>
       <c r="K1553" s="1">
         <v>0</v>
@@ -95908,7 +95986,7 @@
         <v>0</v>
       </c>
       <c r="Q1553" s="1" t="s">
-        <v>1542</v>
+        <v>1549</v>
       </c>
       <c r="R1553" s="1">
         <v>0</v>
@@ -95919,7 +95997,7 @@
     </row>
     <row r="1554" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1554" s="1" t="s">
-        <v>1543</v>
+        <v>1468</v>
       </c>
       <c r="B1554" s="1">
         <v>12</v>
@@ -95931,7 +96009,7 @@
         <v>1405</v>
       </c>
       <c r="E1554" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1554" s="1">
         <v>1</v>
@@ -95940,13 +96018,13 @@
         <v>54</v>
       </c>
       <c r="H1554" s="1">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="I1554" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1554" s="2" t="s">
-        <v>1417</v>
+        <v>1548</v>
       </c>
       <c r="K1554" s="1">
         <v>0</v>
@@ -95960,25 +96038,25 @@
       <c r="N1554" s="1">
         <v>0</v>
       </c>
-      <c r="O1554" s="1" t="s">
-        <v>153</v>
+      <c r="O1554" s="1">
+        <v>0</v>
       </c>
       <c r="P1554" s="1">
         <v>0</v>
       </c>
-      <c r="Q1554" s="1">
-        <v>0</v>
+      <c r="Q1554" s="1" t="s">
+        <v>1550</v>
       </c>
       <c r="R1554" s="1">
         <v>0</v>
       </c>
       <c r="S1554" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1555" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1555" s="1" t="s">
-        <v>1544</v>
+        <v>1469</v>
       </c>
       <c r="B1555" s="1">
         <v>12</v>
@@ -95990,7 +96068,7 @@
         <v>1405</v>
       </c>
       <c r="E1555" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1555" s="1">
         <v>1</v>
@@ -95999,13 +96077,13 @@
         <v>55</v>
       </c>
       <c r="H1555" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1555" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1555" s="2" t="s">
-        <v>1545</v>
+        <v>1551</v>
       </c>
       <c r="K1555" s="1">
         <v>0</v>
@@ -96022,11 +96100,11 @@
       <c r="O1555" s="1">
         <v>0</v>
       </c>
-      <c r="P1555" s="1" t="s">
-        <v>1410</v>
-      </c>
-      <c r="Q1555" s="1">
-        <v>0</v>
+      <c r="P1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1555" s="1" t="s">
+        <v>1552</v>
       </c>
       <c r="R1555" s="1">
         <v>0</v>
@@ -96037,7 +96115,7 @@
     </row>
     <row r="1556" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1556" s="1" t="s">
-        <v>1546</v>
+        <v>1470</v>
       </c>
       <c r="B1556" s="1">
         <v>12</v>
@@ -96049,7 +96127,7 @@
         <v>1405</v>
       </c>
       <c r="E1556" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1556" s="1">
         <v>1</v>
@@ -96058,13 +96136,13 @@
         <v>56</v>
       </c>
       <c r="H1556" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1556" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1556" s="2" t="s">
-        <v>1545</v>
+        <v>1531</v>
       </c>
       <c r="K1556" s="1">
         <v>0</v>
@@ -96085,7 +96163,7 @@
         <v>0</v>
       </c>
       <c r="Q1556" s="1" t="s">
-        <v>1427</v>
+        <v>1553</v>
       </c>
       <c r="R1556" s="1">
         <v>0</v>
@@ -96096,7 +96174,7 @@
     </row>
     <row r="1557" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1557" s="1" t="s">
-        <v>1547</v>
+        <v>1471</v>
       </c>
       <c r="B1557" s="1">
         <v>12</v>
@@ -96108,7 +96186,7 @@
         <v>1405</v>
       </c>
       <c r="E1557" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1557" s="1">
         <v>1</v>
@@ -96117,13 +96195,13 @@
         <v>57</v>
       </c>
       <c r="H1557" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1557" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1557" s="2" t="s">
-        <v>1548</v>
+        <v>1531</v>
       </c>
       <c r="K1557" s="1">
         <v>0</v>
@@ -96144,7 +96222,7 @@
         <v>0</v>
       </c>
       <c r="Q1557" s="1" t="s">
-        <v>1549</v>
+        <v>1554</v>
       </c>
       <c r="R1557" s="1">
         <v>0</v>
@@ -96155,7 +96233,7 @@
     </row>
     <row r="1558" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1558" s="1" t="s">
-        <v>1550</v>
+        <v>1472</v>
       </c>
       <c r="B1558" s="1">
         <v>12</v>
@@ -96167,7 +96245,7 @@
         <v>1405</v>
       </c>
       <c r="E1558" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1558" s="1">
         <v>1</v>
@@ -96176,13 +96254,13 @@
         <v>58</v>
       </c>
       <c r="H1558" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1558" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1558" s="2" t="s">
-        <v>1545</v>
+        <v>1531</v>
       </c>
       <c r="K1558" s="1">
         <v>0</v>
@@ -96203,7 +96281,7 @@
         <v>0</v>
       </c>
       <c r="Q1558" s="1" t="s">
-        <v>1429</v>
+        <v>1555</v>
       </c>
       <c r="R1558" s="1">
         <v>0</v>
@@ -96214,7 +96292,7 @@
     </row>
     <row r="1559" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1559" s="1" t="s">
-        <v>1551</v>
+        <v>1473</v>
       </c>
       <c r="B1559" s="1">
         <v>12</v>
@@ -96226,7 +96304,7 @@
         <v>1405</v>
       </c>
       <c r="E1559" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1559" s="1">
         <v>1</v>
@@ -96235,13 +96313,13 @@
         <v>59</v>
       </c>
       <c r="H1559" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1559" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1559" s="2" t="s">
-        <v>1418</v>
+        <v>1556</v>
       </c>
       <c r="K1559" s="1">
         <v>0</v>
@@ -96262,7 +96340,7 @@
         <v>0</v>
       </c>
       <c r="Q1559" s="1" t="s">
-        <v>1435</v>
+        <v>1557</v>
       </c>
       <c r="R1559" s="1">
         <v>0</v>
@@ -96273,7 +96351,7 @@
     </row>
     <row r="1560" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1560" s="1" t="s">
-        <v>1552</v>
+        <v>1474</v>
       </c>
       <c r="B1560" s="1">
         <v>12</v>
@@ -96285,7 +96363,7 @@
         <v>1405</v>
       </c>
       <c r="E1560" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1560" s="1">
         <v>1</v>
@@ -96294,13 +96372,13 @@
         <v>60</v>
       </c>
       <c r="H1560" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1560" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1560" s="2" t="s">
-        <v>1545</v>
+        <v>1531</v>
       </c>
       <c r="K1560" s="1">
         <v>0</v>
@@ -96321,7 +96399,7 @@
         <v>0</v>
       </c>
       <c r="Q1560" s="1" t="s">
-        <v>1553</v>
+        <v>1558</v>
       </c>
       <c r="R1560" s="1">
         <v>0</v>
@@ -96332,7 +96410,7 @@
     </row>
     <row r="1561" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1561" s="1" t="s">
-        <v>1554</v>
+        <v>1475</v>
       </c>
       <c r="B1561" s="1">
         <v>12</v>
@@ -96344,7 +96422,7 @@
         <v>1405</v>
       </c>
       <c r="E1561" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1561" s="1">
         <v>1</v>
@@ -96353,13 +96431,13 @@
         <v>61</v>
       </c>
       <c r="H1561" s="1">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I1561" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1561" s="2" t="s">
-        <v>1548</v>
+        <v>1559</v>
       </c>
       <c r="K1561" s="1">
         <v>0</v>
@@ -96380,7 +96458,7 @@
         <v>0</v>
       </c>
       <c r="Q1561" s="1" t="s">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="R1561" s="1">
         <v>0</v>
@@ -96391,7 +96469,7 @@
     </row>
     <row r="1562" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1562" s="1" t="s">
-        <v>1556</v>
+        <v>1561</v>
       </c>
       <c r="B1562" s="1">
         <v>12</v>
@@ -96403,7 +96481,7 @@
         <v>1405</v>
       </c>
       <c r="E1562" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1562" s="1">
         <v>1</v>
@@ -96412,13 +96490,13 @@
         <v>62</v>
       </c>
       <c r="H1562" s="1">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I1562" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1562" s="2" t="s">
-        <v>1545</v>
+        <v>1531</v>
       </c>
       <c r="K1562" s="1">
         <v>0</v>
@@ -96439,7 +96517,7 @@
         <v>0</v>
       </c>
       <c r="Q1562" s="1" t="s">
-        <v>1431</v>
+        <v>1562</v>
       </c>
       <c r="R1562" s="1">
         <v>0</v>
@@ -96450,7 +96528,7 @@
     </row>
     <row r="1563" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1563" s="1" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="B1563" s="1">
         <v>12</v>
@@ -96462,7 +96540,7 @@
         <v>1405</v>
       </c>
       <c r="E1563" s="1" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F1563" s="1">
         <v>1</v>
@@ -96474,36 +96552,1039 @@
         <v>1</v>
       </c>
       <c r="I1563" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1563" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="K1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1563" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1563" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="R1563" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1563" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1564" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B1564" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1564" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1564" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1564" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1564" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1564" s="1">
+        <v>64</v>
+      </c>
+      <c r="H1564" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I1564" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1564" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="K1564" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1564" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1564" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1564" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1564" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1564" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1564" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="R1564" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1564" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1565" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B1565" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1565" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1565" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1565" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1565" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1565" s="1">
+        <v>65</v>
+      </c>
+      <c r="H1565" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1565" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1565" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="K1565" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1565" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1565" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1565" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1565" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1565" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1565" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="R1565" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1565" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1566" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B1566" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1566" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1566" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1566" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1566" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1566" s="1">
+        <v>66</v>
+      </c>
+      <c r="H1566" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I1566" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1566" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="K1566" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1566" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1566" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1566" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1566" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1566" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1566" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="R1566" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1566" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1567" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B1567" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1567" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1567" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1567" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1567" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1567" s="1">
+        <v>67</v>
+      </c>
+      <c r="H1567" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1567" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1567" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="K1567" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1567" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1567" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1567" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1567" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1567" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1567" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="R1567" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1567" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1568" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B1568" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1568" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1568" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1568" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1568" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1568" s="1">
+        <v>68</v>
+      </c>
+      <c r="H1568" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I1568" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1568" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="K1568" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1568" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1568" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1568" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1568" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1568" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1568" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="R1568" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1568" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1569" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B1569" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1569" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1569" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1569" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1569" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1569" s="1">
+        <v>69</v>
+      </c>
+      <c r="H1569" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1569" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1569" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="K1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1569" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1569" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="R1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1569" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1570" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B1570" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1570" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1570" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1570" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1570" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1570" s="1">
+        <v>70</v>
+      </c>
+      <c r="H1570" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I1570" s="1">
+        <v>9</v>
+      </c>
+      <c r="J1570" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="K1570" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1570" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1570" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1570" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1570" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1570" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1570" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="R1570" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1570" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1571" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B1571" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1571" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1571" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1571" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1571" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1571" s="1">
+        <v>71</v>
+      </c>
+      <c r="H1571" s="1">
+        <v>500</v>
+      </c>
+      <c r="I1571" s="1">
         <v>10</v>
       </c>
-      <c r="J1563" s="2" t="s">
-        <v>1545</v>
-      </c>
-      <c r="K1563" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1563" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1563" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1563" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1563" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1563" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1563" s="1" t="s">
-        <v>1439</v>
-      </c>
-      <c r="R1563" s="1">
-        <v>0</v>
-      </c>
-      <c r="S1563" s="1">
+      <c r="J1571" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="K1571" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1571" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1571" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1571" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1571" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1571" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1571" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1571" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1571" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1572" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B1572" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1572" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1572" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1572" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1572" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1572" s="1">
+        <v>72</v>
+      </c>
+      <c r="H1572" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1572" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1572" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="K1572" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1572" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1572" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1572" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1572" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1572" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="Q1572" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1572" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1572" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1573" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B1573" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1573" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1573" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1573" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1573" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1573" s="1">
+        <v>73</v>
+      </c>
+      <c r="H1573" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1573" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1573" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="K1573" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1573" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1573" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1573" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1573" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1573" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1573" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="R1573" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1573" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1574" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B1574" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1574" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1574" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1574" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1574" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1574" s="1">
+        <v>74</v>
+      </c>
+      <c r="H1574" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1574" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1574" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="K1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1574" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1574" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="R1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1574" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1575" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B1575" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1575" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1575" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1575" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1575" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1575" s="1">
+        <v>75</v>
+      </c>
+      <c r="H1575" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1575" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1575" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="K1575" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1575" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1575" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1575" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1575" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1575" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1575" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="R1575" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1575" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1576" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B1576" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1576" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1576" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1576" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1576" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1576" s="1">
+        <v>76</v>
+      </c>
+      <c r="H1576" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1576" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1576" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="K1576" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1576" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1576" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1576" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1576" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1576" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1576" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="R1576" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1576" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1577" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B1577" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1577" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1577" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1577" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1577" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1577" s="1">
+        <v>77</v>
+      </c>
+      <c r="H1577" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1577" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1577" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="K1577" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1577" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1577" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1577" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1577" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1577" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1577" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="R1577" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1577" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1578" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B1578" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1578" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1578" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1578" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1578" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1578" s="1">
+        <v>78</v>
+      </c>
+      <c r="H1578" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1578" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1578" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="K1578" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1578" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1578" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1578" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1578" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1578" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1578" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="R1578" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1578" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1579" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B1579" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1579" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1579" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1579" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1579" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1579" s="1">
+        <v>79</v>
+      </c>
+      <c r="H1579" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I1579" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1579" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="K1579" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1579" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1579" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1579" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1579" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1579" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1579" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="R1579" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1579" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1580" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B1580" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1580" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1580" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1580" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1580" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1580" s="1">
+        <v>80</v>
+      </c>
+      <c r="H1580" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1580" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1580" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="K1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1580" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1580" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="R1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1580" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F1002A-96B9-4430-B4FD-0C8A61623F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C48916-C1CC-4658-ACD4-E6B775AA89E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3815" uniqueCount="1584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3815" uniqueCount="1585">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -4620,9 +4620,6 @@
     <t>135,4500,1800</t>
   </si>
   <si>
-    <t>225,4500,1800</t>
-  </si>
-  <si>
     <t>315,4500,1800</t>
   </si>
   <si>
@@ -4897,6 +4894,12 @@
   </si>
   <si>
     <t>225,5500,1800</t>
+  </si>
+  <si>
+    <t>120,4500,1800</t>
+  </si>
+  <si>
+    <t>121101,121101,121101,121101,121101</t>
   </si>
 </sst>
 </file>
@@ -93390,7 +93393,7 @@
         <v>0</v>
       </c>
       <c r="Q1509" s="1" t="s">
-        <v>1490</v>
+        <v>1583</v>
       </c>
       <c r="R1509" s="1">
         <v>0</v>
@@ -93449,7 +93452,7 @@
         <v>0</v>
       </c>
       <c r="Q1510" s="1" t="s">
-        <v>1491</v>
+        <v>1549</v>
       </c>
       <c r="R1510" s="1">
         <v>0</v>
@@ -93487,7 +93490,7 @@
         <v>3</v>
       </c>
       <c r="J1511" s="2" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="K1511" s="1">
         <v>0</v>
@@ -93508,7 +93511,7 @@
         <v>0</v>
       </c>
       <c r="Q1511" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="R1511" s="1">
         <v>0</v>
@@ -93537,7 +93540,7 @@
         <v>1</v>
       </c>
       <c r="G1512" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H1512" s="1">
         <v>1500</v>
@@ -93546,7 +93549,7 @@
         <v>4</v>
       </c>
       <c r="J1512" s="2" t="s">
-        <v>1412</v>
+        <v>1584</v>
       </c>
       <c r="K1512" s="1">
         <v>0</v>
@@ -93567,7 +93570,7 @@
         <v>0</v>
       </c>
       <c r="Q1512" s="1" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="R1512" s="1">
         <v>0</v>
@@ -93596,7 +93599,7 @@
         <v>1</v>
       </c>
       <c r="G1513" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1513" s="1">
         <v>1500</v>
@@ -93605,28 +93608,28 @@
         <v>4</v>
       </c>
       <c r="J1513" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="K1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1513" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1513" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1513" s="1" t="s">
         <v>1494</v>
-      </c>
-      <c r="K1513" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1513" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1513" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1513" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1513" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1513" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1513" s="1" t="s">
-        <v>1495</v>
       </c>
       <c r="R1513" s="1">
         <v>0</v>
@@ -93655,7 +93658,7 @@
         <v>1</v>
       </c>
       <c r="G1514" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H1514" s="1">
         <v>1500</v>
@@ -93664,28 +93667,28 @@
         <v>4</v>
       </c>
       <c r="J1514" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="K1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1514" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1514" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1514" s="1" t="s">
         <v>1496</v>
-      </c>
-      <c r="K1514" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1514" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1514" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1514" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1514" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1514" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1514" s="1" t="s">
-        <v>1497</v>
       </c>
       <c r="R1514" s="1">
         <v>0</v>
@@ -93714,7 +93717,7 @@
         <v>1</v>
       </c>
       <c r="G1515" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H1515" s="1">
         <v>1500</v>
@@ -93723,7 +93726,7 @@
         <v>4</v>
       </c>
       <c r="J1515" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="K1515" s="1">
         <v>0</v>
@@ -93744,7 +93747,7 @@
         <v>0</v>
       </c>
       <c r="Q1515" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="R1515" s="1">
         <v>0</v>
@@ -93773,7 +93776,7 @@
         <v>1</v>
       </c>
       <c r="G1516" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1516" s="1">
         <v>1500</v>
@@ -93782,7 +93785,7 @@
         <v>4</v>
       </c>
       <c r="J1516" s="2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="K1516" s="1">
         <v>0</v>
@@ -93803,7 +93806,7 @@
         <v>0</v>
       </c>
       <c r="Q1516" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="R1516" s="1">
         <v>0</v>
@@ -93832,7 +93835,7 @@
         <v>1</v>
       </c>
       <c r="G1517" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H1517" s="1">
         <v>1500</v>
@@ -93841,28 +93844,28 @@
         <v>5</v>
       </c>
       <c r="J1517" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="K1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1517" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1517" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1517" s="1" t="s">
         <v>1500</v>
-      </c>
-      <c r="K1517" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1517" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1517" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1517" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1517" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1517" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1517" s="1" t="s">
-        <v>1501</v>
       </c>
       <c r="R1517" s="1">
         <v>0</v>
@@ -93891,7 +93894,7 @@
         <v>1</v>
       </c>
       <c r="G1518" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1518" s="1">
         <v>1500</v>
@@ -93921,7 +93924,7 @@
         <v>0</v>
       </c>
       <c r="Q1518" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="R1518" s="1">
         <v>0</v>
@@ -93950,7 +93953,7 @@
         <v>1</v>
       </c>
       <c r="G1519" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H1519" s="1">
         <v>1500</v>
@@ -93980,7 +93983,7 @@
         <v>0</v>
       </c>
       <c r="Q1519" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="R1519" s="1">
         <v>0</v>
@@ -94009,7 +94012,7 @@
         <v>1</v>
       </c>
       <c r="G1520" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1520" s="1">
         <v>500</v>
@@ -94068,7 +94071,7 @@
         <v>1</v>
       </c>
       <c r="G1521" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H1521" s="1">
         <v>1500</v>
@@ -94077,28 +94080,28 @@
         <v>5</v>
       </c>
       <c r="J1521" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="K1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1521" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1521" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1521" s="1" t="s">
         <v>1504</v>
-      </c>
-      <c r="K1521" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1521" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1521" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1521" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1521" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1521" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1521" s="1" t="s">
-        <v>1505</v>
       </c>
       <c r="R1521" s="1">
         <v>0</v>
@@ -94127,7 +94130,7 @@
         <v>1</v>
       </c>
       <c r="G1522" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1522" s="1">
         <v>1500</v>
@@ -94136,7 +94139,7 @@
         <v>5</v>
       </c>
       <c r="J1522" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="K1522" s="1">
         <v>0</v>
@@ -94157,7 +94160,7 @@
         <v>0</v>
       </c>
       <c r="Q1522" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="R1522" s="1">
         <v>0</v>
@@ -94186,7 +94189,7 @@
         <v>1</v>
       </c>
       <c r="G1523" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1523" s="1">
         <v>1350</v>
@@ -94195,7 +94198,7 @@
         <v>6</v>
       </c>
       <c r="J1523" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="K1523" s="1">
         <v>0</v>
@@ -94216,7 +94219,7 @@
         <v>0</v>
       </c>
       <c r="Q1523" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="R1523" s="1">
         <v>0</v>
@@ -94245,7 +94248,7 @@
         <v>1</v>
       </c>
       <c r="G1524" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1524" s="1">
         <v>1350</v>
@@ -94254,28 +94257,28 @@
         <v>6</v>
       </c>
       <c r="J1524" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="K1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1524" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1524" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1524" s="1" t="s">
         <v>1508</v>
-      </c>
-      <c r="K1524" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1524" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1524" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1524" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1524" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1524" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1524" s="1" t="s">
-        <v>1509</v>
       </c>
       <c r="R1524" s="1">
         <v>0</v>
@@ -94304,7 +94307,7 @@
         <v>1</v>
       </c>
       <c r="G1525" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1525" s="1">
         <v>1350</v>
@@ -94313,7 +94316,7 @@
         <v>6</v>
       </c>
       <c r="J1525" s="2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="K1525" s="1">
         <v>0</v>
@@ -94334,7 +94337,7 @@
         <v>0</v>
       </c>
       <c r="Q1525" s="1" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="R1525" s="1">
         <v>0</v>
@@ -94363,7 +94366,7 @@
         <v>1</v>
       </c>
       <c r="G1526" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1526" s="1">
         <v>500</v>
@@ -94422,7 +94425,7 @@
         <v>1</v>
       </c>
       <c r="G1527" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1527" s="1">
         <v>1350</v>
@@ -94431,28 +94434,28 @@
         <v>6</v>
       </c>
       <c r="J1527" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="K1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1527" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1527" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1527" s="1" t="s">
         <v>1511</v>
-      </c>
-      <c r="K1527" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1527" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1527" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1527" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1527" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1527" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1527" s="1" t="s">
-        <v>1512</v>
       </c>
       <c r="R1527" s="1">
         <v>0</v>
@@ -94481,7 +94484,7 @@
         <v>1</v>
       </c>
       <c r="G1528" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1528" s="1">
         <v>1350</v>
@@ -94490,7 +94493,7 @@
         <v>6</v>
       </c>
       <c r="J1528" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="K1528" s="1">
         <v>0</v>
@@ -94511,7 +94514,7 @@
         <v>0</v>
       </c>
       <c r="Q1528" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="R1528" s="1">
         <v>0</v>
@@ -94540,7 +94543,7 @@
         <v>1</v>
       </c>
       <c r="G1529" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1529" s="1">
         <v>1350</v>
@@ -94549,7 +94552,7 @@
         <v>6</v>
       </c>
       <c r="J1529" s="2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="K1529" s="1">
         <v>0</v>
@@ -94570,7 +94573,7 @@
         <v>0</v>
       </c>
       <c r="Q1529" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="R1529" s="1">
         <v>0</v>
@@ -94599,7 +94602,7 @@
         <v>1</v>
       </c>
       <c r="G1530" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1530" s="1">
         <v>1350</v>
@@ -94608,28 +94611,28 @@
         <v>7</v>
       </c>
       <c r="J1530" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="K1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1530" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1530" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1530" s="1" t="s">
         <v>1515</v>
-      </c>
-      <c r="K1530" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1530" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1530" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1530" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1530" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1530" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1530" s="1" t="s">
-        <v>1516</v>
       </c>
       <c r="R1530" s="1">
         <v>0</v>
@@ -94658,7 +94661,7 @@
         <v>1</v>
       </c>
       <c r="G1531" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H1531" s="1">
         <v>1350</v>
@@ -94667,28 +94670,28 @@
         <v>7</v>
       </c>
       <c r="J1531" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1531" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1531" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1531" s="1" t="s">
         <v>1517</v>
-      </c>
-      <c r="K1531" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1531" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1531" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1531" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1531" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1531" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1531" s="1" t="s">
-        <v>1518</v>
       </c>
       <c r="R1531" s="1">
         <v>0</v>
@@ -94717,7 +94720,7 @@
         <v>1</v>
       </c>
       <c r="G1532" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H1532" s="1">
         <v>1350</v>
@@ -94726,7 +94729,7 @@
         <v>7</v>
       </c>
       <c r="J1532" s="2" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="K1532" s="1">
         <v>0</v>
@@ -94747,7 +94750,7 @@
         <v>0</v>
       </c>
       <c r="Q1532" s="1" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="R1532" s="1">
         <v>0</v>
@@ -94776,7 +94779,7 @@
         <v>1</v>
       </c>
       <c r="G1533" s="1">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H1533" s="1">
         <v>1350</v>
@@ -94785,7 +94788,7 @@
         <v>7</v>
       </c>
       <c r="J1533" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="K1533" s="1">
         <v>0</v>
@@ -94835,7 +94838,7 @@
         <v>1</v>
       </c>
       <c r="G1534" s="1">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H1534" s="1">
         <v>1350</v>
@@ -94844,28 +94847,28 @@
         <v>7</v>
       </c>
       <c r="J1534" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="K1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1534" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1534" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1534" s="1" t="s">
         <v>1521</v>
-      </c>
-      <c r="K1534" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1534" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1534" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1534" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1534" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1534" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1534" s="1" t="s">
-        <v>1522</v>
       </c>
       <c r="R1534" s="1">
         <v>0</v>
@@ -94894,7 +94897,7 @@
         <v>1</v>
       </c>
       <c r="G1535" s="1">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H1535" s="1">
         <v>1350</v>
@@ -94903,7 +94906,7 @@
         <v>7</v>
       </c>
       <c r="J1535" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="K1535" s="1">
         <v>0</v>
@@ -94924,7 +94927,7 @@
         <v>0</v>
       </c>
       <c r="Q1535" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="R1535" s="1">
         <v>0</v>
@@ -94953,7 +94956,7 @@
         <v>1</v>
       </c>
       <c r="G1536" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H1536" s="1">
         <v>1350</v>
@@ -94962,7 +94965,7 @@
         <v>7</v>
       </c>
       <c r="J1536" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="K1536" s="1">
         <v>0</v>
@@ -94983,7 +94986,7 @@
         <v>0</v>
       </c>
       <c r="Q1536" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="R1536" s="1">
         <v>0</v>
@@ -95012,7 +95015,7 @@
         <v>1</v>
       </c>
       <c r="G1537" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H1537" s="1">
         <v>1</v>
@@ -95021,7 +95024,7 @@
         <v>8</v>
       </c>
       <c r="J1537" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="K1537" s="1">
         <v>0</v>
@@ -95042,7 +95045,7 @@
         <v>0</v>
       </c>
       <c r="Q1537" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="R1537" s="1">
         <v>0</v>
@@ -95071,7 +95074,7 @@
         <v>1</v>
       </c>
       <c r="G1538" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1538" s="1">
         <v>1200</v>
@@ -95101,7 +95104,7 @@
         <v>0</v>
       </c>
       <c r="Q1538" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="R1538" s="1">
         <v>0</v>
@@ -95130,7 +95133,7 @@
         <v>1</v>
       </c>
       <c r="G1539" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1539" s="1">
         <v>1</v>
@@ -95139,7 +95142,7 @@
         <v>8</v>
       </c>
       <c r="J1539" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="K1539" s="1">
         <v>0</v>
@@ -95160,7 +95163,7 @@
         <v>0</v>
       </c>
       <c r="Q1539" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="R1539" s="1">
         <v>0</v>
@@ -95189,7 +95192,7 @@
         <v>1</v>
       </c>
       <c r="G1540" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1540" s="1">
         <v>1200</v>
@@ -95219,7 +95222,7 @@
         <v>0</v>
       </c>
       <c r="Q1540" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="R1540" s="1">
         <v>0</v>
@@ -95248,7 +95251,7 @@
         <v>1</v>
       </c>
       <c r="G1541" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1541" s="1">
         <v>1</v>
@@ -95257,28 +95260,28 @@
         <v>8</v>
       </c>
       <c r="J1541" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="K1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1541" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1541" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1541" s="1" t="s">
         <v>1528</v>
-      </c>
-      <c r="K1541" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1541" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1541" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1541" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1541" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1541" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1541" s="1" t="s">
-        <v>1529</v>
       </c>
       <c r="R1541" s="1">
         <v>0</v>
@@ -95307,7 +95310,7 @@
         <v>1</v>
       </c>
       <c r="G1542" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1542" s="1">
         <v>1200</v>
@@ -95337,7 +95340,7 @@
         <v>0</v>
       </c>
       <c r="Q1542" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="R1542" s="1">
         <v>0</v>
@@ -95366,7 +95369,7 @@
         <v>1</v>
       </c>
       <c r="G1543" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1543" s="1">
         <v>1</v>
@@ -95375,28 +95378,28 @@
         <v>8</v>
       </c>
       <c r="J1543" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="K1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1543" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1543" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1543" s="1" t="s">
         <v>1531</v>
-      </c>
-      <c r="K1543" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1543" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1543" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1543" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1543" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1543" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1543" s="1" t="s">
-        <v>1532</v>
       </c>
       <c r="R1543" s="1">
         <v>0</v>
@@ -95425,7 +95428,7 @@
         <v>1</v>
       </c>
       <c r="G1544" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H1544" s="1">
         <v>1200</v>
@@ -95434,7 +95437,7 @@
         <v>8</v>
       </c>
       <c r="J1544" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="K1544" s="1">
         <v>0</v>
@@ -95455,7 +95458,7 @@
         <v>0</v>
       </c>
       <c r="Q1544" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="R1544" s="1">
         <v>0</v>
@@ -95466,7 +95469,7 @@
     </row>
     <row r="1545" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1545" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="B1545" s="1">
         <v>12</v>
@@ -95484,7 +95487,7 @@
         <v>1</v>
       </c>
       <c r="G1545" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1545" s="1">
         <v>1</v>
@@ -95493,7 +95496,7 @@
         <v>8</v>
       </c>
       <c r="J1545" s="2" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="K1545" s="1">
         <v>0</v>
@@ -95514,7 +95517,7 @@
         <v>0</v>
       </c>
       <c r="Q1545" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="R1545" s="1">
         <v>0</v>
@@ -95525,7 +95528,7 @@
     </row>
     <row r="1546" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1546" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B1546" s="1">
         <v>12</v>
@@ -95543,7 +95546,7 @@
         <v>1</v>
       </c>
       <c r="G1546" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H1546" s="1">
         <v>1200</v>
@@ -95573,7 +95576,7 @@
         <v>0</v>
       </c>
       <c r="Q1546" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="R1546" s="1">
         <v>0</v>
@@ -95584,7 +95587,7 @@
     </row>
     <row r="1547" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1547" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B1547" s="1">
         <v>12</v>
@@ -95602,7 +95605,7 @@
         <v>1</v>
       </c>
       <c r="G1547" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H1547" s="1">
         <v>1</v>
@@ -95611,7 +95614,7 @@
         <v>8</v>
       </c>
       <c r="J1547" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="K1547" s="1">
         <v>0</v>
@@ -95632,7 +95635,7 @@
         <v>0</v>
       </c>
       <c r="Q1547" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="R1547" s="1">
         <v>0</v>
@@ -95643,7 +95646,7 @@
     </row>
     <row r="1548" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1548" s="1" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B1548" s="1">
         <v>12</v>
@@ -95661,7 +95664,7 @@
         <v>1</v>
       </c>
       <c r="G1548" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H1548" s="1">
         <v>1200</v>
@@ -95670,7 +95673,7 @@
         <v>8</v>
       </c>
       <c r="J1548" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="K1548" s="1">
         <v>0</v>
@@ -95691,7 +95694,7 @@
         <v>0</v>
       </c>
       <c r="Q1548" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="R1548" s="1">
         <v>0</v>
@@ -95702,7 +95705,7 @@
     </row>
     <row r="1549" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1549" s="1" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B1549" s="1">
         <v>12</v>
@@ -95720,7 +95723,7 @@
         <v>1</v>
       </c>
       <c r="G1549" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H1549" s="1">
         <v>1</v>
@@ -95729,7 +95732,7 @@
         <v>8</v>
       </c>
       <c r="J1549" s="2" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="K1549" s="1">
         <v>0</v>
@@ -95750,7 +95753,7 @@
         <v>0</v>
       </c>
       <c r="Q1549" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="R1549" s="1">
         <v>0</v>
@@ -95761,7 +95764,7 @@
     </row>
     <row r="1550" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1550" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B1550" s="1">
         <v>12</v>
@@ -95779,7 +95782,7 @@
         <v>1</v>
       </c>
       <c r="G1550" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H1550" s="1">
         <v>1200</v>
@@ -95809,7 +95812,7 @@
         <v>0</v>
       </c>
       <c r="Q1550" s="1" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="R1550" s="1">
         <v>0</v>
@@ -95820,7 +95823,7 @@
     </row>
     <row r="1551" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1551" s="1" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B1551" s="1">
         <v>12</v>
@@ -95838,7 +95841,7 @@
         <v>1</v>
       </c>
       <c r="G1551" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H1551" s="1">
         <v>1</v>
@@ -95847,28 +95850,28 @@
         <v>8</v>
       </c>
       <c r="J1551" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="K1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1551" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1551" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1551" s="1" t="s">
         <v>1545</v>
-      </c>
-      <c r="K1551" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1551" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1551" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1551" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1551" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1551" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1551" s="1" t="s">
-        <v>1546</v>
       </c>
       <c r="R1551" s="1">
         <v>0</v>
@@ -95879,7 +95882,7 @@
     </row>
     <row r="1552" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1552" s="1" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B1552" s="1">
         <v>12</v>
@@ -95897,7 +95900,7 @@
         <v>1</v>
       </c>
       <c r="G1552" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H1552" s="1">
         <v>1200</v>
@@ -95906,7 +95909,7 @@
         <v>8</v>
       </c>
       <c r="J1552" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="K1552" s="1">
         <v>0</v>
@@ -95927,7 +95930,7 @@
         <v>0</v>
       </c>
       <c r="Q1552" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="R1552" s="1">
         <v>0</v>
@@ -95956,7 +95959,7 @@
         <v>1</v>
       </c>
       <c r="G1553" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H1553" s="1">
         <v>1</v>
@@ -95965,28 +95968,28 @@
         <v>9</v>
       </c>
       <c r="J1553" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1553" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1553" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1553" s="1" t="s">
         <v>1548</v>
-      </c>
-      <c r="K1553" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1553" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1553" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1553" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1553" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1553" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1553" s="1" t="s">
-        <v>1549</v>
       </c>
       <c r="R1553" s="1">
         <v>0</v>
@@ -96015,7 +96018,7 @@
         <v>1</v>
       </c>
       <c r="G1554" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H1554" s="1">
         <v>1200</v>
@@ -96024,7 +96027,7 @@
         <v>9</v>
       </c>
       <c r="J1554" s="2" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="K1554" s="1">
         <v>0</v>
@@ -96045,7 +96048,7 @@
         <v>0</v>
       </c>
       <c r="Q1554" s="1" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="R1554" s="1">
         <v>0</v>
@@ -96074,7 +96077,7 @@
         <v>1</v>
       </c>
       <c r="G1555" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H1555" s="1">
         <v>1</v>
@@ -96083,28 +96086,28 @@
         <v>9</v>
       </c>
       <c r="J1555" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="K1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1555" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1555" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1555" s="1" t="s">
         <v>1551</v>
-      </c>
-      <c r="K1555" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1555" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1555" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1555" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1555" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1555" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1555" s="1" t="s">
-        <v>1552</v>
       </c>
       <c r="R1555" s="1">
         <v>0</v>
@@ -96133,7 +96136,7 @@
         <v>1</v>
       </c>
       <c r="G1556" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1556" s="1">
         <v>1200</v>
@@ -96142,7 +96145,7 @@
         <v>9</v>
       </c>
       <c r="J1556" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1556" s="1">
         <v>0</v>
@@ -96163,7 +96166,7 @@
         <v>0</v>
       </c>
       <c r="Q1556" s="1" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="R1556" s="1">
         <v>0</v>
@@ -96192,7 +96195,7 @@
         <v>1</v>
       </c>
       <c r="G1557" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H1557" s="1">
         <v>1</v>
@@ -96201,7 +96204,7 @@
         <v>9</v>
       </c>
       <c r="J1557" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1557" s="1">
         <v>0</v>
@@ -96222,7 +96225,7 @@
         <v>0</v>
       </c>
       <c r="Q1557" s="1" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="R1557" s="1">
         <v>0</v>
@@ -96251,7 +96254,7 @@
         <v>1</v>
       </c>
       <c r="G1558" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1558" s="1">
         <v>1200</v>
@@ -96260,7 +96263,7 @@
         <v>9</v>
       </c>
       <c r="J1558" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1558" s="1">
         <v>0</v>
@@ -96281,7 +96284,7 @@
         <v>0</v>
       </c>
       <c r="Q1558" s="1" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="R1558" s="1">
         <v>0</v>
@@ -96310,7 +96313,7 @@
         <v>1</v>
       </c>
       <c r="G1559" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1559" s="1">
         <v>1</v>
@@ -96319,28 +96322,28 @@
         <v>9</v>
       </c>
       <c r="J1559" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="K1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1559" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1559" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1559" s="1" t="s">
         <v>1556</v>
-      </c>
-      <c r="K1559" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1559" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1559" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1559" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1559" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1559" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1559" s="1" t="s">
-        <v>1557</v>
       </c>
       <c r="R1559" s="1">
         <v>0</v>
@@ -96369,7 +96372,7 @@
         <v>1</v>
       </c>
       <c r="G1560" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1560" s="1">
         <v>1200</v>
@@ -96378,7 +96381,7 @@
         <v>9</v>
       </c>
       <c r="J1560" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1560" s="1">
         <v>0</v>
@@ -96399,7 +96402,7 @@
         <v>0</v>
       </c>
       <c r="Q1560" s="1" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="R1560" s="1">
         <v>0</v>
@@ -96428,7 +96431,7 @@
         <v>1</v>
       </c>
       <c r="G1561" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1561" s="1">
         <v>1</v>
@@ -96437,28 +96440,28 @@
         <v>9</v>
       </c>
       <c r="J1561" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="K1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1561" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1561" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1561" s="1" t="s">
         <v>1559</v>
-      </c>
-      <c r="K1561" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1561" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1561" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1561" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1561" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1561" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1561" s="1" t="s">
-        <v>1560</v>
       </c>
       <c r="R1561" s="1">
         <v>0</v>
@@ -96469,7 +96472,7 @@
     </row>
     <row r="1562" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1562" s="1" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B1562" s="1">
         <v>12</v>
@@ -96487,7 +96490,7 @@
         <v>1</v>
       </c>
       <c r="G1562" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1562" s="1">
         <v>1200</v>
@@ -96496,7 +96499,7 @@
         <v>9</v>
       </c>
       <c r="J1562" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1562" s="1">
         <v>0</v>
@@ -96517,7 +96520,7 @@
         <v>0</v>
       </c>
       <c r="Q1562" s="1" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="R1562" s="1">
         <v>0</v>
@@ -96528,7 +96531,7 @@
     </row>
     <row r="1563" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1563" s="1" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B1563" s="1">
         <v>12</v>
@@ -96546,7 +96549,7 @@
         <v>1</v>
       </c>
       <c r="G1563" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1563" s="1">
         <v>1</v>
@@ -96555,7 +96558,7 @@
         <v>9</v>
       </c>
       <c r="J1563" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1563" s="1">
         <v>0</v>
@@ -96576,7 +96579,7 @@
         <v>0</v>
       </c>
       <c r="Q1563" s="1" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="R1563" s="1">
         <v>0</v>
@@ -96587,7 +96590,7 @@
     </row>
     <row r="1564" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1564" s="1" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B1564" s="1">
         <v>12</v>
@@ -96605,7 +96608,7 @@
         <v>1</v>
       </c>
       <c r="G1564" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1564" s="1">
         <v>1200</v>
@@ -96614,7 +96617,7 @@
         <v>9</v>
       </c>
       <c r="J1564" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1564" s="1">
         <v>0</v>
@@ -96635,7 +96638,7 @@
         <v>0</v>
       </c>
       <c r="Q1564" s="1" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="R1564" s="1">
         <v>0</v>
@@ -96646,7 +96649,7 @@
     </row>
     <row r="1565" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1565" s="1" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B1565" s="1">
         <v>12</v>
@@ -96664,7 +96667,7 @@
         <v>1</v>
       </c>
       <c r="G1565" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H1565" s="1">
         <v>1</v>
@@ -96673,7 +96676,7 @@
         <v>9</v>
       </c>
       <c r="J1565" s="2" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="K1565" s="1">
         <v>0</v>
@@ -96694,7 +96697,7 @@
         <v>0</v>
       </c>
       <c r="Q1565" s="1" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="R1565" s="1">
         <v>0</v>
@@ -96705,7 +96708,7 @@
     </row>
     <row r="1566" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1566" s="1" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B1566" s="1">
         <v>12</v>
@@ -96723,7 +96726,7 @@
         <v>1</v>
       </c>
       <c r="G1566" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H1566" s="1">
         <v>1200</v>
@@ -96732,7 +96735,7 @@
         <v>9</v>
       </c>
       <c r="J1566" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1566" s="1">
         <v>0</v>
@@ -96753,7 +96756,7 @@
         <v>0</v>
       </c>
       <c r="Q1566" s="1" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="R1566" s="1">
         <v>0</v>
@@ -96764,7 +96767,7 @@
     </row>
     <row r="1567" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1567" s="1" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B1567" s="1">
         <v>12</v>
@@ -96782,7 +96785,7 @@
         <v>1</v>
       </c>
       <c r="G1567" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H1567" s="1">
         <v>1</v>
@@ -96791,7 +96794,7 @@
         <v>9</v>
       </c>
       <c r="J1567" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1567" s="1">
         <v>0</v>
@@ -96812,7 +96815,7 @@
         <v>0</v>
       </c>
       <c r="Q1567" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="R1567" s="1">
         <v>0</v>
@@ -96823,7 +96826,7 @@
     </row>
     <row r="1568" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1568" s="1" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B1568" s="1">
         <v>12</v>
@@ -96841,7 +96844,7 @@
         <v>1</v>
       </c>
       <c r="G1568" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H1568" s="1">
         <v>1200</v>
@@ -96850,7 +96853,7 @@
         <v>9</v>
       </c>
       <c r="J1568" s="2" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K1568" s="1">
         <v>0</v>
@@ -96871,7 +96874,7 @@
         <v>0</v>
       </c>
       <c r="Q1568" s="1" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="R1568" s="1">
         <v>0</v>
@@ -96882,7 +96885,7 @@
     </row>
     <row r="1569" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1569" s="1" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B1569" s="1">
         <v>12</v>
@@ -96900,7 +96903,7 @@
         <v>1</v>
       </c>
       <c r="G1569" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H1569" s="1">
         <v>1</v>
@@ -96909,28 +96912,28 @@
         <v>9</v>
       </c>
       <c r="J1569" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="K1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1569" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1569" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1569" s="1" t="s">
         <v>1574</v>
-      </c>
-      <c r="K1569" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1569" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1569" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1569" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1569" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1569" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1569" s="1" t="s">
-        <v>1575</v>
       </c>
       <c r="R1569" s="1">
         <v>0</v>
@@ -96941,7 +96944,7 @@
     </row>
     <row r="1570" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1570" s="1" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B1570" s="1">
         <v>12</v>
@@ -96959,7 +96962,7 @@
         <v>1</v>
       </c>
       <c r="G1570" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H1570" s="1">
         <v>1200</v>
@@ -96968,7 +96971,7 @@
         <v>9</v>
       </c>
       <c r="J1570" s="2" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="K1570" s="1">
         <v>0</v>
@@ -96989,7 +96992,7 @@
         <v>0</v>
       </c>
       <c r="Q1570" s="1" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="R1570" s="1">
         <v>0</v>
@@ -97018,7 +97021,7 @@
         <v>1</v>
       </c>
       <c r="G1571" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H1571" s="1">
         <v>500</v>
@@ -97077,7 +97080,7 @@
         <v>1</v>
       </c>
       <c r="G1572" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1572" s="1">
         <v>1500</v>
@@ -97086,7 +97089,7 @@
         <v>10</v>
       </c>
       <c r="J1572" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1572" s="1">
         <v>0</v>
@@ -97136,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="G1573" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H1573" s="1">
         <v>1500</v>
@@ -97145,7 +97148,7 @@
         <v>10</v>
       </c>
       <c r="J1573" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1573" s="1">
         <v>0</v>
@@ -97195,7 +97198,7 @@
         <v>1</v>
       </c>
       <c r="G1574" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H1574" s="1">
         <v>1500</v>
@@ -97204,28 +97207,28 @@
         <v>10</v>
       </c>
       <c r="J1574" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="K1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1574" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1574" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1574" s="1" t="s">
         <v>1579</v>
-      </c>
-      <c r="K1574" s="1">
-        <v>0</v>
-      </c>
-      <c r="L1574" s="1">
-        <v>30000</v>
-      </c>
-      <c r="M1574" s="1">
-        <v>0</v>
-      </c>
-      <c r="N1574" s="1">
-        <v>0</v>
-      </c>
-      <c r="O1574" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1574" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1574" s="1" t="s">
-        <v>1580</v>
       </c>
       <c r="R1574" s="1">
         <v>0</v>
@@ -97254,7 +97257,7 @@
         <v>1</v>
       </c>
       <c r="G1575" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H1575" s="1">
         <v>1500</v>
@@ -97263,7 +97266,7 @@
         <v>10</v>
       </c>
       <c r="J1575" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1575" s="1">
         <v>0</v>
@@ -97313,7 +97316,7 @@
         <v>1</v>
       </c>
       <c r="G1576" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H1576" s="1">
         <v>1500</v>
@@ -97322,7 +97325,7 @@
         <v>10</v>
       </c>
       <c r="J1576" s="2" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="K1576" s="1">
         <v>0</v>
@@ -97372,7 +97375,7 @@
         <v>1</v>
       </c>
       <c r="G1577" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H1577" s="1">
         <v>1500</v>
@@ -97381,7 +97384,7 @@
         <v>10</v>
       </c>
       <c r="J1577" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1577" s="1">
         <v>0</v>
@@ -97402,7 +97405,7 @@
         <v>0</v>
       </c>
       <c r="Q1577" s="1" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="R1577" s="1">
         <v>0</v>
@@ -97431,7 +97434,7 @@
         <v>1</v>
       </c>
       <c r="G1578" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H1578" s="1">
         <v>1500</v>
@@ -97440,7 +97443,7 @@
         <v>10</v>
       </c>
       <c r="J1578" s="2" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="K1578" s="1">
         <v>0</v>
@@ -97461,7 +97464,7 @@
         <v>0</v>
       </c>
       <c r="Q1578" s="1" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="R1578" s="1">
         <v>0</v>
@@ -97490,7 +97493,7 @@
         <v>1</v>
       </c>
       <c r="G1579" s="1">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H1579" s="1">
         <v>1500</v>
@@ -97499,7 +97502,7 @@
         <v>10</v>
       </c>
       <c r="J1579" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1579" s="1">
         <v>0</v>
@@ -97549,7 +97552,7 @@
         <v>1</v>
       </c>
       <c r="G1580" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H1580" s="1">
         <v>1</v>
@@ -97558,7 +97561,7 @@
         <v>10</v>
       </c>
       <c r="J1580" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1580" s="1">
         <v>0</v>
@@ -97579,7 +97582,7 @@
         <v>0</v>
       </c>
       <c r="Q1580" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="R1580" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C48916-C1CC-4658-ACD4-E6B775AA89E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674BA40C-BD1B-48E7-973E-202ABC9337DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3815" uniqueCount="1585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3821" uniqueCount="1588">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -4900,6 +4900,15 @@
   </si>
   <si>
     <t>121101,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>1210305</t>
+  </si>
+  <si>
+    <t>345,4500,1800</t>
+  </si>
+  <si>
+    <t>121105,121101,121101,121101,121101</t>
   </si>
 </sst>
 </file>
@@ -5734,7 +5743,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S1580"/>
+  <dimension ref="A1:S1581"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -93490,7 +93499,7 @@
         <v>3</v>
       </c>
       <c r="J1511" s="2" t="s">
-        <v>1413</v>
+        <v>1587</v>
       </c>
       <c r="K1511" s="1">
         <v>0</v>
@@ -93522,7 +93531,7 @@
     </row>
     <row r="1512" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1512" s="1" t="s">
-        <v>1431</v>
+        <v>1585</v>
       </c>
       <c r="B1512" s="1">
         <v>12</v>
@@ -93540,13 +93549,13 @@
         <v>1</v>
       </c>
       <c r="G1512" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H1512" s="1">
         <v>1500</v>
       </c>
       <c r="I1512" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J1512" s="2" t="s">
         <v>1584</v>
@@ -93570,7 +93579,7 @@
         <v>0</v>
       </c>
       <c r="Q1512" s="1" t="s">
-        <v>1492</v>
+        <v>1586</v>
       </c>
       <c r="R1512" s="1">
         <v>0</v>
@@ -93581,7 +93590,7 @@
     </row>
     <row r="1513" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1513" s="1" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B1513" s="1">
         <v>12</v>
@@ -93599,7 +93608,7 @@
         <v>1</v>
       </c>
       <c r="G1513" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H1513" s="1">
         <v>1500</v>
@@ -93608,7 +93617,7 @@
         <v>4</v>
       </c>
       <c r="J1513" s="2" t="s">
-        <v>1493</v>
+        <v>1412</v>
       </c>
       <c r="K1513" s="1">
         <v>0</v>
@@ -93629,7 +93638,7 @@
         <v>0</v>
       </c>
       <c r="Q1513" s="1" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="R1513" s="1">
         <v>0</v>
@@ -93640,7 +93649,7 @@
     </row>
     <row r="1514" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1514" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1514" s="1">
         <v>12</v>
@@ -93658,7 +93667,7 @@
         <v>1</v>
       </c>
       <c r="G1514" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H1514" s="1">
         <v>1500</v>
@@ -93667,7 +93676,7 @@
         <v>4</v>
       </c>
       <c r="J1514" s="2" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="K1514" s="1">
         <v>0</v>
@@ -93688,7 +93697,7 @@
         <v>0</v>
       </c>
       <c r="Q1514" s="1" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="R1514" s="1">
         <v>0</v>
@@ -93699,7 +93708,7 @@
     </row>
     <row r="1515" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1515" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B1515" s="1">
         <v>12</v>
@@ -93717,7 +93726,7 @@
         <v>1</v>
       </c>
       <c r="G1515" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H1515" s="1">
         <v>1500</v>
@@ -93747,7 +93756,7 @@
         <v>0</v>
       </c>
       <c r="Q1515" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="R1515" s="1">
         <v>0</v>
@@ -93758,7 +93767,7 @@
     </row>
     <row r="1516" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1516" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B1516" s="1">
         <v>12</v>
@@ -93776,7 +93785,7 @@
         <v>1</v>
       </c>
       <c r="G1516" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H1516" s="1">
         <v>1500</v>
@@ -93806,7 +93815,7 @@
         <v>0</v>
       </c>
       <c r="Q1516" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="R1516" s="1">
         <v>0</v>
@@ -93817,7 +93826,7 @@
     </row>
     <row r="1517" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1517" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B1517" s="1">
         <v>12</v>
@@ -93835,16 +93844,16 @@
         <v>1</v>
       </c>
       <c r="G1517" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H1517" s="1">
         <v>1500</v>
       </c>
       <c r="I1517" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1517" s="2" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="K1517" s="1">
         <v>0</v>
@@ -93865,7 +93874,7 @@
         <v>0</v>
       </c>
       <c r="Q1517" s="1" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="R1517" s="1">
         <v>0</v>
@@ -93876,7 +93885,7 @@
     </row>
     <row r="1518" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1518" s="1" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B1518" s="1">
         <v>12</v>
@@ -93894,7 +93903,7 @@
         <v>1</v>
       </c>
       <c r="G1518" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1518" s="1">
         <v>1500</v>
@@ -93903,7 +93912,7 @@
         <v>5</v>
       </c>
       <c r="J1518" s="2" t="s">
-        <v>1439</v>
+        <v>1499</v>
       </c>
       <c r="K1518" s="1">
         <v>0</v>
@@ -93924,7 +93933,7 @@
         <v>0</v>
       </c>
       <c r="Q1518" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="R1518" s="1">
         <v>0</v>
@@ -93935,7 +93944,7 @@
     </row>
     <row r="1519" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1519" s="1" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="B1519" s="1">
         <v>12</v>
@@ -93953,7 +93962,7 @@
         <v>1</v>
       </c>
       <c r="G1519" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1519" s="1">
         <v>1500</v>
@@ -93962,7 +93971,7 @@
         <v>5</v>
       </c>
       <c r="J1519" s="2" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="K1519" s="1">
         <v>0</v>
@@ -93983,7 +93992,7 @@
         <v>0</v>
       </c>
       <c r="Q1519" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="R1519" s="1">
         <v>0</v>
@@ -93994,7 +94003,7 @@
     </row>
     <row r="1520" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1520" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B1520" s="1">
         <v>12</v>
@@ -94012,16 +94021,16 @@
         <v>1</v>
       </c>
       <c r="G1520" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H1520" s="1">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="I1520" s="1">
         <v>5</v>
       </c>
       <c r="J1520" s="2" t="s">
-        <v>1414</v>
+        <v>1444</v>
       </c>
       <c r="K1520" s="1">
         <v>0</v>
@@ -94035,25 +94044,25 @@
       <c r="N1520" s="1">
         <v>0</v>
       </c>
-      <c r="O1520" s="1" t="s">
-        <v>1408</v>
+      <c r="O1520" s="1">
+        <v>0</v>
       </c>
       <c r="P1520" s="1">
         <v>0</v>
       </c>
-      <c r="Q1520" s="1">
-        <v>0</v>
+      <c r="Q1520" s="1" t="s">
+        <v>1502</v>
       </c>
       <c r="R1520" s="1">
         <v>0</v>
       </c>
       <c r="S1520" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1521" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1521" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B1521" s="1">
         <v>12</v>
@@ -94071,16 +94080,16 @@
         <v>1</v>
       </c>
       <c r="G1521" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H1521" s="1">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="I1521" s="1">
         <v>5</v>
       </c>
       <c r="J1521" s="2" t="s">
-        <v>1503</v>
+        <v>1414</v>
       </c>
       <c r="K1521" s="1">
         <v>0</v>
@@ -94094,25 +94103,25 @@
       <c r="N1521" s="1">
         <v>0</v>
       </c>
-      <c r="O1521" s="1">
-        <v>0</v>
+      <c r="O1521" s="1" t="s">
+        <v>1408</v>
       </c>
       <c r="P1521" s="1">
         <v>0</v>
       </c>
-      <c r="Q1521" s="1" t="s">
-        <v>1504</v>
+      <c r="Q1521" s="1">
+        <v>0</v>
       </c>
       <c r="R1521" s="1">
         <v>0</v>
       </c>
       <c r="S1521" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1522" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1522" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B1522" s="1">
         <v>12</v>
@@ -94130,7 +94139,7 @@
         <v>1</v>
       </c>
       <c r="G1522" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1522" s="1">
         <v>1500</v>
@@ -94160,7 +94169,7 @@
         <v>0</v>
       </c>
       <c r="Q1522" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="R1522" s="1">
         <v>0</v>
@@ -94171,7 +94180,7 @@
     </row>
     <row r="1523" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1523" s="1" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="B1523" s="1">
         <v>12</v>
@@ -94189,13 +94198,13 @@
         <v>1</v>
       </c>
       <c r="G1523" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H1523" s="1">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="I1523" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J1523" s="2" t="s">
         <v>1503</v>
@@ -94219,7 +94228,7 @@
         <v>0</v>
       </c>
       <c r="Q1523" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="R1523" s="1">
         <v>0</v>
@@ -94230,7 +94239,7 @@
     </row>
     <row r="1524" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1524" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B1524" s="1">
         <v>12</v>
@@ -94248,7 +94257,7 @@
         <v>1</v>
       </c>
       <c r="G1524" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H1524" s="1">
         <v>1350</v>
@@ -94257,7 +94266,7 @@
         <v>6</v>
       </c>
       <c r="J1524" s="2" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="K1524" s="1">
         <v>0</v>
@@ -94278,7 +94287,7 @@
         <v>0</v>
       </c>
       <c r="Q1524" s="1" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="R1524" s="1">
         <v>0</v>
@@ -94289,7 +94298,7 @@
     </row>
     <row r="1525" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1525" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B1525" s="1">
         <v>12</v>
@@ -94307,7 +94316,7 @@
         <v>1</v>
       </c>
       <c r="G1525" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H1525" s="1">
         <v>1350</v>
@@ -94316,7 +94325,7 @@
         <v>6</v>
       </c>
       <c r="J1525" s="2" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="K1525" s="1">
         <v>0</v>
@@ -94337,7 +94346,7 @@
         <v>0</v>
       </c>
       <c r="Q1525" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="R1525" s="1">
         <v>0</v>
@@ -94348,7 +94357,7 @@
     </row>
     <row r="1526" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1526" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B1526" s="1">
         <v>12</v>
@@ -94366,16 +94375,16 @@
         <v>1</v>
       </c>
       <c r="G1526" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H1526" s="1">
-        <v>500</v>
+        <v>1350</v>
       </c>
       <c r="I1526" s="1">
         <v>6</v>
       </c>
       <c r="J1526" s="2" t="s">
-        <v>1415</v>
+        <v>1503</v>
       </c>
       <c r="K1526" s="1">
         <v>0</v>
@@ -94389,25 +94398,25 @@
       <c r="N1526" s="1">
         <v>0</v>
       </c>
-      <c r="O1526" s="1" t="s">
-        <v>1409</v>
+      <c r="O1526" s="1">
+        <v>0</v>
       </c>
       <c r="P1526" s="1">
         <v>0</v>
       </c>
-      <c r="Q1526" s="1">
-        <v>0</v>
+      <c r="Q1526" s="1" t="s">
+        <v>1509</v>
       </c>
       <c r="R1526" s="1">
         <v>0</v>
       </c>
       <c r="S1526" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1527" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1527" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B1527" s="1">
         <v>12</v>
@@ -94425,16 +94434,16 @@
         <v>1</v>
       </c>
       <c r="G1527" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H1527" s="1">
-        <v>1350</v>
+        <v>500</v>
       </c>
       <c r="I1527" s="1">
         <v>6</v>
       </c>
       <c r="J1527" s="2" t="s">
-        <v>1510</v>
+        <v>1415</v>
       </c>
       <c r="K1527" s="1">
         <v>0</v>
@@ -94448,25 +94457,25 @@
       <c r="N1527" s="1">
         <v>0</v>
       </c>
-      <c r="O1527" s="1">
-        <v>0</v>
+      <c r="O1527" s="1" t="s">
+        <v>1409</v>
       </c>
       <c r="P1527" s="1">
         <v>0</v>
       </c>
-      <c r="Q1527" s="1" t="s">
-        <v>1511</v>
+      <c r="Q1527" s="1">
+        <v>0</v>
       </c>
       <c r="R1527" s="1">
         <v>0</v>
       </c>
       <c r="S1527" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1528" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1528" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B1528" s="1">
         <v>12</v>
@@ -94484,7 +94493,7 @@
         <v>1</v>
       </c>
       <c r="G1528" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H1528" s="1">
         <v>1350</v>
@@ -94514,7 +94523,7 @@
         <v>0</v>
       </c>
       <c r="Q1528" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="R1528" s="1">
         <v>0</v>
@@ -94525,7 +94534,7 @@
     </row>
     <row r="1529" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1529" s="1" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B1529" s="1">
         <v>12</v>
@@ -94543,7 +94552,7 @@
         <v>1</v>
       </c>
       <c r="G1529" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H1529" s="1">
         <v>1350</v>
@@ -94573,7 +94582,7 @@
         <v>0</v>
       </c>
       <c r="Q1529" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="R1529" s="1">
         <v>0</v>
@@ -94584,7 +94593,7 @@
     </row>
     <row r="1530" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1530" s="1" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B1530" s="1">
         <v>12</v>
@@ -94602,16 +94611,16 @@
         <v>1</v>
       </c>
       <c r="G1530" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H1530" s="1">
         <v>1350</v>
       </c>
       <c r="I1530" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J1530" s="2" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="K1530" s="1">
         <v>0</v>
@@ -94632,7 +94641,7 @@
         <v>0</v>
       </c>
       <c r="Q1530" s="1" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="R1530" s="1">
         <v>0</v>
@@ -94643,7 +94652,7 @@
     </row>
     <row r="1531" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1531" s="1" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B1531" s="1">
         <v>12</v>
@@ -94661,7 +94670,7 @@
         <v>1</v>
       </c>
       <c r="G1531" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H1531" s="1">
         <v>1350</v>
@@ -94670,7 +94679,7 @@
         <v>7</v>
       </c>
       <c r="J1531" s="2" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="K1531" s="1">
         <v>0</v>
@@ -94691,7 +94700,7 @@
         <v>0</v>
       </c>
       <c r="Q1531" s="1" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="R1531" s="1">
         <v>0</v>
@@ -94702,7 +94711,7 @@
     </row>
     <row r="1532" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1532" s="1" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B1532" s="1">
         <v>12</v>
@@ -94720,7 +94729,7 @@
         <v>1</v>
       </c>
       <c r="G1532" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H1532" s="1">
         <v>1350</v>
@@ -94729,7 +94738,7 @@
         <v>7</v>
       </c>
       <c r="J1532" s="2" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="K1532" s="1">
         <v>0</v>
@@ -94750,7 +94759,7 @@
         <v>0</v>
       </c>
       <c r="Q1532" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="R1532" s="1">
         <v>0</v>
@@ -94761,7 +94770,7 @@
     </row>
     <row r="1533" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1533" s="1" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B1533" s="1">
         <v>12</v>
@@ -94779,7 +94788,7 @@
         <v>1</v>
       </c>
       <c r="G1533" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H1533" s="1">
         <v>1350</v>
@@ -94788,7 +94797,7 @@
         <v>7</v>
       </c>
       <c r="J1533" s="2" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="K1533" s="1">
         <v>0</v>
@@ -94809,7 +94818,7 @@
         <v>0</v>
       </c>
       <c r="Q1533" s="1" t="s">
-        <v>1486</v>
+        <v>1518</v>
       </c>
       <c r="R1533" s="1">
         <v>0</v>
@@ -94820,7 +94829,7 @@
     </row>
     <row r="1534" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1534" s="1" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1534" s="1">
         <v>12</v>
@@ -94838,7 +94847,7 @@
         <v>1</v>
       </c>
       <c r="G1534" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H1534" s="1">
         <v>1350</v>
@@ -94847,7 +94856,7 @@
         <v>7</v>
       </c>
       <c r="J1534" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="K1534" s="1">
         <v>0</v>
@@ -94868,7 +94877,7 @@
         <v>0</v>
       </c>
       <c r="Q1534" s="1" t="s">
-        <v>1521</v>
+        <v>1486</v>
       </c>
       <c r="R1534" s="1">
         <v>0</v>
@@ -94879,7 +94888,7 @@
     </row>
     <row r="1535" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1535" s="1" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B1535" s="1">
         <v>12</v>
@@ -94897,7 +94906,7 @@
         <v>1</v>
       </c>
       <c r="G1535" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H1535" s="1">
         <v>1350</v>
@@ -94927,7 +94936,7 @@
         <v>0</v>
       </c>
       <c r="Q1535" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="R1535" s="1">
         <v>0</v>
@@ -94938,7 +94947,7 @@
     </row>
     <row r="1536" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1536" s="1" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B1536" s="1">
         <v>12</v>
@@ -94956,7 +94965,7 @@
         <v>1</v>
       </c>
       <c r="G1536" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H1536" s="1">
         <v>1350</v>
@@ -94986,7 +94995,7 @@
         <v>0</v>
       </c>
       <c r="Q1536" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="R1536" s="1">
         <v>0</v>
@@ -94997,7 +95006,7 @@
     </row>
     <row r="1537" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1537" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B1537" s="1">
         <v>12</v>
@@ -95015,13 +95024,13 @@
         <v>1</v>
       </c>
       <c r="G1537" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H1537" s="1">
-        <v>1</v>
+        <v>1350</v>
       </c>
       <c r="I1537" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J1537" s="2" t="s">
         <v>1520</v>
@@ -95045,7 +95054,7 @@
         <v>0</v>
       </c>
       <c r="Q1537" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="R1537" s="1">
         <v>0</v>
@@ -95056,7 +95065,7 @@
     </row>
     <row r="1538" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1538" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B1538" s="1">
         <v>12</v>
@@ -95074,16 +95083,16 @@
         <v>1</v>
       </c>
       <c r="G1538" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H1538" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1538" s="1">
         <v>8</v>
       </c>
       <c r="J1538" s="2" t="s">
-        <v>1437</v>
+        <v>1520</v>
       </c>
       <c r="K1538" s="1">
         <v>0</v>
@@ -95104,7 +95113,7 @@
         <v>0</v>
       </c>
       <c r="Q1538" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="R1538" s="1">
         <v>0</v>
@@ -95115,7 +95124,7 @@
     </row>
     <row r="1539" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1539" s="1" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B1539" s="1">
         <v>12</v>
@@ -95133,16 +95142,16 @@
         <v>1</v>
       </c>
       <c r="G1539" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H1539" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1539" s="1">
         <v>8</v>
       </c>
       <c r="J1539" s="2" t="s">
-        <v>1519</v>
+        <v>1437</v>
       </c>
       <c r="K1539" s="1">
         <v>0</v>
@@ -95163,7 +95172,7 @@
         <v>0</v>
       </c>
       <c r="Q1539" s="1" t="s">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="R1539" s="1">
         <v>0</v>
@@ -95174,7 +95183,7 @@
     </row>
     <row r="1540" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1540" s="1" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B1540" s="1">
         <v>12</v>
@@ -95192,16 +95201,16 @@
         <v>1</v>
       </c>
       <c r="G1540" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H1540" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1540" s="1">
         <v>8</v>
       </c>
       <c r="J1540" s="2" t="s">
-        <v>1437</v>
+        <v>1519</v>
       </c>
       <c r="K1540" s="1">
         <v>0</v>
@@ -95222,7 +95231,7 @@
         <v>0</v>
       </c>
       <c r="Q1540" s="1" t="s">
-        <v>1526</v>
+        <v>1500</v>
       </c>
       <c r="R1540" s="1">
         <v>0</v>
@@ -95233,7 +95242,7 @@
     </row>
     <row r="1541" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1541" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B1541" s="1">
         <v>12</v>
@@ -95251,16 +95260,16 @@
         <v>1</v>
       </c>
       <c r="G1541" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1541" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1541" s="1">
         <v>8</v>
       </c>
       <c r="J1541" s="2" t="s">
-        <v>1527</v>
+        <v>1437</v>
       </c>
       <c r="K1541" s="1">
         <v>0</v>
@@ -95281,7 +95290,7 @@
         <v>0</v>
       </c>
       <c r="Q1541" s="1" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="R1541" s="1">
         <v>0</v>
@@ -95292,7 +95301,7 @@
     </row>
     <row r="1542" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1542" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B1542" s="1">
         <v>12</v>
@@ -95310,16 +95319,16 @@
         <v>1</v>
       </c>
       <c r="G1542" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H1542" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1542" s="1">
         <v>8</v>
       </c>
       <c r="J1542" s="2" t="s">
-        <v>1437</v>
+        <v>1527</v>
       </c>
       <c r="K1542" s="1">
         <v>0</v>
@@ -95340,7 +95349,7 @@
         <v>0</v>
       </c>
       <c r="Q1542" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="R1542" s="1">
         <v>0</v>
@@ -95351,7 +95360,7 @@
     </row>
     <row r="1543" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1543" s="1" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B1543" s="1">
         <v>12</v>
@@ -95369,16 +95378,16 @@
         <v>1</v>
       </c>
       <c r="G1543" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H1543" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1543" s="1">
         <v>8</v>
       </c>
       <c r="J1543" s="2" t="s">
-        <v>1530</v>
+        <v>1437</v>
       </c>
       <c r="K1543" s="1">
         <v>0</v>
@@ -95399,7 +95408,7 @@
         <v>0</v>
       </c>
       <c r="Q1543" s="1" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="R1543" s="1">
         <v>0</v>
@@ -95410,7 +95419,7 @@
     </row>
     <row r="1544" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1544" s="1" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B1544" s="1">
         <v>12</v>
@@ -95428,16 +95437,16 @@
         <v>1</v>
       </c>
       <c r="G1544" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H1544" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1544" s="1">
         <v>8</v>
       </c>
       <c r="J1544" s="2" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="K1544" s="1">
         <v>0</v>
@@ -95458,7 +95467,7 @@
         <v>0</v>
       </c>
       <c r="Q1544" s="1" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="R1544" s="1">
         <v>0</v>
@@ -95469,7 +95478,7 @@
     </row>
     <row r="1545" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1545" s="1" t="s">
-        <v>1533</v>
+        <v>1466</v>
       </c>
       <c r="B1545" s="1">
         <v>12</v>
@@ -95487,16 +95496,16 @@
         <v>1</v>
       </c>
       <c r="G1545" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H1545" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1545" s="1">
         <v>8</v>
       </c>
       <c r="J1545" s="2" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="K1545" s="1">
         <v>0</v>
@@ -95517,7 +95526,7 @@
         <v>0</v>
       </c>
       <c r="Q1545" s="1" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="R1545" s="1">
         <v>0</v>
@@ -95528,7 +95537,7 @@
     </row>
     <row r="1546" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1546" s="1" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="B1546" s="1">
         <v>12</v>
@@ -95546,16 +95555,16 @@
         <v>1</v>
       </c>
       <c r="G1546" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H1546" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1546" s="1">
         <v>8</v>
       </c>
       <c r="J1546" s="2" t="s">
-        <v>1437</v>
+        <v>1534</v>
       </c>
       <c r="K1546" s="1">
         <v>0</v>
@@ -95576,7 +95585,7 @@
         <v>0</v>
       </c>
       <c r="Q1546" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="R1546" s="1">
         <v>0</v>
@@ -95587,7 +95596,7 @@
     </row>
     <row r="1547" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1547" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B1547" s="1">
         <v>12</v>
@@ -95605,16 +95614,16 @@
         <v>1</v>
       </c>
       <c r="G1547" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H1547" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1547" s="1">
         <v>8</v>
       </c>
       <c r="J1547" s="2" t="s">
-        <v>1537</v>
+        <v>1437</v>
       </c>
       <c r="K1547" s="1">
         <v>0</v>
@@ -95635,7 +95644,7 @@
         <v>0</v>
       </c>
       <c r="Q1547" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="R1547" s="1">
         <v>0</v>
@@ -95646,7 +95655,7 @@
     </row>
     <row r="1548" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1548" s="1" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="B1548" s="1">
         <v>12</v>
@@ -95664,16 +95673,16 @@
         <v>1</v>
       </c>
       <c r="G1548" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H1548" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1548" s="1">
         <v>8</v>
       </c>
       <c r="J1548" s="2" t="s">
-        <v>1532</v>
+        <v>1537</v>
       </c>
       <c r="K1548" s="1">
         <v>0</v>
@@ -95694,7 +95703,7 @@
         <v>0</v>
       </c>
       <c r="Q1548" s="1" t="s">
-        <v>1500</v>
+        <v>1526</v>
       </c>
       <c r="R1548" s="1">
         <v>0</v>
@@ -95705,7 +95714,7 @@
     </row>
     <row r="1549" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1549" s="1" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B1549" s="1">
         <v>12</v>
@@ -95723,16 +95732,16 @@
         <v>1</v>
       </c>
       <c r="G1549" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H1549" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1549" s="1">
         <v>8</v>
       </c>
       <c r="J1549" s="2" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="K1549" s="1">
         <v>0</v>
@@ -95753,7 +95762,7 @@
         <v>0</v>
       </c>
       <c r="Q1549" s="1" t="s">
-        <v>1540</v>
+        <v>1500</v>
       </c>
       <c r="R1549" s="1">
         <v>0</v>
@@ -95764,7 +95773,7 @@
     </row>
     <row r="1550" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1550" s="1" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="B1550" s="1">
         <v>12</v>
@@ -95782,16 +95791,16 @@
         <v>1</v>
       </c>
       <c r="G1550" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H1550" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1550" s="1">
         <v>8</v>
       </c>
       <c r="J1550" s="2" t="s">
-        <v>1437</v>
+        <v>1537</v>
       </c>
       <c r="K1550" s="1">
         <v>0</v>
@@ -95812,7 +95821,7 @@
         <v>0</v>
       </c>
       <c r="Q1550" s="1" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="R1550" s="1">
         <v>0</v>
@@ -95823,7 +95832,7 @@
     </row>
     <row r="1551" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1551" s="1" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="B1551" s="1">
         <v>12</v>
@@ -95841,16 +95850,16 @@
         <v>1</v>
       </c>
       <c r="G1551" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H1551" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1551" s="1">
         <v>8</v>
       </c>
       <c r="J1551" s="2" t="s">
-        <v>1544</v>
+        <v>1437</v>
       </c>
       <c r="K1551" s="1">
         <v>0</v>
@@ -95871,7 +95880,7 @@
         <v>0</v>
       </c>
       <c r="Q1551" s="1" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="R1551" s="1">
         <v>0</v>
@@ -95882,7 +95891,7 @@
     </row>
     <row r="1552" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1552" s="1" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="B1552" s="1">
         <v>12</v>
@@ -95900,16 +95909,16 @@
         <v>1</v>
       </c>
       <c r="G1552" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H1552" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1552" s="1">
         <v>8</v>
       </c>
       <c r="J1552" s="2" t="s">
-        <v>1532</v>
+        <v>1544</v>
       </c>
       <c r="K1552" s="1">
         <v>0</v>
@@ -95930,7 +95939,7 @@
         <v>0</v>
       </c>
       <c r="Q1552" s="1" t="s">
-        <v>1531</v>
+        <v>1545</v>
       </c>
       <c r="R1552" s="1">
         <v>0</v>
@@ -95941,7 +95950,7 @@
     </row>
     <row r="1553" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1553" s="1" t="s">
-        <v>1467</v>
+        <v>1546</v>
       </c>
       <c r="B1553" s="1">
         <v>12</v>
@@ -95959,16 +95968,16 @@
         <v>1</v>
       </c>
       <c r="G1553" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H1553" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1553" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1553" s="2" t="s">
-        <v>1547</v>
+        <v>1532</v>
       </c>
       <c r="K1553" s="1">
         <v>0</v>
@@ -95989,7 +95998,7 @@
         <v>0</v>
       </c>
       <c r="Q1553" s="1" t="s">
-        <v>1548</v>
+        <v>1531</v>
       </c>
       <c r="R1553" s="1">
         <v>0</v>
@@ -96000,7 +96009,7 @@
     </row>
     <row r="1554" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1554" s="1" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B1554" s="1">
         <v>12</v>
@@ -96018,10 +96027,10 @@
         <v>1</v>
       </c>
       <c r="G1554" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H1554" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1554" s="1">
         <v>9</v>
@@ -96048,7 +96057,7 @@
         <v>0</v>
       </c>
       <c r="Q1554" s="1" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="R1554" s="1">
         <v>0</v>
@@ -96059,7 +96068,7 @@
     </row>
     <row r="1555" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1555" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B1555" s="1">
         <v>12</v>
@@ -96077,16 +96086,16 @@
         <v>1</v>
       </c>
       <c r="G1555" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H1555" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1555" s="1">
         <v>9</v>
       </c>
       <c r="J1555" s="2" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="K1555" s="1">
         <v>0</v>
@@ -96107,7 +96116,7 @@
         <v>0</v>
       </c>
       <c r="Q1555" s="1" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="R1555" s="1">
         <v>0</v>
@@ -96118,7 +96127,7 @@
     </row>
     <row r="1556" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1556" s="1" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B1556" s="1">
         <v>12</v>
@@ -96136,16 +96145,16 @@
         <v>1</v>
       </c>
       <c r="G1556" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H1556" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1556" s="1">
         <v>9</v>
       </c>
       <c r="J1556" s="2" t="s">
-        <v>1530</v>
+        <v>1550</v>
       </c>
       <c r="K1556" s="1">
         <v>0</v>
@@ -96166,7 +96175,7 @@
         <v>0</v>
       </c>
       <c r="Q1556" s="1" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="R1556" s="1">
         <v>0</v>
@@ -96177,7 +96186,7 @@
     </row>
     <row r="1557" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1557" s="1" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B1557" s="1">
         <v>12</v>
@@ -96195,10 +96204,10 @@
         <v>1</v>
       </c>
       <c r="G1557" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H1557" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1557" s="1">
         <v>9</v>
@@ -96225,7 +96234,7 @@
         <v>0</v>
       </c>
       <c r="Q1557" s="1" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="R1557" s="1">
         <v>0</v>
@@ -96236,7 +96245,7 @@
     </row>
     <row r="1558" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1558" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B1558" s="1">
         <v>12</v>
@@ -96254,10 +96263,10 @@
         <v>1</v>
       </c>
       <c r="G1558" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H1558" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1558" s="1">
         <v>9</v>
@@ -96284,7 +96293,7 @@
         <v>0</v>
       </c>
       <c r="Q1558" s="1" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="R1558" s="1">
         <v>0</v>
@@ -96295,7 +96304,7 @@
     </row>
     <row r="1559" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1559" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B1559" s="1">
         <v>12</v>
@@ -96313,16 +96322,16 @@
         <v>1</v>
       </c>
       <c r="G1559" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H1559" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1559" s="1">
         <v>9</v>
       </c>
       <c r="J1559" s="2" t="s">
-        <v>1555</v>
+        <v>1530</v>
       </c>
       <c r="K1559" s="1">
         <v>0</v>
@@ -96343,7 +96352,7 @@
         <v>0</v>
       </c>
       <c r="Q1559" s="1" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="R1559" s="1">
         <v>0</v>
@@ -96354,7 +96363,7 @@
     </row>
     <row r="1560" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1560" s="1" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B1560" s="1">
         <v>12</v>
@@ -96372,16 +96381,16 @@
         <v>1</v>
       </c>
       <c r="G1560" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H1560" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1560" s="1">
         <v>9</v>
       </c>
       <c r="J1560" s="2" t="s">
-        <v>1530</v>
+        <v>1555</v>
       </c>
       <c r="K1560" s="1">
         <v>0</v>
@@ -96402,7 +96411,7 @@
         <v>0</v>
       </c>
       <c r="Q1560" s="1" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="R1560" s="1">
         <v>0</v>
@@ -96413,7 +96422,7 @@
     </row>
     <row r="1561" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1561" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B1561" s="1">
         <v>12</v>
@@ -96431,16 +96440,16 @@
         <v>1</v>
       </c>
       <c r="G1561" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H1561" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1561" s="1">
         <v>9</v>
       </c>
       <c r="J1561" s="2" t="s">
-        <v>1558</v>
+        <v>1530</v>
       </c>
       <c r="K1561" s="1">
         <v>0</v>
@@ -96461,7 +96470,7 @@
         <v>0</v>
       </c>
       <c r="Q1561" s="1" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="R1561" s="1">
         <v>0</v>
@@ -96472,7 +96481,7 @@
     </row>
     <row r="1562" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1562" s="1" t="s">
-        <v>1560</v>
+        <v>1475</v>
       </c>
       <c r="B1562" s="1">
         <v>12</v>
@@ -96490,16 +96499,16 @@
         <v>1</v>
       </c>
       <c r="G1562" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H1562" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1562" s="1">
         <v>9</v>
       </c>
       <c r="J1562" s="2" t="s">
-        <v>1530</v>
+        <v>1558</v>
       </c>
       <c r="K1562" s="1">
         <v>0</v>
@@ -96520,7 +96529,7 @@
         <v>0</v>
       </c>
       <c r="Q1562" s="1" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="R1562" s="1">
         <v>0</v>
@@ -96531,7 +96540,7 @@
     </row>
     <row r="1563" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1563" s="1" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="B1563" s="1">
         <v>12</v>
@@ -96549,10 +96558,10 @@
         <v>1</v>
       </c>
       <c r="G1563" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H1563" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1563" s="1">
         <v>9</v>
@@ -96579,7 +96588,7 @@
         <v>0</v>
       </c>
       <c r="Q1563" s="1" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="R1563" s="1">
         <v>0</v>
@@ -96590,7 +96599,7 @@
     </row>
     <row r="1564" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1564" s="1" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="B1564" s="1">
         <v>12</v>
@@ -96608,10 +96617,10 @@
         <v>1</v>
       </c>
       <c r="G1564" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H1564" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1564" s="1">
         <v>9</v>
@@ -96638,7 +96647,7 @@
         <v>0</v>
       </c>
       <c r="Q1564" s="1" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="R1564" s="1">
         <v>0</v>
@@ -96649,7 +96658,7 @@
     </row>
     <row r="1565" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1565" s="1" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="B1565" s="1">
         <v>12</v>
@@ -96667,16 +96676,16 @@
         <v>1</v>
       </c>
       <c r="G1565" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H1565" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1565" s="1">
         <v>9</v>
       </c>
       <c r="J1565" s="2" t="s">
-        <v>1558</v>
+        <v>1530</v>
       </c>
       <c r="K1565" s="1">
         <v>0</v>
@@ -96697,7 +96706,7 @@
         <v>0</v>
       </c>
       <c r="Q1565" s="1" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="R1565" s="1">
         <v>0</v>
@@ -96708,7 +96717,7 @@
     </row>
     <row r="1566" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1566" s="1" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="B1566" s="1">
         <v>12</v>
@@ -96726,16 +96735,16 @@
         <v>1</v>
       </c>
       <c r="G1566" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H1566" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1566" s="1">
         <v>9</v>
       </c>
       <c r="J1566" s="2" t="s">
-        <v>1530</v>
+        <v>1558</v>
       </c>
       <c r="K1566" s="1">
         <v>0</v>
@@ -96756,7 +96765,7 @@
         <v>0</v>
       </c>
       <c r="Q1566" s="1" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="R1566" s="1">
         <v>0</v>
@@ -96767,7 +96776,7 @@
     </row>
     <row r="1567" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1567" s="1" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="B1567" s="1">
         <v>12</v>
@@ -96785,10 +96794,10 @@
         <v>1</v>
       </c>
       <c r="G1567" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H1567" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1567" s="1">
         <v>9</v>
@@ -96815,7 +96824,7 @@
         <v>0</v>
       </c>
       <c r="Q1567" s="1" t="s">
-        <v>1540</v>
+        <v>1569</v>
       </c>
       <c r="R1567" s="1">
         <v>0</v>
@@ -96826,7 +96835,7 @@
     </row>
     <row r="1568" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1568" s="1" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B1568" s="1">
         <v>12</v>
@@ -96844,10 +96853,10 @@
         <v>1</v>
       </c>
       <c r="G1568" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H1568" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1568" s="1">
         <v>9</v>
@@ -96874,7 +96883,7 @@
         <v>0</v>
       </c>
       <c r="Q1568" s="1" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="R1568" s="1">
         <v>0</v>
@@ -96885,7 +96894,7 @@
     </row>
     <row r="1569" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1569" s="1" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B1569" s="1">
         <v>12</v>
@@ -96903,16 +96912,16 @@
         <v>1</v>
       </c>
       <c r="G1569" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H1569" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1569" s="1">
         <v>9</v>
       </c>
       <c r="J1569" s="2" t="s">
-        <v>1573</v>
+        <v>1530</v>
       </c>
       <c r="K1569" s="1">
         <v>0</v>
@@ -96933,7 +96942,7 @@
         <v>0</v>
       </c>
       <c r="Q1569" s="1" t="s">
-        <v>1574</v>
+        <v>1542</v>
       </c>
       <c r="R1569" s="1">
         <v>0</v>
@@ -96944,7 +96953,7 @@
     </row>
     <row r="1570" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1570" s="1" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="B1570" s="1">
         <v>12</v>
@@ -96962,16 +96971,16 @@
         <v>1</v>
       </c>
       <c r="G1570" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H1570" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1570" s="1">
         <v>9</v>
       </c>
       <c r="J1570" s="2" t="s">
-        <v>1547</v>
+        <v>1573</v>
       </c>
       <c r="K1570" s="1">
         <v>0</v>
@@ -96992,7 +97001,7 @@
         <v>0</v>
       </c>
       <c r="Q1570" s="1" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="R1570" s="1">
         <v>0</v>
@@ -97003,7 +97012,7 @@
     </row>
     <row r="1571" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1571" s="1" t="s">
-        <v>1476</v>
+        <v>1575</v>
       </c>
       <c r="B1571" s="1">
         <v>12</v>
@@ -97021,16 +97030,16 @@
         <v>1</v>
       </c>
       <c r="G1571" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H1571" s="1">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="I1571" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1571" s="2" t="s">
-        <v>1416</v>
+        <v>1547</v>
       </c>
       <c r="K1571" s="1">
         <v>0</v>
@@ -97044,25 +97053,25 @@
       <c r="N1571" s="1">
         <v>0</v>
       </c>
-      <c r="O1571" s="1" t="s">
-        <v>153</v>
+      <c r="O1571" s="1">
+        <v>0</v>
       </c>
       <c r="P1571" s="1">
         <v>0</v>
       </c>
-      <c r="Q1571" s="1">
-        <v>0</v>
+      <c r="Q1571" s="1" t="s">
+        <v>1576</v>
       </c>
       <c r="R1571" s="1">
         <v>0</v>
       </c>
       <c r="S1571" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1572" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1572" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B1572" s="1">
         <v>12</v>
@@ -97080,16 +97089,16 @@
         <v>1</v>
       </c>
       <c r="G1572" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H1572" s="1">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="I1572" s="1">
         <v>10</v>
       </c>
       <c r="J1572" s="2" t="s">
-        <v>1577</v>
+        <v>1416</v>
       </c>
       <c r="K1572" s="1">
         <v>0</v>
@@ -97103,11 +97112,11 @@
       <c r="N1572" s="1">
         <v>0</v>
       </c>
-      <c r="O1572" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1572" s="1" t="s">
-        <v>1410</v>
+      <c r="O1572" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1572" s="1">
+        <v>0</v>
       </c>
       <c r="Q1572" s="1">
         <v>0</v>
@@ -97116,12 +97125,12 @@
         <v>0</v>
       </c>
       <c r="S1572" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1573" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1573" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1573" s="1">
         <v>12</v>
@@ -97139,7 +97148,7 @@
         <v>1</v>
       </c>
       <c r="G1573" s="1">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H1573" s="1">
         <v>1500</v>
@@ -97165,11 +97174,11 @@
       <c r="O1573" s="1">
         <v>0</v>
       </c>
-      <c r="P1573" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1573" s="1" t="s">
-        <v>1486</v>
+      <c r="P1573" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="Q1573" s="1">
+        <v>0</v>
       </c>
       <c r="R1573" s="1">
         <v>0</v>
@@ -97180,7 +97189,7 @@
     </row>
     <row r="1574" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1574" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1574" s="1">
         <v>12</v>
@@ -97198,7 +97207,7 @@
         <v>1</v>
       </c>
       <c r="G1574" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H1574" s="1">
         <v>1500</v>
@@ -97207,7 +97216,7 @@
         <v>10</v>
       </c>
       <c r="J1574" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1574" s="1">
         <v>0</v>
@@ -97228,7 +97237,7 @@
         <v>0</v>
       </c>
       <c r="Q1574" s="1" t="s">
-        <v>1579</v>
+        <v>1486</v>
       </c>
       <c r="R1574" s="1">
         <v>0</v>
@@ -97239,7 +97248,7 @@
     </row>
     <row r="1575" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1575" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B1575" s="1">
         <v>12</v>
@@ -97257,7 +97266,7 @@
         <v>1</v>
       </c>
       <c r="G1575" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H1575" s="1">
         <v>1500</v>
@@ -97266,7 +97275,7 @@
         <v>10</v>
       </c>
       <c r="J1575" s="2" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K1575" s="1">
         <v>0</v>
@@ -97287,7 +97296,7 @@
         <v>0</v>
       </c>
       <c r="Q1575" s="1" t="s">
-        <v>1487</v>
+        <v>1579</v>
       </c>
       <c r="R1575" s="1">
         <v>0</v>
@@ -97298,7 +97307,7 @@
     </row>
     <row r="1576" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1576" s="1" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="B1576" s="1">
         <v>12</v>
@@ -97316,7 +97325,7 @@
         <v>1</v>
       </c>
       <c r="G1576" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H1576" s="1">
         <v>1500</v>
@@ -97325,7 +97334,7 @@
         <v>10</v>
       </c>
       <c r="J1576" s="2" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="K1576" s="1">
         <v>0</v>
@@ -97346,7 +97355,7 @@
         <v>0</v>
       </c>
       <c r="Q1576" s="1" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="R1576" s="1">
         <v>0</v>
@@ -97357,7 +97366,7 @@
     </row>
     <row r="1577" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1577" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1577" s="1">
         <v>12</v>
@@ -97375,7 +97384,7 @@
         <v>1</v>
       </c>
       <c r="G1577" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H1577" s="1">
         <v>1500</v>
@@ -97384,7 +97393,7 @@
         <v>10</v>
       </c>
       <c r="J1577" s="2" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="K1577" s="1">
         <v>0</v>
@@ -97405,7 +97414,7 @@
         <v>0</v>
       </c>
       <c r="Q1577" s="1" t="s">
-        <v>1581</v>
+        <v>1490</v>
       </c>
       <c r="R1577" s="1">
         <v>0</v>
@@ -97416,7 +97425,7 @@
     </row>
     <row r="1578" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1578" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B1578" s="1">
         <v>12</v>
@@ -97434,7 +97443,7 @@
         <v>1</v>
       </c>
       <c r="G1578" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H1578" s="1">
         <v>1500</v>
@@ -97443,7 +97452,7 @@
         <v>10</v>
       </c>
       <c r="J1578" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1578" s="1">
         <v>0</v>
@@ -97464,7 +97473,7 @@
         <v>0</v>
       </c>
       <c r="Q1578" s="1" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="R1578" s="1">
         <v>0</v>
@@ -97475,7 +97484,7 @@
     </row>
     <row r="1579" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1579" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B1579" s="1">
         <v>12</v>
@@ -97493,7 +97502,7 @@
         <v>1</v>
       </c>
       <c r="G1579" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H1579" s="1">
         <v>1500</v>
@@ -97502,7 +97511,7 @@
         <v>10</v>
       </c>
       <c r="J1579" s="2" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K1579" s="1">
         <v>0</v>
@@ -97523,7 +97532,7 @@
         <v>0</v>
       </c>
       <c r="Q1579" s="1" t="s">
-        <v>1488</v>
+        <v>1582</v>
       </c>
       <c r="R1579" s="1">
         <v>0</v>
@@ -97534,7 +97543,7 @@
     </row>
     <row r="1580" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1580" s="1" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B1580" s="1">
         <v>12</v>
@@ -97552,10 +97561,10 @@
         <v>1</v>
       </c>
       <c r="G1580" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H1580" s="1">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="I1580" s="1">
         <v>10</v>
@@ -97582,12 +97591,71 @@
         <v>0</v>
       </c>
       <c r="Q1580" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="R1580" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1580" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1581" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B1581" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1581" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1581" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1581" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1581" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1581" s="1">
+        <v>81</v>
+      </c>
+      <c r="H1581" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1581" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1581" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1581" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1581" s="1" t="s">
         <v>1491</v>
       </c>
-      <c r="R1580" s="1">
-        <v>0</v>
-      </c>
-      <c r="S1580" s="1">
+      <c r="R1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1581" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674BA40C-BD1B-48E7-973E-202ABC9337DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FE7577-6F50-4E61-B95D-0CEB77EF4FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3821" uniqueCount="1588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3827" uniqueCount="1590">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -4909,6 +4909,12 @@
   </si>
   <si>
     <t>121105,121101,121101,121101,121101</t>
+  </si>
+  <si>
+    <t>1210104</t>
+  </si>
+  <si>
+    <t>0,4000,1200</t>
   </si>
 </sst>
 </file>
@@ -5743,7 +5749,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S1581"/>
+  <dimension ref="A1:S1582"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -93021,13 +93027,13 @@
         <v>3</v>
       </c>
       <c r="H1503" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I1503" s="1">
         <v>1</v>
       </c>
       <c r="J1503" s="2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="K1503" s="1">
         <v>0</v>
@@ -93059,7 +93065,7 @@
     </row>
     <row r="1504" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1504" s="1" t="s">
-        <v>1423</v>
+        <v>1588</v>
       </c>
       <c r="B1504" s="1">
         <v>12</v>
@@ -93083,7 +93089,7 @@
         <v>2000</v>
       </c>
       <c r="I1504" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J1504" s="2" t="s">
         <v>1407</v>
@@ -93103,11 +93109,11 @@
       <c r="O1504" s="1">
         <v>0</v>
       </c>
-      <c r="P1504" s="1" t="s">
-        <v>1422</v>
-      </c>
-      <c r="Q1504" s="1">
-        <v>0</v>
+      <c r="P1504" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1504" s="1" t="s">
+        <v>1589</v>
       </c>
       <c r="R1504" s="1">
         <v>0</v>
@@ -93118,7 +93124,7 @@
     </row>
     <row r="1505" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1505" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B1505" s="1">
         <v>12</v>
@@ -93145,7 +93151,7 @@
         <v>2</v>
       </c>
       <c r="J1505" s="2" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="K1505" s="1">
         <v>0</v>
@@ -93162,11 +93168,11 @@
       <c r="O1505" s="1">
         <v>0</v>
       </c>
-      <c r="P1505" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1505" s="1" t="s">
-        <v>1486</v>
+      <c r="P1505" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="Q1505" s="1">
+        <v>0</v>
       </c>
       <c r="R1505" s="1">
         <v>0</v>
@@ -93177,7 +93183,7 @@
     </row>
     <row r="1506" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1506" s="1" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B1506" s="1">
         <v>12</v>
@@ -93225,7 +93231,7 @@
         <v>0</v>
       </c>
       <c r="Q1506" s="1" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="R1506" s="1">
         <v>0</v>
@@ -93236,7 +93242,7 @@
     </row>
     <row r="1507" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1507" s="1" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B1507" s="1">
         <v>12</v>
@@ -93284,7 +93290,7 @@
         <v>0</v>
       </c>
       <c r="Q1507" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="R1507" s="1">
         <v>0</v>
@@ -93295,7 +93301,7 @@
     </row>
     <row r="1508" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1508" s="1" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B1508" s="1">
         <v>12</v>
@@ -93316,13 +93322,13 @@
         <v>8</v>
       </c>
       <c r="H1508" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I1508" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J1508" s="2" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="K1508" s="1">
         <v>0</v>
@@ -93343,7 +93349,7 @@
         <v>0</v>
       </c>
       <c r="Q1508" s="1" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="R1508" s="1">
         <v>0</v>
@@ -93354,7 +93360,7 @@
     </row>
     <row r="1509" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1509" s="1" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B1509" s="1">
         <v>12</v>
@@ -93402,7 +93408,7 @@
         <v>0</v>
       </c>
       <c r="Q1509" s="1" t="s">
-        <v>1583</v>
+        <v>1489</v>
       </c>
       <c r="R1509" s="1">
         <v>0</v>
@@ -93413,7 +93419,7 @@
     </row>
     <row r="1510" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1510" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B1510" s="1">
         <v>12</v>
@@ -93440,7 +93446,7 @@
         <v>3</v>
       </c>
       <c r="J1510" s="2" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="K1510" s="1">
         <v>0</v>
@@ -93461,7 +93467,7 @@
         <v>0</v>
       </c>
       <c r="Q1510" s="1" t="s">
-        <v>1549</v>
+        <v>1583</v>
       </c>
       <c r="R1510" s="1">
         <v>0</v>
@@ -93472,7 +93478,7 @@
     </row>
     <row r="1511" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1511" s="1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B1511" s="1">
         <v>12</v>
@@ -93499,7 +93505,7 @@
         <v>3</v>
       </c>
       <c r="J1511" s="2" t="s">
-        <v>1587</v>
+        <v>1413</v>
       </c>
       <c r="K1511" s="1">
         <v>0</v>
@@ -93520,7 +93526,7 @@
         <v>0</v>
       </c>
       <c r="Q1511" s="1" t="s">
-        <v>1488</v>
+        <v>1549</v>
       </c>
       <c r="R1511" s="1">
         <v>0</v>
@@ -93531,7 +93537,7 @@
     </row>
     <row r="1512" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1512" s="1" t="s">
-        <v>1585</v>
+        <v>1430</v>
       </c>
       <c r="B1512" s="1">
         <v>12</v>
@@ -93558,7 +93564,7 @@
         <v>3</v>
       </c>
       <c r="J1512" s="2" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
       <c r="K1512" s="1">
         <v>0</v>
@@ -93579,7 +93585,7 @@
         <v>0</v>
       </c>
       <c r="Q1512" s="1" t="s">
-        <v>1586</v>
+        <v>1488</v>
       </c>
       <c r="R1512" s="1">
         <v>0</v>
@@ -93590,7 +93596,7 @@
     </row>
     <row r="1513" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1513" s="1" t="s">
-        <v>1431</v>
+        <v>1585</v>
       </c>
       <c r="B1513" s="1">
         <v>12</v>
@@ -93614,10 +93620,10 @@
         <v>1500</v>
       </c>
       <c r="I1513" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J1513" s="2" t="s">
-        <v>1412</v>
+        <v>1584</v>
       </c>
       <c r="K1513" s="1">
         <v>0</v>
@@ -93638,7 +93644,7 @@
         <v>0</v>
       </c>
       <c r="Q1513" s="1" t="s">
-        <v>1492</v>
+        <v>1586</v>
       </c>
       <c r="R1513" s="1">
         <v>0</v>
@@ -93649,7 +93655,7 @@
     </row>
     <row r="1514" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1514" s="1" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B1514" s="1">
         <v>12</v>
@@ -93676,7 +93682,7 @@
         <v>4</v>
       </c>
       <c r="J1514" s="2" t="s">
-        <v>1493</v>
+        <v>1412</v>
       </c>
       <c r="K1514" s="1">
         <v>0</v>
@@ -93697,7 +93703,7 @@
         <v>0</v>
       </c>
       <c r="Q1514" s="1" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="R1514" s="1">
         <v>0</v>
@@ -93708,7 +93714,7 @@
     </row>
     <row r="1515" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1515" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B1515" s="1">
         <v>12</v>
@@ -93735,7 +93741,7 @@
         <v>4</v>
       </c>
       <c r="J1515" s="2" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="K1515" s="1">
         <v>0</v>
@@ -93756,7 +93762,7 @@
         <v>0</v>
       </c>
       <c r="Q1515" s="1" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="R1515" s="1">
         <v>0</v>
@@ -93767,7 +93773,7 @@
     </row>
     <row r="1516" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1516" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B1516" s="1">
         <v>12</v>
@@ -93815,7 +93821,7 @@
         <v>0</v>
       </c>
       <c r="Q1516" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="R1516" s="1">
         <v>0</v>
@@ -93826,7 +93832,7 @@
     </row>
     <row r="1517" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1517" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B1517" s="1">
         <v>12</v>
@@ -93874,7 +93880,7 @@
         <v>0</v>
       </c>
       <c r="Q1517" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="R1517" s="1">
         <v>0</v>
@@ -93885,7 +93891,7 @@
     </row>
     <row r="1518" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1518" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B1518" s="1">
         <v>12</v>
@@ -93909,10 +93915,10 @@
         <v>1500</v>
       </c>
       <c r="I1518" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J1518" s="2" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="K1518" s="1">
         <v>0</v>
@@ -93933,7 +93939,7 @@
         <v>0</v>
       </c>
       <c r="Q1518" s="1" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="R1518" s="1">
         <v>0</v>
@@ -93944,7 +93950,7 @@
     </row>
     <row r="1519" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1519" s="1" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B1519" s="1">
         <v>12</v>
@@ -93971,7 +93977,7 @@
         <v>5</v>
       </c>
       <c r="J1519" s="2" t="s">
-        <v>1439</v>
+        <v>1499</v>
       </c>
       <c r="K1519" s="1">
         <v>0</v>
@@ -93992,7 +93998,7 @@
         <v>0</v>
       </c>
       <c r="Q1519" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="R1519" s="1">
         <v>0</v>
@@ -94003,7 +94009,7 @@
     </row>
     <row r="1520" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1520" s="1" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="B1520" s="1">
         <v>12</v>
@@ -94030,7 +94036,7 @@
         <v>5</v>
       </c>
       <c r="J1520" s="2" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="K1520" s="1">
         <v>0</v>
@@ -94051,7 +94057,7 @@
         <v>0</v>
       </c>
       <c r="Q1520" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="R1520" s="1">
         <v>0</v>
@@ -94062,7 +94068,7 @@
     </row>
     <row r="1521" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1521" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B1521" s="1">
         <v>12</v>
@@ -94083,13 +94089,13 @@
         <v>21</v>
       </c>
       <c r="H1521" s="1">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="I1521" s="1">
         <v>5</v>
       </c>
       <c r="J1521" s="2" t="s">
-        <v>1414</v>
+        <v>1444</v>
       </c>
       <c r="K1521" s="1">
         <v>0</v>
@@ -94103,25 +94109,25 @@
       <c r="N1521" s="1">
         <v>0</v>
       </c>
-      <c r="O1521" s="1" t="s">
-        <v>1408</v>
+      <c r="O1521" s="1">
+        <v>0</v>
       </c>
       <c r="P1521" s="1">
         <v>0</v>
       </c>
-      <c r="Q1521" s="1">
-        <v>0</v>
+      <c r="Q1521" s="1" t="s">
+        <v>1502</v>
       </c>
       <c r="R1521" s="1">
         <v>0</v>
       </c>
       <c r="S1521" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1522" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1522" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B1522" s="1">
         <v>12</v>
@@ -94142,13 +94148,13 @@
         <v>22</v>
       </c>
       <c r="H1522" s="1">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="I1522" s="1">
         <v>5</v>
       </c>
       <c r="J1522" s="2" t="s">
-        <v>1503</v>
+        <v>1414</v>
       </c>
       <c r="K1522" s="1">
         <v>0</v>
@@ -94162,25 +94168,25 @@
       <c r="N1522" s="1">
         <v>0</v>
       </c>
-      <c r="O1522" s="1">
-        <v>0</v>
+      <c r="O1522" s="1" t="s">
+        <v>1408</v>
       </c>
       <c r="P1522" s="1">
         <v>0</v>
       </c>
-      <c r="Q1522" s="1" t="s">
-        <v>1504</v>
+      <c r="Q1522" s="1">
+        <v>0</v>
       </c>
       <c r="R1522" s="1">
         <v>0</v>
       </c>
       <c r="S1522" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1523" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1523" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B1523" s="1">
         <v>12</v>
@@ -94228,7 +94234,7 @@
         <v>0</v>
       </c>
       <c r="Q1523" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="R1523" s="1">
         <v>0</v>
@@ -94239,7 +94245,7 @@
     </row>
     <row r="1524" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1524" s="1" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="B1524" s="1">
         <v>12</v>
@@ -94260,10 +94266,10 @@
         <v>24</v>
       </c>
       <c r="H1524" s="1">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="I1524" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J1524" s="2" t="s">
         <v>1503</v>
@@ -94287,7 +94293,7 @@
         <v>0</v>
       </c>
       <c r="Q1524" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="R1524" s="1">
         <v>0</v>
@@ -94298,7 +94304,7 @@
     </row>
     <row r="1525" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1525" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B1525" s="1">
         <v>12</v>
@@ -94325,7 +94331,7 @@
         <v>6</v>
       </c>
       <c r="J1525" s="2" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="K1525" s="1">
         <v>0</v>
@@ -94346,7 +94352,7 @@
         <v>0</v>
       </c>
       <c r="Q1525" s="1" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="R1525" s="1">
         <v>0</v>
@@ -94357,7 +94363,7 @@
     </row>
     <row r="1526" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1526" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B1526" s="1">
         <v>12</v>
@@ -94384,7 +94390,7 @@
         <v>6</v>
       </c>
       <c r="J1526" s="2" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="K1526" s="1">
         <v>0</v>
@@ -94405,7 +94411,7 @@
         <v>0</v>
       </c>
       <c r="Q1526" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="R1526" s="1">
         <v>0</v>
@@ -94416,7 +94422,7 @@
     </row>
     <row r="1527" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1527" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B1527" s="1">
         <v>12</v>
@@ -94437,13 +94443,13 @@
         <v>27</v>
       </c>
       <c r="H1527" s="1">
-        <v>500</v>
+        <v>1350</v>
       </c>
       <c r="I1527" s="1">
         <v>6</v>
       </c>
       <c r="J1527" s="2" t="s">
-        <v>1415</v>
+        <v>1503</v>
       </c>
       <c r="K1527" s="1">
         <v>0</v>
@@ -94457,25 +94463,25 @@
       <c r="N1527" s="1">
         <v>0</v>
       </c>
-      <c r="O1527" s="1" t="s">
-        <v>1409</v>
+      <c r="O1527" s="1">
+        <v>0</v>
       </c>
       <c r="P1527" s="1">
         <v>0</v>
       </c>
-      <c r="Q1527" s="1">
-        <v>0</v>
+      <c r="Q1527" s="1" t="s">
+        <v>1509</v>
       </c>
       <c r="R1527" s="1">
         <v>0</v>
       </c>
       <c r="S1527" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1528" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1528" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B1528" s="1">
         <v>12</v>
@@ -94496,13 +94502,13 @@
         <v>28</v>
       </c>
       <c r="H1528" s="1">
-        <v>1350</v>
+        <v>500</v>
       </c>
       <c r="I1528" s="1">
         <v>6</v>
       </c>
       <c r="J1528" s="2" t="s">
-        <v>1510</v>
+        <v>1415</v>
       </c>
       <c r="K1528" s="1">
         <v>0</v>
@@ -94516,25 +94522,25 @@
       <c r="N1528" s="1">
         <v>0</v>
       </c>
-      <c r="O1528" s="1">
-        <v>0</v>
+      <c r="O1528" s="1" t="s">
+        <v>1409</v>
       </c>
       <c r="P1528" s="1">
         <v>0</v>
       </c>
-      <c r="Q1528" s="1" t="s">
-        <v>1511</v>
+      <c r="Q1528" s="1">
+        <v>0</v>
       </c>
       <c r="R1528" s="1">
         <v>0</v>
       </c>
       <c r="S1528" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1529" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1529" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B1529" s="1">
         <v>12</v>
@@ -94582,7 +94588,7 @@
         <v>0</v>
       </c>
       <c r="Q1529" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="R1529" s="1">
         <v>0</v>
@@ -94593,7 +94599,7 @@
     </row>
     <row r="1530" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1530" s="1" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B1530" s="1">
         <v>12</v>
@@ -94641,7 +94647,7 @@
         <v>0</v>
       </c>
       <c r="Q1530" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="R1530" s="1">
         <v>0</v>
@@ -94652,7 +94658,7 @@
     </row>
     <row r="1531" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1531" s="1" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B1531" s="1">
         <v>12</v>
@@ -94676,10 +94682,10 @@
         <v>1350</v>
       </c>
       <c r="I1531" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J1531" s="2" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="K1531" s="1">
         <v>0</v>
@@ -94700,7 +94706,7 @@
         <v>0</v>
       </c>
       <c r="Q1531" s="1" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="R1531" s="1">
         <v>0</v>
@@ -94711,7 +94717,7 @@
     </row>
     <row r="1532" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1532" s="1" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B1532" s="1">
         <v>12</v>
@@ -94738,7 +94744,7 @@
         <v>7</v>
       </c>
       <c r="J1532" s="2" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="K1532" s="1">
         <v>0</v>
@@ -94759,7 +94765,7 @@
         <v>0</v>
       </c>
       <c r="Q1532" s="1" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="R1532" s="1">
         <v>0</v>
@@ -94770,7 +94776,7 @@
     </row>
     <row r="1533" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1533" s="1" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B1533" s="1">
         <v>12</v>
@@ -94797,7 +94803,7 @@
         <v>7</v>
       </c>
       <c r="J1533" s="2" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="K1533" s="1">
         <v>0</v>
@@ -94818,7 +94824,7 @@
         <v>0</v>
       </c>
       <c r="Q1533" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="R1533" s="1">
         <v>0</v>
@@ -94829,7 +94835,7 @@
     </row>
     <row r="1534" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1534" s="1" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B1534" s="1">
         <v>12</v>
@@ -94856,7 +94862,7 @@
         <v>7</v>
       </c>
       <c r="J1534" s="2" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="K1534" s="1">
         <v>0</v>
@@ -94877,7 +94883,7 @@
         <v>0</v>
       </c>
       <c r="Q1534" s="1" t="s">
-        <v>1486</v>
+        <v>1518</v>
       </c>
       <c r="R1534" s="1">
         <v>0</v>
@@ -94888,7 +94894,7 @@
     </row>
     <row r="1535" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1535" s="1" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1535" s="1">
         <v>12</v>
@@ -94915,7 +94921,7 @@
         <v>7</v>
       </c>
       <c r="J1535" s="2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="K1535" s="1">
         <v>0</v>
@@ -94936,7 +94942,7 @@
         <v>0</v>
       </c>
       <c r="Q1535" s="1" t="s">
-        <v>1521</v>
+        <v>1486</v>
       </c>
       <c r="R1535" s="1">
         <v>0</v>
@@ -94947,7 +94953,7 @@
     </row>
     <row r="1536" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1536" s="1" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B1536" s="1">
         <v>12</v>
@@ -94995,7 +95001,7 @@
         <v>0</v>
       </c>
       <c r="Q1536" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="R1536" s="1">
         <v>0</v>
@@ -95006,7 +95012,7 @@
     </row>
     <row r="1537" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1537" s="1" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B1537" s="1">
         <v>12</v>
@@ -95054,7 +95060,7 @@
         <v>0</v>
       </c>
       <c r="Q1537" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="R1537" s="1">
         <v>0</v>
@@ -95065,7 +95071,7 @@
     </row>
     <row r="1538" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1538" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B1538" s="1">
         <v>12</v>
@@ -95086,10 +95092,10 @@
         <v>38</v>
       </c>
       <c r="H1538" s="1">
-        <v>1</v>
+        <v>1350</v>
       </c>
       <c r="I1538" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J1538" s="2" t="s">
         <v>1520</v>
@@ -95113,7 +95119,7 @@
         <v>0</v>
       </c>
       <c r="Q1538" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="R1538" s="1">
         <v>0</v>
@@ -95124,7 +95130,7 @@
     </row>
     <row r="1539" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1539" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B1539" s="1">
         <v>12</v>
@@ -95145,13 +95151,13 @@
         <v>39</v>
       </c>
       <c r="H1539" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1539" s="1">
         <v>8</v>
       </c>
       <c r="J1539" s="2" t="s">
-        <v>1437</v>
+        <v>1520</v>
       </c>
       <c r="K1539" s="1">
         <v>0</v>
@@ -95172,7 +95178,7 @@
         <v>0</v>
       </c>
       <c r="Q1539" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="R1539" s="1">
         <v>0</v>
@@ -95183,7 +95189,7 @@
     </row>
     <row r="1540" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1540" s="1" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B1540" s="1">
         <v>12</v>
@@ -95204,13 +95210,13 @@
         <v>40</v>
       </c>
       <c r="H1540" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1540" s="1">
         <v>8</v>
       </c>
       <c r="J1540" s="2" t="s">
-        <v>1519</v>
+        <v>1437</v>
       </c>
       <c r="K1540" s="1">
         <v>0</v>
@@ -95231,7 +95237,7 @@
         <v>0</v>
       </c>
       <c r="Q1540" s="1" t="s">
-        <v>1500</v>
+        <v>1525</v>
       </c>
       <c r="R1540" s="1">
         <v>0</v>
@@ -95242,7 +95248,7 @@
     </row>
     <row r="1541" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1541" s="1" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B1541" s="1">
         <v>12</v>
@@ -95263,13 +95269,13 @@
         <v>41</v>
       </c>
       <c r="H1541" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1541" s="1">
         <v>8</v>
       </c>
       <c r="J1541" s="2" t="s">
-        <v>1437</v>
+        <v>1519</v>
       </c>
       <c r="K1541" s="1">
         <v>0</v>
@@ -95290,7 +95296,7 @@
         <v>0</v>
       </c>
       <c r="Q1541" s="1" t="s">
-        <v>1526</v>
+        <v>1500</v>
       </c>
       <c r="R1541" s="1">
         <v>0</v>
@@ -95301,7 +95307,7 @@
     </row>
     <row r="1542" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1542" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B1542" s="1">
         <v>12</v>
@@ -95322,13 +95328,13 @@
         <v>42</v>
       </c>
       <c r="H1542" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1542" s="1">
         <v>8</v>
       </c>
       <c r="J1542" s="2" t="s">
-        <v>1527</v>
+        <v>1437</v>
       </c>
       <c r="K1542" s="1">
         <v>0</v>
@@ -95349,7 +95355,7 @@
         <v>0</v>
       </c>
       <c r="Q1542" s="1" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="R1542" s="1">
         <v>0</v>
@@ -95360,7 +95366,7 @@
     </row>
     <row r="1543" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1543" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B1543" s="1">
         <v>12</v>
@@ -95381,13 +95387,13 @@
         <v>43</v>
       </c>
       <c r="H1543" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1543" s="1">
         <v>8</v>
       </c>
       <c r="J1543" s="2" t="s">
-        <v>1437</v>
+        <v>1527</v>
       </c>
       <c r="K1543" s="1">
         <v>0</v>
@@ -95408,7 +95414,7 @@
         <v>0</v>
       </c>
       <c r="Q1543" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="R1543" s="1">
         <v>0</v>
@@ -95419,7 +95425,7 @@
     </row>
     <row r="1544" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1544" s="1" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B1544" s="1">
         <v>12</v>
@@ -95440,13 +95446,13 @@
         <v>44</v>
       </c>
       <c r="H1544" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1544" s="1">
         <v>8</v>
       </c>
       <c r="J1544" s="2" t="s">
-        <v>1530</v>
+        <v>1437</v>
       </c>
       <c r="K1544" s="1">
         <v>0</v>
@@ -95467,7 +95473,7 @@
         <v>0</v>
       </c>
       <c r="Q1544" s="1" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="R1544" s="1">
         <v>0</v>
@@ -95478,7 +95484,7 @@
     </row>
     <row r="1545" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1545" s="1" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B1545" s="1">
         <v>12</v>
@@ -95499,13 +95505,13 @@
         <v>45</v>
       </c>
       <c r="H1545" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1545" s="1">
         <v>8</v>
       </c>
       <c r="J1545" s="2" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="K1545" s="1">
         <v>0</v>
@@ -95526,7 +95532,7 @@
         <v>0</v>
       </c>
       <c r="Q1545" s="1" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="R1545" s="1">
         <v>0</v>
@@ -95537,7 +95543,7 @@
     </row>
     <row r="1546" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1546" s="1" t="s">
-        <v>1533</v>
+        <v>1466</v>
       </c>
       <c r="B1546" s="1">
         <v>12</v>
@@ -95558,13 +95564,13 @@
         <v>46</v>
       </c>
       <c r="H1546" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1546" s="1">
         <v>8</v>
       </c>
       <c r="J1546" s="2" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="K1546" s="1">
         <v>0</v>
@@ -95585,7 +95591,7 @@
         <v>0</v>
       </c>
       <c r="Q1546" s="1" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="R1546" s="1">
         <v>0</v>
@@ -95596,7 +95602,7 @@
     </row>
     <row r="1547" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1547" s="1" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="B1547" s="1">
         <v>12</v>
@@ -95617,13 +95623,13 @@
         <v>47</v>
       </c>
       <c r="H1547" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1547" s="1">
         <v>8</v>
       </c>
       <c r="J1547" s="2" t="s">
-        <v>1437</v>
+        <v>1534</v>
       </c>
       <c r="K1547" s="1">
         <v>0</v>
@@ -95644,7 +95650,7 @@
         <v>0</v>
       </c>
       <c r="Q1547" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="R1547" s="1">
         <v>0</v>
@@ -95655,7 +95661,7 @@
     </row>
     <row r="1548" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1548" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B1548" s="1">
         <v>12</v>
@@ -95676,13 +95682,13 @@
         <v>48</v>
       </c>
       <c r="H1548" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1548" s="1">
         <v>8</v>
       </c>
       <c r="J1548" s="2" t="s">
-        <v>1537</v>
+        <v>1437</v>
       </c>
       <c r="K1548" s="1">
         <v>0</v>
@@ -95703,7 +95709,7 @@
         <v>0</v>
       </c>
       <c r="Q1548" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="R1548" s="1">
         <v>0</v>
@@ -95714,7 +95720,7 @@
     </row>
     <row r="1549" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1549" s="1" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="B1549" s="1">
         <v>12</v>
@@ -95735,13 +95741,13 @@
         <v>49</v>
       </c>
       <c r="H1549" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1549" s="1">
         <v>8</v>
       </c>
       <c r="J1549" s="2" t="s">
-        <v>1532</v>
+        <v>1537</v>
       </c>
       <c r="K1549" s="1">
         <v>0</v>
@@ -95762,7 +95768,7 @@
         <v>0</v>
       </c>
       <c r="Q1549" s="1" t="s">
-        <v>1500</v>
+        <v>1526</v>
       </c>
       <c r="R1549" s="1">
         <v>0</v>
@@ -95773,7 +95779,7 @@
     </row>
     <row r="1550" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1550" s="1" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B1550" s="1">
         <v>12</v>
@@ -95794,13 +95800,13 @@
         <v>50</v>
       </c>
       <c r="H1550" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1550" s="1">
         <v>8</v>
       </c>
       <c r="J1550" s="2" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="K1550" s="1">
         <v>0</v>
@@ -95821,7 +95827,7 @@
         <v>0</v>
       </c>
       <c r="Q1550" s="1" t="s">
-        <v>1540</v>
+        <v>1500</v>
       </c>
       <c r="R1550" s="1">
         <v>0</v>
@@ -95832,7 +95838,7 @@
     </row>
     <row r="1551" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1551" s="1" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="B1551" s="1">
         <v>12</v>
@@ -95853,13 +95859,13 @@
         <v>51</v>
       </c>
       <c r="H1551" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1551" s="1">
         <v>8</v>
       </c>
       <c r="J1551" s="2" t="s">
-        <v>1437</v>
+        <v>1537</v>
       </c>
       <c r="K1551" s="1">
         <v>0</v>
@@ -95880,7 +95886,7 @@
         <v>0</v>
       </c>
       <c r="Q1551" s="1" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="R1551" s="1">
         <v>0</v>
@@ -95891,7 +95897,7 @@
     </row>
     <row r="1552" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1552" s="1" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="B1552" s="1">
         <v>12</v>
@@ -95912,13 +95918,13 @@
         <v>52</v>
       </c>
       <c r="H1552" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1552" s="1">
         <v>8</v>
       </c>
       <c r="J1552" s="2" t="s">
-        <v>1544</v>
+        <v>1437</v>
       </c>
       <c r="K1552" s="1">
         <v>0</v>
@@ -95939,7 +95945,7 @@
         <v>0</v>
       </c>
       <c r="Q1552" s="1" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="R1552" s="1">
         <v>0</v>
@@ -95950,7 +95956,7 @@
     </row>
     <row r="1553" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1553" s="1" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="B1553" s="1">
         <v>12</v>
@@ -95971,13 +95977,13 @@
         <v>53</v>
       </c>
       <c r="H1553" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1553" s="1">
         <v>8</v>
       </c>
       <c r="J1553" s="2" t="s">
-        <v>1532</v>
+        <v>1544</v>
       </c>
       <c r="K1553" s="1">
         <v>0</v>
@@ -95998,7 +96004,7 @@
         <v>0</v>
       </c>
       <c r="Q1553" s="1" t="s">
-        <v>1531</v>
+        <v>1545</v>
       </c>
       <c r="R1553" s="1">
         <v>0</v>
@@ -96009,7 +96015,7 @@
     </row>
     <row r="1554" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1554" s="1" t="s">
-        <v>1467</v>
+        <v>1546</v>
       </c>
       <c r="B1554" s="1">
         <v>12</v>
@@ -96030,13 +96036,13 @@
         <v>54</v>
       </c>
       <c r="H1554" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1554" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J1554" s="2" t="s">
-        <v>1547</v>
+        <v>1532</v>
       </c>
       <c r="K1554" s="1">
         <v>0</v>
@@ -96057,7 +96063,7 @@
         <v>0</v>
       </c>
       <c r="Q1554" s="1" t="s">
-        <v>1548</v>
+        <v>1531</v>
       </c>
       <c r="R1554" s="1">
         <v>0</v>
@@ -96068,7 +96074,7 @@
     </row>
     <row r="1555" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1555" s="1" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B1555" s="1">
         <v>12</v>
@@ -96089,7 +96095,7 @@
         <v>55</v>
       </c>
       <c r="H1555" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1555" s="1">
         <v>9</v>
@@ -96116,7 +96122,7 @@
         <v>0</v>
       </c>
       <c r="Q1555" s="1" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="R1555" s="1">
         <v>0</v>
@@ -96127,7 +96133,7 @@
     </row>
     <row r="1556" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1556" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B1556" s="1">
         <v>12</v>
@@ -96148,13 +96154,13 @@
         <v>56</v>
       </c>
       <c r="H1556" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1556" s="1">
         <v>9</v>
       </c>
       <c r="J1556" s="2" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="K1556" s="1">
         <v>0</v>
@@ -96175,7 +96181,7 @@
         <v>0</v>
       </c>
       <c r="Q1556" s="1" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="R1556" s="1">
         <v>0</v>
@@ -96186,7 +96192,7 @@
     </row>
     <row r="1557" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1557" s="1" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B1557" s="1">
         <v>12</v>
@@ -96207,13 +96213,13 @@
         <v>57</v>
       </c>
       <c r="H1557" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1557" s="1">
         <v>9</v>
       </c>
       <c r="J1557" s="2" t="s">
-        <v>1530</v>
+        <v>1550</v>
       </c>
       <c r="K1557" s="1">
         <v>0</v>
@@ -96234,7 +96240,7 @@
         <v>0</v>
       </c>
       <c r="Q1557" s="1" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="R1557" s="1">
         <v>0</v>
@@ -96245,7 +96251,7 @@
     </row>
     <row r="1558" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1558" s="1" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B1558" s="1">
         <v>12</v>
@@ -96266,7 +96272,7 @@
         <v>58</v>
       </c>
       <c r="H1558" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1558" s="1">
         <v>9</v>
@@ -96293,7 +96299,7 @@
         <v>0</v>
       </c>
       <c r="Q1558" s="1" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="R1558" s="1">
         <v>0</v>
@@ -96304,7 +96310,7 @@
     </row>
     <row r="1559" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1559" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B1559" s="1">
         <v>12</v>
@@ -96325,7 +96331,7 @@
         <v>59</v>
       </c>
       <c r="H1559" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1559" s="1">
         <v>9</v>
@@ -96352,7 +96358,7 @@
         <v>0</v>
       </c>
       <c r="Q1559" s="1" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="R1559" s="1">
         <v>0</v>
@@ -96363,7 +96369,7 @@
     </row>
     <row r="1560" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1560" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B1560" s="1">
         <v>12</v>
@@ -96384,13 +96390,13 @@
         <v>60</v>
       </c>
       <c r="H1560" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1560" s="1">
         <v>9</v>
       </c>
       <c r="J1560" s="2" t="s">
-        <v>1555</v>
+        <v>1530</v>
       </c>
       <c r="K1560" s="1">
         <v>0</v>
@@ -96411,7 +96417,7 @@
         <v>0</v>
       </c>
       <c r="Q1560" s="1" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="R1560" s="1">
         <v>0</v>
@@ -96422,7 +96428,7 @@
     </row>
     <row r="1561" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1561" s="1" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B1561" s="1">
         <v>12</v>
@@ -96443,13 +96449,13 @@
         <v>61</v>
       </c>
       <c r="H1561" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1561" s="1">
         <v>9</v>
       </c>
       <c r="J1561" s="2" t="s">
-        <v>1530</v>
+        <v>1555</v>
       </c>
       <c r="K1561" s="1">
         <v>0</v>
@@ -96470,7 +96476,7 @@
         <v>0</v>
       </c>
       <c r="Q1561" s="1" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="R1561" s="1">
         <v>0</v>
@@ -96481,7 +96487,7 @@
     </row>
     <row r="1562" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1562" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B1562" s="1">
         <v>12</v>
@@ -96502,13 +96508,13 @@
         <v>62</v>
       </c>
       <c r="H1562" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1562" s="1">
         <v>9</v>
       </c>
       <c r="J1562" s="2" t="s">
-        <v>1558</v>
+        <v>1530</v>
       </c>
       <c r="K1562" s="1">
         <v>0</v>
@@ -96529,7 +96535,7 @@
         <v>0</v>
       </c>
       <c r="Q1562" s="1" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="R1562" s="1">
         <v>0</v>
@@ -96540,7 +96546,7 @@
     </row>
     <row r="1563" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1563" s="1" t="s">
-        <v>1560</v>
+        <v>1475</v>
       </c>
       <c r="B1563" s="1">
         <v>12</v>
@@ -96561,13 +96567,13 @@
         <v>63</v>
       </c>
       <c r="H1563" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1563" s="1">
         <v>9</v>
       </c>
       <c r="J1563" s="2" t="s">
-        <v>1530</v>
+        <v>1558</v>
       </c>
       <c r="K1563" s="1">
         <v>0</v>
@@ -96588,7 +96594,7 @@
         <v>0</v>
       </c>
       <c r="Q1563" s="1" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="R1563" s="1">
         <v>0</v>
@@ -96599,7 +96605,7 @@
     </row>
     <row r="1564" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1564" s="1" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="B1564" s="1">
         <v>12</v>
@@ -96620,7 +96626,7 @@
         <v>64</v>
       </c>
       <c r="H1564" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1564" s="1">
         <v>9</v>
@@ -96647,7 +96653,7 @@
         <v>0</v>
       </c>
       <c r="Q1564" s="1" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="R1564" s="1">
         <v>0</v>
@@ -96658,7 +96664,7 @@
     </row>
     <row r="1565" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1565" s="1" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="B1565" s="1">
         <v>12</v>
@@ -96679,7 +96685,7 @@
         <v>65</v>
       </c>
       <c r="H1565" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1565" s="1">
         <v>9</v>
@@ -96706,7 +96712,7 @@
         <v>0</v>
       </c>
       <c r="Q1565" s="1" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="R1565" s="1">
         <v>0</v>
@@ -96717,7 +96723,7 @@
     </row>
     <row r="1566" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1566" s="1" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="B1566" s="1">
         <v>12</v>
@@ -96738,13 +96744,13 @@
         <v>66</v>
       </c>
       <c r="H1566" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1566" s="1">
         <v>9</v>
       </c>
       <c r="J1566" s="2" t="s">
-        <v>1558</v>
+        <v>1530</v>
       </c>
       <c r="K1566" s="1">
         <v>0</v>
@@ -96765,7 +96771,7 @@
         <v>0</v>
       </c>
       <c r="Q1566" s="1" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="R1566" s="1">
         <v>0</v>
@@ -96776,7 +96782,7 @@
     </row>
     <row r="1567" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1567" s="1" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="B1567" s="1">
         <v>12</v>
@@ -96797,13 +96803,13 @@
         <v>67</v>
       </c>
       <c r="H1567" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1567" s="1">
         <v>9</v>
       </c>
       <c r="J1567" s="2" t="s">
-        <v>1530</v>
+        <v>1558</v>
       </c>
       <c r="K1567" s="1">
         <v>0</v>
@@ -96824,7 +96830,7 @@
         <v>0</v>
       </c>
       <c r="Q1567" s="1" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="R1567" s="1">
         <v>0</v>
@@ -96835,7 +96841,7 @@
     </row>
     <row r="1568" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1568" s="1" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="B1568" s="1">
         <v>12</v>
@@ -96856,7 +96862,7 @@
         <v>68</v>
       </c>
       <c r="H1568" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1568" s="1">
         <v>9</v>
@@ -96883,7 +96889,7 @@
         <v>0</v>
       </c>
       <c r="Q1568" s="1" t="s">
-        <v>1540</v>
+        <v>1569</v>
       </c>
       <c r="R1568" s="1">
         <v>0</v>
@@ -96894,7 +96900,7 @@
     </row>
     <row r="1569" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1569" s="1" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B1569" s="1">
         <v>12</v>
@@ -96915,7 +96921,7 @@
         <v>69</v>
       </c>
       <c r="H1569" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1569" s="1">
         <v>9</v>
@@ -96942,7 +96948,7 @@
         <v>0</v>
       </c>
       <c r="Q1569" s="1" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="R1569" s="1">
         <v>0</v>
@@ -96953,7 +96959,7 @@
     </row>
     <row r="1570" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1570" s="1" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B1570" s="1">
         <v>12</v>
@@ -96974,13 +96980,13 @@
         <v>70</v>
       </c>
       <c r="H1570" s="1">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="I1570" s="1">
         <v>9</v>
       </c>
       <c r="J1570" s="2" t="s">
-        <v>1573</v>
+        <v>1530</v>
       </c>
       <c r="K1570" s="1">
         <v>0</v>
@@ -97001,7 +97007,7 @@
         <v>0</v>
       </c>
       <c r="Q1570" s="1" t="s">
-        <v>1574</v>
+        <v>1542</v>
       </c>
       <c r="R1570" s="1">
         <v>0</v>
@@ -97012,7 +97018,7 @@
     </row>
     <row r="1571" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1571" s="1" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="B1571" s="1">
         <v>12</v>
@@ -97033,13 +97039,13 @@
         <v>71</v>
       </c>
       <c r="H1571" s="1">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I1571" s="1">
         <v>9</v>
       </c>
       <c r="J1571" s="2" t="s">
-        <v>1547</v>
+        <v>1573</v>
       </c>
       <c r="K1571" s="1">
         <v>0</v>
@@ -97060,7 +97066,7 @@
         <v>0</v>
       </c>
       <c r="Q1571" s="1" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="R1571" s="1">
         <v>0</v>
@@ -97071,7 +97077,7 @@
     </row>
     <row r="1572" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1572" s="1" t="s">
-        <v>1476</v>
+        <v>1575</v>
       </c>
       <c r="B1572" s="1">
         <v>12</v>
@@ -97092,13 +97098,13 @@
         <v>72</v>
       </c>
       <c r="H1572" s="1">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="I1572" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J1572" s="2" t="s">
-        <v>1416</v>
+        <v>1547</v>
       </c>
       <c r="K1572" s="1">
         <v>0</v>
@@ -97112,25 +97118,25 @@
       <c r="N1572" s="1">
         <v>0</v>
       </c>
-      <c r="O1572" s="1" t="s">
-        <v>153</v>
+      <c r="O1572" s="1">
+        <v>0</v>
       </c>
       <c r="P1572" s="1">
         <v>0</v>
       </c>
-      <c r="Q1572" s="1">
-        <v>0</v>
+      <c r="Q1572" s="1" t="s">
+        <v>1576</v>
       </c>
       <c r="R1572" s="1">
         <v>0</v>
       </c>
       <c r="S1572" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1573" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1573" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="B1573" s="1">
         <v>12</v>
@@ -97151,13 +97157,13 @@
         <v>73</v>
       </c>
       <c r="H1573" s="1">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="I1573" s="1">
         <v>10</v>
       </c>
       <c r="J1573" s="2" t="s">
-        <v>1577</v>
+        <v>1416</v>
       </c>
       <c r="K1573" s="1">
         <v>0</v>
@@ -97171,11 +97177,11 @@
       <c r="N1573" s="1">
         <v>0</v>
       </c>
-      <c r="O1573" s="1">
-        <v>0</v>
-      </c>
-      <c r="P1573" s="1" t="s">
-        <v>1410</v>
+      <c r="O1573" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1573" s="1">
+        <v>0</v>
       </c>
       <c r="Q1573" s="1">
         <v>0</v>
@@ -97184,12 +97190,12 @@
         <v>0</v>
       </c>
       <c r="S1573" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1574" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1574" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B1574" s="1">
         <v>12</v>
@@ -97233,11 +97239,11 @@
       <c r="O1574" s="1">
         <v>0</v>
       </c>
-      <c r="P1574" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q1574" s="1" t="s">
-        <v>1486</v>
+      <c r="P1574" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="Q1574" s="1">
+        <v>0</v>
       </c>
       <c r="R1574" s="1">
         <v>0</v>
@@ -97248,7 +97254,7 @@
     </row>
     <row r="1575" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1575" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1575" s="1">
         <v>12</v>
@@ -97275,7 +97281,7 @@
         <v>10</v>
       </c>
       <c r="J1575" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1575" s="1">
         <v>0</v>
@@ -97296,7 +97302,7 @@
         <v>0</v>
       </c>
       <c r="Q1575" s="1" t="s">
-        <v>1579</v>
+        <v>1486</v>
       </c>
       <c r="R1575" s="1">
         <v>0</v>
@@ -97307,7 +97313,7 @@
     </row>
     <row r="1576" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1576" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B1576" s="1">
         <v>12</v>
@@ -97334,7 +97340,7 @@
         <v>10</v>
       </c>
       <c r="J1576" s="2" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K1576" s="1">
         <v>0</v>
@@ -97355,7 +97361,7 @@
         <v>0</v>
       </c>
       <c r="Q1576" s="1" t="s">
-        <v>1487</v>
+        <v>1579</v>
       </c>
       <c r="R1576" s="1">
         <v>0</v>
@@ -97366,7 +97372,7 @@
     </row>
     <row r="1577" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1577" s="1" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="B1577" s="1">
         <v>12</v>
@@ -97393,7 +97399,7 @@
         <v>10</v>
       </c>
       <c r="J1577" s="2" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="K1577" s="1">
         <v>0</v>
@@ -97414,7 +97420,7 @@
         <v>0</v>
       </c>
       <c r="Q1577" s="1" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="R1577" s="1">
         <v>0</v>
@@ -97425,7 +97431,7 @@
     </row>
     <row r="1578" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1578" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1578" s="1">
         <v>12</v>
@@ -97452,7 +97458,7 @@
         <v>10</v>
       </c>
       <c r="J1578" s="2" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="K1578" s="1">
         <v>0</v>
@@ -97473,7 +97479,7 @@
         <v>0</v>
       </c>
       <c r="Q1578" s="1" t="s">
-        <v>1581</v>
+        <v>1490</v>
       </c>
       <c r="R1578" s="1">
         <v>0</v>
@@ -97484,7 +97490,7 @@
     </row>
     <row r="1579" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1579" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B1579" s="1">
         <v>12</v>
@@ -97511,7 +97517,7 @@
         <v>10</v>
       </c>
       <c r="J1579" s="2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="K1579" s="1">
         <v>0</v>
@@ -97532,7 +97538,7 @@
         <v>0</v>
       </c>
       <c r="Q1579" s="1" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="R1579" s="1">
         <v>0</v>
@@ -97543,7 +97549,7 @@
     </row>
     <row r="1580" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1580" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B1580" s="1">
         <v>12</v>
@@ -97570,7 +97576,7 @@
         <v>10</v>
       </c>
       <c r="J1580" s="2" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="K1580" s="1">
         <v>0</v>
@@ -97591,7 +97597,7 @@
         <v>0</v>
       </c>
       <c r="Q1580" s="1" t="s">
-        <v>1488</v>
+        <v>1582</v>
       </c>
       <c r="R1580" s="1">
         <v>0</v>
@@ -97602,7 +97608,7 @@
     </row>
     <row r="1581" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1581" s="1" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B1581" s="1">
         <v>12</v>
@@ -97623,7 +97629,7 @@
         <v>81</v>
       </c>
       <c r="H1581" s="1">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="I1581" s="1">
         <v>10</v>
@@ -97650,12 +97656,71 @@
         <v>0</v>
       </c>
       <c r="Q1581" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="R1581" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1581" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1582" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B1582" s="1">
+        <v>12</v>
+      </c>
+      <c r="C1582" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D1582" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1582" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F1582" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1582" s="1">
+        <v>82</v>
+      </c>
+      <c r="H1582" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1582" s="1">
+        <v>10</v>
+      </c>
+      <c r="J1582" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K1582" s="1">
+        <v>0</v>
+      </c>
+      <c r="L1582" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1582" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1582" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1582" s="1">
+        <v>0</v>
+      </c>
+      <c r="P1582" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1582" s="1" t="s">
         <v>1491</v>
       </c>
-      <c r="R1581" s="1">
-        <v>0</v>
-      </c>
-      <c r="S1581" s="1">
+      <c r="R1582" s="1">
+        <v>0</v>
+      </c>
+      <c r="S1582" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FE7577-6F50-4E61-B95D-0CEB77EF4FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA155AEC-7CE1-449C-9D28-1ADBE4CB598B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4605,144 +4605,42 @@
     <t>1211010</t>
   </si>
   <si>
-    <t>0,4500,1800</t>
-  </si>
-  <si>
-    <t>90,4500,1800</t>
-  </si>
-  <si>
-    <t>270,4500,1800</t>
-  </si>
-  <si>
-    <t>45,4500,1800</t>
-  </si>
-  <si>
-    <t>135,4500,1800</t>
-  </si>
-  <si>
-    <t>315,4500,1800</t>
-  </si>
-  <si>
-    <t>30,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121101,121101,121101,121101,121104</t>
   </si>
   <si>
-    <t>102,5500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>174,4500,1800</t>
-  </si>
-  <si>
-    <t>246,4500,1800</t>
-  </si>
-  <si>
-    <t>318,4500,1800</t>
-  </si>
-  <si>
     <t>121101,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>70,4500,1800</t>
-  </si>
-  <si>
-    <t>142,5500,1800</t>
-  </si>
-  <si>
-    <t>214,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>286,4500,1800</t>
-  </si>
-  <si>
-    <t>358,4500,1800</t>
-  </si>
-  <si>
-    <t>50,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121101,121101,121101,121101,121104,121101,121104</t>
   </si>
   <si>
-    <t>110,5500,1800</t>
-  </si>
-  <si>
-    <t>170,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>230,4500,1800</t>
-  </si>
-  <si>
-    <t>290,4500,1800</t>
-  </si>
-  <si>
-    <t>350,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>204,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121105,121101,121101,121101,121104,121104,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>256,5500,1800</t>
-  </si>
-  <si>
-    <t>308,4500,1800</t>
-  </si>
-  <si>
     <t>121102,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
     <t>121105,121105,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>52,4500,1800</t>
-  </si>
-  <si>
-    <t>104,4500,1800</t>
-  </si>
-  <si>
-    <t>156,4500,1800</t>
-  </si>
-  <si>
-    <t>25,4500,1800</t>
-  </si>
-  <si>
-    <t>205,4500,1800</t>
-  </si>
-  <si>
-    <t>250,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121105,121105,121101,121101,121101,121101,121104,121104,121101,121101</t>
   </si>
   <si>
-    <t>115,5500,1800</t>
-  </si>
-  <si>
-    <t>295,5500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>160,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121105,121101,121101,121101</t>
   </si>
   <si>
@@ -4767,96 +4665,45 @@
     <t>1210813</t>
   </si>
   <si>
-    <t>295,4500,1800</t>
-  </si>
-  <si>
     <t>1210814</t>
   </si>
   <si>
-    <t>115,4500,1800</t>
-  </si>
-  <si>
     <t>1210815</t>
   </si>
   <si>
     <t>121102,121105,121105,121105,121105,121105,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>340,4500,1800</t>
-  </si>
-  <si>
     <t>1210816</t>
   </si>
   <si>
     <t>121105,121105,121105,121105,121105,121105,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>15,4500,1800</t>
-  </si>
-  <si>
-    <t>195,4500,1800</t>
-  </si>
-  <si>
     <t>121102,121102,121101,121101,121101,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>55,4500,1800</t>
-  </si>
-  <si>
-    <t>235,4500,1800</t>
-  </si>
-  <si>
-    <t>95,4500,1800</t>
-  </si>
-  <si>
-    <t>275,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121105,121105,121101,121101,121101,121101,121101,121104,121104,121101</t>
   </si>
   <si>
-    <t>135,5500,1800</t>
-  </si>
-  <si>
-    <t>315,5500,1800</t>
-  </si>
-  <si>
     <t>121102,121105,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>175,4500,1800</t>
-  </si>
-  <si>
     <t>1210910</t>
   </si>
   <si>
-    <t>355,4500,1800</t>
-  </si>
-  <si>
     <t>1210911</t>
   </si>
   <si>
-    <t>215,4500,1800</t>
-  </si>
-  <si>
     <t>1210912</t>
   </si>
   <si>
-    <t>35,4500,1800</t>
-  </si>
-  <si>
     <t>1210913</t>
   </si>
   <si>
-    <t>255,4500,1800</t>
-  </si>
-  <si>
     <t>1210914</t>
   </si>
   <si>
-    <t>75,4500,1800</t>
-  </si>
-  <si>
     <t>1210915</t>
   </si>
   <si>
@@ -4869,52 +4716,205 @@
     <t>121102,121102,121105,121105,121101,121101,121101,121101,121101,121101,121101,121101</t>
   </si>
   <si>
-    <t>335,4500,1800</t>
-  </si>
-  <si>
     <t>1210918</t>
   </si>
   <si>
-    <t>155,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121105,121105,121105,121105,121105,121101,121101,121101</t>
   </si>
   <si>
     <t>121104,121104,121105,121105,121101,121101,121101</t>
   </si>
   <si>
-    <t>45,5500,1800</t>
-  </si>
-  <si>
     <t>121102,121102,121101,121101,121101</t>
   </si>
   <si>
-    <t>180,4500,1800</t>
-  </si>
-  <si>
-    <t>225,5500,1800</t>
-  </si>
-  <si>
-    <t>120,4500,1800</t>
-  </si>
-  <si>
     <t>121101,121101,121101,121101,121101</t>
   </si>
   <si>
     <t>1210305</t>
   </si>
   <si>
-    <t>345,4500,1800</t>
-  </si>
-  <si>
     <t>121105,121101,121101,121101,121101</t>
   </si>
   <si>
     <t>1210104</t>
   </si>
   <si>
-    <t>0,4000,1200</t>
+    <t>0,4000,1600</t>
+  </si>
+  <si>
+    <t>0,5500,2400</t>
+  </si>
+  <si>
+    <t>90,5500,2400</t>
+  </si>
+  <si>
+    <t>270,5500,2400</t>
+  </si>
+  <si>
+    <t>45,5500,2400</t>
+  </si>
+  <si>
+    <t>120,5500,2400</t>
+  </si>
+  <si>
+    <t>195,5500,2400</t>
+  </si>
+  <si>
+    <t>345,5500,2400</t>
+  </si>
+  <si>
+    <t>30,5500,2400</t>
+  </si>
+  <si>
+    <t>102,6500,2400</t>
+  </si>
+  <si>
+    <t>174,5500,2400</t>
+  </si>
+  <si>
+    <t>246,5500,2400</t>
+  </si>
+  <si>
+    <t>318,5500,2400</t>
+  </si>
+  <si>
+    <t>70,5500,2400</t>
+  </si>
+  <si>
+    <t>142,6500,2400</t>
+  </si>
+  <si>
+    <t>214,5500,2400</t>
+  </si>
+  <si>
+    <t>286,5500,2400</t>
+  </si>
+  <si>
+    <t>358,5500,2400</t>
+  </si>
+  <si>
+    <t>50,5500,2400</t>
+  </si>
+  <si>
+    <t>110,6500,2400</t>
+  </si>
+  <si>
+    <t>170,5500,2400</t>
+  </si>
+  <si>
+    <t>230,5500,2400</t>
+  </si>
+  <si>
+    <t>290,5500,2400</t>
+  </si>
+  <si>
+    <t>350,5500,2400</t>
+  </si>
+  <si>
+    <t>204,5500,2400</t>
+  </si>
+  <si>
+    <t>256,6500,2400</t>
+  </si>
+  <si>
+    <t>308,5500,2400</t>
+  </si>
+  <si>
+    <t>52,5500,2400</t>
+  </si>
+  <si>
+    <t>104,5500,2400</t>
+  </si>
+  <si>
+    <t>156,5500,2400</t>
+  </si>
+  <si>
+    <t>25,5500,2400</t>
+  </si>
+  <si>
+    <t>205,5500,2400</t>
+  </si>
+  <si>
+    <t>250,5500,2400</t>
+  </si>
+  <si>
+    <t>115,6500,2400</t>
+  </si>
+  <si>
+    <t>295,6500,2400</t>
+  </si>
+  <si>
+    <t>160,5500,2400</t>
+  </si>
+  <si>
+    <t>295,5500,2400</t>
+  </si>
+  <si>
+    <t>115,5500,2400</t>
+  </si>
+  <si>
+    <t>340,5500,2400</t>
+  </si>
+  <si>
+    <t>15,5500,2400</t>
+  </si>
+  <si>
+    <t>55,5500,2400</t>
+  </si>
+  <si>
+    <t>235,5500,2400</t>
+  </si>
+  <si>
+    <t>95,5500,2400</t>
+  </si>
+  <si>
+    <t>275,5500,2400</t>
+  </si>
+  <si>
+    <t>135,6500,2400</t>
+  </si>
+  <si>
+    <t>315,6500,2400</t>
+  </si>
+  <si>
+    <t>175,5500,2400</t>
+  </si>
+  <si>
+    <t>355,5500,2400</t>
+  </si>
+  <si>
+    <t>215,5500,2400</t>
+  </si>
+  <si>
+    <t>35,5500,2400</t>
+  </si>
+  <si>
+    <t>255,5500,2400</t>
+  </si>
+  <si>
+    <t>75,5500,2400</t>
+  </si>
+  <si>
+    <t>335,5500,2400</t>
+  </si>
+  <si>
+    <t>155,5500,2400</t>
+  </si>
+  <si>
+    <t>45,6500,2400</t>
+  </si>
+  <si>
+    <t>135,5500,2400</t>
+  </si>
+  <si>
+    <t>180,5500,2400</t>
+  </si>
+  <si>
+    <t>225,6500,2400</t>
+  </si>
+  <si>
+    <t>315,5500,2400</t>
   </si>
 </sst>
 </file>
@@ -93065,7 +93065,7 @@
     </row>
     <row r="1504" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1504" s="1" t="s">
-        <v>1588</v>
+        <v>1530</v>
       </c>
       <c r="B1504" s="1">
         <v>12</v>
@@ -93113,7 +93113,7 @@
         <v>0</v>
       </c>
       <c r="Q1504" s="1" t="s">
-        <v>1589</v>
+        <v>1531</v>
       </c>
       <c r="R1504" s="1">
         <v>0</v>
@@ -93231,7 +93231,7 @@
         <v>0</v>
       </c>
       <c r="Q1506" s="1" t="s">
-        <v>1486</v>
+        <v>1532</v>
       </c>
       <c r="R1506" s="1">
         <v>0</v>
@@ -93290,7 +93290,7 @@
         <v>0</v>
       </c>
       <c r="Q1507" s="1" t="s">
-        <v>1487</v>
+        <v>1533</v>
       </c>
       <c r="R1507" s="1">
         <v>0</v>
@@ -93349,7 +93349,7 @@
         <v>0</v>
       </c>
       <c r="Q1508" s="1" t="s">
-        <v>1488</v>
+        <v>1534</v>
       </c>
       <c r="R1508" s="1">
         <v>0</v>
@@ -93408,7 +93408,7 @@
         <v>0</v>
       </c>
       <c r="Q1509" s="1" t="s">
-        <v>1489</v>
+        <v>1535</v>
       </c>
       <c r="R1509" s="1">
         <v>0</v>
@@ -93467,7 +93467,7 @@
         <v>0</v>
       </c>
       <c r="Q1510" s="1" t="s">
-        <v>1583</v>
+        <v>1536</v>
       </c>
       <c r="R1510" s="1">
         <v>0</v>
@@ -93526,7 +93526,7 @@
         <v>0</v>
       </c>
       <c r="Q1511" s="1" t="s">
-        <v>1549</v>
+        <v>1537</v>
       </c>
       <c r="R1511" s="1">
         <v>0</v>
@@ -93564,7 +93564,7 @@
         <v>3</v>
       </c>
       <c r="J1512" s="2" t="s">
-        <v>1587</v>
+        <v>1529</v>
       </c>
       <c r="K1512" s="1">
         <v>0</v>
@@ -93585,7 +93585,7 @@
         <v>0</v>
       </c>
       <c r="Q1512" s="1" t="s">
-        <v>1488</v>
+        <v>1534</v>
       </c>
       <c r="R1512" s="1">
         <v>0</v>
@@ -93596,7 +93596,7 @@
     </row>
     <row r="1513" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1513" s="1" t="s">
-        <v>1585</v>
+        <v>1528</v>
       </c>
       <c r="B1513" s="1">
         <v>12</v>
@@ -93623,7 +93623,7 @@
         <v>3</v>
       </c>
       <c r="J1513" s="2" t="s">
-        <v>1584</v>
+        <v>1527</v>
       </c>
       <c r="K1513" s="1">
         <v>0</v>
@@ -93644,7 +93644,7 @@
         <v>0</v>
       </c>
       <c r="Q1513" s="1" t="s">
-        <v>1586</v>
+        <v>1538</v>
       </c>
       <c r="R1513" s="1">
         <v>0</v>
@@ -93703,7 +93703,7 @@
         <v>0</v>
       </c>
       <c r="Q1514" s="1" t="s">
-        <v>1492</v>
+        <v>1539</v>
       </c>
       <c r="R1514" s="1">
         <v>0</v>
@@ -93741,7 +93741,7 @@
         <v>4</v>
       </c>
       <c r="J1515" s="2" t="s">
-        <v>1493</v>
+        <v>1486</v>
       </c>
       <c r="K1515" s="1">
         <v>0</v>
@@ -93762,7 +93762,7 @@
         <v>0</v>
       </c>
       <c r="Q1515" s="1" t="s">
-        <v>1494</v>
+        <v>1540</v>
       </c>
       <c r="R1515" s="1">
         <v>0</v>
@@ -93800,7 +93800,7 @@
         <v>4</v>
       </c>
       <c r="J1516" s="2" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
       <c r="K1516" s="1">
         <v>0</v>
@@ -93821,7 +93821,7 @@
         <v>0</v>
       </c>
       <c r="Q1516" s="1" t="s">
-        <v>1496</v>
+        <v>1541</v>
       </c>
       <c r="R1516" s="1">
         <v>0</v>
@@ -93859,7 +93859,7 @@
         <v>4</v>
       </c>
       <c r="J1517" s="2" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
       <c r="K1517" s="1">
         <v>0</v>
@@ -93880,7 +93880,7 @@
         <v>0</v>
       </c>
       <c r="Q1517" s="1" t="s">
-        <v>1497</v>
+        <v>1542</v>
       </c>
       <c r="R1517" s="1">
         <v>0</v>
@@ -93918,7 +93918,7 @@
         <v>4</v>
       </c>
       <c r="J1518" s="2" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
       <c r="K1518" s="1">
         <v>0</v>
@@ -93939,7 +93939,7 @@
         <v>0</v>
       </c>
       <c r="Q1518" s="1" t="s">
-        <v>1498</v>
+        <v>1543</v>
       </c>
       <c r="R1518" s="1">
         <v>0</v>
@@ -93977,7 +93977,7 @@
         <v>5</v>
       </c>
       <c r="J1519" s="2" t="s">
-        <v>1499</v>
+        <v>1488</v>
       </c>
       <c r="K1519" s="1">
         <v>0</v>
@@ -93998,7 +93998,7 @@
         <v>0</v>
       </c>
       <c r="Q1519" s="1" t="s">
-        <v>1500</v>
+        <v>1544</v>
       </c>
       <c r="R1519" s="1">
         <v>0</v>
@@ -94057,7 +94057,7 @@
         <v>0</v>
       </c>
       <c r="Q1520" s="1" t="s">
-        <v>1501</v>
+        <v>1545</v>
       </c>
       <c r="R1520" s="1">
         <v>0</v>
@@ -94116,7 +94116,7 @@
         <v>0</v>
       </c>
       <c r="Q1521" s="1" t="s">
-        <v>1502</v>
+        <v>1546</v>
       </c>
       <c r="R1521" s="1">
         <v>0</v>
@@ -94213,7 +94213,7 @@
         <v>5</v>
       </c>
       <c r="J1523" s="2" t="s">
-        <v>1503</v>
+        <v>1489</v>
       </c>
       <c r="K1523" s="1">
         <v>0</v>
@@ -94234,7 +94234,7 @@
         <v>0</v>
       </c>
       <c r="Q1523" s="1" t="s">
-        <v>1504</v>
+        <v>1547</v>
       </c>
       <c r="R1523" s="1">
         <v>0</v>
@@ -94272,7 +94272,7 @@
         <v>5</v>
       </c>
       <c r="J1524" s="2" t="s">
-        <v>1503</v>
+        <v>1489</v>
       </c>
       <c r="K1524" s="1">
         <v>0</v>
@@ -94293,7 +94293,7 @@
         <v>0</v>
       </c>
       <c r="Q1524" s="1" t="s">
-        <v>1505</v>
+        <v>1548</v>
       </c>
       <c r="R1524" s="1">
         <v>0</v>
@@ -94331,7 +94331,7 @@
         <v>6</v>
       </c>
       <c r="J1525" s="2" t="s">
-        <v>1503</v>
+        <v>1489</v>
       </c>
       <c r="K1525" s="1">
         <v>0</v>
@@ -94352,7 +94352,7 @@
         <v>0</v>
       </c>
       <c r="Q1525" s="1" t="s">
-        <v>1506</v>
+        <v>1549</v>
       </c>
       <c r="R1525" s="1">
         <v>0</v>
@@ -94390,7 +94390,7 @@
         <v>6</v>
       </c>
       <c r="J1526" s="2" t="s">
-        <v>1507</v>
+        <v>1490</v>
       </c>
       <c r="K1526" s="1">
         <v>0</v>
@@ -94411,7 +94411,7 @@
         <v>0</v>
       </c>
       <c r="Q1526" s="1" t="s">
-        <v>1508</v>
+        <v>1550</v>
       </c>
       <c r="R1526" s="1">
         <v>0</v>
@@ -94449,7 +94449,7 @@
         <v>6</v>
       </c>
       <c r="J1527" s="2" t="s">
-        <v>1503</v>
+        <v>1489</v>
       </c>
       <c r="K1527" s="1">
         <v>0</v>
@@ -94470,7 +94470,7 @@
         <v>0</v>
       </c>
       <c r="Q1527" s="1" t="s">
-        <v>1509</v>
+        <v>1551</v>
       </c>
       <c r="R1527" s="1">
         <v>0</v>
@@ -94567,7 +94567,7 @@
         <v>6</v>
       </c>
       <c r="J1529" s="2" t="s">
-        <v>1510</v>
+        <v>1491</v>
       </c>
       <c r="K1529" s="1">
         <v>0</v>
@@ -94588,7 +94588,7 @@
         <v>0</v>
       </c>
       <c r="Q1529" s="1" t="s">
-        <v>1511</v>
+        <v>1552</v>
       </c>
       <c r="R1529" s="1">
         <v>0</v>
@@ -94626,7 +94626,7 @@
         <v>6</v>
       </c>
       <c r="J1530" s="2" t="s">
-        <v>1510</v>
+        <v>1491</v>
       </c>
       <c r="K1530" s="1">
         <v>0</v>
@@ -94647,7 +94647,7 @@
         <v>0</v>
       </c>
       <c r="Q1530" s="1" t="s">
-        <v>1512</v>
+        <v>1553</v>
       </c>
       <c r="R1530" s="1">
         <v>0</v>
@@ -94685,7 +94685,7 @@
         <v>6</v>
       </c>
       <c r="J1531" s="2" t="s">
-        <v>1510</v>
+        <v>1491</v>
       </c>
       <c r="K1531" s="1">
         <v>0</v>
@@ -94706,7 +94706,7 @@
         <v>0</v>
       </c>
       <c r="Q1531" s="1" t="s">
-        <v>1513</v>
+        <v>1554</v>
       </c>
       <c r="R1531" s="1">
         <v>0</v>
@@ -94744,7 +94744,7 @@
         <v>7</v>
       </c>
       <c r="J1532" s="2" t="s">
-        <v>1514</v>
+        <v>1492</v>
       </c>
       <c r="K1532" s="1">
         <v>0</v>
@@ -94765,7 +94765,7 @@
         <v>0</v>
       </c>
       <c r="Q1532" s="1" t="s">
-        <v>1515</v>
+        <v>1555</v>
       </c>
       <c r="R1532" s="1">
         <v>0</v>
@@ -94803,7 +94803,7 @@
         <v>7</v>
       </c>
       <c r="J1533" s="2" t="s">
-        <v>1516</v>
+        <v>1493</v>
       </c>
       <c r="K1533" s="1">
         <v>0</v>
@@ -94824,7 +94824,7 @@
         <v>0</v>
       </c>
       <c r="Q1533" s="1" t="s">
-        <v>1517</v>
+        <v>1556</v>
       </c>
       <c r="R1533" s="1">
         <v>0</v>
@@ -94862,7 +94862,7 @@
         <v>7</v>
       </c>
       <c r="J1534" s="2" t="s">
-        <v>1514</v>
+        <v>1492</v>
       </c>
       <c r="K1534" s="1">
         <v>0</v>
@@ -94883,7 +94883,7 @@
         <v>0</v>
       </c>
       <c r="Q1534" s="1" t="s">
-        <v>1518</v>
+        <v>1557</v>
       </c>
       <c r="R1534" s="1">
         <v>0</v>
@@ -94921,7 +94921,7 @@
         <v>7</v>
       </c>
       <c r="J1535" s="2" t="s">
-        <v>1519</v>
+        <v>1494</v>
       </c>
       <c r="K1535" s="1">
         <v>0</v>
@@ -94942,7 +94942,7 @@
         <v>0</v>
       </c>
       <c r="Q1535" s="1" t="s">
-        <v>1486</v>
+        <v>1532</v>
       </c>
       <c r="R1535" s="1">
         <v>0</v>
@@ -94980,7 +94980,7 @@
         <v>7</v>
       </c>
       <c r="J1536" s="2" t="s">
-        <v>1520</v>
+        <v>1495</v>
       </c>
       <c r="K1536" s="1">
         <v>0</v>
@@ -95001,7 +95001,7 @@
         <v>0</v>
       </c>
       <c r="Q1536" s="1" t="s">
-        <v>1521</v>
+        <v>1558</v>
       </c>
       <c r="R1536" s="1">
         <v>0</v>
@@ -95039,7 +95039,7 @@
         <v>7</v>
       </c>
       <c r="J1537" s="2" t="s">
-        <v>1520</v>
+        <v>1495</v>
       </c>
       <c r="K1537" s="1">
         <v>0</v>
@@ -95060,7 +95060,7 @@
         <v>0</v>
       </c>
       <c r="Q1537" s="1" t="s">
-        <v>1522</v>
+        <v>1559</v>
       </c>
       <c r="R1537" s="1">
         <v>0</v>
@@ -95098,7 +95098,7 @@
         <v>7</v>
       </c>
       <c r="J1538" s="2" t="s">
-        <v>1520</v>
+        <v>1495</v>
       </c>
       <c r="K1538" s="1">
         <v>0</v>
@@ -95119,7 +95119,7 @@
         <v>0</v>
       </c>
       <c r="Q1538" s="1" t="s">
-        <v>1523</v>
+        <v>1560</v>
       </c>
       <c r="R1538" s="1">
         <v>0</v>
@@ -95157,7 +95157,7 @@
         <v>8</v>
       </c>
       <c r="J1539" s="2" t="s">
-        <v>1520</v>
+        <v>1495</v>
       </c>
       <c r="K1539" s="1">
         <v>0</v>
@@ -95178,7 +95178,7 @@
         <v>0</v>
       </c>
       <c r="Q1539" s="1" t="s">
-        <v>1524</v>
+        <v>1561</v>
       </c>
       <c r="R1539" s="1">
         <v>0</v>
@@ -95237,7 +95237,7 @@
         <v>0</v>
       </c>
       <c r="Q1540" s="1" t="s">
-        <v>1525</v>
+        <v>1562</v>
       </c>
       <c r="R1540" s="1">
         <v>0</v>
@@ -95275,7 +95275,7 @@
         <v>8</v>
       </c>
       <c r="J1541" s="2" t="s">
-        <v>1519</v>
+        <v>1494</v>
       </c>
       <c r="K1541" s="1">
         <v>0</v>
@@ -95296,7 +95296,7 @@
         <v>0</v>
       </c>
       <c r="Q1541" s="1" t="s">
-        <v>1500</v>
+        <v>1544</v>
       </c>
       <c r="R1541" s="1">
         <v>0</v>
@@ -95355,7 +95355,7 @@
         <v>0</v>
       </c>
       <c r="Q1542" s="1" t="s">
-        <v>1526</v>
+        <v>1563</v>
       </c>
       <c r="R1542" s="1">
         <v>0</v>
@@ -95393,7 +95393,7 @@
         <v>8</v>
       </c>
       <c r="J1543" s="2" t="s">
-        <v>1527</v>
+        <v>1496</v>
       </c>
       <c r="K1543" s="1">
         <v>0</v>
@@ -95414,7 +95414,7 @@
         <v>0</v>
       </c>
       <c r="Q1543" s="1" t="s">
-        <v>1528</v>
+        <v>1564</v>
       </c>
       <c r="R1543" s="1">
         <v>0</v>
@@ -95473,7 +95473,7 @@
         <v>0</v>
       </c>
       <c r="Q1544" s="1" t="s">
-        <v>1529</v>
+        <v>1565</v>
       </c>
       <c r="R1544" s="1">
         <v>0</v>
@@ -95511,7 +95511,7 @@
         <v>8</v>
       </c>
       <c r="J1545" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1545" s="1">
         <v>0</v>
@@ -95532,7 +95532,7 @@
         <v>0</v>
       </c>
       <c r="Q1545" s="1" t="s">
-        <v>1531</v>
+        <v>1566</v>
       </c>
       <c r="R1545" s="1">
         <v>0</v>
@@ -95570,7 +95570,7 @@
         <v>8</v>
       </c>
       <c r="J1546" s="2" t="s">
-        <v>1532</v>
+        <v>1498</v>
       </c>
       <c r="K1546" s="1">
         <v>0</v>
@@ -95591,7 +95591,7 @@
         <v>0</v>
       </c>
       <c r="Q1546" s="1" t="s">
-        <v>1525</v>
+        <v>1562</v>
       </c>
       <c r="R1546" s="1">
         <v>0</v>
@@ -95602,7 +95602,7 @@
     </row>
     <row r="1547" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1547" s="1" t="s">
-        <v>1533</v>
+        <v>1499</v>
       </c>
       <c r="B1547" s="1">
         <v>12</v>
@@ -95629,7 +95629,7 @@
         <v>8</v>
       </c>
       <c r="J1547" s="2" t="s">
-        <v>1534</v>
+        <v>1500</v>
       </c>
       <c r="K1547" s="1">
         <v>0</v>
@@ -95650,7 +95650,7 @@
         <v>0</v>
       </c>
       <c r="Q1547" s="1" t="s">
-        <v>1524</v>
+        <v>1561</v>
       </c>
       <c r="R1547" s="1">
         <v>0</v>
@@ -95661,7 +95661,7 @@
     </row>
     <row r="1548" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1548" s="1" t="s">
-        <v>1535</v>
+        <v>1501</v>
       </c>
       <c r="B1548" s="1">
         <v>12</v>
@@ -95709,7 +95709,7 @@
         <v>0</v>
       </c>
       <c r="Q1548" s="1" t="s">
-        <v>1525</v>
+        <v>1562</v>
       </c>
       <c r="R1548" s="1">
         <v>0</v>
@@ -95720,7 +95720,7 @@
     </row>
     <row r="1549" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1549" s="1" t="s">
-        <v>1536</v>
+        <v>1502</v>
       </c>
       <c r="B1549" s="1">
         <v>12</v>
@@ -95747,7 +95747,7 @@
         <v>8</v>
       </c>
       <c r="J1549" s="2" t="s">
-        <v>1537</v>
+        <v>1503</v>
       </c>
       <c r="K1549" s="1">
         <v>0</v>
@@ -95768,7 +95768,7 @@
         <v>0</v>
       </c>
       <c r="Q1549" s="1" t="s">
-        <v>1526</v>
+        <v>1563</v>
       </c>
       <c r="R1549" s="1">
         <v>0</v>
@@ -95779,7 +95779,7 @@
     </row>
     <row r="1550" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1550" s="1" t="s">
-        <v>1538</v>
+        <v>1504</v>
       </c>
       <c r="B1550" s="1">
         <v>12</v>
@@ -95806,7 +95806,7 @@
         <v>8</v>
       </c>
       <c r="J1550" s="2" t="s">
-        <v>1532</v>
+        <v>1498</v>
       </c>
       <c r="K1550" s="1">
         <v>0</v>
@@ -95827,7 +95827,7 @@
         <v>0</v>
       </c>
       <c r="Q1550" s="1" t="s">
-        <v>1500</v>
+        <v>1544</v>
       </c>
       <c r="R1550" s="1">
         <v>0</v>
@@ -95838,7 +95838,7 @@
     </row>
     <row r="1551" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1551" s="1" t="s">
-        <v>1539</v>
+        <v>1505</v>
       </c>
       <c r="B1551" s="1">
         <v>12</v>
@@ -95865,7 +95865,7 @@
         <v>8</v>
       </c>
       <c r="J1551" s="2" t="s">
-        <v>1537</v>
+        <v>1503</v>
       </c>
       <c r="K1551" s="1">
         <v>0</v>
@@ -95886,7 +95886,7 @@
         <v>0</v>
       </c>
       <c r="Q1551" s="1" t="s">
-        <v>1540</v>
+        <v>1567</v>
       </c>
       <c r="R1551" s="1">
         <v>0</v>
@@ -95897,7 +95897,7 @@
     </row>
     <row r="1552" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1552" s="1" t="s">
-        <v>1541</v>
+        <v>1506</v>
       </c>
       <c r="B1552" s="1">
         <v>12</v>
@@ -95945,7 +95945,7 @@
         <v>0</v>
       </c>
       <c r="Q1552" s="1" t="s">
-        <v>1542</v>
+        <v>1568</v>
       </c>
       <c r="R1552" s="1">
         <v>0</v>
@@ -95956,7 +95956,7 @@
     </row>
     <row r="1553" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1553" s="1" t="s">
-        <v>1543</v>
+        <v>1507</v>
       </c>
       <c r="B1553" s="1">
         <v>12</v>
@@ -95983,7 +95983,7 @@
         <v>8</v>
       </c>
       <c r="J1553" s="2" t="s">
-        <v>1544</v>
+        <v>1508</v>
       </c>
       <c r="K1553" s="1">
         <v>0</v>
@@ -96004,7 +96004,7 @@
         <v>0</v>
       </c>
       <c r="Q1553" s="1" t="s">
-        <v>1545</v>
+        <v>1569</v>
       </c>
       <c r="R1553" s="1">
         <v>0</v>
@@ -96015,7 +96015,7 @@
     </row>
     <row r="1554" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1554" s="1" t="s">
-        <v>1546</v>
+        <v>1509</v>
       </c>
       <c r="B1554" s="1">
         <v>12</v>
@@ -96042,7 +96042,7 @@
         <v>8</v>
       </c>
       <c r="J1554" s="2" t="s">
-        <v>1532</v>
+        <v>1498</v>
       </c>
       <c r="K1554" s="1">
         <v>0</v>
@@ -96063,7 +96063,7 @@
         <v>0</v>
       </c>
       <c r="Q1554" s="1" t="s">
-        <v>1531</v>
+        <v>1566</v>
       </c>
       <c r="R1554" s="1">
         <v>0</v>
@@ -96101,7 +96101,7 @@
         <v>9</v>
       </c>
       <c r="J1555" s="2" t="s">
-        <v>1547</v>
+        <v>1510</v>
       </c>
       <c r="K1555" s="1">
         <v>0</v>
@@ -96122,7 +96122,7 @@
         <v>0</v>
       </c>
       <c r="Q1555" s="1" t="s">
-        <v>1548</v>
+        <v>1570</v>
       </c>
       <c r="R1555" s="1">
         <v>0</v>
@@ -96160,7 +96160,7 @@
         <v>9</v>
       </c>
       <c r="J1556" s="2" t="s">
-        <v>1547</v>
+        <v>1510</v>
       </c>
       <c r="K1556" s="1">
         <v>0</v>
@@ -96181,7 +96181,7 @@
         <v>0</v>
       </c>
       <c r="Q1556" s="1" t="s">
-        <v>1549</v>
+        <v>1537</v>
       </c>
       <c r="R1556" s="1">
         <v>0</v>
@@ -96219,7 +96219,7 @@
         <v>9</v>
       </c>
       <c r="J1557" s="2" t="s">
-        <v>1550</v>
+        <v>1511</v>
       </c>
       <c r="K1557" s="1">
         <v>0</v>
@@ -96240,7 +96240,7 @@
         <v>0</v>
       </c>
       <c r="Q1557" s="1" t="s">
-        <v>1551</v>
+        <v>1571</v>
       </c>
       <c r="R1557" s="1">
         <v>0</v>
@@ -96278,7 +96278,7 @@
         <v>9</v>
       </c>
       <c r="J1558" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1558" s="1">
         <v>0</v>
@@ -96299,7 +96299,7 @@
         <v>0</v>
       </c>
       <c r="Q1558" s="1" t="s">
-        <v>1552</v>
+        <v>1572</v>
       </c>
       <c r="R1558" s="1">
         <v>0</v>
@@ -96337,7 +96337,7 @@
         <v>9</v>
       </c>
       <c r="J1559" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1559" s="1">
         <v>0</v>
@@ -96358,7 +96358,7 @@
         <v>0</v>
       </c>
       <c r="Q1559" s="1" t="s">
-        <v>1553</v>
+        <v>1573</v>
       </c>
       <c r="R1559" s="1">
         <v>0</v>
@@ -96396,7 +96396,7 @@
         <v>9</v>
       </c>
       <c r="J1560" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1560" s="1">
         <v>0</v>
@@ -96417,7 +96417,7 @@
         <v>0</v>
       </c>
       <c r="Q1560" s="1" t="s">
-        <v>1554</v>
+        <v>1574</v>
       </c>
       <c r="R1560" s="1">
         <v>0</v>
@@ -96455,7 +96455,7 @@
         <v>9</v>
       </c>
       <c r="J1561" s="2" t="s">
-        <v>1555</v>
+        <v>1512</v>
       </c>
       <c r="K1561" s="1">
         <v>0</v>
@@ -96476,7 +96476,7 @@
         <v>0</v>
       </c>
       <c r="Q1561" s="1" t="s">
-        <v>1556</v>
+        <v>1575</v>
       </c>
       <c r="R1561" s="1">
         <v>0</v>
@@ -96514,7 +96514,7 @@
         <v>9</v>
       </c>
       <c r="J1562" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1562" s="1">
         <v>0</v>
@@ -96535,7 +96535,7 @@
         <v>0</v>
       </c>
       <c r="Q1562" s="1" t="s">
-        <v>1557</v>
+        <v>1576</v>
       </c>
       <c r="R1562" s="1">
         <v>0</v>
@@ -96573,7 +96573,7 @@
         <v>9</v>
       </c>
       <c r="J1563" s="2" t="s">
-        <v>1558</v>
+        <v>1513</v>
       </c>
       <c r="K1563" s="1">
         <v>0</v>
@@ -96594,7 +96594,7 @@
         <v>0</v>
       </c>
       <c r="Q1563" s="1" t="s">
-        <v>1559</v>
+        <v>1577</v>
       </c>
       <c r="R1563" s="1">
         <v>0</v>
@@ -96605,7 +96605,7 @@
     </row>
     <row r="1564" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1564" s="1" t="s">
-        <v>1560</v>
+        <v>1514</v>
       </c>
       <c r="B1564" s="1">
         <v>12</v>
@@ -96632,7 +96632,7 @@
         <v>9</v>
       </c>
       <c r="J1564" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1564" s="1">
         <v>0</v>
@@ -96653,7 +96653,7 @@
         <v>0</v>
       </c>
       <c r="Q1564" s="1" t="s">
-        <v>1561</v>
+        <v>1578</v>
       </c>
       <c r="R1564" s="1">
         <v>0</v>
@@ -96664,7 +96664,7 @@
     </row>
     <row r="1565" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1565" s="1" t="s">
-        <v>1562</v>
+        <v>1515</v>
       </c>
       <c r="B1565" s="1">
         <v>12</v>
@@ -96691,7 +96691,7 @@
         <v>9</v>
       </c>
       <c r="J1565" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1565" s="1">
         <v>0</v>
@@ -96712,7 +96712,7 @@
         <v>0</v>
       </c>
       <c r="Q1565" s="1" t="s">
-        <v>1563</v>
+        <v>1579</v>
       </c>
       <c r="R1565" s="1">
         <v>0</v>
@@ -96723,7 +96723,7 @@
     </row>
     <row r="1566" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1566" s="1" t="s">
-        <v>1564</v>
+        <v>1516</v>
       </c>
       <c r="B1566" s="1">
         <v>12</v>
@@ -96750,7 +96750,7 @@
         <v>9</v>
       </c>
       <c r="J1566" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1566" s="1">
         <v>0</v>
@@ -96771,7 +96771,7 @@
         <v>0</v>
       </c>
       <c r="Q1566" s="1" t="s">
-        <v>1565</v>
+        <v>1580</v>
       </c>
       <c r="R1566" s="1">
         <v>0</v>
@@ -96782,7 +96782,7 @@
     </row>
     <row r="1567" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1567" s="1" t="s">
-        <v>1566</v>
+        <v>1517</v>
       </c>
       <c r="B1567" s="1">
         <v>12</v>
@@ -96809,7 +96809,7 @@
         <v>9</v>
       </c>
       <c r="J1567" s="2" t="s">
-        <v>1558</v>
+        <v>1513</v>
       </c>
       <c r="K1567" s="1">
         <v>0</v>
@@ -96830,7 +96830,7 @@
         <v>0</v>
       </c>
       <c r="Q1567" s="1" t="s">
-        <v>1567</v>
+        <v>1581</v>
       </c>
       <c r="R1567" s="1">
         <v>0</v>
@@ -96841,7 +96841,7 @@
     </row>
     <row r="1568" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1568" s="1" t="s">
-        <v>1568</v>
+        <v>1518</v>
       </c>
       <c r="B1568" s="1">
         <v>12</v>
@@ -96868,7 +96868,7 @@
         <v>9</v>
       </c>
       <c r="J1568" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1568" s="1">
         <v>0</v>
@@ -96889,7 +96889,7 @@
         <v>0</v>
       </c>
       <c r="Q1568" s="1" t="s">
-        <v>1569</v>
+        <v>1582</v>
       </c>
       <c r="R1568" s="1">
         <v>0</v>
@@ -96900,7 +96900,7 @@
     </row>
     <row r="1569" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1569" s="1" t="s">
-        <v>1570</v>
+        <v>1519</v>
       </c>
       <c r="B1569" s="1">
         <v>12</v>
@@ -96927,7 +96927,7 @@
         <v>9</v>
       </c>
       <c r="J1569" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1569" s="1">
         <v>0</v>
@@ -96948,7 +96948,7 @@
         <v>0</v>
       </c>
       <c r="Q1569" s="1" t="s">
-        <v>1540</v>
+        <v>1567</v>
       </c>
       <c r="R1569" s="1">
         <v>0</v>
@@ -96959,7 +96959,7 @@
     </row>
     <row r="1570" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1570" s="1" t="s">
-        <v>1571</v>
+        <v>1520</v>
       </c>
       <c r="B1570" s="1">
         <v>12</v>
@@ -96986,7 +96986,7 @@
         <v>9</v>
       </c>
       <c r="J1570" s="2" t="s">
-        <v>1530</v>
+        <v>1497</v>
       </c>
       <c r="K1570" s="1">
         <v>0</v>
@@ -97007,7 +97007,7 @@
         <v>0</v>
       </c>
       <c r="Q1570" s="1" t="s">
-        <v>1542</v>
+        <v>1568</v>
       </c>
       <c r="R1570" s="1">
         <v>0</v>
@@ -97018,7 +97018,7 @@
     </row>
     <row r="1571" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1571" s="1" t="s">
-        <v>1572</v>
+        <v>1521</v>
       </c>
       <c r="B1571" s="1">
         <v>12</v>
@@ -97045,7 +97045,7 @@
         <v>9</v>
       </c>
       <c r="J1571" s="2" t="s">
-        <v>1573</v>
+        <v>1522</v>
       </c>
       <c r="K1571" s="1">
         <v>0</v>
@@ -97066,7 +97066,7 @@
         <v>0</v>
       </c>
       <c r="Q1571" s="1" t="s">
-        <v>1574</v>
+        <v>1583</v>
       </c>
       <c r="R1571" s="1">
         <v>0</v>
@@ -97077,7 +97077,7 @@
     </row>
     <row r="1572" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1572" s="1" t="s">
-        <v>1575</v>
+        <v>1523</v>
       </c>
       <c r="B1572" s="1">
         <v>12</v>
@@ -97104,7 +97104,7 @@
         <v>9</v>
       </c>
       <c r="J1572" s="2" t="s">
-        <v>1547</v>
+        <v>1510</v>
       </c>
       <c r="K1572" s="1">
         <v>0</v>
@@ -97125,7 +97125,7 @@
         <v>0</v>
       </c>
       <c r="Q1572" s="1" t="s">
-        <v>1576</v>
+        <v>1584</v>
       </c>
       <c r="R1572" s="1">
         <v>0</v>
@@ -97222,7 +97222,7 @@
         <v>10</v>
       </c>
       <c r="J1574" s="2" t="s">
-        <v>1577</v>
+        <v>1524</v>
       </c>
       <c r="K1574" s="1">
         <v>0</v>
@@ -97281,7 +97281,7 @@
         <v>10</v>
       </c>
       <c r="J1575" s="2" t="s">
-        <v>1577</v>
+        <v>1524</v>
       </c>
       <c r="K1575" s="1">
         <v>0</v>
@@ -97302,7 +97302,7 @@
         <v>0</v>
       </c>
       <c r="Q1575" s="1" t="s">
-        <v>1486</v>
+        <v>1532</v>
       </c>
       <c r="R1575" s="1">
         <v>0</v>
@@ -97340,7 +97340,7 @@
         <v>10</v>
       </c>
       <c r="J1576" s="2" t="s">
-        <v>1578</v>
+        <v>1525</v>
       </c>
       <c r="K1576" s="1">
         <v>0</v>
@@ -97361,7 +97361,7 @@
         <v>0</v>
       </c>
       <c r="Q1576" s="1" t="s">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="R1576" s="1">
         <v>0</v>
@@ -97399,7 +97399,7 @@
         <v>10</v>
       </c>
       <c r="J1577" s="2" t="s">
-        <v>1577</v>
+        <v>1524</v>
       </c>
       <c r="K1577" s="1">
         <v>0</v>
@@ -97420,7 +97420,7 @@
         <v>0</v>
       </c>
       <c r="Q1577" s="1" t="s">
-        <v>1487</v>
+        <v>1533</v>
       </c>
       <c r="R1577" s="1">
         <v>0</v>
@@ -97458,7 +97458,7 @@
         <v>10</v>
       </c>
       <c r="J1578" s="2" t="s">
-        <v>1580</v>
+        <v>1526</v>
       </c>
       <c r="K1578" s="1">
         <v>0</v>
@@ -97479,7 +97479,7 @@
         <v>0</v>
       </c>
       <c r="Q1578" s="1" t="s">
-        <v>1490</v>
+        <v>1586</v>
       </c>
       <c r="R1578" s="1">
         <v>0</v>
@@ -97517,7 +97517,7 @@
         <v>10</v>
       </c>
       <c r="J1579" s="2" t="s">
-        <v>1577</v>
+        <v>1524</v>
       </c>
       <c r="K1579" s="1">
         <v>0</v>
@@ -97538,7 +97538,7 @@
         <v>0</v>
       </c>
       <c r="Q1579" s="1" t="s">
-        <v>1581</v>
+        <v>1587</v>
       </c>
       <c r="R1579" s="1">
         <v>0</v>
@@ -97576,7 +97576,7 @@
         <v>10</v>
       </c>
       <c r="J1580" s="2" t="s">
-        <v>1578</v>
+        <v>1525</v>
       </c>
       <c r="K1580" s="1">
         <v>0</v>
@@ -97597,7 +97597,7 @@
         <v>0</v>
       </c>
       <c r="Q1580" s="1" t="s">
-        <v>1582</v>
+        <v>1588</v>
       </c>
       <c r="R1580" s="1">
         <v>0</v>
@@ -97635,7 +97635,7 @@
         <v>10</v>
       </c>
       <c r="J1581" s="2" t="s">
-        <v>1577</v>
+        <v>1524</v>
       </c>
       <c r="K1581" s="1">
         <v>0</v>
@@ -97656,7 +97656,7 @@
         <v>0</v>
       </c>
       <c r="Q1581" s="1" t="s">
-        <v>1488</v>
+        <v>1534</v>
       </c>
       <c r="R1581" s="1">
         <v>0</v>
@@ -97694,7 +97694,7 @@
         <v>10</v>
       </c>
       <c r="J1582" s="2" t="s">
-        <v>1577</v>
+        <v>1524</v>
       </c>
       <c r="K1582" s="1">
         <v>0</v>
@@ -97715,7 +97715,7 @@
         <v>0</v>
       </c>
       <c r="Q1582" s="1" t="s">
-        <v>1491</v>
+        <v>1589</v>
       </c>
       <c r="R1582" s="1">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA155AEC-7CE1-449C-9D28-1ADBE4CB598B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04F0789-48EC-447F-95B6-3D4F1052ADB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4740,181 +4740,181 @@
     <t>1210104</t>
   </si>
   <si>
-    <t>0,4000,1600</t>
-  </si>
-  <si>
-    <t>0,5500,2400</t>
-  </si>
-  <si>
-    <t>90,5500,2400</t>
-  </si>
-  <si>
-    <t>270,5500,2400</t>
-  </si>
-  <si>
-    <t>45,5500,2400</t>
-  </si>
-  <si>
-    <t>120,5500,2400</t>
-  </si>
-  <si>
-    <t>195,5500,2400</t>
-  </si>
-  <si>
-    <t>345,5500,2400</t>
-  </si>
-  <si>
-    <t>30,5500,2400</t>
-  </si>
-  <si>
-    <t>102,6500,2400</t>
-  </si>
-  <si>
-    <t>174,5500,2400</t>
-  </si>
-  <si>
-    <t>246,5500,2400</t>
-  </si>
-  <si>
-    <t>318,5500,2400</t>
-  </si>
-  <si>
-    <t>70,5500,2400</t>
-  </si>
-  <si>
-    <t>142,6500,2400</t>
-  </si>
-  <si>
-    <t>214,5500,2400</t>
-  </si>
-  <si>
-    <t>286,5500,2400</t>
-  </si>
-  <si>
-    <t>358,5500,2400</t>
-  </si>
-  <si>
-    <t>50,5500,2400</t>
-  </si>
-  <si>
-    <t>110,6500,2400</t>
-  </si>
-  <si>
-    <t>170,5500,2400</t>
-  </si>
-  <si>
-    <t>230,5500,2400</t>
-  </si>
-  <si>
-    <t>290,5500,2400</t>
-  </si>
-  <si>
-    <t>350,5500,2400</t>
-  </si>
-  <si>
-    <t>204,5500,2400</t>
-  </si>
-  <si>
-    <t>256,6500,2400</t>
-  </si>
-  <si>
-    <t>308,5500,2400</t>
-  </si>
-  <si>
-    <t>52,5500,2400</t>
-  </si>
-  <si>
-    <t>104,5500,2400</t>
-  </si>
-  <si>
-    <t>156,5500,2400</t>
-  </si>
-  <si>
-    <t>25,5500,2400</t>
-  </si>
-  <si>
-    <t>205,5500,2400</t>
-  </si>
-  <si>
-    <t>250,5500,2400</t>
-  </si>
-  <si>
     <t>115,6500,2400</t>
   </si>
   <si>
     <t>295,6500,2400</t>
   </si>
   <si>
-    <t>160,5500,2400</t>
-  </si>
-  <si>
-    <t>295,5500,2400</t>
-  </si>
-  <si>
-    <t>115,5500,2400</t>
-  </si>
-  <si>
-    <t>340,5500,2400</t>
-  </si>
-  <si>
-    <t>15,5500,2400</t>
-  </si>
-  <si>
-    <t>55,5500,2400</t>
-  </si>
-  <si>
-    <t>235,5500,2400</t>
-  </si>
-  <si>
-    <t>95,5500,2400</t>
-  </si>
-  <si>
-    <t>275,5500,2400</t>
-  </si>
-  <si>
     <t>135,6500,2400</t>
   </si>
   <si>
     <t>315,6500,2400</t>
   </si>
   <si>
-    <t>175,5500,2400</t>
-  </si>
-  <si>
-    <t>355,5500,2400</t>
-  </si>
-  <si>
-    <t>215,5500,2400</t>
-  </si>
-  <si>
-    <t>35,5500,2400</t>
-  </si>
-  <si>
-    <t>255,5500,2400</t>
-  </si>
-  <si>
-    <t>75,5500,2400</t>
-  </si>
-  <si>
-    <t>335,5500,2400</t>
-  </si>
-  <si>
-    <t>155,5500,2400</t>
-  </si>
-  <si>
     <t>45,6500,2400</t>
   </si>
   <si>
-    <t>135,5500,2400</t>
-  </si>
-  <si>
-    <t>180,5500,2400</t>
-  </si>
-  <si>
-    <t>225,6500,2400</t>
-  </si>
-  <si>
-    <t>315,5500,2400</t>
+    <t>0,4500,1600</t>
+  </si>
+  <si>
+    <t>0,6500,2400</t>
+  </si>
+  <si>
+    <t>90,6500,2400</t>
+  </si>
+  <si>
+    <t>270,6500,2400</t>
+  </si>
+  <si>
+    <t>120,6500,2400</t>
+  </si>
+  <si>
+    <t>195,6500,2400</t>
+  </si>
+  <si>
+    <t>345,6500,2400</t>
+  </si>
+  <si>
+    <t>30,6500,2400</t>
+  </si>
+  <si>
+    <t>102,7500,2400</t>
+  </si>
+  <si>
+    <t>174,6500,2400</t>
+  </si>
+  <si>
+    <t>246,6500,2400</t>
+  </si>
+  <si>
+    <t>318,6500,2400</t>
+  </si>
+  <si>
+    <t>70,6500,2400</t>
+  </si>
+  <si>
+    <t>142,7500,2400</t>
+  </si>
+  <si>
+    <t>214,6500,2400</t>
+  </si>
+  <si>
+    <t>286,6500,2400</t>
+  </si>
+  <si>
+    <t>358,6500,2400</t>
+  </si>
+  <si>
+    <t>50,6500,2400</t>
+  </si>
+  <si>
+    <t>110,7500,2400</t>
+  </si>
+  <si>
+    <t>170,6500,2400</t>
+  </si>
+  <si>
+    <t>230,6500,2400</t>
+  </si>
+  <si>
+    <t>290,6500,2400</t>
+  </si>
+  <si>
+    <t>350,6500,2400</t>
+  </si>
+  <si>
+    <t>204,6500,2400</t>
+  </si>
+  <si>
+    <t>256,7500,2400</t>
+  </si>
+  <si>
+    <t>308,6500,2400</t>
+  </si>
+  <si